--- a/docs/avances/Avances_Green_Alliance.xlsx
+++ b/docs/avances/Avances_Green_Alliance.xlsx
@@ -17,8 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bitácora" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$4:$R$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$4:$R$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="C9" s="9">
-        <f>COUNTA(Plan!$A$5:$A$46)</f>
+        <f>COUNTA(Plan!$A$5:$A$51)</f>
         <v/>
       </c>
     </row>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>COUNTIF(Plan!$O$5:$O$46,"Hecho")</f>
+        <f>COUNTIF(Plan!$O$5:$O$51,"Hecho")</f>
         <v/>
       </c>
     </row>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="C11" s="9">
-        <f>COUNTIF(Plan!$O$5:$O$46,"En curso")</f>
+        <f>COUNTIF(Plan!$O$5:$O$51,"En curso")</f>
         <v/>
       </c>
     </row>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="C12" s="9">
-        <f>COUNTIF(Plan!$O$5:$O$46,"Pendiente")</f>
+        <f>COUNTIF(Plan!$O$5:$O$51,"Pendiente")</f>
         <v/>
       </c>
     </row>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C13" s="9">
-        <f>COUNTIF(Plan!$O$5:$O$46,"Bloqueado")</f>
+        <f>COUNTIF(Plan!$O$5:$O$51,"Bloqueado")</f>
         <v/>
       </c>
     </row>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="C14" s="9">
-        <f>SUM(Plan!$D$5:$D$46)</f>
+        <f>SUM(Plan!$D$5:$D$51)</f>
         <v/>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="C15" s="9">
-        <f>SUMIF(Plan!$O$5:$O$46,"Hecho",Plan!$D$5:$D$46)</f>
+        <f>SUMIF(Plan!$O$5:$O$51,"Hecho",Plan!$D$5:$D$51)</f>
         <v/>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C17" s="9">
-        <f>MAX(Plan!$L$5:$L$46)</f>
+        <f>MAX(Plan!$L$5:$L$51)</f>
         <v/>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C23" s="12">
-        <f>IF(C17=0,0,(SUMIF(Plan!$I$5:$I$46,"A",Plan!$E$5:$E$46)+SUMIF(Plan!$I$5:$I$46,"A+B",Plan!$E$5:$E$46))/C17)</f>
+        <f>IF(C17=0,0,(SUMIF(Plan!$I$5:$I$51,"A",Plan!$E$5:$E$51)+SUMIF(Plan!$I$5:$I$51,"A+B",Plan!$E$5:$E$51))/C17)</f>
         <v/>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="C24" s="12">
-        <f>IF(C17=0,0,(SUMIF(Plan!$I$5:$I$46,"B",Plan!$E$5:$E$46)+SUMIF(Plan!$I$5:$I$46,"A+B",Plan!$E$5:$E$46))/C17)</f>
+        <f>IF(C17=0,0,(SUMIF(Plan!$I$5:$I$51,"B",Plan!$E$5:$E$51)+SUMIF(Plan!$I$5:$I$51,"A+B",Plan!$E$5:$E$51))/C17)</f>
         <v/>
       </c>
     </row>
@@ -1093,11 +1093,11 @@
         </is>
       </c>
       <c r="C29" s="15">
-        <f>SUMIF(Plan!$B$5:$B$46,"1. Diseño y arquitectura",Plan!$D$5:$D$46)</f>
+        <f>SUMIF(Plan!$B$5:$B$51,"1. Diseño y arquitectura",Plan!$D$5:$D$51)</f>
         <v/>
       </c>
       <c r="D29" s="15">
-        <f>SUMIFS(Plan!$D$5:$D$46,Plan!$B$5:$B$46,"1. Diseño y arquitectura",Plan!$O$5:$O$46,"Hecho")</f>
+        <f>SUMIFS(Plan!$D$5:$D$51,Plan!$B$5:$B$51,"1. Diseño y arquitectura",Plan!$O$5:$O$51,"Hecho")</f>
         <v/>
       </c>
       <c r="E29" s="12">
@@ -1105,7 +1105,7 @@
         <v/>
       </c>
       <c r="F29" s="15">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="1. Diseño y arquitectura")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="1. Diseño y arquitectura")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G29" s="8">
@@ -1124,11 +1124,11 @@
         </is>
       </c>
       <c r="C30" s="15">
-        <f>SUMIF(Plan!$B$5:$B$46,"2. Landing y autenticación",Plan!$D$5:$D$46)</f>
+        <f>SUMIF(Plan!$B$5:$B$51,"2. Landing y autenticación",Plan!$D$5:$D$51)</f>
         <v/>
       </c>
       <c r="D30" s="15">
-        <f>SUMIFS(Plan!$D$5:$D$46,Plan!$B$5:$B$46,"2. Landing y autenticación",Plan!$O$5:$O$46,"Hecho")</f>
+        <f>SUMIFS(Plan!$D$5:$D$51,Plan!$B$5:$B$51,"2. Landing y autenticación",Plan!$O$5:$O$51,"Hecho")</f>
         <v/>
       </c>
       <c r="E30" s="12">
@@ -1136,7 +1136,7 @@
         <v/>
       </c>
       <c r="F30" s="15">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="2. Landing y autenticación")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="2. Landing y autenticación")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G30" s="8">
@@ -1155,11 +1155,11 @@
         </is>
       </c>
       <c r="C31" s="15">
-        <f>SUMIF(Plan!$B$5:$B$46,"3. Flujo de solicitud de crédito",Plan!$D$5:$D$46)</f>
+        <f>SUMIF(Plan!$B$5:$B$51,"3. Flujo de solicitud de crédito",Plan!$D$5:$D$51)</f>
         <v/>
       </c>
       <c r="D31" s="15">
-        <f>SUMIFS(Plan!$D$5:$D$46,Plan!$B$5:$B$46,"3. Flujo de solicitud de crédito",Plan!$O$5:$O$46,"Hecho")</f>
+        <f>SUMIFS(Plan!$D$5:$D$51,Plan!$B$5:$B$51,"3. Flujo de solicitud de crédito",Plan!$O$5:$O$51,"Hecho")</f>
         <v/>
       </c>
       <c r="E31" s="12">
@@ -1167,7 +1167,7 @@
         <v/>
       </c>
       <c r="F31" s="15">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="3. Flujo de solicitud de crédito")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="3. Flujo de solicitud de crédito")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G31" s="8">
@@ -1186,11 +1186,11 @@
         </is>
       </c>
       <c r="C32" s="15">
-        <f>SUMIF(Plan!$B$5:$B$46,"4. Panel de administración",Plan!$D$5:$D$46)</f>
+        <f>SUMIF(Plan!$B$5:$B$51,"4. Panel de administración",Plan!$D$5:$D$51)</f>
         <v/>
       </c>
       <c r="D32" s="15">
-        <f>SUMIFS(Plan!$D$5:$D$46,Plan!$B$5:$B$46,"4. Panel de administración",Plan!$O$5:$O$46,"Hecho")</f>
+        <f>SUMIFS(Plan!$D$5:$D$51,Plan!$B$5:$B$51,"4. Panel de administración",Plan!$O$5:$O$51,"Hecho")</f>
         <v/>
       </c>
       <c r="E32" s="12">
@@ -1198,7 +1198,7 @@
         <v/>
       </c>
       <c r="F32" s="15">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="4. Panel de administración")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="4. Panel de administración")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G32" s="8">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="C33" s="15">
-        <f>SUMIF(Plan!$B$5:$B$46,"5. Convenios y pulido",Plan!$D$5:$D$46)</f>
+        <f>SUMIF(Plan!$B$5:$B$51,"5. Convenios y pulido",Plan!$D$5:$D$51)</f>
         <v/>
       </c>
       <c r="D33" s="15">
-        <f>SUMIFS(Plan!$D$5:$D$46,Plan!$B$5:$B$46,"5. Convenios y pulido",Plan!$O$5:$O$46,"Hecho")</f>
+        <f>SUMIFS(Plan!$D$5:$D$51,Plan!$B$5:$B$51,"5. Convenios y pulido",Plan!$O$5:$O$51,"Hecho")</f>
         <v/>
       </c>
       <c r="E33" s="12">
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="F33" s="15">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="5. Convenios y pulido")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="5. Convenios y pulido")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G33" s="8">
@@ -1248,11 +1248,11 @@
         </is>
       </c>
       <c r="C34" s="15">
-        <f>SUMIF(Plan!$B$5:$B$46,"6. Pruebas y lanzamiento",Plan!$D$5:$D$46)</f>
+        <f>SUMIF(Plan!$B$5:$B$51,"6. Pruebas y lanzamiento",Plan!$D$5:$D$51)</f>
         <v/>
       </c>
       <c r="D34" s="15">
-        <f>SUMIFS(Plan!$D$5:$D$46,Plan!$B$5:$B$46,"6. Pruebas y lanzamiento",Plan!$O$5:$O$46,"Hecho")</f>
+        <f>SUMIFS(Plan!$D$5:$D$51,Plan!$B$5:$B$51,"6. Pruebas y lanzamiento",Plan!$O$5:$O$51,"Hecho")</f>
         <v/>
       </c>
       <c r="E34" s="12">
@@ -1260,7 +1260,7 @@
         <v/>
       </c>
       <c r="F34" s="15">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="6. Pruebas y lanzamiento")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="6. Pruebas y lanzamiento")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G34" s="8">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B46,Pendientes!$G$5:$G$55,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B46,Pendientes!$G$5:$G$60,"Hecho")</f>
         <v/>
       </c>
       <c r="D46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B46,Pendientes!$G$5:$G$55,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B46,Pendientes!$G$5:$G$60,"En curso")</f>
         <v/>
       </c>
       <c r="E46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B46,Pendientes!$G$5:$G$55,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B46,Pendientes!$G$5:$G$60,"Pendiente")</f>
         <v/>
       </c>
       <c r="F46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B46,Pendientes!$G$5:$G$55,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B46,Pendientes!$G$5:$G$60,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G46" s="9">
@@ -1522,19 +1522,19 @@
         </is>
       </c>
       <c r="C47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B47,Pendientes!$G$5:$G$55,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B47,Pendientes!$G$5:$G$60,"Hecho")</f>
         <v/>
       </c>
       <c r="D47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B47,Pendientes!$G$5:$G$55,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B47,Pendientes!$G$5:$G$60,"En curso")</f>
         <v/>
       </c>
       <c r="E47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B47,Pendientes!$G$5:$G$55,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B47,Pendientes!$G$5:$G$60,"Pendiente")</f>
         <v/>
       </c>
       <c r="F47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B47,Pendientes!$G$5:$G$55,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B47,Pendientes!$G$5:$G$60,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G47" s="9">
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B48,Pendientes!$G$5:$G$55,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B48,Pendientes!$G$5:$G$60,"Hecho")</f>
         <v/>
       </c>
       <c r="D48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B48,Pendientes!$G$5:$G$55,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B48,Pendientes!$G$5:$G$60,"En curso")</f>
         <v/>
       </c>
       <c r="E48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B48,Pendientes!$G$5:$G$55,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B48,Pendientes!$G$5:$G$60,"Pendiente")</f>
         <v/>
       </c>
       <c r="F48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B48,Pendientes!$G$5:$G$55,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B48,Pendientes!$G$5:$G$60,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G48" s="9">
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B49,Pendientes!$G$5:$G$55,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B49,Pendientes!$G$5:$G$60,"Hecho")</f>
         <v/>
       </c>
       <c r="D49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B49,Pendientes!$G$5:$G$55,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B49,Pendientes!$G$5:$G$60,"En curso")</f>
         <v/>
       </c>
       <c r="E49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B49,Pendientes!$G$5:$G$55,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B49,Pendientes!$G$5:$G$60,"Pendiente")</f>
         <v/>
       </c>
       <c r="F49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B49,Pendientes!$G$5:$G$55,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B49,Pendientes!$G$5:$G$60,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G49" s="9">
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B50,Pendientes!$G$5:$G$55,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B50,Pendientes!$G$5:$G$60,"Hecho")</f>
         <v/>
       </c>
       <c r="D50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B50,Pendientes!$G$5:$G$55,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B50,Pendientes!$G$5:$G$60,"En curso")</f>
         <v/>
       </c>
       <c r="E50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B50,Pendientes!$G$5:$G$55,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B50,Pendientes!$G$5:$G$60,"Pendiente")</f>
         <v/>
       </c>
       <c r="F50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$55,$B50,Pendientes!$G$5:$G$55,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$60,$B50,Pendientes!$G$5:$G$60,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G50" s="9">
@@ -1639,7 +1639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="I5" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H5,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H5,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1813,12 +1813,12 @@
         </is>
       </c>
       <c r="I6" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H6,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H6,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Crea la tabla limites_intentos y la función registrar_intento, que usan /afiliacion, /ingresar y «Reenviar código» (dentroDelLimite). Sin ella esos límites fallan en producción. Antes del despliegue (6.5).</t>
+          <t>Crea la tabla limites_intentos y la función registrar_intento, que usan /afiliacion, /ingresar y «Reenviar código» (dentroDelLimite). Sin ella esos límites fallan en producción. Antes del despliegue (6.5). 23-sep: auditada por ga-auditor-supabase, se puede aplicar tal cual (docs/auditorias/2026-09-23-limite-de-intentos.md); falta que Sebas haga db push.</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Variables: SUPABASE_SERVICE_ROLE_KEY, INGRESO_COOKIE_SECRET, RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_INGRESO_ACEPTADO, RESEND_TEMPLATE_CREDITO_APROBADO, RESEND_TEMPLATE_CREDITO_RECHAZADO, NEXT_PUBLIC_WHATSAPP</t>
+          <t>Variables: SUPABASE_SERVICE_ROLE_KEY, INGRESO_COOKIE_SECRET, LIMITE_HMAC_SECRET, RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_INGRESO_ACEPTADO, RESEND_TEMPLATE_CREDITO_APROBADO, RESEND_TEMPLATE_CREDITO_RECHAZADO, NEXT_PUBLIC_WHATSAPP</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1864,12 +1864,12 @@
         </is>
       </c>
       <c r="I7" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H7,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H7,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>NEXT_PUBLIC_WHATSAPP espera el número de la cooperativa (P-10).</t>
+          <t>NEXT_PUBLIC_WHATSAPP espera el número de la cooperativa (P-10). LIMITE_HMAC_SECRET: 32+ caracteres, distinto de INGRESO_COOKIE_SECRET, en Production y Preview (sin él el build falla); también en .env.local para `npm start`.</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="I8" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H8,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H8,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="I9" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H9,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H9,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J9" s="7" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1984,119 +1984,119 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>SMTP propio con Resend (Authentication → Emails → SMTP Settings)</t>
+          <t>Alerta en los logs de Vercel para limite_de_intentos_fallo y limite_secreto_faltante</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Yo (panel Supabase/Resend)</t>
+          <t>Yo (panel Vercel)</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="I10" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H10,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H10,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Configurado por Sebas el 23-sep. El código de 6 dígitos lo envía Supabase Auth (no Resend desde la app); funciona en local. Ver docs/resend-plantillas.md.</t>
+          <t>Sugerido por ga-auditor-supabase en la auditoría de P-43.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-55</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Funcionalidad</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Asociados</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Importación de asociados desde Excel</t>
+          <t>Opcional: revocar la secuencia limites_intentos_id_seq a anon y authenticated</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Yo + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="I11" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H11,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H11,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Espera el Excel de la cooperativa (P-18).</t>
+          <t>Sugerido por ga-auditor-supabase en la auditoría de P-43.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Funcionalidad</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Panel /admin: listado, aprobar y rechazar con motivo</t>
+          <t>SMTP propio con Resend (Authentication → Emails → SMTP Settings)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Yo (panel Supabase/Resend)</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2106,28 +2106,28 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I12" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H12,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H12,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Un admin no puede resolver su propia solicitud. Mientras no exista, el equipo revisa solicitudes y afiliaciones nuevas directamente en Supabase (ya no hay correos de aviso).</t>
+          <t>Configurado por Sebas el 23-sep. El código de 6 dígitos lo envía Supabase Auth (no Resend desde la app); funciona en local. Ver docs/resend-plantillas.md.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>P-37</t>
+          <t>P-38</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Correos</t>
+          <t>Asociados</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Correo «Resultado del crédito» (aprobado / no aprobado) al asociado al resolver una solicitud</t>
+          <t>Importación de asociados desde Excel</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -2157,28 +2157,28 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Bloqueado</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I13" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H13,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H13,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>enviarResultadoCredito ya existe pero no está conectado: falta la pantalla de admin para aprobar o rechazar (4.2). Ya no hay correo al crear la solicitud (quitado el 23-sep).</t>
+          <t>Espera el Excel de la cooperativa (P-18).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-36</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Correos</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Correo «Ingreso aceptado» (plantilla ga-ingreso-aceptado): acción del admin que aprueba la afiliación, crea el usuario y envía el correo</t>
+          <t>Panel /admin: listado, aprobar y rechazar con motivo</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -2213,23 +2213,23 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I14" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H14,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H14,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>No implementado en la app. Requiere RESEND_TEMPLATE_INGRESO_ACEPTADO (P-44). Ver docs/resend-plantillas.md.</t>
+          <t>Un admin no puede resolver su propia solicitud. Mientras no exista, el equipo revisa solicitudes y afiliaciones nuevas directamente en Supabase (ya no hay correos de aviso).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-37</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>F-01: el select «Grado» se vacía tras un error de validación</t>
+          <t>Correo «Resultado del crédito» (aprobado / no aprobado) al asociado al resolver una solicitud</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2264,23 +2264,23 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I15" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H15,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H15,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Falla media de la verificación QA 1 (docs/verificaciones/2026-09-23-verificacion-1.md).</t>
+          <t>enviarResultadoCredito ya existe pero no está conectado: falta la pantalla de admin para aprobar o rechazar (4.2). Ya no hay correo al crear la solicitud (quitado el 23-sep).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-51</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Server Action: correo_por_cedula(), signInWithOtp, cookie firmada, ir a /ingresar/codigo</t>
+          <t>Correo «Ingreso aceptado» (plantilla ga-ingreso-aceptado): acción del admin que aprueba la afiliación, crea el usuario y envía el correo</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -2310,24 +2310,28 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I16" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H16,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J16" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H16,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>No implementado en la app. Requiere RESEND_TEMPLATE_INGRESO_ACEPTADO (P-44). Ver docs/resend-plantillas.md.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2337,12 +2341,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>/ingresar/codigo</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Leer la cookie del paso 1; sin cookie, volver a /ingresar</t>
+          <t>F-01: el select «Grado» se vacía tras un error de validación</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -2352,29 +2356,33 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I17" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H17,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J17" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H17,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Falla media de la verificación QA 1 (docs/verificaciones/2026-09-23-verificacion-1.md).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2384,44 +2392,48 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>/ingresar/codigo</t>
+          <t>/cuenta/solicitar</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>verifyOtp y entrar a /cuenta</t>
+          <t>Revisar el diseño de /cuenta/solicitar (sin maqueta; selector 50/100 como radios)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I18" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H18,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J18" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H18,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Pedido por ga-funcionalidad-botones el 23-sep.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2431,12 +2443,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>/ingresar</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Server Action: zod, límites por IP y cédula, guardar</t>
+          <t>Server Action: correo_por_cedula(), signInWithOtp, cookie firmada, ir a /ingresar/codigo</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -2456,23 +2468,19 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I19" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H19,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>23-sep: se quitaron los correos al equipo y al solicitante (decisión de Sebas). El equipo revisa las afiliaciones en Supabase hasta que exista el panel /admin; el correo «Ingreso aceptado» sale al aprobar (P-51).</t>
-        </is>
-      </c>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H19,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2482,12 +2490,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>/ingresar/codigo</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Proteger con proxy.ts y «Salir» con signOut</t>
+          <t>Leer la cookie del paso 1; sin cookie, volver a /ingresar</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -2507,11 +2515,11 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I20" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H20,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H20,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -2519,7 +2527,7 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>P-32</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2529,12 +2537,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>/ingresar/codigo</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Cargar perfil, última solicitud (con tasa), tope y convenios</t>
+          <t>verifyOtp y entrar a /cuenta</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -2554,11 +2562,11 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I21" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H21,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H21,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
@@ -2566,7 +2574,7 @@
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2576,12 +2584,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Conectar el formulario de crédito a /cuenta</t>
+          <t>Server Action: zod, límites por IP y cédula, guardar</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -2601,23 +2609,23 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I22" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H22,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H22,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Conectado desde /cuenta («Nueva solicitud»).</t>
+          <t>23-sep: se quitaron los correos al equipo y al solicitante (decisión de Sebas). El equipo revisa las afiliaciones en Supabase hasta que exista el panel /admin; el correo «Ingreso aceptado» sale al aprobar (P-51).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-31</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2627,12 +2635,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Estado «Enviando…» (prop cargando) y errores (prop error)</t>
+          <t>Proteger con proxy.ts y «Salir» con signOut</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -2642,7 +2650,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -2652,11 +2660,11 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I23" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H23,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H23,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J23" s="7" t="inlineStr"/>
@@ -2664,7 +2672,7 @@
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2674,12 +2682,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>/ingresar/codigo</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Casillas OTP: avance automático, Backspace, pegar; «Entrar» con 6 dígitos</t>
+          <t>Cargar perfil, última solicitud (con tasa), tope y convenios</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -2689,7 +2697,7 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -2699,11 +2707,11 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I24" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H24,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H24,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J24" s="7" t="inlineStr"/>
@@ -2711,7 +2719,7 @@
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-35</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2721,12 +2729,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>/ingresar/codigo</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>«Reenviar código» con contador de 45 s; «Cambiar cédula» limpia la cookie</t>
+          <t>Conectar el formulario de crédito a /cuenta</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -2736,7 +2744,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -2746,19 +2754,23 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I25" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H25,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J25" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H25,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>23-sep: el formulario vive en /cuenta/solicitar (protegida por proxy.ts, encabezado compartido EncabezadoCuenta); «Nueva solicitud» lleva ahí.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2768,12 +2780,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>/ingresar</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Grados desde grados_credito, honeypot, errores y estado de carga</t>
+          <t>Estado «Enviando…» (prop cargando) y errores (prop error)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -2793,11 +2805,11 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I26" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H26,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H26,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J26" s="7" t="inlineStr"/>
@@ -2805,7 +2817,7 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2815,12 +2827,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>/ingresar/codigo</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>«Mis datos»: actualizar solo perfiles.telefono</t>
+          <t>Casillas OTP: avance automático, Backspace, pegar; «Entrar» con 6 dígitos</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -2840,23 +2852,19 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I27" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H27,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>Con error, alinear «Guardar» con el campo desde 640 px.</t>
-        </is>
-      </c>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H27,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>P-30</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2866,12 +2874,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion/enviada</t>
+          <t>/ingresar/codigo</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Mostrar el correo real; si se entra directo, redirigir</t>
+          <t>«Reenviar código» con contador de 45 s; «Cambiar cédula» limpia la cookie</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -2881,7 +2889,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -2891,11 +2899,11 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I28" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H28,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H28,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J28" s="7" t="inlineStr"/>
@@ -2903,7 +2911,7 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>P-34</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2913,12 +2921,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>«Mi cuenta», «Ingresar», «Solicitar crédito», «Ver beneficios» → /cuenta con sesión</t>
+          <t>Grados desde grados_credito, honeypot, errores y estado de carga</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -2928,7 +2936,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -2938,176 +2946,168 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I29" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H29,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>Convenios fijos en la landing por ahora.</t>
-        </is>
-      </c>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H29,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Dato de la cooperativa</t>
+          <t>Funcionalidad</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Texto de la política de datos</t>
+          <t>«Mis datos»: actualizar solo perfiles.telefono</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I30" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H30,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H30,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>Hoy el enlace es href="#". Ruta sugerida /politica-de-datos.</t>
+          <t>Con error, alinear «Guardar» con el campo desde 640 px.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-30</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Dato de la cooperativa</t>
+          <t>Funcionalidad</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Asociados</t>
+          <t>/afiliacion/enviada</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Correos reales de los asociados (Excel de importación)</t>
+          <t>Mostrar el correo real; si se entra directo, redirigir</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="I31" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H31,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>Sin esto el ingreso con código no sirve para cuentas reales.</t>
-        </is>
-      </c>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H31,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-34</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Dato de la cooperativa</t>
+          <t>Funcionalidad</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Número de WhatsApp (NEXT_PUBLIC_WHATSAPP)</t>
+          <t>«Mi cuenta», «Ingresar», «Solicitar crédito», «Ver beneficios» → /cuenta con sesión</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I32" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H32,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H32,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>Para los enlaces wa.me/57&lt;NÚMERO&gt;.</t>
+          <t>Convenios fijos en la landing por ahora.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Días hábiles de respuesta (DIAS_RESPUESTA)</t>
+          <t>Texto de la política de datos</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -3142,19 +3142,23 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I33" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H33,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J33" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H33,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>Hoy el enlace es href="#". Ruta sugerida /politica-de-datos.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3164,12 +3168,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>Asociados</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Correo de contacto (CORREO_CONTACTO)</t>
+          <t>Correos reales de los asociados (Excel de importación)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -3179,7 +3183,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -3189,19 +3193,23 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I34" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H34,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J34" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H34,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>Sin esto el ingreso con código no sirve para cuentas reales.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3216,7 +3224,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Texto de vigilancia de Supersolidaria (TEXTO_VIGILANCIA)</t>
+          <t>Número de WhatsApp (NEXT_PUBLIC_WHATSAPP)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -3240,15 +3248,19 @@
         </is>
       </c>
       <c r="I35" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H35,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J35" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H35,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>Para los enlaces wa.me/57&lt;NÚMERO&gt;.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3258,12 +3270,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Nombres oficiales de los grados</t>
+          <t>Días hábiles de respuesta (DIAS_RESPUESTA)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -3287,19 +3299,15 @@
         </is>
       </c>
       <c r="I36" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H36,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>Se usan en el select «Grado» (grados_credito).</t>
-        </is>
-      </c>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H36,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>P-47</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3309,12 +3317,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Estado de desembolso (cómo y cuándo se informa al asociado)</t>
+          <t>Correo de contacto (CORREO_CONTACTO)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -3338,19 +3346,15 @@
         </is>
       </c>
       <c r="I37" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H37,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>Reportado por ga-funcionalidad-botones el 23-sep.</t>
-        </is>
-      </c>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H37,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -3360,12 +3364,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Fotos reales, cifras y testimonios</t>
+          <t>Texto de vigilancia de Supersolidaria (TEXTO_VIGILANCIA)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -3375,7 +3379,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -3389,7 +3393,7 @@
         </is>
       </c>
       <c r="I38" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H38,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H38,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J38" s="7" t="inlineStr"/>
@@ -3397,7 +3401,7 @@
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-46</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3407,12 +3411,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Tiempo de respuesta real ([TIEMPO] y [T])</t>
+          <t>Nombres oficiales de los grados</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -3422,7 +3426,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -3436,15 +3440,19 @@
         </is>
       </c>
       <c r="I39" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H39,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J39" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H39,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>Se usan en el select «Grado» (grados_credito).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>P-47</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -3459,12 +3467,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Destino de «Nueva solicitud» (nav y acceso rápido)</t>
+          <t>Estado de desembolso (cómo y cuándo se informa al asociado)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -3474,104 +3482,104 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I40" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H40,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H40,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>Hoy es href="#".</t>
+          <t>Reportado por ga-funcionalidad-botones el 23-sep.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Verificación y cierre</t>
+          <t>Dato de la cooperativa</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Calidad</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Correr ga-verificador-qa y ga-verificador-responsive</t>
+          <t>Fotos reales, cifras y testimonios</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I41" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H41,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H41,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>QA 1 hecha el 23-sep (186 pasan, 2 fallan; informe docs/verificaciones/2026-09-23-verificacion-1.md). Falta ga-verificador-responsive.</t>
+          <t>23-sep: los espacios de foto de la landing ya tienen diseño de marca (EspacioFoto). Para poner la foto real se cambia `null` por { src, alt }. Faltan las fotos de la cooperativa.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Verificación y cierre</t>
+          <t>Dato de la cooperativa</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Despliegue</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Subir a GitHub y desplegar en Vercel</t>
+          <t>Tiempo de respuesta real ([TIEMPO] y [T])</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -3581,11 +3589,11 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I42" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H42,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H42,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J42" s="7" t="inlineStr"/>
@@ -3593,22 +3601,22 @@
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Verificación y cierre</t>
+          <t>Dato de la cooperativa</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Borrar /login y /dashboard cuando /ingresar y /cuenta funcionen</t>
+          <t>Destino de «Nueva solicitud» (nav y acceso rápido)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -3623,24 +3631,28 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I43" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H43,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J43" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H43,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>Hoy es href="#".</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3650,22 +3662,22 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Despliegue</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Revisar si conviene confiar en x-forwarded-for para el límite de intentos por IP</t>
+          <t>Subir a GitHub y desplegar en Vercel</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -3675,23 +3687,19 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I44" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H44,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>Sugerido por ga-verificador-qa el 23-sep.</t>
-        </is>
-      </c>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H44,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3701,48 +3709,48 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Commit de las pantallas nuevas</t>
+          <t>Revisar si conviene confiar en x-forwarded-for para el límite de intentos por IP</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I45" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H45,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H45,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>Commit d86db86 en develop.</t>
+          <t>Sugerido por ga-verificador-qa el 23-sep.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3752,12 +3760,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Correos</t>
+          <t>Calidad</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Confirmar que salen los correos de afiliación (el log queda en la terminal de next dev)</t>
+          <t>Correr ga-verificador-qa y ga-verificador-responsive</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -3767,7 +3775,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -3777,99 +3785,99 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I46" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H46,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H46,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>Ya no aplica: el 23-sep se quitaron los correos de afiliación del código (decisión de Sebas).</t>
+          <t>QA 1 hecha el 23-sep (186 pasan, 2 fallan; informe docs/verificaciones/2026-09-23-verificacion-1.md). Responsive hecha el 23-sep: 2 fallas de scroll corregidas (5.8) y segunda pasada con 0 fallas en 13 anchos (320–1920 px); tests/responsive 10/10. La QA final sigue en 6.3.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
+          <t>Commit de las pantallas nuevas</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I47" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H47,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H47,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>Por ahora son una sección en /cuenta (#convenios).</t>
+          <t>Commit d86db86 en develop.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
+          <t>Borrar /login y /dashboard cuando /ingresar y /cuenta funcionen</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Sebas (ga-auditor-supabase revisa antes)</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -3879,38 +3887,38 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I48" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H48,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H48,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
+          <t>Borradas el 23-sep (incluida /dashboard/solicitar, su parte del proxy y los colores heredados de tailwind.config.ts).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
+          <t>Confirmar que salen los correos de afiliación (el log queda en la terminal de next dev)</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -3930,43 +3938,43 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I49" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H49,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H49,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Apartado «Mis datos» ya maquetado.</t>
+          <t>Ya no aplica: el 23-sep se quitaron los correos de afiliación del código (decisión de Sebas).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Color de error #B3261E</t>
+          <t>Mapa de botones: §4 «Nueva solicitud» → /cuenta/solicitar y sección para la ruta /cuenta/solicitar</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -3981,23 +3989,23 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I50" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H50,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H50,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>Se deja.</t>
+          <t>Reportado por ga-diseno-a-codigo. Verificado el 23-sep: docs/mapa-de-botones.md ya tiene §4 «Nueva solicitud» → /cuenta/solicitar (Definido) y §4b /cuenta/solicitar; /dashboard se eliminó.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -4012,12 +4020,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Estado vacío de «Tu solicitud»</t>
+          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -4027,28 +4035,28 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I51" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H51,Plan!$A$5:$A$46,0)),"—")</f>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H51,Plan!$A$5:$A$51,0)),"—")</f>
         <v/>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Ver con /cuenta?vacio=1.</t>
+          <t>Por ahora son una sección en /cuenta (#convenios).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -4058,12 +4066,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Logo en celular como enlace a la landing</t>
+          <t>A 320 px la línea «COOPERATIVA» del logo mide ~5 px de alto (opcional: ocultarla o achicar «Ingresar» bajo 360 px)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -4078,7 +4086,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -4087,15 +4095,19 @@
         </is>
       </c>
       <c r="I52" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H52,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J52" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H52,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>Menor y opcional, reportado por ga-verificador-responsive el 23-sep.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -4105,22 +4117,22 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Escudo: public/logos/vector/green-alliance-logo.svg</t>
+          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Sebas (ga-auditor-supabase revisa antes)</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -4130,19 +4142,23 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="I53" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H53,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J53" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H53,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -4152,12 +4168,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Formulario de ingreso entre 640 y 767 px (columna de 440 px)</t>
+          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -4167,7 +4183,7 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
@@ -4177,65 +4193,312 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I54" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H54,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J54" s="7" t="inlineStr"/>
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H54,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>Apartado «Mis datos» ya maquetado.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
         <is>
+          <t>P-01</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Color de error #B3261E</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H55,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>Se deja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>P-03</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>/cuenta</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Estado vacío de «Tu solicitud»</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="I56" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H56,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>Ver con /cuenta?vacio=1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>P-04</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Logo en celular como enlace a la landing</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H57,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>P-05</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Escudo: public/logos/vector/green-alliance-logo.svg</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H58,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>P-06</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>/ingresar</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Formulario de ingreso entre 640 y 767 px (columna de 440 px)</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="I59" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H59,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
           <t>P-07</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Decisión</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>/ingresar</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Panel verde en tableta (640–1023 px) centrado</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>Yo</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Hecho</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="I55" s="21">
-        <f>IFERROR(INDEX(Plan!$B$5:$B$46,MATCH(H55,Plan!$A$5:$A$46,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="J55" s="7" t="inlineStr"/>
+      <c r="I60" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$51,MATCH(H60,Plan!$A$5:$A$51,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J60" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J55"/>
-  <conditionalFormatting sqref="G5:G55">
+  <autoFilter ref="A4:J60"/>
+  <conditionalFormatting sqref="G5:G60">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$G5="Hecho"</formula>
     </cfRule>
@@ -4249,7 +4512,7 @@
       <formula>$G5="Bloqueado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F55">
+  <conditionalFormatting sqref="F5:F60">
     <cfRule type="expression" priority="5" dxfId="5">
       <formula>$F5="Alta"</formula>
     </cfRule>
@@ -4260,16 +4523,16 @@
       <formula>$F5="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:F55">
+  <conditionalFormatting sqref="A5:F60">
     <cfRule type="expression" priority="8" dxfId="8">
       <formula>$G5="Hecho"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Hecho,En curso,Pendiente,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4283,7 +4546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4759,19 +5022,19 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>2.10, 5.1</t>
+          <t>3.3, 3.5</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J9" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L9" s="8">
         <f>K9+E9</f>
@@ -4915,7 +5178,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
@@ -4927,7 +5190,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L11" s="8">
         <f>K11+E11</f>
@@ -5002,10 +5265,10 @@
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L12" s="8">
         <f>K12+E12</f>
@@ -5071,7 +5334,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>2.3, 3.4</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
@@ -5149,7 +5412,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>3.4, 2.9</t>
+          <t>2.3, 2.9</t>
         </is>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -5305,7 +5568,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I16" s="18" t="inlineStr">
@@ -5314,10 +5577,10 @@
         </is>
       </c>
       <c r="J16" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L16" s="8">
         <f>K16+E16</f>
@@ -5392,7 +5655,7 @@
         </is>
       </c>
       <c r="J17" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K17" s="8" t="n">
         <v>13</v>
@@ -5461,7 +5724,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr">
@@ -5539,7 +5802,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I19" s="18" t="inlineStr">
@@ -5548,10 +5811,10 @@
         </is>
       </c>
       <c r="J19" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L19" s="8">
         <f>K19+E19</f>
@@ -5695,19 +5958,19 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J21" s="8" t="n">
         <v>8</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L21" s="8">
         <f>K21+E21</f>
@@ -5773,7 +6036,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>3.6, 2.8</t>
+          <t>2.10, 2.1</t>
         </is>
       </c>
       <c r="I22" s="18" t="inlineStr">
@@ -5785,7 +6048,7 @@
         <v>8</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L22" s="8">
         <f>K22+E22</f>
@@ -5851,7 +6114,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>2.5, 2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I23" s="18" t="inlineStr">
@@ -5863,7 +6126,7 @@
         <v>6</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L23" s="8">
         <f>K23+E23</f>
@@ -5929,7 +6192,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.1, 2.8, 6.11</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -6007,7 +6270,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="I25" s="18" t="inlineStr">
@@ -6085,7 +6348,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.2, 5.7</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
@@ -6094,10 +6357,10 @@
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L26" s="8">
         <f>K26+E26</f>
@@ -6163,7 +6426,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>2.4, 5.4, 5.5</t>
+          <t>2.4, 2.11, 5.6</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
@@ -6172,10 +6435,10 @@
         </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L27" s="8">
         <f>K27+E27</f>
@@ -6246,14 +6509,14 @@
       </c>
       <c r="I28" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J28" s="8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L28" s="8">
         <f>K28+E28</f>
@@ -6319,7 +6582,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>6.8, 2.11</t>
+          <t>5.4, 6.8</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr">
@@ -6328,10 +6591,10 @@
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L29" s="8">
         <f>K29+E29</f>
@@ -6406,10 +6669,10 @@
         </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L30" s="8">
         <f>K30+E30</f>
@@ -6484,14 +6747,14 @@
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J31" s="8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L31" s="8">
         <f>K31+E31</f>
@@ -6557,19 +6820,19 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I32" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J32" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L32" s="8">
         <f>K32+E32</f>
@@ -6635,19 +6898,19 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.6, 3.7</t>
         </is>
       </c>
       <c r="I33" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J33" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L33" s="8">
         <f>K33+E33</f>
@@ -6722,10 +6985,10 @@
         </is>
       </c>
       <c r="J34" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L34" s="8">
         <f>K34+E34</f>
@@ -6795,7 +7058,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I35" s="18" t="inlineStr">
@@ -6804,10 +7067,10 @@
         </is>
       </c>
       <c r="J35" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L35" s="8">
         <f>K35+E35</f>
@@ -6877,19 +7140,19 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L36" s="8">
         <f>K36+E36</f>
@@ -6905,7 +7168,7 @@
       </c>
       <c r="O36" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P36" s="8" t="inlineStr">
@@ -6923,21 +7186,21 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>6. Pruebas y lanzamiento</t>
+          <t>5. Convenios y pulido</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Pruebas de las nuevas Server Actions (login, afiliación, crédito, admin)</t>
+          <t>Revisar el diseño de /cuenta/solicitar (pantalla sin maqueta; selector 50/100 ahora son radios)</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" s="8">
         <f>D37</f>
@@ -6945,7 +7208,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2.10, 3.6, 4.3, 4.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -6955,7 +7218,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>6.2, 6.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I37" s="18" t="inlineStr">
@@ -6964,10 +7227,10 @@
         </is>
       </c>
       <c r="J37" s="8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L37" s="8">
         <f>K37+E37</f>
@@ -6983,17 +7246,17 @@
       </c>
       <c r="O37" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="P37" s="8" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Agregado</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
         <is>
-          <t>ga-escritor-tests</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr"/>
@@ -7001,17 +7264,17 @@
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>6. Pruebas y lanzamiento</t>
+          <t>5. Convenios y pulido</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad completa</t>
+          <t>Logo horizontal con las letras oficiales (SVG) y espacios de foto de marca en la landing (EspacioFoto)</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -7023,7 +7286,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2.10, 3.6, 4.3, 4.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -7033,19 +7296,19 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I38" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J38" s="8" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L38" s="8">
         <f>K38+E38</f>
@@ -7061,17 +7324,17 @@
       </c>
       <c r="O38" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P38" s="8" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Agregado</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr"/>
@@ -7079,29 +7342,29 @@
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>6. Pruebas y lanzamiento</t>
+          <t>5. Convenios y pulido</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>QA de punta a punta y verificación responsive</t>
+          <t>Corregir scroll horizontal: headers con logo (320 px) y formulario de /ingresar y /ingresar/codigo (1024–1075 px)</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" s="8">
         <f>D39</f>
         <v/>
       </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>6.1, 5.5, 2.8, 5.3, 5.4, 2.11</t>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>5.2, 5.7</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -7111,19 +7374,19 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J39" s="8" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="L39" s="8">
         <f>K39+E39</f>
@@ -7139,17 +7402,17 @@
       </c>
       <c r="O39" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>Propuesta</t>
+          <t>Agregado</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>ga-verificador-qa + ga-verificador-responsive</t>
+          <t>ga-diseno-a-codigo + ga-verificador-responsive</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr"/>
@@ -7157,7 +7420,7 @@
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -7167,11 +7430,11 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Registrar dominio (5 años) y protección de dominio</t>
+          <t>Pruebas de las nuevas Server Actions (login, afiliación, crédito, admin)</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="8">
         <f>D40</f>
@@ -7179,7 +7442,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.10, 3.6, 4.3, 4.5</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -7189,7 +7452,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.2, 6.4</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">
@@ -7198,10 +7461,10 @@
         </is>
       </c>
       <c r="J40" s="8" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L40" s="8">
         <f>K40+E40</f>
@@ -7217,7 +7480,7 @@
       </c>
       <c r="O40" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="P40" s="8" t="inlineStr">
@@ -7227,7 +7490,7 @@
       </c>
       <c r="Q40" s="7" t="inlineStr">
         <is>
-          <t>Yo + cooperativa</t>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr"/>
@@ -7235,7 +7498,7 @@
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -7245,7 +7508,7 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Subir a GitHub y desplegar en Vercel (producción)</t>
+          <t>Revisión de seguridad completa</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -7255,31 +7518,31 @@
         <f>D41</f>
         <v/>
       </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>6.2, 6.3, 6.4, 2.4, 6.8, 6.9, 6.10</t>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>2.10, 3.6, 4.3, 4.5</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>No (usa las 2 filas)</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
-          <t>A+B</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J41" s="8" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L41" s="8">
         <f>K41+E41</f>
@@ -7305,7 +7568,7 @@
       </c>
       <c r="Q41" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="R41" s="7" t="inlineStr"/>
@@ -7313,7 +7576,7 @@
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -7323,7 +7586,7 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Pruebas con usuarios reales y corrección de errores</t>
+          <t>QA de punta a punta y verificación responsive</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
@@ -7333,9 +7596,9 @@
         <f>D42</f>
         <v/>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>6.5, 4.4</t>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>6.1, 5.5, 2.8, 5.3, 5.4, 2.11, 5.6</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -7345,7 +7608,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I42" s="18" t="inlineStr">
@@ -7354,10 +7617,10 @@
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L42" s="8">
         <f>K42+E42</f>
@@ -7373,7 +7636,7 @@
       </c>
       <c r="O42" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="P42" s="8" t="inlineStr">
@@ -7383,7 +7646,7 @@
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>Yo + cooperativa</t>
+          <t>ga-verificador-qa + ga-verificador-responsive</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr"/>
@@ -7391,7 +7654,7 @@
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -7401,7 +7664,7 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Capacitación al equipo de la cooperativa</t>
+          <t>Registrar dominio (5 años) y protección de dominio</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
@@ -7413,7 +7676,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -7423,7 +7686,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I43" s="18" t="inlineStr">
@@ -7432,10 +7695,10 @@
         </is>
       </c>
       <c r="J43" s="8" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L43" s="8">
         <f>K43+E43</f>
@@ -7461,7 +7724,7 @@
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Yo + cooperativa</t>
         </is>
       </c>
       <c r="R43" s="7" t="inlineStr"/>
@@ -7469,7 +7732,7 @@
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -7479,41 +7742,41 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Revisar y aplicar en producción la migración 20260923210000_limite_de_intentos.sql (ga-auditor-supabase revisa antes)</t>
+          <t>Subir a GitHub y desplegar en Vercel (producción)</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="8">
         <f>D44</f>
         <v/>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>2.5, 2.9</t>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>6.2, 6.3, 6.4, 2.4, 6.8, 6.9, 6.10</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No (usa las 2 filas)</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+B</t>
         </is>
       </c>
       <c r="J44" s="8" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L44" s="8">
         <f>K44+E44</f>
@@ -7534,12 +7797,12 @@
       </c>
       <c r="P44" s="8" t="inlineStr">
         <is>
-          <t>Agregado</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>Yo + ga-auditor-supabase</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="R44" s="7" t="inlineStr"/>
@@ -7547,7 +7810,7 @@
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -7557,11 +7820,11 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Variables en Vercel (SUPABASE_SERVICE_ROLE_KEY, INGRESO_COOKIE_SECRET, RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_INGRESO_ACEPTADO, RESEND_TEMPLATE_CREDITO_APROBADO, RESEND_TEMPLATE_CREDITO_RECHAZADO, NEXT_PUBLIC_WHATSAPP)</t>
+          <t>Pruebas con usuarios reales y corrección de errores</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" s="8">
         <f>D45</f>
@@ -7569,7 +7832,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2.5, 2.9</t>
+          <t>6.5, 4.4</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -7579,7 +7842,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.12, 6.7</t>
         </is>
       </c>
       <c r="I45" s="18" t="inlineStr">
@@ -7588,10 +7851,10 @@
         </is>
       </c>
       <c r="J45" s="8" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="L45" s="8">
         <f>K45+E45</f>
@@ -7612,12 +7875,12 @@
       </c>
       <c r="P45" s="8" t="inlineStr">
         <is>
-          <t>Agregado</t>
+          <t>Propuesta</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>Yo (panel Vercel)</t>
+          <t>Yo + cooperativa</t>
         </is>
       </c>
       <c r="R45" s="7" t="inlineStr"/>
@@ -7625,7 +7888,7 @@
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -7635,7 +7898,7 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones (tasa_interes_mensual); ga-auditor-supabase revisa antes</t>
+          <t>Capacitación al equipo de la cooperativa</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
@@ -7647,7 +7910,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -7657,7 +7920,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="I46" s="18" t="inlineStr">
@@ -7666,10 +7929,10 @@
         </is>
       </c>
       <c r="J46" s="8" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="L46" s="8">
         <f>K46+E46</f>
@@ -7685,59 +7948,449 @@
       </c>
       <c r="O46" s="8" t="inlineStr">
         <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t>Propuesta</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="R46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>6. Pruebas y lanzamiento</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Revisar y aplicar en producción la migración 20260923210000_limite_de_intentos.sql (ga-auditor-supabase revisa antes)</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="8">
+        <f>D47</f>
+        <v/>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>2.5, 2.9</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L47" s="8">
+        <f>K47+E47</f>
+        <v/>
+      </c>
+      <c r="M47" s="8">
+        <f>K47-J47</f>
+        <v/>
+      </c>
+      <c r="N47" s="8">
+        <f>"S"&amp;(INT(K47/Resumen!$C$5)+1)&amp;"–S"&amp;MAX(INT(K47/Resumen!$C$5)+1,ROUNDUP(L47/Resumen!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="P47" s="8" t="inlineStr">
+        <is>
+          <t>Agregado</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>Yo + ga-auditor-supabase</t>
+        </is>
+      </c>
+      <c r="R47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>6. Pruebas y lanzamiento</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Variables en Vercel (SUPABASE_SERVICE_ROLE_KEY, INGRESO_COOKIE_SECRET, LIMITE_HMAC_SECRET, RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_INGRESO_ACEPTADO, RESEND_TEMPLATE_CREDITO_APROBADO, RESEND_TEMPLATE_CREDITO_RECHAZADO, NEXT_PUBLIC_WHATSAPP)</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="8">
+        <f>D48</f>
+        <v/>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>2.5, 2.9, 6.11</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="K48" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="L48" s="8">
+        <f>K48+E48</f>
+        <v/>
+      </c>
+      <c r="M48" s="8">
+        <f>K48-J48</f>
+        <v/>
+      </c>
+      <c r="N48" s="8">
+        <f>"S"&amp;(INT(K48/Resumen!$C$5)+1)&amp;"–S"&amp;MAX(INT(K48/Resumen!$C$5)+1,ROUNDUP(L48/Resumen!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="O48" s="8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="P48" s="8" t="inlineStr">
+        <is>
+          <t>Agregado</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>Yo (panel Vercel)</t>
+        </is>
+      </c>
+      <c r="R48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>6.10</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>6. Pruebas y lanzamiento</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones (tasa_interes_mensual); ga-auditor-supabase revisa antes</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="8">
+        <f>D49</f>
+        <v/>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="L49" s="8">
+        <f>K49+E49</f>
+        <v/>
+      </c>
+      <c r="M49" s="8">
+        <f>K49-J49</f>
+        <v/>
+      </c>
+      <c r="N49" s="8">
+        <f>"S"&amp;(INT(K49/Resumen!$C$5)+1)&amp;"–S"&amp;MAX(INT(K49/Resumen!$C$5)+1,ROUNDUP(L49/Resumen!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
           <t>Hecho</t>
         </is>
       </c>
-      <c r="P46" s="8" t="inlineStr">
+      <c r="P49" s="8" t="inlineStr">
         <is>
           <t>Agregado</t>
         </is>
       </c>
-      <c r="Q46" s="7" t="inlineStr">
+      <c r="Q49" s="7" t="inlineStr">
         <is>
           <t>Yo + ga-auditor-supabase</t>
         </is>
       </c>
-      <c r="R46" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="R49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>6. Pruebas y lanzamiento</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Clave del límite de intentos con HMAC-SHA256 y LIMITE_HMAC_SECRET (M-2 de la auditoría de P-43)</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="8">
+        <f>D50</f>
+        <v/>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>2.5, 2.9</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="K50" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="L50" s="8">
+        <f>K50+E50</f>
+        <v/>
+      </c>
+      <c r="M50" s="8">
+        <f>K50-J50</f>
+        <v/>
+      </c>
+      <c r="N50" s="8">
+        <f>"S"&amp;(INT(K50/Resumen!$C$5)+1)&amp;"–S"&amp;MAX(INT(K50/Resumen!$C$5)+1,ROUNDUP(L50/Resumen!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="O50" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="P50" s="8" t="inlineStr">
+        <is>
+          <t>Agregado</t>
+        </is>
+      </c>
+      <c r="Q50" s="7" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="R50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>6. Pruebas y lanzamiento</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Alerta en los logs de Vercel para limite_de_intentos_fallo y limite_secreto_faltante</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8">
+        <f>D51</f>
+        <v/>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="L51" s="8">
+        <f>K51+E51</f>
+        <v/>
+      </c>
+      <c r="M51" s="8">
+        <f>K51-J51</f>
+        <v/>
+      </c>
+      <c r="N51" s="8">
+        <f>"S"&amp;(INT(K51/Resumen!$C$5)+1)&amp;"–S"&amp;MAX(INT(K51/Resumen!$C$5)+1,ROUNDUP(L51/Resumen!$C$5,0))</f>
+        <v/>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="P51" s="8" t="inlineStr">
+        <is>
+          <t>Agregado</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>Yo (panel Vercel)</t>
+        </is>
+      </c>
+      <c r="R51" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Peso (azul, fondo amarillo) = dato de entrada; 1 punto de peso = 1 bloque de tiempo (ver hoja Pesos).</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>«Origen: Agregado» = actividad que no estaba en la propuesta del 31-ago (p. ej. ingreso con código, afiliación, importación).</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>«En paralelo con» lista las tareas que comparten tiempo con esta en el plan optimizado.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Espera en cola = bloques entre que la tarea queda lista y una fila la toma.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R46"/>
-  <conditionalFormatting sqref="O5:O46">
+  <autoFilter ref="A4:R51"/>
+  <conditionalFormatting sqref="O5:O51">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$O5="Hecho"</formula>
     </cfRule>
@@ -7752,7 +8405,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O5:O46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="O5:O51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Hecho,En curso,Pendiente,Bloqueado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7766,7 +8419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO56"/>
+  <dimension ref="A1:BO61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8108,243 +8761,243 @@
         </is>
       </c>
       <c r="H6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;H$5)*(Plan!$L$5:$L$46&gt;=H$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;H$5)*(Plan!$L$5:$L$46&gt;=H$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;H$5)*(Plan!$L$5:$L$51&gt;=H$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;H$5)*(Plan!$L$5:$L$51&gt;=H$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="I6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;I$5)*(Plan!$L$5:$L$46&gt;=I$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;I$5)*(Plan!$L$5:$L$46&gt;=I$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;I$5)*(Plan!$L$5:$L$51&gt;=I$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;I$5)*(Plan!$L$5:$L$51&gt;=I$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="J6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;J$5)*(Plan!$L$5:$L$46&gt;=J$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;J$5)*(Plan!$L$5:$L$46&gt;=J$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;J$5)*(Plan!$L$5:$L$51&gt;=J$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;J$5)*(Plan!$L$5:$L$51&gt;=J$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="K6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;K$5)*(Plan!$L$5:$L$46&gt;=K$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;K$5)*(Plan!$L$5:$L$46&gt;=K$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;K$5)*(Plan!$L$5:$L$51&gt;=K$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;K$5)*(Plan!$L$5:$L$51&gt;=K$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="L6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;L$5)*(Plan!$L$5:$L$46&gt;=L$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;L$5)*(Plan!$L$5:$L$46&gt;=L$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;L$5)*(Plan!$L$5:$L$51&gt;=L$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;L$5)*(Plan!$L$5:$L$51&gt;=L$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="M6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;M$5)*(Plan!$L$5:$L$46&gt;=M$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;M$5)*(Plan!$L$5:$L$46&gt;=M$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;M$5)*(Plan!$L$5:$L$51&gt;=M$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;M$5)*(Plan!$L$5:$L$51&gt;=M$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="N6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;N$5)*(Plan!$L$5:$L$46&gt;=N$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;N$5)*(Plan!$L$5:$L$46&gt;=N$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;N$5)*(Plan!$L$5:$L$51&gt;=N$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;N$5)*(Plan!$L$5:$L$51&gt;=N$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="O6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;O$5)*(Plan!$L$5:$L$46&gt;=O$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;O$5)*(Plan!$L$5:$L$46&gt;=O$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;O$5)*(Plan!$L$5:$L$51&gt;=O$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;O$5)*(Plan!$L$5:$L$51&gt;=O$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="P6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;P$5)*(Plan!$L$5:$L$46&gt;=P$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;P$5)*(Plan!$L$5:$L$46&gt;=P$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;P$5)*(Plan!$L$5:$L$51&gt;=P$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;P$5)*(Plan!$L$5:$L$51&gt;=P$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="Q6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Q$5)*(Plan!$L$5:$L$46&gt;=Q$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Q$5)*(Plan!$L$5:$L$46&gt;=Q$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Q$5)*(Plan!$L$5:$L$51&gt;=Q$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Q$5)*(Plan!$L$5:$L$51&gt;=Q$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="R6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;R$5)*(Plan!$L$5:$L$46&gt;=R$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;R$5)*(Plan!$L$5:$L$46&gt;=R$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;R$5)*(Plan!$L$5:$L$51&gt;=R$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;R$5)*(Plan!$L$5:$L$51&gt;=R$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="S6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;S$5)*(Plan!$L$5:$L$46&gt;=S$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;S$5)*(Plan!$L$5:$L$46&gt;=S$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;S$5)*(Plan!$L$5:$L$51&gt;=S$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;S$5)*(Plan!$L$5:$L$51&gt;=S$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="T6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;T$5)*(Plan!$L$5:$L$46&gt;=T$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;T$5)*(Plan!$L$5:$L$46&gt;=T$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;T$5)*(Plan!$L$5:$L$51&gt;=T$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;T$5)*(Plan!$L$5:$L$51&gt;=T$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="U6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;U$5)*(Plan!$L$5:$L$46&gt;=U$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;U$5)*(Plan!$L$5:$L$46&gt;=U$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;U$5)*(Plan!$L$5:$L$51&gt;=U$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;U$5)*(Plan!$L$5:$L$51&gt;=U$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="V6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;V$5)*(Plan!$L$5:$L$46&gt;=V$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;V$5)*(Plan!$L$5:$L$46&gt;=V$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;V$5)*(Plan!$L$5:$L$51&gt;=V$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;V$5)*(Plan!$L$5:$L$51&gt;=V$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="W6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;W$5)*(Plan!$L$5:$L$46&gt;=W$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;W$5)*(Plan!$L$5:$L$46&gt;=W$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;W$5)*(Plan!$L$5:$L$51&gt;=W$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;W$5)*(Plan!$L$5:$L$51&gt;=W$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="X6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;X$5)*(Plan!$L$5:$L$46&gt;=X$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;X$5)*(Plan!$L$5:$L$46&gt;=X$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;X$5)*(Plan!$L$5:$L$51&gt;=X$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;X$5)*(Plan!$L$5:$L$51&gt;=X$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="Y6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Y$5)*(Plan!$L$5:$L$46&gt;=Y$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Y$5)*(Plan!$L$5:$L$46&gt;=Y$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Y$5)*(Plan!$L$5:$L$51&gt;=Y$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Y$5)*(Plan!$L$5:$L$51&gt;=Y$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="Z6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Z$5)*(Plan!$L$5:$L$46&gt;=Z$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Z$5)*(Plan!$L$5:$L$46&gt;=Z$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Z$5)*(Plan!$L$5:$L$51&gt;=Z$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Z$5)*(Plan!$L$5:$L$51&gt;=Z$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AA6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AA$5)*(Plan!$L$5:$L$46&gt;=AA$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AA$5)*(Plan!$L$5:$L$46&gt;=AA$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AA$5)*(Plan!$L$5:$L$51&gt;=AA$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AA$5)*(Plan!$L$5:$L$51&gt;=AA$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AB6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AB$5)*(Plan!$L$5:$L$46&gt;=AB$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AB$5)*(Plan!$L$5:$L$46&gt;=AB$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AB$5)*(Plan!$L$5:$L$51&gt;=AB$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AB$5)*(Plan!$L$5:$L$51&gt;=AB$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AC6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AC$5)*(Plan!$L$5:$L$46&gt;=AC$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AC$5)*(Plan!$L$5:$L$46&gt;=AC$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AC$5)*(Plan!$L$5:$L$51&gt;=AC$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AC$5)*(Plan!$L$5:$L$51&gt;=AC$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AD6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AD$5)*(Plan!$L$5:$L$46&gt;=AD$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AD$5)*(Plan!$L$5:$L$46&gt;=AD$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AD$5)*(Plan!$L$5:$L$51&gt;=AD$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AD$5)*(Plan!$L$5:$L$51&gt;=AD$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AE6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AE$5)*(Plan!$L$5:$L$46&gt;=AE$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AE$5)*(Plan!$L$5:$L$46&gt;=AE$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AE$5)*(Plan!$L$5:$L$51&gt;=AE$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AE$5)*(Plan!$L$5:$L$51&gt;=AE$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AF6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AF$5)*(Plan!$L$5:$L$46&gt;=AF$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AF$5)*(Plan!$L$5:$L$46&gt;=AF$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AF$5)*(Plan!$L$5:$L$51&gt;=AF$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AF$5)*(Plan!$L$5:$L$51&gt;=AF$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AG6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AG$5)*(Plan!$L$5:$L$46&gt;=AG$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AG$5)*(Plan!$L$5:$L$46&gt;=AG$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AG$5)*(Plan!$L$5:$L$51&gt;=AG$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AG$5)*(Plan!$L$5:$L$51&gt;=AG$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AH6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AH$5)*(Plan!$L$5:$L$46&gt;=AH$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AH$5)*(Plan!$L$5:$L$46&gt;=AH$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AH$5)*(Plan!$L$5:$L$51&gt;=AH$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AH$5)*(Plan!$L$5:$L$51&gt;=AH$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AI6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AI$5)*(Plan!$L$5:$L$46&gt;=AI$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AI$5)*(Plan!$L$5:$L$46&gt;=AI$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AI$5)*(Plan!$L$5:$L$51&gt;=AI$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AI$5)*(Plan!$L$5:$L$51&gt;=AI$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AJ6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AJ$5)*(Plan!$L$5:$L$46&gt;=AJ$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AJ$5)*(Plan!$L$5:$L$46&gt;=AJ$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AJ$5)*(Plan!$L$5:$L$51&gt;=AJ$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AJ$5)*(Plan!$L$5:$L$51&gt;=AJ$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AK6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AK$5)*(Plan!$L$5:$L$46&gt;=AK$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AK$5)*(Plan!$L$5:$L$46&gt;=AK$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AK$5)*(Plan!$L$5:$L$51&gt;=AK$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AK$5)*(Plan!$L$5:$L$51&gt;=AK$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AL6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AL$5)*(Plan!$L$5:$L$46&gt;=AL$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AL$5)*(Plan!$L$5:$L$46&gt;=AL$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AL$5)*(Plan!$L$5:$L$51&gt;=AL$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AL$5)*(Plan!$L$5:$L$51&gt;=AL$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AM6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AM$5)*(Plan!$L$5:$L$46&gt;=AM$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AM$5)*(Plan!$L$5:$L$46&gt;=AM$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AM$5)*(Plan!$L$5:$L$51&gt;=AM$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AM$5)*(Plan!$L$5:$L$51&gt;=AM$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AN6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AN$5)*(Plan!$L$5:$L$46&gt;=AN$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AN$5)*(Plan!$L$5:$L$46&gt;=AN$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AN$5)*(Plan!$L$5:$L$51&gt;=AN$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AN$5)*(Plan!$L$5:$L$51&gt;=AN$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AO6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AO$5)*(Plan!$L$5:$L$46&gt;=AO$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AO$5)*(Plan!$L$5:$L$46&gt;=AO$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AO$5)*(Plan!$L$5:$L$51&gt;=AO$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AO$5)*(Plan!$L$5:$L$51&gt;=AO$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AP6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AP$5)*(Plan!$L$5:$L$46&gt;=AP$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AP$5)*(Plan!$L$5:$L$46&gt;=AP$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AP$5)*(Plan!$L$5:$L$51&gt;=AP$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AP$5)*(Plan!$L$5:$L$51&gt;=AP$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AQ6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AQ$5)*(Plan!$L$5:$L$46&gt;=AQ$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AQ$5)*(Plan!$L$5:$L$46&gt;=AQ$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AQ$5)*(Plan!$L$5:$L$51&gt;=AQ$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AQ$5)*(Plan!$L$5:$L$51&gt;=AQ$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AR6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AR$5)*(Plan!$L$5:$L$46&gt;=AR$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AR$5)*(Plan!$L$5:$L$46&gt;=AR$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AR$5)*(Plan!$L$5:$L$51&gt;=AR$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AR$5)*(Plan!$L$5:$L$51&gt;=AR$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AS6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AS$5)*(Plan!$L$5:$L$46&gt;=AS$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AS$5)*(Plan!$L$5:$L$46&gt;=AS$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AS$5)*(Plan!$L$5:$L$51&gt;=AS$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AS$5)*(Plan!$L$5:$L$51&gt;=AS$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AT6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AT$5)*(Plan!$L$5:$L$46&gt;=AT$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AT$5)*(Plan!$L$5:$L$46&gt;=AT$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AT$5)*(Plan!$L$5:$L$51&gt;=AT$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AT$5)*(Plan!$L$5:$L$51&gt;=AT$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AU6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AU$5)*(Plan!$L$5:$L$46&gt;=AU$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AU$5)*(Plan!$L$5:$L$46&gt;=AU$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AU$5)*(Plan!$L$5:$L$51&gt;=AU$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AU$5)*(Plan!$L$5:$L$51&gt;=AU$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AV6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AV$5)*(Plan!$L$5:$L$46&gt;=AV$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AV$5)*(Plan!$L$5:$L$46&gt;=AV$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AV$5)*(Plan!$L$5:$L$51&gt;=AV$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AV$5)*(Plan!$L$5:$L$51&gt;=AV$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AW6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AW$5)*(Plan!$L$5:$L$46&gt;=AW$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AW$5)*(Plan!$L$5:$L$46&gt;=AW$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AW$5)*(Plan!$L$5:$L$51&gt;=AW$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AW$5)*(Plan!$L$5:$L$51&gt;=AW$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AX6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AX$5)*(Plan!$L$5:$L$46&gt;=AX$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AX$5)*(Plan!$L$5:$L$46&gt;=AX$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AX$5)*(Plan!$L$5:$L$51&gt;=AX$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AX$5)*(Plan!$L$5:$L$51&gt;=AX$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AY6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AY$5)*(Plan!$L$5:$L$46&gt;=AY$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AY$5)*(Plan!$L$5:$L$46&gt;=AY$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AY$5)*(Plan!$L$5:$L$51&gt;=AY$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AY$5)*(Plan!$L$5:$L$51&gt;=AY$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AZ6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AZ$5)*(Plan!$L$5:$L$46&gt;=AZ$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AZ$5)*(Plan!$L$5:$L$46&gt;=AZ$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AZ$5)*(Plan!$L$5:$L$51&gt;=AZ$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AZ$5)*(Plan!$L$5:$L$51&gt;=AZ$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BA6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BA$5)*(Plan!$L$5:$L$46&gt;=BA$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BA$5)*(Plan!$L$5:$L$46&gt;=BA$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BA$5)*(Plan!$L$5:$L$51&gt;=BA$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BA$5)*(Plan!$L$5:$L$51&gt;=BA$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BB6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BB$5)*(Plan!$L$5:$L$46&gt;=BB$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BB$5)*(Plan!$L$5:$L$46&gt;=BB$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BB$5)*(Plan!$L$5:$L$51&gt;=BB$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BB$5)*(Plan!$L$5:$L$51&gt;=BB$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BC6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BC$5)*(Plan!$L$5:$L$46&gt;=BC$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BC$5)*(Plan!$L$5:$L$46&gt;=BC$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BC$5)*(Plan!$L$5:$L$51&gt;=BC$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BC$5)*(Plan!$L$5:$L$51&gt;=BC$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BD6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BD$5)*(Plan!$L$5:$L$46&gt;=BD$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BD$5)*(Plan!$L$5:$L$46&gt;=BD$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BD$5)*(Plan!$L$5:$L$51&gt;=BD$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BD$5)*(Plan!$L$5:$L$51&gt;=BD$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BE6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BE$5)*(Plan!$L$5:$L$46&gt;=BE$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BE$5)*(Plan!$L$5:$L$46&gt;=BE$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BE$5)*(Plan!$L$5:$L$51&gt;=BE$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BE$5)*(Plan!$L$5:$L$51&gt;=BE$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BF6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BF$5)*(Plan!$L$5:$L$46&gt;=BF$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BF$5)*(Plan!$L$5:$L$46&gt;=BF$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BF$5)*(Plan!$L$5:$L$51&gt;=BF$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BF$5)*(Plan!$L$5:$L$51&gt;=BF$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BG6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BG$5)*(Plan!$L$5:$L$46&gt;=BG$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BG$5)*(Plan!$L$5:$L$46&gt;=BG$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BG$5)*(Plan!$L$5:$L$51&gt;=BG$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BG$5)*(Plan!$L$5:$L$51&gt;=BG$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BH6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BH$5)*(Plan!$L$5:$L$46&gt;=BH$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BH$5)*(Plan!$L$5:$L$46&gt;=BH$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BH$5)*(Plan!$L$5:$L$51&gt;=BH$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BH$5)*(Plan!$L$5:$L$51&gt;=BH$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BI6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BI$5)*(Plan!$L$5:$L$46&gt;=BI$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BI$5)*(Plan!$L$5:$L$46&gt;=BI$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BI$5)*(Plan!$L$5:$L$51&gt;=BI$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BI$5)*(Plan!$L$5:$L$51&gt;=BI$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BJ6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BJ$5)*(Plan!$L$5:$L$46&gt;=BJ$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BJ$5)*(Plan!$L$5:$L$46&gt;=BJ$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BJ$5)*(Plan!$L$5:$L$51&gt;=BJ$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BJ$5)*(Plan!$L$5:$L$51&gt;=BJ$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BK6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BK$5)*(Plan!$L$5:$L$46&gt;=BK$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BK$5)*(Plan!$L$5:$L$46&gt;=BK$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BK$5)*(Plan!$L$5:$L$51&gt;=BK$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BK$5)*(Plan!$L$5:$L$51&gt;=BK$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BL6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BL$5)*(Plan!$L$5:$L$46&gt;=BL$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BL$5)*(Plan!$L$5:$L$46&gt;=BL$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BL$5)*(Plan!$L$5:$L$51&gt;=BL$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BL$5)*(Plan!$L$5:$L$51&gt;=BL$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BM6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BM$5)*(Plan!$L$5:$L$46&gt;=BM$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BM$5)*(Plan!$L$5:$L$46&gt;=BM$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BM$5)*(Plan!$L$5:$L$51&gt;=BM$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BM$5)*(Plan!$L$5:$L$51&gt;=BM$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BN6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BN$5)*(Plan!$L$5:$L$46&gt;=BN$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BN$5)*(Plan!$L$5:$L$46&gt;=BN$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BN$5)*(Plan!$L$5:$L$51&gt;=BN$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BN$5)*(Plan!$L$5:$L$51&gt;=BN$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BO6" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BO$5)*(Plan!$L$5:$L$46&gt;=BO$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="A")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BO$5)*(Plan!$L$5:$L$46&gt;=BO$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BO$5)*(Plan!$L$5:$L$51&gt;=BO$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="A")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BO$5)*(Plan!$L$5:$L$51&gt;=BO$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
     </row>
@@ -8355,243 +9008,243 @@
         </is>
       </c>
       <c r="H7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;H$5)*(Plan!$L$5:$L$46&gt;=H$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;H$5)*(Plan!$L$5:$L$46&gt;=H$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;H$5)*(Plan!$L$5:$L$51&gt;=H$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;H$5)*(Plan!$L$5:$L$51&gt;=H$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="I7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;I$5)*(Plan!$L$5:$L$46&gt;=I$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;I$5)*(Plan!$L$5:$L$46&gt;=I$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;I$5)*(Plan!$L$5:$L$51&gt;=I$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;I$5)*(Plan!$L$5:$L$51&gt;=I$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="J7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;J$5)*(Plan!$L$5:$L$46&gt;=J$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;J$5)*(Plan!$L$5:$L$46&gt;=J$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;J$5)*(Plan!$L$5:$L$51&gt;=J$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;J$5)*(Plan!$L$5:$L$51&gt;=J$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="K7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;K$5)*(Plan!$L$5:$L$46&gt;=K$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;K$5)*(Plan!$L$5:$L$46&gt;=K$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;K$5)*(Plan!$L$5:$L$51&gt;=K$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;K$5)*(Plan!$L$5:$L$51&gt;=K$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="L7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;L$5)*(Plan!$L$5:$L$46&gt;=L$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;L$5)*(Plan!$L$5:$L$46&gt;=L$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;L$5)*(Plan!$L$5:$L$51&gt;=L$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;L$5)*(Plan!$L$5:$L$51&gt;=L$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="M7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;M$5)*(Plan!$L$5:$L$46&gt;=M$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;M$5)*(Plan!$L$5:$L$46&gt;=M$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;M$5)*(Plan!$L$5:$L$51&gt;=M$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;M$5)*(Plan!$L$5:$L$51&gt;=M$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="N7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;N$5)*(Plan!$L$5:$L$46&gt;=N$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;N$5)*(Plan!$L$5:$L$46&gt;=N$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;N$5)*(Plan!$L$5:$L$51&gt;=N$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;N$5)*(Plan!$L$5:$L$51&gt;=N$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="O7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;O$5)*(Plan!$L$5:$L$46&gt;=O$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;O$5)*(Plan!$L$5:$L$46&gt;=O$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;O$5)*(Plan!$L$5:$L$51&gt;=O$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;O$5)*(Plan!$L$5:$L$51&gt;=O$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="P7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;P$5)*(Plan!$L$5:$L$46&gt;=P$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;P$5)*(Plan!$L$5:$L$46&gt;=P$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;P$5)*(Plan!$L$5:$L$51&gt;=P$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;P$5)*(Plan!$L$5:$L$51&gt;=P$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="Q7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Q$5)*(Plan!$L$5:$L$46&gt;=Q$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Q$5)*(Plan!$L$5:$L$46&gt;=Q$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Q$5)*(Plan!$L$5:$L$51&gt;=Q$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Q$5)*(Plan!$L$5:$L$51&gt;=Q$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="R7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;R$5)*(Plan!$L$5:$L$46&gt;=R$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;R$5)*(Plan!$L$5:$L$46&gt;=R$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;R$5)*(Plan!$L$5:$L$51&gt;=R$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;R$5)*(Plan!$L$5:$L$51&gt;=R$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="S7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;S$5)*(Plan!$L$5:$L$46&gt;=S$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;S$5)*(Plan!$L$5:$L$46&gt;=S$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;S$5)*(Plan!$L$5:$L$51&gt;=S$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;S$5)*(Plan!$L$5:$L$51&gt;=S$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="T7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;T$5)*(Plan!$L$5:$L$46&gt;=T$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;T$5)*(Plan!$L$5:$L$46&gt;=T$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;T$5)*(Plan!$L$5:$L$51&gt;=T$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;T$5)*(Plan!$L$5:$L$51&gt;=T$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="U7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;U$5)*(Plan!$L$5:$L$46&gt;=U$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;U$5)*(Plan!$L$5:$L$46&gt;=U$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;U$5)*(Plan!$L$5:$L$51&gt;=U$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;U$5)*(Plan!$L$5:$L$51&gt;=U$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="V7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;V$5)*(Plan!$L$5:$L$46&gt;=V$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;V$5)*(Plan!$L$5:$L$46&gt;=V$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;V$5)*(Plan!$L$5:$L$51&gt;=V$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;V$5)*(Plan!$L$5:$L$51&gt;=V$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="W7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;W$5)*(Plan!$L$5:$L$46&gt;=W$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;W$5)*(Plan!$L$5:$L$46&gt;=W$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;W$5)*(Plan!$L$5:$L$51&gt;=W$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;W$5)*(Plan!$L$5:$L$51&gt;=W$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="X7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;X$5)*(Plan!$L$5:$L$46&gt;=X$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;X$5)*(Plan!$L$5:$L$46&gt;=X$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;X$5)*(Plan!$L$5:$L$51&gt;=X$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;X$5)*(Plan!$L$5:$L$51&gt;=X$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="Y7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Y$5)*(Plan!$L$5:$L$46&gt;=Y$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Y$5)*(Plan!$L$5:$L$46&gt;=Y$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Y$5)*(Plan!$L$5:$L$51&gt;=Y$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Y$5)*(Plan!$L$5:$L$51&gt;=Y$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="Z7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Z$5)*(Plan!$L$5:$L$46&gt;=Z$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;Z$5)*(Plan!$L$5:$L$46&gt;=Z$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Z$5)*(Plan!$L$5:$L$51&gt;=Z$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;Z$5)*(Plan!$L$5:$L$51&gt;=Z$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AA7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AA$5)*(Plan!$L$5:$L$46&gt;=AA$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AA$5)*(Plan!$L$5:$L$46&gt;=AA$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AA$5)*(Plan!$L$5:$L$51&gt;=AA$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AA$5)*(Plan!$L$5:$L$51&gt;=AA$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AB7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AB$5)*(Plan!$L$5:$L$46&gt;=AB$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AB$5)*(Plan!$L$5:$L$46&gt;=AB$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AB$5)*(Plan!$L$5:$L$51&gt;=AB$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AB$5)*(Plan!$L$5:$L$51&gt;=AB$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AC7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AC$5)*(Plan!$L$5:$L$46&gt;=AC$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AC$5)*(Plan!$L$5:$L$46&gt;=AC$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AC$5)*(Plan!$L$5:$L$51&gt;=AC$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AC$5)*(Plan!$L$5:$L$51&gt;=AC$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AD7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AD$5)*(Plan!$L$5:$L$46&gt;=AD$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AD$5)*(Plan!$L$5:$L$46&gt;=AD$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AD$5)*(Plan!$L$5:$L$51&gt;=AD$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AD$5)*(Plan!$L$5:$L$51&gt;=AD$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AE7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AE$5)*(Plan!$L$5:$L$46&gt;=AE$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AE$5)*(Plan!$L$5:$L$46&gt;=AE$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AE$5)*(Plan!$L$5:$L$51&gt;=AE$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AE$5)*(Plan!$L$5:$L$51&gt;=AE$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AF7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AF$5)*(Plan!$L$5:$L$46&gt;=AF$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AF$5)*(Plan!$L$5:$L$46&gt;=AF$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AF$5)*(Plan!$L$5:$L$51&gt;=AF$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AF$5)*(Plan!$L$5:$L$51&gt;=AF$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AG7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AG$5)*(Plan!$L$5:$L$46&gt;=AG$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AG$5)*(Plan!$L$5:$L$46&gt;=AG$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AG$5)*(Plan!$L$5:$L$51&gt;=AG$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AG$5)*(Plan!$L$5:$L$51&gt;=AG$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AH7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AH$5)*(Plan!$L$5:$L$46&gt;=AH$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AH$5)*(Plan!$L$5:$L$46&gt;=AH$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AH$5)*(Plan!$L$5:$L$51&gt;=AH$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AH$5)*(Plan!$L$5:$L$51&gt;=AH$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AI7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AI$5)*(Plan!$L$5:$L$46&gt;=AI$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AI$5)*(Plan!$L$5:$L$46&gt;=AI$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AI$5)*(Plan!$L$5:$L$51&gt;=AI$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AI$5)*(Plan!$L$5:$L$51&gt;=AI$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AJ7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AJ$5)*(Plan!$L$5:$L$46&gt;=AJ$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AJ$5)*(Plan!$L$5:$L$46&gt;=AJ$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AJ$5)*(Plan!$L$5:$L$51&gt;=AJ$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AJ$5)*(Plan!$L$5:$L$51&gt;=AJ$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AK7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AK$5)*(Plan!$L$5:$L$46&gt;=AK$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AK$5)*(Plan!$L$5:$L$46&gt;=AK$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AK$5)*(Plan!$L$5:$L$51&gt;=AK$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AK$5)*(Plan!$L$5:$L$51&gt;=AK$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AL7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AL$5)*(Plan!$L$5:$L$46&gt;=AL$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AL$5)*(Plan!$L$5:$L$46&gt;=AL$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AL$5)*(Plan!$L$5:$L$51&gt;=AL$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AL$5)*(Plan!$L$5:$L$51&gt;=AL$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AM7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AM$5)*(Plan!$L$5:$L$46&gt;=AM$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AM$5)*(Plan!$L$5:$L$46&gt;=AM$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AM$5)*(Plan!$L$5:$L$51&gt;=AM$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AM$5)*(Plan!$L$5:$L$51&gt;=AM$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AN7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AN$5)*(Plan!$L$5:$L$46&gt;=AN$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AN$5)*(Plan!$L$5:$L$46&gt;=AN$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AN$5)*(Plan!$L$5:$L$51&gt;=AN$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AN$5)*(Plan!$L$5:$L$51&gt;=AN$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AO7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AO$5)*(Plan!$L$5:$L$46&gt;=AO$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AO$5)*(Plan!$L$5:$L$46&gt;=AO$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AO$5)*(Plan!$L$5:$L$51&gt;=AO$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AO$5)*(Plan!$L$5:$L$51&gt;=AO$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AP7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AP$5)*(Plan!$L$5:$L$46&gt;=AP$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AP$5)*(Plan!$L$5:$L$46&gt;=AP$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AP$5)*(Plan!$L$5:$L$51&gt;=AP$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AP$5)*(Plan!$L$5:$L$51&gt;=AP$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AQ7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AQ$5)*(Plan!$L$5:$L$46&gt;=AQ$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AQ$5)*(Plan!$L$5:$L$46&gt;=AQ$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AQ$5)*(Plan!$L$5:$L$51&gt;=AQ$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AQ$5)*(Plan!$L$5:$L$51&gt;=AQ$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AR7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AR$5)*(Plan!$L$5:$L$46&gt;=AR$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AR$5)*(Plan!$L$5:$L$46&gt;=AR$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AR$5)*(Plan!$L$5:$L$51&gt;=AR$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AR$5)*(Plan!$L$5:$L$51&gt;=AR$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AS7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AS$5)*(Plan!$L$5:$L$46&gt;=AS$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AS$5)*(Plan!$L$5:$L$46&gt;=AS$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AS$5)*(Plan!$L$5:$L$51&gt;=AS$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AS$5)*(Plan!$L$5:$L$51&gt;=AS$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AT7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AT$5)*(Plan!$L$5:$L$46&gt;=AT$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AT$5)*(Plan!$L$5:$L$46&gt;=AT$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AT$5)*(Plan!$L$5:$L$51&gt;=AT$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AT$5)*(Plan!$L$5:$L$51&gt;=AT$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AU7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AU$5)*(Plan!$L$5:$L$46&gt;=AU$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AU$5)*(Plan!$L$5:$L$46&gt;=AU$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AU$5)*(Plan!$L$5:$L$51&gt;=AU$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AU$5)*(Plan!$L$5:$L$51&gt;=AU$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AV7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AV$5)*(Plan!$L$5:$L$46&gt;=AV$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AV$5)*(Plan!$L$5:$L$46&gt;=AV$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AV$5)*(Plan!$L$5:$L$51&gt;=AV$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AV$5)*(Plan!$L$5:$L$51&gt;=AV$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AW7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AW$5)*(Plan!$L$5:$L$46&gt;=AW$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AW$5)*(Plan!$L$5:$L$46&gt;=AW$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AW$5)*(Plan!$L$5:$L$51&gt;=AW$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AW$5)*(Plan!$L$5:$L$51&gt;=AW$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AX7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AX$5)*(Plan!$L$5:$L$46&gt;=AX$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AX$5)*(Plan!$L$5:$L$46&gt;=AX$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AX$5)*(Plan!$L$5:$L$51&gt;=AX$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AX$5)*(Plan!$L$5:$L$51&gt;=AX$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AY7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AY$5)*(Plan!$L$5:$L$46&gt;=AY$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AY$5)*(Plan!$L$5:$L$46&gt;=AY$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AY$5)*(Plan!$L$5:$L$51&gt;=AY$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AY$5)*(Plan!$L$5:$L$51&gt;=AY$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="AZ7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AZ$5)*(Plan!$L$5:$L$46&gt;=AZ$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;AZ$5)*(Plan!$L$5:$L$46&gt;=AZ$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AZ$5)*(Plan!$L$5:$L$51&gt;=AZ$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;AZ$5)*(Plan!$L$5:$L$51&gt;=AZ$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BA7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BA$5)*(Plan!$L$5:$L$46&gt;=BA$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BA$5)*(Plan!$L$5:$L$46&gt;=BA$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BA$5)*(Plan!$L$5:$L$51&gt;=BA$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BA$5)*(Plan!$L$5:$L$51&gt;=BA$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BB7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BB$5)*(Plan!$L$5:$L$46&gt;=BB$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BB$5)*(Plan!$L$5:$L$46&gt;=BB$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BB$5)*(Plan!$L$5:$L$51&gt;=BB$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BB$5)*(Plan!$L$5:$L$51&gt;=BB$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BC7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BC$5)*(Plan!$L$5:$L$46&gt;=BC$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BC$5)*(Plan!$L$5:$L$46&gt;=BC$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BC$5)*(Plan!$L$5:$L$51&gt;=BC$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BC$5)*(Plan!$L$5:$L$51&gt;=BC$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BD7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BD$5)*(Plan!$L$5:$L$46&gt;=BD$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BD$5)*(Plan!$L$5:$L$46&gt;=BD$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BD$5)*(Plan!$L$5:$L$51&gt;=BD$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BD$5)*(Plan!$L$5:$L$51&gt;=BD$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BE7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BE$5)*(Plan!$L$5:$L$46&gt;=BE$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BE$5)*(Plan!$L$5:$L$46&gt;=BE$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BE$5)*(Plan!$L$5:$L$51&gt;=BE$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BE$5)*(Plan!$L$5:$L$51&gt;=BE$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BF7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BF$5)*(Plan!$L$5:$L$46&gt;=BF$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BF$5)*(Plan!$L$5:$L$46&gt;=BF$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BF$5)*(Plan!$L$5:$L$51&gt;=BF$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BF$5)*(Plan!$L$5:$L$51&gt;=BF$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BG7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BG$5)*(Plan!$L$5:$L$46&gt;=BG$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BG$5)*(Plan!$L$5:$L$46&gt;=BG$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BG$5)*(Plan!$L$5:$L$51&gt;=BG$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BG$5)*(Plan!$L$5:$L$51&gt;=BG$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BH7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BH$5)*(Plan!$L$5:$L$46&gt;=BH$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BH$5)*(Plan!$L$5:$L$46&gt;=BH$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BH$5)*(Plan!$L$5:$L$51&gt;=BH$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BH$5)*(Plan!$L$5:$L$51&gt;=BH$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BI7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BI$5)*(Plan!$L$5:$L$46&gt;=BI$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BI$5)*(Plan!$L$5:$L$46&gt;=BI$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BI$5)*(Plan!$L$5:$L$51&gt;=BI$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BI$5)*(Plan!$L$5:$L$51&gt;=BI$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BJ7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BJ$5)*(Plan!$L$5:$L$46&gt;=BJ$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BJ$5)*(Plan!$L$5:$L$46&gt;=BJ$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BJ$5)*(Plan!$L$5:$L$51&gt;=BJ$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BJ$5)*(Plan!$L$5:$L$51&gt;=BJ$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BK7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BK$5)*(Plan!$L$5:$L$46&gt;=BK$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BK$5)*(Plan!$L$5:$L$46&gt;=BK$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BK$5)*(Plan!$L$5:$L$51&gt;=BK$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BK$5)*(Plan!$L$5:$L$51&gt;=BK$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BL7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BL$5)*(Plan!$L$5:$L$46&gt;=BL$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BL$5)*(Plan!$L$5:$L$46&gt;=BL$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BL$5)*(Plan!$L$5:$L$51&gt;=BL$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BL$5)*(Plan!$L$5:$L$51&gt;=BL$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BM7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BM$5)*(Plan!$L$5:$L$46&gt;=BM$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BM$5)*(Plan!$L$5:$L$46&gt;=BM$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BM$5)*(Plan!$L$5:$L$51&gt;=BM$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BM$5)*(Plan!$L$5:$L$51&gt;=BM$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BN7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BN$5)*(Plan!$L$5:$L$46&gt;=BN$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BN$5)*(Plan!$L$5:$L$46&gt;=BN$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BN$5)*(Plan!$L$5:$L$51&gt;=BN$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BN$5)*(Plan!$L$5:$L$51&gt;=BN$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
       <c r="BO7" s="26">
-        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BO$5)*(Plan!$L$5:$L$46&gt;=BO$5))=0,"",INDEX(Plan!$A$5:$A$46,SUMPRODUCT(((Plan!$I$5:$I$46="B")+(Plan!$I$5:$I$46="A+B"))*(Plan!$K$5:$K$46&lt;BO$5)*(Plan!$L$5:$L$46&gt;=BO$5)*(ROW(Plan!$A$5:$A$46)-4))))</f>
+        <f>IF(SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BO$5)*(Plan!$L$5:$L$51&gt;=BO$5))=0,"",INDEX(Plan!$A$5:$A$51,SUMPRODUCT(((Plan!$I$5:$I$51="B")+(Plan!$I$5:$I$51="A+B"))*(Plan!$K$5:$K$51&lt;BO$5)*(Plan!$L$5:$L$51&gt;=BO$5)*(ROW(Plan!$A$5:$A$51)-4))))</f>
         <v/>
       </c>
     </row>
@@ -8606,11 +9259,11 @@
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="28" t="n"/>
       <c r="E9" s="29">
-        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$46="1. Diseño y arquitectura")*Plan!$K$5:$K$46+(Plan!$B$5:$B$46&lt;&gt;"1. Diseño y arquitectura")*1E9))</f>
+        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$51="1. Diseño y arquitectura")*Plan!$K$5:$K$51+(Plan!$B$5:$B$51&lt;&gt;"1. Diseño y arquitectura")*1E9))</f>
         <v/>
       </c>
       <c r="F9" s="29">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="1. Diseño y arquitectura")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="1. Diseño y arquitectura")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G9" s="30">
@@ -9768,11 +10421,11 @@
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="28" t="n"/>
       <c r="E14" s="29">
-        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$46="2. Landing y autenticación")*Plan!$K$5:$K$46+(Plan!$B$5:$B$46&lt;&gt;"2. Landing y autenticación")*1E9))</f>
+        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$51="2. Landing y autenticación")*Plan!$K$5:$K$51+(Plan!$B$5:$B$51&lt;&gt;"2. Landing y autenticación")*1E9))</f>
         <v/>
       </c>
       <c r="F14" s="29">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="2. Landing y autenticación")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="2. Landing y autenticación")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G14" s="30">
@@ -12820,11 +13473,11 @@
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
       <c r="E26" s="29">
-        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$46="3. Flujo de solicitud de crédito")*Plan!$K$5:$K$46+(Plan!$B$5:$B$46&lt;&gt;"3. Flujo de solicitud de crédito")*1E9))</f>
+        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$51="3. Flujo de solicitud de crédito")*Plan!$K$5:$K$51+(Plan!$B$5:$B$51&lt;&gt;"3. Flujo de solicitud de crédito")*1E9))</f>
         <v/>
       </c>
       <c r="F26" s="29">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="3. Flujo de solicitud de crédito")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="3. Flujo de solicitud de crédito")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G26" s="30">
@@ -14792,11 +15445,11 @@
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="28" t="n"/>
       <c r="E34" s="29">
-        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$46="4. Panel de administración")*Plan!$K$5:$K$46+(Plan!$B$5:$B$46&lt;&gt;"4. Panel de administración")*1E9))</f>
+        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$51="4. Panel de administración")*Plan!$K$5:$K$51+(Plan!$B$5:$B$51&lt;&gt;"4. Panel de administración")*1E9))</f>
         <v/>
       </c>
       <c r="F34" s="29">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="4. Panel de administración")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="4. Panel de administración")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G34" s="30">
@@ -16224,11 +16877,11 @@
       <c r="C40" s="28" t="n"/>
       <c r="D40" s="28" t="n"/>
       <c r="E40" s="29">
-        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$46="5. Convenios y pulido")*Plan!$K$5:$K$46+(Plan!$B$5:$B$46&lt;&gt;"5. Convenios y pulido")*1E9))</f>
+        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$51="5. Convenios y pulido")*Plan!$K$5:$K$51+(Plan!$B$5:$B$51&lt;&gt;"5. Convenios y pulido")*1E9))</f>
         <v/>
       </c>
       <c r="F40" s="29">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="5. Convenios y pulido")*Plan!$L$5:$L$46))</f>
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="5. Convenios y pulido")*Plan!$L$5:$L$51))</f>
         <v/>
       </c>
       <c r="G40" s="30">
@@ -17647,114 +18300,302 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="27" t="inlineStr">
-        <is>
-          <t>Fase 6. Pruebas y lanzamiento</t>
-        </is>
-      </c>
-      <c r="B46" s="28" t="n"/>
-      <c r="C46" s="28" t="n"/>
-      <c r="D46" s="28" t="n"/>
-      <c r="E46" s="29">
-        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$46="6. Pruebas y lanzamiento")*Plan!$K$5:$K$46+(Plan!$B$5:$B$46&lt;&gt;"6. Pruebas y lanzamiento")*1E9))</f>
-        <v/>
-      </c>
-      <c r="F46" s="29">
-        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$46="6. Pruebas y lanzamiento")*Plan!$L$5:$L$46))</f>
-        <v/>
-      </c>
-      <c r="G46" s="30">
-        <f>Resumen!E34</f>
-        <v/>
-      </c>
-      <c r="H46" s="31" t="n"/>
-      <c r="I46" s="31" t="n"/>
-      <c r="J46" s="31" t="n"/>
-      <c r="K46" s="31" t="n"/>
-      <c r="L46" s="31" t="n"/>
-      <c r="M46" s="31" t="n"/>
-      <c r="N46" s="31" t="n"/>
-      <c r="O46" s="31" t="n"/>
-      <c r="P46" s="31" t="n"/>
-      <c r="Q46" s="31" t="n"/>
-      <c r="R46" s="31" t="n"/>
-      <c r="S46" s="31" t="n"/>
-      <c r="T46" s="31" t="n"/>
-      <c r="U46" s="31" t="n"/>
-      <c r="V46" s="31" t="n"/>
-      <c r="W46" s="31" t="n"/>
-      <c r="X46" s="31" t="n"/>
-      <c r="Y46" s="31" t="n"/>
-      <c r="Z46" s="31" t="n"/>
-      <c r="AA46" s="31" t="n"/>
-      <c r="AB46" s="31" t="n"/>
-      <c r="AC46" s="31" t="n"/>
-      <c r="AD46" s="31" t="n"/>
-      <c r="AE46" s="31" t="n"/>
-      <c r="AF46" s="31" t="n"/>
-      <c r="AG46" s="31" t="n"/>
-      <c r="AH46" s="31" t="n"/>
-      <c r="AI46" s="31" t="n"/>
-      <c r="AJ46" s="31" t="n"/>
-      <c r="AK46" s="31" t="n"/>
-      <c r="AL46" s="31" t="n"/>
-      <c r="AM46" s="31" t="n"/>
-      <c r="AN46" s="31" t="n"/>
-      <c r="AO46" s="31" t="n"/>
-      <c r="AP46" s="31" t="n"/>
-      <c r="AQ46" s="31" t="n"/>
-      <c r="AR46" s="31" t="n"/>
-      <c r="AS46" s="31" t="n"/>
-      <c r="AT46" s="31" t="n"/>
-      <c r="AU46" s="31" t="n"/>
-      <c r="AV46" s="31" t="n"/>
-      <c r="AW46" s="31" t="n"/>
-      <c r="AX46" s="31" t="n"/>
-      <c r="AY46" s="31" t="n"/>
-      <c r="AZ46" s="31" t="n"/>
-      <c r="BA46" s="31" t="n"/>
-      <c r="BB46" s="31" t="n"/>
-      <c r="BC46" s="31" t="n"/>
-      <c r="BD46" s="31" t="n"/>
-      <c r="BE46" s="31" t="n"/>
-      <c r="BF46" s="31" t="n"/>
-      <c r="BG46" s="31" t="n"/>
-      <c r="BH46" s="31" t="n"/>
-      <c r="BI46" s="31" t="n"/>
-      <c r="BJ46" s="31" t="n"/>
-      <c r="BK46" s="31" t="n"/>
-      <c r="BL46" s="31" t="n"/>
-      <c r="BM46" s="31" t="n"/>
-      <c r="BN46" s="31" t="n"/>
-      <c r="BO46" s="31" t="n"/>
+      <c r="A46" s="32">
+        <f>Plan!A37</f>
+        <v/>
+      </c>
+      <c r="B46" s="33">
+        <f>Plan!C37</f>
+        <v/>
+      </c>
+      <c r="C46" s="16">
+        <f>Plan!D37</f>
+        <v/>
+      </c>
+      <c r="D46" s="16">
+        <f>Plan!I37</f>
+        <v/>
+      </c>
+      <c r="E46" s="16">
+        <f>Plan!K37</f>
+        <v/>
+      </c>
+      <c r="F46" s="16">
+        <f>Plan!L37</f>
+        <v/>
+      </c>
+      <c r="G46" s="16">
+        <f>Plan!O37</f>
+        <v/>
+      </c>
+      <c r="H46" s="34">
+        <f>IF(AND(H$5&gt;$E46,H$5&lt;=$F46),IF(H$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="34">
+        <f>IF(AND(I$5&gt;$E46,I$5&lt;=$F46),IF(I$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="34">
+        <f>IF(AND(J$5&gt;$E46,J$5&lt;=$F46),IF(J$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="K46" s="34">
+        <f>IF(AND(K$5&gt;$E46,K$5&lt;=$F46),IF(K$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="34">
+        <f>IF(AND(L$5&gt;$E46,L$5&lt;=$F46),IF(L$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="34">
+        <f>IF(AND(M$5&gt;$E46,M$5&lt;=$F46),IF(M$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="N46" s="34">
+        <f>IF(AND(N$5&gt;$E46,N$5&lt;=$F46),IF(N$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="O46" s="34">
+        <f>IF(AND(O$5&gt;$E46,O$5&lt;=$F46),IF(O$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="P46" s="34">
+        <f>IF(AND(P$5&gt;$E46,P$5&lt;=$F46),IF(P$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="Q46" s="34">
+        <f>IF(AND(Q$5&gt;$E46,Q$5&lt;=$F46),IF(Q$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="R46" s="34">
+        <f>IF(AND(R$5&gt;$E46,R$5&lt;=$F46),IF(R$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="S46" s="34">
+        <f>IF(AND(S$5&gt;$E46,S$5&lt;=$F46),IF(S$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="T46" s="34">
+        <f>IF(AND(T$5&gt;$E46,T$5&lt;=$F46),IF(T$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="U46" s="34">
+        <f>IF(AND(U$5&gt;$E46,U$5&lt;=$F46),IF(U$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="V46" s="34">
+        <f>IF(AND(V$5&gt;$E46,V$5&lt;=$F46),IF(V$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="W46" s="34">
+        <f>IF(AND(W$5&gt;$E46,W$5&lt;=$F46),IF(W$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="X46" s="34">
+        <f>IF(AND(X$5&gt;$E46,X$5&lt;=$F46),IF(X$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="Y46" s="34">
+        <f>IF(AND(Y$5&gt;$E46,Y$5&lt;=$F46),IF(Y$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="Z46" s="34">
+        <f>IF(AND(Z$5&gt;$E46,Z$5&lt;=$F46),IF(Z$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AA46" s="34">
+        <f>IF(AND(AA$5&gt;$E46,AA$5&lt;=$F46),IF(AA$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AB46" s="34">
+        <f>IF(AND(AB$5&gt;$E46,AB$5&lt;=$F46),IF(AB$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AC46" s="34">
+        <f>IF(AND(AC$5&gt;$E46,AC$5&lt;=$F46),IF(AC$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AD46" s="34">
+        <f>IF(AND(AD$5&gt;$E46,AD$5&lt;=$F46),IF(AD$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AE46" s="34">
+        <f>IF(AND(AE$5&gt;$E46,AE$5&lt;=$F46),IF(AE$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AF46" s="34">
+        <f>IF(AND(AF$5&gt;$E46,AF$5&lt;=$F46),IF(AF$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AG46" s="34">
+        <f>IF(AND(AG$5&gt;$E46,AG$5&lt;=$F46),IF(AG$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AH46" s="34">
+        <f>IF(AND(AH$5&gt;$E46,AH$5&lt;=$F46),IF(AH$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AI46" s="34">
+        <f>IF(AND(AI$5&gt;$E46,AI$5&lt;=$F46),IF(AI$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AJ46" s="34">
+        <f>IF(AND(AJ$5&gt;$E46,AJ$5&lt;=$F46),IF(AJ$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AK46" s="34">
+        <f>IF(AND(AK$5&gt;$E46,AK$5&lt;=$F46),IF(AK$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AL46" s="34">
+        <f>IF(AND(AL$5&gt;$E46,AL$5&lt;=$F46),IF(AL$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AM46" s="34">
+        <f>IF(AND(AM$5&gt;$E46,AM$5&lt;=$F46),IF(AM$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AN46" s="34">
+        <f>IF(AND(AN$5&gt;$E46,AN$5&lt;=$F46),IF(AN$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AO46" s="34">
+        <f>IF(AND(AO$5&gt;$E46,AO$5&lt;=$F46),IF(AO$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AP46" s="34">
+        <f>IF(AND(AP$5&gt;$E46,AP$5&lt;=$F46),IF(AP$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AQ46" s="34">
+        <f>IF(AND(AQ$5&gt;$E46,AQ$5&lt;=$F46),IF(AQ$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AR46" s="34">
+        <f>IF(AND(AR$5&gt;$E46,AR$5&lt;=$F46),IF(AR$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AS46" s="34">
+        <f>IF(AND(AS$5&gt;$E46,AS$5&lt;=$F46),IF(AS$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AT46" s="34">
+        <f>IF(AND(AT$5&gt;$E46,AT$5&lt;=$F46),IF(AT$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AU46" s="34">
+        <f>IF(AND(AU$5&gt;$E46,AU$5&lt;=$F46),IF(AU$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AV46" s="34">
+        <f>IF(AND(AV$5&gt;$E46,AV$5&lt;=$F46),IF(AV$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AW46" s="34">
+        <f>IF(AND(AW$5&gt;$E46,AW$5&lt;=$F46),IF(AW$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AX46" s="34">
+        <f>IF(AND(AX$5&gt;$E46,AX$5&lt;=$F46),IF(AX$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AY46" s="34">
+        <f>IF(AND(AY$5&gt;$E46,AY$5&lt;=$F46),IF(AY$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="AZ46" s="34">
+        <f>IF(AND(AZ$5&gt;$E46,AZ$5&lt;=$F46),IF(AZ$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BA46" s="34">
+        <f>IF(AND(BA$5&gt;$E46,BA$5&lt;=$F46),IF(BA$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BB46" s="34">
+        <f>IF(AND(BB$5&gt;$E46,BB$5&lt;=$F46),IF(BB$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BC46" s="34">
+        <f>IF(AND(BC$5&gt;$E46,BC$5&lt;=$F46),IF(BC$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BD46" s="34">
+        <f>IF(AND(BD$5&gt;$E46,BD$5&lt;=$F46),IF(BD$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BE46" s="34">
+        <f>IF(AND(BE$5&gt;$E46,BE$5&lt;=$F46),IF(BE$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BF46" s="34">
+        <f>IF(AND(BF$5&gt;$E46,BF$5&lt;=$F46),IF(BF$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BG46" s="34">
+        <f>IF(AND(BG$5&gt;$E46,BG$5&lt;=$F46),IF(BG$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BH46" s="34">
+        <f>IF(AND(BH$5&gt;$E46,BH$5&lt;=$F46),IF(BH$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BI46" s="34">
+        <f>IF(AND(BI$5&gt;$E46,BI$5&lt;=$F46),IF(BI$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BJ46" s="34">
+        <f>IF(AND(BJ$5&gt;$E46,BJ$5&lt;=$F46),IF(BJ$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BK46" s="34">
+        <f>IF(AND(BK$5&gt;$E46,BK$5&lt;=$F46),IF(BK$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BL46" s="34">
+        <f>IF(AND(BL$5&gt;$E46,BL$5&lt;=$F46),IF(BL$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BM46" s="34">
+        <f>IF(AND(BM$5&gt;$E46,BM$5&lt;=$F46),IF(BM$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BN46" s="34">
+        <f>IF(AND(BN$5&gt;$E46,BN$5&lt;=$F46),IF(BN$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
+      <c r="BO46" s="34">
+        <f>IF(AND(BO$5&gt;$E46,BO$5&lt;=$F46),IF(BO$5=$E46+1,$C46,""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="32">
-        <f>Plan!A37</f>
+        <f>Plan!A38</f>
         <v/>
       </c>
       <c r="B47" s="33">
-        <f>Plan!C37</f>
+        <f>Plan!C38</f>
         <v/>
       </c>
       <c r="C47" s="16">
-        <f>Plan!D37</f>
+        <f>Plan!D38</f>
         <v/>
       </c>
       <c r="D47" s="16">
-        <f>Plan!I37</f>
+        <f>Plan!I38</f>
         <v/>
       </c>
       <c r="E47" s="16">
-        <f>Plan!K37</f>
+        <f>Plan!K38</f>
         <v/>
       </c>
       <c r="F47" s="16">
-        <f>Plan!L37</f>
+        <f>Plan!L38</f>
         <v/>
       </c>
       <c r="G47" s="16">
-        <f>Plan!O37</f>
+        <f>Plan!O38</f>
         <v/>
       </c>
       <c r="H47" s="34">
@@ -18000,31 +18841,31 @@
     </row>
     <row r="48">
       <c r="A48" s="32">
-        <f>Plan!A38</f>
+        <f>Plan!A39</f>
         <v/>
       </c>
       <c r="B48" s="33">
-        <f>Plan!C38</f>
+        <f>Plan!C39</f>
         <v/>
       </c>
       <c r="C48" s="16">
-        <f>Plan!D38</f>
+        <f>Plan!D39</f>
         <v/>
       </c>
       <c r="D48" s="16">
-        <f>Plan!I38</f>
+        <f>Plan!I39</f>
         <v/>
       </c>
       <c r="E48" s="16">
-        <f>Plan!K38</f>
+        <f>Plan!K39</f>
         <v/>
       </c>
       <c r="F48" s="16">
-        <f>Plan!L38</f>
+        <f>Plan!L39</f>
         <v/>
       </c>
       <c r="G48" s="16">
-        <f>Plan!O38</f>
+        <f>Plan!O39</f>
         <v/>
       </c>
       <c r="H48" s="34">
@@ -18269,274 +19110,86 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="32">
-        <f>Plan!A39</f>
-        <v/>
-      </c>
-      <c r="B49" s="33">
-        <f>Plan!C39</f>
-        <v/>
-      </c>
-      <c r="C49" s="16">
-        <f>Plan!D39</f>
-        <v/>
-      </c>
-      <c r="D49" s="16">
-        <f>Plan!I39</f>
-        <v/>
-      </c>
-      <c r="E49" s="16">
-        <f>Plan!K39</f>
-        <v/>
-      </c>
-      <c r="F49" s="16">
-        <f>Plan!L39</f>
-        <v/>
-      </c>
-      <c r="G49" s="16">
-        <f>Plan!O39</f>
-        <v/>
-      </c>
-      <c r="H49" s="34">
-        <f>IF(AND(H$5&gt;$E49,H$5&lt;=$F49),IF(H$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="34">
-        <f>IF(AND(I$5&gt;$E49,I$5&lt;=$F49),IF(I$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="34">
-        <f>IF(AND(J$5&gt;$E49,J$5&lt;=$F49),IF(J$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="K49" s="34">
-        <f>IF(AND(K$5&gt;$E49,K$5&lt;=$F49),IF(K$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="L49" s="34">
-        <f>IF(AND(L$5&gt;$E49,L$5&lt;=$F49),IF(L$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="34">
-        <f>IF(AND(M$5&gt;$E49,M$5&lt;=$F49),IF(M$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="N49" s="34">
-        <f>IF(AND(N$5&gt;$E49,N$5&lt;=$F49),IF(N$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="O49" s="34">
-        <f>IF(AND(O$5&gt;$E49,O$5&lt;=$F49),IF(O$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="P49" s="34">
-        <f>IF(AND(P$5&gt;$E49,P$5&lt;=$F49),IF(P$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="Q49" s="34">
-        <f>IF(AND(Q$5&gt;$E49,Q$5&lt;=$F49),IF(Q$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="R49" s="34">
-        <f>IF(AND(R$5&gt;$E49,R$5&lt;=$F49),IF(R$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="S49" s="34">
-        <f>IF(AND(S$5&gt;$E49,S$5&lt;=$F49),IF(S$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="T49" s="34">
-        <f>IF(AND(T$5&gt;$E49,T$5&lt;=$F49),IF(T$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="U49" s="34">
-        <f>IF(AND(U$5&gt;$E49,U$5&lt;=$F49),IF(U$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="V49" s="34">
-        <f>IF(AND(V$5&gt;$E49,V$5&lt;=$F49),IF(V$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="W49" s="34">
-        <f>IF(AND(W$5&gt;$E49,W$5&lt;=$F49),IF(W$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="X49" s="34">
-        <f>IF(AND(X$5&gt;$E49,X$5&lt;=$F49),IF(X$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="Y49" s="34">
-        <f>IF(AND(Y$5&gt;$E49,Y$5&lt;=$F49),IF(Y$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="Z49" s="34">
-        <f>IF(AND(Z$5&gt;$E49,Z$5&lt;=$F49),IF(Z$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AA49" s="34">
-        <f>IF(AND(AA$5&gt;$E49,AA$5&lt;=$F49),IF(AA$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AB49" s="34">
-        <f>IF(AND(AB$5&gt;$E49,AB$5&lt;=$F49),IF(AB$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AC49" s="34">
-        <f>IF(AND(AC$5&gt;$E49,AC$5&lt;=$F49),IF(AC$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AD49" s="34">
-        <f>IF(AND(AD$5&gt;$E49,AD$5&lt;=$F49),IF(AD$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AE49" s="34">
-        <f>IF(AND(AE$5&gt;$E49,AE$5&lt;=$F49),IF(AE$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AF49" s="34">
-        <f>IF(AND(AF$5&gt;$E49,AF$5&lt;=$F49),IF(AF$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AG49" s="34">
-        <f>IF(AND(AG$5&gt;$E49,AG$5&lt;=$F49),IF(AG$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AH49" s="34">
-        <f>IF(AND(AH$5&gt;$E49,AH$5&lt;=$F49),IF(AH$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AI49" s="34">
-        <f>IF(AND(AI$5&gt;$E49,AI$5&lt;=$F49),IF(AI$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AJ49" s="34">
-        <f>IF(AND(AJ$5&gt;$E49,AJ$5&lt;=$F49),IF(AJ$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AK49" s="34">
-        <f>IF(AND(AK$5&gt;$E49,AK$5&lt;=$F49),IF(AK$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AL49" s="34">
-        <f>IF(AND(AL$5&gt;$E49,AL$5&lt;=$F49),IF(AL$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AM49" s="34">
-        <f>IF(AND(AM$5&gt;$E49,AM$5&lt;=$F49),IF(AM$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AN49" s="34">
-        <f>IF(AND(AN$5&gt;$E49,AN$5&lt;=$F49),IF(AN$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AO49" s="34">
-        <f>IF(AND(AO$5&gt;$E49,AO$5&lt;=$F49),IF(AO$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AP49" s="34">
-        <f>IF(AND(AP$5&gt;$E49,AP$5&lt;=$F49),IF(AP$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AQ49" s="34">
-        <f>IF(AND(AQ$5&gt;$E49,AQ$5&lt;=$F49),IF(AQ$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AR49" s="34">
-        <f>IF(AND(AR$5&gt;$E49,AR$5&lt;=$F49),IF(AR$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AS49" s="34">
-        <f>IF(AND(AS$5&gt;$E49,AS$5&lt;=$F49),IF(AS$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AT49" s="34">
-        <f>IF(AND(AT$5&gt;$E49,AT$5&lt;=$F49),IF(AT$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AU49" s="34">
-        <f>IF(AND(AU$5&gt;$E49,AU$5&lt;=$F49),IF(AU$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AV49" s="34">
-        <f>IF(AND(AV$5&gt;$E49,AV$5&lt;=$F49),IF(AV$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AW49" s="34">
-        <f>IF(AND(AW$5&gt;$E49,AW$5&lt;=$F49),IF(AW$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AX49" s="34">
-        <f>IF(AND(AX$5&gt;$E49,AX$5&lt;=$F49),IF(AX$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AY49" s="34">
-        <f>IF(AND(AY$5&gt;$E49,AY$5&lt;=$F49),IF(AY$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="AZ49" s="34">
-        <f>IF(AND(AZ$5&gt;$E49,AZ$5&lt;=$F49),IF(AZ$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BA49" s="34">
-        <f>IF(AND(BA$5&gt;$E49,BA$5&lt;=$F49),IF(BA$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BB49" s="34">
-        <f>IF(AND(BB$5&gt;$E49,BB$5&lt;=$F49),IF(BB$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BC49" s="34">
-        <f>IF(AND(BC$5&gt;$E49,BC$5&lt;=$F49),IF(BC$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BD49" s="34">
-        <f>IF(AND(BD$5&gt;$E49,BD$5&lt;=$F49),IF(BD$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BE49" s="34">
-        <f>IF(AND(BE$5&gt;$E49,BE$5&lt;=$F49),IF(BE$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BF49" s="34">
-        <f>IF(AND(BF$5&gt;$E49,BF$5&lt;=$F49),IF(BF$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BG49" s="34">
-        <f>IF(AND(BG$5&gt;$E49,BG$5&lt;=$F49),IF(BG$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BH49" s="34">
-        <f>IF(AND(BH$5&gt;$E49,BH$5&lt;=$F49),IF(BH$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BI49" s="34">
-        <f>IF(AND(BI$5&gt;$E49,BI$5&lt;=$F49),IF(BI$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BJ49" s="34">
-        <f>IF(AND(BJ$5&gt;$E49,BJ$5&lt;=$F49),IF(BJ$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BK49" s="34">
-        <f>IF(AND(BK$5&gt;$E49,BK$5&lt;=$F49),IF(BK$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BL49" s="34">
-        <f>IF(AND(BL$5&gt;$E49,BL$5&lt;=$F49),IF(BL$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BM49" s="34">
-        <f>IF(AND(BM$5&gt;$E49,BM$5&lt;=$F49),IF(BM$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BN49" s="34">
-        <f>IF(AND(BN$5&gt;$E49,BN$5&lt;=$F49),IF(BN$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
-      <c r="BO49" s="34">
-        <f>IF(AND(BO$5&gt;$E49,BO$5&lt;=$F49),IF(BO$5=$E49+1,$C49,""),"")</f>
-        <v/>
-      </c>
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>Fase 6. Pruebas y lanzamiento</t>
+        </is>
+      </c>
+      <c r="B49" s="28" t="n"/>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="29">
+        <f>SUMPRODUCT(MIN((Plan!$B$5:$B$51="6. Pruebas y lanzamiento")*Plan!$K$5:$K$51+(Plan!$B$5:$B$51&lt;&gt;"6. Pruebas y lanzamiento")*1E9))</f>
+        <v/>
+      </c>
+      <c r="F49" s="29">
+        <f>SUMPRODUCT(MAX((Plan!$B$5:$B$51="6. Pruebas y lanzamiento")*Plan!$L$5:$L$51))</f>
+        <v/>
+      </c>
+      <c r="G49" s="30">
+        <f>Resumen!E34</f>
+        <v/>
+      </c>
+      <c r="H49" s="31" t="n"/>
+      <c r="I49" s="31" t="n"/>
+      <c r="J49" s="31" t="n"/>
+      <c r="K49" s="31" t="n"/>
+      <c r="L49" s="31" t="n"/>
+      <c r="M49" s="31" t="n"/>
+      <c r="N49" s="31" t="n"/>
+      <c r="O49" s="31" t="n"/>
+      <c r="P49" s="31" t="n"/>
+      <c r="Q49" s="31" t="n"/>
+      <c r="R49" s="31" t="n"/>
+      <c r="S49" s="31" t="n"/>
+      <c r="T49" s="31" t="n"/>
+      <c r="U49" s="31" t="n"/>
+      <c r="V49" s="31" t="n"/>
+      <c r="W49" s="31" t="n"/>
+      <c r="X49" s="31" t="n"/>
+      <c r="Y49" s="31" t="n"/>
+      <c r="Z49" s="31" t="n"/>
+      <c r="AA49" s="31" t="n"/>
+      <c r="AB49" s="31" t="n"/>
+      <c r="AC49" s="31" t="n"/>
+      <c r="AD49" s="31" t="n"/>
+      <c r="AE49" s="31" t="n"/>
+      <c r="AF49" s="31" t="n"/>
+      <c r="AG49" s="31" t="n"/>
+      <c r="AH49" s="31" t="n"/>
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="n"/>
+      <c r="AK49" s="31" t="n"/>
+      <c r="AL49" s="31" t="n"/>
+      <c r="AM49" s="31" t="n"/>
+      <c r="AN49" s="31" t="n"/>
+      <c r="AO49" s="31" t="n"/>
+      <c r="AP49" s="31" t="n"/>
+      <c r="AQ49" s="31" t="n"/>
+      <c r="AR49" s="31" t="n"/>
+      <c r="AS49" s="31" t="n"/>
+      <c r="AT49" s="31" t="n"/>
+      <c r="AU49" s="31" t="n"/>
+      <c r="AV49" s="31" t="n"/>
+      <c r="AW49" s="31" t="n"/>
+      <c r="AX49" s="31" t="n"/>
+      <c r="AY49" s="31" t="n"/>
+      <c r="AZ49" s="31" t="n"/>
+      <c r="BA49" s="31" t="n"/>
+      <c r="BB49" s="31" t="n"/>
+      <c r="BC49" s="31" t="n"/>
+      <c r="BD49" s="31" t="n"/>
+      <c r="BE49" s="31" t="n"/>
+      <c r="BF49" s="31" t="n"/>
+      <c r="BG49" s="31" t="n"/>
+      <c r="BH49" s="31" t="n"/>
+      <c r="BI49" s="31" t="n"/>
+      <c r="BJ49" s="31" t="n"/>
+      <c r="BK49" s="31" t="n"/>
+      <c r="BL49" s="31" t="n"/>
+      <c r="BM49" s="31" t="n"/>
+      <c r="BN49" s="31" t="n"/>
+      <c r="BO49" s="31" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="32">
@@ -20428,9 +21081,1358 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="32">
+        <f>Plan!A47</f>
+        <v/>
+      </c>
+      <c r="B57" s="33">
+        <f>Plan!C47</f>
+        <v/>
+      </c>
+      <c r="C57" s="16">
+        <f>Plan!D47</f>
+        <v/>
+      </c>
+      <c r="D57" s="16">
+        <f>Plan!I47</f>
+        <v/>
+      </c>
+      <c r="E57" s="16">
+        <f>Plan!K47</f>
+        <v/>
+      </c>
+      <c r="F57" s="16">
+        <f>Plan!L47</f>
+        <v/>
+      </c>
+      <c r="G57" s="16">
+        <f>Plan!O47</f>
+        <v/>
+      </c>
+      <c r="H57" s="34">
+        <f>IF(AND(H$5&gt;$E57,H$5&lt;=$F57),IF(H$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="I57" s="34">
+        <f>IF(AND(I$5&gt;$E57,I$5&lt;=$F57),IF(I$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="J57" s="34">
+        <f>IF(AND(J$5&gt;$E57,J$5&lt;=$F57),IF(J$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="K57" s="34">
+        <f>IF(AND(K$5&gt;$E57,K$5&lt;=$F57),IF(K$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="L57" s="34">
+        <f>IF(AND(L$5&gt;$E57,L$5&lt;=$F57),IF(L$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="34">
+        <f>IF(AND(M$5&gt;$E57,M$5&lt;=$F57),IF(M$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="N57" s="34">
+        <f>IF(AND(N$5&gt;$E57,N$5&lt;=$F57),IF(N$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="O57" s="34">
+        <f>IF(AND(O$5&gt;$E57,O$5&lt;=$F57),IF(O$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="P57" s="34">
+        <f>IF(AND(P$5&gt;$E57,P$5&lt;=$F57),IF(P$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="Q57" s="34">
+        <f>IF(AND(Q$5&gt;$E57,Q$5&lt;=$F57),IF(Q$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="R57" s="34">
+        <f>IF(AND(R$5&gt;$E57,R$5&lt;=$F57),IF(R$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="S57" s="34">
+        <f>IF(AND(S$5&gt;$E57,S$5&lt;=$F57),IF(S$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="T57" s="34">
+        <f>IF(AND(T$5&gt;$E57,T$5&lt;=$F57),IF(T$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="U57" s="34">
+        <f>IF(AND(U$5&gt;$E57,U$5&lt;=$F57),IF(U$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="V57" s="34">
+        <f>IF(AND(V$5&gt;$E57,V$5&lt;=$F57),IF(V$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="W57" s="34">
+        <f>IF(AND(W$5&gt;$E57,W$5&lt;=$F57),IF(W$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="X57" s="34">
+        <f>IF(AND(X$5&gt;$E57,X$5&lt;=$F57),IF(X$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="Y57" s="34">
+        <f>IF(AND(Y$5&gt;$E57,Y$5&lt;=$F57),IF(Y$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="Z57" s="34">
+        <f>IF(AND(Z$5&gt;$E57,Z$5&lt;=$F57),IF(Z$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AA57" s="34">
+        <f>IF(AND(AA$5&gt;$E57,AA$5&lt;=$F57),IF(AA$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AB57" s="34">
+        <f>IF(AND(AB$5&gt;$E57,AB$5&lt;=$F57),IF(AB$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AC57" s="34">
+        <f>IF(AND(AC$5&gt;$E57,AC$5&lt;=$F57),IF(AC$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AD57" s="34">
+        <f>IF(AND(AD$5&gt;$E57,AD$5&lt;=$F57),IF(AD$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AE57" s="34">
+        <f>IF(AND(AE$5&gt;$E57,AE$5&lt;=$F57),IF(AE$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AF57" s="34">
+        <f>IF(AND(AF$5&gt;$E57,AF$5&lt;=$F57),IF(AF$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AG57" s="34">
+        <f>IF(AND(AG$5&gt;$E57,AG$5&lt;=$F57),IF(AG$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AH57" s="34">
+        <f>IF(AND(AH$5&gt;$E57,AH$5&lt;=$F57),IF(AH$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AI57" s="34">
+        <f>IF(AND(AI$5&gt;$E57,AI$5&lt;=$F57),IF(AI$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AJ57" s="34">
+        <f>IF(AND(AJ$5&gt;$E57,AJ$5&lt;=$F57),IF(AJ$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AK57" s="34">
+        <f>IF(AND(AK$5&gt;$E57,AK$5&lt;=$F57),IF(AK$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AL57" s="34">
+        <f>IF(AND(AL$5&gt;$E57,AL$5&lt;=$F57),IF(AL$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AM57" s="34">
+        <f>IF(AND(AM$5&gt;$E57,AM$5&lt;=$F57),IF(AM$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AN57" s="34">
+        <f>IF(AND(AN$5&gt;$E57,AN$5&lt;=$F57),IF(AN$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AO57" s="34">
+        <f>IF(AND(AO$5&gt;$E57,AO$5&lt;=$F57),IF(AO$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AP57" s="34">
+        <f>IF(AND(AP$5&gt;$E57,AP$5&lt;=$F57),IF(AP$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AQ57" s="34">
+        <f>IF(AND(AQ$5&gt;$E57,AQ$5&lt;=$F57),IF(AQ$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AR57" s="34">
+        <f>IF(AND(AR$5&gt;$E57,AR$5&lt;=$F57),IF(AR$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AS57" s="34">
+        <f>IF(AND(AS$5&gt;$E57,AS$5&lt;=$F57),IF(AS$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AT57" s="34">
+        <f>IF(AND(AT$5&gt;$E57,AT$5&lt;=$F57),IF(AT$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AU57" s="34">
+        <f>IF(AND(AU$5&gt;$E57,AU$5&lt;=$F57),IF(AU$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AV57" s="34">
+        <f>IF(AND(AV$5&gt;$E57,AV$5&lt;=$F57),IF(AV$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AW57" s="34">
+        <f>IF(AND(AW$5&gt;$E57,AW$5&lt;=$F57),IF(AW$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AX57" s="34">
+        <f>IF(AND(AX$5&gt;$E57,AX$5&lt;=$F57),IF(AX$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AY57" s="34">
+        <f>IF(AND(AY$5&gt;$E57,AY$5&lt;=$F57),IF(AY$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="AZ57" s="34">
+        <f>IF(AND(AZ$5&gt;$E57,AZ$5&lt;=$F57),IF(AZ$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BA57" s="34">
+        <f>IF(AND(BA$5&gt;$E57,BA$5&lt;=$F57),IF(BA$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BB57" s="34">
+        <f>IF(AND(BB$5&gt;$E57,BB$5&lt;=$F57),IF(BB$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BC57" s="34">
+        <f>IF(AND(BC$5&gt;$E57,BC$5&lt;=$F57),IF(BC$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BD57" s="34">
+        <f>IF(AND(BD$5&gt;$E57,BD$5&lt;=$F57),IF(BD$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BE57" s="34">
+        <f>IF(AND(BE$5&gt;$E57,BE$5&lt;=$F57),IF(BE$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BF57" s="34">
+        <f>IF(AND(BF$5&gt;$E57,BF$5&lt;=$F57),IF(BF$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BG57" s="34">
+        <f>IF(AND(BG$5&gt;$E57,BG$5&lt;=$F57),IF(BG$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BH57" s="34">
+        <f>IF(AND(BH$5&gt;$E57,BH$5&lt;=$F57),IF(BH$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BI57" s="34">
+        <f>IF(AND(BI$5&gt;$E57,BI$5&lt;=$F57),IF(BI$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BJ57" s="34">
+        <f>IF(AND(BJ$5&gt;$E57,BJ$5&lt;=$F57),IF(BJ$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BK57" s="34">
+        <f>IF(AND(BK$5&gt;$E57,BK$5&lt;=$F57),IF(BK$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BL57" s="34">
+        <f>IF(AND(BL$5&gt;$E57,BL$5&lt;=$F57),IF(BL$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BM57" s="34">
+        <f>IF(AND(BM$5&gt;$E57,BM$5&lt;=$F57),IF(BM$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BN57" s="34">
+        <f>IF(AND(BN$5&gt;$E57,BN$5&lt;=$F57),IF(BN$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+      <c r="BO57" s="34">
+        <f>IF(AND(BO$5&gt;$E57,BO$5&lt;=$F57),IF(BO$5=$E57+1,$C57,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32">
+        <f>Plan!A48</f>
+        <v/>
+      </c>
+      <c r="B58" s="33">
+        <f>Plan!C48</f>
+        <v/>
+      </c>
+      <c r="C58" s="16">
+        <f>Plan!D48</f>
+        <v/>
+      </c>
+      <c r="D58" s="16">
+        <f>Plan!I48</f>
+        <v/>
+      </c>
+      <c r="E58" s="16">
+        <f>Plan!K48</f>
+        <v/>
+      </c>
+      <c r="F58" s="16">
+        <f>Plan!L48</f>
+        <v/>
+      </c>
+      <c r="G58" s="16">
+        <f>Plan!O48</f>
+        <v/>
+      </c>
+      <c r="H58" s="34">
+        <f>IF(AND(H$5&gt;$E58,H$5&lt;=$F58),IF(H$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="I58" s="34">
+        <f>IF(AND(I$5&gt;$E58,I$5&lt;=$F58),IF(I$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="J58" s="34">
+        <f>IF(AND(J$5&gt;$E58,J$5&lt;=$F58),IF(J$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="K58" s="34">
+        <f>IF(AND(K$5&gt;$E58,K$5&lt;=$F58),IF(K$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="L58" s="34">
+        <f>IF(AND(L$5&gt;$E58,L$5&lt;=$F58),IF(L$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="34">
+        <f>IF(AND(M$5&gt;$E58,M$5&lt;=$F58),IF(M$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="N58" s="34">
+        <f>IF(AND(N$5&gt;$E58,N$5&lt;=$F58),IF(N$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="O58" s="34">
+        <f>IF(AND(O$5&gt;$E58,O$5&lt;=$F58),IF(O$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="P58" s="34">
+        <f>IF(AND(P$5&gt;$E58,P$5&lt;=$F58),IF(P$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="Q58" s="34">
+        <f>IF(AND(Q$5&gt;$E58,Q$5&lt;=$F58),IF(Q$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="R58" s="34">
+        <f>IF(AND(R$5&gt;$E58,R$5&lt;=$F58),IF(R$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="S58" s="34">
+        <f>IF(AND(S$5&gt;$E58,S$5&lt;=$F58),IF(S$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="T58" s="34">
+        <f>IF(AND(T$5&gt;$E58,T$5&lt;=$F58),IF(T$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="U58" s="34">
+        <f>IF(AND(U$5&gt;$E58,U$5&lt;=$F58),IF(U$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="V58" s="34">
+        <f>IF(AND(V$5&gt;$E58,V$5&lt;=$F58),IF(V$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="W58" s="34">
+        <f>IF(AND(W$5&gt;$E58,W$5&lt;=$F58),IF(W$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="X58" s="34">
+        <f>IF(AND(X$5&gt;$E58,X$5&lt;=$F58),IF(X$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="Y58" s="34">
+        <f>IF(AND(Y$5&gt;$E58,Y$5&lt;=$F58),IF(Y$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="Z58" s="34">
+        <f>IF(AND(Z$5&gt;$E58,Z$5&lt;=$F58),IF(Z$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AA58" s="34">
+        <f>IF(AND(AA$5&gt;$E58,AA$5&lt;=$F58),IF(AA$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AB58" s="34">
+        <f>IF(AND(AB$5&gt;$E58,AB$5&lt;=$F58),IF(AB$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AC58" s="34">
+        <f>IF(AND(AC$5&gt;$E58,AC$5&lt;=$F58),IF(AC$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AD58" s="34">
+        <f>IF(AND(AD$5&gt;$E58,AD$5&lt;=$F58),IF(AD$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AE58" s="34">
+        <f>IF(AND(AE$5&gt;$E58,AE$5&lt;=$F58),IF(AE$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AF58" s="34">
+        <f>IF(AND(AF$5&gt;$E58,AF$5&lt;=$F58),IF(AF$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AG58" s="34">
+        <f>IF(AND(AG$5&gt;$E58,AG$5&lt;=$F58),IF(AG$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AH58" s="34">
+        <f>IF(AND(AH$5&gt;$E58,AH$5&lt;=$F58),IF(AH$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AI58" s="34">
+        <f>IF(AND(AI$5&gt;$E58,AI$5&lt;=$F58),IF(AI$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AJ58" s="34">
+        <f>IF(AND(AJ$5&gt;$E58,AJ$5&lt;=$F58),IF(AJ$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AK58" s="34">
+        <f>IF(AND(AK$5&gt;$E58,AK$5&lt;=$F58),IF(AK$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AL58" s="34">
+        <f>IF(AND(AL$5&gt;$E58,AL$5&lt;=$F58),IF(AL$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AM58" s="34">
+        <f>IF(AND(AM$5&gt;$E58,AM$5&lt;=$F58),IF(AM$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AN58" s="34">
+        <f>IF(AND(AN$5&gt;$E58,AN$5&lt;=$F58),IF(AN$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AO58" s="34">
+        <f>IF(AND(AO$5&gt;$E58,AO$5&lt;=$F58),IF(AO$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AP58" s="34">
+        <f>IF(AND(AP$5&gt;$E58,AP$5&lt;=$F58),IF(AP$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AQ58" s="34">
+        <f>IF(AND(AQ$5&gt;$E58,AQ$5&lt;=$F58),IF(AQ$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AR58" s="34">
+        <f>IF(AND(AR$5&gt;$E58,AR$5&lt;=$F58),IF(AR$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AS58" s="34">
+        <f>IF(AND(AS$5&gt;$E58,AS$5&lt;=$F58),IF(AS$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AT58" s="34">
+        <f>IF(AND(AT$5&gt;$E58,AT$5&lt;=$F58),IF(AT$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AU58" s="34">
+        <f>IF(AND(AU$5&gt;$E58,AU$5&lt;=$F58),IF(AU$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AV58" s="34">
+        <f>IF(AND(AV$5&gt;$E58,AV$5&lt;=$F58),IF(AV$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AW58" s="34">
+        <f>IF(AND(AW$5&gt;$E58,AW$5&lt;=$F58),IF(AW$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AX58" s="34">
+        <f>IF(AND(AX$5&gt;$E58,AX$5&lt;=$F58),IF(AX$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AY58" s="34">
+        <f>IF(AND(AY$5&gt;$E58,AY$5&lt;=$F58),IF(AY$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="AZ58" s="34">
+        <f>IF(AND(AZ$5&gt;$E58,AZ$5&lt;=$F58),IF(AZ$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BA58" s="34">
+        <f>IF(AND(BA$5&gt;$E58,BA$5&lt;=$F58),IF(BA$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BB58" s="34">
+        <f>IF(AND(BB$5&gt;$E58,BB$5&lt;=$F58),IF(BB$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BC58" s="34">
+        <f>IF(AND(BC$5&gt;$E58,BC$5&lt;=$F58),IF(BC$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BD58" s="34">
+        <f>IF(AND(BD$5&gt;$E58,BD$5&lt;=$F58),IF(BD$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BE58" s="34">
+        <f>IF(AND(BE$5&gt;$E58,BE$5&lt;=$F58),IF(BE$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BF58" s="34">
+        <f>IF(AND(BF$5&gt;$E58,BF$5&lt;=$F58),IF(BF$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BG58" s="34">
+        <f>IF(AND(BG$5&gt;$E58,BG$5&lt;=$F58),IF(BG$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BH58" s="34">
+        <f>IF(AND(BH$5&gt;$E58,BH$5&lt;=$F58),IF(BH$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BI58" s="34">
+        <f>IF(AND(BI$5&gt;$E58,BI$5&lt;=$F58),IF(BI$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BJ58" s="34">
+        <f>IF(AND(BJ$5&gt;$E58,BJ$5&lt;=$F58),IF(BJ$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BK58" s="34">
+        <f>IF(AND(BK$5&gt;$E58,BK$5&lt;=$F58),IF(BK$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BL58" s="34">
+        <f>IF(AND(BL$5&gt;$E58,BL$5&lt;=$F58),IF(BL$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BM58" s="34">
+        <f>IF(AND(BM$5&gt;$E58,BM$5&lt;=$F58),IF(BM$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BN58" s="34">
+        <f>IF(AND(BN$5&gt;$E58,BN$5&lt;=$F58),IF(BN$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+      <c r="BO58" s="34">
+        <f>IF(AND(BO$5&gt;$E58,BO$5&lt;=$F58),IF(BO$5=$E58+1,$C58,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="32">
+        <f>Plan!A49</f>
+        <v/>
+      </c>
+      <c r="B59" s="33">
+        <f>Plan!C49</f>
+        <v/>
+      </c>
+      <c r="C59" s="16">
+        <f>Plan!D49</f>
+        <v/>
+      </c>
+      <c r="D59" s="16">
+        <f>Plan!I49</f>
+        <v/>
+      </c>
+      <c r="E59" s="16">
+        <f>Plan!K49</f>
+        <v/>
+      </c>
+      <c r="F59" s="16">
+        <f>Plan!L49</f>
+        <v/>
+      </c>
+      <c r="G59" s="16">
+        <f>Plan!O49</f>
+        <v/>
+      </c>
+      <c r="H59" s="34">
+        <f>IF(AND(H$5&gt;$E59,H$5&lt;=$F59),IF(H$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="I59" s="34">
+        <f>IF(AND(I$5&gt;$E59,I$5&lt;=$F59),IF(I$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="J59" s="34">
+        <f>IF(AND(J$5&gt;$E59,J$5&lt;=$F59),IF(J$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="K59" s="34">
+        <f>IF(AND(K$5&gt;$E59,K$5&lt;=$F59),IF(K$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="L59" s="34">
+        <f>IF(AND(L$5&gt;$E59,L$5&lt;=$F59),IF(L$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="34">
+        <f>IF(AND(M$5&gt;$E59,M$5&lt;=$F59),IF(M$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="N59" s="34">
+        <f>IF(AND(N$5&gt;$E59,N$5&lt;=$F59),IF(N$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="O59" s="34">
+        <f>IF(AND(O$5&gt;$E59,O$5&lt;=$F59),IF(O$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="P59" s="34">
+        <f>IF(AND(P$5&gt;$E59,P$5&lt;=$F59),IF(P$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="Q59" s="34">
+        <f>IF(AND(Q$5&gt;$E59,Q$5&lt;=$F59),IF(Q$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="R59" s="34">
+        <f>IF(AND(R$5&gt;$E59,R$5&lt;=$F59),IF(R$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="S59" s="34">
+        <f>IF(AND(S$5&gt;$E59,S$5&lt;=$F59),IF(S$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="T59" s="34">
+        <f>IF(AND(T$5&gt;$E59,T$5&lt;=$F59),IF(T$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="U59" s="34">
+        <f>IF(AND(U$5&gt;$E59,U$5&lt;=$F59),IF(U$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="V59" s="34">
+        <f>IF(AND(V$5&gt;$E59,V$5&lt;=$F59),IF(V$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="W59" s="34">
+        <f>IF(AND(W$5&gt;$E59,W$5&lt;=$F59),IF(W$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="X59" s="34">
+        <f>IF(AND(X$5&gt;$E59,X$5&lt;=$F59),IF(X$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="Y59" s="34">
+        <f>IF(AND(Y$5&gt;$E59,Y$5&lt;=$F59),IF(Y$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="Z59" s="34">
+        <f>IF(AND(Z$5&gt;$E59,Z$5&lt;=$F59),IF(Z$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AA59" s="34">
+        <f>IF(AND(AA$5&gt;$E59,AA$5&lt;=$F59),IF(AA$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AB59" s="34">
+        <f>IF(AND(AB$5&gt;$E59,AB$5&lt;=$F59),IF(AB$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AC59" s="34">
+        <f>IF(AND(AC$5&gt;$E59,AC$5&lt;=$F59),IF(AC$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AD59" s="34">
+        <f>IF(AND(AD$5&gt;$E59,AD$5&lt;=$F59),IF(AD$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AE59" s="34">
+        <f>IF(AND(AE$5&gt;$E59,AE$5&lt;=$F59),IF(AE$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AF59" s="34">
+        <f>IF(AND(AF$5&gt;$E59,AF$5&lt;=$F59),IF(AF$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AG59" s="34">
+        <f>IF(AND(AG$5&gt;$E59,AG$5&lt;=$F59),IF(AG$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AH59" s="34">
+        <f>IF(AND(AH$5&gt;$E59,AH$5&lt;=$F59),IF(AH$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AI59" s="34">
+        <f>IF(AND(AI$5&gt;$E59,AI$5&lt;=$F59),IF(AI$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AJ59" s="34">
+        <f>IF(AND(AJ$5&gt;$E59,AJ$5&lt;=$F59),IF(AJ$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AK59" s="34">
+        <f>IF(AND(AK$5&gt;$E59,AK$5&lt;=$F59),IF(AK$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AL59" s="34">
+        <f>IF(AND(AL$5&gt;$E59,AL$5&lt;=$F59),IF(AL$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AM59" s="34">
+        <f>IF(AND(AM$5&gt;$E59,AM$5&lt;=$F59),IF(AM$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AN59" s="34">
+        <f>IF(AND(AN$5&gt;$E59,AN$5&lt;=$F59),IF(AN$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AO59" s="34">
+        <f>IF(AND(AO$5&gt;$E59,AO$5&lt;=$F59),IF(AO$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AP59" s="34">
+        <f>IF(AND(AP$5&gt;$E59,AP$5&lt;=$F59),IF(AP$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AQ59" s="34">
+        <f>IF(AND(AQ$5&gt;$E59,AQ$5&lt;=$F59),IF(AQ$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AR59" s="34">
+        <f>IF(AND(AR$5&gt;$E59,AR$5&lt;=$F59),IF(AR$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AS59" s="34">
+        <f>IF(AND(AS$5&gt;$E59,AS$5&lt;=$F59),IF(AS$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AT59" s="34">
+        <f>IF(AND(AT$5&gt;$E59,AT$5&lt;=$F59),IF(AT$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AU59" s="34">
+        <f>IF(AND(AU$5&gt;$E59,AU$5&lt;=$F59),IF(AU$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AV59" s="34">
+        <f>IF(AND(AV$5&gt;$E59,AV$5&lt;=$F59),IF(AV$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AW59" s="34">
+        <f>IF(AND(AW$5&gt;$E59,AW$5&lt;=$F59),IF(AW$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AX59" s="34">
+        <f>IF(AND(AX$5&gt;$E59,AX$5&lt;=$F59),IF(AX$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AY59" s="34">
+        <f>IF(AND(AY$5&gt;$E59,AY$5&lt;=$F59),IF(AY$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="AZ59" s="34">
+        <f>IF(AND(AZ$5&gt;$E59,AZ$5&lt;=$F59),IF(AZ$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BA59" s="34">
+        <f>IF(AND(BA$5&gt;$E59,BA$5&lt;=$F59),IF(BA$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BB59" s="34">
+        <f>IF(AND(BB$5&gt;$E59,BB$5&lt;=$F59),IF(BB$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BC59" s="34">
+        <f>IF(AND(BC$5&gt;$E59,BC$5&lt;=$F59),IF(BC$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BD59" s="34">
+        <f>IF(AND(BD$5&gt;$E59,BD$5&lt;=$F59),IF(BD$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BE59" s="34">
+        <f>IF(AND(BE$5&gt;$E59,BE$5&lt;=$F59),IF(BE$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BF59" s="34">
+        <f>IF(AND(BF$5&gt;$E59,BF$5&lt;=$F59),IF(BF$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BG59" s="34">
+        <f>IF(AND(BG$5&gt;$E59,BG$5&lt;=$F59),IF(BG$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BH59" s="34">
+        <f>IF(AND(BH$5&gt;$E59,BH$5&lt;=$F59),IF(BH$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BI59" s="34">
+        <f>IF(AND(BI$5&gt;$E59,BI$5&lt;=$F59),IF(BI$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BJ59" s="34">
+        <f>IF(AND(BJ$5&gt;$E59,BJ$5&lt;=$F59),IF(BJ$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BK59" s="34">
+        <f>IF(AND(BK$5&gt;$E59,BK$5&lt;=$F59),IF(BK$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BL59" s="34">
+        <f>IF(AND(BL$5&gt;$E59,BL$5&lt;=$F59),IF(BL$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BM59" s="34">
+        <f>IF(AND(BM$5&gt;$E59,BM$5&lt;=$F59),IF(BM$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BN59" s="34">
+        <f>IF(AND(BN$5&gt;$E59,BN$5&lt;=$F59),IF(BN$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+      <c r="BO59" s="34">
+        <f>IF(AND(BO$5&gt;$E59,BO$5&lt;=$F59),IF(BO$5=$E59+1,$C59,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32">
+        <f>Plan!A50</f>
+        <v/>
+      </c>
+      <c r="B60" s="33">
+        <f>Plan!C50</f>
+        <v/>
+      </c>
+      <c r="C60" s="16">
+        <f>Plan!D50</f>
+        <v/>
+      </c>
+      <c r="D60" s="16">
+        <f>Plan!I50</f>
+        <v/>
+      </c>
+      <c r="E60" s="16">
+        <f>Plan!K50</f>
+        <v/>
+      </c>
+      <c r="F60" s="16">
+        <f>Plan!L50</f>
+        <v/>
+      </c>
+      <c r="G60" s="16">
+        <f>Plan!O50</f>
+        <v/>
+      </c>
+      <c r="H60" s="34">
+        <f>IF(AND(H$5&gt;$E60,H$5&lt;=$F60),IF(H$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="I60" s="34">
+        <f>IF(AND(I$5&gt;$E60,I$5&lt;=$F60),IF(I$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="34">
+        <f>IF(AND(J$5&gt;$E60,J$5&lt;=$F60),IF(J$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="K60" s="34">
+        <f>IF(AND(K$5&gt;$E60,K$5&lt;=$F60),IF(K$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="L60" s="34">
+        <f>IF(AND(L$5&gt;$E60,L$5&lt;=$F60),IF(L$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="34">
+        <f>IF(AND(M$5&gt;$E60,M$5&lt;=$F60),IF(M$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="N60" s="34">
+        <f>IF(AND(N$5&gt;$E60,N$5&lt;=$F60),IF(N$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="O60" s="34">
+        <f>IF(AND(O$5&gt;$E60,O$5&lt;=$F60),IF(O$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="P60" s="34">
+        <f>IF(AND(P$5&gt;$E60,P$5&lt;=$F60),IF(P$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="Q60" s="34">
+        <f>IF(AND(Q$5&gt;$E60,Q$5&lt;=$F60),IF(Q$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="R60" s="34">
+        <f>IF(AND(R$5&gt;$E60,R$5&lt;=$F60),IF(R$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="S60" s="34">
+        <f>IF(AND(S$5&gt;$E60,S$5&lt;=$F60),IF(S$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="T60" s="34">
+        <f>IF(AND(T$5&gt;$E60,T$5&lt;=$F60),IF(T$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="U60" s="34">
+        <f>IF(AND(U$5&gt;$E60,U$5&lt;=$F60),IF(U$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="V60" s="34">
+        <f>IF(AND(V$5&gt;$E60,V$5&lt;=$F60),IF(V$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="W60" s="34">
+        <f>IF(AND(W$5&gt;$E60,W$5&lt;=$F60),IF(W$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="X60" s="34">
+        <f>IF(AND(X$5&gt;$E60,X$5&lt;=$F60),IF(X$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="Y60" s="34">
+        <f>IF(AND(Y$5&gt;$E60,Y$5&lt;=$F60),IF(Y$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="Z60" s="34">
+        <f>IF(AND(Z$5&gt;$E60,Z$5&lt;=$F60),IF(Z$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AA60" s="34">
+        <f>IF(AND(AA$5&gt;$E60,AA$5&lt;=$F60),IF(AA$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AB60" s="34">
+        <f>IF(AND(AB$5&gt;$E60,AB$5&lt;=$F60),IF(AB$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AC60" s="34">
+        <f>IF(AND(AC$5&gt;$E60,AC$5&lt;=$F60),IF(AC$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AD60" s="34">
+        <f>IF(AND(AD$5&gt;$E60,AD$5&lt;=$F60),IF(AD$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AE60" s="34">
+        <f>IF(AND(AE$5&gt;$E60,AE$5&lt;=$F60),IF(AE$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AF60" s="34">
+        <f>IF(AND(AF$5&gt;$E60,AF$5&lt;=$F60),IF(AF$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AG60" s="34">
+        <f>IF(AND(AG$5&gt;$E60,AG$5&lt;=$F60),IF(AG$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AH60" s="34">
+        <f>IF(AND(AH$5&gt;$E60,AH$5&lt;=$F60),IF(AH$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AI60" s="34">
+        <f>IF(AND(AI$5&gt;$E60,AI$5&lt;=$F60),IF(AI$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AJ60" s="34">
+        <f>IF(AND(AJ$5&gt;$E60,AJ$5&lt;=$F60),IF(AJ$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AK60" s="34">
+        <f>IF(AND(AK$5&gt;$E60,AK$5&lt;=$F60),IF(AK$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AL60" s="34">
+        <f>IF(AND(AL$5&gt;$E60,AL$5&lt;=$F60),IF(AL$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AM60" s="34">
+        <f>IF(AND(AM$5&gt;$E60,AM$5&lt;=$F60),IF(AM$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AN60" s="34">
+        <f>IF(AND(AN$5&gt;$E60,AN$5&lt;=$F60),IF(AN$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AO60" s="34">
+        <f>IF(AND(AO$5&gt;$E60,AO$5&lt;=$F60),IF(AO$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AP60" s="34">
+        <f>IF(AND(AP$5&gt;$E60,AP$5&lt;=$F60),IF(AP$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AQ60" s="34">
+        <f>IF(AND(AQ$5&gt;$E60,AQ$5&lt;=$F60),IF(AQ$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AR60" s="34">
+        <f>IF(AND(AR$5&gt;$E60,AR$5&lt;=$F60),IF(AR$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AS60" s="34">
+        <f>IF(AND(AS$5&gt;$E60,AS$5&lt;=$F60),IF(AS$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AT60" s="34">
+        <f>IF(AND(AT$5&gt;$E60,AT$5&lt;=$F60),IF(AT$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AU60" s="34">
+        <f>IF(AND(AU$5&gt;$E60,AU$5&lt;=$F60),IF(AU$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AV60" s="34">
+        <f>IF(AND(AV$5&gt;$E60,AV$5&lt;=$F60),IF(AV$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AW60" s="34">
+        <f>IF(AND(AW$5&gt;$E60,AW$5&lt;=$F60),IF(AW$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AX60" s="34">
+        <f>IF(AND(AX$5&gt;$E60,AX$5&lt;=$F60),IF(AX$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AY60" s="34">
+        <f>IF(AND(AY$5&gt;$E60,AY$5&lt;=$F60),IF(AY$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="AZ60" s="34">
+        <f>IF(AND(AZ$5&gt;$E60,AZ$5&lt;=$F60),IF(AZ$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BA60" s="34">
+        <f>IF(AND(BA$5&gt;$E60,BA$5&lt;=$F60),IF(BA$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BB60" s="34">
+        <f>IF(AND(BB$5&gt;$E60,BB$5&lt;=$F60),IF(BB$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BC60" s="34">
+        <f>IF(AND(BC$5&gt;$E60,BC$5&lt;=$F60),IF(BC$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BD60" s="34">
+        <f>IF(AND(BD$5&gt;$E60,BD$5&lt;=$F60),IF(BD$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BE60" s="34">
+        <f>IF(AND(BE$5&gt;$E60,BE$5&lt;=$F60),IF(BE$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BF60" s="34">
+        <f>IF(AND(BF$5&gt;$E60,BF$5&lt;=$F60),IF(BF$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BG60" s="34">
+        <f>IF(AND(BG$5&gt;$E60,BG$5&lt;=$F60),IF(BG$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BH60" s="34">
+        <f>IF(AND(BH$5&gt;$E60,BH$5&lt;=$F60),IF(BH$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BI60" s="34">
+        <f>IF(AND(BI$5&gt;$E60,BI$5&lt;=$F60),IF(BI$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BJ60" s="34">
+        <f>IF(AND(BJ$5&gt;$E60,BJ$5&lt;=$F60),IF(BJ$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BK60" s="34">
+        <f>IF(AND(BK$5&gt;$E60,BK$5&lt;=$F60),IF(BK$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BL60" s="34">
+        <f>IF(AND(BL$5&gt;$E60,BL$5&lt;=$F60),IF(BL$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BM60" s="34">
+        <f>IF(AND(BM$5&gt;$E60,BM$5&lt;=$F60),IF(BM$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BN60" s="34">
+        <f>IF(AND(BN$5&gt;$E60,BN$5&lt;=$F60),IF(BN$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+      <c r="BO60" s="34">
+        <f>IF(AND(BO$5&gt;$E60,BO$5&lt;=$F60),IF(BO$5=$E60+1,$C60,""),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="32">
+        <f>Plan!A51</f>
+        <v/>
+      </c>
+      <c r="B61" s="33">
+        <f>Plan!C51</f>
+        <v/>
+      </c>
+      <c r="C61" s="16">
+        <f>Plan!D51</f>
+        <v/>
+      </c>
+      <c r="D61" s="16">
+        <f>Plan!I51</f>
+        <v/>
+      </c>
+      <c r="E61" s="16">
+        <f>Plan!K51</f>
+        <v/>
+      </c>
+      <c r="F61" s="16">
+        <f>Plan!L51</f>
+        <v/>
+      </c>
+      <c r="G61" s="16">
+        <f>Plan!O51</f>
+        <v/>
+      </c>
+      <c r="H61" s="34">
+        <f>IF(AND(H$5&gt;$E61,H$5&lt;=$F61),IF(H$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="I61" s="34">
+        <f>IF(AND(I$5&gt;$E61,I$5&lt;=$F61),IF(I$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="J61" s="34">
+        <f>IF(AND(J$5&gt;$E61,J$5&lt;=$F61),IF(J$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="K61" s="34">
+        <f>IF(AND(K$5&gt;$E61,K$5&lt;=$F61),IF(K$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="L61" s="34">
+        <f>IF(AND(L$5&gt;$E61,L$5&lt;=$F61),IF(L$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="M61" s="34">
+        <f>IF(AND(M$5&gt;$E61,M$5&lt;=$F61),IF(M$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="N61" s="34">
+        <f>IF(AND(N$5&gt;$E61,N$5&lt;=$F61),IF(N$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="O61" s="34">
+        <f>IF(AND(O$5&gt;$E61,O$5&lt;=$F61),IF(O$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="P61" s="34">
+        <f>IF(AND(P$5&gt;$E61,P$5&lt;=$F61),IF(P$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="Q61" s="34">
+        <f>IF(AND(Q$5&gt;$E61,Q$5&lt;=$F61),IF(Q$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="R61" s="34">
+        <f>IF(AND(R$5&gt;$E61,R$5&lt;=$F61),IF(R$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="S61" s="34">
+        <f>IF(AND(S$5&gt;$E61,S$5&lt;=$F61),IF(S$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="T61" s="34">
+        <f>IF(AND(T$5&gt;$E61,T$5&lt;=$F61),IF(T$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="U61" s="34">
+        <f>IF(AND(U$5&gt;$E61,U$5&lt;=$F61),IF(U$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="V61" s="34">
+        <f>IF(AND(V$5&gt;$E61,V$5&lt;=$F61),IF(V$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="W61" s="34">
+        <f>IF(AND(W$5&gt;$E61,W$5&lt;=$F61),IF(W$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="X61" s="34">
+        <f>IF(AND(X$5&gt;$E61,X$5&lt;=$F61),IF(X$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="Y61" s="34">
+        <f>IF(AND(Y$5&gt;$E61,Y$5&lt;=$F61),IF(Y$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="Z61" s="34">
+        <f>IF(AND(Z$5&gt;$E61,Z$5&lt;=$F61),IF(Z$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AA61" s="34">
+        <f>IF(AND(AA$5&gt;$E61,AA$5&lt;=$F61),IF(AA$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AB61" s="34">
+        <f>IF(AND(AB$5&gt;$E61,AB$5&lt;=$F61),IF(AB$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AC61" s="34">
+        <f>IF(AND(AC$5&gt;$E61,AC$5&lt;=$F61),IF(AC$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AD61" s="34">
+        <f>IF(AND(AD$5&gt;$E61,AD$5&lt;=$F61),IF(AD$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AE61" s="34">
+        <f>IF(AND(AE$5&gt;$E61,AE$5&lt;=$F61),IF(AE$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AF61" s="34">
+        <f>IF(AND(AF$5&gt;$E61,AF$5&lt;=$F61),IF(AF$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AG61" s="34">
+        <f>IF(AND(AG$5&gt;$E61,AG$5&lt;=$F61),IF(AG$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AH61" s="34">
+        <f>IF(AND(AH$5&gt;$E61,AH$5&lt;=$F61),IF(AH$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AI61" s="34">
+        <f>IF(AND(AI$5&gt;$E61,AI$5&lt;=$F61),IF(AI$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AJ61" s="34">
+        <f>IF(AND(AJ$5&gt;$E61,AJ$5&lt;=$F61),IF(AJ$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AK61" s="34">
+        <f>IF(AND(AK$5&gt;$E61,AK$5&lt;=$F61),IF(AK$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AL61" s="34">
+        <f>IF(AND(AL$5&gt;$E61,AL$5&lt;=$F61),IF(AL$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AM61" s="34">
+        <f>IF(AND(AM$5&gt;$E61,AM$5&lt;=$F61),IF(AM$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AN61" s="34">
+        <f>IF(AND(AN$5&gt;$E61,AN$5&lt;=$F61),IF(AN$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AO61" s="34">
+        <f>IF(AND(AO$5&gt;$E61,AO$5&lt;=$F61),IF(AO$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AP61" s="34">
+        <f>IF(AND(AP$5&gt;$E61,AP$5&lt;=$F61),IF(AP$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AQ61" s="34">
+        <f>IF(AND(AQ$5&gt;$E61,AQ$5&lt;=$F61),IF(AQ$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AR61" s="34">
+        <f>IF(AND(AR$5&gt;$E61,AR$5&lt;=$F61),IF(AR$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AS61" s="34">
+        <f>IF(AND(AS$5&gt;$E61,AS$5&lt;=$F61),IF(AS$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AT61" s="34">
+        <f>IF(AND(AT$5&gt;$E61,AT$5&lt;=$F61),IF(AT$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AU61" s="34">
+        <f>IF(AND(AU$5&gt;$E61,AU$5&lt;=$F61),IF(AU$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AV61" s="34">
+        <f>IF(AND(AV$5&gt;$E61,AV$5&lt;=$F61),IF(AV$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AW61" s="34">
+        <f>IF(AND(AW$5&gt;$E61,AW$5&lt;=$F61),IF(AW$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AX61" s="34">
+        <f>IF(AND(AX$5&gt;$E61,AX$5&lt;=$F61),IF(AX$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AY61" s="34">
+        <f>IF(AND(AY$5&gt;$E61,AY$5&lt;=$F61),IF(AY$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="AZ61" s="34">
+        <f>IF(AND(AZ$5&gt;$E61,AZ$5&lt;=$F61),IF(AZ$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BA61" s="34">
+        <f>IF(AND(BA$5&gt;$E61,BA$5&lt;=$F61),IF(BA$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BB61" s="34">
+        <f>IF(AND(BB$5&gt;$E61,BB$5&lt;=$F61),IF(BB$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BC61" s="34">
+        <f>IF(AND(BC$5&gt;$E61,BC$5&lt;=$F61),IF(BC$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BD61" s="34">
+        <f>IF(AND(BD$5&gt;$E61,BD$5&lt;=$F61),IF(BD$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BE61" s="34">
+        <f>IF(AND(BE$5&gt;$E61,BE$5&lt;=$F61),IF(BE$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BF61" s="34">
+        <f>IF(AND(BF$5&gt;$E61,BF$5&lt;=$F61),IF(BF$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BG61" s="34">
+        <f>IF(AND(BG$5&gt;$E61,BG$5&lt;=$F61),IF(BG$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BH61" s="34">
+        <f>IF(AND(BH$5&gt;$E61,BH$5&lt;=$F61),IF(BH$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BI61" s="34">
+        <f>IF(AND(BI$5&gt;$E61,BI$5&lt;=$F61),IF(BI$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BJ61" s="34">
+        <f>IF(AND(BJ$5&gt;$E61,BJ$5&lt;=$F61),IF(BJ$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BK61" s="34">
+        <f>IF(AND(BK$5&gt;$E61,BK$5&lt;=$F61),IF(BK$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BL61" s="34">
+        <f>IF(AND(BL$5&gt;$E61,BL$5&lt;=$F61),IF(BL$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BM61" s="34">
+        <f>IF(AND(BM$5&gt;$E61,BM$5&lt;=$F61),IF(BM$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BN61" s="34">
+        <f>IF(AND(BN$5&gt;$E61,BN$5&lt;=$F61),IF(BN$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+      <c r="BO61" s="34">
+        <f>IF(AND(BO$5&gt;$E61,BO$5&lt;=$F61),IF(BO$5=$E61+1,$C61,""),"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A46:D46"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="R4:AA4"/>
@@ -20441,6 +22443,7 @@
     <mergeCell ref="AB4:AK4"/>
     <mergeCell ref="AV4:BE4"/>
     <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A49:D49"/>
     <mergeCell ref="AL4:AU4"/>
     <mergeCell ref="BF4:BO4"/>
     <mergeCell ref="A14:D14"/>
@@ -20480,12 +22483,12 @@
       <formula>AND(H$5&gt;$E40,H$5&lt;=$F40)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H46:BO46">
+  <conditionalFormatting sqref="H49:BO49">
     <cfRule type="expression" priority="8" dxfId="11">
-      <formula>AND(H$5&gt;$E46,H$5&lt;=$F46)</formula>
+      <formula>AND(H$5&gt;$E49,H$5&lt;=$F49)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H9:BO56">
+  <conditionalFormatting sqref="H9:BO61">
     <cfRule type="expression" priority="9" dxfId="12" stopIfTrue="1">
       <formula>AND(AND(H$5&gt;$E9,H$5&lt;=$F9,$A9&lt;&gt;""),$G9="Hecho")</formula>
     </cfRule>
@@ -20520,7 +22523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -20860,22 +22863,22 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C12" s="35">
-        <f>Plan!C11</f>
+        <f>Plan!C23</f>
         <v/>
       </c>
       <c r="D12" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="16">
-        <f>Plan!J11</f>
+        <f>Plan!J23</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>Plan!K11</f>
+        <f>Plan!K23</f>
         <v/>
       </c>
       <c r="G12" s="8">
@@ -20883,11 +22886,11 @@
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>Plan!I11</f>
+        <f>Plan!I23</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>Plan!O11</f>
+        <f>Plan!O23</f>
         <v/>
       </c>
     </row>
@@ -20897,22 +22900,22 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="C13" s="35">
-        <f>Plan!C23</f>
+        <f>Plan!C14</f>
         <v/>
       </c>
       <c r="D13" s="8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E13" s="16">
-        <f>Plan!J23</f>
+        <f>Plan!J14</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>Plan!K23</f>
+        <f>Plan!K14</f>
         <v/>
       </c>
       <c r="G13" s="8">
@@ -20920,11 +22923,11 @@
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>Plan!I23</f>
+        <f>Plan!I14</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>Plan!O23</f>
+        <f>Plan!O14</f>
         <v/>
       </c>
     </row>
@@ -20934,22 +22937,22 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C14" s="35">
-        <f>Plan!C14</f>
+        <f>Plan!C11</f>
         <v/>
       </c>
       <c r="D14" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E14" s="16">
-        <f>Plan!J14</f>
+        <f>Plan!J11</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>Plan!K14</f>
+        <f>Plan!K11</f>
         <v/>
       </c>
       <c r="G14" s="8">
@@ -20957,11 +22960,11 @@
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>Plan!I14</f>
+        <f>Plan!I11</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>Plan!O14</f>
+        <f>Plan!O11</f>
         <v/>
       </c>
     </row>
@@ -21049,18 +23052,18 @@
         </is>
       </c>
       <c r="C17" s="35">
-        <f>Plan!C46</f>
+        <f>Plan!C49</f>
         <v/>
       </c>
       <c r="D17" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="16">
-        <f>Plan!J46</f>
+        <f>Plan!J49</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>Plan!K46</f>
+        <f>Plan!K49</f>
         <v/>
       </c>
       <c r="G17" s="8">
@@ -21068,11 +23071,11 @@
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>Plan!I46</f>
+        <f>Plan!I49</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>Plan!O46</f>
+        <f>Plan!O49</f>
         <v/>
       </c>
     </row>
@@ -21082,22 +23085,22 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C18" s="35">
-        <f>Plan!C9</f>
+        <f>Plan!C22</f>
         <v/>
       </c>
       <c r="D18" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" s="16">
-        <f>Plan!J9</f>
+        <f>Plan!J22</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>Plan!K9</f>
+        <f>Plan!K22</f>
         <v/>
       </c>
       <c r="G18" s="8">
@@ -21105,11 +23108,11 @@
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>Plan!I9</f>
+        <f>Plan!I22</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>Plan!O9</f>
+        <f>Plan!O22</f>
         <v/>
       </c>
     </row>
@@ -21156,22 +23159,22 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C20" s="35">
-        <f>Plan!C32</f>
+        <f>Plan!C9</f>
         <v/>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E20" s="16">
-        <f>Plan!J32</f>
+        <f>Plan!J9</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>Plan!K32</f>
+        <f>Plan!K9</f>
         <v/>
       </c>
       <c r="G20" s="8">
@@ -21179,11 +23182,11 @@
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>Plan!I32</f>
+        <f>Plan!I9</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>Plan!O32</f>
+        <f>Plan!O9</f>
         <v/>
       </c>
     </row>
@@ -21230,22 +23233,22 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C22" s="35">
-        <f>Plan!C33</f>
+        <f>Plan!C16</f>
         <v/>
       </c>
       <c r="D22" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E22" s="16">
-        <f>Plan!J33</f>
+        <f>Plan!J16</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>Plan!K33</f>
+        <f>Plan!K16</f>
         <v/>
       </c>
       <c r="G22" s="8">
@@ -21253,11 +23256,11 @@
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>Plan!I33</f>
+        <f>Plan!I16</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>Plan!O33</f>
+        <f>Plan!O16</f>
         <v/>
       </c>
     </row>
@@ -21267,22 +23270,22 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="C23" s="35">
-        <f>Plan!C22</f>
+        <f>Plan!C50</f>
         <v/>
       </c>
       <c r="D23" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E23" s="16">
-        <f>Plan!J22</f>
+        <f>Plan!J50</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>Plan!K22</f>
+        <f>Plan!K50</f>
         <v/>
       </c>
       <c r="G23" s="8">
@@ -21290,11 +23293,11 @@
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>Plan!I22</f>
+        <f>Plan!I50</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>Plan!O22</f>
+        <f>Plan!O50</f>
         <v/>
       </c>
     </row>
@@ -21341,22 +23344,22 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C25" s="35">
-        <f>Plan!C16</f>
+        <f>Plan!C33</f>
         <v/>
       </c>
       <c r="D25" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E25" s="16">
-        <f>Plan!J16</f>
+        <f>Plan!J33</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>Plan!K16</f>
+        <f>Plan!K33</f>
         <v/>
       </c>
       <c r="G25" s="8">
@@ -21364,11 +23367,11 @@
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>Plan!I16</f>
+        <f>Plan!I33</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>Plan!O16</f>
+        <f>Plan!O33</f>
         <v/>
       </c>
     </row>
@@ -21415,22 +23418,22 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="C27" s="35">
-        <f>Plan!C21</f>
+        <f>Plan!C38</f>
         <v/>
       </c>
       <c r="D27" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E27" s="16">
-        <f>Plan!J21</f>
+        <f>Plan!J38</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>Plan!K21</f>
+        <f>Plan!K38</f>
         <v/>
       </c>
       <c r="G27" s="8">
@@ -21438,11 +23441,11 @@
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>Plan!I21</f>
+        <f>Plan!I38</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>Plan!O21</f>
+        <f>Plan!O38</f>
         <v/>
       </c>
     </row>
@@ -21452,22 +23455,22 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C28" s="35">
-        <f>Plan!C27</f>
+        <f>Plan!C36</f>
         <v/>
       </c>
       <c r="D28" s="8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E28" s="16">
-        <f>Plan!J27</f>
+        <f>Plan!J36</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>Plan!K27</f>
+        <f>Plan!K36</f>
         <v/>
       </c>
       <c r="G28" s="8">
@@ -21475,11 +23478,11 @@
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>Plan!I27</f>
+        <f>Plan!I36</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>Plan!O27</f>
+        <f>Plan!O36</f>
         <v/>
       </c>
     </row>
@@ -21489,22 +23492,22 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="C29" s="35">
-        <f>Plan!C12</f>
+        <f>Plan!C39</f>
         <v/>
       </c>
       <c r="D29" s="8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E29" s="16">
-        <f>Plan!J12</f>
+        <f>Plan!J39</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>Plan!K12</f>
+        <f>Plan!K39</f>
         <v/>
       </c>
       <c r="G29" s="8">
@@ -21512,11 +23515,11 @@
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>Plan!I12</f>
+        <f>Plan!I39</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>Plan!O12</f>
+        <f>Plan!O39</f>
         <v/>
       </c>
     </row>
@@ -21526,22 +23529,22 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C30" s="35">
-        <f>Plan!C35</f>
+        <f>Plan!C21</f>
         <v/>
       </c>
       <c r="D30" s="8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E30" s="16">
-        <f>Plan!J35</f>
+        <f>Plan!J21</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>Plan!K35</f>
+        <f>Plan!K21</f>
         <v/>
       </c>
       <c r="G30" s="8">
@@ -21549,11 +23552,11 @@
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>Plan!I35</f>
+        <f>Plan!I21</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>Plan!O35</f>
+        <f>Plan!O21</f>
         <v/>
       </c>
     </row>
@@ -21563,22 +23566,22 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C31" s="35">
-        <f>Plan!C36</f>
+        <f>Plan!C32</f>
         <v/>
       </c>
       <c r="D31" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E31" s="16">
-        <f>Plan!J36</f>
+        <f>Plan!J32</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>Plan!K36</f>
+        <f>Plan!K32</f>
         <v/>
       </c>
       <c r="G31" s="8">
@@ -21586,11 +23589,11 @@
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>Plan!I36</f>
+        <f>Plan!I32</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>Plan!O36</f>
+        <f>Plan!O32</f>
         <v/>
       </c>
     </row>
@@ -21600,22 +23603,22 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C32" s="35">
-        <f>Plan!C28</f>
+        <f>Plan!C27</f>
         <v/>
       </c>
       <c r="D32" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E32" s="16">
-        <f>Plan!J28</f>
+        <f>Plan!J27</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>Plan!K28</f>
+        <f>Plan!K27</f>
         <v/>
       </c>
       <c r="G32" s="8">
@@ -21623,11 +23626,11 @@
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>Plan!I28</f>
+        <f>Plan!I27</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>Plan!O28</f>
+        <f>Plan!O27</f>
         <v/>
       </c>
     </row>
@@ -21637,22 +23640,22 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C33" s="35">
-        <f>Plan!C31</f>
+        <f>Plan!C12</f>
         <v/>
       </c>
       <c r="D33" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33" s="16">
-        <f>Plan!J31</f>
+        <f>Plan!J12</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>Plan!K31</f>
+        <f>Plan!K12</f>
         <v/>
       </c>
       <c r="G33" s="8">
@@ -21660,11 +23663,11 @@
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>Plan!I31</f>
+        <f>Plan!I12</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>Plan!O31</f>
+        <f>Plan!O12</f>
         <v/>
       </c>
     </row>
@@ -21674,22 +23677,22 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="C34" s="35">
-        <f>Plan!C29</f>
+        <f>Plan!C19</f>
         <v/>
       </c>
       <c r="D34" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E34" s="16">
-        <f>Plan!J29</f>
+        <f>Plan!J19</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>Plan!K29</f>
+        <f>Plan!K19</f>
         <v/>
       </c>
       <c r="G34" s="8">
@@ -21697,11 +23700,11 @@
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>Plan!I29</f>
+        <f>Plan!I19</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>Plan!O29</f>
+        <f>Plan!O19</f>
         <v/>
       </c>
     </row>
@@ -21711,22 +23714,22 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="C35" s="35">
-        <f>Plan!C44</f>
+        <f>Plan!C37</f>
         <v/>
       </c>
       <c r="D35" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E35" s="16">
-        <f>Plan!J44</f>
+        <f>Plan!J37</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>Plan!K44</f>
+        <f>Plan!K37</f>
         <v/>
       </c>
       <c r="G35" s="8">
@@ -21734,11 +23737,11 @@
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>Plan!I44</f>
+        <f>Plan!I37</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>Plan!O44</f>
+        <f>Plan!O37</f>
         <v/>
       </c>
     </row>
@@ -21748,22 +23751,22 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C36" s="35">
-        <f>Plan!C19</f>
+        <f>Plan!C28</f>
         <v/>
       </c>
       <c r="D36" s="8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E36" s="16">
-        <f>Plan!J19</f>
+        <f>Plan!J28</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>Plan!K19</f>
+        <f>Plan!K28</f>
         <v/>
       </c>
       <c r="G36" s="8">
@@ -21771,11 +23774,11 @@
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>Plan!I19</f>
+        <f>Plan!I28</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>Plan!O19</f>
+        <f>Plan!O28</f>
         <v/>
       </c>
     </row>
@@ -21785,22 +23788,22 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C37" s="35">
-        <f>Plan!C37</f>
+        <f>Plan!C31</f>
         <v/>
       </c>
       <c r="D37" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E37" s="16">
-        <f>Plan!J37</f>
+        <f>Plan!J31</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>Plan!K37</f>
+        <f>Plan!K31</f>
         <v/>
       </c>
       <c r="G37" s="8">
@@ -21808,11 +23811,11 @@
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>Plan!I37</f>
+        <f>Plan!I31</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>Plan!O37</f>
+        <f>Plan!O31</f>
         <v/>
       </c>
     </row>
@@ -21822,22 +23825,22 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C38" s="35">
-        <f>Plan!C38</f>
+        <f>Plan!C29</f>
         <v/>
       </c>
       <c r="D38" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E38" s="16">
-        <f>Plan!J38</f>
+        <f>Plan!J29</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>Plan!K38</f>
+        <f>Plan!K29</f>
         <v/>
       </c>
       <c r="G38" s="8">
@@ -21845,11 +23848,11 @@
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>Plan!I38</f>
+        <f>Plan!I29</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>Plan!O38</f>
+        <f>Plan!O29</f>
         <v/>
       </c>
     </row>
@@ -21859,22 +23862,22 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="C39" s="35">
-        <f>Plan!C40</f>
+        <f>Plan!C35</f>
         <v/>
       </c>
       <c r="D39" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E39" s="16">
-        <f>Plan!J40</f>
+        <f>Plan!J35</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>Plan!K40</f>
+        <f>Plan!K35</f>
         <v/>
       </c>
       <c r="G39" s="8">
@@ -21882,11 +23885,11 @@
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>Plan!I40</f>
+        <f>Plan!I35</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>Plan!O40</f>
+        <f>Plan!O35</f>
         <v/>
       </c>
     </row>
@@ -21896,22 +23899,22 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="C40" s="35">
-        <f>Plan!C34</f>
+        <f>Plan!C47</f>
         <v/>
       </c>
       <c r="D40" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40" s="16">
-        <f>Plan!J34</f>
+        <f>Plan!J47</f>
         <v/>
       </c>
       <c r="F40" s="16">
-        <f>Plan!K34</f>
+        <f>Plan!K47</f>
         <v/>
       </c>
       <c r="G40" s="8">
@@ -21919,11 +23922,11 @@
         <v/>
       </c>
       <c r="H40" s="16">
-        <f>Plan!I34</f>
+        <f>Plan!I47</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>Plan!O34</f>
+        <f>Plan!O47</f>
         <v/>
       </c>
     </row>
@@ -21933,22 +23936,22 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C41" s="35">
-        <f>Plan!C45</f>
+        <f>Plan!C40</f>
         <v/>
       </c>
       <c r="D41" s="8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E41" s="16">
-        <f>Plan!J45</f>
+        <f>Plan!J40</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>Plan!K45</f>
+        <f>Plan!K40</f>
         <v/>
       </c>
       <c r="G41" s="8">
@@ -21956,11 +23959,11 @@
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>Plan!I45</f>
+        <f>Plan!I40</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>Plan!O45</f>
+        <f>Plan!O40</f>
         <v/>
       </c>
     </row>
@@ -21970,22 +23973,22 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="C42" s="35">
-        <f>Plan!C30</f>
+        <f>Plan!C41</f>
         <v/>
       </c>
       <c r="D42" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E42" s="16">
-        <f>Plan!J30</f>
+        <f>Plan!J41</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>Plan!K30</f>
+        <f>Plan!K41</f>
         <v/>
       </c>
       <c r="G42" s="8">
@@ -21993,11 +23996,11 @@
         <v/>
       </c>
       <c r="H42" s="16">
-        <f>Plan!I30</f>
+        <f>Plan!I41</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>Plan!O30</f>
+        <f>Plan!O41</f>
         <v/>
       </c>
     </row>
@@ -22007,22 +24010,22 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="C43" s="35">
-        <f>Plan!C39</f>
+        <f>Plan!C43</f>
         <v/>
       </c>
       <c r="D43" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E43" s="16">
-        <f>Plan!J39</f>
+        <f>Plan!J43</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>Plan!K39</f>
+        <f>Plan!K43</f>
         <v/>
       </c>
       <c r="G43" s="8">
@@ -22030,11 +24033,11 @@
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>Plan!I39</f>
+        <f>Plan!I43</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>Plan!O39</f>
+        <f>Plan!O43</f>
         <v/>
       </c>
     </row>
@@ -22044,22 +24047,22 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C44" s="35">
-        <f>Plan!C41</f>
+        <f>Plan!C34</f>
         <v/>
       </c>
       <c r="D44" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E44" s="16">
-        <f>Plan!J41</f>
+        <f>Plan!J34</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>Plan!K41</f>
+        <f>Plan!K34</f>
         <v/>
       </c>
       <c r="G44" s="8">
@@ -22067,11 +24070,11 @@
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>Plan!I41</f>
+        <f>Plan!I34</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>Plan!O41</f>
+        <f>Plan!O34</f>
         <v/>
       </c>
     </row>
@@ -22081,22 +24084,22 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C45" s="35">
-        <f>Plan!C42</f>
+        <f>Plan!C48</f>
         <v/>
       </c>
       <c r="D45" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E45" s="16">
-        <f>Plan!J42</f>
+        <f>Plan!J48</f>
         <v/>
       </c>
       <c r="F45" s="16">
-        <f>Plan!K42</f>
+        <f>Plan!K48</f>
         <v/>
       </c>
       <c r="G45" s="8">
@@ -22104,11 +24107,11 @@
         <v/>
       </c>
       <c r="H45" s="16">
-        <f>Plan!I42</f>
+        <f>Plan!I48</f>
         <v/>
       </c>
       <c r="I45" s="16">
-        <f>Plan!O42</f>
+        <f>Plan!O48</f>
         <v/>
       </c>
     </row>
@@ -22118,22 +24121,22 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C46" s="35">
-        <f>Plan!C43</f>
+        <f>Plan!C30</f>
         <v/>
       </c>
       <c r="D46" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E46" s="16">
-        <f>Plan!J43</f>
+        <f>Plan!J30</f>
         <v/>
       </c>
       <c r="F46" s="16">
-        <f>Plan!K43</f>
+        <f>Plan!K30</f>
         <v/>
       </c>
       <c r="G46" s="8">
@@ -22141,134 +24144,319 @@
         <v/>
       </c>
       <c r="H46" s="16">
-        <f>Plan!I43</f>
+        <f>Plan!I30</f>
         <v/>
       </c>
       <c r="I46" s="16">
-        <f>Plan!O43</f>
+        <f>Plan!O30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="C47" s="35">
+        <f>Plan!C42</f>
+        <v/>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" s="16">
+        <f>Plan!J42</f>
+        <v/>
+      </c>
+      <c r="F47" s="16">
+        <f>Plan!K42</f>
+        <v/>
+      </c>
+      <c r="G47" s="8">
+        <f>F47-E47</f>
+        <v/>
+      </c>
+      <c r="H47" s="16">
+        <f>Plan!I42</f>
+        <v/>
+      </c>
+      <c r="I47" s="16">
+        <f>Plan!O42</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="3" t="inlineStr">
+      <c r="A48" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="C48" s="35">
+        <f>Plan!C44</f>
+        <v/>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" s="16">
+        <f>Plan!J44</f>
+        <v/>
+      </c>
+      <c r="F48" s="16">
+        <f>Plan!K44</f>
+        <v/>
+      </c>
+      <c r="G48" s="8">
+        <f>F48-E48</f>
+        <v/>
+      </c>
+      <c r="H48" s="16">
+        <f>Plan!I44</f>
+        <v/>
+      </c>
+      <c r="I48" s="16">
+        <f>Plan!O44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="C49" s="35">
+        <f>Plan!C45</f>
+        <v/>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="16">
+        <f>Plan!J45</f>
+        <v/>
+      </c>
+      <c r="F49" s="16">
+        <f>Plan!K45</f>
+        <v/>
+      </c>
+      <c r="G49" s="8">
+        <f>F49-E49</f>
+        <v/>
+      </c>
+      <c r="H49" s="16">
+        <f>Plan!I45</f>
+        <v/>
+      </c>
+      <c r="I49" s="16">
+        <f>Plan!O45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="C50" s="35">
+        <f>Plan!C51</f>
+        <v/>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="16">
+        <f>Plan!J51</f>
+        <v/>
+      </c>
+      <c r="F50" s="16">
+        <f>Plan!K51</f>
+        <v/>
+      </c>
+      <c r="G50" s="8">
+        <f>F50-E50</f>
+        <v/>
+      </c>
+      <c r="H50" s="16">
+        <f>Plan!I51</f>
+        <v/>
+      </c>
+      <c r="I50" s="16">
+        <f>Plan!O51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="C51" s="35">
+        <f>Plan!C46</f>
+        <v/>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="16">
+        <f>Plan!J46</f>
+        <v/>
+      </c>
+      <c r="F51" s="16">
+        <f>Plan!K46</f>
+        <v/>
+      </c>
+      <c r="G51" s="8">
+        <f>F51-E51</f>
+        <v/>
+      </c>
+      <c r="H51" s="16">
+        <f>Plan!I46</f>
+        <v/>
+      </c>
+      <c r="I51" s="16">
+        <f>Plan!O46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Estadísticas de la cola</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="23" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="23" t="inlineStr">
         <is>
           <t>Fila</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C54" s="23" t="inlineStr">
         <is>
           <t>Actividades</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D54" s="23" t="inlineStr">
         <is>
           <t>Bloques ocupados</t>
         </is>
       </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="E54" s="23" t="inlineStr">
         <is>
           <t>Uso</t>
         </is>
       </c>
-      <c r="F49" s="23" t="inlineStr">
+      <c r="F54" s="23" t="inlineStr">
         <is>
           <t>Espera promedio</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="18" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C50" s="15">
-        <f>COUNTIF($H$5:$H$46,B50)</f>
-        <v/>
-      </c>
-      <c r="D50" s="15">
-        <f>SUMIF(Plan!$I$5:$I$46,B50,Plan!$E$5:$E$46)</f>
-        <v/>
-      </c>
-      <c r="E50" s="36">
-        <f>IF(Resumen!$C$17=0,0,D50/Resumen!$C$17)</f>
-        <v/>
-      </c>
-      <c r="F50" s="37">
-        <f>IFERROR(AVERAGEIF($H$5:$H$46,B50,$G$5:$G$46),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="18" t="inlineStr">
+      <c r="C55" s="15">
+        <f>COUNTIF($H$5:$H$51,B55)</f>
+        <v/>
+      </c>
+      <c r="D55" s="15">
+        <f>SUMIF(Plan!$I$5:$I$51,B55,Plan!$E$5:$E$51)</f>
+        <v/>
+      </c>
+      <c r="E55" s="36">
+        <f>IF(Resumen!$C$17=0,0,D55/Resumen!$C$17)</f>
+        <v/>
+      </c>
+      <c r="F55" s="37">
+        <f>IFERROR(AVERAGEIF($H$5:$H$51,B55,$G$5:$G$51),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C51" s="15">
-        <f>COUNTIF($H$5:$H$46,B51)</f>
-        <v/>
-      </c>
-      <c r="D51" s="15">
-        <f>SUMIF(Plan!$I$5:$I$46,B51,Plan!$E$5:$E$46)</f>
-        <v/>
-      </c>
-      <c r="E51" s="36">
-        <f>IF(Resumen!$C$17=0,0,D51/Resumen!$C$17)</f>
-        <v/>
-      </c>
-      <c r="F51" s="37">
-        <f>IFERROR(AVERAGEIF($H$5:$H$46,B51,$G$5:$G$46),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="18" t="inlineStr">
+      <c r="C56" s="15">
+        <f>COUNTIF($H$5:$H$51,B56)</f>
+        <v/>
+      </c>
+      <c r="D56" s="15">
+        <f>SUMIF(Plan!$I$5:$I$51,B56,Plan!$E$5:$E$51)</f>
+        <v/>
+      </c>
+      <c r="E56" s="36">
+        <f>IF(Resumen!$C$17=0,0,D56/Resumen!$C$17)</f>
+        <v/>
+      </c>
+      <c r="F56" s="37">
+        <f>IFERROR(AVERAGEIF($H$5:$H$51,B56,$G$5:$G$51),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="18" t="inlineStr">
         <is>
           <t>A+B</t>
         </is>
       </c>
-      <c r="C52" s="15">
-        <f>COUNTIF($H$5:$H$46,B52)</f>
-        <v/>
-      </c>
-      <c r="D52" s="15">
-        <f>SUMIF(Plan!$I$5:$I$46,B52,Plan!$E$5:$E$46)</f>
-        <v/>
-      </c>
-      <c r="E52" s="36">
-        <f>IF(Resumen!$C$17=0,0,D52/Resumen!$C$17)</f>
-        <v/>
-      </c>
-      <c r="F52" s="37">
-        <f>IFERROR(AVERAGEIF($H$5:$H$46,B52,$G$5:$G$46),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="19" t="inlineStr">
+      <c r="C57" s="15">
+        <f>COUNTIF($H$5:$H$51,B57)</f>
+        <v/>
+      </c>
+      <c r="D57" s="15">
+        <f>SUMIF(Plan!$I$5:$I$51,B57,Plan!$E$5:$E$51)</f>
+        <v/>
+      </c>
+      <c r="E57" s="36">
+        <f>IF(Resumen!$C$17=0,0,D57/Resumen!$C$17)</f>
+        <v/>
+      </c>
+      <c r="F57" s="37">
+        <f>IFERROR(AVERAGEIF($H$5:$H$51,B57,$G$5:$G$51),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C53" s="9">
-        <f>SUM(C50:C52)</f>
-        <v/>
-      </c>
-      <c r="F53" s="11">
-        <f>AVERAGE($G$5:$G$46)</f>
+      <c r="C58" s="9">
+        <f>SUM(C55:C57)</f>
+        <v/>
+      </c>
+      <c r="F58" s="11">
+        <f>AVERAGE($G$5:$G$51)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I5:I46">
+  <conditionalFormatting sqref="I5:I51">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$I5="Hecho"</formula>
     </cfRule>
@@ -22282,7 +24470,7 @@
       <formula>$I5="Bloqueado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G46">
+  <conditionalFormatting sqref="G5:G51">
     <cfRule type="expression" priority="5" dxfId="17">
       <formula>G5&gt;0</formula>
     </cfRule>
@@ -22685,7 +24873,7 @@
         </is>
       </c>
       <c r="F5" s="15">
-        <f>COUNTIF(Plan!$D$5:$D$46,A5)</f>
+        <f>COUNTIF(Plan!$D$5:$D$51,A5)</f>
         <v/>
       </c>
     </row>
@@ -22712,7 +24900,7 @@
         </is>
       </c>
       <c r="F6" s="15">
-        <f>COUNTIF(Plan!$D$5:$D$46,A6)</f>
+        <f>COUNTIF(Plan!$D$5:$D$51,A6)</f>
         <v/>
       </c>
     </row>
@@ -22739,7 +24927,7 @@
         </is>
       </c>
       <c r="F7" s="15">
-        <f>COUNTIF(Plan!$D$5:$D$46,A7)</f>
+        <f>COUNTIF(Plan!$D$5:$D$51,A7)</f>
         <v/>
       </c>
     </row>
@@ -22766,7 +24954,7 @@
         </is>
       </c>
       <c r="F8" s="15">
-        <f>COUNTIF(Plan!$D$5:$D$46,A8)</f>
+        <f>COUNTIF(Plan!$D$5:$D$51,A8)</f>
         <v/>
       </c>
     </row>
@@ -22793,7 +24981,7 @@
         </is>
       </c>
       <c r="F9" s="15">
-        <f>COUNTIF(Plan!$D$5:$D$46,A9)</f>
+        <f>COUNTIF(Plan!$D$5:$D$51,A9)</f>
         <v/>
       </c>
     </row>
@@ -22843,7 +25031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22900,24 +25088,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
+          <t>6.3, 5.2, 5.8; P-39, P-53</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
+          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
+          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
         </is>
       </c>
     </row>
@@ -22929,22 +25117,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Agente ga-auditor-supabase corregido</t>
+          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
         </is>
       </c>
     </row>
@@ -22954,24 +25142,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>3.1, 6.5, 6.10; P-09</t>
+          <t>5.2, 5.8, 6.3</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
         </is>
       </c>
     </row>
@@ -22983,22 +25171,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ga-escritor-tests</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
         </is>
       </c>
     </row>
@@ -23008,24 +25196,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-funcionalidad-botones</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+          <t>2.1, 5.3, 5.7; P-16, P-52</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
         </is>
       </c>
     </row>
@@ -23037,22 +25225,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
         </is>
       </c>
     </row>
@@ -23062,24 +25250,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
         </is>
       </c>
     </row>
@@ -23091,20 +25279,182 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>Sebas</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Agente ga-auditor-supabase corregido</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>3.1, 6.5, 6.10; P-09</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ga-verificador-qa</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>Claude (sesión principal)</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Todas</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Creación del Excel de avances</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Pendientes desde PENDIENTES.md, plan desde la propuesta (6 fases, 8 semanas) reorganizado en 2 filas con cola infinita y pesos 1–5.</t>
         </is>

--- a/docs/avances/Avances_Green_Alliance.xlsx
+++ b/docs/avances/Avances_Green_Alliance.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bitácora" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$4:$R$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B46,Pendientes!$G$5:$G$78,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B46,Pendientes!$G$5:$G$85,"Hecho")</f>
         <v/>
       </c>
       <c r="D46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B46,Pendientes!$G$5:$G$78,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B46,Pendientes!$G$5:$G$85,"En curso")</f>
         <v/>
       </c>
       <c r="E46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B46,Pendientes!$G$5:$G$78,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B46,Pendientes!$G$5:$G$85,"Pendiente")</f>
         <v/>
       </c>
       <c r="F46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B46,Pendientes!$G$5:$G$78,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B46,Pendientes!$G$5:$G$85,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G46" s="9">
@@ -1522,19 +1522,19 @@
         </is>
       </c>
       <c r="C47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B47,Pendientes!$G$5:$G$78,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B47,Pendientes!$G$5:$G$85,"Hecho")</f>
         <v/>
       </c>
       <c r="D47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B47,Pendientes!$G$5:$G$78,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B47,Pendientes!$G$5:$G$85,"En curso")</f>
         <v/>
       </c>
       <c r="E47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B47,Pendientes!$G$5:$G$78,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B47,Pendientes!$G$5:$G$85,"Pendiente")</f>
         <v/>
       </c>
       <c r="F47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B47,Pendientes!$G$5:$G$78,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B47,Pendientes!$G$5:$G$85,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G47" s="9">
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B48,Pendientes!$G$5:$G$78,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B48,Pendientes!$G$5:$G$85,"Hecho")</f>
         <v/>
       </c>
       <c r="D48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B48,Pendientes!$G$5:$G$78,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B48,Pendientes!$G$5:$G$85,"En curso")</f>
         <v/>
       </c>
       <c r="E48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B48,Pendientes!$G$5:$G$78,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B48,Pendientes!$G$5:$G$85,"Pendiente")</f>
         <v/>
       </c>
       <c r="F48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B48,Pendientes!$G$5:$G$78,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B48,Pendientes!$G$5:$G$85,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G48" s="9">
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B49,Pendientes!$G$5:$G$78,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B49,Pendientes!$G$5:$G$85,"Hecho")</f>
         <v/>
       </c>
       <c r="D49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B49,Pendientes!$G$5:$G$78,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B49,Pendientes!$G$5:$G$85,"En curso")</f>
         <v/>
       </c>
       <c r="E49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B49,Pendientes!$G$5:$G$78,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B49,Pendientes!$G$5:$G$85,"Pendiente")</f>
         <v/>
       </c>
       <c r="F49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B49,Pendientes!$G$5:$G$78,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B49,Pendientes!$G$5:$G$85,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G49" s="9">
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B50,Pendientes!$G$5:$G$78,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B50,Pendientes!$G$5:$G$85,"Hecho")</f>
         <v/>
       </c>
       <c r="D50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B50,Pendientes!$G$5:$G$78,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B50,Pendientes!$G$5:$G$85,"En curso")</f>
         <v/>
       </c>
       <c r="E50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B50,Pendientes!$G$5:$G$78,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B50,Pendientes!$G$5:$G$85,"Pendiente")</f>
         <v/>
       </c>
       <c r="F50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$78,$B50,Pendientes!$G$5:$G$78,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$85,$B50,Pendientes!$G$5:$G$85,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G50" s="9">
@@ -1639,7 +1639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>P-43</t>
+          <t>P-72</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Aplicar en producción la migración 20260923210000_limite_de_intentos.sql</t>
+          <t>Dar a Carlos acceso de colaborador al repo GitHub GreenAllianceCoo/PagGreenAlliance y compartirle el encargo (sin llaves de producción)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Sebas (ga-auditor-supabase revisa antes)</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="21">
@@ -1818,14 +1818,14 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Crea la tabla limites_intentos y la función registrar_intento, que usan /afiliacion, /ingresar y «Reenviar código» (dentroDelLimite). Sin ella esos límites fallan en producción. Antes del despliegue (6.5). 23-sep: auditada por ga-auditor-supabase, se puede aplicar tal cual (docs/auditorias/2026-09-23-limite-de-intentos.md); falta que Sebas haga db push.</t>
+          <t>Necesario antes de que Carlos pueda abrir PRs a develop desde su propia rama. 24-sep: Sebas ya habló con Carlos para darle el acceso; falta confirmarlo en GitHub.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>P-44</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Variables: SUPABASE_SERVICE_ROLE_KEY, INGRESO_COOKIE_SECRET, LIMITE_HMAC_SECRET, RESEND_API_KEY, EMAIL_FROM, SITIO_URL, RESEND_TEMPLATE_INGRESO_ACEPTADO, RESEND_TEMPLATE_CREDITO_APROBADO, RESEND_TEMPLATE_CREDITO_RECHAZADO, RESEND_TEMPLATE_SORTEO_BOLETA, NEXT_PUBLIC_WHATSAPP</t>
+          <t>Aplicar en producción la migración 20260923210000_limite_de_intentos.sql</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Sebas (ga-auditor-supabase revisa antes)</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="I7" s="21">
@@ -1869,14 +1869,14 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>NEXT_PUBLIC_WHATSAPP ya tiene dato (P-10, 311 724 1942). LIMITE_HMAC_SECRET: 32+ caracteres, distinto de INGRESO_COOKIE_SECRET, en Production y Preview (sin él el build falla); también en .env.local para `npm start`. 24-sep: SUPABASE_SERVICE_ROLE_KEY da «Invalid API key» en Vercel (P-60) y RESEND_API_KEY, EMAIL_FROM y RESEND_TEMPLATE_SORTEO_BOLETA ahora son obligatorias para el build (P-61).</t>
+          <t>Crea la tabla limites_intentos y la función registrar_intento, que usan /afiliacion, /ingresar y «Reenviar código» (dentroDelLimite). Sin ella esos límites fallan en producción. Antes del despliegue (6.5). 23-sep: auditada por ga-auditor-supabase, se puede aplicar tal cual (docs/auditorias/2026-09-23-limite-de-intentos.md); falta que Sebas haga db push.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>P-45</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Panel de producción: OTP de 6 dígitos, vencimiento del código en 600 s (10 min) e intervalo entre correos ≤ 45 s</t>
+          <t>Variables: SUPABASE_SERVICE_ROLE_KEY, INGRESO_COOKIE_SECRET, LIMITE_HMAC_SECRET, RESEND_API_KEY, EMAIL_FROM, SITIO_URL, RESEND_TEMPLATE_INGRESO_ACEPTADO, RESEND_TEMPLATE_CREDITO_APROBADO, RESEND_TEMPLATE_CREDITO_RECHAZADO, RESEND_TEMPLATE_SORTEO_BOLETA, NEXT_PUBLIC_WHATSAPP</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Yo (panel Supabase/Resend)</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="I8" s="21">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Complementa P-19 (SMTP) y P-20 (plantilla Magic Link con {{ .Token }}).</t>
+          <t>NEXT_PUBLIC_WHATSAPP ya tiene dato (P-10, 311 724 1942). LIMITE_HMAC_SECRET: 32+ caracteres, distinto de INGRESO_COOKIE_SECRET, en Production y Preview (sin él el build falla); también en .env.local para `npm start`. 24-sep: SUPABASE_SERVICE_ROLE_KEY da «Invalid API key» en Vercel (P-60) y RESEND_API_KEY, EMAIL_FROM y RESEND_TEMPLATE_SORTEO_BOLETA ahora son obligatorias para el build (P-61). El dominio www.greenallianceco.com ya quedó conectado en Vercel; falta poner SITIO_URL=https://www.greenallianceco.com junto con RESEND_API_KEY, EMAIL_FROM y las 4 RESEND_TEMPLATE_*.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>P-59</t>
+          <t>P-45</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Aplicar en producción las 9 migraciones de fase 2 (20260924000000…000800) y desplegar enseguida</t>
+          <t>Panel de producción: OTP de 6 dígitos, vencimiento del código en 600 s (10 min) e intervalo entre correos ≤ 45 s</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Sebas (ga-auditor-supabase revisa antes)</t>
+          <t>Yo (panel Supabase/Resend)</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I9" s="21">
@@ -1971,14 +1971,14 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Comprobar que hay 0 afiliaciones en producción antes de hacer db push.</t>
+          <t>Complementa P-19 (SMTP) y P-20 (plantilla Magic Link con {{ .Token }}).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>P-60</t>
+          <t>P-59</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1988,17 +1988,17 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (hoy da «Invalid API key»)</t>
+          <t>Aplicar en producción las 9 migraciones de fase 2 (20260924000000…000800) y desplegar enseguida</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Sebas (ga-auditor-supabase revisa antes)</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -2013,19 +2013,23 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I10" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H10,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Comprobar que hay 0 afiliaciones en producción antes de hacer db push.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>P-61</t>
+          <t>P-60</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2035,12 +2039,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Crear en Resend las plantillas de ingreso aceptado, crédito aprobado/rechazado y boleta del sorteo (ga-sorteo-boleta); confirmar el tope de 3 reenvíos de boleta al día</t>
+          <t>Corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (hoy da «Invalid API key»)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2067,16 +2071,12 @@
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H11,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>RESEND_API_KEY, EMAIL_FROM y RESEND_TEMPLATE_SORTEO_BOLETA ya son obligatorias para el build.</t>
-        </is>
-      </c>
+      <c r="J11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>P-72</t>
+          <t>P-61</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Dar a Carlos acceso de colaborador al repo GitHub GreenAllianceCoo/PagGreenAlliance y compartirle el encargo (sin llaves de producción)</t>
+          <t>Crear en Resend las plantillas de ingreso aceptado, crédito aprobado/rechazado y boleta del sorteo (ga-sorteo-boleta); confirmar el tope de 3 reenvíos de boleta al día</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="I12" s="21">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Necesario antes de que Carlos pueda abrir PRs a develop desde su propia rama.</t>
+          <t>RESEND_API_KEY, EMAIL_FROM y RESEND_TEMPLATE_SORTEO_BOLETA ya son obligatorias para el build. 24-sep: el HTML de las 4 plantillas (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) ya está listo en docs/resend/, con el mismo diseño del correo del código; falta que Sebas las cree y publique en Resend.</t>
         </is>
       </c>
     </row>
@@ -3708,14 +3708,14 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>Ruta /politica-de-datos ya existe (placeholder). 24-sep: debe incluir la autorización de datos sensibles para las fotos de cédula y la selfie (Ley 1581). Bloquea el despliegue.</t>
+          <t>Ruta /politica-de-datos ya existe. 24-sep: borrador completo con 10 secciones (Ley 1581, Decreto 1377) y la autorización de datos sensibles para fotos y selfie; los datos que faltan quedan resaltados en la página con &lt;Pendiente&gt;. Faltan de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa de verificación sin selfie (P-78), plazos de conservación de fotos y demás datos (P-79, ligado a P-63) y si reportan a centrales de riesgo Ley 1266 (P-80); y falta revisión de un abogado (P-81). Bloquea el despliegue.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-75</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Texto de vigilancia de Supersolidaria (TEXTO_VIGILANCIA)</t>
+          <t>NIT, dirección y ciudad de la cooperativa para la política de datos</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -3750,19 +3750,23 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I45" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H45,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J45" s="7" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>24-sep: reportado por la sesión principal, necesario para publicar /politica-de-datos.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-76</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3772,12 +3776,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Nombres oficiales de los grados</t>
+          <t>Fecha de vigencia de la política de datos</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -3787,7 +3791,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -3797,7 +3801,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I46" s="21">
@@ -3806,14 +3810,14 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>Se usan en el select «Grado» (grados_credito).</t>
+          <t>24-sep: reportado por la sesión principal.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>P-47</t>
+          <t>P-77</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -3823,12 +3827,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Estado de desembolso (cómo y cuándo se informa al asociado)</t>
+          <t>País o región de los servidores (Supabase, Vercel, Resend)</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -3838,7 +3842,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -3848,7 +3852,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I47" s="21">
@@ -3857,14 +3861,14 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>Reportado por ga-funcionalidad-botones el 23-sep.</t>
+          <t>24-sep: reportado por la sesión principal, dato exigido por la Ley 1581 para informar transferencia internacional de datos.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-78</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -3874,12 +3878,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Fotos reales, cifras y testimonios</t>
+          <t>Alternativa de verificación para quien no quiera subir la selfie</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -3889,7 +3893,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -3899,7 +3903,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I48" s="21">
@@ -3908,14 +3912,14 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>23-sep: los espacios de foto de la landing ya tienen diseño de marca (EspacioFoto). Para poner la foto real se cambia `null` por { src, alt }. Faltan las fotos de la cooperativa.</t>
+          <t>24-sep: reportado por la sesión principal.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-79</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -3925,12 +3929,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Asociados</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Correos reales de los asociados (Excel de importación)</t>
+          <t>Plazos de conservación de los datos (fotos de rechazados y de asociados, y demás datos)</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -3945,12 +3949,12 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I49" s="21">
@@ -3959,14 +3963,14 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Ya no aplica: decisión de la cooperativa 2026-09-24, no habrá importación de Excel. El ingreso ahora se resuelve con la afiliación v2 (correo institucional propio) más aprobación en /admin.</t>
+          <t>24-sep: reportado por la sesión principal; el plazo de las fotos es el mismo que decida P-63 (borrado automático de fotos rechazadas, 5.10).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3981,7 +3985,7 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Número de WhatsApp (NEXT_PUBLIC_WHATSAPP)</t>
+          <t>Texto de vigilancia de Supersolidaria (TEXTO_VIGILANCIA)</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -3996,7 +4000,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -4008,16 +4012,12 @@
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H50,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>24-sep: 311 724 1942.</t>
-        </is>
-      </c>
+      <c r="J50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>P-46</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Días hábiles de respuesta (DIAS_RESPUESTA)</t>
+          <t>Nombres oficiales de los grados</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -4061,14 +4061,14 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>24-sep: la cooperativa dio el tiempo de respuesta como «4 horas o menos» (ver P-17); se usa ese dato en vez de días hábiles.</t>
+          <t>Se usan en el select «Grado» (grados_credito).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-47</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -4078,12 +4078,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Correo de contacto (CORREO_CONTACTO)</t>
+          <t>Estado de desembolso (cómo y cuándo se informa al asociado)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>24-sep: soporte@greenallianceco.com.</t>
+          <t>Reportado por ga-funcionalidad-botones el 23-sep.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>P-80</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -4129,17 +4129,17 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Destino de «Nueva solicitud» (nav y acceso rápido)</t>
+          <t>Si van a reportar a centrales de riesgo (Ley 1266, autorización aparte)</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I53" s="21">
@@ -4163,14 +4163,14 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>Hoy es href="#".</t>
+          <t>24-sep: reportado por la sesión principal.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Tiempo de respuesta real ([TIEMPO] y [T])</t>
+          <t>Fotos reales, cifras y testimonios</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
@@ -4214,34 +4214,34 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>24-sep: «4 horas o menos».</t>
+          <t>23-sep: los espacios de foto de la landing ya tienen diseño de marca (EspacioFoto). Para poner la foto real se cambia `null` por { src, alt }. Faltan las fotos de la cooperativa.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>P-58</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Verificación y cierre</t>
+          <t>Dato de la cooperativa</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Asociados</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Actualizar tests/e2e a la afiliación v2 y a la nueva máscara de correo</t>
+          <t>Correos reales de los asociados (Excel de importación)</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>ga-escritor-tests</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I55" s="21">
@@ -4265,128 +4265,136 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>d-afiliacion.spec.ts usa el formulario viejo (nombres y apellidos, unidad) y hace falta reescribirlo entero para institución/Nequi/asesor/fotos (k-roles.spec.ts ya cubre un caso feliz v2 pero no reemplaza la cobertura de D). 24-sep: ga-escritor-tests lo reescribió entero (48 pruebas × 2 proyectos); 92/96 pasan, 4 fallan por un bug real de la app (ver P-74), no de la prueba. b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts siguen con el formato viejo de máscara de correo y dominios (formato nuevo xx•••@yy•••.co); ese trabajo pasa a Carlos Pardo (ver P-71, 6.15). Falta correr npm run test:db (pgTAP), bloqueado por el permiso de la sandbox. Actualización: el bug de P-74 ya está corregido y d-afiliacion pasa 96/96; pgTAP 222/222 corrido por la sesión principal.</t>
+          <t>Ya no aplica: decisión de la cooperativa 2026-09-24, no habrá importación de Excel. El ingreso ahora se resuelve con la afiliación v2 (correo institucional propio) más aprobación en /admin.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Verificación y cierre</t>
+          <t>Dato de la cooperativa</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Despliegue</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Subir a GitHub y desplegar en Vercel</t>
+          <t>Número de WhatsApp (NEXT_PUBLIC_WHATSAPP)</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I56" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H56,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>24-sep: 311 724 1942.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>P-64</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Verificación y cierre</t>
+          <t>Dato de la cooperativa</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Abrir el PR de develop a main</t>
+          <t>Días hábiles de respuesta (DIAS_RESPUESTA)</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I57" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H57,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>24-sep: la cooperativa dio el tiempo de respuesta como «4 horas o menos» (ver P-17); se usa ese dato en vez de días hábiles.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>P-62</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Verificación y cierre</t>
+          <t>Dato de la cooperativa</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Borrar la cuenta admin de prueba «Test QA» (cédula 1099887766) desde el panel de Supabase</t>
+          <t>Correo de contacto (CORREO_CONTACTO)</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -4396,12 +4404,12 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I58" s="21">
@@ -4410,34 +4418,34 @@
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>Ya hay 3 administradores reales en producción: Ricardo, Abogados Prieto y Sebas.</t>
+          <t>24-sep: soporte@greenallianceco.com.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>P-70</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Verificación y cierre</t>
+          <t>Dato de la cooperativa</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Pruebas en celulares reales (Android e iPhone): cámara, código, sorteo, crédito y correos en Gmail/Outlook, con informe y capturas</t>
+          <t>Destino de «Nueva solicitud» (nav y acceso rápido)</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Carlos Pardo</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -4447,12 +4455,12 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I59" s="21">
@@ -4461,49 +4469,49 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
+          <t>Hoy es href="#".</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>P-71</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Verificación y cierre</t>
+          <t>Dato de la cooperativa</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Actualizar tests/e2e b-ingreso, i-despliegue y j-produccion al formato nuevo de máscara de correo</t>
+          <t>Tiempo de respuesta real ([TIEMPO] y [T])</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Carlos Pardo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I60" s="21">
@@ -4512,14 +4520,14 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Parte del alcance que P-58 dejó fuera. Ver P-73.</t>
+          <t>24-sep: «4 horas o menos».</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-58</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -4529,17 +4537,17 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Calidad</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Correr ga-verificador-qa y ga-verificador-responsive</t>
+          <t>Actualizar tests/e2e a la afiliación v2 y a la nueva máscara de correo</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -4549,12 +4557,12 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I61" s="21">
@@ -4563,14 +4571,14 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>QA 1 hecha el 23-sep (186 pasan, 2 fallan; informe docs/verificaciones/2026-09-23-verificacion-1.md). Responsive hecha el 23-sep: 2 fallas de scroll corregidas (5.8) y segunda pasada con 0 fallas en 13 anchos (320–1920 px); tests/responsive 10/10. La QA final sigue en 6.3.</t>
+          <t>d-afiliacion.spec.ts usa el formulario viejo (nombres y apellidos, unidad) y hace falta reescribirlo entero para institución/Nequi/asesor/fotos (k-roles.spec.ts ya cubre un caso feliz v2 pero no reemplaza la cobertura de D). 24-sep: ga-escritor-tests lo reescribió entero (48 pruebas × 2 proyectos); 92/96 pasan, 4 fallan por un bug real de la app (ver P-74), no de la prueba. b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts siguen con el formato viejo de máscara de correo y dominios (formato nuevo xx•••@yy•••.co); ese trabajo pasa a Carlos Pardo (ver P-71, 6.15). Falta correr npm run test:db (pgTAP), bloqueado por el permiso de la sandbox. Actualización: el bug de P-74 ya está corregido y d-afiliacion pasa 96/96; pgTAP 222/222 corrido por la sesión principal.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -4580,12 +4588,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Despliegue</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Commit de las pantallas nuevas</t>
+          <t>Subir a GitHub y desplegar en Vercel</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -4600,28 +4608,24 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I62" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H62,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>Commit d86db86 en develop.</t>
-        </is>
-      </c>
+      <c r="J62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-64</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -4631,48 +4635,44 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Borrar /login y /dashboard cuando /ingresar y /cuenta funcionen</t>
+          <t>Abrir el PR de develop a main</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I63" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H63,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J63" s="7" t="inlineStr">
-        <is>
-          <t>Borradas el 23-sep (incluida /dashboard/solicitar, su parte del proxy y los colores heredados de tailwind.config.ts).</t>
-        </is>
-      </c>
+      <c r="J63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-81</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -4682,32 +4682,32 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Revisar si conviene confiar en x-forwarded-for para el límite de intentos por IP</t>
+          <t>Revisión de la política de datos por un abogado</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I64" s="21">
@@ -4716,14 +4716,14 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-verificador-qa el 23-sep. Documentado por ga-funcionalidad-botones como O-01 en lib/servidor/limite.ts: x-forwarded-for/x-real-ip solo son confiables detrás de Vercel (nuestro caso); el límite real por cédula/IP lo hace la app, no Supabase.</t>
+          <t>24-sep: reportado por la sesión principal; falta antes de publicar /politica-de-datos.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-70</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -4733,17 +4733,17 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Correos</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Confirmar que salen los correos de afiliación (el log queda en la terminal de next dev)</t>
+          <t>Pruebas en celulares reales (Android e iPhone): cámara, código, sorteo, crédito y correos en Gmail/Outlook, con informe y capturas</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Carlos Pardo</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="I65" s="21">
@@ -4767,14 +4767,14 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>Ya no aplica: el 23-sep se quitaron los correos de afiliación del código (decisión de Sebas).</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-71</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -4784,32 +4784,32 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Mapa de botones: §4 «Nueva solicitud» → /cuenta/solicitar y sección para la ruta /cuenta/solicitar</t>
+          <t>Actualizar tests/e2e b-ingreso, i-despliegue y j-produccion al formato nuevo de máscara de correo</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Carlos Pardo</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="I66" s="21">
@@ -4818,34 +4818,34 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>Reportado por ga-diseno-a-codigo. Verificado el 23-sep: docs/mapa-de-botones.md ya tiene §4 «Nueva solicitud» → /cuenta/solicitar (Definido) y §4b /cuenta/solicitar; /dashboard se eliminó.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Parte del alcance que P-58 dejó fuera. Ver P-73.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>P-63</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Fase 2</t>
+          <t>Calidad</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Preguntas abiertas de fase 2 para la cooperativa: grados del Ejército, dominios de correo institucionales (hoy solo policia.gov.co, buzonejercito.mil.co, ejercito.mil.co), tiempo que se guardan las fotos y tope de intentos del sorteo</t>
+          <t>Correr ga-verificador-qa y ga-verificador-responsive</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I67" s="21">
@@ -4869,49 +4869,49 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>Ver docs/spec-fase-2.md §Preguntas abiertas.</t>
+          <t>QA 1 hecha el 23-sep (186 pasan, 2 fallan; informe docs/verificaciones/2026-09-23-verificacion-1.md). Responsive hecha el 23-sep: 2 fallas de scroll corregidas (5.8) y segunda pasada con 0 fallas en 13 anchos (320–1920 px); tests/responsive 10/10. La QA final sigue en 6.3.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
+          <t>Commit de las pantallas nuevas</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I68" s="21">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>Por ahora son una sección en /cuenta (#convenios).</t>
+          <t>Commit d86db86 en develop.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>A 320 px la línea «COOPERATIVA» del logo mide ~5 px de alto (opcional: ocultarla o achicar «Ingresar» bajo 360 px)</t>
+          <t>Borrar /login y /dashboard cuando /ingresar y /cuenta funcionen</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -4952,17 +4952,17 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I69" s="21">
@@ -4971,39 +4971,39 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>Menor y opcional, reportado por ga-verificador-responsive el 23-sep.</t>
+          <t>Borradas el 23-sep (incluida /dashboard/solicitar, su parte del proxy y los colores heredados de tailwind.config.ts).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
+          <t>Revisar si conviene confiar en x-forwarded-for para el límite de intentos por IP</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Sebas (ga-auditor-supabase revisa antes)</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I70" s="21">
@@ -5022,29 +5022,29 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
+          <t>Sugerido por ga-verificador-qa el 23-sep. Documentado por ga-funcionalidad-botones como O-01 en lib/servidor/limite.ts: x-forwarded-for/x-real-ip solo son confiables detrás de Vercel (nuestro caso); el límite real por cédula/IP lo hace la app, no Supabase.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
+          <t>Confirmar que salen los correos de afiliación (el log queda en la terminal de next dev)</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="21">
@@ -5073,34 +5073,34 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>Apartado «Mis datos» ya maquetado.</t>
+          <t>Ya no aplica: el 23-sep se quitaron los correos de afiliación del código (decisión de Sebas).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>P-65</t>
+          <t>P-62</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Sorteo</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Decidir si un admin o un asesor pueden participar en el sorteo mensual</t>
+          <t>Borrar la cuenta admin de prueba «Test QA» (cédula 1099887766) desde el panel de Supabase</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I72" s="21">
@@ -5124,34 +5124,34 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-revisor-seguridad el 24-sep. 24-sep: decidido que solo participan asociados (S-13, ya implementado en participarSorteo).</t>
+          <t>Ya hay 3 administradores reales en producción: Ricardo, Abogados Prieto y Sebas. 24-sep: usuario «Test QA» borrado de producción por Sebas.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Color de error #B3261E</t>
+          <t>Mapa de botones: §4 «Nueva solicitud» → /cuenta/solicitar y sección para la ruta /cuenta/solicitar</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I73" s="21">
@@ -5175,14 +5175,14 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>Se deja.</t>
+          <t>Reportado por ga-diseno-a-codigo. Verificado el 23-sep: docs/mapa-de-botones.md ya tiene §4 «Nueva solicitud» → /cuenta/solicitar (Definido) y §4b /cuenta/solicitar; /dashboard se eliminó.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-63</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -5192,32 +5192,32 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Fase 2</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Estado vacío de «Tu solicitud»</t>
+          <t>Preguntas abiertas de fase 2 para la cooperativa: grados del Ejército, dominios de correo institucionales (hoy solo policia.gov.co, buzonejercito.mil.co, ejercito.mil.co), tiempo que se guardan las fotos y tope de intentos del sorteo</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I74" s="21">
@@ -5226,14 +5226,14 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>Ver con /cuenta?vacio=1.</t>
+          <t>Ver docs/spec-fase-2.md §Preguntas abiertas.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -5243,17 +5243,17 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Logo en celular como enlace a la landing</t>
+          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -5263,24 +5263,28 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I75" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H75,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>Por ahora son una sección en /cuenta (#convenios).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -5290,12 +5294,12 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Escudo: public/logos/vector/green-alliance-logo.svg</t>
+          <t>A 320 px la línea «COOPERATIVA» del logo mide ~5 px de alto (opcional: ocultarla o achicar «Ingresar» bajo 360 px)</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -5310,7 +5314,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
@@ -5322,12 +5326,16 @@
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H76,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J76" s="7" t="inlineStr"/>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>Menor y opcional, reportado por ga-verificador-responsive el 23-sep.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -5337,22 +5345,22 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Formulario de ingreso entre 640 y 767 px (columna de 440 px)</t>
+          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Sebas (ga-auditor-supabase revisa antes)</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
@@ -5362,19 +5370,23 @@
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="I77" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H77,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
         <is>
-          <t>P-07</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -5384,12 +5396,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Panel verde en tableta (640–1023 px) centrado</t>
+          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
@@ -5399,7 +5411,7 @@
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
@@ -5409,18 +5421,363 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I78" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H78,Plan!$A$5:$A$64,0)),"—")</f>
         <v/>
       </c>
-      <c r="J78" s="7" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>Apartado «Mis datos» ya maquetado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>P-65</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Sorteo</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Decidir si un admin o un asesor pueden participar en el sorteo mensual</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Cooperativa</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="I79" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H79,Plan!$A$5:$A$64,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>Sugerido por ga-revisor-seguridad el 24-sep. 24-sep: decidido que solo participan asociados (S-13, ya implementado en participarSorteo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>P-01</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Color de error #B3261E</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H80,Plan!$A$5:$A$64,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>Se deja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>P-03</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>/cuenta</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Estado vacío de «Tu solicitud»</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="I81" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H81,Plan!$A$5:$A$64,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>Ver con /cuenta?vacio=1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>P-04</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Logo en celular como enlace a la landing</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H82,Plan!$A$5:$A$64,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>P-05</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Escudo: public/logos/vector/green-alliance-logo.svg</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H83,Plan!$A$5:$A$64,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="inlineStr">
+        <is>
+          <t>P-06</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>/ingresar</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>Formulario de ingreso entre 640 y 767 px (columna de 440 px)</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="I84" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H84,Plan!$A$5:$A$64,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>P-07</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>/ingresar</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Panel verde en tableta (640–1023 px) centrado</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="I85" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$64,MATCH(H85,Plan!$A$5:$A$64,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J85" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J78"/>
-  <conditionalFormatting sqref="G5:G78">
+  <autoFilter ref="A4:J85"/>
+  <conditionalFormatting sqref="G5:G85">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$G5="Hecho"</formula>
     </cfRule>
@@ -5434,7 +5791,7 @@
       <formula>$G5="Bloqueado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F78">
+  <conditionalFormatting sqref="F5:F85">
     <cfRule type="expression" priority="5" dxfId="5">
       <formula>$F5="Alta"</formula>
     </cfRule>
@@ -5445,16 +5802,16 @@
       <formula>$F5="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:F78">
+  <conditionalFormatting sqref="A5:F85">
     <cfRule type="expression" priority="8" dxfId="8">
       <formula>$G5="Hecho"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Hecho,En curso,Pendiente,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8647,7 +9004,7 @@
       </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
-          <t>Página placeholder lista; falta el texto de la política, incluida la autorización de datos sensibles para las fotos de cédula y la selfie (Ley 1581). Bloquea el despliegue (6.5).</t>
+          <t>24-sep: borrador completo (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para fotos y selfie) ya en la página. Falta que la cooperativa dé NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores (P-77), alternativa sin selfie (P-78), plazos de conservación (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); y que un abogado la revise (P-81). Bloquea el despliegue (6.5).</t>
         </is>
       </c>
     </row>
@@ -36130,7 +36487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36189,22 +36546,22 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Sebas (acuerdo con Carlos Pardo)</t>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
+          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
+          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
+          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
         </is>
       </c>
     </row>
@@ -36214,24 +36571,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (acuerdo con Carlos Pardo)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>6.1, P-58</t>
+          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
+          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
+          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
         </is>
       </c>
     </row>
@@ -36241,24 +36598,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Sebas (coordinación con la cooperativa)</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
+          <t>6.1, P-58</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
+          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
+          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
         </is>
       </c>
     </row>
@@ -36268,24 +36625,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (coordinación con la cooperativa)</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
+          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
+          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
+          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
         </is>
       </c>
     </row>
@@ -36297,22 +36654,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
+          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
+          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
         </is>
       </c>
     </row>
@@ -36324,22 +36681,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
+          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
+          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
         </is>
       </c>
     </row>
@@ -36351,22 +36708,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Sorteo mensual en /cuenta</t>
+          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
+          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
         </is>
       </c>
     </row>
@@ -36383,17 +36740,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>4.6; P-57</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
+          <t>Sorteo mensual en /cuenta</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
+          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
         </is>
       </c>
     </row>
@@ -36405,49 +36762,49 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>1.5; P-63</t>
+          <t>4.6; P-57</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
+          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
+          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>1.5; P-63</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
+          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
+          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
         </is>
       </c>
     </row>
@@ -36459,22 +36816,22 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive + ga-verificador-qa</t>
+          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>6.3; P-39</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
+          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
+          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
         </is>
       </c>
     </row>
@@ -36484,24 +36841,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive</t>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>ga-verificador-responsive + ga-verificador-qa</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 5.8; P-39, P-53</t>
+          <t>6.3; P-39</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
+          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
+          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
         </is>
       </c>
     </row>
@@ -36513,22 +36870,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
+          <t>6.3, 5.2, 5.8; P-39, P-53</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
+          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
+          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
         </is>
       </c>
     </row>
@@ -36540,22 +36897,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>5.2, 5.8, 6.3</t>
+          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
+          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
+          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
         </is>
       </c>
     </row>
@@ -36567,22 +36924,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
+          <t>5.2, 5.8, 6.3</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
+          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
+          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
         </is>
       </c>
     </row>
@@ -36594,22 +36951,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>2.1, 5.3, 5.7; P-16, P-52</t>
+          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
+          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
+          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
         </is>
       </c>
     </row>
@@ -36621,22 +36978,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
+          <t>2.1, 5.3, 5.7; P-16, P-52</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
+          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
+          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
         </is>
       </c>
     </row>
@@ -36646,24 +37003,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
+          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
+          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
+          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
         </is>
       </c>
     </row>
@@ -36673,24 +37030,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Sebas</t>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Agente ga-auditor-supabase corregido</t>
+          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
         </is>
       </c>
     </row>
@@ -36700,24 +37057,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>3.1, 6.5, 6.10; P-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+          <t>Agente ga-auditor-supabase corregido</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
         </is>
       </c>
     </row>
@@ -36727,24 +37084,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1, 6.5, 6.10; P-09</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
         </is>
       </c>
     </row>
@@ -36754,24 +37111,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-funcionalidad-botones</t>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
         </is>
       </c>
     </row>
@@ -36781,24 +37138,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-qa</t>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
         </is>
       </c>
     </row>
@@ -36810,22 +37167,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
         </is>
       </c>
     </row>
@@ -36837,20 +37194,47 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>Claude (sesión principal)</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Todas</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Creación del Excel de avances</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>Pendientes desde PENDIENTES.md, plan desde la propuesta (6 fases, 8 semanas) reorganizado en 2 filas con cola infinita y pesos 1–5.</t>
         </is>

--- a/docs/avances/Avances_Green_Alliance.xlsx
+++ b/docs/avances/Avances_Green_Alliance.xlsx
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>P-85</t>
+          <t>P-51</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Correo de afiliación acepta cualquier dominio (ya no exige @policia.gov.co / @ejercito.mil.co)</t>
+          <t>Correo «Ingreso aceptado» (plantilla ga-ingreso-aceptado): acción del admin que aprueba la afiliación, crea el usuario y envía el correo</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I20" s="21">
@@ -2609,14 +2609,14 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>25-sep: esquema zod, campo del formulario y pruebas (unitarias, e2e, pgTAP) actualizados; migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (base de datos) y el archivo local renombrado a esa versión para que el historial coincida. F-01 revisado: la máscara del correo ahora oculta también el dominio («ju•••@•••»). En el commit de hoy, falta desplegar; hasta entonces el formulario en vivo sigue exigiendo correo institucional.</t>
+          <t>No implementado en la app. Requiere RESEND_TEMPLATE_INGRESO_ACEPTADO (P-44). Ver docs/resend-plantillas.md.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>P-89</t>
+          <t>P-66</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2631,27 +2631,27 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Cuenta de demostración para administradores en /admin/demo (pestaña «Demostración»)</t>
+          <t>Dashboard de clientes en /admin: métricas (asociados por grado/institución, afiliaciones y créditos pendientes, montos del mes, inscritos al sorteo), lista con buscador/filtros, detalle de cliente y reasignar asesor</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>Carlos Pardo</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I21" s="21">
@@ -2660,14 +2660,14 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>25-sep: reutiliza la cuenta fantasma de /asesor/demo; lectura de grados compartida en lib/asesor/cargarPaquetesDemo.ts; un asesor no puede entrar. En el commit de hoy, falta desplegar.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-67</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2677,17 +2677,17 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Correos</t>
+          <t>Asesor</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Correo «Ingreso aceptado» (plantilla ga-ingreso-aceptado): acción del admin que aprueba la afiliación, crea el usuario y envía el correo</t>
+          <t>Dashboard del asesor en /asesor: métricas de sus clientes y detalle de cliente sin celular, correo, Nequi ni fotos</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Carlos Pardo</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="I22" s="21">
@@ -2711,14 +2711,14 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>No implementado en la app. Requiere RESEND_TEMPLATE_INGRESO_ACEPTADO (P-44). Ver docs/resend-plantillas.md.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>P-66</t>
+          <t>P-69</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Dashboard de clientes en /admin: métricas (asociados por grado/institución, afiliaciones y créditos pendientes, montos del mes, inscritos al sorteo), lista con buscador/filtros, detalle de cliente y reasignar asesor</t>
+          <t>Ley 1581: borrado automático de fotos de afiliaciones rechazadas tras X días y motivo de rechazo en /admin</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="I23" s="21">
@@ -2762,14 +2762,14 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Falta que la cooperativa dé el X de días (ver P-63). Ver P-73.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>P-67</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2779,22 +2779,22 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Asesor</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Dashboard del asesor en /asesor: métricas de sus clientes y detalle de cliente sin celular, correo, Nequi ni fotos</t>
+          <t>F-01: el select «Grado» se vacía tras un error de validación</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Carlos Pardo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I24" s="21">
@@ -2813,14 +2813,14 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
+          <t>Falla media de la verificación QA 1 (docs/verificaciones/2026-09-23-verificacion-1.md).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>P-69</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2830,22 +2830,22 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>/cuenta/solicitar</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Ley 1581: borrado automático de fotos de afiliaciones rechazadas tras X días y motivo de rechazo en /admin</t>
+          <t>Revisar el diseño de /cuenta/solicitar (sin maqueta; selector 50/100 como radios)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Carlos Pardo</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I25" s="21">
@@ -2864,14 +2864,14 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Falta que la cooperativa dé el X de días (ver P-63). Ver P-73.</t>
+          <t>Pedido por ga-funcionalidad-botones el 23-sep.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-57</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>/asesor</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>F-01: el select «Grado» se vacía tras un error de validación</t>
+          <t>Agregar /asesor al matcher de proxy.ts y redirigir por rol tras el login</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="I26" s="21">
@@ -2915,14 +2915,14 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>Falla media de la verificación QA 1 (docs/verificaciones/2026-09-23-verificacion-1.md).</t>
+          <t>Hoy un asesor que ingresa cae en /cuenta, no en /asesor; la página /asesor igual se protege por su cuenta si se navega directo.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>P-56</t>
+          <t>P-68</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>/cuenta/solicitar</t>
+          <t>Convenios</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Revisar el diseño de /cuenta/solicitar (sin maqueta; selector 50/100 como radios)</t>
+          <t>Convenios administrables desde /admin (crear, editar, ocultar, ordenar, logo en Storage); landing y /cuenta leen de la tabla convenios</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>Carlos Pardo</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="I27" s="21">
@@ -2966,14 +2966,14 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>Pedido por ga-funcionalidad-botones el 23-sep.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>P-57</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>/asesor</t>
+          <t>/ingresar</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Agregar /asesor al matcher de proxy.ts y redirigir por rol tras el login</t>
+          <t>Server Action: correo_por_cedula(), signInWithOtp, cookie firmada, ir a /ingresar/codigo</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -2998,33 +2998,29 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I28" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$65,MATCH(H28,Plan!$A$5:$A$65,0)),"—")</f>
         <v/>
       </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Hoy un asesor que ingresa cae en /cuenta, no en /asesor; la página /asesor igual se protege por su cuenta si se navega directo.</t>
-        </is>
-      </c>
+      <c r="J28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>P-68</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -3034,48 +3030,44 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Convenios</t>
+          <t>/ingresar/codigo</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Convenios administrables desde /admin (crear, editar, ocultar, ordenar, logo en Storage); landing y /cuenta leen de la tabla convenios</t>
+          <t>Leer la cookie del paso 1; sin cookie, volver a /ingresar</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Carlos Pardo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I29" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$65,MATCH(H29,Plan!$A$5:$A$65,0)),"—")</f>
         <v/>
       </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
-        </is>
-      </c>
+      <c r="J29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -3085,12 +3077,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>/ingresar/codigo</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Server Action: correo_por_cedula(), signInWithOtp, cookie firmada, ir a /ingresar/codigo</t>
+          <t>verifyOtp y entrar a /cuenta</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -3110,7 +3102,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I30" s="21">
@@ -3122,7 +3114,7 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3132,12 +3124,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>/ingresar/codigo</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Leer la cookie del paso 1; sin cookie, volver a /ingresar</t>
+          <t>Server Action: zod, límites por IP y cédula, guardar</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -3157,19 +3149,23 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I31" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$65,MATCH(H31,Plan!$A$5:$A$65,0)),"—")</f>
         <v/>
       </c>
-      <c r="J31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>23-sep: se quitaron los correos al equipo y al solicitante (decisión de Sebas). El equipo revisa las afiliaciones en Supabase hasta que exista el panel /admin; el correo «Ingreso aceptado» sale al aprobar (P-51).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-31</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3179,12 +3175,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>/ingresar/codigo</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>verifyOtp y entrar a /cuenta</t>
+          <t>Proteger con proxy.ts y «Salir» con signOut</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -3204,7 +3200,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I32" s="21">
@@ -3216,7 +3212,7 @@
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3226,12 +3222,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Server Action: zod, límites por IP y cédula, guardar</t>
+          <t>Cargar perfil, última solicitud (con tasa), tope y convenios</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -3251,23 +3247,19 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I33" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$65,MATCH(H33,Plan!$A$5:$A$65,0)),"—")</f>
         <v/>
       </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>23-sep: se quitaron los correos al equipo y al solicitante (decisión de Sebas). El equipo revisa las afiliaciones en Supabase hasta que exista el panel /admin; el correo «Ingreso aceptado» sale al aprobar (P-51).</t>
-        </is>
-      </c>
+      <c r="J33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-35</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3277,12 +3269,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Proteger con proxy.ts y «Salir» con signOut</t>
+          <t>Conectar el formulario de crédito a /cuenta</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -3302,19 +3294,23 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I34" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$65,MATCH(H34,Plan!$A$5:$A$65,0)),"—")</f>
         <v/>
       </c>
-      <c r="J34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>23-sep: el formulario vive en /cuenta/solicitar (protegida por proxy.ts, encabezado compartido EncabezadoCuenta); «Nueva solicitud» lleva ahí.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>P-32</t>
+          <t>P-36</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3324,12 +3320,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Cargar perfil, última solicitud (con tasa), tope y convenios</t>
+          <t>Panel /admin: listado, aprobar y rechazar con motivo</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -3349,19 +3345,23 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I35" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$65,MATCH(H35,Plan!$A$5:$A$65,0)),"—")</f>
         <v/>
       </c>
-      <c r="J35" s="7" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>24-sep: implementado y probado en local (commits 235ffbe, a13c2de). Un admin no puede resolver su propia solicitud.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-38</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Asociados</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Conectar el formulario de crédito a /cuenta</t>
+          <t>Importación de asociados desde Excel</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I36" s="21">
@@ -3405,14 +3405,14 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>23-sep: el formulario vive en /cuenta/solicitar (protegida por proxy.ts, encabezado compartido EncabezadoCuenta); «Nueva solicitud» lleva ahí.</t>
+          <t>Ya no aplica: decisión de la cooperativa 2026-09-24, no habrá importación de Excel.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-85</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Panel /admin: listado, aprobar y rechazar con motivo</t>
+          <t>Correo de afiliación acepta cualquier dominio (ya no exige @policia.gov.co / @ejercito.mil.co)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I37" s="21">
@@ -3456,14 +3456,14 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>24-sep: implementado y probado en local (commits 235ffbe, a13c2de). Un admin no puede resolver su propia solicitud.</t>
+          <t>25-sep: esquema zod, campo del formulario y pruebas (unitarias, e2e, pgTAP) actualizados; migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (base de datos) y el archivo local renombrado a esa versión para que el historial coincida. F-01 revisado: la máscara del correo ahora oculta también el dominio («ju•••@•••»). 25-sep: desplegado con el PR #2 (merge 2c19d02); confirmado en vivo que /afiliacion ya no exige correo institucional.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Asociados</t>
+          <t>/ingresar</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Importación de asociados desde Excel</t>
+          <t>Estado «Enviando…» (prop cargando) y errores (prop error)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -3498,23 +3498,19 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I38" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$65,MATCH(H38,Plan!$A$5:$A$65,0)),"—")</f>
         <v/>
       </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>Ya no aplica: decisión de la cooperativa 2026-09-24, no habrá importación de Excel.</t>
-        </is>
-      </c>
+      <c r="J38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3524,12 +3520,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>/ingresar/codigo</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Estado «Enviando…» (prop cargando) y errores (prop error)</t>
+          <t>Casillas OTP: avance automático, Backspace, pegar; «Entrar» con 6 dígitos</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -3549,7 +3545,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I39" s="21">
@@ -3561,7 +3557,7 @@
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -3576,7 +3572,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Casillas OTP: avance automático, Backspace, pegar; «Entrar» con 6 dígitos</t>
+          <t>«Reenviar código» con contador de 45 s; «Cambiar cédula» limpia la cookie</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -3608,7 +3604,7 @@
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -3618,12 +3614,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>/ingresar/codigo</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>«Reenviar código» con contador de 45 s; «Cambiar cédula» limpia la cookie</t>
+          <t>Grados desde grados_credito, honeypot, errores y estado de carga</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -3643,7 +3639,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I41" s="21">
@@ -3655,7 +3651,7 @@
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -3665,12 +3661,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Grados desde grados_credito, honeypot, errores y estado de carga</t>
+          <t>«Mis datos»: actualizar solo perfiles.telefono</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -3690,19 +3686,23 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I42" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$65,MATCH(H42,Plan!$A$5:$A$65,0)),"—")</f>
         <v/>
       </c>
-      <c r="J42" s="7" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>Con error, alinear «Guardar» con el campo desde 640 px.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-74</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>«Mis datos»: actualizar solo perfiles.telefono</t>
+          <t>Bug: esquemaAfiliacion no valida el cruce institución↔correo institucional si falla cualquier otro campo del formulario</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I43" s="21">
@@ -3746,14 +3746,14 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>Con error, alinear «Guardar» con el campo desde 640 px.</t>
+          <t>Reportado por ga-escritor-tests el 24-sep; reproducido en tests/unit/validaciones.test.ts y en tests/e2e/d-afiliacion.spec.ts (D4, casos bug: true). Falta correr npm run test:db (pgTAP), bloqueado por el permiso de la sandbox. Corregido por la sesión principal el 2026-09-24 (commit fedf620): superRefine con `when`; 308 unitarias, 96 e2e de afiliación y 222 pgTAP en verde.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>P-74</t>
+          <t>P-89</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3763,17 +3763,17 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Bug: esquemaAfiliacion no valida el cruce institución↔correo institucional si falla cualquier otro campo del formulario</t>
+          <t>Cuenta de demostración para administradores en /admin/demo (pestaña «Demostración»)</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I44" s="21">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>Reportado por ga-escritor-tests el 24-sep; reproducido en tests/unit/validaciones.test.ts y en tests/e2e/d-afiliacion.spec.ts (D4, casos bug: true). Falta correr npm run test:db (pgTAP), bloqueado por el permiso de la sandbox. Corregido por la sesión principal el 2026-09-24 (commit fedf620): superRefine con `when`; 308 unitarias, 96 e2e de afiliación y 222 pgTAP en verde.</t>
+          <t>25-sep: reutiliza la cuenta fantasma de /asesor/demo; lectura de grados compartida en lib/asesor/cargarPaquetesDemo.ts; un asesor no puede entrar. 25-sep: desplegado con el PR #2 (merge 2c19d02); confirmado por HTTP que /admin/demo redirige a /ingresar sin sesión. Falta que Sebas la confirme a ojo con su propia sesión.</t>
         </is>
       </c>
     </row>
@@ -6126,42 +6126,42 @@
     <row r="91">
       <c r="A91" s="19" t="inlineStr">
         <is>
-          <t>P-83</t>
+          <t>P-88</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Correos</t>
-        </is>
-      </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>S-15: escapar/validar HTML en las variables NOMBRE/MOTIVO de los correos de Resend</t>
+          <t>F2-08: tr_componer_nombre_afiliacion no cubre el update directo de solicitudes_afiliacion.nombre por un admin</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I91" s="21">
@@ -6170,29 +6170,29 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>25-sep: hallazgo de ga-revisor-seguridad (un admin puede meter HTML en perfiles.nombre_completo o en el motivo de rechazo). Corregido en local con pruebas (tests/unit/correo-resend.test.ts); en el commit de hoy, falta desplegar.</t>
+          <t>Documentado en docs/auditorias/2026-09-24-fase-2.md; confirmado sin corregir por ga-revisor-seguridad el 25-sep. Un admin puede reescribir `nombre` por SQL directo, y ese texto lo usan el correo «Ingreso aceptado» y el nombre_completo del perfil. Solo afecta a admins.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="19" t="inlineStr">
         <is>
-          <t>P-84</t>
+          <t>P-83</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>M-01: el número de WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts</t>
+          <t>S-15: escapar/validar HTML en las variables NOMBRE/MOTIVO de los correos de Resend</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I92" s="21">
@@ -6221,49 +6221,49 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>25-sep: hallazgo de ga-verificador-qa (patrón sin la barra invertida de \D/\d; el enlace wa.me sí funciona). Corregido en local con pruebas (tests/unit/config-whatsapp.test.ts); en el commit de hoy, falta desplegar.</t>
+          <t>25-sep: hallazgo de ga-revisor-seguridad (un admin puede meter HTML en perfiles.nombre_completo o en el motivo de rechazo). Corregido en local con pruebas (tests/unit/correo-resend.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>P-88</t>
+          <t>P-84</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>F2-08: tr_componer_nombre_afiliacion no cubre el update directo de solicitudes_afiliacion.nombre por un admin</t>
+          <t>M-01: el número de WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I93" s="21">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>Documentado en docs/auditorias/2026-09-24-fase-2.md; confirmado sin corregir por ga-revisor-seguridad el 25-sep. Un admin puede reescribir `nombre` por SQL directo, y ese texto lo usan el correo «Ingreso aceptado» y el nombre_completo del perfil. Solo afecta a admins.</t>
+          <t>25-sep: hallazgo de ga-verificador-qa (patrón sin la barra invertida de \D/\d; el enlace wa.me sí funciona). Corregido en local con pruebas (tests/unit/config-whatsapp.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02); confirmado en vivo «311 724 1942».</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J5" s="8" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="I6" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J6" s="8" t="n">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J7" s="8" t="n">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>3.7, 5.5, 6.11</t>
+          <t>4.1, 4.2, 2.9</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -6814,7 +6814,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L9" s="8">
         <f>K9+E9</f>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L10" s="8">
         <f>K10+E10</f>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>4.1, 4.2</t>
+          <t>4.6, 6.8, 6.11</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
@@ -6970,7 +6970,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="L11" s="8">
         <f>K11+E11</f>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I12" s="18" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
@@ -7126,7 +7126,7 @@
         <v>6</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L13" s="8">
         <f>K13+E13</f>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.6, 2.7</t>
         </is>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -7204,7 +7204,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L14" s="8">
         <f>K14+E14</f>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.3, 3.4</t>
         </is>
       </c>
       <c r="I15" s="18" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>3.1, 3.4</t>
+          <t>3.4, 2.4</t>
         </is>
       </c>
       <c r="I16" s="18" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>3.4, 2.9</t>
+          <t>2.4, 6.10</t>
         </is>
       </c>
       <c r="I17" s="18" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr">
@@ -7513,10 +7513,10 @@
         </is>
       </c>
       <c r="J18" s="8" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L18" s="8">
         <f>K18+E18</f>
@@ -7582,19 +7582,19 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>2.7, 4.1</t>
+          <t>1.5, 3.6, 6.4</t>
         </is>
       </c>
       <c r="I19" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J19" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L19" s="8">
         <f>K19+E19</f>
@@ -7660,19 +7660,19 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I20" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J20" s="8" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L20" s="8">
         <f>K20+E20</f>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>53</v>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>5.2, 1.6</t>
+          <t>5.5, 1.6</t>
         </is>
       </c>
       <c r="I22" s="18" t="inlineStr">
@@ -7825,10 +7825,10 @@
         </is>
       </c>
       <c r="J22" s="8" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L22" s="8">
         <f>K22+E22</f>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I23" s="18" t="inlineStr">
@@ -7903,10 +7903,10 @@
         </is>
       </c>
       <c r="J23" s="8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L23" s="8">
         <f>K23+E23</f>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>2.5, 2.6</t>
+          <t>1.4, 2.2</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -7984,7 +7984,7 @@
         <v>4</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L24" s="8">
         <f>K24+E24</f>
@@ -8050,19 +8050,19 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>5.7, 5.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L25" s="8">
         <f>K25+E25</f>
@@ -8128,7 +8128,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3.6, 2.8</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L26" s="8">
         <f>K26+E26</f>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>2.6, 2.7</t>
+          <t>2.5, 2.6</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
@@ -8218,7 +8218,7 @@
         <v>6</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L27" s="8">
         <f>K27+E27</f>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>4.2, 2.10, 6.10</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I28" s="18" t="inlineStr">
@@ -8296,7 +8296,7 @@
         <v>16</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L28" s="8">
         <f>K28+E28</f>
@@ -8362,19 +8362,19 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L29" s="8">
         <f>K29+E29</f>
@@ -8440,19 +8440,19 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.8, 5.1</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L30" s="8">
         <f>K30+E30</f>
@@ -8518,19 +8518,19 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>4.6, 4.5</t>
+          <t>4.5, 4.6</t>
         </is>
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J31" s="8" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L31" s="8">
         <f>K31+E31</f>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>2.9, 2.1</t>
+          <t>3.5, 1.5</t>
         </is>
       </c>
       <c r="I32" s="18" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>2.1, 3.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I33" s="18" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>2.11, 6.14</t>
+          <t>2.11, 5.6</t>
         </is>
       </c>
       <c r="I34" s="18" t="inlineStr">
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="J34" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K34" s="8" t="n">
         <v>53</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>6.13, 6.8, 2.13, 5.7</t>
+          <t>3.2, 6.13</t>
         </is>
       </c>
       <c r="I35" s="18" t="inlineStr">
@@ -8912,19 +8912,19 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>3.9, 5.2</t>
+          <t>2.10, 3.9</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L36" s="8">
         <f>K36+E36</f>
@@ -8990,19 +8990,19 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.9, 2.1</t>
         </is>
       </c>
       <c r="I37" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J37" s="8" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L37" s="8">
         <f>K37+E37</f>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>4.9, 4.8</t>
+          <t>6.6, 5.9</t>
         </is>
       </c>
       <c r="I38" s="18" t="inlineStr">
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="J38" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K38" s="8" t="n">
         <v>68</v>
@@ -9146,19 +9146,19 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.7, 6.6</t>
         </is>
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J39" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L39" s="8">
         <f>K39+E39</f>
@@ -9224,19 +9224,19 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>6.7, 4.7</t>
+          <t>6.9, 5.7</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J40" s="8" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="L40" s="8">
         <f>K40+E40</f>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="O40" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P40" s="8" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>6.9, 6.4</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I41" s="18" t="inlineStr">
@@ -9311,10 +9311,10 @@
         </is>
       </c>
       <c r="J41" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L41" s="8">
         <f>K41+E41</f>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>4.5, 2.12</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I42" s="18" t="inlineStr">
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L42" s="8">
         <f>K42+E42</f>
@@ -9458,19 +9458,19 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>6.1, 6.12</t>
+          <t>6.15, 6.12</t>
         </is>
       </c>
       <c r="I43" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J43" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L43" s="8">
         <f>K43+E43</f>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr">
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="J44" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L44" s="8">
         <f>K44+E44</f>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I45" s="18" t="inlineStr">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="J45" s="8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L45" s="8">
         <f>K45+E45</f>
@@ -9700,19 +9700,19 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I46" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J46" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L46" s="8">
         <f>K46+E46</f>
@@ -9778,19 +9778,19 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>4.4, 3.2</t>
+          <t>4.9, 2.13</t>
         </is>
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J47" s="8" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L47" s="8">
         <f>K47+E47</f>
@@ -9851,24 +9851,24 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (sin par en el plan)</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L48" s="8">
         <f>K48+E48</f>
@@ -9934,19 +9934,19 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J49" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L49" s="8">
         <f>K49+E49</f>
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="J50" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L50" s="8">
         <f>K50+E50</f>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>6.2, 5.3</t>
+          <t>6.2, 5.4</t>
         </is>
       </c>
       <c r="I51" s="18" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>5.10, 6.15</t>
+          <t>6.14, 5.10</t>
         </is>
       </c>
       <c r="I53" s="18" t="inlineStr">
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="J53" s="8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L53" s="8">
         <f>K53+E53</f>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I54" s="18" t="inlineStr">
@@ -10336,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="L54" s="8">
         <f>K54+E54</f>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="J55" s="8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L55" s="8">
         <f>K55+E55</f>
@@ -10480,7 +10480,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>4.8, 4.7</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr">
@@ -10489,10 +10489,10 @@
         </is>
       </c>
       <c r="J56" s="8" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L56" s="8">
         <f>K56+E56</f>
@@ -10558,19 +10558,19 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="I57" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J57" s="8" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L57" s="8">
         <f>K57+E57</f>
@@ -10636,19 +10636,19 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="I58" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J58" s="8" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="L58" s="8">
         <f>K58+E58</f>
@@ -10714,19 +10714,19 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I59" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J59" s="8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L59" s="8">
         <f>K59+E59</f>
@@ -10792,19 +10792,19 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I60" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J60" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L60" s="8">
         <f>K60+E60</f>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="I61" s="18" t="inlineStr">
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="J61" s="8" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L61" s="8">
         <f>K61+E61</f>
@@ -10953,14 +10953,14 @@
       </c>
       <c r="I62" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J62" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L62" s="8">
         <f>K62+E62</f>
@@ -11035,10 +11035,10 @@
         </is>
       </c>
       <c r="J63" s="8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L63" s="8">
         <f>K63+E63</f>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I64" s="18" t="inlineStr">
@@ -11113,10 +11113,10 @@
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L64" s="8">
         <f>K64+E64</f>
@@ -11182,7 +11182,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I65" s="18" t="inlineStr">
@@ -11194,7 +11194,7 @@
         <v>58</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L65" s="8">
         <f>K65+E65</f>
@@ -34656,22 +34656,22 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C9" s="35">
-        <f>Plan!C14</f>
+        <f>Plan!C24</f>
         <v/>
       </c>
       <c r="D9" s="8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E9" s="16">
-        <f>Plan!J14</f>
+        <f>Plan!J24</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>Plan!K14</f>
+        <f>Plan!K24</f>
         <v/>
       </c>
       <c r="G9" s="8">
@@ -34679,11 +34679,11 @@
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>Plan!I14</f>
+        <f>Plan!I24</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>Plan!O14</f>
+        <f>Plan!O24</f>
         <v/>
       </c>
     </row>
@@ -34730,22 +34730,22 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C11" s="35">
-        <f>Plan!C13</f>
+        <f>Plan!C15</f>
         <v/>
       </c>
       <c r="D11" s="8" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E11" s="16">
-        <f>Plan!J13</f>
+        <f>Plan!J15</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>Plan!K13</f>
+        <f>Plan!K15</f>
         <v/>
       </c>
       <c r="G11" s="8">
@@ -34753,11 +34753,11 @@
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>Plan!I13</f>
+        <f>Plan!I15</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>Plan!O13</f>
+        <f>Plan!O15</f>
         <v/>
       </c>
     </row>
@@ -34767,22 +34767,22 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C12" s="35">
-        <f>Plan!C15</f>
+        <f>Plan!C13</f>
         <v/>
       </c>
       <c r="D12" s="8" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E12" s="16">
-        <f>Plan!J15</f>
+        <f>Plan!J13</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>Plan!K15</f>
+        <f>Plan!K13</f>
         <v/>
       </c>
       <c r="G12" s="8">
@@ -34790,11 +34790,11 @@
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>Plan!I15</f>
+        <f>Plan!I13</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>Plan!O15</f>
+        <f>Plan!O13</f>
         <v/>
       </c>
     </row>
@@ -34804,22 +34804,22 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C13" s="35">
-        <f>Plan!C24</f>
+        <f>Plan!C27</f>
         <v/>
       </c>
       <c r="D13" s="8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E13" s="16">
-        <f>Plan!J24</f>
+        <f>Plan!J27</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>Plan!K24</f>
+        <f>Plan!K27</f>
         <v/>
       </c>
       <c r="G13" s="8">
@@ -34827,11 +34827,11 @@
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>Plan!I24</f>
+        <f>Plan!I27</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>Plan!O24</f>
+        <f>Plan!O27</f>
         <v/>
       </c>
     </row>
@@ -34878,22 +34878,22 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C15" s="35">
-        <f>Plan!C27</f>
+        <f>Plan!C14</f>
         <v/>
       </c>
       <c r="D15" s="8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E15" s="16">
-        <f>Plan!J27</f>
+        <f>Plan!J14</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>Plan!K27</f>
+        <f>Plan!K14</f>
         <v/>
       </c>
       <c r="G15" s="8">
@@ -34901,11 +34901,11 @@
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>Plan!I27</f>
+        <f>Plan!I14</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>Plan!O27</f>
+        <f>Plan!O14</f>
         <v/>
       </c>
     </row>
@@ -34952,22 +34952,22 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="C17" s="35">
-        <f>Plan!C19</f>
+        <f>Plan!C60</f>
         <v/>
       </c>
       <c r="D17" s="8" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E17" s="16">
-        <f>Plan!J19</f>
+        <f>Plan!J60</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>Plan!K19</f>
+        <f>Plan!K60</f>
         <v/>
       </c>
       <c r="G17" s="8">
@@ -34975,11 +34975,11 @@
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>Plan!I19</f>
+        <f>Plan!I60</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>Plan!O19</f>
+        <f>Plan!O60</f>
         <v/>
       </c>
     </row>
@@ -35026,22 +35026,22 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="C19" s="35">
-        <f>Plan!C11</f>
+        <f>Plan!C28</f>
         <v/>
       </c>
       <c r="D19" s="8" t="n">
         <v>16</v>
       </c>
       <c r="E19" s="16">
-        <f>Plan!J11</f>
+        <f>Plan!J28</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>Plan!K11</f>
+        <f>Plan!K28</f>
         <v/>
       </c>
       <c r="G19" s="8">
@@ -35049,11 +35049,11 @@
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>Plan!I11</f>
+        <f>Plan!I28</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>Plan!O11</f>
+        <f>Plan!O28</f>
         <v/>
       </c>
     </row>
@@ -35063,22 +35063,22 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C20" s="35">
-        <f>Plan!C33</f>
+        <f>Plan!C9</f>
         <v/>
       </c>
       <c r="D20" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" s="16">
-        <f>Plan!J33</f>
+        <f>Plan!J9</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>Plan!K33</f>
+        <f>Plan!K9</f>
         <v/>
       </c>
       <c r="G20" s="8">
@@ -35086,11 +35086,11 @@
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>Plan!I33</f>
+        <f>Plan!I9</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>Plan!O33</f>
+        <f>Plan!O9</f>
         <v/>
       </c>
     </row>
@@ -35100,22 +35100,22 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C21" s="35">
-        <f>Plan!C28</f>
+        <f>Plan!C33</f>
         <v/>
       </c>
       <c r="D21" s="8" t="n">
         <v>16</v>
       </c>
       <c r="E21" s="16">
-        <f>Plan!J28</f>
+        <f>Plan!J33</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>Plan!K28</f>
+        <f>Plan!K33</f>
         <v/>
       </c>
       <c r="G21" s="8">
@@ -35123,11 +35123,11 @@
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>Plan!I28</f>
+        <f>Plan!I33</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>Plan!O28</f>
+        <f>Plan!O33</f>
         <v/>
       </c>
     </row>
@@ -35137,22 +35137,22 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="C22" s="35">
-        <f>Plan!C20</f>
+        <f>Plan!C19</f>
         <v/>
       </c>
       <c r="D22" s="8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E22" s="16">
-        <f>Plan!J20</f>
+        <f>Plan!J19</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>Plan!K20</f>
+        <f>Plan!K19</f>
         <v/>
       </c>
       <c r="G22" s="8">
@@ -35160,11 +35160,11 @@
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>Plan!I20</f>
+        <f>Plan!I19</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>Plan!O20</f>
+        <f>Plan!O19</f>
         <v/>
       </c>
     </row>
@@ -35174,22 +35174,22 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="C23" s="35">
-        <f>Plan!C60</f>
+        <f>Plan!C29</f>
         <v/>
       </c>
       <c r="D23" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E23" s="16">
-        <f>Plan!J60</f>
+        <f>Plan!J29</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>Plan!K60</f>
+        <f>Plan!K29</f>
         <v/>
       </c>
       <c r="G23" s="8">
@@ -35197,11 +35197,11 @@
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>Plan!I60</f>
+        <f>Plan!I29</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>Plan!O60</f>
+        <f>Plan!O29</f>
         <v/>
       </c>
     </row>
@@ -35211,22 +35211,22 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="C24" s="35">
-        <f>Plan!C26</f>
+        <f>Plan!C54</f>
         <v/>
       </c>
       <c r="D24" s="8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E24" s="16">
-        <f>Plan!J26</f>
+        <f>Plan!J54</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>Plan!K26</f>
+        <f>Plan!K54</f>
         <v/>
       </c>
       <c r="G24" s="8">
@@ -35234,11 +35234,11 @@
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>Plan!I26</f>
+        <f>Plan!I54</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>Plan!O26</f>
+        <f>Plan!O54</f>
         <v/>
       </c>
     </row>
@@ -35248,22 +35248,22 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C25" s="35">
-        <f>Plan!C29</f>
+        <f>Plan!C36</f>
         <v/>
       </c>
       <c r="D25" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="16">
-        <f>Plan!J29</f>
+        <f>Plan!J36</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>Plan!K29</f>
+        <f>Plan!K36</f>
         <v/>
       </c>
       <c r="G25" s="8">
@@ -35271,11 +35271,11 @@
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>Plan!I29</f>
+        <f>Plan!I36</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>Plan!O29</f>
+        <f>Plan!O36</f>
         <v/>
       </c>
     </row>
@@ -35285,22 +35285,22 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C26" s="35">
-        <f>Plan!C18</f>
+        <f>Plan!C20</f>
         <v/>
       </c>
       <c r="D26" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26" s="16">
-        <f>Plan!J18</f>
+        <f>Plan!J20</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>Plan!K18</f>
+        <f>Plan!K20</f>
         <v/>
       </c>
       <c r="G26" s="8">
@@ -35308,11 +35308,11 @@
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>Plan!I18</f>
+        <f>Plan!I20</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>Plan!O18</f>
+        <f>Plan!O20</f>
         <v/>
       </c>
     </row>
@@ -35322,22 +35322,22 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C27" s="35">
-        <f>Plan!C9</f>
+        <f>Plan!C31</f>
         <v/>
       </c>
       <c r="D27" s="8" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E27" s="16">
-        <f>Plan!J9</f>
+        <f>Plan!J31</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>Plan!K9</f>
+        <f>Plan!K31</f>
         <v/>
       </c>
       <c r="G27" s="8">
@@ -35345,11 +35345,11 @@
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>Plan!I9</f>
+        <f>Plan!I31</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>Plan!O9</f>
+        <f>Plan!O31</f>
         <v/>
       </c>
     </row>
@@ -35359,22 +35359,22 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C28" s="35">
-        <f>Plan!C30</f>
+        <f>Plan!C37</f>
         <v/>
       </c>
       <c r="D28" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" s="16">
-        <f>Plan!J30</f>
+        <f>Plan!J37</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>Plan!K30</f>
+        <f>Plan!K37</f>
         <v/>
       </c>
       <c r="G28" s="8">
@@ -35382,11 +35382,11 @@
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>Plan!I30</f>
+        <f>Plan!I37</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>Plan!O30</f>
+        <f>Plan!O37</f>
         <v/>
       </c>
     </row>
@@ -35396,22 +35396,22 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C29" s="35">
-        <f>Plan!C45</f>
+        <f>Plan!C11</f>
         <v/>
       </c>
       <c r="D29" s="8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E29" s="16">
-        <f>Plan!J45</f>
+        <f>Plan!J11</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>Plan!K45</f>
+        <f>Plan!K11</f>
         <v/>
       </c>
       <c r="G29" s="8">
@@ -35419,11 +35419,11 @@
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>Plan!I45</f>
+        <f>Plan!I11</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>Plan!O45</f>
+        <f>Plan!O11</f>
         <v/>
       </c>
     </row>
@@ -35433,22 +35433,22 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="C30" s="35">
-        <f>Plan!C61</f>
+        <f>Plan!C58</f>
         <v/>
       </c>
       <c r="D30" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" s="16">
-        <f>Plan!J61</f>
+        <f>Plan!J58</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>Plan!K61</f>
+        <f>Plan!K58</f>
         <v/>
       </c>
       <c r="G30" s="8">
@@ -35456,11 +35456,11 @@
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>Plan!I61</f>
+        <f>Plan!I58</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>Plan!O61</f>
+        <f>Plan!O58</f>
         <v/>
       </c>
     </row>
@@ -35470,22 +35470,22 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="C31" s="35">
-        <f>Plan!C31</f>
+        <f>Plan!C61</f>
         <v/>
       </c>
       <c r="D31" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E31" s="16">
-        <f>Plan!J31</f>
+        <f>Plan!J61</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>Plan!K31</f>
+        <f>Plan!K61</f>
         <v/>
       </c>
       <c r="G31" s="8">
@@ -35493,11 +35493,11 @@
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>Plan!I31</f>
+        <f>Plan!I61</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>Plan!O31</f>
+        <f>Plan!O61</f>
         <v/>
       </c>
     </row>
@@ -35507,22 +35507,22 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C32" s="35">
-        <f>Plan!C37</f>
+        <f>Plan!C26</f>
         <v/>
       </c>
       <c r="D32" s="8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E32" s="16">
-        <f>Plan!J37</f>
+        <f>Plan!J26</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>Plan!K37</f>
+        <f>Plan!K26</f>
         <v/>
       </c>
       <c r="G32" s="8">
@@ -35530,11 +35530,11 @@
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>Plan!I37</f>
+        <f>Plan!I26</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>Plan!O37</f>
+        <f>Plan!O26</f>
         <v/>
       </c>
     </row>
@@ -35544,22 +35544,22 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C33" s="35">
-        <f>Plan!C36</f>
+        <f>Plan!C42</f>
         <v/>
       </c>
       <c r="D33" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E33" s="16">
-        <f>Plan!J36</f>
+        <f>Plan!J42</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>Plan!K36</f>
+        <f>Plan!K42</f>
         <v/>
       </c>
       <c r="G33" s="8">
@@ -35567,11 +35567,11 @@
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>Plan!I36</f>
+        <f>Plan!I42</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>Plan!O36</f>
+        <f>Plan!O42</f>
         <v/>
       </c>
     </row>
@@ -35581,22 +35581,22 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="C34" s="35">
-        <f>Plan!C42</f>
+        <f>Plan!C30</f>
         <v/>
       </c>
       <c r="D34" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" s="16">
-        <f>Plan!J42</f>
+        <f>Plan!J30</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>Plan!K42</f>
+        <f>Plan!K30</f>
         <v/>
       </c>
       <c r="G34" s="8">
@@ -35604,11 +35604,11 @@
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>Plan!I42</f>
+        <f>Plan!I30</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>Plan!O42</f>
+        <f>Plan!O30</f>
         <v/>
       </c>
     </row>
@@ -35618,22 +35618,22 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C35" s="35">
-        <f>Plan!C22</f>
+        <f>Plan!C18</f>
         <v/>
       </c>
       <c r="D35" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E35" s="16">
-        <f>Plan!J22</f>
+        <f>Plan!J18</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>Plan!K22</f>
+        <f>Plan!K18</f>
         <v/>
       </c>
       <c r="G35" s="8">
@@ -35641,11 +35641,11 @@
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>Plan!I22</f>
+        <f>Plan!I18</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>Plan!O22</f>
+        <f>Plan!O18</f>
         <v/>
       </c>
     </row>
@@ -35655,22 +35655,22 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C36" s="35">
-        <f>Plan!C10</f>
+        <f>Plan!C41</f>
         <v/>
       </c>
       <c r="D36" s="8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E36" s="16">
-        <f>Plan!J10</f>
+        <f>Plan!J41</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>Plan!K10</f>
+        <f>Plan!K41</f>
         <v/>
       </c>
       <c r="G36" s="8">
@@ -35678,11 +35678,11 @@
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>Plan!I10</f>
+        <f>Plan!I41</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>Plan!O10</f>
+        <f>Plan!O41</f>
         <v/>
       </c>
     </row>
@@ -35692,22 +35692,22 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="C37" s="35">
-        <f>Plan!C59</f>
+        <f>Plan!C22</f>
         <v/>
       </c>
       <c r="D37" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E37" s="16">
-        <f>Plan!J59</f>
+        <f>Plan!J22</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>Plan!K59</f>
+        <f>Plan!K22</f>
         <v/>
       </c>
       <c r="G37" s="8">
@@ -35715,11 +35715,11 @@
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>Plan!I59</f>
+        <f>Plan!I22</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>Plan!O59</f>
+        <f>Plan!O22</f>
         <v/>
       </c>
     </row>
@@ -35729,22 +35729,22 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C38" s="35">
-        <f>Plan!C41</f>
+        <f>Plan!C45</f>
         <v/>
       </c>
       <c r="D38" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E38" s="16">
-        <f>Plan!J41</f>
+        <f>Plan!J45</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>Plan!K41</f>
+        <f>Plan!K45</f>
         <v/>
       </c>
       <c r="G38" s="8">
@@ -35752,11 +35752,11 @@
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>Plan!I41</f>
+        <f>Plan!I45</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>Plan!O41</f>
+        <f>Plan!O45</f>
         <v/>
       </c>
     </row>
@@ -35766,22 +35766,22 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C39" s="35">
-        <f>Plan!C54</f>
+        <f>Plan!C10</f>
         <v/>
       </c>
       <c r="D39" s="8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E39" s="16">
-        <f>Plan!J54</f>
+        <f>Plan!J10</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>Plan!K54</f>
+        <f>Plan!K10</f>
         <v/>
       </c>
       <c r="G39" s="8">
@@ -35789,11 +35789,11 @@
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>Plan!I54</f>
+        <f>Plan!I10</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>Plan!O54</f>
+        <f>Plan!O10</f>
         <v/>
       </c>
     </row>
@@ -35840,22 +35840,22 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C41" s="35">
-        <f>Plan!C63</f>
+        <f>Plan!C25</f>
         <v/>
       </c>
       <c r="D41" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E41" s="16">
-        <f>Plan!J63</f>
+        <f>Plan!J25</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>Plan!K63</f>
+        <f>Plan!K25</f>
         <v/>
       </c>
       <c r="G41" s="8">
@@ -35863,11 +35863,11 @@
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>Plan!I63</f>
+        <f>Plan!I25</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>Plan!O63</f>
+        <f>Plan!O25</f>
         <v/>
       </c>
     </row>
@@ -35877,22 +35877,22 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="C42" s="35">
-        <f>Plan!C58</f>
+        <f>Plan!C63</f>
         <v/>
       </c>
       <c r="D42" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E42" s="16">
-        <f>Plan!J58</f>
+        <f>Plan!J63</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>Plan!K58</f>
+        <f>Plan!K63</f>
         <v/>
       </c>
       <c r="G42" s="8">
@@ -35900,11 +35900,11 @@
         <v/>
       </c>
       <c r="H42" s="16">
-        <f>Plan!I58</f>
+        <f>Plan!I63</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>Plan!O58</f>
+        <f>Plan!O63</f>
         <v/>
       </c>
     </row>
@@ -35914,22 +35914,22 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C43" s="35">
-        <f>Plan!C23</f>
+        <f>Plan!C59</f>
         <v/>
       </c>
       <c r="D43" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E43" s="16">
-        <f>Plan!J23</f>
+        <f>Plan!J59</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>Plan!K23</f>
+        <f>Plan!K59</f>
         <v/>
       </c>
       <c r="G43" s="8">
@@ -35937,11 +35937,11 @@
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>Plan!I23</f>
+        <f>Plan!I59</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>Plan!O23</f>
+        <f>Plan!O59</f>
         <v/>
       </c>
     </row>
@@ -35951,22 +35951,22 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C44" s="35">
-        <f>Plan!C47</f>
+        <f>Plan!C40</f>
         <v/>
       </c>
       <c r="D44" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" s="16">
-        <f>Plan!J47</f>
+        <f>Plan!J40</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>Plan!K47</f>
+        <f>Plan!K40</f>
         <v/>
       </c>
       <c r="G44" s="8">
@@ -35974,11 +35974,11 @@
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>Plan!I47</f>
+        <f>Plan!I40</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>Plan!O47</f>
+        <f>Plan!O40</f>
         <v/>
       </c>
     </row>
@@ -35988,22 +35988,22 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="C45" s="35">
-        <f>Plan!C25</f>
+        <f>Plan!C47</f>
         <v/>
       </c>
       <c r="D45" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E45" s="16">
-        <f>Plan!J25</f>
+        <f>Plan!J47</f>
         <v/>
       </c>
       <c r="F45" s="16">
-        <f>Plan!K25</f>
+        <f>Plan!K47</f>
         <v/>
       </c>
       <c r="G45" s="8">
@@ -36011,11 +36011,11 @@
         <v/>
       </c>
       <c r="H45" s="16">
-        <f>Plan!I25</f>
+        <f>Plan!I47</f>
         <v/>
       </c>
       <c r="I45" s="16">
-        <f>Plan!O25</f>
+        <f>Plan!O47</f>
         <v/>
       </c>
     </row>
@@ -36025,22 +36025,22 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C46" s="35">
-        <f>Plan!C48</f>
+        <f>Plan!C23</f>
         <v/>
       </c>
       <c r="D46" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E46" s="16">
-        <f>Plan!J48</f>
+        <f>Plan!J23</f>
         <v/>
       </c>
       <c r="F46" s="16">
-        <f>Plan!K48</f>
+        <f>Plan!K23</f>
         <v/>
       </c>
       <c r="G46" s="8">
@@ -36048,11 +36048,11 @@
         <v/>
       </c>
       <c r="H46" s="16">
-        <f>Plan!I48</f>
+        <f>Plan!I23</f>
         <v/>
       </c>
       <c r="I46" s="16">
-        <f>Plan!O48</f>
+        <f>Plan!O23</f>
         <v/>
       </c>
     </row>
@@ -36062,22 +36062,22 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="C47" s="35">
-        <f>Plan!C44</f>
+        <f>Plan!C48</f>
         <v/>
       </c>
       <c r="D47" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E47" s="16">
-        <f>Plan!J44</f>
+        <f>Plan!J48</f>
         <v/>
       </c>
       <c r="F47" s="16">
-        <f>Plan!K44</f>
+        <f>Plan!K48</f>
         <v/>
       </c>
       <c r="G47" s="8">
@@ -36085,11 +36085,11 @@
         <v/>
       </c>
       <c r="H47" s="16">
-        <f>Plan!I44</f>
+        <f>Plan!I48</f>
         <v/>
       </c>
       <c r="I47" s="16">
-        <f>Plan!O44</f>
+        <f>Plan!O48</f>
         <v/>
       </c>
     </row>
@@ -36099,22 +36099,22 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C48" s="35">
-        <f>Plan!C46</f>
+        <f>Plan!C34</f>
         <v/>
       </c>
       <c r="D48" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E48" s="16">
-        <f>Plan!J46</f>
+        <f>Plan!J34</f>
         <v/>
       </c>
       <c r="F48" s="16">
-        <f>Plan!K46</f>
+        <f>Plan!K34</f>
         <v/>
       </c>
       <c r="G48" s="8">
@@ -36122,11 +36122,11 @@
         <v/>
       </c>
       <c r="H48" s="16">
-        <f>Plan!I46</f>
+        <f>Plan!I34</f>
         <v/>
       </c>
       <c r="I48" s="16">
-        <f>Plan!O46</f>
+        <f>Plan!O34</f>
         <v/>
       </c>
     </row>
@@ -36136,22 +36136,22 @@
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="C49" s="35">
-        <f>Plan!C34</f>
+        <f>Plan!C21</f>
         <v/>
       </c>
       <c r="D49" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E49" s="16">
-        <f>Plan!J34</f>
+        <f>Plan!J21</f>
         <v/>
       </c>
       <c r="F49" s="16">
-        <f>Plan!K34</f>
+        <f>Plan!K21</f>
         <v/>
       </c>
       <c r="G49" s="8">
@@ -36159,11 +36159,11 @@
         <v/>
       </c>
       <c r="H49" s="16">
-        <f>Plan!I34</f>
+        <f>Plan!I21</f>
         <v/>
       </c>
       <c r="I49" s="16">
-        <f>Plan!O34</f>
+        <f>Plan!O21</f>
         <v/>
       </c>
     </row>
@@ -36173,22 +36173,22 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="C50" s="35">
-        <f>Plan!C21</f>
+        <f>Plan!C46</f>
         <v/>
       </c>
       <c r="D50" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E50" s="16">
-        <f>Plan!J21</f>
+        <f>Plan!J46</f>
         <v/>
       </c>
       <c r="F50" s="16">
-        <f>Plan!K21</f>
+        <f>Plan!K46</f>
         <v/>
       </c>
       <c r="G50" s="8">
@@ -36196,11 +36196,11 @@
         <v/>
       </c>
       <c r="H50" s="16">
-        <f>Plan!I21</f>
+        <f>Plan!I46</f>
         <v/>
       </c>
       <c r="I50" s="16">
-        <f>Plan!O21</f>
+        <f>Plan!O46</f>
         <v/>
       </c>
     </row>
@@ -36210,22 +36210,22 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C51" s="35">
-        <f>Plan!C64</f>
+        <f>Plan!C51</f>
         <v/>
       </c>
       <c r="D51" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E51" s="16">
-        <f>Plan!J64</f>
+        <f>Plan!J51</f>
         <v/>
       </c>
       <c r="F51" s="16">
-        <f>Plan!K64</f>
+        <f>Plan!K51</f>
         <v/>
       </c>
       <c r="G51" s="8">
@@ -36233,11 +36233,11 @@
         <v/>
       </c>
       <c r="H51" s="16">
-        <f>Plan!I64</f>
+        <f>Plan!I51</f>
         <v/>
       </c>
       <c r="I51" s="16">
-        <f>Plan!O64</f>
+        <f>Plan!O51</f>
         <v/>
       </c>
     </row>
@@ -36247,22 +36247,22 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="C52" s="35">
-        <f>Plan!C51</f>
+        <f>Plan!C52</f>
         <v/>
       </c>
       <c r="D52" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E52" s="16">
-        <f>Plan!J51</f>
+        <f>Plan!J52</f>
         <v/>
       </c>
       <c r="F52" s="16">
-        <f>Plan!K51</f>
+        <f>Plan!K52</f>
         <v/>
       </c>
       <c r="G52" s="8">
@@ -36270,11 +36270,11 @@
         <v/>
       </c>
       <c r="H52" s="16">
-        <f>Plan!I51</f>
+        <f>Plan!I52</f>
         <v/>
       </c>
       <c r="I52" s="16">
-        <f>Plan!O51</f>
+        <f>Plan!O52</f>
         <v/>
       </c>
     </row>
@@ -36284,22 +36284,22 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="C53" s="35">
-        <f>Plan!C52</f>
+        <f>Plan!C44</f>
         <v/>
       </c>
       <c r="D53" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E53" s="16">
-        <f>Plan!J52</f>
+        <f>Plan!J44</f>
         <v/>
       </c>
       <c r="F53" s="16">
-        <f>Plan!K52</f>
+        <f>Plan!K44</f>
         <v/>
       </c>
       <c r="G53" s="8">
@@ -36307,11 +36307,11 @@
         <v/>
       </c>
       <c r="H53" s="16">
-        <f>Plan!I52</f>
+        <f>Plan!I44</f>
         <v/>
       </c>
       <c r="I53" s="16">
-        <f>Plan!O52</f>
+        <f>Plan!O44</f>
         <v/>
       </c>
     </row>
@@ -36358,22 +36358,22 @@
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="C55" s="35">
-        <f>Plan!C62</f>
+        <f>Plan!C65</f>
         <v/>
       </c>
       <c r="D55" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E55" s="16">
-        <f>Plan!J62</f>
+        <f>Plan!J65</f>
         <v/>
       </c>
       <c r="F55" s="16">
-        <f>Plan!K62</f>
+        <f>Plan!K65</f>
         <v/>
       </c>
       <c r="G55" s="8">
@@ -36381,11 +36381,11 @@
         <v/>
       </c>
       <c r="H55" s="16">
-        <f>Plan!I62</f>
+        <f>Plan!I65</f>
         <v/>
       </c>
       <c r="I55" s="16">
-        <f>Plan!O62</f>
+        <f>Plan!O65</f>
         <v/>
       </c>
     </row>
@@ -36395,22 +36395,22 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="C56" s="35">
-        <f>Plan!C53</f>
+        <f>Plan!C62</f>
         <v/>
       </c>
       <c r="D56" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E56" s="16">
-        <f>Plan!J53</f>
+        <f>Plan!J62</f>
         <v/>
       </c>
       <c r="F56" s="16">
-        <f>Plan!K53</f>
+        <f>Plan!K62</f>
         <v/>
       </c>
       <c r="G56" s="8">
@@ -36418,11 +36418,11 @@
         <v/>
       </c>
       <c r="H56" s="16">
-        <f>Plan!I53</f>
+        <f>Plan!I62</f>
         <v/>
       </c>
       <c r="I56" s="16">
-        <f>Plan!O53</f>
+        <f>Plan!O62</f>
         <v/>
       </c>
     </row>
@@ -36432,22 +36432,22 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="C57" s="35">
-        <f>Plan!C50</f>
+        <f>Plan!C53</f>
         <v/>
       </c>
       <c r="D57" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E57" s="16">
-        <f>Plan!J50</f>
+        <f>Plan!J53</f>
         <v/>
       </c>
       <c r="F57" s="16">
-        <f>Plan!K50</f>
+        <f>Plan!K53</f>
         <v/>
       </c>
       <c r="G57" s="8">
@@ -36455,11 +36455,11 @@
         <v/>
       </c>
       <c r="H57" s="16">
-        <f>Plan!I50</f>
+        <f>Plan!I53</f>
         <v/>
       </c>
       <c r="I57" s="16">
-        <f>Plan!O50</f>
+        <f>Plan!O53</f>
         <v/>
       </c>
     </row>
@@ -36469,22 +36469,22 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="C58" s="35">
-        <f>Plan!C65</f>
+        <f>Plan!C64</f>
         <v/>
       </c>
       <c r="D58" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E58" s="16">
-        <f>Plan!J65</f>
+        <f>Plan!J64</f>
         <v/>
       </c>
       <c r="F58" s="16">
-        <f>Plan!K65</f>
+        <f>Plan!K64</f>
         <v/>
       </c>
       <c r="G58" s="8">
@@ -36492,11 +36492,11 @@
         <v/>
       </c>
       <c r="H58" s="16">
-        <f>Plan!I65</f>
+        <f>Plan!I64</f>
         <v/>
       </c>
       <c r="I58" s="16">
-        <f>Plan!O65</f>
+        <f>Plan!O64</f>
         <v/>
       </c>
     </row>
@@ -36506,22 +36506,22 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="C59" s="35">
-        <f>Plan!C55</f>
+        <f>Plan!C50</f>
         <v/>
       </c>
       <c r="D59" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E59" s="16">
-        <f>Plan!J55</f>
+        <f>Plan!J50</f>
         <v/>
       </c>
       <c r="F59" s="16">
-        <f>Plan!K55</f>
+        <f>Plan!K50</f>
         <v/>
       </c>
       <c r="G59" s="8">
@@ -36529,11 +36529,11 @@
         <v/>
       </c>
       <c r="H59" s="16">
-        <f>Plan!I55</f>
+        <f>Plan!I50</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>Plan!O55</f>
+        <f>Plan!O50</f>
         <v/>
       </c>
     </row>
@@ -36543,22 +36543,22 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="C60" s="35">
-        <f>Plan!C49</f>
+        <f>Plan!C55</f>
         <v/>
       </c>
       <c r="D60" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E60" s="16">
-        <f>Plan!J49</f>
+        <f>Plan!J55</f>
         <v/>
       </c>
       <c r="F60" s="16">
-        <f>Plan!K49</f>
+        <f>Plan!K55</f>
         <v/>
       </c>
       <c r="G60" s="8">
@@ -36566,11 +36566,11 @@
         <v/>
       </c>
       <c r="H60" s="16">
-        <f>Plan!I49</f>
+        <f>Plan!I55</f>
         <v/>
       </c>
       <c r="I60" s="16">
-        <f>Plan!O49</f>
+        <f>Plan!O55</f>
         <v/>
       </c>
     </row>
@@ -36580,22 +36580,22 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C61" s="35">
-        <f>Plan!C56</f>
+        <f>Plan!C39</f>
         <v/>
       </c>
       <c r="D61" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E61" s="16">
-        <f>Plan!J56</f>
+        <f>Plan!J39</f>
         <v/>
       </c>
       <c r="F61" s="16">
-        <f>Plan!K56</f>
+        <f>Plan!K39</f>
         <v/>
       </c>
       <c r="G61" s="8">
@@ -36603,11 +36603,11 @@
         <v/>
       </c>
       <c r="H61" s="16">
-        <f>Plan!I56</f>
+        <f>Plan!I39</f>
         <v/>
       </c>
       <c r="I61" s="16">
-        <f>Plan!O56</f>
+        <f>Plan!O39</f>
         <v/>
       </c>
     </row>
@@ -36617,22 +36617,22 @@
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="C62" s="35">
-        <f>Plan!C40</f>
+        <f>Plan!C57</f>
         <v/>
       </c>
       <c r="D62" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="16">
-        <f>Plan!J40</f>
+        <f>Plan!J57</f>
         <v/>
       </c>
       <c r="F62" s="16">
-        <f>Plan!K40</f>
+        <f>Plan!K57</f>
         <v/>
       </c>
       <c r="G62" s="8">
@@ -36640,11 +36640,11 @@
         <v/>
       </c>
       <c r="H62" s="16">
-        <f>Plan!I40</f>
+        <f>Plan!I57</f>
         <v/>
       </c>
       <c r="I62" s="16">
-        <f>Plan!O40</f>
+        <f>Plan!O57</f>
         <v/>
       </c>
     </row>
@@ -36654,22 +36654,22 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="C63" s="35">
-        <f>Plan!C57</f>
+        <f>Plan!C56</f>
         <v/>
       </c>
       <c r="D63" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" s="16">
-        <f>Plan!J57</f>
+        <f>Plan!J56</f>
         <v/>
       </c>
       <c r="F63" s="16">
-        <f>Plan!K57</f>
+        <f>Plan!K56</f>
         <v/>
       </c>
       <c r="G63" s="8">
@@ -36677,11 +36677,11 @@
         <v/>
       </c>
       <c r="H63" s="16">
-        <f>Plan!I57</f>
+        <f>Plan!I56</f>
         <v/>
       </c>
       <c r="I63" s="16">
-        <f>Plan!O57</f>
+        <f>Plan!O56</f>
         <v/>
       </c>
     </row>
@@ -36728,22 +36728,22 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="C65" s="35">
-        <f>Plan!C39</f>
+        <f>Plan!C49</f>
         <v/>
       </c>
       <c r="D65" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="16">
-        <f>Plan!J39</f>
+        <f>Plan!J49</f>
         <v/>
       </c>
       <c r="F65" s="16">
-        <f>Plan!K39</f>
+        <f>Plan!K49</f>
         <v/>
       </c>
       <c r="G65" s="8">
@@ -36751,11 +36751,11 @@
         <v/>
       </c>
       <c r="H65" s="16">
-        <f>Plan!I39</f>
+        <f>Plan!I49</f>
         <v/>
       </c>
       <c r="I65" s="16">
-        <f>Plan!O39</f>
+        <f>Plan!O49</f>
         <v/>
       </c>
     </row>
@@ -37453,7 +37453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37512,22 +37512,22 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>sesión principal (coordinador)</t>
+          <t>sesión principal (despliegue PR #2)</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
+          <t>4.9; P-83, P-84, P-85, P-89</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
+          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
+          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
         </is>
       </c>
     </row>
@@ -37537,24 +37537,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>sesión principal</t>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-13</t>
+          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Texto de vigilancia de Supersolidaria confirmado</t>
+          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
+          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
         </is>
       </c>
     </row>
@@ -37566,22 +37566,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>6.3; nuevos P-84, P-86, P-87</t>
+          <t>5.3; P-13</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>QA de producción: con observaciones</t>
+          <t>Texto de vigilancia de Supersolidaria confirmado</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
+          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
         </is>
       </c>
     </row>
@@ -37593,22 +37593,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2.12; nuevo P-85</t>
+          <t>6.3; nuevos P-84, P-86, P-87</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
+          <t>QA de producción: con observaciones</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
+          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
         </is>
       </c>
     </row>
@@ -37620,22 +37620,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>6.2; nuevos P-83, P-88</t>
+          <t>2.12; nuevo P-85</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
+          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
+          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
         </is>
       </c>
     </row>
@@ -37645,24 +37645,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
+          <t>6.2; nuevos P-83, P-88</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
+          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
+          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
         </is>
       </c>
     </row>
@@ -37679,24 +37679,24 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>6.9, 6.13; P-44, P-59, P-61</t>
+          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
+          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
+          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -37706,17 +37706,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
+          <t>6.9, 6.13; P-44, P-59, P-61</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
+          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
+          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
         </is>
       </c>
     </row>
@@ -37728,22 +37728,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Sebas (acuerdo con Carlos Pardo)</t>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
+          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
+          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
+          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
         </is>
       </c>
     </row>
@@ -37753,24 +37753,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (acuerdo con Carlos Pardo)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>6.1, P-58</t>
+          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
+          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
+          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
         </is>
       </c>
     </row>
@@ -37780,24 +37780,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Sebas (coordinación con la cooperativa)</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
+          <t>6.1, P-58</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
+          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
+          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
         </is>
       </c>
     </row>
@@ -37807,24 +37807,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (coordinación con la cooperativa)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
+          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
+          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
+          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
         </is>
       </c>
     </row>
@@ -37836,22 +37836,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
+          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
+          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
         </is>
       </c>
     </row>
@@ -37863,22 +37863,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
+          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
+          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
         </is>
       </c>
     </row>
@@ -37890,22 +37890,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Sorteo mensual en /cuenta</t>
+          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
+          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
         </is>
       </c>
     </row>
@@ -37922,17 +37922,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>4.6; P-57</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
+          <t>Sorteo mensual en /cuenta</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
+          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
         </is>
       </c>
     </row>
@@ -37944,49 +37944,49 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>1.5; P-63</t>
+          <t>4.6; P-57</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
+          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
+          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>1.5; P-63</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
+          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
+          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
         </is>
       </c>
     </row>
@@ -37998,22 +37998,22 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive + ga-verificador-qa</t>
+          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>6.3; P-39</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
+          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
+          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
         </is>
       </c>
     </row>
@@ -38023,24 +38023,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive</t>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>ga-verificador-responsive + ga-verificador-qa</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 5.8; P-39, P-53</t>
+          <t>6.3; P-39</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
+          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
+          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
         </is>
       </c>
     </row>
@@ -38052,22 +38052,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
+          <t>6.3, 5.2, 5.8; P-39, P-53</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
+          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
+          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
         </is>
       </c>
     </row>
@@ -38079,22 +38079,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>5.2, 5.8, 6.3</t>
+          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
+          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
+          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
         </is>
       </c>
     </row>
@@ -38106,22 +38106,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
+          <t>5.2, 5.8, 6.3</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
+          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
+          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
         </is>
       </c>
     </row>
@@ -38133,22 +38133,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>2.1, 5.3, 5.7; P-16, P-52</t>
+          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
+          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
+          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
         </is>
       </c>
     </row>
@@ -38160,22 +38160,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
+          <t>2.1, 5.3, 5.7; P-16, P-52</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
+          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
+          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
         </is>
       </c>
     </row>
@@ -38185,24 +38185,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
+          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
+          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
+          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
         </is>
       </c>
     </row>
@@ -38212,24 +38212,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Sebas</t>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Agente ga-auditor-supabase corregido</t>
+          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
         </is>
       </c>
     </row>
@@ -38239,24 +38239,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>3.1, 6.5, 6.10; P-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+          <t>Agente ga-auditor-supabase corregido</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
         </is>
       </c>
     </row>
@@ -38266,24 +38266,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1, 6.5, 6.10; P-09</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
         </is>
       </c>
     </row>
@@ -38293,24 +38293,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-funcionalidad-botones</t>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
         </is>
       </c>
     </row>
@@ -38320,24 +38320,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-qa</t>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
         </is>
       </c>
     </row>
@@ -38349,22 +38349,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
         </is>
       </c>
     </row>
@@ -38376,20 +38376,47 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>Claude (sesión principal)</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Todas</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Creación del Excel de avances</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>Pendientes desde PENDIENTES.md, plan desde la propuesta (6 fases, 8 semanas) reorganizado en 2 filas con cola infinita y pesos 1–5.</t>
         </is>

--- a/docs/avances/Avances_Green_Alliance.xlsx
+++ b/docs/avances/Avances_Green_Alliance.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bitácora" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$4:$R$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B46,Pendientes!$G$5:$G$97,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B46,Pendientes!$G$5:$G$101,"Hecho")</f>
         <v/>
       </c>
       <c r="D46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B46,Pendientes!$G$5:$G$97,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B46,Pendientes!$G$5:$G$101,"En curso")</f>
         <v/>
       </c>
       <c r="E46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B46,Pendientes!$G$5:$G$97,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B46,Pendientes!$G$5:$G$101,"Pendiente")</f>
         <v/>
       </c>
       <c r="F46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B46,Pendientes!$G$5:$G$97,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B46,Pendientes!$G$5:$G$101,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G46" s="9">
@@ -1522,19 +1522,19 @@
         </is>
       </c>
       <c r="C47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B47,Pendientes!$G$5:$G$97,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B47,Pendientes!$G$5:$G$101,"Hecho")</f>
         <v/>
       </c>
       <c r="D47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B47,Pendientes!$G$5:$G$97,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B47,Pendientes!$G$5:$G$101,"En curso")</f>
         <v/>
       </c>
       <c r="E47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B47,Pendientes!$G$5:$G$97,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B47,Pendientes!$G$5:$G$101,"Pendiente")</f>
         <v/>
       </c>
       <c r="F47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B47,Pendientes!$G$5:$G$97,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B47,Pendientes!$G$5:$G$101,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G47" s="9">
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B48,Pendientes!$G$5:$G$97,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B48,Pendientes!$G$5:$G$101,"Hecho")</f>
         <v/>
       </c>
       <c r="D48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B48,Pendientes!$G$5:$G$97,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B48,Pendientes!$G$5:$G$101,"En curso")</f>
         <v/>
       </c>
       <c r="E48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B48,Pendientes!$G$5:$G$97,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B48,Pendientes!$G$5:$G$101,"Pendiente")</f>
         <v/>
       </c>
       <c r="F48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B48,Pendientes!$G$5:$G$97,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B48,Pendientes!$G$5:$G$101,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G48" s="9">
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B49,Pendientes!$G$5:$G$97,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B49,Pendientes!$G$5:$G$101,"Hecho")</f>
         <v/>
       </c>
       <c r="D49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B49,Pendientes!$G$5:$G$97,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B49,Pendientes!$G$5:$G$101,"En curso")</f>
         <v/>
       </c>
       <c r="E49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B49,Pendientes!$G$5:$G$97,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B49,Pendientes!$G$5:$G$101,"Pendiente")</f>
         <v/>
       </c>
       <c r="F49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B49,Pendientes!$G$5:$G$97,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B49,Pendientes!$G$5:$G$101,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G49" s="9">
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B50,Pendientes!$G$5:$G$97,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B50,Pendientes!$G$5:$G$101,"Hecho")</f>
         <v/>
       </c>
       <c r="D50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B50,Pendientes!$G$5:$G$97,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B50,Pendientes!$G$5:$G$101,"En curso")</f>
         <v/>
       </c>
       <c r="E50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B50,Pendientes!$G$5:$G$97,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B50,Pendientes!$G$5:$G$101,"Pendiente")</f>
         <v/>
       </c>
       <c r="F50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B50,Pendientes!$G$5:$G$97,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B50,Pendientes!$G$5:$G$101,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G50" s="9">
@@ -1630,19 +1630,19 @@
         </is>
       </c>
       <c r="C51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B51,Pendientes!$G$5:$G$97,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B51,Pendientes!$G$5:$G$101,"Hecho")</f>
         <v/>
       </c>
       <c r="D51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B51,Pendientes!$G$5:$G$97,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B51,Pendientes!$G$5:$G$101,"En curso")</f>
         <v/>
       </c>
       <c r="E51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B51,Pendientes!$G$5:$G$97,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B51,Pendientes!$G$5:$G$101,"Pendiente")</f>
         <v/>
       </c>
       <c r="F51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B51,Pendientes!$G$5:$G$97,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B51,Pendientes!$G$5:$G$101,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G51" s="9">
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c r="C52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B52,Pendientes!$G$5:$G$97,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B52,Pendientes!$G$5:$G$101,"Hecho")</f>
         <v/>
       </c>
       <c r="D52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B52,Pendientes!$G$5:$G$97,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B52,Pendientes!$G$5:$G$101,"En curso")</f>
         <v/>
       </c>
       <c r="E52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B52,Pendientes!$G$5:$G$97,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B52,Pendientes!$G$5:$G$101,"Pendiente")</f>
         <v/>
       </c>
       <c r="F52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B52,Pendientes!$G$5:$G$97,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B52,Pendientes!$G$5:$G$101,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G52" s="9">
@@ -1684,19 +1684,19 @@
         </is>
       </c>
       <c r="C53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B53,Pendientes!$G$5:$G$97,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B53,Pendientes!$G$5:$G$101,"Hecho")</f>
         <v/>
       </c>
       <c r="D53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B53,Pendientes!$G$5:$G$97,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B53,Pendientes!$G$5:$G$101,"En curso")</f>
         <v/>
       </c>
       <c r="E53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B53,Pendientes!$G$5:$G$97,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B53,Pendientes!$G$5:$G$101,"Pendiente")</f>
         <v/>
       </c>
       <c r="F53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$97,$B53,Pendientes!$G$5:$G$97,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B53,Pendientes!$G$5:$G$101,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G53" s="9">
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5224,7 +5224,7 @@
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-94</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -5234,32 +5234,32 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Calidad</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Correr ga-verificador-qa y ga-verificador-responsive</t>
+          <t>Correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra la maquetación C+ de ingreso y afiliación, con Supabase local</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-verificador-qa o ga-escritor-tests</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I73" s="21">
@@ -5268,14 +5268,14 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>QA 1 hecha el 23-sep (186 pasan, 2 fallan; informe docs/verificaciones/2026-09-23-verificacion-1.md). Responsive hecha el 23-sep: 2 fallas de scroll corregidas (5.8) y segunda pasada con 0 fallas en 13 anchos (320–1920 px); tests/responsive 10/10. La QA final sigue en 6.3.</t>
+          <t>25-sep: reportado por ga-diseno-a-codigo tras maquetar 2.15 en C+; no se corrieron porque requieren Supabase local.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Calidad</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Commit de las pantallas nuevas</t>
+          <t>Correr ga-verificador-qa y ga-verificador-responsive</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I74" s="21">
@@ -5319,14 +5319,14 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>Commit d86db86 en develop.</t>
+          <t>QA 1 hecha el 23-sep (186 pasan, 2 fallan; informe docs/verificaciones/2026-09-23-verificacion-1.md). Responsive hecha el 23-sep: 2 fallas de scroll corregidas (5.8) y segunda pasada con 0 fallas en 13 anchos (320–1920 px); tests/responsive 10/10. La QA final sigue en 6.3.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>P-64</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -5341,12 +5341,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Abrir el PR de develop a main</t>
+          <t>Commit de las pantallas nuevas</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I75" s="21">
@@ -5370,14 +5370,14 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>25-sep: Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en producción.</t>
+          <t>Commit d86db86 en develop.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>P-82</t>
+          <t>P-64</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Despliegue</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Probar en producción con sesión real de los 3 administradores (ingreso con código OTP y logo del correo)</t>
+          <t>Abrir el PR de develop a main</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
@@ -5421,14 +5421,14 @@
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>25-sep: Sebas entró con su cédula y le apareció el panel de administrador (falta confirmar Ricardo y abogadosprieto). 25-sep: reportado por la sesión principal tras el despliegue de fase 2; falta esta prueba manual antes de cerrar 6.5.</t>
+          <t>25-sep: Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en producción.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
         <is>
-          <t>P-86</t>
+          <t>P-82</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>Despliegue</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>A-01: la ayuda del dominio de correo institucional no se actualiza en vivo al elegir Policía/Ejército</t>
+          <t>Probar en producción con sesión real de los 3 administradores (ingreso con código OTP y logo del correo)</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I77" s="21">
@@ -5472,14 +5472,14 @@
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>25-sep: Sebas confirmó el correo de cualquier dominio (P-85); la ayuda por institución ya no existe. 25-sep: hallazgo de ga-verificador-qa. Condicionado a P-85: si se despliega el cambio a «correo de cualquier dominio» queda superado (ya no habría ayuda de dominio que actualizar); si Sebas decide mantener el chequeo institucional, hay que corregir el texto en vivo. Pendiente de esa decisión.</t>
+          <t>25-sep: Sebas entró con su cédula y le apareció el panel de administrador (falta confirmar Ricardo y abogadosprieto). 25-sep: reportado por la sesión principal tras el despliegue de fase 2; falta esta prueba manual antes de cerrar 6.5.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-86</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -5489,22 +5489,22 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Borrar /login y /dashboard cuando /ingresar y /cuenta funcionen</t>
+          <t>A-01: la ayuda del dominio de correo institucional no se actualiza en vivo al elegir Policía/Ejército</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I78" s="21">
@@ -5523,14 +5523,14 @@
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>Borradas el 23-sep (incluida /dashboard/solicitar, su parte del proxy y los colores heredados de tailwind.config.ts).</t>
+          <t>25-sep: Sebas confirmó el correo de cualquier dominio (P-85); la ayuda por institución ya no existe. 25-sep: hallazgo de ga-verificador-qa. Condicionado a P-85: si se despliega el cambio a «correo de cualquier dominio» queda superado (ya no habría ayuda de dominio que actualizar); si Sebas decide mantener el chequeo institucional, hay que corregir el texto en vivo. Pendiente de esa decisión.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -5540,17 +5540,17 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Revisar si conviene confiar en x-forwarded-for para el límite de intentos por IP</t>
+          <t>Borrar /login y /dashboard cuando /ingresar y /cuenta funcionen</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I79" s="21">
@@ -5574,14 +5574,14 @@
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-verificador-qa el 23-sep. Documentado por ga-funcionalidad-botones como O-01 en lib/servidor/limite.ts: x-forwarded-for/x-real-ip solo son confiables detrás de Vercel (nuestro caso); el límite real por cédula/IP lo hace la app, no Supabase.</t>
+          <t>Borradas el 23-sep (incluida /dashboard/solicitar, su parte del proxy y los colores heredados de tailwind.config.ts).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="19" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Correos</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Confirmar que salen los correos de afiliación (el log queda en la terminal de next dev)</t>
+          <t>Revisar si conviene confiar en x-forwarded-for para el límite de intentos por IP</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I80" s="21">
@@ -5625,14 +5625,14 @@
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>Ya no aplica: el 23-sep se quitaron los correos de afiliación del código (decisión de Sebas).</t>
+          <t>Sugerido por ga-verificador-qa el 23-sep. Documentado por ga-funcionalidad-botones como O-01 en lib/servidor/limite.ts: x-forwarded-for/x-real-ip solo son confiables detrás de Vercel (nuestro caso); el límite real por cédula/IP lo hace la app, no Supabase.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="19" t="inlineStr">
         <is>
-          <t>P-62</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -5642,17 +5642,17 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Borrar la cuenta admin de prueba «Test QA» (cédula 1099887766) desde el panel de Supabase</t>
+          <t>Confirmar que salen los correos de afiliación (el log queda en la terminal de next dev)</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I81" s="21">
@@ -5676,14 +5676,14 @@
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>Ya hay 3 administradores reales en producción: Ricardo, Abogados Prieto y Sebas. 24-sep: usuario «Test QA» borrado de producción por Sebas.</t>
+          <t>Ya no aplica: el 23-sep se quitaron los correos de afiliación del código (decisión de Sebas).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-62</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5693,22 +5693,22 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Mapa de botones: §4 «Nueva solicitud» → /cuenta/solicitar y sección para la ruta /cuenta/solicitar</t>
+          <t>Borrar la cuenta admin de prueba «Test QA» (cédula 1099887766) desde el panel de Supabase</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I82" s="21">
@@ -5727,49 +5727,49 @@
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>Reportado por ga-diseno-a-codigo. Verificado el 23-sep: docs/mapa-de-botones.md ya tiene §4 «Nueva solicitud» → /cuenta/solicitar (Definido) y §4b /cuenta/solicitar; /dashboard se eliminó.</t>
+          <t>Ya hay 3 administradores reales en producción: Ricardo, Abogados Prieto y Sebas. 24-sep: usuario «Test QA» borrado de producción por Sebas.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>P-63</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Fase 2</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Preguntas abiertas de fase 2 para la cooperativa: grados del Ejército, dominios de correo institucionales (hoy solo policia.gov.co, buzonejercito.mil.co, ejercito.mil.co), tiempo que se guardan las fotos y tope de intentos del sorteo</t>
+          <t>Mapa de botones: §4 «Nueva solicitud» → /cuenta/solicitar y sección para la ruta /cuenta/solicitar</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I83" s="21">
@@ -5778,14 +5778,14 @@
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Ver docs/spec-fase-2.md §Preguntas abiertas.</t>
+          <t>Reportado por ga-diseno-a-codigo. Verificado el 23-sep: docs/mapa-de-botones.md ya tiene §4 «Nueva solicitud» → /cuenta/solicitar (Definido) y §4b /cuenta/solicitar; /dashboard se eliminó.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="19" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-63</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Fase 2</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
+          <t>Preguntas abiertas de fase 2 para la cooperativa: grados del Ejército, dominios de correo institucionales (hoy solo policia.gov.co, buzonejercito.mil.co, ejercito.mil.co), tiempo que se guardan las fotos y tope de intentos del sorteo</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I84" s="21">
@@ -5829,14 +5829,14 @@
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>Por ahora son una sección en /cuenta (#convenios).</t>
+          <t>Ver docs/spec-fase-2.md §Preguntas abiertas.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-95</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5846,22 +5846,22 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>A 320 px la línea «COOPERATIVA» del logo mide ~5 px de alto (opcional: ocultarla o achicar «Ingresar» bajo 360 px)</t>
+          <t>Botón «Escribir por WhatsApp» en el detalle de afiliación del admin</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I85" s="21">
@@ -5880,14 +5880,14 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>Menor y opcional, reportado por ga-verificador-responsive el 23-sep.</t>
+          <t>25-sep: propuesto por el diseño (pieza 3e del lienzo, detalle de afiliación); es funcionalidad nueva, no existía antes. El resto de las piezas 3d–3h usa componentes/rutas que ya existen.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="19" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-96</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5897,32 +5897,32 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
+          <t>Asignar/desactivar el asesor de un asociado (proceso sin definir)</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Sebas (ga-auditor-supabase revisa antes)</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I86" s="21">
@@ -5931,14 +5931,14 @@
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
+          <t>25-sep: ga-disenador-lienzo no puede diseñar esta pantalla porque no hay backend ni proceso definido para asignar o desactivar el asesor de un asociado.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="19" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-97</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5948,17 +5948,17 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
+          <t>Motivo de rechazo visible en el detalle de afiliación (requiere migración)</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I87" s="21">
@@ -5982,14 +5982,14 @@
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>Apartado «Mis datos» ya maquetado.</t>
+          <t>25-sep: identificado en el detalle de afiliación del lienzo (pieza 3e). Relacionado con P-69/5.10 (Carlos Pardo ya tiene encargada la columna motivo_rechazo y el borrado automático de fotos); se deja anotado aparte para que la cooperativa confirme el texto/proceso del motivo que verá el admin.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>P-65</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Sorteo</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Decidir si un admin o un asesor pueden participar en el sorteo mensual</t>
+          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -6014,17 +6014,17 @@
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I88" s="21">
@@ -6033,14 +6033,14 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-revisor-seguridad el 24-sep. 24-sep: decidido que solo participan asociados (S-13, ya implementado en participarSorteo).</t>
+          <t>Por ahora son una sección en /cuenta (#convenios).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="19" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Color de error #B3261E</t>
+          <t>A 320 px la línea «COOPERATIVA» del logo mide ~5 px de alto (opcional: ocultarla o achicar «Ingresar» bajo 360 px)</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -6084,14 +6084,14 @@
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>Se deja.</t>
+          <t>Menor y opcional, reportado por ga-verificador-responsive el 23-sep.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="19" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -6101,22 +6101,22 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Estado vacío de «Tu solicitud»</t>
+          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Sebas (ga-auditor-supabase revisa antes)</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="I90" s="21">
@@ -6135,14 +6135,14 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>Ver con /cuenta?vacio=1.</t>
+          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="19" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Logo en celular como enlace a la landing</t>
+          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -6177,19 +6177,23 @@
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I91" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H91,Plan!$A$5:$A$75,0)),"—")</f>
         <v/>
       </c>
-      <c r="J91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>Apartado «Mis datos» ya maquetado.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="19" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-65</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -6199,22 +6203,22 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Sorteo</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Escudo: public/logos/vector/green-alliance-logo.svg</t>
+          <t>Decidir si un admin o un asesor pueden participar en el sorteo mensual</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
@@ -6224,19 +6228,23 @@
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I92" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H92,Plan!$A$5:$A$75,0)),"—")</f>
         <v/>
       </c>
-      <c r="J92" s="7" t="inlineStr"/>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>Sugerido por ga-revisor-seguridad el 24-sep. 24-sep: decidido que solo participan asociados (S-13, ya implementado en participarSorteo).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -6246,12 +6254,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Formulario de ingreso entre 640 y 767 px (columna de 440 px)</t>
+          <t>Color de error #B3261E</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -6271,19 +6279,23 @@
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I93" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H93,Plan!$A$5:$A$75,0)),"—")</f>
         <v/>
       </c>
-      <c r="J93" s="7" t="inlineStr"/>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>Se deja.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="19" t="inlineStr">
         <is>
-          <t>P-07</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -6293,12 +6305,12 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Panel verde en tableta (640–1023 px) centrado</t>
+          <t>Estado vacío de «Tu solicitud»</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -6318,39 +6330,43 @@
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I94" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H94,Plan!$A$5:$A$75,0)),"—")</f>
         <v/>
       </c>
-      <c r="J94" s="7" t="inlineStr"/>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>Ver con /cuenta?vacio=1.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="19" t="inlineStr">
         <is>
-          <t>P-88</t>
+          <t>P-04</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Decisión</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>F2-08: tr_componer_nombre_afiliacion no cubre el update directo de solicitudes_afiliacion.nombre por un admin</t>
+          <t>Logo en celular como enlace a la landing</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -6360,53 +6376,49 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I95" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H95,Plan!$A$5:$A$75,0)),"—")</f>
         <v/>
       </c>
-      <c r="J95" s="7" t="inlineStr">
-        <is>
-          <t>Documentado en docs/auditorias/2026-09-24-fase-2.md; confirmado sin corregir por ga-revisor-seguridad el 25-sep. Un admin puede reescribir `nombre` por SQL directo, y ese texto lo usan el correo «Ingreso aceptado» y el nombre_completo del perfil. Solo afecta a admins.</t>
-        </is>
-      </c>
+      <c r="J95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="19" t="inlineStr">
         <is>
-          <t>P-83</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Decisión</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Correos</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>S-15: escapar/validar HTML en las variables NOMBRE/MOTIVO de los correos de Resend</t>
+          <t>Escudo: public/logos/vector/green-alliance-logo.svg</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -6416,48 +6428,44 @@
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I96" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H96,Plan!$A$5:$A$75,0)),"—")</f>
         <v/>
       </c>
-      <c r="J96" s="7" t="inlineStr">
-        <is>
-          <t>25-sep: hallazgo de ga-revisor-seguridad (un admin puede meter HTML en perfiles.nombre_completo o en el motivo de rechazo). Corregido en local con pruebas (tests/unit/correo-resend.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02).</t>
-        </is>
-      </c>
+      <c r="J96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="19" t="inlineStr">
         <is>
-          <t>P-84</t>
+          <t>P-06</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Decisión</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>/ingresar</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>M-01: el número de WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts</t>
+          <t>Formulario de ingreso entre 640 y 767 px (columna de 440 px)</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -6467,22 +6475,218 @@
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="I97" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H97,Plan!$A$5:$A$75,0)),"—")</f>
         <v/>
       </c>
-      <c r="J97" s="7" t="inlineStr">
+      <c r="J97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="19" t="inlineStr">
+        <is>
+          <t>P-07</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>/ingresar</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Panel verde en tableta (640–1023 px) centrado</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Yo</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="I98" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H98,Plan!$A$5:$A$75,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>P-88</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>F2-08: tr_componer_nombre_afiliacion no cubre el update directo de solicitudes_afiliacion.nombre por un admin</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="I99" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H99,Plan!$A$5:$A$75,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>Documentado en docs/auditorias/2026-09-24-fase-2.md; confirmado sin corregir por ga-revisor-seguridad el 25-sep. Un admin puede reescribir `nombre` por SQL directo, y ese texto lo usan el correo «Ingreso aceptado» y el nombre_completo del perfil. Solo afecta a admins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="19" t="inlineStr">
+        <is>
+          <t>P-83</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Correos</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>S-15: escapar/validar HTML en las variables NOMBRE/MOTIVO de los correos de Resend</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="I100" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H100,Plan!$A$5:$A$75,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>25-sep: hallazgo de ga-revisor-seguridad (un admin puede meter HTML en perfiles.nombre_completo o en el motivo de rechazo). Corregido en local con pruebas (tests/unit/correo-resend.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>P-84</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>M-01: el número de WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="I101" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H101,Plan!$A$5:$A$75,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
         <is>
           <t>25-sep: hallazgo de ga-verificador-qa (patrón sin la barra invertida de \D/\d; el enlace wa.me sí funciona). Corregido en local con pruebas (tests/unit/config-whatsapp.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02); confirmado en vivo «311 724 1942».</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J97"/>
-  <conditionalFormatting sqref="G5:G97">
+  <autoFilter ref="A4:J101"/>
+  <conditionalFormatting sqref="G5:G101">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$G5="Hecho"</formula>
     </cfRule>
@@ -6496,7 +6700,7 @@
       <formula>$G5="Bloqueado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F97">
+  <conditionalFormatting sqref="F5:F101">
     <cfRule type="expression" priority="5" dxfId="5">
       <formula>$F5="Alta"</formula>
     </cfRule>
@@ -6507,16 +6711,16 @@
       <formula>$F5="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:F97">
+  <conditionalFormatting sqref="A5:F101">
     <cfRule type="expression" priority="8" dxfId="8">
       <formula>$G5="Hecho"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Hecho,En curso,Pendiente,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6928,7 +7132,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -7006,7 +7210,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>4.5, 2.10, 4.2</t>
+          <t>4.5, 2.10, 6.8</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -7084,19 +7288,19 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.12, 5.2</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J10" s="8" t="n">
         <v>28</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="L10" s="8">
         <f>K10+E10</f>
@@ -7162,7 +7366,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>2.12, 5.5</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
@@ -7174,7 +7378,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L11" s="8">
         <f>K11+E11</f>
@@ -7240,7 +7444,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>5.9, 4.7</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="I12" s="18" t="inlineStr">
@@ -7249,10 +7453,10 @@
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L12" s="8">
         <f>K12+E12</f>
@@ -7318,7 +7522,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>4.2, 6.11</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
@@ -7396,7 +7600,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -7474,7 +7678,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I15" s="18" t="inlineStr">
@@ -7486,7 +7690,7 @@
         <v>6</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L15" s="8">
         <f>K15+E15</f>
@@ -7552,7 +7756,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.6, 2.7</t>
         </is>
       </c>
       <c r="I16" s="18" t="inlineStr">
@@ -7564,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L16" s="8">
         <f>K16+E16</f>
@@ -7630,7 +7834,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.3, 3.4</t>
         </is>
       </c>
       <c r="I17" s="18" t="inlineStr">
@@ -7708,7 +7912,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>3.1, 3.4</t>
+          <t>3.4, 2.4</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr">
@@ -7786,7 +7990,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>3.4, 6.10</t>
+          <t>2.4, 6.10</t>
         </is>
       </c>
       <c r="I19" s="18" t="inlineStr">
@@ -7864,7 +8068,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I20" s="18" t="inlineStr">
@@ -7951,7 +8155,7 @@
         </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>19</v>
@@ -8103,14 +8307,14 @@
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J23" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L23" s="8">
         <f>K23+E23</f>
@@ -8176,7 +8380,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>3.7, 1.7</t>
+          <t>4.6, 1.7, 1.6</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -8254,7 +8458,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I25" s="18" t="inlineStr">
@@ -8266,7 +8470,7 @@
         <v>38</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L25" s="8">
         <f>K25+E25</f>
@@ -8332,19 +8536,19 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.7, 5.5, 2.8</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L26" s="8">
         <f>K26+E26</f>
@@ -8410,7 +8614,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.3, 3.7</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
@@ -8419,10 +8623,10 @@
         </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L27" s="8">
         <f>K27+E27</f>
@@ -8438,7 +8642,7 @@
       </c>
       <c r="O27" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P27" s="8" t="inlineStr">
@@ -8488,7 +8692,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>2.5, 2.6</t>
+          <t>1.4, 2.2</t>
         </is>
       </c>
       <c r="I28" s="18" t="inlineStr">
@@ -8500,7 +8704,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L28" s="8">
         <f>K28+E28</f>
@@ -8566,7 +8770,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>4.4, 5.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr">
@@ -8575,10 +8779,10 @@
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L29" s="8">
         <f>K29+E29</f>
@@ -8644,19 +8848,19 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.2, 2.15</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L30" s="8">
         <f>K30+E30</f>
@@ -8722,7 +8926,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>2.6, 2.7</t>
+          <t>2.5, 2.6</t>
         </is>
       </c>
       <c r="I31" s="18" t="inlineStr">
@@ -8734,7 +8938,7 @@
         <v>6</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L31" s="8">
         <f>K31+E31</f>
@@ -8956,7 +9160,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.15, 2.14</t>
         </is>
       </c>
       <c r="I34" s="18" t="inlineStr">
@@ -8965,10 +9169,10 @@
         </is>
       </c>
       <c r="J34" s="8" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L34" s="8">
         <f>K34+E34</f>
@@ -9034,19 +9238,19 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.1, 4.2</t>
         </is>
       </c>
       <c r="I35" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J35" s="8" t="n">
         <v>28</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L35" s="8">
         <f>K35+E35</f>
@@ -9112,7 +9316,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>6.3, 4.10</t>
+          <t>6.1, 6.3</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr">
@@ -9121,10 +9325,10 @@
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L36" s="8">
         <f>K36+E36</f>
@@ -9268,19 +9472,19 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>1.5, 2.1</t>
+          <t>3.9, 4.6</t>
         </is>
       </c>
       <c r="I38" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J38" s="8" t="n">
         <v>20</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L38" s="8">
         <f>K38+E38</f>
@@ -9346,19 +9550,19 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>5.4, 2.11</t>
+          <t>2.11, 6.14</t>
         </is>
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J39" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L39" s="8">
         <f>K39+E39</f>
@@ -9424,7 +9628,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>5.1, 2.13, 3.2</t>
+          <t>6.9, 3.2</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">
@@ -9436,7 +9640,7 @@
         <v>4</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L40" s="8">
         <f>K40+E40</f>
@@ -9584,7 +9788,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.2, 2.12</t>
         </is>
       </c>
       <c r="I42" s="18" t="inlineStr">
@@ -9596,7 +9800,7 @@
         <v>28</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L42" s="8">
         <f>K42+E42</f>
@@ -9662,19 +9866,19 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>1.8, 6.18, 4.8</t>
+          <t>4.8, 5.9</t>
         </is>
       </c>
       <c r="I43" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J43" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L43" s="8">
         <f>K43+E43</f>
@@ -9740,19 +9944,19 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.18, 4.7</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J44" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L44" s="8">
         <f>K44+E44</f>
@@ -9818,19 +10022,19 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.8, 2.13</t>
         </is>
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J45" s="8" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="L45" s="8">
         <f>K45+E45</f>
@@ -9896,19 +10100,19 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.11, 6.6</t>
         </is>
       </c>
       <c r="I46" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J46" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="L46" s="8">
         <f>K46+E46</f>
@@ -9974,19 +10178,19 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>6.16, 6.15</t>
+          <t>5.10, 4.10</t>
         </is>
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J47" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L47" s="8">
         <f>K47+E47</f>
@@ -10052,7 +10256,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr">
@@ -10061,10 +10265,10 @@
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L48" s="8">
         <f>K48+E48</f>
@@ -10130,19 +10334,19 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.6, 3.3</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J49" s="8" t="n">
         <v>31</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L49" s="8">
         <f>K49+E49</f>
@@ -10208,7 +10412,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>5.6, 6.12</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I50" s="18" t="inlineStr">
@@ -10217,10 +10421,10 @@
         </is>
       </c>
       <c r="J50" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L50" s="8">
         <f>K50+E50</f>
@@ -10290,19 +10494,19 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J51" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L51" s="8">
         <f>K51+E51</f>
@@ -10372,19 +10576,19 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I52" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J52" s="8" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L52" s="8">
         <f>K52+E52</f>
@@ -10450,19 +10654,19 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I53" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J53" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L53" s="8">
         <f>K53+E53</f>
@@ -10528,7 +10732,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I54" s="18" t="inlineStr">
@@ -10540,7 +10744,7 @@
         <v>31</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L54" s="8">
         <f>K54+E54</f>
@@ -10606,19 +10810,19 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J55" s="8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L55" s="8">
         <f>K55+E55</f>
@@ -10684,7 +10888,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>6.6, 1.8</t>
+          <t>4.7, 6.7</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr">
@@ -10693,10 +10897,10 @@
         </is>
       </c>
       <c r="J56" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L56" s="8">
         <f>K56+E56</f>
@@ -10762,7 +10966,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I57" s="18" t="inlineStr">
@@ -10771,7 +10975,7 @@
         </is>
       </c>
       <c r="J57" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K57" s="8" t="n">
         <v>71</v>
@@ -10840,7 +11044,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>5.3, 3.10</t>
         </is>
       </c>
       <c r="I58" s="18" t="inlineStr">
@@ -10849,10 +11053,10 @@
         </is>
       </c>
       <c r="J58" s="8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L58" s="8">
         <f>K58+E58</f>
@@ -10918,7 +11122,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.3, 6.12</t>
         </is>
       </c>
       <c r="I59" s="18" t="inlineStr">
@@ -10927,10 +11131,10 @@
         </is>
       </c>
       <c r="J59" s="8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L59" s="8">
         <f>K59+E59</f>
@@ -10996,7 +11200,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>6.2, 3.10</t>
+          <t>3.10, 6.2</t>
         </is>
       </c>
       <c r="I60" s="18" t="inlineStr">
@@ -11161,10 +11365,10 @@
         </is>
       </c>
       <c r="J62" s="8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="L62" s="8">
         <f>K62+E62</f>
@@ -11230,7 +11434,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>6.7, 5.9</t>
+          <t>4.10, 6.17</t>
         </is>
       </c>
       <c r="I63" s="18" t="inlineStr">
@@ -11239,10 +11443,10 @@
         </is>
       </c>
       <c r="J63" s="8" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L63" s="8">
         <f>K63+E63</f>
@@ -11308,19 +11512,19 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="I64" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="L64" s="8">
         <f>K64+E64</f>
@@ -11386,19 +11590,19 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I65" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J65" s="8" t="n">
         <v>23</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="L65" s="8">
         <f>K65+E65</f>
@@ -11464,19 +11668,19 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I66" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J66" s="8" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L66" s="8">
         <f>K66+E66</f>
@@ -11551,7 +11755,7 @@
         </is>
       </c>
       <c r="J67" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K67" s="8" t="n">
         <v>15</v>
@@ -11620,7 +11824,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I68" s="18" t="inlineStr">
@@ -11632,7 +11836,7 @@
         <v>23</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="L68" s="8">
         <f>K68+E68</f>
@@ -11698,7 +11902,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I69" s="18" t="inlineStr">
@@ -11707,10 +11911,10 @@
         </is>
       </c>
       <c r="J69" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L69" s="8">
         <f>K69+E69</f>
@@ -11776,19 +11980,19 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="I70" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J70" s="8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L70" s="8">
         <f>K70+E70</f>
@@ -11854,19 +12058,19 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I71" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J71" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L71" s="8">
         <f>K71+E71</f>
@@ -11932,7 +12136,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="I72" s="18" t="inlineStr">
@@ -11941,10 +12145,10 @@
         </is>
       </c>
       <c r="J72" s="8" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L72" s="8">
         <f>K72+E72</f>
@@ -12010,19 +12214,19 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J73" s="8" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L73" s="8">
         <f>K73+E73</f>
@@ -12088,19 +12292,19 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>5.10, 6.14</t>
+          <t>6.6, 6.15</t>
         </is>
       </c>
       <c r="I74" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J74" s="8" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L74" s="8">
         <f>K74+E74</f>
@@ -12166,7 +12370,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr">
@@ -12175,10 +12379,10 @@
         </is>
       </c>
       <c r="J75" s="8" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L75" s="8">
         <f>K75+E75</f>
@@ -42166,22 +42370,22 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C9" s="35">
-        <f>Plan!C16</f>
+        <f>Plan!C28</f>
         <v/>
       </c>
       <c r="D9" s="8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E9" s="16">
-        <f>Plan!J16</f>
+        <f>Plan!J28</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>Plan!K16</f>
+        <f>Plan!K28</f>
         <v/>
       </c>
       <c r="G9" s="8">
@@ -42189,11 +42393,11 @@
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>Plan!I16</f>
+        <f>Plan!I28</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>Plan!O16</f>
+        <f>Plan!O28</f>
         <v/>
       </c>
     </row>
@@ -42240,22 +42444,22 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C11" s="35">
-        <f>Plan!C15</f>
+        <f>Plan!C17</f>
         <v/>
       </c>
       <c r="D11" s="8" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E11" s="16">
-        <f>Plan!J15</f>
+        <f>Plan!J17</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>Plan!K15</f>
+        <f>Plan!K17</f>
         <v/>
       </c>
       <c r="G11" s="8">
@@ -42263,11 +42467,11 @@
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>Plan!I15</f>
+        <f>Plan!I17</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>Plan!O15</f>
+        <f>Plan!O17</f>
         <v/>
       </c>
     </row>
@@ -42277,22 +42481,22 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C12" s="35">
-        <f>Plan!C17</f>
+        <f>Plan!C15</f>
         <v/>
       </c>
       <c r="D12" s="8" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E12" s="16">
-        <f>Plan!J17</f>
+        <f>Plan!J15</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>Plan!K17</f>
+        <f>Plan!K15</f>
         <v/>
       </c>
       <c r="G12" s="8">
@@ -42300,11 +42504,11 @@
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>Plan!I17</f>
+        <f>Plan!I15</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>Plan!O17</f>
+        <f>Plan!O15</f>
         <v/>
       </c>
     </row>
@@ -42314,22 +42518,22 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C13" s="35">
-        <f>Plan!C28</f>
+        <f>Plan!C31</f>
         <v/>
       </c>
       <c r="D13" s="8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E13" s="16">
-        <f>Plan!J28</f>
+        <f>Plan!J31</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>Plan!K28</f>
+        <f>Plan!K31</f>
         <v/>
       </c>
       <c r="G13" s="8">
@@ -42337,11 +42541,11 @@
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>Plan!I28</f>
+        <f>Plan!I31</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>Plan!O28</f>
+        <f>Plan!O31</f>
         <v/>
       </c>
     </row>
@@ -42388,22 +42592,22 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C15" s="35">
-        <f>Plan!C31</f>
+        <f>Plan!C16</f>
         <v/>
       </c>
       <c r="D15" s="8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E15" s="16">
-        <f>Plan!J31</f>
+        <f>Plan!J16</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>Plan!K31</f>
+        <f>Plan!K16</f>
         <v/>
       </c>
       <c r="G15" s="8">
@@ -42411,11 +42615,11 @@
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>Plan!I31</f>
+        <f>Plan!I16</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>Plan!O31</f>
+        <f>Plan!O16</f>
         <v/>
       </c>
     </row>
@@ -42795,22 +42999,22 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="C26" s="35">
-        <f>Plan!C38</f>
+        <f>Plan!C65</f>
         <v/>
       </c>
       <c r="D26" s="8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E26" s="16">
-        <f>Plan!J38</f>
+        <f>Plan!J65</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>Plan!K38</f>
+        <f>Plan!K65</f>
         <v/>
       </c>
       <c r="G26" s="8">
@@ -42818,11 +43022,11 @@
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>Plan!I38</f>
+        <f>Plan!I65</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>Plan!O38</f>
+        <f>Plan!O65</f>
         <v/>
       </c>
     </row>
@@ -42869,22 +43073,22 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C28" s="35">
-        <f>Plan!C68</f>
+        <f>Plan!C35</f>
         <v/>
       </c>
       <c r="D28" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E28" s="16">
-        <f>Plan!J68</f>
+        <f>Plan!J35</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>Plan!K68</f>
+        <f>Plan!K35</f>
         <v/>
       </c>
       <c r="G28" s="8">
@@ -42892,11 +43096,11 @@
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>Plan!I68</f>
+        <f>Plan!I35</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>Plan!O68</f>
+        <f>Plan!O35</f>
         <v/>
       </c>
     </row>
@@ -42906,22 +43110,22 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C29" s="35">
-        <f>Plan!C30</f>
+        <f>Plan!C38</f>
         <v/>
       </c>
       <c r="D29" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E29" s="16">
-        <f>Plan!J30</f>
+        <f>Plan!J38</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>Plan!K30</f>
+        <f>Plan!K38</f>
         <v/>
       </c>
       <c r="G29" s="8">
@@ -42929,11 +43133,11 @@
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>Plan!I30</f>
+        <f>Plan!I38</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>Plan!O30</f>
+        <f>Plan!O38</f>
         <v/>
       </c>
     </row>
@@ -42943,22 +43147,22 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C30" s="35">
-        <f>Plan!C49</f>
+        <f>Plan!C42</f>
         <v/>
       </c>
       <c r="D30" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E30" s="16">
-        <f>Plan!J49</f>
+        <f>Plan!J42</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>Plan!K49</f>
+        <f>Plan!K42</f>
         <v/>
       </c>
       <c r="G30" s="8">
@@ -42966,11 +43170,11 @@
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>Plan!I49</f>
+        <f>Plan!I42</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>Plan!O49</f>
+        <f>Plan!O42</f>
         <v/>
       </c>
     </row>
@@ -43017,22 +43221,22 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C32" s="35">
-        <f>Plan!C34</f>
+        <f>Plan!C11</f>
         <v/>
       </c>
       <c r="D32" s="8" t="n">
         <v>12</v>
       </c>
       <c r="E32" s="16">
-        <f>Plan!J34</f>
+        <f>Plan!J11</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>Plan!K34</f>
+        <f>Plan!K11</f>
         <v/>
       </c>
       <c r="G32" s="8">
@@ -43040,11 +43244,11 @@
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>Plan!I34</f>
+        <f>Plan!I11</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>Plan!O34</f>
+        <f>Plan!O11</f>
         <v/>
       </c>
     </row>
@@ -43054,22 +43258,22 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C33" s="35">
-        <f>Plan!C11</f>
+        <f>Plan!C10</f>
         <v/>
       </c>
       <c r="D33" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33" s="16">
-        <f>Plan!J11</f>
+        <f>Plan!J10</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>Plan!K11</f>
+        <f>Plan!K10</f>
         <v/>
       </c>
       <c r="G33" s="8">
@@ -43077,11 +43281,11 @@
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>Plan!I11</f>
+        <f>Plan!I10</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>Plan!O11</f>
+        <f>Plan!O10</f>
         <v/>
       </c>
     </row>
@@ -43091,22 +43295,22 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C34" s="35">
-        <f>Plan!C52</f>
+        <f>Plan!C49</f>
         <v/>
       </c>
       <c r="D34" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E34" s="16">
-        <f>Plan!J52</f>
+        <f>Plan!J49</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>Plan!K52</f>
+        <f>Plan!K49</f>
         <v/>
       </c>
       <c r="G34" s="8">
@@ -43114,11 +43318,11 @@
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>Plan!I52</f>
+        <f>Plan!I49</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>Plan!O52</f>
+        <f>Plan!O49</f>
         <v/>
       </c>
     </row>
@@ -43128,22 +43332,22 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C35" s="35">
-        <f>Plan!C35</f>
+        <f>Plan!C30</f>
         <v/>
       </c>
       <c r="D35" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E35" s="16">
-        <f>Plan!J35</f>
+        <f>Plan!J30</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>Plan!K35</f>
+        <f>Plan!K30</f>
         <v/>
       </c>
       <c r="G35" s="8">
@@ -43151,11 +43355,11 @@
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>Plan!I35</f>
+        <f>Plan!I30</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>Plan!O35</f>
+        <f>Plan!O30</f>
         <v/>
       </c>
     </row>
@@ -43165,22 +43369,22 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C36" s="35">
-        <f>Plan!C26</f>
+        <f>Plan!C27</f>
         <v/>
       </c>
       <c r="D36" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="16">
-        <f>Plan!J26</f>
+        <f>Plan!J27</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>Plan!K26</f>
+        <f>Plan!K27</f>
         <v/>
       </c>
       <c r="G36" s="8">
@@ -43188,11 +43392,11 @@
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>Plan!I26</f>
+        <f>Plan!I27</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>Plan!O26</f>
+        <f>Plan!O27</f>
         <v/>
       </c>
     </row>
@@ -43202,22 +43406,22 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="C37" s="35">
-        <f>Plan!C10</f>
+        <f>Plan!C34</f>
         <v/>
       </c>
       <c r="D37" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E37" s="16">
-        <f>Plan!J10</f>
+        <f>Plan!J34</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>Plan!K10</f>
+        <f>Plan!K34</f>
         <v/>
       </c>
       <c r="G37" s="8">
@@ -43225,11 +43429,11 @@
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>Plan!I10</f>
+        <f>Plan!I34</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>Plan!O10</f>
+        <f>Plan!O34</f>
         <v/>
       </c>
     </row>
@@ -43239,22 +43443,22 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="C38" s="35">
-        <f>Plan!C42</f>
+        <f>Plan!C26</f>
         <v/>
       </c>
       <c r="D38" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E38" s="16">
-        <f>Plan!J42</f>
+        <f>Plan!J26</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>Plan!K42</f>
+        <f>Plan!K26</f>
         <v/>
       </c>
       <c r="G38" s="8">
@@ -43262,11 +43466,11 @@
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>Plan!I42</f>
+        <f>Plan!I26</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>Plan!O42</f>
+        <f>Plan!O26</f>
         <v/>
       </c>
     </row>
@@ -43276,22 +43480,22 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C39" s="35">
-        <f>Plan!C70</f>
+        <f>Plan!C52</f>
         <v/>
       </c>
       <c r="D39" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E39" s="16">
-        <f>Plan!J70</f>
+        <f>Plan!J52</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>Plan!K70</f>
+        <f>Plan!K52</f>
         <v/>
       </c>
       <c r="G39" s="8">
@@ -43299,11 +43503,11 @@
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>Plan!I70</f>
+        <f>Plan!I52</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>Plan!O70</f>
+        <f>Plan!O52</f>
         <v/>
       </c>
     </row>
@@ -43313,22 +43517,22 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C40" s="35">
-        <f>Plan!C65</f>
+        <f>Plan!C20</f>
         <v/>
       </c>
       <c r="D40" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E40" s="16">
-        <f>Plan!J65</f>
+        <f>Plan!J20</f>
         <v/>
       </c>
       <c r="F40" s="16">
-        <f>Plan!K65</f>
+        <f>Plan!K20</f>
         <v/>
       </c>
       <c r="G40" s="8">
@@ -43336,11 +43540,11 @@
         <v/>
       </c>
       <c r="H40" s="16">
-        <f>Plan!I65</f>
+        <f>Plan!I20</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>Plan!O65</f>
+        <f>Plan!O20</f>
         <v/>
       </c>
     </row>
@@ -43350,22 +43554,22 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="C41" s="35">
-        <f>Plan!C20</f>
+        <f>Plan!C68</f>
         <v/>
       </c>
       <c r="D41" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E41" s="16">
-        <f>Plan!J20</f>
+        <f>Plan!J68</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>Plan!K20</f>
+        <f>Plan!K68</f>
         <v/>
       </c>
       <c r="G41" s="8">
@@ -43373,11 +43577,11 @@
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>Plan!I20</f>
+        <f>Plan!I68</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>Plan!O20</f>
+        <f>Plan!O68</f>
         <v/>
       </c>
     </row>
@@ -43387,22 +43591,22 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="C42" s="35">
-        <f>Plan!C66</f>
+        <f>Plan!C70</f>
         <v/>
       </c>
       <c r="D42" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E42" s="16">
-        <f>Plan!J66</f>
+        <f>Plan!J70</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>Plan!K66</f>
+        <f>Plan!K70</f>
         <v/>
       </c>
       <c r="G42" s="8">
@@ -43410,11 +43614,11 @@
         <v/>
       </c>
       <c r="H42" s="16">
-        <f>Plan!I66</f>
+        <f>Plan!I70</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>Plan!O66</f>
+        <f>Plan!O70</f>
         <v/>
       </c>
     </row>
@@ -43424,22 +43628,22 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C43" s="35">
-        <f>Plan!C54</f>
+        <f>Plan!C40</f>
         <v/>
       </c>
       <c r="D43" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E43" s="16">
-        <f>Plan!J54</f>
+        <f>Plan!J40</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>Plan!K54</f>
+        <f>Plan!K40</f>
         <v/>
       </c>
       <c r="G43" s="8">
@@ -43447,11 +43651,11 @@
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>Plan!I54</f>
+        <f>Plan!I40</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>Plan!O54</f>
+        <f>Plan!O40</f>
         <v/>
       </c>
     </row>
@@ -43461,22 +43665,22 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C44" s="35">
-        <f>Plan!C45</f>
+        <f>Plan!C66</f>
         <v/>
       </c>
       <c r="D44" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E44" s="16">
-        <f>Plan!J45</f>
+        <f>Plan!J66</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>Plan!K45</f>
+        <f>Plan!K66</f>
         <v/>
       </c>
       <c r="G44" s="8">
@@ -43484,11 +43688,11 @@
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>Plan!I45</f>
+        <f>Plan!I66</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>Plan!O45</f>
+        <f>Plan!O66</f>
         <v/>
       </c>
     </row>
@@ -43498,22 +43702,22 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C45" s="35">
-        <f>Plan!C40</f>
+        <f>Plan!C29</f>
         <v/>
       </c>
       <c r="D45" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E45" s="16">
-        <f>Plan!J40</f>
+        <f>Plan!J29</f>
         <v/>
       </c>
       <c r="F45" s="16">
-        <f>Plan!K40</f>
+        <f>Plan!K29</f>
         <v/>
       </c>
       <c r="G45" s="8">
@@ -43521,11 +43725,11 @@
         <v/>
       </c>
       <c r="H45" s="16">
-        <f>Plan!I40</f>
+        <f>Plan!I29</f>
         <v/>
       </c>
       <c r="I45" s="16">
-        <f>Plan!O40</f>
+        <f>Plan!O29</f>
         <v/>
       </c>
     </row>
@@ -43572,22 +43776,22 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="C47" s="35">
-        <f>Plan!C25</f>
+        <f>Plan!C54</f>
         <v/>
       </c>
       <c r="D47" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" s="16">
-        <f>Plan!J25</f>
+        <f>Plan!J54</f>
         <v/>
       </c>
       <c r="F47" s="16">
-        <f>Plan!K25</f>
+        <f>Plan!K54</f>
         <v/>
       </c>
       <c r="G47" s="8">
@@ -43595,11 +43799,11 @@
         <v/>
       </c>
       <c r="H47" s="16">
-        <f>Plan!I25</f>
+        <f>Plan!I54</f>
         <v/>
       </c>
       <c r="I47" s="16">
-        <f>Plan!O25</f>
+        <f>Plan!O54</f>
         <v/>
       </c>
     </row>
@@ -43609,22 +43813,22 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C48" s="35">
-        <f>Plan!C29</f>
+        <f>Plan!C45</f>
         <v/>
       </c>
       <c r="D48" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" s="16">
-        <f>Plan!J29</f>
+        <f>Plan!J45</f>
         <v/>
       </c>
       <c r="F48" s="16">
-        <f>Plan!K29</f>
+        <f>Plan!K45</f>
         <v/>
       </c>
       <c r="G48" s="8">
@@ -43632,11 +43836,11 @@
         <v/>
       </c>
       <c r="H48" s="16">
-        <f>Plan!I29</f>
+        <f>Plan!I45</f>
         <v/>
       </c>
       <c r="I48" s="16">
-        <f>Plan!O29</f>
+        <f>Plan!O45</f>
         <v/>
       </c>
     </row>
@@ -43683,22 +43887,22 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C50" s="35">
-        <f>Plan!C39</f>
+        <f>Plan!C25</f>
         <v/>
       </c>
       <c r="D50" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E50" s="16">
-        <f>Plan!J39</f>
+        <f>Plan!J25</f>
         <v/>
       </c>
       <c r="F50" s="16">
-        <f>Plan!K39</f>
+        <f>Plan!K25</f>
         <v/>
       </c>
       <c r="G50" s="8">
@@ -43706,11 +43910,11 @@
         <v/>
       </c>
       <c r="H50" s="16">
-        <f>Plan!I39</f>
+        <f>Plan!I25</f>
         <v/>
       </c>
       <c r="I50" s="16">
-        <f>Plan!O39</f>
+        <f>Plan!O25</f>
         <v/>
       </c>
     </row>
@@ -43757,22 +43961,22 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="C52" s="35">
-        <f>Plan!C23</f>
+        <f>Plan!C53</f>
         <v/>
       </c>
       <c r="D52" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E52" s="16">
-        <f>Plan!J23</f>
+        <f>Plan!J53</f>
         <v/>
       </c>
       <c r="F52" s="16">
-        <f>Plan!K23</f>
+        <f>Plan!K53</f>
         <v/>
       </c>
       <c r="G52" s="8">
@@ -43780,11 +43984,11 @@
         <v/>
       </c>
       <c r="H52" s="16">
-        <f>Plan!I23</f>
+        <f>Plan!I53</f>
         <v/>
       </c>
       <c r="I52" s="16">
-        <f>Plan!O23</f>
+        <f>Plan!O53</f>
         <v/>
       </c>
     </row>
@@ -43794,22 +43998,22 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C53" s="35">
-        <f>Plan!C58</f>
+        <f>Plan!C39</f>
         <v/>
       </c>
       <c r="D53" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E53" s="16">
-        <f>Plan!J58</f>
+        <f>Plan!J39</f>
         <v/>
       </c>
       <c r="F53" s="16">
-        <f>Plan!K58</f>
+        <f>Plan!K39</f>
         <v/>
       </c>
       <c r="G53" s="8">
@@ -43817,11 +44021,11 @@
         <v/>
       </c>
       <c r="H53" s="16">
-        <f>Plan!I58</f>
+        <f>Plan!I39</f>
         <v/>
       </c>
       <c r="I53" s="16">
-        <f>Plan!O58</f>
+        <f>Plan!O39</f>
         <v/>
       </c>
     </row>
@@ -43831,22 +44035,22 @@
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="C54" s="35">
-        <f>Plan!C27</f>
+        <f>Plan!C23</f>
         <v/>
       </c>
       <c r="D54" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E54" s="16">
-        <f>Plan!J27</f>
+        <f>Plan!J23</f>
         <v/>
       </c>
       <c r="F54" s="16">
-        <f>Plan!K27</f>
+        <f>Plan!K23</f>
         <v/>
       </c>
       <c r="G54" s="8">
@@ -43854,11 +44058,11 @@
         <v/>
       </c>
       <c r="H54" s="16">
-        <f>Plan!I27</f>
+        <f>Plan!I23</f>
         <v/>
       </c>
       <c r="I54" s="16">
-        <f>Plan!O27</f>
+        <f>Plan!O23</f>
         <v/>
       </c>
     </row>
@@ -43868,22 +44072,22 @@
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="C55" s="35">
-        <f>Plan!C50</f>
+        <f>Plan!C71</f>
         <v/>
       </c>
       <c r="D55" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E55" s="16">
-        <f>Plan!J50</f>
+        <f>Plan!J71</f>
         <v/>
       </c>
       <c r="F55" s="16">
-        <f>Plan!K50</f>
+        <f>Plan!K71</f>
         <v/>
       </c>
       <c r="G55" s="8">
@@ -43891,11 +44095,11 @@
         <v/>
       </c>
       <c r="H55" s="16">
-        <f>Plan!I50</f>
+        <f>Plan!I71</f>
         <v/>
       </c>
       <c r="I55" s="16">
-        <f>Plan!O50</f>
+        <f>Plan!O71</f>
         <v/>
       </c>
     </row>
@@ -43905,22 +44109,22 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C56" s="35">
-        <f>Plan!C53</f>
+        <f>Plan!C58</f>
         <v/>
       </c>
       <c r="D56" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E56" s="16">
-        <f>Plan!J53</f>
+        <f>Plan!J58</f>
         <v/>
       </c>
       <c r="F56" s="16">
-        <f>Plan!K53</f>
+        <f>Plan!K58</f>
         <v/>
       </c>
       <c r="G56" s="8">
@@ -43928,11 +44132,11 @@
         <v/>
       </c>
       <c r="H56" s="16">
-        <f>Plan!I53</f>
+        <f>Plan!I58</f>
         <v/>
       </c>
       <c r="I56" s="16">
-        <f>Plan!O53</f>
+        <f>Plan!O58</f>
         <v/>
       </c>
     </row>
@@ -43942,22 +44146,22 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C57" s="35">
-        <f>Plan!C69</f>
+        <f>Plan!C50</f>
         <v/>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E57" s="16">
-        <f>Plan!J69</f>
+        <f>Plan!J50</f>
         <v/>
       </c>
       <c r="F57" s="16">
-        <f>Plan!K69</f>
+        <f>Plan!K50</f>
         <v/>
       </c>
       <c r="G57" s="8">
@@ -43965,11 +44169,11 @@
         <v/>
       </c>
       <c r="H57" s="16">
-        <f>Plan!I69</f>
+        <f>Plan!I50</f>
         <v/>
       </c>
       <c r="I57" s="16">
-        <f>Plan!O69</f>
+        <f>Plan!O50</f>
         <v/>
       </c>
     </row>
@@ -43979,22 +44183,22 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C58" s="35">
-        <f>Plan!C60</f>
+        <f>Plan!C36</f>
         <v/>
       </c>
       <c r="D58" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E58" s="16">
-        <f>Plan!J60</f>
+        <f>Plan!J36</f>
         <v/>
       </c>
       <c r="F58" s="16">
-        <f>Plan!K60</f>
+        <f>Plan!K36</f>
         <v/>
       </c>
       <c r="G58" s="8">
@@ -44002,11 +44206,11 @@
         <v/>
       </c>
       <c r="H58" s="16">
-        <f>Plan!I60</f>
+        <f>Plan!I36</f>
         <v/>
       </c>
       <c r="I58" s="16">
-        <f>Plan!O60</f>
+        <f>Plan!O36</f>
         <v/>
       </c>
     </row>
@@ -44016,22 +44220,22 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="C59" s="35">
-        <f>Plan!C59</f>
+        <f>Plan!C60</f>
         <v/>
       </c>
       <c r="D59" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E59" s="16">
-        <f>Plan!J59</f>
+        <f>Plan!J60</f>
         <v/>
       </c>
       <c r="F59" s="16">
-        <f>Plan!K59</f>
+        <f>Plan!K60</f>
         <v/>
       </c>
       <c r="G59" s="8">
@@ -44039,11 +44243,11 @@
         <v/>
       </c>
       <c r="H59" s="16">
-        <f>Plan!I59</f>
+        <f>Plan!I60</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>Plan!O59</f>
+        <f>Plan!O60</f>
         <v/>
       </c>
     </row>
@@ -44053,22 +44257,22 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="C60" s="35">
-        <f>Plan!C36</f>
+        <f>Plan!C59</f>
         <v/>
       </c>
       <c r="D60" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E60" s="16">
-        <f>Plan!J36</f>
+        <f>Plan!J59</f>
         <v/>
       </c>
       <c r="F60" s="16">
-        <f>Plan!K36</f>
+        <f>Plan!K59</f>
         <v/>
       </c>
       <c r="G60" s="8">
@@ -44076,11 +44280,11 @@
         <v/>
       </c>
       <c r="H60" s="16">
-        <f>Plan!I36</f>
+        <f>Plan!I59</f>
         <v/>
       </c>
       <c r="I60" s="16">
-        <f>Plan!O36</f>
+        <f>Plan!O59</f>
         <v/>
       </c>
     </row>
@@ -44090,22 +44294,22 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="C61" s="35">
-        <f>Plan!C46</f>
+        <f>Plan!C69</f>
         <v/>
       </c>
       <c r="D61" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E61" s="16">
-        <f>Plan!J46</f>
+        <f>Plan!J69</f>
         <v/>
       </c>
       <c r="F61" s="16">
-        <f>Plan!K46</f>
+        <f>Plan!K69</f>
         <v/>
       </c>
       <c r="G61" s="8">
@@ -44113,11 +44317,11 @@
         <v/>
       </c>
       <c r="H61" s="16">
-        <f>Plan!I46</f>
+        <f>Plan!I69</f>
         <v/>
       </c>
       <c r="I61" s="16">
-        <f>Plan!O46</f>
+        <f>Plan!O69</f>
         <v/>
       </c>
     </row>
@@ -44127,22 +44331,22 @@
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="C62" s="35">
-        <f>Plan!C47</f>
+        <f>Plan!C62</f>
         <v/>
       </c>
       <c r="D62" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E62" s="16">
-        <f>Plan!J47</f>
+        <f>Plan!J62</f>
         <v/>
       </c>
       <c r="F62" s="16">
-        <f>Plan!K47</f>
+        <f>Plan!K62</f>
         <v/>
       </c>
       <c r="G62" s="8">
@@ -44150,11 +44354,11 @@
         <v/>
       </c>
       <c r="H62" s="16">
-        <f>Plan!I47</f>
+        <f>Plan!I62</f>
         <v/>
       </c>
       <c r="I62" s="16">
-        <f>Plan!O47</f>
+        <f>Plan!O62</f>
         <v/>
       </c>
     </row>
@@ -44201,22 +44405,22 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C64" s="35">
-        <f>Plan!C72</f>
+        <f>Plan!C12</f>
         <v/>
       </c>
       <c r="D64" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" s="16">
-        <f>Plan!J72</f>
+        <f>Plan!J12</f>
         <v/>
       </c>
       <c r="F64" s="16">
-        <f>Plan!K72</f>
+        <f>Plan!K12</f>
         <v/>
       </c>
       <c r="G64" s="8">
@@ -44224,11 +44428,11 @@
         <v/>
       </c>
       <c r="H64" s="16">
-        <f>Plan!I72</f>
+        <f>Plan!I12</f>
         <v/>
       </c>
       <c r="I64" s="16">
-        <f>Plan!O72</f>
+        <f>Plan!O12</f>
         <v/>
       </c>
     </row>
@@ -44238,22 +44442,22 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="C65" s="35">
-        <f>Plan!C74</f>
+        <f>Plan!C47</f>
         <v/>
       </c>
       <c r="D65" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E65" s="16">
-        <f>Plan!J74</f>
+        <f>Plan!J47</f>
         <v/>
       </c>
       <c r="F65" s="16">
-        <f>Plan!K74</f>
+        <f>Plan!K47</f>
         <v/>
       </c>
       <c r="G65" s="8">
@@ -44261,11 +44465,11 @@
         <v/>
       </c>
       <c r="H65" s="16">
-        <f>Plan!I74</f>
+        <f>Plan!I47</f>
         <v/>
       </c>
       <c r="I65" s="16">
-        <f>Plan!O74</f>
+        <f>Plan!O47</f>
         <v/>
       </c>
     </row>
@@ -44312,22 +44516,22 @@
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C67" s="35">
-        <f>Plan!C71</f>
+        <f>Plan!C46</f>
         <v/>
       </c>
       <c r="D67" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E67" s="16">
-        <f>Plan!J71</f>
+        <f>Plan!J46</f>
         <v/>
       </c>
       <c r="F67" s="16">
-        <f>Plan!K71</f>
+        <f>Plan!K46</f>
         <v/>
       </c>
       <c r="G67" s="8">
@@ -44335,11 +44539,11 @@
         <v/>
       </c>
       <c r="H67" s="16">
-        <f>Plan!I71</f>
+        <f>Plan!I46</f>
         <v/>
       </c>
       <c r="I67" s="16">
-        <f>Plan!O71</f>
+        <f>Plan!O46</f>
         <v/>
       </c>
     </row>
@@ -44349,22 +44553,22 @@
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="C68" s="35">
-        <f>Plan!C62</f>
+        <f>Plan!C63</f>
         <v/>
       </c>
       <c r="D68" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E68" s="16">
-        <f>Plan!J62</f>
+        <f>Plan!J63</f>
         <v/>
       </c>
       <c r="F68" s="16">
-        <f>Plan!K62</f>
+        <f>Plan!K63</f>
         <v/>
       </c>
       <c r="G68" s="8">
@@ -44372,11 +44576,11 @@
         <v/>
       </c>
       <c r="H68" s="16">
-        <f>Plan!I62</f>
+        <f>Plan!I63</f>
         <v/>
       </c>
       <c r="I68" s="16">
-        <f>Plan!O62</f>
+        <f>Plan!O63</f>
         <v/>
       </c>
     </row>
@@ -44386,22 +44590,22 @@
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="C69" s="35">
-        <f>Plan!C63</f>
+        <f>Plan!C74</f>
         <v/>
       </c>
       <c r="D69" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69" s="16">
-        <f>Plan!J63</f>
+        <f>Plan!J74</f>
         <v/>
       </c>
       <c r="F69" s="16">
-        <f>Plan!K63</f>
+        <f>Plan!K74</f>
         <v/>
       </c>
       <c r="G69" s="8">
@@ -44409,11 +44613,11 @@
         <v/>
       </c>
       <c r="H69" s="16">
-        <f>Plan!I63</f>
+        <f>Plan!I74</f>
         <v/>
       </c>
       <c r="I69" s="16">
-        <f>Plan!O63</f>
+        <f>Plan!O74</f>
         <v/>
       </c>
     </row>
@@ -44423,22 +44627,22 @@
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="C70" s="35">
-        <f>Plan!C64</f>
+        <f>Plan!C72</f>
         <v/>
       </c>
       <c r="D70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="16">
-        <f>Plan!J64</f>
+        <f>Plan!J72</f>
         <v/>
       </c>
       <c r="F70" s="16">
-        <f>Plan!K64</f>
+        <f>Plan!K72</f>
         <v/>
       </c>
       <c r="G70" s="8">
@@ -44446,11 +44650,11 @@
         <v/>
       </c>
       <c r="H70" s="16">
-        <f>Plan!I64</f>
+        <f>Plan!I72</f>
         <v/>
       </c>
       <c r="I70" s="16">
-        <f>Plan!O64</f>
+        <f>Plan!O72</f>
         <v/>
       </c>
     </row>
@@ -44460,22 +44664,22 @@
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C71" s="35">
-        <f>Plan!C56</f>
+        <f>Plan!C44</f>
         <v/>
       </c>
       <c r="D71" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E71" s="16">
-        <f>Plan!J56</f>
+        <f>Plan!J44</f>
         <v/>
       </c>
       <c r="F71" s="16">
-        <f>Plan!K56</f>
+        <f>Plan!K44</f>
         <v/>
       </c>
       <c r="G71" s="8">
@@ -44483,11 +44687,11 @@
         <v/>
       </c>
       <c r="H71" s="16">
-        <f>Plan!I56</f>
+        <f>Plan!I44</f>
         <v/>
       </c>
       <c r="I71" s="16">
-        <f>Plan!O56</f>
+        <f>Plan!O44</f>
         <v/>
       </c>
     </row>
@@ -44497,22 +44701,22 @@
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="C72" s="35">
-        <f>Plan!C12</f>
+        <f>Plan!C75</f>
         <v/>
       </c>
       <c r="D72" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" s="16">
-        <f>Plan!J12</f>
+        <f>Plan!J75</f>
         <v/>
       </c>
       <c r="F72" s="16">
-        <f>Plan!K12</f>
+        <f>Plan!K75</f>
         <v/>
       </c>
       <c r="G72" s="8">
@@ -44520,11 +44724,11 @@
         <v/>
       </c>
       <c r="H72" s="16">
-        <f>Plan!I12</f>
+        <f>Plan!I75</f>
         <v/>
       </c>
       <c r="I72" s="16">
-        <f>Plan!O12</f>
+        <f>Plan!O75</f>
         <v/>
       </c>
     </row>
@@ -44571,22 +44775,22 @@
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="C74" s="35">
-        <f>Plan!C75</f>
+        <f>Plan!C56</f>
         <v/>
       </c>
       <c r="D74" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="16">
-        <f>Plan!J75</f>
+        <f>Plan!J56</f>
         <v/>
       </c>
       <c r="F74" s="16">
-        <f>Plan!K75</f>
+        <f>Plan!K56</f>
         <v/>
       </c>
       <c r="G74" s="8">
@@ -44594,11 +44798,11 @@
         <v/>
       </c>
       <c r="H74" s="16">
-        <f>Plan!I75</f>
+        <f>Plan!I56</f>
         <v/>
       </c>
       <c r="I74" s="16">
-        <f>Plan!O75</f>
+        <f>Plan!O56</f>
         <v/>
       </c>
     </row>
@@ -44608,22 +44812,22 @@
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="C75" s="35">
-        <f>Plan!C44</f>
+        <f>Plan!C64</f>
         <v/>
       </c>
       <c r="D75" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" s="16">
-        <f>Plan!J44</f>
+        <f>Plan!J64</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>Plan!K44</f>
+        <f>Plan!K64</f>
         <v/>
       </c>
       <c r="G75" s="8">
@@ -44631,11 +44835,11 @@
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>Plan!I44</f>
+        <f>Plan!I64</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>Plan!O44</f>
+        <f>Plan!O64</f>
         <v/>
       </c>
     </row>
@@ -45333,7 +45537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45397,17 +45601,17 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.14; nuevo 6.16</t>
+          <t>1.7, 2.15</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Tokens y landing del rediseño C+ llevados a código</t>
+          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
+          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
         </is>
       </c>
     </row>
@@ -45424,17 +45628,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
+          <t>3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
+          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
+          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
         </is>
       </c>
     </row>
@@ -45446,22 +45650,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>1.8; P-47, P-90, P-91, P-92</t>
+          <t>1.7, 2.14; nuevo 6.16</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
+          <t>Tokens y landing del rediseño C+ llevados a código</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
+          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
         </is>
       </c>
     </row>
@@ -45471,24 +45675,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (despliegue PR #2)</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89</t>
+          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
+          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
+          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
         </is>
       </c>
     </row>
@@ -45498,24 +45702,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
+          <t>1.8; P-47, P-90, P-91, P-92</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
+          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
+          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
         </is>
       </c>
     </row>
@@ -45525,24 +45729,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>sesión principal</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (despliegue PR #2)</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-13</t>
+          <t>4.9; P-83, P-84, P-85, P-89</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Texto de vigilancia de Supersolidaria confirmado</t>
+          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
+          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
         </is>
       </c>
     </row>
@@ -45552,24 +45756,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-qa</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>6.3; nuevos P-84, P-86, P-87</t>
+          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>QA de producción: con observaciones</t>
+          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
+          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
         </is>
       </c>
     </row>
@@ -45586,17 +45790,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>2.12; nuevo P-85</t>
+          <t>5.3; P-13</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
+          <t>Texto de vigilancia de Supersolidaria confirmado</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
+          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
         </is>
       </c>
     </row>
@@ -45608,22 +45812,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>6.2; nuevos P-83, P-88</t>
+          <t>6.3; nuevos P-84, P-86, P-87</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
+          <t>QA de producción: con observaciones</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
+          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
         </is>
       </c>
     </row>
@@ -45633,24 +45837,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
+          <t>2.12; nuevo P-85</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
+          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
+          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
         </is>
       </c>
     </row>
@@ -45660,31 +45864,31 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>6.9, 6.13; P-44, P-59, P-61</t>
+          <t>6.2; nuevos P-83, P-88</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
+          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
+          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -45694,44 +45898,44 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
+          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
+          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
+          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Sebas (acuerdo con Carlos Pardo)</t>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
+          <t>6.9, 6.13; P-44, P-59, P-61</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
+          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
+          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
         </is>
       </c>
     </row>
@@ -45741,24 +45945,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>6.1, P-58</t>
+          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
+          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
+          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
         </is>
       </c>
     </row>
@@ -45770,22 +45974,22 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Sebas (coordinación con la cooperativa)</t>
+          <t>Sebas (acuerdo con Carlos Pardo)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
+          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
+          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
+          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
         </is>
       </c>
     </row>
@@ -45797,22 +46001,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
+          <t>6.1, P-58</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
+          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
+          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
         </is>
       </c>
     </row>
@@ -45822,24 +46026,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>ga-revisor-seguridad</t>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (coordinación con la cooperativa)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
+          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
+          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
         </is>
       </c>
     </row>
@@ -45851,22 +46055,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
+          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
+          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
         </is>
       </c>
     </row>
@@ -45878,22 +46082,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Sorteo mensual en /cuenta</t>
+          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
+          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
         </is>
       </c>
     </row>
@@ -45905,22 +46109,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>4.6; P-57</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
+          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
+          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
         </is>
       </c>
     </row>
@@ -45932,76 +46136,76 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>1.5; P-63</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
+          <t>Sorteo mensual en /cuenta</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
+          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>4.6; P-57</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
+          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
+          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive + ga-verificador-qa</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>6.3; P-39</t>
+          <t>1.5; P-63</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
+          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
+          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
         </is>
       </c>
     </row>
@@ -46011,24 +46215,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive</t>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 5.8; P-39, P-53</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
+          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
+          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
         </is>
       </c>
     </row>
@@ -46038,24 +46242,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>ga-verificador-responsive + ga-verificador-qa</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
+          <t>6.3; P-39</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
+          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
+          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
         </is>
       </c>
     </row>
@@ -46067,22 +46271,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>5.2, 5.8, 6.3</t>
+          <t>6.3, 5.2, 5.8; P-39, P-53</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
+          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
+          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
         </is>
       </c>
     </row>
@@ -46094,22 +46298,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
+          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
+          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
+          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
         </is>
       </c>
     </row>
@@ -46126,17 +46330,17 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>2.1, 5.3, 5.7; P-16, P-52</t>
+          <t>5.2, 5.8, 6.3</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
+          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
+          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
         </is>
       </c>
     </row>
@@ -46148,22 +46352,22 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
+          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
+          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
+          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
         </is>
       </c>
     </row>
@@ -46173,24 +46377,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
+          <t>2.1, 5.3, 5.7; P-16, P-52</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
+          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
+          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
         </is>
       </c>
     </row>
@@ -46202,22 +46406,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Agente ga-auditor-supabase corregido</t>
+          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
         </is>
       </c>
     </row>
@@ -46234,17 +46438,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>3.1, 6.5, 6.10; P-09</t>
+          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
         </is>
       </c>
     </row>
@@ -46256,22 +46460,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ga-escritor-tests</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+          <t>Agente ga-auditor-supabase corregido</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
         </is>
       </c>
     </row>
@@ -46283,22 +46487,22 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Sebas + ga-funcionalidad-botones</t>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+          <t>3.1, 6.5, 6.10; P-09</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
         </is>
       </c>
     </row>
@@ -46310,22 +46514,22 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
         </is>
       </c>
     </row>
@@ -46335,24 +46539,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
         </is>
       </c>
     </row>
@@ -46364,20 +46568,74 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>ga-verificador-qa</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
           <t>Claude (sesión principal)</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>Todas</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Creación del Excel de avances</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Pendientes desde PENDIENTES.md, plan desde la propuesta (6 fases, 8 semanas) reorganizado en 2 filas con cola infinita y pesos 1–5.</t>
         </is>

--- a/docs/avances/Avances_Green_Alliance.xlsx
+++ b/docs/avances/Avances_Green_Alliance.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bitácora" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$4:$R$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -806,7 +806,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actualizado: 2026-09-25. Lo mantiene el agente ga-supervisor-avances a partir de docs/avances/plan.json.</t>
+          <t>Actualizado: 2026-09-27. Lo mantiene el agente ga-supervisor-avances a partir de docs/avances/plan.json.</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B46,Pendientes!$G$5:$G$101,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B46,Pendientes!$G$5:$G$102,"Hecho")</f>
         <v/>
       </c>
       <c r="D46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B46,Pendientes!$G$5:$G$101,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B46,Pendientes!$G$5:$G$102,"En curso")</f>
         <v/>
       </c>
       <c r="E46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B46,Pendientes!$G$5:$G$101,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B46,Pendientes!$G$5:$G$102,"Pendiente")</f>
         <v/>
       </c>
       <c r="F46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B46,Pendientes!$G$5:$G$101,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B46,Pendientes!$G$5:$G$102,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G46" s="9">
@@ -1522,19 +1522,19 @@
         </is>
       </c>
       <c r="C47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B47,Pendientes!$G$5:$G$101,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B47,Pendientes!$G$5:$G$102,"Hecho")</f>
         <v/>
       </c>
       <c r="D47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B47,Pendientes!$G$5:$G$101,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B47,Pendientes!$G$5:$G$102,"En curso")</f>
         <v/>
       </c>
       <c r="E47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B47,Pendientes!$G$5:$G$101,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B47,Pendientes!$G$5:$G$102,"Pendiente")</f>
         <v/>
       </c>
       <c r="F47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B47,Pendientes!$G$5:$G$101,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B47,Pendientes!$G$5:$G$102,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G47" s="9">
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B48,Pendientes!$G$5:$G$101,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B48,Pendientes!$G$5:$G$102,"Hecho")</f>
         <v/>
       </c>
       <c r="D48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B48,Pendientes!$G$5:$G$101,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B48,Pendientes!$G$5:$G$102,"En curso")</f>
         <v/>
       </c>
       <c r="E48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B48,Pendientes!$G$5:$G$101,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B48,Pendientes!$G$5:$G$102,"Pendiente")</f>
         <v/>
       </c>
       <c r="F48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B48,Pendientes!$G$5:$G$101,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B48,Pendientes!$G$5:$G$102,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G48" s="9">
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B49,Pendientes!$G$5:$G$101,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B49,Pendientes!$G$5:$G$102,"Hecho")</f>
         <v/>
       </c>
       <c r="D49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B49,Pendientes!$G$5:$G$101,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B49,Pendientes!$G$5:$G$102,"En curso")</f>
         <v/>
       </c>
       <c r="E49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B49,Pendientes!$G$5:$G$101,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B49,Pendientes!$G$5:$G$102,"Pendiente")</f>
         <v/>
       </c>
       <c r="F49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B49,Pendientes!$G$5:$G$101,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B49,Pendientes!$G$5:$G$102,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G49" s="9">
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B50,Pendientes!$G$5:$G$101,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B50,Pendientes!$G$5:$G$102,"Hecho")</f>
         <v/>
       </c>
       <c r="D50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B50,Pendientes!$G$5:$G$101,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B50,Pendientes!$G$5:$G$102,"En curso")</f>
         <v/>
       </c>
       <c r="E50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B50,Pendientes!$G$5:$G$101,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B50,Pendientes!$G$5:$G$102,"Pendiente")</f>
         <v/>
       </c>
       <c r="F50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B50,Pendientes!$G$5:$G$101,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B50,Pendientes!$G$5:$G$102,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G50" s="9">
@@ -1630,19 +1630,19 @@
         </is>
       </c>
       <c r="C51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B51,Pendientes!$G$5:$G$101,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B51,Pendientes!$G$5:$G$102,"Hecho")</f>
         <v/>
       </c>
       <c r="D51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B51,Pendientes!$G$5:$G$101,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B51,Pendientes!$G$5:$G$102,"En curso")</f>
         <v/>
       </c>
       <c r="E51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B51,Pendientes!$G$5:$G$101,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B51,Pendientes!$G$5:$G$102,"Pendiente")</f>
         <v/>
       </c>
       <c r="F51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B51,Pendientes!$G$5:$G$101,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B51,Pendientes!$G$5:$G$102,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G51" s="9">
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c r="C52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B52,Pendientes!$G$5:$G$101,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B52,Pendientes!$G$5:$G$102,"Hecho")</f>
         <v/>
       </c>
       <c r="D52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B52,Pendientes!$G$5:$G$101,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B52,Pendientes!$G$5:$G$102,"En curso")</f>
         <v/>
       </c>
       <c r="E52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B52,Pendientes!$G$5:$G$101,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B52,Pendientes!$G$5:$G$102,"Pendiente")</f>
         <v/>
       </c>
       <c r="F52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B52,Pendientes!$G$5:$G$101,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B52,Pendientes!$G$5:$G$102,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G52" s="9">
@@ -1684,19 +1684,19 @@
         </is>
       </c>
       <c r="C53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B53,Pendientes!$G$5:$G$101,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B53,Pendientes!$G$5:$G$102,"Hecho")</f>
         <v/>
       </c>
       <c r="D53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B53,Pendientes!$G$5:$G$101,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B53,Pendientes!$G$5:$G$102,"En curso")</f>
         <v/>
       </c>
       <c r="E53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B53,Pendientes!$G$5:$G$101,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B53,Pendientes!$G$5:$G$102,"Pendiente")</f>
         <v/>
       </c>
       <c r="F53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$101,$B53,Pendientes!$G$5:$G$101,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$102,$B53,Pendientes!$G$5:$G$102,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G53" s="9">
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5989,7 +5989,7 @@
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-98</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5999,22 +5999,22 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Asesor</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
+          <t>Confirmar la regla de categorización de asociados ya afiliados como «Aprobada» en las tarjetas/chips de /asesor (pedido D-06 del lienzo)</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="I88" s="21">
@@ -6033,14 +6033,14 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>Por ahora son una sección en /cuenta (#convenios).</t>
+          <t>27-sep: ga-diseno-a-codigo implementó en lib/asesor/resumen.ts (categoriaAfiliacion, TODO(diseno: D-06)) la regla «un asociado ya es, por definición, una afiliación Aprobada» (agrupa origen:'asociado' en la tarjeta/chip «Aprobada» sin importar su estado de crédito), documentada como decisión provisional de la sesión principal. Falta que Sebas o ga-disenador-lienzo la confirmen, o decidan si un asociado con crédito rechazado debe verse distinto, y si la columna «Último crédito» necesita su propio color en el lienzo. Ver docs/diseno/pedidos.md D-06.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="19" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -6050,17 +6050,17 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>A 320 px la línea «COOPERATIVA» del logo mide ~5 px de alto (opcional: ocultarla o achicar «Ingresar» bajo 360 px)</t>
+          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I89" s="21">
@@ -6084,14 +6084,14 @@
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>Menor y opcional, reportado por ga-verificador-responsive el 23-sep.</t>
+          <t>Por ahora son una sección en /cuenta (#convenios).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="19" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -6101,32 +6101,32 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
+          <t>A 320 px la línea «COOPERATIVA» del logo mide ~5 px de alto (opcional: ocultarla o achicar «Ingresar» bajo 360 px)</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Sebas (ga-auditor-supabase revisa antes)</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I90" s="21">
@@ -6135,14 +6135,14 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
+          <t>Menor y opcional, reportado por ga-verificador-responsive el 23-sep.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="19" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
+          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Sebas (ga-auditor-supabase revisa antes)</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="I91" s="21">
@@ -6186,14 +6186,14 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>Apartado «Mis datos» ya maquetado.</t>
+          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="19" t="inlineStr">
         <is>
-          <t>P-65</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -6203,17 +6203,17 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Sorteo</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Decidir si un admin o un asesor pueden participar en el sorteo mensual</t>
+          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I92" s="21">
@@ -6237,14 +6237,14 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-revisor-seguridad el 24-sep. 24-sep: decidido que solo participan asociados (S-13, ya implementado en participarSorteo).</t>
+          <t>Apartado «Mis datos» ya maquetado.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>P-65</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -6254,22 +6254,22 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Sorteo</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Color de error #B3261E</t>
+          <t>Decidir si un admin o un asesor pueden participar en el sorteo mensual</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I93" s="21">
@@ -6288,14 +6288,14 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>Se deja.</t>
+          <t>Sugerido por ga-revisor-seguridad el 24-sep. 24-sep: decidido que solo participan asociados (S-13, ya implementado en participarSorteo).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="19" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Estado vacío de «Tu solicitud»</t>
+          <t>Color de error #B3261E</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I94" s="21">
@@ -6339,14 +6339,14 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>Ver con /cuenta?vacio=1.</t>
+          <t>Se deja.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="19" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Logo en celular como enlace a la landing</t>
+          <t>Estado vacío de «Tu solicitud»</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -6381,19 +6381,23 @@
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I95" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H95,Plan!$A$5:$A$75,0)),"—")</f>
         <v/>
       </c>
-      <c r="J95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>Ver con /cuenta?vacio=1.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="19" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-04</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -6408,7 +6412,7 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Escudo: public/logos/vector/green-alliance-logo.svg</t>
+          <t>Logo en celular como enlace a la landing</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -6440,7 +6444,7 @@
     <row r="97">
       <c r="A97" s="19" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -6450,12 +6454,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Formulario de ingreso entre 640 y 767 px (columna de 440 px)</t>
+          <t>Escudo: public/logos/vector/green-alliance-logo.svg</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -6475,7 +6479,7 @@
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I97" s="21">
@@ -6487,7 +6491,7 @@
     <row r="98">
       <c r="A98" s="19" t="inlineStr">
         <is>
-          <t>P-07</t>
+          <t>P-06</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -6502,7 +6506,7 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Panel verde en tableta (640–1023 px) centrado</t>
+          <t>Formulario de ingreso entre 640 y 767 px (columna de 440 px)</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
@@ -6534,27 +6538,27 @@
     <row r="99">
       <c r="A99" s="19" t="inlineStr">
         <is>
-          <t>P-88</t>
+          <t>P-07</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Decisión</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>/ingresar</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>F2-08: tr_componer_nombre_afiliacion no cubre el update directo de solicitudes_afiliacion.nombre por un admin</t>
+          <t>Panel verde en tableta (640–1023 px) centrado</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -6564,63 +6568,59 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="I99" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H99,Plan!$A$5:$A$75,0)),"—")</f>
         <v/>
       </c>
-      <c r="J99" s="7" t="inlineStr">
-        <is>
-          <t>Documentado en docs/auditorias/2026-09-24-fase-2.md; confirmado sin corregir por ga-revisor-seguridad el 25-sep. Un admin puede reescribir `nombre` por SQL directo, y ese texto lo usan el correo «Ingreso aceptado» y el nombre_completo del perfil. Solo afecta a admins.</t>
-        </is>
-      </c>
+      <c r="J99" s="7" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="19" t="inlineStr">
         <is>
-          <t>P-83</t>
+          <t>P-88</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>Correos</t>
-        </is>
-      </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>S-15: escapar/validar HTML en las variables NOMBRE/MOTIVO de los correos de Resend</t>
+          <t>F2-08: tr_componer_nombre_afiliacion no cubre el update directo de solicitudes_afiliacion.nombre por un admin</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I100" s="21">
@@ -6629,29 +6629,29 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>25-sep: hallazgo de ga-revisor-seguridad (un admin puede meter HTML en perfiles.nombre_completo o en el motivo de rechazo). Corregido en local con pruebas (tests/unit/correo-resend.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02).</t>
+          <t>Documentado en docs/auditorias/2026-09-24-fase-2.md; confirmado sin corregir por ga-revisor-seguridad el 25-sep. Un admin puede reescribir `nombre` por SQL directo, y ese texto lo usan el correo «Ingreso aceptado» y el nombre_completo del perfil. Solo afecta a admins.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="19" t="inlineStr">
         <is>
-          <t>P-84</t>
+          <t>P-83</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>M-01: el número de WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts</t>
+          <t>S-15: escapar/validar HTML en las variables NOMBRE/MOTIVO de los correos de Resend</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I101" s="21">
@@ -6680,13 +6680,64 @@
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
+          <t>25-sep: hallazgo de ga-revisor-seguridad (un admin puede meter HTML en perfiles.nombre_completo o en el motivo de rechazo). Corregido en local con pruebas (tests/unit/correo-resend.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="19" t="inlineStr">
+        <is>
+          <t>P-84</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>M-01: el número de WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="I102" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$75,MATCH(H102,Plan!$A$5:$A$75,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
           <t>25-sep: hallazgo de ga-verificador-qa (patrón sin la barra invertida de \D/\d; el enlace wa.me sí funciona). Corregido en local con pruebas (tests/unit/config-whatsapp.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02); confirmado en vivo «311 724 1942».</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J101"/>
-  <conditionalFormatting sqref="G5:G101">
+  <autoFilter ref="A4:J102"/>
+  <conditionalFormatting sqref="G5:G102">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$G5="Hecho"</formula>
     </cfRule>
@@ -6700,7 +6751,7 @@
       <formula>$G5="Bloqueado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F101">
+  <conditionalFormatting sqref="F5:F102">
     <cfRule type="expression" priority="5" dxfId="5">
       <formula>$F5="Alta"</formula>
     </cfRule>
@@ -6711,16 +6762,16 @@
       <formula>$F5="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:F101">
+  <conditionalFormatting sqref="A5:F102">
     <cfRule type="expression" priority="8" dxfId="8">
       <formula>$G5="Hecho"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Hecho,En curso,Pendiente,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7210,19 +7261,19 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>4.5, 2.10, 6.8</t>
+          <t>4.5, 6.11, 2.10</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J9" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L9" s="8">
         <f>K9+E9</f>
@@ -7288,7 +7339,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>2.12, 5.2</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
@@ -7297,10 +7348,10 @@
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L10" s="8">
         <f>K10+E10</f>
@@ -7366,7 +7417,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
@@ -7378,7 +7429,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L11" s="8">
         <f>K11+E11</f>
@@ -7444,19 +7495,19 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L12" s="8">
         <f>K12+E12</f>
@@ -7522,7 +7573,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.6, 1.7</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
@@ -7534,7 +7585,7 @@
         <v>6</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L13" s="8">
         <f>K13+E13</f>
@@ -7678,7 +7729,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I15" s="18" t="inlineStr">
@@ -7690,7 +7741,7 @@
         <v>6</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L15" s="8">
         <f>K15+E15</f>
@@ -7834,7 +7885,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>2.3, 3.4</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I17" s="18" t="inlineStr">
@@ -7912,7 +7963,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>3.4, 2.4</t>
+          <t>2.3, 2.4</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr">
@@ -8077,10 +8128,10 @@
         </is>
       </c>
       <c r="J20" s="8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L20" s="8">
         <f>K20+E20</f>
@@ -8146,7 +8197,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>4.1, 3.6, 6.4</t>
+          <t>4.2, 3.6</t>
         </is>
       </c>
       <c r="I21" s="18" t="inlineStr">
@@ -8155,10 +8206,10 @@
         </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L21" s="8">
         <f>K21+E21</f>
@@ -8229,14 +8280,14 @@
       </c>
       <c r="I22" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J22" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L22" s="8">
         <f>K22+E22</f>
@@ -8307,14 +8358,14 @@
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J23" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L23" s="8">
         <f>K23+E23</f>
@@ -8380,7 +8431,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>4.6, 1.7, 1.6</t>
+          <t>1.6, 3.3</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -8389,10 +8440,10 @@
         </is>
       </c>
       <c r="J24" s="8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L24" s="8">
         <f>K24+E24</f>
@@ -8458,19 +8509,19 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L25" s="8">
         <f>K25+E25</f>
@@ -8536,7 +8587,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3.7, 5.5, 2.8</t>
+          <t>3.9, 2.8, 4.4</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
@@ -8545,10 +8596,10 @@
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L26" s="8">
         <f>K26+E26</f>
@@ -8614,7 +8665,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>3.3, 3.7</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
@@ -8623,10 +8674,10 @@
         </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L27" s="8">
         <f>K27+E27</f>
@@ -8770,7 +8821,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.11, 4.10</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr">
@@ -8782,7 +8833,7 @@
         <v>8</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L29" s="8">
         <f>K29+E29</f>
@@ -8848,7 +8899,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>5.2, 2.15</t>
+          <t>2.12, 4.6</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
@@ -8860,7 +8911,7 @@
         <v>8</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L30" s="8">
         <f>K30+E30</f>
@@ -8926,7 +8977,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>2.5, 2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I31" s="18" t="inlineStr">
@@ -8938,7 +8989,7 @@
         <v>6</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L31" s="8">
         <f>K31+E31</f>
@@ -9009,7 +9060,7 @@
       </c>
       <c r="I32" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J32" s="8" t="n">
@@ -9082,7 +9133,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.9, 2.1</t>
         </is>
       </c>
       <c r="I33" s="18" t="inlineStr">
@@ -9094,7 +9145,7 @@
         <v>19</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L33" s="8">
         <f>K33+E33</f>
@@ -9160,7 +9211,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>2.15, 2.14</t>
+          <t>4.6, 5.2</t>
         </is>
       </c>
       <c r="I34" s="18" t="inlineStr">
@@ -9169,10 +9220,10 @@
         </is>
       </c>
       <c r="J34" s="8" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L34" s="8">
         <f>K34+E34</f>
@@ -9238,7 +9289,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>2.1, 4.2</t>
+          <t>2.15, 2.14</t>
         </is>
       </c>
       <c r="I35" s="18" t="inlineStr">
@@ -9247,10 +9298,10 @@
         </is>
       </c>
       <c r="J35" s="8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="L35" s="8">
         <f>K35+E35</f>
@@ -9316,19 +9367,19 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>6.1, 6.3</t>
+          <t>6.8, 5.1</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="L36" s="8">
         <f>K36+E36</f>
@@ -9344,7 +9395,7 @@
       </c>
       <c r="O36" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P36" s="8" t="inlineStr">
@@ -9354,7 +9405,7 @@
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-disenador-lienzo + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr"/>
@@ -9394,12 +9445,12 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>3.5, 2.9</t>
+          <t>3.5, 6.4</t>
         </is>
       </c>
       <c r="I37" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J37" s="8" t="n">
@@ -9472,19 +9523,19 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>3.9, 4.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I38" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J38" s="8" t="n">
         <v>20</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="L38" s="8">
         <f>K38+E38</f>
@@ -9555,14 +9606,14 @@
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J39" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L39" s="8">
         <f>K39+E39</f>
@@ -9628,19 +9679,19 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>6.9, 3.2</t>
+          <t>2.14, 6.9, 4.11</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J40" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L40" s="8">
         <f>K40+E40</f>
@@ -9715,14 +9766,14 @@
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J41" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L41" s="8">
         <f>K41+E41</f>
@@ -9788,19 +9839,19 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>4.2, 2.12</t>
+          <t>3.3, 3.7</t>
         </is>
       </c>
       <c r="I42" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L42" s="8">
         <f>K42+E42</f>
@@ -9866,19 +9917,19 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>4.8, 5.9</t>
+          <t>6.17, 5.10</t>
         </is>
       </c>
       <c r="I43" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J43" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L43" s="8">
         <f>K43+E43</f>
@@ -9944,7 +9995,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>6.18, 4.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr">
@@ -9953,10 +10004,10 @@
         </is>
       </c>
       <c r="J44" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L44" s="8">
         <f>K44+E44</f>
@@ -10022,7 +10073,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>5.8, 2.13</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I45" s="18" t="inlineStr">
@@ -10031,10 +10082,10 @@
         </is>
       </c>
       <c r="J45" s="8" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L45" s="8">
         <f>K45+E45</f>
@@ -10100,7 +10151,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>4.11, 6.6</t>
+          <t>3.2, 6.13</t>
         </is>
       </c>
       <c r="I46" s="18" t="inlineStr">
@@ -10109,10 +10160,10 @@
         </is>
       </c>
       <c r="J46" s="8" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L46" s="8">
         <f>K46+E46</f>
@@ -10128,7 +10179,7 @@
       </c>
       <c r="O46" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P46" s="8" t="inlineStr">
@@ -10138,7 +10189,7 @@
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-disenador-lienzo + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr"/>
@@ -10178,19 +10229,19 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>5.10, 4.10</t>
+          <t>4.4, 3.2</t>
         </is>
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J47" s="8" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="L47" s="8">
         <f>K47+E47</f>
@@ -10206,7 +10257,7 @@
       </c>
       <c r="O47" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P47" s="8" t="inlineStr">
@@ -10216,7 +10267,7 @@
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-disenador-lienzo + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr"/>
@@ -10256,19 +10307,19 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L48" s="8">
         <f>K48+E48</f>
@@ -10334,7 +10385,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>1.6, 3.3</t>
+          <t>3.7, 5.5</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
@@ -10343,10 +10394,10 @@
         </is>
       </c>
       <c r="J49" s="8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L49" s="8">
         <f>K49+E49</f>
@@ -10412,7 +10463,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.1, 6.15</t>
         </is>
       </c>
       <c r="I50" s="18" t="inlineStr">
@@ -10421,10 +10472,10 @@
         </is>
       </c>
       <c r="J50" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L50" s="8">
         <f>K50+E50</f>
@@ -10503,10 +10554,10 @@
         </is>
       </c>
       <c r="J51" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L51" s="8">
         <f>K51+E51</f>
@@ -10576,7 +10627,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="I52" s="18" t="inlineStr">
@@ -10585,10 +10636,10 @@
         </is>
       </c>
       <c r="J52" s="8" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L52" s="8">
         <f>K52+E52</f>
@@ -10663,10 +10714,10 @@
         </is>
       </c>
       <c r="J53" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L53" s="8">
         <f>K53+E53</f>
@@ -10732,19 +10783,19 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I54" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J54" s="8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L54" s="8">
         <f>K54+E54</f>
@@ -10810,7 +10861,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I55" s="18" t="inlineStr">
@@ -10819,10 +10870,10 @@
         </is>
       </c>
       <c r="J55" s="8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L55" s="8">
         <f>K55+E55</f>
@@ -10888,7 +10939,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>4.7, 6.7</t>
+          <t>6.16, 6.17</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr">
@@ -10897,10 +10948,10 @@
         </is>
       </c>
       <c r="J56" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L56" s="8">
         <f>K56+E56</f>
@@ -10966,19 +11017,19 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I57" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J57" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="L57" s="8">
         <f>K57+E57</f>
@@ -11044,7 +11095,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>5.3, 3.10</t>
+          <t>6.2, 5.3</t>
         </is>
       </c>
       <c r="I58" s="18" t="inlineStr">
@@ -11053,10 +11104,10 @@
         </is>
       </c>
       <c r="J58" s="8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L58" s="8">
         <f>K58+E58</f>
@@ -11122,7 +11173,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>6.3, 6.12</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I59" s="18" t="inlineStr">
@@ -11131,10 +11182,10 @@
         </is>
       </c>
       <c r="J59" s="8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L59" s="8">
         <f>K59+E59</f>
@@ -11200,7 +11251,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>3.10, 6.2</t>
+          <t>1.8, 6.12</t>
         </is>
       </c>
       <c r="I60" s="18" t="inlineStr">
@@ -11209,10 +11260,10 @@
         </is>
       </c>
       <c r="J60" s="8" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L60" s="8">
         <f>K60+E60</f>
@@ -11278,7 +11329,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I61" s="18" t="inlineStr">
@@ -11290,7 +11341,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L61" s="8">
         <f>K61+E61</f>
@@ -11365,10 +11416,10 @@
         </is>
       </c>
       <c r="J62" s="8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L62" s="8">
         <f>K62+E62</f>
@@ -11434,7 +11485,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>4.10, 6.17</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="I63" s="18" t="inlineStr">
@@ -11443,10 +11494,10 @@
         </is>
       </c>
       <c r="J63" s="8" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L63" s="8">
         <f>K63+E63</f>
@@ -11512,7 +11563,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="I64" s="18" t="inlineStr">
@@ -11521,10 +11572,10 @@
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L64" s="8">
         <f>K64+E64</f>
@@ -11590,19 +11641,19 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I65" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J65" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="L65" s="8">
         <f>K65+E65</f>
@@ -11673,11 +11724,11 @@
       </c>
       <c r="I66" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J66" s="8" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K66" s="8" t="n">
         <v>49</v>
@@ -11824,19 +11875,19 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I68" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J68" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="L68" s="8">
         <f>K68+E68</f>
@@ -11902,19 +11953,19 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J69" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L69" s="8">
         <f>K69+E69</f>
@@ -11980,19 +12031,19 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="I70" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J70" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="L70" s="8">
         <f>K70+E70</f>
@@ -12063,14 +12114,14 @@
       </c>
       <c r="I71" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J71" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L71" s="8">
         <f>K71+E71</f>
@@ -12136,7 +12187,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I72" s="18" t="inlineStr">
@@ -12145,10 +12196,10 @@
         </is>
       </c>
       <c r="J72" s="8" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="L72" s="8">
         <f>K72+E72</f>
@@ -12214,19 +12265,19 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J73" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L73" s="8">
         <f>K73+E73</f>
@@ -12292,12 +12343,12 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>6.6, 6.15</t>
+          <t>5.9, 4.7</t>
         </is>
       </c>
       <c r="I74" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J74" s="8" t="n">
@@ -12370,19 +12421,19 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J75" s="8" t="n">
         <v>78</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L75" s="8">
         <f>K75+E75</f>
@@ -42481,22 +42532,22 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C12" s="35">
-        <f>Plan!C15</f>
+        <f>Plan!C31</f>
         <v/>
       </c>
       <c r="D12" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="16">
-        <f>Plan!J15</f>
+        <f>Plan!J31</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>Plan!K15</f>
+        <f>Plan!K31</f>
         <v/>
       </c>
       <c r="G12" s="8">
@@ -42504,11 +42555,11 @@
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>Plan!I15</f>
+        <f>Plan!I31</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>Plan!O15</f>
+        <f>Plan!O31</f>
         <v/>
       </c>
     </row>
@@ -42518,22 +42569,22 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="C13" s="35">
-        <f>Plan!C31</f>
+        <f>Plan!C18</f>
         <v/>
       </c>
       <c r="D13" s="8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E13" s="16">
-        <f>Plan!J31</f>
+        <f>Plan!J18</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>Plan!K31</f>
+        <f>Plan!K18</f>
         <v/>
       </c>
       <c r="G13" s="8">
@@ -42541,11 +42592,11 @@
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>Plan!I31</f>
+        <f>Plan!I18</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>Plan!O31</f>
+        <f>Plan!O18</f>
         <v/>
       </c>
     </row>
@@ -42555,22 +42606,22 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C14" s="35">
-        <f>Plan!C18</f>
+        <f>Plan!C15</f>
         <v/>
       </c>
       <c r="D14" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E14" s="16">
-        <f>Plan!J18</f>
+        <f>Plan!J15</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>Plan!K18</f>
+        <f>Plan!K15</f>
         <v/>
       </c>
       <c r="G14" s="8">
@@ -42578,11 +42629,11 @@
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>Plan!I18</f>
+        <f>Plan!I15</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>Plan!O18</f>
+        <f>Plan!O15</f>
         <v/>
       </c>
     </row>
@@ -42777,22 +42828,22 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="C20" s="35">
-        <f>Plan!C21</f>
+        <f>Plan!C61</f>
         <v/>
       </c>
       <c r="D20" s="8" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E20" s="16">
-        <f>Plan!J21</f>
+        <f>Plan!J61</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>Plan!K21</f>
+        <f>Plan!K61</f>
         <v/>
       </c>
       <c r="G20" s="8">
@@ -42800,11 +42851,11 @@
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>Plan!I21</f>
+        <f>Plan!I61</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>Plan!O21</f>
+        <f>Plan!O61</f>
         <v/>
       </c>
     </row>
@@ -42814,22 +42865,22 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="C21" s="35">
-        <f>Plan!C33</f>
+        <f>Plan!C21</f>
         <v/>
       </c>
       <c r="D21" s="8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="16">
-        <f>Plan!J33</f>
+        <f>Plan!J21</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>Plan!K33</f>
+        <f>Plan!K21</f>
         <v/>
       </c>
       <c r="G21" s="8">
@@ -42837,11 +42888,11 @@
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>Plan!I33</f>
+        <f>Plan!I21</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>Plan!O33</f>
+        <f>Plan!O21</f>
         <v/>
       </c>
     </row>
@@ -42851,22 +42902,22 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C22" s="35">
-        <f>Plan!C61</f>
+        <f>Plan!C38</f>
         <v/>
       </c>
       <c r="D22" s="8" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E22" s="16">
-        <f>Plan!J61</f>
+        <f>Plan!J38</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>Plan!K61</f>
+        <f>Plan!K38</f>
         <v/>
       </c>
       <c r="G22" s="8">
@@ -42874,11 +42925,11 @@
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>Plan!I61</f>
+        <f>Plan!I38</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>Plan!O61</f>
+        <f>Plan!O38</f>
         <v/>
       </c>
     </row>
@@ -42888,22 +42939,22 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="C23" s="35">
-        <f>Plan!C9</f>
+        <f>Plan!C33</f>
         <v/>
       </c>
       <c r="D23" s="8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E23" s="16">
-        <f>Plan!J9</f>
+        <f>Plan!J33</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>Plan!K9</f>
+        <f>Plan!K33</f>
         <v/>
       </c>
       <c r="G23" s="8">
@@ -42911,11 +42962,11 @@
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>Plan!I9</f>
+        <f>Plan!I33</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>Plan!O9</f>
+        <f>Plan!O33</f>
         <v/>
       </c>
     </row>
@@ -42925,22 +42976,22 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C24" s="35">
-        <f>Plan!C41</f>
+        <f>Plan!C13</f>
         <v/>
       </c>
       <c r="D24" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" s="16">
-        <f>Plan!J41</f>
+        <f>Plan!J13</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>Plan!K41</f>
+        <f>Plan!K13</f>
         <v/>
       </c>
       <c r="G24" s="8">
@@ -42948,11 +42999,11 @@
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>Plan!I41</f>
+        <f>Plan!I13</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>Plan!O41</f>
+        <f>Plan!O13</f>
         <v/>
       </c>
     </row>
@@ -42962,22 +43013,22 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C25" s="35">
-        <f>Plan!C22</f>
+        <f>Plan!C11</f>
         <v/>
       </c>
       <c r="D25" s="8" t="n">
         <v>12</v>
       </c>
       <c r="E25" s="16">
-        <f>Plan!J22</f>
+        <f>Plan!J11</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>Plan!K22</f>
+        <f>Plan!K11</f>
         <v/>
       </c>
       <c r="G25" s="8">
@@ -42985,11 +43036,11 @@
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>Plan!I22</f>
+        <f>Plan!I11</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>Plan!O22</f>
+        <f>Plan!O11</f>
         <v/>
       </c>
     </row>
@@ -42999,22 +43050,22 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C26" s="35">
-        <f>Plan!C65</f>
+        <f>Plan!C9</f>
         <v/>
       </c>
       <c r="D26" s="8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E26" s="16">
-        <f>Plan!J65</f>
+        <f>Plan!J9</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>Plan!K65</f>
+        <f>Plan!K9</f>
         <v/>
       </c>
       <c r="G26" s="8">
@@ -43022,11 +43073,11 @@
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>Plan!I65</f>
+        <f>Plan!I9</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>Plan!O65</f>
+        <f>Plan!O9</f>
         <v/>
       </c>
     </row>
@@ -43036,22 +43087,22 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C27" s="35">
-        <f>Plan!C13</f>
+        <f>Plan!C41</f>
         <v/>
       </c>
       <c r="D27" s="8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E27" s="16">
-        <f>Plan!J13</f>
+        <f>Plan!J41</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>Plan!K13</f>
+        <f>Plan!K41</f>
         <v/>
       </c>
       <c r="G27" s="8">
@@ -43059,11 +43110,11 @@
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>Plan!I13</f>
+        <f>Plan!I41</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>Plan!O13</f>
+        <f>Plan!O41</f>
         <v/>
       </c>
     </row>
@@ -43073,22 +43124,22 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="C28" s="35">
-        <f>Plan!C35</f>
+        <f>Plan!C68</f>
         <v/>
       </c>
       <c r="D28" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E28" s="16">
-        <f>Plan!J35</f>
+        <f>Plan!J68</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>Plan!K35</f>
+        <f>Plan!K68</f>
         <v/>
       </c>
       <c r="G28" s="8">
@@ -43096,11 +43147,11 @@
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>Plan!I35</f>
+        <f>Plan!I68</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>Plan!O35</f>
+        <f>Plan!O68</f>
         <v/>
       </c>
     </row>
@@ -43110,22 +43161,22 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C29" s="35">
-        <f>Plan!C38</f>
+        <f>Plan!C22</f>
         <v/>
       </c>
       <c r="D29" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E29" s="16">
-        <f>Plan!J38</f>
+        <f>Plan!J22</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>Plan!K38</f>
+        <f>Plan!K22</f>
         <v/>
       </c>
       <c r="G29" s="8">
@@ -43133,11 +43184,11 @@
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>Plan!I38</f>
+        <f>Plan!I22</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>Plan!O38</f>
+        <f>Plan!O22</f>
         <v/>
       </c>
     </row>
@@ -43147,22 +43198,22 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="C30" s="35">
-        <f>Plan!C42</f>
+        <f>Plan!C24</f>
         <v/>
       </c>
       <c r="D30" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" s="16">
-        <f>Plan!J42</f>
+        <f>Plan!J24</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>Plan!K42</f>
+        <f>Plan!K24</f>
         <v/>
       </c>
       <c r="G30" s="8">
@@ -43170,11 +43221,11 @@
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>Plan!I42</f>
+        <f>Plan!I24</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>Plan!O42</f>
+        <f>Plan!O24</f>
         <v/>
       </c>
     </row>
@@ -43184,22 +43235,22 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C31" s="35">
-        <f>Plan!C24</f>
+        <f>Plan!C10</f>
         <v/>
       </c>
       <c r="D31" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" s="16">
-        <f>Plan!J24</f>
+        <f>Plan!J10</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>Plan!K24</f>
+        <f>Plan!K10</f>
         <v/>
       </c>
       <c r="G31" s="8">
@@ -43207,11 +43258,11 @@
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>Plan!I24</f>
+        <f>Plan!I10</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>Plan!O24</f>
+        <f>Plan!O10</f>
         <v/>
       </c>
     </row>
@@ -43221,22 +43272,22 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C32" s="35">
-        <f>Plan!C11</f>
+        <f>Plan!C30</f>
         <v/>
       </c>
       <c r="D32" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32" s="16">
-        <f>Plan!J11</f>
+        <f>Plan!J30</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>Plan!K11</f>
+        <f>Plan!K30</f>
         <v/>
       </c>
       <c r="G32" s="8">
@@ -43244,11 +43295,11 @@
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>Plan!I11</f>
+        <f>Plan!I30</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>Plan!O11</f>
+        <f>Plan!O30</f>
         <v/>
       </c>
     </row>
@@ -43258,22 +43309,22 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C33" s="35">
-        <f>Plan!C10</f>
+        <f>Plan!C42</f>
         <v/>
       </c>
       <c r="D33" s="8" t="n">
         <v>11</v>
       </c>
       <c r="E33" s="16">
-        <f>Plan!J10</f>
+        <f>Plan!J42</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>Plan!K10</f>
+        <f>Plan!K42</f>
         <v/>
       </c>
       <c r="G33" s="8">
@@ -43281,11 +43332,11 @@
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>Plan!I10</f>
+        <f>Plan!I42</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>Plan!O10</f>
+        <f>Plan!O42</f>
         <v/>
       </c>
     </row>
@@ -43295,22 +43346,22 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="C34" s="35">
-        <f>Plan!C49</f>
+        <f>Plan!C34</f>
         <v/>
       </c>
       <c r="D34" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" s="16">
-        <f>Plan!J49</f>
+        <f>Plan!J34</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>Plan!K49</f>
+        <f>Plan!K34</f>
         <v/>
       </c>
       <c r="G34" s="8">
@@ -43318,11 +43369,11 @@
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>Plan!I49</f>
+        <f>Plan!I34</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>Plan!O49</f>
+        <f>Plan!O34</f>
         <v/>
       </c>
     </row>
@@ -43332,22 +43383,22 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C35" s="35">
-        <f>Plan!C30</f>
+        <f>Plan!C49</f>
         <v/>
       </c>
       <c r="D35" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E35" s="16">
-        <f>Plan!J30</f>
+        <f>Plan!J49</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>Plan!K30</f>
+        <f>Plan!K49</f>
         <v/>
       </c>
       <c r="G35" s="8">
@@ -43355,11 +43406,11 @@
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>Plan!I30</f>
+        <f>Plan!I49</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>Plan!O30</f>
+        <f>Plan!O49</f>
         <v/>
       </c>
     </row>
@@ -43369,22 +43420,22 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C36" s="35">
-        <f>Plan!C27</f>
+        <f>Plan!C52</f>
         <v/>
       </c>
       <c r="D36" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E36" s="16">
-        <f>Plan!J27</f>
+        <f>Plan!J52</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>Plan!K27</f>
+        <f>Plan!K52</f>
         <v/>
       </c>
       <c r="G36" s="8">
@@ -43392,11 +43443,11 @@
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>Plan!I27</f>
+        <f>Plan!I52</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>Plan!O27</f>
+        <f>Plan!O52</f>
         <v/>
       </c>
     </row>
@@ -43406,22 +43457,22 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C37" s="35">
-        <f>Plan!C34</f>
+        <f>Plan!C35</f>
         <v/>
       </c>
       <c r="D37" s="8" t="n">
         <v>12</v>
       </c>
       <c r="E37" s="16">
-        <f>Plan!J34</f>
+        <f>Plan!J35</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>Plan!K34</f>
+        <f>Plan!K35</f>
         <v/>
       </c>
       <c r="G37" s="8">
@@ -43429,11 +43480,11 @@
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>Plan!I34</f>
+        <f>Plan!I35</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>Plan!O34</f>
+        <f>Plan!O35</f>
         <v/>
       </c>
     </row>
@@ -43443,22 +43494,22 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C38" s="35">
-        <f>Plan!C26</f>
+        <f>Plan!C27</f>
         <v/>
       </c>
       <c r="D38" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" s="16">
-        <f>Plan!J26</f>
+        <f>Plan!J27</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>Plan!K26</f>
+        <f>Plan!K27</f>
         <v/>
       </c>
       <c r="G38" s="8">
@@ -43466,11 +43517,11 @@
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>Plan!I26</f>
+        <f>Plan!I27</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>Plan!O26</f>
+        <f>Plan!O27</f>
         <v/>
       </c>
     </row>
@@ -43480,22 +43531,22 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="C39" s="35">
-        <f>Plan!C52</f>
+        <f>Plan!C26</f>
         <v/>
       </c>
       <c r="D39" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39" s="16">
-        <f>Plan!J52</f>
+        <f>Plan!J26</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>Plan!K52</f>
+        <f>Plan!K26</f>
         <v/>
       </c>
       <c r="G39" s="8">
@@ -43503,11 +43554,11 @@
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>Plan!I52</f>
+        <f>Plan!I26</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>Plan!O52</f>
+        <f>Plan!O26</f>
         <v/>
       </c>
     </row>
@@ -43554,22 +43605,22 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C41" s="35">
-        <f>Plan!C68</f>
+        <f>Plan!C40</f>
         <v/>
       </c>
       <c r="D41" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E41" s="16">
-        <f>Plan!J68</f>
+        <f>Plan!J40</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>Plan!K68</f>
+        <f>Plan!K40</f>
         <v/>
       </c>
       <c r="G41" s="8">
@@ -43577,11 +43628,11 @@
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>Plan!I68</f>
+        <f>Plan!I40</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>Plan!O68</f>
+        <f>Plan!O40</f>
         <v/>
       </c>
     </row>
@@ -43591,22 +43642,22 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C42" s="35">
-        <f>Plan!C70</f>
+        <f>Plan!C66</f>
         <v/>
       </c>
       <c r="D42" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E42" s="16">
-        <f>Plan!J70</f>
+        <f>Plan!J66</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>Plan!K70</f>
+        <f>Plan!K66</f>
         <v/>
       </c>
       <c r="G42" s="8">
@@ -43614,11 +43665,11 @@
         <v/>
       </c>
       <c r="H42" s="16">
-        <f>Plan!I70</f>
+        <f>Plan!I66</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>Plan!O70</f>
+        <f>Plan!O66</f>
         <v/>
       </c>
     </row>
@@ -43628,22 +43679,22 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="C43" s="35">
-        <f>Plan!C40</f>
+        <f>Plan!C47</f>
         <v/>
       </c>
       <c r="D43" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E43" s="16">
-        <f>Plan!J40</f>
+        <f>Plan!J47</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>Plan!K40</f>
+        <f>Plan!K47</f>
         <v/>
       </c>
       <c r="G43" s="8">
@@ -43651,11 +43702,11 @@
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>Plan!I40</f>
+        <f>Plan!I47</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>Plan!O40</f>
+        <f>Plan!O47</f>
         <v/>
       </c>
     </row>
@@ -43665,22 +43716,22 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C44" s="35">
-        <f>Plan!C66</f>
+        <f>Plan!C29</f>
         <v/>
       </c>
       <c r="D44" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E44" s="16">
-        <f>Plan!J66</f>
+        <f>Plan!J29</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>Plan!K66</f>
+        <f>Plan!K29</f>
         <v/>
       </c>
       <c r="G44" s="8">
@@ -43688,11 +43739,11 @@
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>Plan!I66</f>
+        <f>Plan!I29</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>Plan!O66</f>
+        <f>Plan!O29</f>
         <v/>
       </c>
     </row>
@@ -43702,22 +43753,22 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C45" s="35">
-        <f>Plan!C29</f>
+        <f>Plan!C46</f>
         <v/>
       </c>
       <c r="D45" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E45" s="16">
-        <f>Plan!J29</f>
+        <f>Plan!J46</f>
         <v/>
       </c>
       <c r="F45" s="16">
-        <f>Plan!K29</f>
+        <f>Plan!K46</f>
         <v/>
       </c>
       <c r="G45" s="8">
@@ -43725,11 +43776,11 @@
         <v/>
       </c>
       <c r="H45" s="16">
-        <f>Plan!I29</f>
+        <f>Plan!I46</f>
         <v/>
       </c>
       <c r="I45" s="16">
-        <f>Plan!O29</f>
+        <f>Plan!O46</f>
         <v/>
       </c>
     </row>
@@ -43739,22 +43790,22 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="C46" s="35">
-        <f>Plan!C48</f>
+        <f>Plan!C70</f>
         <v/>
       </c>
       <c r="D46" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" s="16">
-        <f>Plan!J48</f>
+        <f>Plan!J70</f>
         <v/>
       </c>
       <c r="F46" s="16">
-        <f>Plan!K48</f>
+        <f>Plan!K70</f>
         <v/>
       </c>
       <c r="G46" s="8">
@@ -43762,11 +43813,11 @@
         <v/>
       </c>
       <c r="H46" s="16">
-        <f>Plan!I48</f>
+        <f>Plan!I70</f>
         <v/>
       </c>
       <c r="I46" s="16">
-        <f>Plan!O48</f>
+        <f>Plan!O70</f>
         <v/>
       </c>
     </row>
@@ -43776,22 +43827,22 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C47" s="35">
-        <f>Plan!C54</f>
+        <f>Plan!C36</f>
         <v/>
       </c>
       <c r="D47" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E47" s="16">
-        <f>Plan!J54</f>
+        <f>Plan!J36</f>
         <v/>
       </c>
       <c r="F47" s="16">
-        <f>Plan!K54</f>
+        <f>Plan!K36</f>
         <v/>
       </c>
       <c r="G47" s="8">
@@ -43799,11 +43850,11 @@
         <v/>
       </c>
       <c r="H47" s="16">
-        <f>Plan!I54</f>
+        <f>Plan!I36</f>
         <v/>
       </c>
       <c r="I47" s="16">
-        <f>Plan!O54</f>
+        <f>Plan!O36</f>
         <v/>
       </c>
     </row>
@@ -43813,22 +43864,22 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="C48" s="35">
-        <f>Plan!C45</f>
+        <f>Plan!C65</f>
         <v/>
       </c>
       <c r="D48" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E48" s="16">
-        <f>Plan!J45</f>
+        <f>Plan!J65</f>
         <v/>
       </c>
       <c r="F48" s="16">
-        <f>Plan!K45</f>
+        <f>Plan!K65</f>
         <v/>
       </c>
       <c r="G48" s="8">
@@ -43836,11 +43887,11 @@
         <v/>
       </c>
       <c r="H48" s="16">
-        <f>Plan!I45</f>
+        <f>Plan!I65</f>
         <v/>
       </c>
       <c r="I48" s="16">
-        <f>Plan!O45</f>
+        <f>Plan!O65</f>
         <v/>
       </c>
     </row>
@@ -43850,22 +43901,22 @@
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C49" s="35">
-        <f>Plan!C55</f>
+        <f>Plan!C48</f>
         <v/>
       </c>
       <c r="D49" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49" s="16">
-        <f>Plan!J55</f>
+        <f>Plan!J48</f>
         <v/>
       </c>
       <c r="F49" s="16">
-        <f>Plan!K55</f>
+        <f>Plan!K48</f>
         <v/>
       </c>
       <c r="G49" s="8">
@@ -43873,11 +43924,11 @@
         <v/>
       </c>
       <c r="H49" s="16">
-        <f>Plan!I55</f>
+        <f>Plan!I48</f>
         <v/>
       </c>
       <c r="I49" s="16">
-        <f>Plan!O55</f>
+        <f>Plan!O48</f>
         <v/>
       </c>
     </row>
@@ -43887,22 +43938,22 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="C50" s="35">
-        <f>Plan!C25</f>
+        <f>Plan!C54</f>
         <v/>
       </c>
       <c r="D50" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" s="16">
-        <f>Plan!J25</f>
+        <f>Plan!J54</f>
         <v/>
       </c>
       <c r="F50" s="16">
-        <f>Plan!K25</f>
+        <f>Plan!K54</f>
         <v/>
       </c>
       <c r="G50" s="8">
@@ -43910,11 +43961,11 @@
         <v/>
       </c>
       <c r="H50" s="16">
-        <f>Plan!I25</f>
+        <f>Plan!I54</f>
         <v/>
       </c>
       <c r="I50" s="16">
-        <f>Plan!O25</f>
+        <f>Plan!O54</f>
         <v/>
       </c>
     </row>
@@ -43924,22 +43975,22 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C51" s="35">
-        <f>Plan!C51</f>
+        <f>Plan!C45</f>
         <v/>
       </c>
       <c r="D51" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E51" s="16">
-        <f>Plan!J51</f>
+        <f>Plan!J45</f>
         <v/>
       </c>
       <c r="F51" s="16">
-        <f>Plan!K51</f>
+        <f>Plan!K45</f>
         <v/>
       </c>
       <c r="G51" s="8">
@@ -43947,11 +43998,11 @@
         <v/>
       </c>
       <c r="H51" s="16">
-        <f>Plan!I51</f>
+        <f>Plan!I45</f>
         <v/>
       </c>
       <c r="I51" s="16">
-        <f>Plan!O51</f>
+        <f>Plan!O45</f>
         <v/>
       </c>
     </row>
@@ -43961,22 +44012,22 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C52" s="35">
-        <f>Plan!C53</f>
+        <f>Plan!C25</f>
         <v/>
       </c>
       <c r="D52" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E52" s="16">
-        <f>Plan!J53</f>
+        <f>Plan!J25</f>
         <v/>
       </c>
       <c r="F52" s="16">
-        <f>Plan!K53</f>
+        <f>Plan!K25</f>
         <v/>
       </c>
       <c r="G52" s="8">
@@ -43984,11 +44035,11 @@
         <v/>
       </c>
       <c r="H52" s="16">
-        <f>Plan!I53</f>
+        <f>Plan!I25</f>
         <v/>
       </c>
       <c r="I52" s="16">
-        <f>Plan!O53</f>
+        <f>Plan!O25</f>
         <v/>
       </c>
     </row>
@@ -43998,22 +44049,22 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="C53" s="35">
-        <f>Plan!C39</f>
+        <f>Plan!C55</f>
         <v/>
       </c>
       <c r="D53" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E53" s="16">
-        <f>Plan!J39</f>
+        <f>Plan!J55</f>
         <v/>
       </c>
       <c r="F53" s="16">
-        <f>Plan!K39</f>
+        <f>Plan!K55</f>
         <v/>
       </c>
       <c r="G53" s="8">
@@ -44021,11 +44072,11 @@
         <v/>
       </c>
       <c r="H53" s="16">
-        <f>Plan!I39</f>
+        <f>Plan!I55</f>
         <v/>
       </c>
       <c r="I53" s="16">
-        <f>Plan!O39</f>
+        <f>Plan!O55</f>
         <v/>
       </c>
     </row>
@@ -44035,22 +44086,22 @@
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="C54" s="35">
-        <f>Plan!C23</f>
+        <f>Plan!C51</f>
         <v/>
       </c>
       <c r="D54" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E54" s="16">
-        <f>Plan!J23</f>
+        <f>Plan!J51</f>
         <v/>
       </c>
       <c r="F54" s="16">
-        <f>Plan!K23</f>
+        <f>Plan!K51</f>
         <v/>
       </c>
       <c r="G54" s="8">
@@ -44058,11 +44109,11 @@
         <v/>
       </c>
       <c r="H54" s="16">
-        <f>Plan!I23</f>
+        <f>Plan!I51</f>
         <v/>
       </c>
       <c r="I54" s="16">
-        <f>Plan!O23</f>
+        <f>Plan!O51</f>
         <v/>
       </c>
     </row>
@@ -44072,22 +44123,22 @@
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="C55" s="35">
-        <f>Plan!C71</f>
+        <f>Plan!C53</f>
         <v/>
       </c>
       <c r="D55" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E55" s="16">
-        <f>Plan!J71</f>
+        <f>Plan!J53</f>
         <v/>
       </c>
       <c r="F55" s="16">
-        <f>Plan!K71</f>
+        <f>Plan!K53</f>
         <v/>
       </c>
       <c r="G55" s="8">
@@ -44095,11 +44146,11 @@
         <v/>
       </c>
       <c r="H55" s="16">
-        <f>Plan!I71</f>
+        <f>Plan!I53</f>
         <v/>
       </c>
       <c r="I55" s="16">
-        <f>Plan!O71</f>
+        <f>Plan!O53</f>
         <v/>
       </c>
     </row>
@@ -44109,22 +44160,22 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C56" s="35">
-        <f>Plan!C58</f>
+        <f>Plan!C39</f>
         <v/>
       </c>
       <c r="D56" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E56" s="16">
-        <f>Plan!J58</f>
+        <f>Plan!J39</f>
         <v/>
       </c>
       <c r="F56" s="16">
-        <f>Plan!K58</f>
+        <f>Plan!K39</f>
         <v/>
       </c>
       <c r="G56" s="8">
@@ -44132,11 +44183,11 @@
         <v/>
       </c>
       <c r="H56" s="16">
-        <f>Plan!I58</f>
+        <f>Plan!I39</f>
         <v/>
       </c>
       <c r="I56" s="16">
-        <f>Plan!O58</f>
+        <f>Plan!O39</f>
         <v/>
       </c>
     </row>
@@ -44146,22 +44197,22 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="C57" s="35">
-        <f>Plan!C50</f>
+        <f>Plan!C23</f>
         <v/>
       </c>
       <c r="D57" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E57" s="16">
-        <f>Plan!J50</f>
+        <f>Plan!J23</f>
         <v/>
       </c>
       <c r="F57" s="16">
-        <f>Plan!K50</f>
+        <f>Plan!K23</f>
         <v/>
       </c>
       <c r="G57" s="8">
@@ -44169,11 +44220,11 @@
         <v/>
       </c>
       <c r="H57" s="16">
-        <f>Plan!I50</f>
+        <f>Plan!I23</f>
         <v/>
       </c>
       <c r="I57" s="16">
-        <f>Plan!O50</f>
+        <f>Plan!O23</f>
         <v/>
       </c>
     </row>
@@ -44183,22 +44234,22 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="C58" s="35">
-        <f>Plan!C36</f>
+        <f>Plan!C71</f>
         <v/>
       </c>
       <c r="D58" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E58" s="16">
-        <f>Plan!J36</f>
+        <f>Plan!J71</f>
         <v/>
       </c>
       <c r="F58" s="16">
-        <f>Plan!K36</f>
+        <f>Plan!K71</f>
         <v/>
       </c>
       <c r="G58" s="8">
@@ -44206,11 +44257,11 @@
         <v/>
       </c>
       <c r="H58" s="16">
-        <f>Plan!I36</f>
+        <f>Plan!I71</f>
         <v/>
       </c>
       <c r="I58" s="16">
-        <f>Plan!O36</f>
+        <f>Plan!O71</f>
         <v/>
       </c>
     </row>
@@ -44220,22 +44271,22 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C59" s="35">
-        <f>Plan!C60</f>
+        <f>Plan!C58</f>
         <v/>
       </c>
       <c r="D59" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E59" s="16">
-        <f>Plan!J60</f>
+        <f>Plan!J58</f>
         <v/>
       </c>
       <c r="F59" s="16">
-        <f>Plan!K60</f>
+        <f>Plan!K58</f>
         <v/>
       </c>
       <c r="G59" s="8">
@@ -44243,11 +44294,11 @@
         <v/>
       </c>
       <c r="H59" s="16">
-        <f>Plan!I60</f>
+        <f>Plan!I58</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>Plan!O60</f>
+        <f>Plan!O58</f>
         <v/>
       </c>
     </row>
@@ -44294,22 +44345,22 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C61" s="35">
-        <f>Plan!C69</f>
+        <f>Plan!C50</f>
         <v/>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E61" s="16">
-        <f>Plan!J69</f>
+        <f>Plan!J50</f>
         <v/>
       </c>
       <c r="F61" s="16">
-        <f>Plan!K69</f>
+        <f>Plan!K50</f>
         <v/>
       </c>
       <c r="G61" s="8">
@@ -44317,11 +44368,11 @@
         <v/>
       </c>
       <c r="H61" s="16">
-        <f>Plan!I69</f>
+        <f>Plan!I50</f>
         <v/>
       </c>
       <c r="I61" s="16">
-        <f>Plan!O69</f>
+        <f>Plan!O50</f>
         <v/>
       </c>
     </row>
@@ -44331,22 +44382,22 @@
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="C62" s="35">
-        <f>Plan!C62</f>
+        <f>Plan!C72</f>
         <v/>
       </c>
       <c r="D62" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E62" s="16">
-        <f>Plan!J62</f>
+        <f>Plan!J72</f>
         <v/>
       </c>
       <c r="F62" s="16">
-        <f>Plan!K62</f>
+        <f>Plan!K72</f>
         <v/>
       </c>
       <c r="G62" s="8">
@@ -44354,11 +44405,11 @@
         <v/>
       </c>
       <c r="H62" s="16">
-        <f>Plan!I62</f>
+        <f>Plan!I72</f>
         <v/>
       </c>
       <c r="I62" s="16">
-        <f>Plan!O62</f>
+        <f>Plan!O72</f>
         <v/>
       </c>
     </row>
@@ -44368,22 +44419,22 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="C63" s="35">
-        <f>Plan!C73</f>
+        <f>Plan!C60</f>
         <v/>
       </c>
       <c r="D63" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E63" s="16">
-        <f>Plan!J73</f>
+        <f>Plan!J60</f>
         <v/>
       </c>
       <c r="F63" s="16">
-        <f>Plan!K73</f>
+        <f>Plan!K60</f>
         <v/>
       </c>
       <c r="G63" s="8">
@@ -44391,11 +44442,11 @@
         <v/>
       </c>
       <c r="H63" s="16">
-        <f>Plan!I73</f>
+        <f>Plan!I60</f>
         <v/>
       </c>
       <c r="I63" s="16">
-        <f>Plan!O73</f>
+        <f>Plan!O60</f>
         <v/>
       </c>
     </row>
@@ -44442,22 +44493,22 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="C65" s="35">
-        <f>Plan!C47</f>
+        <f>Plan!C69</f>
         <v/>
       </c>
       <c r="D65" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E65" s="16">
-        <f>Plan!J47</f>
+        <f>Plan!J69</f>
         <v/>
       </c>
       <c r="F65" s="16">
-        <f>Plan!K47</f>
+        <f>Plan!K69</f>
         <v/>
       </c>
       <c r="G65" s="8">
@@ -44465,11 +44516,11 @@
         <v/>
       </c>
       <c r="H65" s="16">
-        <f>Plan!I47</f>
+        <f>Plan!I69</f>
         <v/>
       </c>
       <c r="I65" s="16">
-        <f>Plan!O47</f>
+        <f>Plan!O69</f>
         <v/>
       </c>
     </row>
@@ -44479,22 +44530,22 @@
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="C66" s="35">
-        <f>Plan!C57</f>
+        <f>Plan!C62</f>
         <v/>
       </c>
       <c r="D66" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E66" s="16">
-        <f>Plan!J57</f>
+        <f>Plan!J62</f>
         <v/>
       </c>
       <c r="F66" s="16">
-        <f>Plan!K57</f>
+        <f>Plan!K62</f>
         <v/>
       </c>
       <c r="G66" s="8">
@@ -44502,11 +44553,11 @@
         <v/>
       </c>
       <c r="H66" s="16">
-        <f>Plan!I57</f>
+        <f>Plan!I62</f>
         <v/>
       </c>
       <c r="I66" s="16">
-        <f>Plan!O57</f>
+        <f>Plan!O62</f>
         <v/>
       </c>
     </row>
@@ -44516,22 +44567,22 @@
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="C67" s="35">
-        <f>Plan!C46</f>
+        <f>Plan!C73</f>
         <v/>
       </c>
       <c r="D67" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E67" s="16">
-        <f>Plan!J46</f>
+        <f>Plan!J73</f>
         <v/>
       </c>
       <c r="F67" s="16">
-        <f>Plan!K46</f>
+        <f>Plan!K73</f>
         <v/>
       </c>
       <c r="G67" s="8">
@@ -44539,11 +44590,11 @@
         <v/>
       </c>
       <c r="H67" s="16">
-        <f>Plan!I46</f>
+        <f>Plan!I73</f>
         <v/>
       </c>
       <c r="I67" s="16">
-        <f>Plan!O46</f>
+        <f>Plan!O73</f>
         <v/>
       </c>
     </row>
@@ -44553,22 +44604,22 @@
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="C68" s="35">
-        <f>Plan!C63</f>
+        <f>Plan!C56</f>
         <v/>
       </c>
       <c r="D68" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E68" s="16">
-        <f>Plan!J63</f>
+        <f>Plan!J56</f>
         <v/>
       </c>
       <c r="F68" s="16">
-        <f>Plan!K63</f>
+        <f>Plan!K56</f>
         <v/>
       </c>
       <c r="G68" s="8">
@@ -44576,11 +44627,11 @@
         <v/>
       </c>
       <c r="H68" s="16">
-        <f>Plan!I63</f>
+        <f>Plan!I56</f>
         <v/>
       </c>
       <c r="I68" s="16">
-        <f>Plan!O63</f>
+        <f>Plan!O56</f>
         <v/>
       </c>
     </row>
@@ -44627,22 +44678,22 @@
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C70" s="35">
-        <f>Plan!C72</f>
+        <f>Plan!C43</f>
         <v/>
       </c>
       <c r="D70" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E70" s="16">
-        <f>Plan!J72</f>
+        <f>Plan!J43</f>
         <v/>
       </c>
       <c r="F70" s="16">
-        <f>Plan!K72</f>
+        <f>Plan!K43</f>
         <v/>
       </c>
       <c r="G70" s="8">
@@ -44650,11 +44701,11 @@
         <v/>
       </c>
       <c r="H70" s="16">
-        <f>Plan!I72</f>
+        <f>Plan!I43</f>
         <v/>
       </c>
       <c r="I70" s="16">
-        <f>Plan!O72</f>
+        <f>Plan!O43</f>
         <v/>
       </c>
     </row>
@@ -44664,22 +44715,22 @@
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="C71" s="35">
-        <f>Plan!C44</f>
+        <f>Plan!C57</f>
         <v/>
       </c>
       <c r="D71" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" s="16">
-        <f>Plan!J44</f>
+        <f>Plan!J57</f>
         <v/>
       </c>
       <c r="F71" s="16">
-        <f>Plan!K44</f>
+        <f>Plan!K57</f>
         <v/>
       </c>
       <c r="G71" s="8">
@@ -44687,11 +44738,11 @@
         <v/>
       </c>
       <c r="H71" s="16">
-        <f>Plan!I44</f>
+        <f>Plan!I57</f>
         <v/>
       </c>
       <c r="I71" s="16">
-        <f>Plan!O44</f>
+        <f>Plan!O57</f>
         <v/>
       </c>
     </row>
@@ -44738,22 +44789,22 @@
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="C73" s="35">
-        <f>Plan!C43</f>
+        <f>Plan!C64</f>
         <v/>
       </c>
       <c r="D73" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E73" s="16">
-        <f>Plan!J43</f>
+        <f>Plan!J64</f>
         <v/>
       </c>
       <c r="F73" s="16">
-        <f>Plan!K43</f>
+        <f>Plan!K64</f>
         <v/>
       </c>
       <c r="G73" s="8">
@@ -44761,11 +44812,11 @@
         <v/>
       </c>
       <c r="H73" s="16">
-        <f>Plan!I43</f>
+        <f>Plan!I64</f>
         <v/>
       </c>
       <c r="I73" s="16">
-        <f>Plan!O43</f>
+        <f>Plan!O64</f>
         <v/>
       </c>
     </row>
@@ -44775,22 +44826,22 @@
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C74" s="35">
-        <f>Plan!C56</f>
+        <f>Plan!C44</f>
         <v/>
       </c>
       <c r="D74" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E74" s="16">
-        <f>Plan!J56</f>
+        <f>Plan!J44</f>
         <v/>
       </c>
       <c r="F74" s="16">
-        <f>Plan!K56</f>
+        <f>Plan!K44</f>
         <v/>
       </c>
       <c r="G74" s="8">
@@ -44798,11 +44849,11 @@
         <v/>
       </c>
       <c r="H74" s="16">
-        <f>Plan!I56</f>
+        <f>Plan!I44</f>
         <v/>
       </c>
       <c r="I74" s="16">
-        <f>Plan!O56</f>
+        <f>Plan!O44</f>
         <v/>
       </c>
     </row>
@@ -44812,22 +44863,22 @@
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="C75" s="35">
-        <f>Plan!C64</f>
+        <f>Plan!C63</f>
         <v/>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="16">
-        <f>Plan!J64</f>
+        <f>Plan!J63</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>Plan!K64</f>
+        <f>Plan!K63</f>
         <v/>
       </c>
       <c r="G75" s="8">
@@ -44835,11 +44886,11 @@
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>Plan!I64</f>
+        <f>Plan!I63</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>Plan!O64</f>
+        <f>Plan!O63</f>
         <v/>
       </c>
     </row>
@@ -45537,7 +45588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45591,7 +45642,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -45601,51 +45652,51 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
+          <t>Panel del admin C+ en modo oscuro maquetado en código; 4.11 pasa a Hecho</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
+          <t>Maquetó el panel de administración completo en modo oscuro (piezas 2d y 3e–3h): Créditos (menú lateral, 4 KPI con guion donde falta consulta nueva, búsqueda, filtro, lista+ficha, aprobar en 2 pasos, rechazar con motivo obligatorio, nota interna e historial UI), Afiliaciones (lista+ficha, visor de 3 fotos con sus 3 estados, aprobar/rechazar en 2 pasos, WhatsApp deshabilitado por P-95), Asesores y Sorteo con el mismo restyle, y EncabezadoAdmin (patrón de celular) también en /admin/demo. Tokens nuevos en globals.css/tailwind.config.ts. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus (junto con 4.10). Pasa a Hecho en maquetación con 2 frentes abiertos: (1) tests/e2e/k-roles.spec.ts va a fallar porque Aprobar ahora pide un segundo clic «Sí, aprobar» — hace falta que ga-verificador-qa/ga-escritor-tests actualicen ese paso; (2) sin backend nuevo, KPIs completos, tope real desde grados_credito y nota interna/historial reales siguen bloqueados por las 5 migraciones de 1.8 (docs/auditorias/2026-09-25-backend-rediseno-c-plus.md), sin aplicar.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>3.10, 4.10, 4.11</t>
+          <t>4.10; nuevo P-98</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
+          <t>Panel del asesor C+ maquetado en código; 4.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
+          <t>Maquetó /asesor y /asesor/demo siguiendo las piezas 2c/3h del lienzo: EncabezadoAsesor en píldora, tarjetas de resumen con categoría de afiliación, chips de filtro, buscador, tabla de 5 columnas reescrita (sin datos de contacto), estado vacío, transición de lista y barra inferior en celular; agregó el marco ámbar de demostración compartido con /admin/demo y el estado «neutral» a Badge. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus. Documentó como pedido D-06 (docs/diseno/pedidos.md) la falta de regla de diseño para categorizar asociados ya afiliados (no solo solicitudes) en las tarjetas/chips; se registra como decisión provisional de la sesión principal, pendiente de que Sebas la confirme (nuevo pendiente P-98).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -45655,17 +45706,17 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.14; nuevo 6.16</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Tokens y landing del rediseño C+ llevados a código</t>
+          <t>Panel del asociado C+ maquetado en código; 3.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
+          <t>Maquetó /cuenta y /cuenta/solicitar siguiendo las piezas 2b/3d del lienzo: EncabezadoCuenta en píldora flotante, comprobante «Tu solicitud» con sello y pasos animados, insignia de estado con color real, tope con medidor, carné de asociado (institución/activo como props opcionales sin usar, TODO backend), franja del sorteo, barra inferior en celular y deslizador de monto propio en /cuenta/solicitar; agregó enmascararCedula a lib/mascara.ts. tsc, lint, build y 311 pruebas de vitest en verde; no corrió Playwright (requiere Supabase local). Commit local 51da63f en rediseno-c-plus. «Tu camino a la estabilidad» sigue sin renderizarse por P-90 (fecha del primer descuento del embargo solidario); el carné de asociado sigue esperando institución/activo en perfiles (1.8). Falta correr tests/e2e/c-cuenta, h-credito, i-despliegue, j-produccion y k-roles contra Supabase local (ga-verificador-qa).</t>
         </is>
       </c>
     </row>
@@ -45677,22 +45728,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
+          <t>1.7, 2.15</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
+          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
+          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
         </is>
       </c>
     </row>
@@ -45704,22 +45755,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>1.8; P-47, P-90, P-91, P-92</t>
+          <t>3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
+          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
+          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
         </is>
       </c>
     </row>
@@ -45729,24 +45780,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (despliegue PR #2)</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89</t>
+          <t>1.7, 2.14; nuevo 6.16</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
+          <t>Tokens y landing del rediseño C+ llevados a código</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
+          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
         </is>
       </c>
     </row>
@@ -45756,24 +45807,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
+          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
+          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
+          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
         </is>
       </c>
     </row>
@@ -45785,22 +45836,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-13</t>
+          <t>1.8; P-47, P-90, P-91, P-92</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Texto de vigilancia de Supersolidaria confirmado</t>
+          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
+          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
         </is>
       </c>
     </row>
@@ -45810,24 +45861,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-qa</t>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (despliegue PR #2)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>6.3; nuevos P-84, P-86, P-87</t>
+          <t>4.9; P-83, P-84, P-85, P-89</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>QA de producción: con observaciones</t>
+          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
+          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
         </is>
       </c>
     </row>
@@ -45837,24 +45888,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>sesión principal</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>2.12; nuevo P-85</t>
+          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
+          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
+          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
         </is>
       </c>
     </row>
@@ -45866,22 +45917,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>6.2; nuevos P-83, P-88</t>
+          <t>5.3; P-13</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
+          <t>Texto de vigilancia de Supersolidaria confirmado</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
+          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
         </is>
       </c>
     </row>
@@ -45891,24 +45942,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
+          <t>6.3; nuevos P-84, P-86, P-87</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
+          <t>QA de producción: con observaciones</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
+          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
         </is>
       </c>
     </row>
@@ -45918,105 +45969,105 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>6.9, 6.13; P-44, P-59, P-61</t>
+          <t>2.12; nuevo P-85</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
+          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
+          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
+          <t>6.2; nuevos P-83, P-88</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
+          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
+          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Sebas (acuerdo con Carlos Pardo)</t>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
+          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
+          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
+          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>6.1, P-58</t>
+          <t>6.9, 6.13; P-44, P-59, P-61</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
+          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
+          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
         </is>
       </c>
     </row>
@@ -46028,22 +46079,22 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Sebas (coordinación con la cooperativa)</t>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
+          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
+          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
+          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
         </is>
       </c>
     </row>
@@ -46053,24 +46104,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (acuerdo con Carlos Pardo)</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
+          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
+          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
+          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
         </is>
       </c>
     </row>
@@ -46082,22 +46133,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1, P-58</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
+          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
+          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
         </is>
       </c>
     </row>
@@ -46107,24 +46158,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>ga-auditor-supabase</t>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (coordinación con la cooperativa)</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
+          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
+          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
         </is>
       </c>
     </row>
@@ -46141,17 +46192,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Sorteo mensual en /cuenta</t>
+          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
+          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
         </is>
       </c>
     </row>
@@ -46163,22 +46214,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>4.6; P-57</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
+          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
+          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
         </is>
       </c>
     </row>
@@ -46195,98 +46246,98 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>1.5; P-63</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
+          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
+          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
+          <t>Sorteo mensual en /cuenta</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
+          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive + ga-verificador-qa</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>6.3; P-39</t>
+          <t>4.6; P-57</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
+          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
+          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 5.8; P-39, P-53</t>
+          <t>1.5; P-63</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
+          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
+          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
         </is>
       </c>
     </row>
@@ -46296,24 +46347,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
+          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
+          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
         </is>
       </c>
     </row>
@@ -46323,24 +46374,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>ga-diseno-a-codigo</t>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>ga-verificador-responsive + ga-verificador-qa</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>5.2, 5.8, 6.3</t>
+          <t>6.3; P-39</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
+          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
+          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
         </is>
       </c>
     </row>
@@ -46357,17 +46408,17 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
+          <t>6.3, 5.2, 5.8; P-39, P-53</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
+          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
+          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
         </is>
       </c>
     </row>
@@ -46379,22 +46430,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>2.1, 5.3, 5.7; P-16, P-52</t>
+          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
+          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
+          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
         </is>
       </c>
     </row>
@@ -46406,22 +46457,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
+          <t>5.2, 5.8, 6.3</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
+          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
+          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
         </is>
       </c>
     </row>
@@ -46431,24 +46482,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
+          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
+          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
+          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
         </is>
       </c>
     </row>
@@ -46460,22 +46511,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.1, 5.3, 5.7; P-16, P-52</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Agente ga-auditor-supabase corregido</t>
+          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
         </is>
       </c>
     </row>
@@ -46485,24 +46536,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>3.1, 6.5, 6.10; P-09</t>
+          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
         </is>
       </c>
     </row>
@@ -46512,24 +46563,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
         </is>
       </c>
     </row>
@@ -46539,24 +46590,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-funcionalidad-botones</t>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+          <t>Agente ga-auditor-supabase corregido</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
         </is>
       </c>
     </row>
@@ -46566,24 +46617,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-qa</t>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+          <t>3.1, 6.5, 6.10; P-09</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
         </is>
       </c>
     </row>
@@ -46595,22 +46646,22 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
         </is>
       </c>
     </row>
@@ -46620,22 +46671,103 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>ga-verificador-qa</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Claude (sesión principal)</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Todas</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Creación del Excel de avances</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Pendientes desde PENDIENTES.md, plan desde la propuesta (6 fases, 8 semanas) reorganizado en 2 filas con cola infinita y pesos 1–5.</t>
         </is>

--- a/docs/avances/Avances_Green_Alliance.xlsx
+++ b/docs/avances/Avances_Green_Alliance.xlsx
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -7516,19 +7516,19 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>3.3, 2.10, 2.8, 6.4</t>
+          <t>4.2, 2.9</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J9" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="L9" s="8">
         <f>K9+E9</f>
@@ -7594,19 +7594,19 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>1.7, 3.7</t>
+          <t>2.12, 5.5, 3.9</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L10" s="8">
         <f>K10+E10</f>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
@@ -7684,7 +7684,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L11" s="8">
         <f>K11+E11</f>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>6.17, 6.12</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I12" s="18" t="inlineStr">
@@ -7759,10 +7759,10 @@
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L12" s="8">
         <f>K12+E12</f>
@@ -7828,19 +7828,19 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.5, 3.3</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J13" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L13" s="8">
         <f>K13+E13</f>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.6, 2.7</t>
         </is>
       </c>
       <c r="I15" s="18" t="inlineStr">
@@ -7996,7 +7996,7 @@
         <v>6</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L15" s="8">
         <f>K15+E15</f>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4, 3.1</t>
         </is>
       </c>
       <c r="I17" s="18" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>3.1, 3.4</t>
+          <t>3.1, 2.3</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>3.4, 6.10</t>
+          <t>2.3, 6.10</t>
         </is>
       </c>
       <c r="I19" s="18" t="inlineStr">
@@ -8374,19 +8374,19 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I20" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J20" s="8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="L20" s="8">
         <f>K20+E20</f>
@@ -8452,19 +8452,19 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>4.1, 4.2</t>
+          <t>1.5, 3.6</t>
         </is>
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L21" s="8">
         <f>K21+E21</f>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I22" s="18" t="inlineStr">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="J22" s="8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L22" s="8">
         <f>K22+E22</f>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I23" s="18" t="inlineStr">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="J23" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L23" s="8">
         <f>K23+E23</f>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.7, 1.7, 1.6</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="J24" s="8" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L24" s="8">
         <f>K24+E24</f>
@@ -8764,19 +8764,19 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L25" s="8">
         <f>K25+E25</f>
@@ -8842,19 +8842,19 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3.10, 6.13, 5.1</t>
+          <t>6.13, 2.8, 4.10</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L26" s="8">
         <f>K26+E26</f>
@@ -8920,19 +8920,19 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>5.5, 4.6</t>
+          <t>5.1, 4.4</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L27" s="8">
         <f>K27+E27</f>
@@ -9010,7 +9010,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L28" s="8">
         <f>K28+E28</f>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>4.4, 6.9</t>
+          <t>6.17, 4.9</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L29" s="8">
         <f>K29+E29</f>
@@ -9154,19 +9154,19 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>5.2, 1.5</t>
+          <t>2.1, 4.6</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L30" s="8">
         <f>K30+E30</f>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>2.6, 2.7</t>
+          <t>2.2, 2.5</t>
         </is>
       </c>
       <c r="I31" s="18" t="inlineStr">
@@ -9244,7 +9244,7 @@
         <v>6</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L31" s="8">
         <f>K31+E31</f>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="I32" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J32" s="8" t="n">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I33" s="18" t="inlineStr">
@@ -9400,7 +9400,7 @@
         <v>19</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L33" s="8">
         <f>K33+E33</f>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>1.6, 6.8, 6.11</t>
+          <t>5.2, 2.12</t>
         </is>
       </c>
       <c r="I34" s="18" t="inlineStr">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="J34" s="8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L34" s="8">
         <f>K34+E34</f>
@@ -9544,19 +9544,19 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.6, 4.11</t>
         </is>
       </c>
       <c r="I35" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J35" s="8" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L35" s="8">
         <f>K35+E35</f>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>4.6, 2.14</t>
+          <t>5.7, 6.16, 6.9</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="L36" s="8">
         <f>K36+E36</f>
@@ -9700,12 +9700,12 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>3.5, 2.9</t>
+          <t>3.5, 6.4</t>
         </is>
       </c>
       <c r="I37" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J37" s="8" t="n">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I38" s="18" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.6, 6.12</t>
         </is>
       </c>
       <c r="I39" s="18" t="inlineStr">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="J39" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L39" s="8">
         <f>K39+E39</f>
@@ -9934,19 +9934,19 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>5.7, 3.2</t>
+          <t>2.15, 6.19, 6.11, 5.7</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J40" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L40" s="8">
         <f>K40+E40</f>
@@ -10016,19 +10016,19 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.10, 2.1</t>
         </is>
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J41" s="8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L41" s="8">
         <f>K41+E41</f>
@@ -10094,19 +10094,19 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>2.15, 3.10</t>
+          <t>3.3, 5.2</t>
         </is>
       </c>
       <c r="I42" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="L42" s="8">
         <f>K42+E42</f>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>6.6, 6.17</t>
+          <t>5.9, 6.15, 6.7</t>
         </is>
       </c>
       <c r="I43" s="18" t="inlineStr">
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="J43" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L43" s="8">
         <f>K43+E43</f>
@@ -10250,19 +10250,19 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.6, 5.9</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J44" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L44" s="8">
         <f>K44+E44</f>
@@ -10328,19 +10328,19 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J45" s="8" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L45" s="8">
         <f>K45+E45</f>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I46" s="18" t="inlineStr">
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="J46" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="K46" s="8" t="n">
         <v>47</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>57</v>
       </c>
       <c r="L46" s="8">
         <f>K46+E46</f>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>4.10, 5.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I47" s="18" t="inlineStr">
@@ -10493,10 +10493,10 @@
         </is>
       </c>
       <c r="J47" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="L47" s="8">
         <f>K47+E47</f>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>2.14, 6.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr">
@@ -10571,10 +10571,10 @@
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L48" s="8">
         <f>K48+E48</f>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>3.6, 3.3</t>
+          <t>4.6, 3.7</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="J49" s="8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L49" s="8">
         <f>K49+E49</f>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.1, 6.18</t>
         </is>
       </c>
       <c r="I50" s="18" t="inlineStr">
@@ -10727,10 +10727,10 @@
         </is>
       </c>
       <c r="J50" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L50" s="8">
         <f>K50+E50</f>
@@ -10800,19 +10800,19 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J51" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L51" s="8">
         <f>K51+E51</f>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I52" s="18" t="inlineStr">
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="J52" s="8" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L52" s="8">
         <f>K52+E52</f>
@@ -10960,19 +10960,19 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I53" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J53" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L53" s="8">
         <f>K53+E53</f>
@@ -11038,19 +11038,19 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.4, 3.10</t>
         </is>
       </c>
       <c r="I54" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J54" s="8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L54" s="8">
         <f>K54+E54</f>
@@ -11116,19 +11116,19 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J55" s="8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L55" s="8">
         <f>K55+E55</f>
@@ -11194,19 +11194,19 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>6.18, 4.8</t>
+          <t>4.8, 4.7</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J56" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L56" s="8">
         <f>K56+E56</f>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>6.3, 6.14</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="I57" s="18" t="inlineStr">
@@ -11281,10 +11281,10 @@
         </is>
       </c>
       <c r="J57" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L57" s="8">
         <f>K57+E57</f>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>5.4, 6.19, 6.2</t>
+          <t>6.2, 5.3</t>
         </is>
       </c>
       <c r="I58" s="18" t="inlineStr">
@@ -11359,10 +11359,10 @@
         </is>
       </c>
       <c r="J58" s="8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L58" s="8">
         <f>K58+E58</f>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>6.1, 6.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I59" s="18" t="inlineStr">
@@ -11437,7 +11437,7 @@
         </is>
       </c>
       <c r="J59" s="8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K59" s="8" t="n">
         <v>67</v>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>6.2, 6.15, 5.10</t>
+          <t>1.8, 6.14</t>
         </is>
       </c>
       <c r="I60" s="18" t="inlineStr">
@@ -11515,10 +11515,10 @@
         </is>
       </c>
       <c r="J60" s="8" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L60" s="8">
         <f>K60+E60</f>
@@ -11584,19 +11584,19 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I61" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="L61" s="8">
         <f>K61+E61</f>
@@ -11671,10 +11671,10 @@
         </is>
       </c>
       <c r="J62" s="8" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L62" s="8">
         <f>K62+E62</f>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>6.7, 4.7</t>
+          <t>5.10, 4.8</t>
         </is>
       </c>
       <c r="I63" s="18" t="inlineStr">
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="J63" s="8" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L63" s="8">
         <f>K63+E63</f>
@@ -11818,19 +11818,19 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I64" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="L64" s="8">
         <f>K64+E64</f>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="I65" s="18" t="inlineStr">
@@ -11905,10 +11905,10 @@
         </is>
       </c>
       <c r="J65" s="8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="L65" s="8">
         <f>K65+E65</f>
@@ -11974,7 +11974,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I66" s="18" t="inlineStr">
@@ -11983,10 +11983,10 @@
         </is>
       </c>
       <c r="J66" s="8" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L66" s="8">
         <f>K66+E66</f>
@@ -12061,7 +12061,7 @@
         </is>
       </c>
       <c r="J67" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K67" s="8" t="n">
         <v>15</v>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I68" s="18" t="inlineStr">
@@ -12139,10 +12139,10 @@
         </is>
       </c>
       <c r="J68" s="8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L68" s="8">
         <f>K68+E68</f>
@@ -12208,19 +12208,19 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J69" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="L69" s="8">
         <f>K69+E69</f>
@@ -12291,14 +12291,14 @@
       </c>
       <c r="I70" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J70" s="8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L70" s="8">
         <f>K70+E70</f>
@@ -12364,19 +12364,19 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I71" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J71" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L71" s="8">
         <f>K71+E71</f>
@@ -12442,19 +12442,19 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I72" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J72" s="8" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="L72" s="8">
         <f>K72+E72</f>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I73" s="18" t="inlineStr">
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="J73" s="8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L73" s="8">
         <f>K73+E73</f>
@@ -12598,19 +12598,19 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I74" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J74" s="8" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="L74" s="8">
         <f>K74+E74</f>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="O74" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P74" s="8" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>4.7, 1.8</t>
+          <t>2.13, 3.2</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr">
@@ -12685,10 +12685,10 @@
         </is>
       </c>
       <c r="J75" s="8" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="L75" s="8">
         <f>K75+E75</f>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="O75" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P75" s="8" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>6.17, 1.8</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I76" s="18" t="inlineStr">
@@ -12763,10 +12763,10 @@
         </is>
       </c>
       <c r="J76" s="8" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="L76" s="8">
         <f>K76+E76</f>
@@ -43218,22 +43218,22 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C11" s="35">
-        <f>Plan!C15</f>
+        <f>Plan!C31</f>
         <v/>
       </c>
       <c r="D11" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" s="16">
-        <f>Plan!J15</f>
+        <f>Plan!J31</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>Plan!K15</f>
+        <f>Plan!K31</f>
         <v/>
       </c>
       <c r="G11" s="8">
@@ -43241,11 +43241,11 @@
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>Plan!I15</f>
+        <f>Plan!I31</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>Plan!O15</f>
+        <f>Plan!O31</f>
         <v/>
       </c>
     </row>
@@ -43366,22 +43366,22 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C15" s="35">
-        <f>Plan!C31</f>
+        <f>Plan!C15</f>
         <v/>
       </c>
       <c r="D15" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E15" s="16">
-        <f>Plan!J31</f>
+        <f>Plan!J15</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>Plan!K31</f>
+        <f>Plan!K15</f>
         <v/>
       </c>
       <c r="G15" s="8">
@@ -43389,11 +43389,11 @@
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>Plan!I31</f>
+        <f>Plan!I15</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>Plan!O31</f>
+        <f>Plan!O15</f>
         <v/>
       </c>
     </row>
@@ -43551,22 +43551,22 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="C20" s="35">
-        <f>Plan!C21</f>
+        <f>Plan!C61</f>
         <v/>
       </c>
       <c r="D20" s="8" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E20" s="16">
-        <f>Plan!J21</f>
+        <f>Plan!J61</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>Plan!K21</f>
+        <f>Plan!K61</f>
         <v/>
       </c>
       <c r="G20" s="8">
@@ -43574,11 +43574,11 @@
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>Plan!I21</f>
+        <f>Plan!I61</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>Plan!O21</f>
+        <f>Plan!O61</f>
         <v/>
       </c>
     </row>
@@ -43588,22 +43588,22 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C21" s="35">
-        <f>Plan!C38</f>
+        <f>Plan!C9</f>
         <v/>
       </c>
       <c r="D21" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" s="16">
-        <f>Plan!J38</f>
+        <f>Plan!J9</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>Plan!K38</f>
+        <f>Plan!K9</f>
         <v/>
       </c>
       <c r="G21" s="8">
@@ -43611,11 +43611,11 @@
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>Plan!I38</f>
+        <f>Plan!I9</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>Plan!O38</f>
+        <f>Plan!O9</f>
         <v/>
       </c>
     </row>
@@ -43625,22 +43625,22 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C22" s="35">
-        <f>Plan!C13</f>
+        <f>Plan!C38</f>
         <v/>
       </c>
       <c r="D22" s="8" t="n">
         <v>16</v>
       </c>
       <c r="E22" s="16">
-        <f>Plan!J13</f>
+        <f>Plan!J38</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>Plan!K13</f>
+        <f>Plan!K38</f>
         <v/>
       </c>
       <c r="G22" s="8">
@@ -43648,11 +43648,11 @@
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>Plan!I13</f>
+        <f>Plan!I38</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>Plan!O13</f>
+        <f>Plan!O38</f>
         <v/>
       </c>
     </row>
@@ -43662,22 +43662,22 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="C23" s="35">
-        <f>Plan!C41</f>
+        <f>Plan!C21</f>
         <v/>
       </c>
       <c r="D23" s="8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E23" s="16">
-        <f>Plan!J41</f>
+        <f>Plan!J21</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>Plan!K41</f>
+        <f>Plan!K21</f>
         <v/>
       </c>
       <c r="G23" s="8">
@@ -43685,11 +43685,11 @@
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>Plan!I41</f>
+        <f>Plan!I21</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>Plan!O41</f>
+        <f>Plan!O21</f>
         <v/>
       </c>
     </row>
@@ -43736,22 +43736,22 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C25" s="35">
-        <f>Plan!C49</f>
+        <f>Plan!C41</f>
         <v/>
       </c>
       <c r="D25" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="16">
-        <f>Plan!J49</f>
+        <f>Plan!J41</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>Plan!K49</f>
+        <f>Plan!K41</f>
         <v/>
       </c>
       <c r="G25" s="8">
@@ -43759,11 +43759,11 @@
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>Plan!I49</f>
+        <f>Plan!I41</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>Plan!O49</f>
+        <f>Plan!O41</f>
         <v/>
       </c>
     </row>
@@ -43773,22 +43773,22 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C26" s="35">
-        <f>Plan!C30</f>
+        <f>Plan!C22</f>
         <v/>
       </c>
       <c r="D26" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E26" s="16">
-        <f>Plan!J30</f>
+        <f>Plan!J22</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>Plan!K30</f>
+        <f>Plan!K22</f>
         <v/>
       </c>
       <c r="G26" s="8">
@@ -43796,11 +43796,11 @@
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>Plan!I30</f>
+        <f>Plan!I22</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>Plan!O30</f>
+        <f>Plan!O22</f>
         <v/>
       </c>
     </row>
@@ -43810,22 +43810,22 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C27" s="35">
-        <f>Plan!C9</f>
+        <f>Plan!C13</f>
         <v/>
       </c>
       <c r="D27" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" s="16">
-        <f>Plan!J9</f>
+        <f>Plan!J13</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>Plan!K9</f>
+        <f>Plan!K13</f>
         <v/>
       </c>
       <c r="G27" s="8">
@@ -43833,11 +43833,11 @@
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>Plan!I9</f>
+        <f>Plan!I13</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>Plan!O9</f>
+        <f>Plan!O13</f>
         <v/>
       </c>
     </row>
@@ -43847,22 +43847,22 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C28" s="35">
-        <f>Plan!C22</f>
+        <f>Plan!C30</f>
         <v/>
       </c>
       <c r="D28" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E28" s="16">
-        <f>Plan!J22</f>
+        <f>Plan!J30</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>Plan!K22</f>
+        <f>Plan!K30</f>
         <v/>
       </c>
       <c r="G28" s="8">
@@ -43870,11 +43870,11 @@
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>Plan!I22</f>
+        <f>Plan!I30</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>Plan!O22</f>
+        <f>Plan!O30</f>
         <v/>
       </c>
     </row>
@@ -43884,22 +43884,22 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C29" s="35">
-        <f>Plan!C20</f>
+        <f>Plan!C42</f>
         <v/>
       </c>
       <c r="D29" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E29" s="16">
-        <f>Plan!J20</f>
+        <f>Plan!J42</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>Plan!K20</f>
+        <f>Plan!K42</f>
         <v/>
       </c>
       <c r="G29" s="8">
@@ -43907,11 +43907,11 @@
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>Plan!I20</f>
+        <f>Plan!I42</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>Plan!O20</f>
+        <f>Plan!O42</f>
         <v/>
       </c>
     </row>
@@ -43921,22 +43921,22 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C30" s="35">
-        <f>Plan!C61</f>
+        <f>Plan!C49</f>
         <v/>
       </c>
       <c r="D30" s="8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E30" s="16">
-        <f>Plan!J61</f>
+        <f>Plan!J49</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>Plan!K61</f>
+        <f>Plan!K49</f>
         <v/>
       </c>
       <c r="G30" s="8">
@@ -43944,11 +43944,11 @@
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>Plan!I61</f>
+        <f>Plan!I49</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>Plan!O61</f>
+        <f>Plan!O49</f>
         <v/>
       </c>
     </row>
@@ -43958,22 +43958,22 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="C31" s="35">
-        <f>Plan!C24</f>
+        <f>Plan!C34</f>
         <v/>
       </c>
       <c r="D31" s="8" t="n">
         <v>12</v>
       </c>
       <c r="E31" s="16">
-        <f>Plan!J24</f>
+        <f>Plan!J34</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>Plan!K24</f>
+        <f>Plan!K34</f>
         <v/>
       </c>
       <c r="G31" s="8">
@@ -43981,11 +43981,11 @@
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>Plan!I24</f>
+        <f>Plan!I34</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>Plan!O24</f>
+        <f>Plan!O34</f>
         <v/>
       </c>
     </row>
@@ -43995,22 +43995,22 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="C32" s="35">
-        <f>Plan!C35</f>
+        <f>Plan!C24</f>
         <v/>
       </c>
       <c r="D32" s="8" t="n">
         <v>12</v>
       </c>
       <c r="E32" s="16">
-        <f>Plan!J35</f>
+        <f>Plan!J24</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>Plan!K35</f>
+        <f>Plan!K24</f>
         <v/>
       </c>
       <c r="G32" s="8">
@@ -44018,11 +44018,11 @@
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>Plan!I35</f>
+        <f>Plan!I24</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>Plan!O35</f>
+        <f>Plan!O24</f>
         <v/>
       </c>
     </row>
@@ -44032,22 +44032,22 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C33" s="35">
-        <f>Plan!C10</f>
+        <f>Plan!C11</f>
         <v/>
       </c>
       <c r="D33" s="8" t="n">
         <v>11</v>
       </c>
       <c r="E33" s="16">
-        <f>Plan!J10</f>
+        <f>Plan!J11</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>Plan!K10</f>
+        <f>Plan!K11</f>
         <v/>
       </c>
       <c r="G33" s="8">
@@ -44055,11 +44055,11 @@
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>Plan!I10</f>
+        <f>Plan!I11</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>Plan!O10</f>
+        <f>Plan!O11</f>
         <v/>
       </c>
     </row>
@@ -44069,22 +44069,22 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C34" s="35">
-        <f>Plan!C11</f>
+        <f>Plan!C10</f>
         <v/>
       </c>
       <c r="D34" s="8" t="n">
         <v>11</v>
       </c>
       <c r="E34" s="16">
-        <f>Plan!J11</f>
+        <f>Plan!J10</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>Plan!K11</f>
+        <f>Plan!K10</f>
         <v/>
       </c>
       <c r="G34" s="8">
@@ -44092,11 +44092,11 @@
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>Plan!I11</f>
+        <f>Plan!I10</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>Plan!O11</f>
+        <f>Plan!O10</f>
         <v/>
       </c>
     </row>
@@ -44106,22 +44106,22 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C35" s="35">
-        <f>Plan!C34</f>
+        <f>Plan!C52</f>
         <v/>
       </c>
       <c r="D35" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E35" s="16">
-        <f>Plan!J34</f>
+        <f>Plan!J52</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>Plan!K34</f>
+        <f>Plan!K52</f>
         <v/>
       </c>
       <c r="G35" s="8">
@@ -44129,11 +44129,11 @@
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>Plan!I34</f>
+        <f>Plan!I52</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>Plan!O34</f>
+        <f>Plan!O52</f>
         <v/>
       </c>
     </row>
@@ -44143,22 +44143,22 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C36" s="35">
-        <f>Plan!C65</f>
+        <f>Plan!C35</f>
         <v/>
       </c>
       <c r="D36" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E36" s="16">
-        <f>Plan!J65</f>
+        <f>Plan!J35</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>Plan!K65</f>
+        <f>Plan!K35</f>
         <v/>
       </c>
       <c r="G36" s="8">
@@ -44166,11 +44166,11 @@
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>Plan!I65</f>
+        <f>Plan!I35</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>Plan!O65</f>
+        <f>Plan!O35</f>
         <v/>
       </c>
     </row>
@@ -44180,22 +44180,22 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="C37" s="35">
-        <f>Plan!C68</f>
+        <f>Plan!C47</f>
         <v/>
       </c>
       <c r="D37" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E37" s="16">
-        <f>Plan!J68</f>
+        <f>Plan!J47</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>Plan!K68</f>
+        <f>Plan!K47</f>
         <v/>
       </c>
       <c r="G37" s="8">
@@ -44203,11 +44203,11 @@
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>Plan!I68</f>
+        <f>Plan!I47</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>Plan!O68</f>
+        <f>Plan!O47</f>
         <v/>
       </c>
     </row>
@@ -44217,22 +44217,22 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="C38" s="35">
-        <f>Plan!C52</f>
+        <f>Plan!C26</f>
         <v/>
       </c>
       <c r="D38" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E38" s="16">
-        <f>Plan!J52</f>
+        <f>Plan!J26</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>Plan!K52</f>
+        <f>Plan!K26</f>
         <v/>
       </c>
       <c r="G38" s="8">
@@ -44240,11 +44240,11 @@
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>Plan!I52</f>
+        <f>Plan!I26</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>Plan!O52</f>
+        <f>Plan!O26</f>
         <v/>
       </c>
     </row>
@@ -44254,22 +44254,22 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="C39" s="35">
-        <f>Plan!C27</f>
+        <f>Plan!C70</f>
         <v/>
       </c>
       <c r="D39" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E39" s="16">
-        <f>Plan!J27</f>
+        <f>Plan!J70</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>Plan!K27</f>
+        <f>Plan!K70</f>
         <v/>
       </c>
       <c r="G39" s="8">
@@ -44277,11 +44277,11 @@
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>Plan!I27</f>
+        <f>Plan!I70</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>Plan!O27</f>
+        <f>Plan!O70</f>
         <v/>
       </c>
     </row>
@@ -44291,22 +44291,22 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C40" s="35">
-        <f>Plan!C42</f>
+        <f>Plan!C20</f>
         <v/>
       </c>
       <c r="D40" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E40" s="16">
-        <f>Plan!J42</f>
+        <f>Plan!J20</f>
         <v/>
       </c>
       <c r="F40" s="16">
-        <f>Plan!K42</f>
+        <f>Plan!K20</f>
         <v/>
       </c>
       <c r="G40" s="8">
@@ -44314,11 +44314,11 @@
         <v/>
       </c>
       <c r="H40" s="16">
-        <f>Plan!I42</f>
+        <f>Plan!I20</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>Plan!O42</f>
+        <f>Plan!O20</f>
         <v/>
       </c>
     </row>
@@ -44328,22 +44328,22 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C41" s="35">
-        <f>Plan!C36</f>
+        <f>Plan!C46</f>
         <v/>
       </c>
       <c r="D41" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="16">
-        <f>Plan!J36</f>
+        <f>Plan!J46</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>Plan!K36</f>
+        <f>Plan!K46</f>
         <v/>
       </c>
       <c r="G41" s="8">
@@ -44351,11 +44351,11 @@
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>Plan!I36</f>
+        <f>Plan!I46</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>Plan!O36</f>
+        <f>Plan!O46</f>
         <v/>
       </c>
     </row>
@@ -44365,22 +44365,22 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C42" s="35">
-        <f>Plan!C26</f>
+        <f>Plan!C27</f>
         <v/>
       </c>
       <c r="D42" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E42" s="16">
-        <f>Plan!J26</f>
+        <f>Plan!J27</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>Plan!K26</f>
+        <f>Plan!K27</f>
         <v/>
       </c>
       <c r="G42" s="8">
@@ -44388,11 +44388,11 @@
         <v/>
       </c>
       <c r="H42" s="16">
-        <f>Plan!I26</f>
+        <f>Plan!I27</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>Plan!O26</f>
+        <f>Plan!O27</f>
         <v/>
       </c>
     </row>
@@ -44402,22 +44402,22 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C43" s="35">
-        <f>Plan!C70</f>
+        <f>Plan!C48</f>
         <v/>
       </c>
       <c r="D43" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" s="16">
-        <f>Plan!J70</f>
+        <f>Plan!J48</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>Plan!K70</f>
+        <f>Plan!K48</f>
         <v/>
       </c>
       <c r="G43" s="8">
@@ -44425,11 +44425,11 @@
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>Plan!I70</f>
+        <f>Plan!I48</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>Plan!O70</f>
+        <f>Plan!O48</f>
         <v/>
       </c>
     </row>
@@ -44439,22 +44439,22 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C44" s="35">
-        <f>Plan!C48</f>
+        <f>Plan!C40</f>
         <v/>
       </c>
       <c r="D44" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E44" s="16">
-        <f>Plan!J48</f>
+        <f>Plan!J40</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>Plan!K48</f>
+        <f>Plan!K40</f>
         <v/>
       </c>
       <c r="G44" s="8">
@@ -44462,11 +44462,11 @@
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>Plan!I48</f>
+        <f>Plan!I40</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>Plan!O48</f>
+        <f>Plan!O40</f>
         <v/>
       </c>
     </row>
@@ -44476,22 +44476,22 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="C45" s="35">
-        <f>Plan!C73</f>
+        <f>Plan!C74</f>
         <v/>
       </c>
       <c r="D45" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E45" s="16">
-        <f>Plan!J73</f>
+        <f>Plan!J74</f>
         <v/>
       </c>
       <c r="F45" s="16">
-        <f>Plan!K73</f>
+        <f>Plan!K74</f>
         <v/>
       </c>
       <c r="G45" s="8">
@@ -44499,11 +44499,11 @@
         <v/>
       </c>
       <c r="H45" s="16">
-        <f>Plan!I73</f>
+        <f>Plan!I74</f>
         <v/>
       </c>
       <c r="I45" s="16">
-        <f>Plan!O73</f>
+        <f>Plan!O74</f>
         <v/>
       </c>
     </row>
@@ -44513,22 +44513,22 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="C46" s="35">
-        <f>Plan!C40</f>
+        <f>Plan!C68</f>
         <v/>
       </c>
       <c r="D46" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E46" s="16">
-        <f>Plan!J40</f>
+        <f>Plan!J68</f>
         <v/>
       </c>
       <c r="F46" s="16">
-        <f>Plan!K40</f>
+        <f>Plan!K68</f>
         <v/>
       </c>
       <c r="G46" s="8">
@@ -44536,11 +44536,11 @@
         <v/>
       </c>
       <c r="H46" s="16">
-        <f>Plan!I40</f>
+        <f>Plan!I68</f>
         <v/>
       </c>
       <c r="I46" s="16">
-        <f>Plan!O40</f>
+        <f>Plan!O68</f>
         <v/>
       </c>
     </row>
@@ -44587,22 +44587,22 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C48" s="35">
-        <f>Plan!C29</f>
+        <f>Plan!C36</f>
         <v/>
       </c>
       <c r="D48" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E48" s="16">
-        <f>Plan!J29</f>
+        <f>Plan!J36</f>
         <v/>
       </c>
       <c r="F48" s="16">
-        <f>Plan!K29</f>
+        <f>Plan!K36</f>
         <v/>
       </c>
       <c r="G48" s="8">
@@ -44610,11 +44610,11 @@
         <v/>
       </c>
       <c r="H48" s="16">
-        <f>Plan!I29</f>
+        <f>Plan!I36</f>
         <v/>
       </c>
       <c r="I48" s="16">
-        <f>Plan!O29</f>
+        <f>Plan!O36</f>
         <v/>
       </c>
     </row>
@@ -44624,22 +44624,22 @@
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="C49" s="35">
-        <f>Plan!C66</f>
+        <f>Plan!C73</f>
         <v/>
       </c>
       <c r="D49" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49" s="16">
-        <f>Plan!J66</f>
+        <f>Plan!J73</f>
         <v/>
       </c>
       <c r="F49" s="16">
-        <f>Plan!K66</f>
+        <f>Plan!K73</f>
         <v/>
       </c>
       <c r="G49" s="8">
@@ -44647,11 +44647,11 @@
         <v/>
       </c>
       <c r="H49" s="16">
-        <f>Plan!I66</f>
+        <f>Plan!I73</f>
         <v/>
       </c>
       <c r="I49" s="16">
-        <f>Plan!O66</f>
+        <f>Plan!O73</f>
         <v/>
       </c>
     </row>
@@ -44661,22 +44661,22 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C50" s="35">
-        <f>Plan!C47</f>
+        <f>Plan!C66</f>
         <v/>
       </c>
       <c r="D50" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E50" s="16">
-        <f>Plan!J47</f>
+        <f>Plan!J66</f>
         <v/>
       </c>
       <c r="F50" s="16">
-        <f>Plan!K47</f>
+        <f>Plan!K66</f>
         <v/>
       </c>
       <c r="G50" s="8">
@@ -44684,11 +44684,11 @@
         <v/>
       </c>
       <c r="H50" s="16">
-        <f>Plan!I47</f>
+        <f>Plan!I66</f>
         <v/>
       </c>
       <c r="I50" s="16">
-        <f>Plan!O47</f>
+        <f>Plan!O66</f>
         <v/>
       </c>
     </row>
@@ -44698,22 +44698,22 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="C51" s="35">
-        <f>Plan!C46</f>
+        <f>Plan!C65</f>
         <v/>
       </c>
       <c r="D51" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E51" s="16">
-        <f>Plan!J46</f>
+        <f>Plan!J65</f>
         <v/>
       </c>
       <c r="F51" s="16">
-        <f>Plan!K46</f>
+        <f>Plan!K65</f>
         <v/>
       </c>
       <c r="G51" s="8">
@@ -44721,11 +44721,11 @@
         <v/>
       </c>
       <c r="H51" s="16">
-        <f>Plan!I46</f>
+        <f>Plan!I65</f>
         <v/>
       </c>
       <c r="I51" s="16">
-        <f>Plan!O46</f>
+        <f>Plan!O65</f>
         <v/>
       </c>
     </row>
@@ -44772,22 +44772,22 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="C53" s="35">
-        <f>Plan!C45</f>
+        <f>Plan!C75</f>
         <v/>
       </c>
       <c r="D53" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" s="16">
-        <f>Plan!J45</f>
+        <f>Plan!J75</f>
         <v/>
       </c>
       <c r="F53" s="16">
-        <f>Plan!K45</f>
+        <f>Plan!K75</f>
         <v/>
       </c>
       <c r="G53" s="8">
@@ -44795,11 +44795,11 @@
         <v/>
       </c>
       <c r="H53" s="16">
-        <f>Plan!I45</f>
+        <f>Plan!I75</f>
         <v/>
       </c>
       <c r="I53" s="16">
-        <f>Plan!O45</f>
+        <f>Plan!O75</f>
         <v/>
       </c>
     </row>
@@ -44846,22 +44846,22 @@
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C55" s="35">
-        <f>Plan!C23</f>
+        <f>Plan!C29</f>
         <v/>
       </c>
       <c r="D55" s="8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E55" s="16">
-        <f>Plan!J23</f>
+        <f>Plan!J29</f>
         <v/>
       </c>
       <c r="F55" s="16">
-        <f>Plan!K23</f>
+        <f>Plan!K29</f>
         <v/>
       </c>
       <c r="G55" s="8">
@@ -44869,11 +44869,11 @@
         <v/>
       </c>
       <c r="H55" s="16">
-        <f>Plan!I23</f>
+        <f>Plan!I29</f>
         <v/>
       </c>
       <c r="I55" s="16">
-        <f>Plan!O23</f>
+        <f>Plan!O29</f>
         <v/>
       </c>
     </row>
@@ -44883,22 +44883,22 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C56" s="35">
-        <f>Plan!C53</f>
+        <f>Plan!C45</f>
         <v/>
       </c>
       <c r="D56" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E56" s="16">
-        <f>Plan!J53</f>
+        <f>Plan!J45</f>
         <v/>
       </c>
       <c r="F56" s="16">
-        <f>Plan!K53</f>
+        <f>Plan!K45</f>
         <v/>
       </c>
       <c r="G56" s="8">
@@ -44906,11 +44906,11 @@
         <v/>
       </c>
       <c r="H56" s="16">
-        <f>Plan!I53</f>
+        <f>Plan!I45</f>
         <v/>
       </c>
       <c r="I56" s="16">
-        <f>Plan!O53</f>
+        <f>Plan!O45</f>
         <v/>
       </c>
     </row>
@@ -44920,22 +44920,22 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="C57" s="35">
-        <f>Plan!C39</f>
+        <f>Plan!C23</f>
         <v/>
       </c>
       <c r="D57" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E57" s="16">
-        <f>Plan!J39</f>
+        <f>Plan!J23</f>
         <v/>
       </c>
       <c r="F57" s="16">
-        <f>Plan!K39</f>
+        <f>Plan!K23</f>
         <v/>
       </c>
       <c r="G57" s="8">
@@ -44943,11 +44943,11 @@
         <v/>
       </c>
       <c r="H57" s="16">
-        <f>Plan!I39</f>
+        <f>Plan!I23</f>
         <v/>
       </c>
       <c r="I57" s="16">
-        <f>Plan!O39</f>
+        <f>Plan!O23</f>
         <v/>
       </c>
     </row>
@@ -44957,22 +44957,22 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="C58" s="35">
-        <f>Plan!C50</f>
+        <f>Plan!C51</f>
         <v/>
       </c>
       <c r="D58" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E58" s="16">
-        <f>Plan!J50</f>
+        <f>Plan!J51</f>
         <v/>
       </c>
       <c r="F58" s="16">
-        <f>Plan!K50</f>
+        <f>Plan!K51</f>
         <v/>
       </c>
       <c r="G58" s="8">
@@ -44980,11 +44980,11 @@
         <v/>
       </c>
       <c r="H58" s="16">
-        <f>Plan!I50</f>
+        <f>Plan!I51</f>
         <v/>
       </c>
       <c r="I58" s="16">
-        <f>Plan!O50</f>
+        <f>Plan!O51</f>
         <v/>
       </c>
     </row>
@@ -44994,22 +44994,22 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C59" s="35">
-        <f>Plan!C58</f>
+        <f>Plan!C39</f>
         <v/>
       </c>
       <c r="D59" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E59" s="16">
-        <f>Plan!J58</f>
+        <f>Plan!J39</f>
         <v/>
       </c>
       <c r="F59" s="16">
-        <f>Plan!K58</f>
+        <f>Plan!K39</f>
         <v/>
       </c>
       <c r="G59" s="8">
@@ -45017,11 +45017,11 @@
         <v/>
       </c>
       <c r="H59" s="16">
-        <f>Plan!I58</f>
+        <f>Plan!I39</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>Plan!O58</f>
+        <f>Plan!O39</f>
         <v/>
       </c>
     </row>
@@ -45031,22 +45031,22 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="C60" s="35">
-        <f>Plan!C51</f>
+        <f>Plan!C53</f>
         <v/>
       </c>
       <c r="D60" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E60" s="16">
-        <f>Plan!J51</f>
+        <f>Plan!J53</f>
         <v/>
       </c>
       <c r="F60" s="16">
-        <f>Plan!K51</f>
+        <f>Plan!K53</f>
         <v/>
       </c>
       <c r="G60" s="8">
@@ -45054,11 +45054,11 @@
         <v/>
       </c>
       <c r="H60" s="16">
-        <f>Plan!I51</f>
+        <f>Plan!I53</f>
         <v/>
       </c>
       <c r="I60" s="16">
-        <f>Plan!O51</f>
+        <f>Plan!O53</f>
         <v/>
       </c>
     </row>
@@ -45068,22 +45068,22 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="C61" s="35">
-        <f>Plan!C74</f>
+        <f>Plan!C69</f>
         <v/>
       </c>
       <c r="D61" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E61" s="16">
-        <f>Plan!J74</f>
+        <f>Plan!J69</f>
         <v/>
       </c>
       <c r="F61" s="16">
-        <f>Plan!K74</f>
+        <f>Plan!K69</f>
         <v/>
       </c>
       <c r="G61" s="8">
@@ -45091,11 +45091,11 @@
         <v/>
       </c>
       <c r="H61" s="16">
-        <f>Plan!I74</f>
+        <f>Plan!I69</f>
         <v/>
       </c>
       <c r="I61" s="16">
-        <f>Plan!O74</f>
+        <f>Plan!O69</f>
         <v/>
       </c>
     </row>
@@ -45105,22 +45105,22 @@
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C62" s="35">
-        <f>Plan!C59</f>
+        <f>Plan!C58</f>
         <v/>
       </c>
       <c r="D62" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E62" s="16">
-        <f>Plan!J59</f>
+        <f>Plan!J58</f>
         <v/>
       </c>
       <c r="F62" s="16">
-        <f>Plan!K59</f>
+        <f>Plan!K58</f>
         <v/>
       </c>
       <c r="G62" s="8">
@@ -45128,11 +45128,11 @@
         <v/>
       </c>
       <c r="H62" s="16">
-        <f>Plan!I59</f>
+        <f>Plan!I58</f>
         <v/>
       </c>
       <c r="I62" s="16">
-        <f>Plan!O59</f>
+        <f>Plan!O58</f>
         <v/>
       </c>
     </row>
@@ -45142,22 +45142,22 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="C63" s="35">
-        <f>Plan!C60</f>
+        <f>Plan!C59</f>
         <v/>
       </c>
       <c r="D63" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E63" s="16">
-        <f>Plan!J60</f>
+        <f>Plan!J59</f>
         <v/>
       </c>
       <c r="F63" s="16">
-        <f>Plan!K60</f>
+        <f>Plan!K59</f>
         <v/>
       </c>
       <c r="G63" s="8">
@@ -45165,11 +45165,11 @@
         <v/>
       </c>
       <c r="H63" s="16">
-        <f>Plan!I60</f>
+        <f>Plan!I59</f>
         <v/>
       </c>
       <c r="I63" s="16">
-        <f>Plan!O60</f>
+        <f>Plan!O59</f>
         <v/>
       </c>
     </row>
@@ -45179,22 +45179,22 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C64" s="35">
-        <f>Plan!C72</f>
+        <f>Plan!C50</f>
         <v/>
       </c>
       <c r="D64" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E64" s="16">
-        <f>Plan!J72</f>
+        <f>Plan!J50</f>
         <v/>
       </c>
       <c r="F64" s="16">
-        <f>Plan!K72</f>
+        <f>Plan!K50</f>
         <v/>
       </c>
       <c r="G64" s="8">
@@ -45202,11 +45202,11 @@
         <v/>
       </c>
       <c r="H64" s="16">
-        <f>Plan!I72</f>
+        <f>Plan!I50</f>
         <v/>
       </c>
       <c r="I64" s="16">
-        <f>Plan!O72</f>
+        <f>Plan!O50</f>
         <v/>
       </c>
     </row>
@@ -45216,22 +45216,22 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="C65" s="35">
-        <f>Plan!C57</f>
+        <f>Plan!C76</f>
         <v/>
       </c>
       <c r="D65" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="16">
-        <f>Plan!J57</f>
+        <f>Plan!J76</f>
         <v/>
       </c>
       <c r="F65" s="16">
-        <f>Plan!K57</f>
+        <f>Plan!K76</f>
         <v/>
       </c>
       <c r="G65" s="8">
@@ -45239,11 +45239,11 @@
         <v/>
       </c>
       <c r="H65" s="16">
-        <f>Plan!I57</f>
+        <f>Plan!I76</f>
         <v/>
       </c>
       <c r="I65" s="16">
-        <f>Plan!O57</f>
+        <f>Plan!O76</f>
         <v/>
       </c>
     </row>
@@ -45253,22 +45253,22 @@
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="C66" s="35">
-        <f>Plan!C71</f>
+        <f>Plan!C60</f>
         <v/>
       </c>
       <c r="D66" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E66" s="16">
-        <f>Plan!J71</f>
+        <f>Plan!J60</f>
         <v/>
       </c>
       <c r="F66" s="16">
-        <f>Plan!K71</f>
+        <f>Plan!K60</f>
         <v/>
       </c>
       <c r="G66" s="8">
@@ -45276,11 +45276,11 @@
         <v/>
       </c>
       <c r="H66" s="16">
-        <f>Plan!I71</f>
+        <f>Plan!I60</f>
         <v/>
       </c>
       <c r="I66" s="16">
-        <f>Plan!O71</f>
+        <f>Plan!O60</f>
         <v/>
       </c>
     </row>
@@ -45290,22 +45290,22 @@
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C67" s="35">
-        <f>Plan!C62</f>
+        <f>Plan!C12</f>
         <v/>
       </c>
       <c r="D67" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E67" s="16">
-        <f>Plan!J62</f>
+        <f>Plan!J12</f>
         <v/>
       </c>
       <c r="F67" s="16">
-        <f>Plan!K62</f>
+        <f>Plan!K12</f>
         <v/>
       </c>
       <c r="G67" s="8">
@@ -45313,11 +45313,11 @@
         <v/>
       </c>
       <c r="H67" s="16">
-        <f>Plan!I62</f>
+        <f>Plan!I12</f>
         <v/>
       </c>
       <c r="I67" s="16">
-        <f>Plan!O62</f>
+        <f>Plan!O12</f>
         <v/>
       </c>
     </row>
@@ -45327,22 +45327,22 @@
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="C68" s="35">
-        <f>Plan!C63</f>
+        <f>Plan!C71</f>
         <v/>
       </c>
       <c r="D68" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E68" s="16">
-        <f>Plan!J63</f>
+        <f>Plan!J71</f>
         <v/>
       </c>
       <c r="F68" s="16">
-        <f>Plan!K63</f>
+        <f>Plan!K71</f>
         <v/>
       </c>
       <c r="G68" s="8">
@@ -45350,11 +45350,11 @@
         <v/>
       </c>
       <c r="H68" s="16">
-        <f>Plan!I63</f>
+        <f>Plan!I71</f>
         <v/>
       </c>
       <c r="I68" s="16">
-        <f>Plan!O63</f>
+        <f>Plan!O71</f>
         <v/>
       </c>
     </row>
@@ -45364,22 +45364,22 @@
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="C69" s="35">
-        <f>Plan!C64</f>
+        <f>Plan!C62</f>
         <v/>
       </c>
       <c r="D69" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E69" s="16">
-        <f>Plan!J64</f>
+        <f>Plan!J62</f>
         <v/>
       </c>
       <c r="F69" s="16">
-        <f>Plan!K64</f>
+        <f>Plan!K62</f>
         <v/>
       </c>
       <c r="G69" s="8">
@@ -45387,11 +45387,11 @@
         <v/>
       </c>
       <c r="H69" s="16">
-        <f>Plan!I64</f>
+        <f>Plan!I62</f>
         <v/>
       </c>
       <c r="I69" s="16">
-        <f>Plan!O64</f>
+        <f>Plan!O62</f>
         <v/>
       </c>
     </row>
@@ -45401,22 +45401,22 @@
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="C70" s="35">
-        <f>Plan!C43</f>
+        <f>Plan!C63</f>
         <v/>
       </c>
       <c r="D70" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70" s="16">
-        <f>Plan!J43</f>
+        <f>Plan!J63</f>
         <v/>
       </c>
       <c r="F70" s="16">
-        <f>Plan!K43</f>
+        <f>Plan!K63</f>
         <v/>
       </c>
       <c r="G70" s="8">
@@ -45424,11 +45424,11 @@
         <v/>
       </c>
       <c r="H70" s="16">
-        <f>Plan!I43</f>
+        <f>Plan!I63</f>
         <v/>
       </c>
       <c r="I70" s="16">
-        <f>Plan!O43</f>
+        <f>Plan!O63</f>
         <v/>
       </c>
     </row>
@@ -45438,22 +45438,22 @@
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="C71" s="35">
-        <f>Plan!C75</f>
+        <f>Plan!C57</f>
         <v/>
       </c>
       <c r="D71" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71" s="16">
-        <f>Plan!J75</f>
+        <f>Plan!J57</f>
         <v/>
       </c>
       <c r="F71" s="16">
-        <f>Plan!K75</f>
+        <f>Plan!K57</f>
         <v/>
       </c>
       <c r="G71" s="8">
@@ -45461,11 +45461,11 @@
         <v/>
       </c>
       <c r="H71" s="16">
-        <f>Plan!I75</f>
+        <f>Plan!I57</f>
         <v/>
       </c>
       <c r="I71" s="16">
-        <f>Plan!O75</f>
+        <f>Plan!O57</f>
         <v/>
       </c>
     </row>
@@ -45475,22 +45475,22 @@
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C72" s="35">
-        <f>Plan!C12</f>
+        <f>Plan!C44</f>
         <v/>
       </c>
       <c r="D72" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E72" s="16">
-        <f>Plan!J12</f>
+        <f>Plan!J44</f>
         <v/>
       </c>
       <c r="F72" s="16">
-        <f>Plan!K12</f>
+        <f>Plan!K44</f>
         <v/>
       </c>
       <c r="G72" s="8">
@@ -45498,11 +45498,11 @@
         <v/>
       </c>
       <c r="H72" s="16">
-        <f>Plan!I12</f>
+        <f>Plan!I44</f>
         <v/>
       </c>
       <c r="I72" s="16">
-        <f>Plan!O12</f>
+        <f>Plan!O44</f>
         <v/>
       </c>
     </row>
@@ -45512,22 +45512,22 @@
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="C73" s="35">
-        <f>Plan!C69</f>
+        <f>Plan!C56</f>
         <v/>
       </c>
       <c r="D73" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" s="16">
-        <f>Plan!J69</f>
+        <f>Plan!J56</f>
         <v/>
       </c>
       <c r="F73" s="16">
-        <f>Plan!K69</f>
+        <f>Plan!K56</f>
         <v/>
       </c>
       <c r="G73" s="8">
@@ -45535,11 +45535,11 @@
         <v/>
       </c>
       <c r="H73" s="16">
-        <f>Plan!I69</f>
+        <f>Plan!I56</f>
         <v/>
       </c>
       <c r="I73" s="16">
-        <f>Plan!O69</f>
+        <f>Plan!O56</f>
         <v/>
       </c>
     </row>
@@ -45549,22 +45549,22 @@
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C74" s="35">
-        <f>Plan!C56</f>
+        <f>Plan!C43</f>
         <v/>
       </c>
       <c r="D74" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74" s="16">
-        <f>Plan!J56</f>
+        <f>Plan!J43</f>
         <v/>
       </c>
       <c r="F74" s="16">
-        <f>Plan!K56</f>
+        <f>Plan!K43</f>
         <v/>
       </c>
       <c r="G74" s="8">
@@ -45572,11 +45572,11 @@
         <v/>
       </c>
       <c r="H74" s="16">
-        <f>Plan!I56</f>
+        <f>Plan!I43</f>
         <v/>
       </c>
       <c r="I74" s="16">
-        <f>Plan!O56</f>
+        <f>Plan!O43</f>
         <v/>
       </c>
     </row>
@@ -45586,22 +45586,22 @@
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="C75" s="35">
-        <f>Plan!C76</f>
+        <f>Plan!C72</f>
         <v/>
       </c>
       <c r="D75" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="16">
-        <f>Plan!J76</f>
+        <f>Plan!J72</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>Plan!K76</f>
+        <f>Plan!K72</f>
         <v/>
       </c>
       <c r="G75" s="8">
@@ -45609,11 +45609,11 @@
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>Plan!I76</f>
+        <f>Plan!I72</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>Plan!O76</f>
+        <f>Plan!O72</f>
         <v/>
       </c>
     </row>
@@ -45623,22 +45623,22 @@
       </c>
       <c r="B76" s="18" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="C76" s="35">
-        <f>Plan!C44</f>
+        <f>Plan!C64</f>
         <v/>
       </c>
       <c r="D76" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76" s="16">
-        <f>Plan!J44</f>
+        <f>Plan!J64</f>
         <v/>
       </c>
       <c r="F76" s="16">
-        <f>Plan!K44</f>
+        <f>Plan!K64</f>
         <v/>
       </c>
       <c r="G76" s="8">
@@ -45646,11 +45646,11 @@
         <v/>
       </c>
       <c r="H76" s="16">
-        <f>Plan!I44</f>
+        <f>Plan!I64</f>
         <v/>
       </c>
       <c r="I76" s="16">
-        <f>Plan!O44</f>
+        <f>Plan!O64</f>
         <v/>
       </c>
     </row>
@@ -46348,7 +46348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46412,17 +46412,17 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>4.11; P-99, P-100, P-101, P-102, P-103</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>H1 corregido (tasa de interés fuera del payload de /cuenta) y H2/B-01 cerrados (cédula de las «hermanas» enmascarada en servidor, testimonios de ejemplo ocultos)</t>
+          <t>Se corrige la dependencia de 6.18: ya no depende de 1.8</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Commit e650033: la tasa de interés ya no viaja al navegador del asociado en /cuenta ni /cuenta/solicitar (hallazgo H1 de ga-revisor-seguridad; el problema también estaba en producción desde el 25-sep, se sugiere llevarlo también a main). Queda un residuo (P-100): un asociado podría seguir leyendo la tasa consultando la API directo con su sesión (la RLS le deja leer sus solicitudes y grados_credito); ocultarlo del todo requiere una migración de permisos por columna, a decisión de Sebas. Commit fdab456: cédula de las «hermanas» del detalle de afiliación enmascarada en el servidor (cierra H2/M-01, P-101) y sección de testimonios de la landing oculta mientras tenga textos de ejemplo (cierra B-01, P-102; D-07 queda abierto como pedido de diseño en P-103: contenido real de testimonios y si la sección se mantiene). e2e de landing y k-roles vueltos a correr en verde.</t>
+          <t>6.18 (fusionar rediseno-c-plus a develop) dependía por error de 1.8 (aplicar las 5 migraciones de backend del rediseño). El código del rediseño funciona sin esas migraciones (KPIs con su propio fallback, tope real leído de grados_credito, nota interna oculta detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false) y lo que sí las necesita queda oculto hasta que se apliquen. Con 6.17 y 6.19 en Hecho, el rediseño C+ queda completo y verificado de punta a punta en la rama rediseno-c-plus (9 commits locales sobre develop, sin push); 6.18 queda Pendiente solo de que Sebas autorice el push de la rama y abra el PR a develop.</t>
         </is>
       </c>
     </row>
@@ -46434,22 +46434,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>4.11, P-94, P-71; 6.16 pasa a Hecho; nuevos P-102, P-103</t>
+          <t>6.17; 3.10, 4.10</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>QA completo del rediseño C+ en verde: 161/162 escritorio, 129/129 celular</t>
+          <t>Correcciones responsive del C+ (commit b0239a8): barra inferior siempre visible en vez de oculta hasta el primer scroll</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>QA de punta a punta contra Supabase local (escritorio 1280×800, celular 390×844). Actualizó las pruebas desactualizadas por el rediseño: a-navegacion (nav sin «Historias»), e-diseno (reescrita casi entera, textos verificados contra el código), afiliación v2 en utils.ts/f-accesibilidad (cierra P-94), aprobar en 2 pasos + atajos de teclado + KPIs + nota interna oculta (k-roles), máscara de correo con dominio oculto en b-ingreso y j-produccion (cierra P-71; i-despliegue ya usaba el formato nuevo). Agregó pruebas de reduced-motion y de que ninguna pantalla diga «Correo institucional». De paso corrigió una prueba de seguridad de i-despliegue que fallaba por una causa ajena al rediseño (React 19 ya no serializa el DOM en un `&lt;form action={...}&gt;`), reescribiéndola con intercepción de red. Hallazgos: 1 Media (cédula de las «hermanas», ya reportada por ga-revisor-seguridad, ver P-101) y 2 Bajos (testimonios de ejemplo con corchetes en la landing, ver P-102/P-103; y los marcadores ya conocidos de /politica-de-datos). 0 violaciones de axe en 19 combinaciones. Informe en docs/verificaciones/2026-09-27-rediseno-c-plus-qa.md.</t>
+          <t>Se descartó la solución de ga-diseno-a-codigo de ocultar la barra inferior de /cuenta y /asesor hasta el primer scroll (con `inert`) porque ocultar la navegación principal al cargar la página perjudicaba la usabilidad y la accesibilidad. En su lugar, la barra queda siempre visible con espacio reservado al final de la página. Incluye también las correcciones de admin en celular y de la vista en tarjetas de /admin/sorteo, y el contraste de /admin/demo. e2e k-roles, c-cuenta y f-accesibilidad en verde (50 pasadas) tras `supabase db reset`.</t>
         </is>
       </c>
     </row>
@@ -46461,22 +46461,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>4.11; nuevos P-99, P-100, P-101</t>
+          <t>4.11; 6.17</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad del rediseño C+ aprobada; 2 fugas de datos confirmadas (no introducidas por el rediseño)</t>
+          <t>Hallazgo 0 corregido en producción del rediseño (commit 846657b): colores del admin oscuro en su propio grupo de Tailwind</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Revisó el diff completo de rediseno-c-plus contra develop (app, components, lib, proxy.ts, supabase): sin cambios en Server Actions ni en proxy.ts, el asesor sigue sin ver datos sensibles de sus clientes, la aprobación en 2 pasos exige confirmar, el login no cambió en funcionalidad. Encontró 2 hallazgos de fuga de datos al payload del cliente, vigentes desde antes de este diff: la tasa de interés viaja en las props de CuentaCliente aunque no se renderice (H1, ver P-99/P-100) y la cédula sin enmascarar de las «hermanas» viaja completa al detalle de afiliación aunque se muestre enmascarada (H2, ver P-101). Revisó también las 5 migraciones propuestas de 1.8 (bien construidas, coherentes con el flag de nota interna). npm audit --omit=dev: 0 vulnerabilidades. Pidió a ga-funcionalidad-botones corregir ambas fugas y a Sebas decidir sobre las 5 migraciones de 1.8.</t>
+          <t>Los colores bg-admin-*/text-admin-* estaban anidados bajo la paleta ga en tailwind.config.ts, por lo que Tailwind nunca generaba esas clases y el panel /admin se veía blanco/sin tema oscuro en todos los anchos. Se movieron a su propio grupo admin en tailwind.config.ts; pruebas de responsive actualizadas en el mismo commit.</t>
         </is>
       </c>
     </row>
@@ -46488,22 +46488,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>KPIs reales, tope real de grados_credito y nota interna oculta en el admin C+</t>
+          <t>Corregidos todos los hallazgos del informe de responsive; 6.17 pasa a Hecho en su parte de código</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Cerró los 2 frentes de backend que dejó abiertos el maquetado del admin en modo oscuro (commit e39ad72): (1) los 4 KPI de /admin/creditos ahora son siempre exactos (lib/admin/kpis.ts: 3 conteos exactos + suma de aprobadas del mes, con el cliente de sesión del admin vía RLS, sin service role; mes calendario en hora de Colombia; pruebas nuevas en tests/unit/admin-kpis.test.ts); (2) el aviso «Dentro/Supera el tope» y el bloqueo de «Aprobar» usan el tope real de grados_credito (cargarPaquetesDemo, con su fallback a la copia estática). Ocultó el textarea de «Nota interna» detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false (lib/admin/flags.ts) con un TODO(backend) hacia la migración sin aplicar 20260925200200_historial_y_notas_internas.sql. Confirmó sin cambios de código que la aprobación en 2 pasos, el rechazo con motivo obligatorio, los atajos J/K/A/R/Esc y el invariante monto≤tope (triggers de la base) siguen intactos. tsc, lint, build y 316 pruebas de vitest (19 archivos) en verde. Sin commits. Sin bloqueos nuevos; sigue pendiente 1.8 (migraciones sin aplicar) para conectar una Server Action a agregar_nota_solicitud() y activar la bandera.</t>
+          <t>Confirmado con capturas que el hallazgo 0 (colores admin-* fuera de la clave ga) ya estaba resuelto en el código. De paso, axe encontró y se corrigió un contraste nuevo: EncabezadoAdmin se volvía transparente en escritorio asumiendo que siempre estaría sobre el fondo oscuro del admin, pero en /admin/demo esa misma barra flota sobre el fondo claro de la vista de asociado. Corregidos también: flex-wrap en el filtro de /admin/creditos, controles del encabezado móvil del admin a 44×44, tabla de /admin/sorteo con versión en tarjetas, botones de /cuenta/solicitar y casillas OTP a 44px, selects de /admin/sorteo a 16px. La corrección de la barra inferior flotante de /cuenta y /asesor de este commit (ocultarla hasta el primer scroll con `inert`) fue reemplazada después por la sesión principal, ver el siguiente asiento. tsc, lint, build, vitest (316/316) y playwright k-roles+f-accesibilidad (36/36, 6 skip esperados) en verde tras `npx supabase db reset`.</t>
         </is>
       </c>
     </row>
@@ -46515,22 +46515,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Panel del admin C+ en modo oscuro maquetado en código; 4.11 pasa a Hecho</t>
+          <t>Verificación responsive de punta a punta del rediseño C+; 6.19 pasa a Hecho</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Maquetó el panel de administración completo en modo oscuro (piezas 2d y 3e–3h): Créditos (menú lateral, 4 KPI con guion donde falta consulta nueva, búsqueda, filtro, lista+ficha, aprobar en 2 pasos, rechazar con motivo obligatorio, nota interna e historial UI), Afiliaciones (lista+ficha, visor de 3 fotos con sus 3 estados, aprobar/rechazar en 2 pasos, WhatsApp deshabilitado por P-95), Asesores y Sorteo con el mismo restyle, y EncabezadoAdmin (patrón de celular) también en /admin/demo. Tokens nuevos en globals.css/tailwind.config.ts. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus (junto con 4.10). Pasa a Hecho en maquetación con 2 frentes abiertos: (1) tests/e2e/k-roles.spec.ts va a fallar porque Aprobar ahora pide un segundo clic «Sí, aprobar» — hace falta que ga-verificador-qa/ga-escritor-tests actualicen ese paso; (2) sin backend nuevo, KPIs completos, tope real desde grados_credito y nota interna/historial reales siguen bloqueados por las 5 migraciones de 1.8 (docs/auditorias/2026-09-25-backend-rediseno-c-plus.md), sin aplicar.</t>
+          <t>15 rutas × 10 anchos (320-1920 px) + horizontal 844×390, Playwright/Chrome contra Supabase local. 9 hallazgos responsive (5 críticos: barra inferior flotante tapaba contenido real en /cuenta y /asesor, scroll horizontal real en /admin/creditos, botones &lt;44px en el encabezado móvil del admin, tabla de /admin/sorteo sin versión en tarjetas; 4 menores) más 1 hallazgo crítico fuera del alcance responsive estricto: los colores bg-admin-*/text-admin-* no existían en el CSS compilado (tailwind.config.ts los anidaba bajo la paleta ga en vez de un grupo propio admin), así que el panel se veía sin tema oscuro. tests/responsive/responsive.spec.ts y logo-y-fotos.spec.ts actualizados. No se pudo probar /admin/* en horizontal por el límite diario de reenvío de código del correo de prueba (no es un hallazgo nuevo). Informe: docs/verificaciones/2026-09-27-rediseno-c-plus-responsive.md.</t>
         </is>
       </c>
     </row>
@@ -46542,22 +46542,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>4.10; nuevo P-98</t>
+          <t>4.11; P-99, P-100, P-101, P-102, P-103</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Panel del asesor C+ maquetado en código; 4.10 pasa a Hecho</t>
+          <t>H1 corregido (tasa de interés fuera del payload de /cuenta) y H2/B-01 cerrados (cédula de las «hermanas» enmascarada en servidor, testimonios de ejemplo ocultos)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Maquetó /asesor y /asesor/demo siguiendo las piezas 2c/3h del lienzo: EncabezadoAsesor en píldora, tarjetas de resumen con categoría de afiliación, chips de filtro, buscador, tabla de 5 columnas reescrita (sin datos de contacto), estado vacío, transición de lista y barra inferior en celular; agregó el marco ámbar de demostración compartido con /admin/demo y el estado «neutral» a Badge. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus. Documentó como pedido D-06 (docs/diseno/pedidos.md) la falta de regla de diseño para categorizar asociados ya afiliados (no solo solicitudes) en las tarjetas/chips; se registra como decisión provisional de la sesión principal, pendiente de que Sebas la confirme (nuevo pendiente P-98).</t>
+          <t>Commit e650033: la tasa de interés ya no viaja al navegador del asociado en /cuenta ni /cuenta/solicitar (hallazgo H1 de ga-revisor-seguridad; el problema también estaba en producción desde el 25-sep, se sugiere llevarlo también a main). Queda un residuo (P-100): un asociado podría seguir leyendo la tasa consultando la API directo con su sesión (la RLS le deja leer sus solicitudes y grados_credito); ocultarlo del todo requiere una migración de permisos por columna, a decisión de Sebas. Commit fdab456: cédula de las «hermanas» del detalle de afiliación enmascarada en el servidor (cierra H2/M-01, P-101) y sección de testimonios de la landing oculta mientras tenga textos de ejemplo (cierra B-01, P-102; D-07 queda abierto como pedido de diseño en P-103: contenido real de testimonios y si la sección se mantiene). e2e de landing y k-roles vueltos a correr en verde.</t>
         </is>
       </c>
     </row>
@@ -46569,83 +46569,83 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.11, P-94, P-71; 6.16 pasa a Hecho; nuevos P-102, P-103</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Panel del asociado C+ maquetado en código; 3.10 pasa a Hecho</t>
+          <t>QA completo del rediseño C+ en verde: 161/162 escritorio, 129/129 celular</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Maquetó /cuenta y /cuenta/solicitar siguiendo las piezas 2b/3d del lienzo: EncabezadoCuenta en píldora flotante, comprobante «Tu solicitud» con sello y pasos animados, insignia de estado con color real, tope con medidor, carné de asociado (institución/activo como props opcionales sin usar, TODO backend), franja del sorteo, barra inferior en celular y deslizador de monto propio en /cuenta/solicitar; agregó enmascararCedula a lib/mascara.ts. tsc, lint, build y 311 pruebas de vitest en verde; no corrió Playwright (requiere Supabase local). Commit local 51da63f en rediseno-c-plus. «Tu camino a la estabilidad» sigue sin renderizarse por P-90 (fecha del primer descuento del embargo solidario); el carné de asociado sigue esperando institución/activo en perfiles (1.8). Falta correr tests/e2e/c-cuenta, h-credito, i-despliegue, j-produccion y k-roles contra Supabase local (ga-verificador-qa).</t>
+          <t>QA de punta a punta contra Supabase local (escritorio 1280×800, celular 390×844). Actualizó las pruebas desactualizadas por el rediseño: a-navegacion (nav sin «Historias»), e-diseno (reescrita casi entera, textos verificados contra el código), afiliación v2 en utils.ts/f-accesibilidad (cierra P-94), aprobar en 2 pasos + atajos de teclado + KPIs + nota interna oculta (k-roles), máscara de correo con dominio oculto en b-ingreso y j-produccion (cierra P-71; i-despliegue ya usaba el formato nuevo). Agregó pruebas de reduced-motion y de que ninguna pantalla diga «Correo institucional». De paso corrigió una prueba de seguridad de i-despliegue que fallaba por una causa ajena al rediseño (React 19 ya no serializa el DOM en un `&lt;form action={...}&gt;`), reescribiéndola con intercepción de red. Hallazgos: 1 Media (cédula de las «hermanas», ya reportada por ga-revisor-seguridad, ver P-101) y 2 Bajos (testimonios de ejemplo con corchetes en la landing, ver P-102/P-103; y los marcadores ya conocidos de /politica-de-datos). 0 violaciones de axe en 19 combinaciones. Informe en docs/verificaciones/2026-09-27-rediseno-c-plus-qa.md.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15</t>
+          <t>4.11; nuevos P-99, P-100, P-101</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
+          <t>Revisión de seguridad del rediseño C+ aprobada; 2 fugas de datos confirmadas (no introducidas por el rediseño)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
+          <t>Revisó el diff completo de rediseno-c-plus contra develop (app, components, lib, proxy.ts, supabase): sin cambios en Server Actions ni en proxy.ts, el asesor sigue sin ver datos sensibles de sus clientes, la aprobación en 2 pasos exige confirmar, el login no cambió en funcionalidad. Encontró 2 hallazgos de fuga de datos al payload del cliente, vigentes desde antes de este diff: la tasa de interés viaja en las props de CuentaCliente aunque no se renderice (H1, ver P-99/P-100) y la cédula sin enmascarar de las «hermanas» viaja completa al detalle de afiliación aunque se muestre enmascarada (H2, ver P-101). Revisó también las 5 migraciones propuestas de 1.8 (bien construidas, coherentes con el flag de nota interna). npm audit --omit=dev: 0 vulnerabilidades. Pidió a ga-funcionalidad-botones corregir ambas fugas y a Sebas decidir sobre las 5 migraciones de 1.8.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>3.10, 4.10, 4.11</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
+          <t>KPIs reales, tope real de grados_credito y nota interna oculta en el admin C+</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
+          <t>Cerró los 2 frentes de backend que dejó abiertos el maquetado del admin en modo oscuro (commit e39ad72): (1) los 4 KPI de /admin/creditos ahora son siempre exactos (lib/admin/kpis.ts: 3 conteos exactos + suma de aprobadas del mes, con el cliente de sesión del admin vía RLS, sin service role; mes calendario en hora de Colombia; pruebas nuevas en tests/unit/admin-kpis.test.ts); (2) el aviso «Dentro/Supera el tope» y el bloqueo de «Aprobar» usan el tope real de grados_credito (cargarPaquetesDemo, con su fallback a la copia estática). Ocultó el textarea de «Nota interna» detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false (lib/admin/flags.ts) con un TODO(backend) hacia la migración sin aplicar 20260925200200_historial_y_notas_internas.sql. Confirmó sin cambios de código que la aprobación en 2 pasos, el rechazo con motivo obligatorio, los atajos J/K/A/R/Esc y el invariante monto≤tope (triggers de la base) siguen intactos. tsc, lint, build y 316 pruebas de vitest (19 archivos) en verde. Sin commits. Sin bloqueos nuevos; sigue pendiente 1.8 (migraciones sin aplicar) para conectar una Server Action a agregar_nota_solicitud() y activar la bandera.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -46655,71 +46655,71 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.14; nuevo 6.16</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Tokens y landing del rediseño C+ llevados a código</t>
+          <t>Panel del admin C+ en modo oscuro maquetado en código; 4.11 pasa a Hecho</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
+          <t>Maquetó el panel de administración completo en modo oscuro (piezas 2d y 3e–3h): Créditos (menú lateral, 4 KPI con guion donde falta consulta nueva, búsqueda, filtro, lista+ficha, aprobar en 2 pasos, rechazar con motivo obligatorio, nota interna e historial UI), Afiliaciones (lista+ficha, visor de 3 fotos con sus 3 estados, aprobar/rechazar en 2 pasos, WhatsApp deshabilitado por P-95), Asesores y Sorteo con el mismo restyle, y EncabezadoAdmin (patrón de celular) también en /admin/demo. Tokens nuevos en globals.css/tailwind.config.ts. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus (junto con 4.10). Pasa a Hecho en maquetación con 2 frentes abiertos: (1) tests/e2e/k-roles.spec.ts va a fallar porque Aprobar ahora pide un segundo clic «Sí, aprobar» — hace falta que ga-verificador-qa/ga-escritor-tests actualicen ese paso; (2) sin backend nuevo, KPIs completos, tope real desde grados_credito y nota interna/historial reales siguen bloqueados por las 5 migraciones de 1.8 (docs/auditorias/2026-09-25-backend-rediseno-c-plus.md), sin aplicar.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
+          <t>4.10; nuevo P-98</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
+          <t>Panel del asesor C+ maquetado en código; 4.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
+          <t>Maquetó /asesor y /asesor/demo siguiendo las piezas 2c/3h del lienzo: EncabezadoAsesor en píldora, tarjetas de resumen con categoría de afiliación, chips de filtro, buscador, tabla de 5 columnas reescrita (sin datos de contacto), estado vacío, transición de lista y barra inferior en celular; agregó el marco ámbar de demostración compartido con /admin/demo y el estado «neutral» a Badge. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus. Documentó como pedido D-06 (docs/diseno/pedidos.md) la falta de regla de diseño para categorizar asociados ya afiliados (no solo solicitudes) en las tarjetas/chips; se registra como decisión provisional de la sesión principal, pendiente de que Sebas la confirme (nuevo pendiente P-98).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>1.8; P-47, P-90, P-91, P-92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
+          <t>Panel del asociado C+ maquetado en código; 3.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
+          <t>Maquetó /cuenta y /cuenta/solicitar siguiendo las piezas 2b/3d del lienzo: EncabezadoCuenta en píldora flotante, comprobante «Tu solicitud» con sello y pasos animados, insignia de estado con color real, tope con medidor, carné de asociado (institución/activo como props opcionales sin usar, TODO backend), franja del sorteo, barra inferior en celular y deslizador de monto propio en /cuenta/solicitar; agregó enmascararCedula a lib/mascara.ts. tsc, lint, build y 311 pruebas de vitest en verde; no corrió Playwright (requiere Supabase local). Commit local 51da63f en rediseno-c-plus. «Tu camino a la estabilidad» sigue sin renderizarse por P-90 (fecha del primer descuento del embargo solidario); el carné de asociado sigue esperando institución/activo en perfiles (1.8). Falta correr tests/e2e/c-cuenta, h-credito, i-despliegue, j-produccion y k-roles contra Supabase local (ga-verificador-qa).</t>
         </is>
       </c>
     </row>
@@ -46729,24 +46729,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (despliegue PR #2)</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89</t>
+          <t>1.7, 2.15</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
+          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
+          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
         </is>
       </c>
     </row>
@@ -46756,24 +46756,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
+          <t>3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
+          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
+          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
         </is>
       </c>
     </row>
@@ -46785,22 +46785,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-13</t>
+          <t>1.7, 2.14; nuevo 6.16</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Texto de vigilancia de Supersolidaria confirmado</t>
+          <t>Tokens y landing del rediseño C+ llevados a código</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
+          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
         </is>
       </c>
     </row>
@@ -46812,22 +46812,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>6.3; nuevos P-84, P-86, P-87</t>
+          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>QA de producción: con observaciones</t>
+          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
+          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
         </is>
       </c>
     </row>
@@ -46839,22 +46839,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>2.12; nuevo P-85</t>
+          <t>1.8; P-47, P-90, P-91, P-92</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
+          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
+          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
         </is>
       </c>
     </row>
@@ -46864,24 +46864,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>ga-revisor-seguridad</t>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (despliegue PR #2)</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>6.2; nuevos P-83, P-88</t>
+          <t>4.9; P-83, P-84, P-85, P-89</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
+          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
+          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
         </is>
       </c>
     </row>
@@ -46898,17 +46898,17 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
+          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
+          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
+          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
         </is>
       </c>
     </row>
@@ -46918,159 +46918,159 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>6.9, 6.13; P-44, P-59, P-61</t>
+          <t>5.3; P-13</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
+          <t>Texto de vigilancia de Supersolidaria confirmado</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
+          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
+          <t>6.3; nuevos P-84, P-86, P-87</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
+          <t>QA de producción: con observaciones</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
+          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Sebas (acuerdo con Carlos Pardo)</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
+          <t>2.12; nuevo P-85</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
+          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
+          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ga-escritor-tests</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>6.1, P-58</t>
+          <t>6.2; nuevos P-83, P-88</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
+          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
+          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Sebas (coordinación con la cooperativa)</t>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
+          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
+          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
+          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
+          <t>6.9, 6.13; P-44, P-59, P-61</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
+          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
+          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
         </is>
       </c>
     </row>
@@ -47080,24 +47080,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>ga-revisor-seguridad</t>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
+          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
+          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
         </is>
       </c>
     </row>
@@ -47107,24 +47107,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>ga-auditor-supabase</t>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (acuerdo con Carlos Pardo)</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
+          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
+          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
         </is>
       </c>
     </row>
@@ -47136,22 +47136,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.1, P-58</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Sorteo mensual en /cuenta</t>
+          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
+          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
         </is>
       </c>
     </row>
@@ -47161,24 +47161,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (coordinación con la cooperativa)</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>4.6; P-57</t>
+          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
+          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
+          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
         </is>
       </c>
     </row>
@@ -47190,110 +47190,110 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>1.5; P-63</t>
+          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
+          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
+          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
+          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
+          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive + ga-verificador-qa</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>6.3; P-39</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
+          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
+          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 5.8; P-39, P-53</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
+          <t>Sorteo mensual en /cuenta</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
+          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -47303,44 +47303,44 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
+          <t>4.6; P-57</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
+          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
+          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>5.2, 5.8, 6.3</t>
+          <t>1.5; P-63</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
+          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
+          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
         </is>
       </c>
     </row>
@@ -47350,24 +47350,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive</t>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
+          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
+          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
         </is>
       </c>
     </row>
@@ -47377,24 +47377,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>ga-diseno-a-codigo</t>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>ga-verificador-responsive + ga-verificador-qa</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>2.1, 5.3, 5.7; P-16, P-52</t>
+          <t>6.3; P-39</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
+          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
+          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
         </is>
       </c>
     </row>
@@ -47406,22 +47406,22 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
+          <t>6.3, 5.2, 5.8; P-39, P-53</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
+          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
+          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
         </is>
       </c>
     </row>
@@ -47431,24 +47431,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
+          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
+          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
+          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
         </is>
       </c>
     </row>
@@ -47460,22 +47460,22 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.2, 5.8, 6.3</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Agente ga-auditor-supabase corregido</t>
+          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
         </is>
       </c>
     </row>
@@ -47485,24 +47485,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>3.1, 6.5, 6.10; P-09</t>
+          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
         </is>
       </c>
     </row>
@@ -47514,22 +47514,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>ga-escritor-tests</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.1, 5.3, 5.7; P-16, P-52</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
         </is>
       </c>
     </row>
@@ -47539,24 +47539,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-funcionalidad-botones</t>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
         </is>
       </c>
     </row>
@@ -47566,24 +47566,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-qa</t>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
         </is>
       </c>
     </row>
@@ -47595,22 +47595,22 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+          <t>Agente ga-auditor-supabase corregido</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
         </is>
       </c>
     </row>
@@ -47620,22 +47620,157 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>3.1, 6.5, 6.10; P-09</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>ga-verificador-qa</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Claude (sesión principal)</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>Todas</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>Creación del Excel de avances</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>Pendientes desde PENDIENTES.md, plan desde la propuesta (6 fases, 8 semanas) reorganizado en 2 filas con cola infinita y pesos 1–5.</t>
         </is>

--- a/docs/avances/Avances_Green_Alliance.xlsx
+++ b/docs/avances/Avances_Green_Alliance.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bitácora" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$J$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$4:$R$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -806,7 +806,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actualizado: 2026-09-27. Lo mantiene el agente ga-supervisor-avances a partir de docs/avances/plan.json.</t>
+          <t>Actualizado: 2026-09-29. Lo mantiene el agente ga-supervisor-avances a partir de docs/avances/plan.json.</t>
         </is>
       </c>
     </row>
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B46,Pendientes!$G$5:$G$107,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B46,Pendientes!$G$5:$G$108,"Hecho")</f>
         <v/>
       </c>
       <c r="D46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B46,Pendientes!$G$5:$G$107,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B46,Pendientes!$G$5:$G$108,"En curso")</f>
         <v/>
       </c>
       <c r="E46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B46,Pendientes!$G$5:$G$107,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B46,Pendientes!$G$5:$G$108,"Pendiente")</f>
         <v/>
       </c>
       <c r="F46" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B46,Pendientes!$G$5:$G$107,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B46,Pendientes!$G$5:$G$108,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G46" s="9">
@@ -1522,19 +1522,19 @@
         </is>
       </c>
       <c r="C47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B47,Pendientes!$G$5:$G$107,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B47,Pendientes!$G$5:$G$108,"Hecho")</f>
         <v/>
       </c>
       <c r="D47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B47,Pendientes!$G$5:$G$107,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B47,Pendientes!$G$5:$G$108,"En curso")</f>
         <v/>
       </c>
       <c r="E47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B47,Pendientes!$G$5:$G$107,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B47,Pendientes!$G$5:$G$108,"Pendiente")</f>
         <v/>
       </c>
       <c r="F47" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B47,Pendientes!$G$5:$G$107,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B47,Pendientes!$G$5:$G$108,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G47" s="9">
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B48,Pendientes!$G$5:$G$107,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B48,Pendientes!$G$5:$G$108,"Hecho")</f>
         <v/>
       </c>
       <c r="D48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B48,Pendientes!$G$5:$G$107,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B48,Pendientes!$G$5:$G$108,"En curso")</f>
         <v/>
       </c>
       <c r="E48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B48,Pendientes!$G$5:$G$107,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B48,Pendientes!$G$5:$G$108,"Pendiente")</f>
         <v/>
       </c>
       <c r="F48" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B48,Pendientes!$G$5:$G$107,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B48,Pendientes!$G$5:$G$108,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G48" s="9">
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="C49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B49,Pendientes!$G$5:$G$107,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B49,Pendientes!$G$5:$G$108,"Hecho")</f>
         <v/>
       </c>
       <c r="D49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B49,Pendientes!$G$5:$G$107,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B49,Pendientes!$G$5:$G$108,"En curso")</f>
         <v/>
       </c>
       <c r="E49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B49,Pendientes!$G$5:$G$107,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B49,Pendientes!$G$5:$G$108,"Pendiente")</f>
         <v/>
       </c>
       <c r="F49" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B49,Pendientes!$G$5:$G$107,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B49,Pendientes!$G$5:$G$108,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G49" s="9">
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="C50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B50,Pendientes!$G$5:$G$107,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B50,Pendientes!$G$5:$G$108,"Hecho")</f>
         <v/>
       </c>
       <c r="D50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B50,Pendientes!$G$5:$G$107,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B50,Pendientes!$G$5:$G$108,"En curso")</f>
         <v/>
       </c>
       <c r="E50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B50,Pendientes!$G$5:$G$107,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B50,Pendientes!$G$5:$G$108,"Pendiente")</f>
         <v/>
       </c>
       <c r="F50" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B50,Pendientes!$G$5:$G$107,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B50,Pendientes!$G$5:$G$108,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G50" s="9">
@@ -1630,19 +1630,19 @@
         </is>
       </c>
       <c r="C51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B51,Pendientes!$G$5:$G$107,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B51,Pendientes!$G$5:$G$108,"Hecho")</f>
         <v/>
       </c>
       <c r="D51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B51,Pendientes!$G$5:$G$107,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B51,Pendientes!$G$5:$G$108,"En curso")</f>
         <v/>
       </c>
       <c r="E51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B51,Pendientes!$G$5:$G$107,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B51,Pendientes!$G$5:$G$108,"Pendiente")</f>
         <v/>
       </c>
       <c r="F51" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B51,Pendientes!$G$5:$G$107,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B51,Pendientes!$G$5:$G$108,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G51" s="9">
@@ -1657,19 +1657,19 @@
         </is>
       </c>
       <c r="C52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B52,Pendientes!$G$5:$G$107,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B52,Pendientes!$G$5:$G$108,"Hecho")</f>
         <v/>
       </c>
       <c r="D52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B52,Pendientes!$G$5:$G$107,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B52,Pendientes!$G$5:$G$108,"En curso")</f>
         <v/>
       </c>
       <c r="E52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B52,Pendientes!$G$5:$G$107,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B52,Pendientes!$G$5:$G$108,"Pendiente")</f>
         <v/>
       </c>
       <c r="F52" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B52,Pendientes!$G$5:$G$107,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B52,Pendientes!$G$5:$G$108,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G52" s="9">
@@ -1684,19 +1684,19 @@
         </is>
       </c>
       <c r="C53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B53,Pendientes!$G$5:$G$107,"Hecho")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B53,Pendientes!$G$5:$G$108,"Hecho")</f>
         <v/>
       </c>
       <c r="D53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B53,Pendientes!$G$5:$G$107,"En curso")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B53,Pendientes!$G$5:$G$108,"En curso")</f>
         <v/>
       </c>
       <c r="E53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B53,Pendientes!$G$5:$G$107,"Pendiente")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B53,Pendientes!$G$5:$G$108,"Pendiente")</f>
         <v/>
       </c>
       <c r="F53" s="15">
-        <f>COUNTIFS(Pendientes!$B$5:$B$107,$B53,Pendientes!$G$5:$G$107,"Bloqueado")</f>
+        <f>COUNTIFS(Pendientes!$B$5:$B$108,$B53,Pendientes!$G$5:$G$108,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G53" s="9">
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Necesario antes de que Carlos pueda abrir PRs a develop desde su propia rama. 24-sep: Sebas ya habló con Carlos para darle el acceso; falta confirmarlo en GitHub.</t>
+          <t>Necesario antes de que Carlos pueda abrir PRs a develop desde su propia rama. 24-sep: Sebas ya habló con Carlos para darle el acceso; falta confirmarlo en GitHub. 29-sep: la primera entrega de Carlos llegó como ZIP de un repo privado propio (no como PR al repo de Green Alliance), señal de que este acceso sigue sin confirmarse; además trabajó sobre una base main anterior al rediseño C+ en vez de rediseno-c-plus. Se le pidió que la próxima entrega sea un PR por tarea sobre rediseno-c-plus, lo que requiere este acceso ya confirmado.</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Falta que la cooperativa dé el X de días (ver P-63). Ver P-73.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Falta que la cooperativa dé el X de días (ver P-63). Ver P-73. 29-sep: primera entrega (ZIP, base main anterior al rediseño C+) NO fusionable — reintroduce F2-03, pierde el revoke en resumen_clientes_asesor, columna de motivo de rechazo inexistente sin migración, purga con columnas/bucket equivocados y cron abierto sin CRON_SECRET, claves en .env.example, console.log, config de túnel, sin pruebas. Se le envió la lista de correcciones para rehacer sobre rediseno-c-plus, un PR por tarea.</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-104</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Subir a GitHub y desplegar en Vercel</t>
+          <t>Aprobar y fusionar el PR develop → main para desplegar el rediseño C+ (con el arreglo de la tasa) en producción</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -5059,19 +5059,23 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="I69" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$76,MATCH(H69,Plan!$A$5:$A$76,0)),"—")</f>
         <v/>
       </c>
-      <c r="J69" s="7" t="inlineStr"/>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>29-sep: rediseno-c-plus ya fusionada a develop y subida a origin (suite e2e 290/290, tsc/lint/build en verde). Falta que Sebas apruebe/fusione el PR develop → main para que Vercel despliegue el rediseño C+ en producción.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
         <is>
-          <t>P-81</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -5081,17 +5085,17 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Despliegue</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Revisión de la política de datos por un abogado</t>
+          <t>Subir a GitHub y desplegar en Vercel</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -5106,23 +5110,19 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I70" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$76,MATCH(H70,Plan!$A$5:$A$76,0)),"—")</f>
         <v/>
       </c>
-      <c r="J70" s="7" t="inlineStr">
-        <is>
-          <t>24-sep: reportado por la sesión principal; falta antes de publicar /politica-de-datos.</t>
-        </is>
-      </c>
+      <c r="J70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
         <is>
-          <t>P-70</t>
+          <t>P-81</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -5132,22 +5132,22 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Pruebas en celulares reales (Android e iPhone): cámara, código, sorteo, crédito y correos en Gmail/Outlook, con informe y capturas</t>
+          <t>Revisión de la política de datos por un abogado</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Carlos Pardo</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I71" s="21">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
+          <t>24-sep: reportado por la sesión principal; falta antes de publicar /politica-de-datos.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-70</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -5183,32 +5183,32 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Calidad</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Correr ga-verificador-qa y ga-verificador-responsive</t>
+          <t>Pruebas en celulares reales (Android e iPhone): cámara, código, sorteo, crédito y correos en Gmail/Outlook, con informe y capturas</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Carlos Pardo</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="I72" s="21">
@@ -5217,14 +5217,14 @@
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>QA 1 hecha el 23-sep (186 pasan, 2 fallan; informe docs/verificaciones/2026-09-23-verificacion-1.md). Responsive hecha el 23-sep: 2 fallas de scroll corregidas (5.8) y segunda pasada con 0 fallas en 13 anchos (320–1920 px); tests/responsive 10/10. La QA final sigue en 6.3.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Calidad</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Commit de las pantallas nuevas</t>
+          <t>Correr ga-verificador-qa y ga-verificador-responsive</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I73" s="21">
@@ -5268,14 +5268,14 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>Commit d86db86 en develop.</t>
+          <t>QA 1 hecha el 23-sep (186 pasan, 2 fallan; informe docs/verificaciones/2026-09-23-verificacion-1.md). Responsive hecha el 23-sep: 2 fallas de scroll corregidas (5.8) y segunda pasada con 0 fallas en 13 anchos (320–1920 px); tests/responsive 10/10. La QA final sigue en 6.3.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
         <is>
-          <t>P-64</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Abrir el PR de develop a main</t>
+          <t>Commit de las pantallas nuevas</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I74" s="21">
@@ -5319,14 +5319,14 @@
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>25-sep: Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en producción.</t>
+          <t>Commit d86db86 en develop.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>P-82</t>
+          <t>P-64</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Despliegue</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Probar en producción con sesión real de los 3 administradores (ingreso con código OTP y logo del correo)</t>
+          <t>Abrir el PR de develop a main</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
@@ -5370,14 +5370,14 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>25-sep: Sebas entró con su cédula y le apareció el panel de administrador (falta confirmar Ricardo y abogadosprieto). 25-sep: reportado por la sesión principal tras el despliegue de fase 2; falta esta prueba manual antes de cerrar 6.5.</t>
+          <t>25-sep: Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en producción.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>P-86</t>
+          <t>P-82</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -5387,17 +5387,17 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>Despliegue</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>A-01: la ayuda del dominio de correo institucional no se actualiza en vivo al elegir Policía/Ejército</t>
+          <t>Probar en producción con sesión real de los 3 administradores (ingreso con código OTP y logo del correo)</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I76" s="21">
@@ -5421,14 +5421,14 @@
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>25-sep: Sebas confirmó el correo de cualquier dominio (P-85); la ayuda por institución ya no existe. 25-sep: hallazgo de ga-verificador-qa. Condicionado a P-85: si se despliega el cambio a «correo de cualquier dominio» queda superado (ya no habría ayuda de dominio que actualizar); si Sebas decide mantener el chequeo institucional, hay que corregir el texto en vivo. Pendiente de esa decisión.</t>
+          <t>25-sep: Sebas entró con su cédula y le apareció el panel de administrador (falta confirmar Ricardo y abogadosprieto). 25-sep: reportado por la sesión principal tras el despliegue de fase 2; falta esta prueba manual antes de cerrar 6.5.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-86</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -5438,22 +5438,22 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Borrar /login y /dashboard cuando /ingresar y /cuenta funcionen</t>
+          <t>A-01: la ayuda del dominio de correo institucional no se actualiza en vivo al elegir Policía/Ejército</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I77" s="21">
@@ -5472,14 +5472,14 @@
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>Borradas el 23-sep (incluida /dashboard/solicitar, su parte del proxy y los colores heredados de tailwind.config.ts).</t>
+          <t>25-sep: Sebas confirmó el correo de cualquier dominio (P-85); la ayuda por institución ya no existe. 25-sep: hallazgo de ga-verificador-qa. Condicionado a P-85: si se despliega el cambio a «correo de cualquier dominio» queda superado (ya no habría ayuda de dominio que actualizar); si Sebas decide mantener el chequeo institucional, hay que corregir el texto en vivo. Pendiente de esa decisión.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -5489,17 +5489,17 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Revisar si conviene confiar en x-forwarded-for para el límite de intentos por IP</t>
+          <t>Borrar /login y /dashboard cuando /ingresar y /cuenta funcionen</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I78" s="21">
@@ -5523,14 +5523,14 @@
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-verificador-qa el 23-sep. Documentado por ga-funcionalidad-botones como O-01 en lib/servidor/limite.ts: x-forwarded-for/x-real-ip solo son confiables detrás de Vercel (nuestro caso); el límite real por cédula/IP lo hace la app, no Supabase.</t>
+          <t>Borradas el 23-sep (incluida /dashboard/solicitar, su parte del proxy y los colores heredados de tailwind.config.ts).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -5540,17 +5540,17 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Correos</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Confirmar que salen los correos de afiliación (el log queda en la terminal de next dev)</t>
+          <t>Revisar si conviene confiar en x-forwarded-for para el límite de intentos por IP</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I79" s="21">
@@ -5574,14 +5574,14 @@
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>Ya no aplica: el 23-sep se quitaron los correos de afiliación del código (decisión de Sebas).</t>
+          <t>Sugerido por ga-verificador-qa el 23-sep. Documentado por ga-funcionalidad-botones como O-01 en lib/servidor/limite.ts: x-forwarded-for/x-real-ip solo son confiables detrás de Vercel (nuestro caso); el límite real por cédula/IP lo hace la app, no Supabase.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="19" t="inlineStr">
         <is>
-          <t>P-62</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Borrar la cuenta admin de prueba «Test QA» (cédula 1099887766) desde el panel de Supabase</t>
+          <t>Confirmar que salen los correos de afiliación (el log queda en la terminal de next dev)</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I80" s="21">
@@ -5625,14 +5625,14 @@
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>Ya hay 3 administradores reales en producción: Ricardo, Abogados Prieto y Sebas. 24-sep: usuario «Test QA» borrado de producción por Sebas.</t>
+          <t>Ya no aplica: el 23-sep se quitaron los correos de afiliación del código (decisión de Sebas).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="19" t="inlineStr">
         <is>
-          <t>P-71</t>
+          <t>P-62</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -5642,17 +5642,17 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Actualizar tests/e2e b-ingreso, i-despliegue y j-produccion al formato nuevo de máscara de correo</t>
+          <t>Borrar la cuenta admin de prueba «Test QA» (cédula 1099887766) desde el panel de Supabase</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Carlos Pardo</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I81" s="21">
@@ -5676,14 +5676,14 @@
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Parte del alcance que P-58 dejó fuera. Ver P-73. 27-sep: ga-verificador-qa se adelantó al encargo de Carlos y actualizó b-ingreso y j-produccion al formato de máscara con dominio oculto; i-despliegue ya usaba el formato nuevo, no necesitó cambio. Los 3 archivos quedan al día. La actividad 6.15 sigue Pendiente en el plan porque depende de 6.1 (En curso), pero su alcance ya está cubierto.</t>
+          <t>Ya hay 3 administradores reales en producción: Ricardo, Abogados Prieto y Sebas. 24-sep: usuario «Test QA» borrado de producción por Sebas.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>P-94</t>
+          <t>P-71</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra la maquetación C+ de ingreso y afiliación, con Supabase local</t>
+          <t>Actualizar tests/e2e b-ingreso, i-despliegue y j-produccion al formato nuevo de máscara de correo</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>ga-verificador-qa o ga-escritor-tests</t>
+          <t>Carlos Pardo</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="I82" s="21">
@@ -5727,14 +5727,14 @@
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>25-sep: reportado por ga-diseno-a-codigo tras maquetar 2.15 en C+; no se corrieron porque requieren Supabase local. 27-sep: ga-verificador-qa corrió el QA completo contra Supabase local (161/162 escritorio, 129/129 celular) y actualizó f-accesibilidad/utils.ts a la afiliación v2; queda cerrado.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Parte del alcance que P-58 dejó fuera. Ver P-73. 27-sep: ga-verificador-qa se adelantó al encargo de Carlos y actualizó b-ingreso y j-produccion al formato de máscara con dominio oculto; i-despliegue ya usaba el formato nuevo, no necesitó cambio. Los 3 archivos quedan al día. La actividad 6.15 sigue Pendiente en el plan porque depende de 6.1 (En curso), pero su alcance ya está cubierto.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>P-102</t>
+          <t>P-94</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5744,22 +5744,22 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>B-01: sección de testimonios de la landing con corchetes de ejemplo visibles ([Nombre], [Testimonio]...)</t>
+          <t>Correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra la maquetación C+ de ingreso y afiliación, con Supabase local</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-verificador-qa o ga-escritor-tests</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I83" s="21">
@@ -5778,14 +5778,14 @@
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>27-sep: hallazgo Bajo de ga-verificador-qa. Corregido en rediseno-c-plus (commit local fdab456): la sección se oculta mientras tenga textos de ejemplo. Falta el contenido real y decidir si se mantiene la sección, ver P-103.</t>
+          <t>25-sep: reportado por ga-diseno-a-codigo tras maquetar 2.15 en C+; no se corrieron porque requieren Supabase local. 27-sep: ga-verificador-qa corrió el QA completo contra Supabase local (161/162 escritorio, 129/129 celular) y actualizó f-accesibilidad/utils.ts a la afiliación v2; queda cerrado.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="19" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-102</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5795,17 +5795,17 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Mapa de botones: §4 «Nueva solicitud» → /cuenta/solicitar y sección para la ruta /cuenta/solicitar</t>
+          <t>B-01: sección de testimonios de la landing con corchetes de ejemplo visibles ([Nombre], [Testimonio]...)</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I84" s="21">
@@ -5829,49 +5829,49 @@
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>Reportado por ga-diseno-a-codigo. Verificado el 23-sep: docs/mapa-de-botones.md ya tiene §4 «Nueva solicitud» → /cuenta/solicitar (Definido) y §4b /cuenta/solicitar; /dashboard se eliminó.</t>
+          <t>27-sep: hallazgo Bajo de ga-verificador-qa. Corregido en rediseno-c-plus (commit local fdab456): la sección se oculta mientras tenga textos de ejemplo. Falta el contenido real y decidir si se mantiene la sección, ver P-103.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>P-63</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Verificación y cierre</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Fase 2</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Preguntas abiertas de fase 2 para la cooperativa: grados del Ejército, dominios de correo institucionales (hoy solo policia.gov.co, buzonejercito.mil.co, ejercito.mil.co), tiempo que se guardan las fotos y tope de intentos del sorteo</t>
+          <t>Mapa de botones: §4 «Nueva solicitud» → /cuenta/solicitar y sección para la ruta /cuenta/solicitar</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I85" s="21">
@@ -5880,14 +5880,14 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>Ver docs/spec-fase-2.md §Preguntas abiertas.</t>
+          <t>Reportado por ga-diseno-a-codigo. Verificado el 23-sep: docs/mapa-de-botones.md ya tiene §4 «Nueva solicitud» → /cuenta/solicitar (Definido) y §4b /cuenta/solicitar; /dashboard se eliminó.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="19" t="inlineStr">
         <is>
-          <t>P-100</t>
+          <t>P-63</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5897,22 +5897,22 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Fase 2</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Migración de permisos por columna para que un asociado no pueda leer la tasa de interés consultando la API directo con su sesión</t>
+          <t>Preguntas abiertas de fase 2 para la cooperativa: grados del Ejército, dominios de correo institucionales (hoy solo policia.gov.co, buzonejercito.mil.co, ejercito.mil.co), tiempo que se guardan las fotos y tope de intentos del sorteo</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I86" s="21">
@@ -5931,14 +5931,14 @@
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>27-sep: residuo tras corregir P-99. Aunque la tasa ya no llega al payload de /cuenta, la RLS actual le sigue permitiendo al asociado leer sus propias solicitudes y grados_credito por la API REST/PostgREST con su sesión, así que la tasa se puede seguir consultando ahí. Ocultarla del todo requiere una migración de permisos por columna (revoke/grant o vista); pendiente de que Sebas decida si vale la pena.</t>
+          <t>Ver docs/spec-fase-2.md §Preguntas abiertas.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="19" t="inlineStr">
         <is>
-          <t>P-95</t>
+          <t>P-100</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5948,17 +5948,17 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Botón «Escribir por WhatsApp» en el detalle de afiliación del admin</t>
+          <t>Migración de permisos por columna para que un asociado no pueda leer la tasa de interés consultando la API directo con su sesión</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I87" s="21">
@@ -5982,14 +5982,14 @@
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>25-sep: propuesto por el diseño (pieza 3e del lienzo, detalle de afiliación); es funcionalidad nueva, no existía antes. El resto de las piezas 3d–3h usa componentes/rutas que ya existen.</t>
+          <t>27-sep: residuo tras corregir P-99. Aunque la tasa ya no llega al payload de /cuenta, la RLS actual le sigue permitiendo al asociado leer sus propias solicitudes y grados_credito por la API REST/PostgREST con su sesión, así que la tasa se puede seguir consultando ahí. Ocultarla del todo requiere una migración de permisos por columna (revoke/grant o vista); pendiente de que Sebas decida si vale la pena.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
         <is>
-          <t>P-96</t>
+          <t>P-97</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Asignar/desactivar el asesor de un asociado (proceso sin definir)</t>
+          <t>Motivo de rechazo visible en el detalle de afiliación (requiere migración)</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -6033,14 +6033,14 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>25-sep: ga-disenador-lienzo no puede diseñar esta pantalla porque no hay backend ni proceso definido para asignar o desactivar el asesor de un asociado.</t>
+          <t>25-sep: identificado en el detalle de afiliación del lienzo (pieza 3e). Relacionado con P-69/5.10 (Carlos Pardo ya tiene encargada la columna motivo_rechazo y el borrado automático de fotos); se deja anotado aparte para que la cooperativa confirme el texto/proceso del motivo que verá el admin.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="19" t="inlineStr">
         <is>
-          <t>P-97</t>
+          <t>P-98</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -6050,17 +6050,17 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Asesor</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Motivo de rechazo visible en el detalle de afiliación (requiere migración)</t>
+          <t>Confirmar la regla de categorización de asociados ya afiliados como «Aprobada» en las tarjetas/chips de /asesor (pedido D-06 del lienzo)</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="I89" s="21">
@@ -6084,14 +6084,14 @@
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>25-sep: identificado en el detalle de afiliación del lienzo (pieza 3e). Relacionado con P-69/5.10 (Carlos Pardo ya tiene encargada la columna motivo_rechazo y el borrado automático de fotos); se deja anotado aparte para que la cooperativa confirme el texto/proceso del motivo que verá el admin.</t>
+          <t>27-sep: ga-diseno-a-codigo implementó en lib/asesor/resumen.ts (categoriaAfiliacion, TODO(diseno: D-06)) la regla «un asociado ya es, por definición, una afiliación Aprobada» (agrupa origen:'asociado' en la tarjeta/chip «Aprobada» sin importar su estado de crédito), documentada como decisión provisional de la sesión principal. Falta que Sebas o ga-disenador-lienzo la confirmen, o decidan si un asociado con crédito rechazado debe verse distinto, y si la columna «Último crédito» necesita su propio color en el lienzo. Ver docs/diseno/pedidos.md D-06.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="19" t="inlineStr">
         <is>
-          <t>P-98</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -6101,22 +6101,22 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Asesor</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Confirmar la regla de categorización de asociados ya afiliados como «Aprobada» en las tarjetas/chips de /asesor (pedido D-06 del lienzo)</t>
+          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I90" s="21">
@@ -6135,14 +6135,14 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>27-sep: ga-diseno-a-codigo implementó en lib/asesor/resumen.ts (categoriaAfiliacion, TODO(diseno: D-06)) la regla «un asociado ya es, por definición, una afiliación Aprobada» (agrupa origen:'asociado' en la tarjeta/chip «Aprobada» sin importar su estado de crédito), documentada como decisión provisional de la sesión principal. Falta que Sebas o ga-disenador-lienzo la confirmen, o decidan si un asociado con crédito rechazado debe verse distinto, y si la columna «Último crédito» necesita su propio color en el lienzo. Ver docs/diseno/pedidos.md D-06.</t>
+          <t>Por ahora son una sección en /cuenta (#convenios).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="19" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -6152,17 +6152,17 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Preguntar a la cooperativa si los convenios tendrán página propia</t>
+          <t>A 320 px la línea «COOPERATIVA» del logo mide ~5 px de alto (opcional: ocultarla o achicar «Ingresar» bajo 360 px)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I91" s="21">
@@ -6186,14 +6186,14 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>Por ahora son una sección en /cuenta (#convenios).</t>
+          <t>Menor y opcional, reportado por ga-verificador-responsive el 23-sep.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="19" t="inlineStr">
         <is>
-          <t>P-103</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -6203,32 +6203,32 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>D-07: ¿se mantiene la sección de testimonios de la landing? si sí, falta su diseño en la pieza 2a y de dónde salen los testimonios reales</t>
+          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Sebas (ga-auditor-supabase revisa antes)</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="I92" s="21">
@@ -6237,14 +6237,14 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>27-sep: pedido de diseño nuevo de ga-verificador-qa (la sección no tiene respaldo en la pieza 2a del lienzo). Relacionado con P-16 (fotos/cifras/testimonios reales, 5.3).</t>
+          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>A 320 px la línea «COOPERATIVA» del logo mide ~5 px de alto (opcional: ocultarla o achicar «Ingresar» bajo 360 px)</t>
+          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -6269,17 +6269,17 @@
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I93" s="21">
@@ -6288,14 +6288,14 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>Menor y opcional, reportado por ga-verificador-responsive el 23-sep.</t>
+          <t>Apartado «Mis datos» ya maquetado.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="19" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-65</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -6305,22 +6305,22 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Sorteo</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Revisar y aplicar en producción la migración blindar_solicitudes_y_revisiones</t>
+          <t>Decidir si un admin o un asesor pueden participar en el sorteo mensual</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>Sebas (ga-auditor-supabase revisa antes)</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I94" s="21">
@@ -6339,14 +6339,14 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>Verificado con list_migrations el 23-sep: producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones.</t>
+          <t>Sugerido por ga-revisor-seguridad el 24-sep. 24-sep: decidido que solo participan asociados (S-13, ya implementado en participarSorteo).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="19" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-95</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -6356,17 +6356,17 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>P-10: el asociado no cambia su nombre pero sí su teléfono</t>
+          <t>Botón «Escribir por WhatsApp» en el detalle de afiliación del admin</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I95" s="21">
@@ -6390,14 +6390,14 @@
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>Apartado «Mis datos» ya maquetado.</t>
+          <t>25-sep: propuesto por el diseño (pieza 3e del lienzo, detalle de afiliación); es funcionalidad nueva, no existía antes. El resto de las piezas 3d–3h usa componentes/rutas que ya existen. 27-sep: Sebas aprobó la funcionalidad; diseñada (D-08) y maquetada en código (enlace wa.me con mensaje prellenado).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="19" t="inlineStr">
         <is>
-          <t>P-65</t>
+          <t>P-96</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Sorteo</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Decidir si un admin o un asesor pueden participar en el sorteo mensual</t>
+          <t>Asignar/desactivar el asesor de un asociado (proceso sin definir)</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I96" s="21">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-revisor-seguridad el 24-sep. 24-sep: decidido que solo participan asociados (S-13, ya implementado en participarSorteo).</t>
+          <t>25-sep: ga-disenador-lienzo no puede diseñar esta pantalla porque no hay backend ni proceso definido para asignar o desactivar el asesor de un asociado. 27-sep: Sebas aprobó únicamente asignar asesor, y solo cuando la afiliación está aprobada y el asociado todavía no tiene asesor; sin cambiar ni quitar un asesor ya asignado por ahora. Diseñada (D-09, bloque «Asesor» 3i), con Server Action asignarAsesor y bloque conectado en código; estado «ya asignado» persistente al recargar agregado por la sesión principal (commit 3b5ae14).</t>
         </is>
       </c>
     </row>
@@ -6738,27 +6738,27 @@
     <row r="103">
       <c r="A103" s="19" t="inlineStr">
         <is>
-          <t>P-88</t>
+          <t>P-103</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Decisión</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>F2-08: tr_componer_nombre_afiliacion no cubre el update directo de solicitudes_afiliacion.nombre por un admin</t>
+          <t>D-07: ¿se mantiene la sección de testimonios de la landing? si sí, falta su diseño en la pieza 2a y de dónde salen los testimonios reales</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>Cooperativa</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I103" s="21">
@@ -6782,49 +6782,49 @@
       </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>Documentado en docs/auditorias/2026-09-24-fase-2.md; confirmado sin corregir por ga-revisor-seguridad el 25-sep. Un admin puede reescribir `nombre` por SQL directo, y ese texto lo usan el correo «Ingreso aceptado» y el nombre_completo del perfil. Solo afecta a admins.</t>
+          <t>27-sep: pedido de diseño nuevo de ga-verificador-qa (la sección no tiene respaldo en la pieza 2a del lienzo). Relacionado con P-16 (fotos/cifras/testimonios reales, 5.3). 27-sep: Sebas decidió quitar la sección de testimonios de la landing (commit 4c63924).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="19" t="inlineStr">
         <is>
-          <t>P-101</t>
+          <t>P-88</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>H2/M-01: cédula sin enmascarar de las «hermanas» en el detalle de afiliación viajaba completa a un client component</t>
+          <t>F2-08: tr_componer_nombre_afiliacion no cubre el update directo de solicitudes_afiliacion.nombre por un admin</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>Hecho</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I104" s="21">
@@ -6833,14 +6833,14 @@
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>27-sep: hallazgo de ga-revisor-seguridad, confirmado por ga-verificador-qa el mismo día (se mostraba enmascarada en pantalla pero viajaba completa en las props de PanelAfiliacionDetalle / app/admin/afiliaciones/_datos.ts). Corregido en rediseno-c-plus (commit local fdab456): la cédula se enmascara en el servidor antes de llegar al client component.</t>
+          <t>Documentado en docs/auditorias/2026-09-24-fase-2.md; confirmado sin corregir por ga-revisor-seguridad el 25-sep. Un admin puede reescribir `nombre` por SQL directo, y ese texto lo usan el correo «Ingreso aceptado» y el nombre_completo del perfil. Solo afecta a admins.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="19" t="inlineStr">
         <is>
-          <t>P-83</t>
+          <t>P-101</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -6850,17 +6850,17 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Correos</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>S-15: escapar/validar HTML en las variables NOMBRE/MOTIVO de los correos de Resend</t>
+          <t>H2/M-01: cédula sin enmascarar de las «hermanas» en el detalle de afiliación viajaba completa a un client component</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I105" s="21">
@@ -6884,29 +6884,29 @@
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>25-sep: hallazgo de ga-revisor-seguridad (un admin puede meter HTML en perfiles.nombre_completo o en el motivo de rechazo). Corregido en local con pruebas (tests/unit/correo-resend.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02).</t>
+          <t>27-sep: hallazgo de ga-revisor-seguridad, confirmado por ga-verificador-qa el mismo día (se mostraba enmascarada en pantalla pero viajaba completa en las props de PanelAfiliacionDetalle / app/admin/afiliaciones/_datos.ts). Corregido en rediseno-c-plus (commit local fdab456): la cédula se enmascara en el servidor antes de llegar al client component.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="19" t="inlineStr">
         <is>
-          <t>P-84</t>
+          <t>P-83</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>Correos</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>M-01: el número de WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts</t>
+          <t>S-15: escapar/validar HTML en las variables NOMBRE/MOTIVO de los correos de Resend</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I106" s="21">
@@ -6935,34 +6935,34 @@
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>25-sep: hallazgo de ga-verificador-qa (patrón sin la barra invertida de \D/\d; el enlace wa.me sí funciona). Corregido en local con pruebas (tests/unit/config-whatsapp.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02); confirmado en vivo «311 724 1942».</t>
+          <t>25-sep: hallazgo de ga-revisor-seguridad (un admin puede meter HTML en perfiles.nombre_completo o en el motivo de rechazo). Corregido en local con pruebas (tests/unit/correo-resend.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="19" t="inlineStr">
         <is>
-          <t>P-99</t>
+          <t>P-84</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>H1: la tasa de interés de la solicitud viajaba en las props de CuentaCliente aunque nunca se renderizara</t>
+          <t>M-01: el número de WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I107" s="21">
@@ -6986,13 +6986,64 @@
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
+          <t>25-sep: hallazgo de ga-verificador-qa (patrón sin la barra invertida de \D/\d; el enlace wa.me sí funciona). Corregido en local con pruebas (tests/unit/config-whatsapp.test.ts). 25-sep: desplegado con el PR #2 (merge 2c19d02); confirmado en vivo «311 724 1942».</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
+          <t>P-99</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>/cuenta</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>H1: la tasa de interés de la solicitud viajaba en las props de CuentaCliente aunque nunca se renderizara</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I108" s="21">
+        <f>IFERROR(INDEX(Plan!$B$5:$B$76,MATCH(H108,Plan!$A$5:$A$76,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
           <t>27-sep: hallazgo de ga-revisor-seguridad al revisar el rediseño C+; confirmado vigente en producción desde el 25-sep, no introducido por el rediseño. Corregido en rediseno-c-plus (commit local e650033): app/cuenta/page.tsx y lib/cuenta.ts ya no mandan tasa/tasa_interes_mensual a CuentaCliente (client component). Como también afecta a producción (main), conviene llevar este hotfix aparte aunque el rediseño no se fusione todavía; queda a decisión de Sebas. Ver el residuo en P-100.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J107"/>
-  <conditionalFormatting sqref="G5:G107">
+  <autoFilter ref="A4:J108"/>
+  <conditionalFormatting sqref="G5:G108">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$G5="Hecho"</formula>
     </cfRule>
@@ -7006,7 +7057,7 @@
       <formula>$G5="Bloqueado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F107">
+  <conditionalFormatting sqref="F5:F108">
     <cfRule type="expression" priority="5" dxfId="5">
       <formula>$F5="Alta"</formula>
     </cfRule>
@@ -7017,16 +7068,16 @@
       <formula>$F5="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:F107">
+  <conditionalFormatting sqref="A5:F108">
     <cfRule type="expression" priority="8" dxfId="8">
       <formula>$G5="Hecho"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Hecho,En curso,Pendiente,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7438,7 +7489,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -7516,7 +7567,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>4.2, 2.9</t>
+          <t>4.1, 2.9</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -7528,7 +7579,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L9" s="8">
         <f>K9+E9</f>
@@ -7594,7 +7645,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>2.12, 5.5, 3.9</t>
+          <t>2.12, 2.8, 6.11</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
@@ -7603,10 +7654,10 @@
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L10" s="8">
         <f>K10+E10</f>
@@ -7684,7 +7735,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L11" s="8">
         <f>K11+E11</f>
@@ -7750,19 +7801,19 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J12" s="8" t="n">
         <v>64</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L12" s="8">
         <f>K12+E12</f>
@@ -7828,19 +7879,19 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>4.5, 3.3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J13" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L13" s="8">
         <f>K13+E13</f>
@@ -7906,7 +7957,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -7984,7 +8035,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>2.6, 2.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I15" s="18" t="inlineStr">
@@ -7996,7 +8047,7 @@
         <v>6</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L15" s="8">
         <f>K15+E15</f>
@@ -8062,7 +8113,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.6, 2.7</t>
         </is>
       </c>
       <c r="I16" s="18" t="inlineStr">
@@ -8074,7 +8125,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L16" s="8">
         <f>K16+E16</f>
@@ -8140,7 +8191,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>3.4, 3.1</t>
+          <t>2.3, 3.4</t>
         </is>
       </c>
       <c r="I17" s="18" t="inlineStr">
@@ -8218,7 +8269,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>3.1, 2.3</t>
+          <t>3.4, 2.4</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr">
@@ -8296,7 +8347,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>2.3, 6.10</t>
+          <t>2.4, 6.10</t>
         </is>
       </c>
       <c r="I19" s="18" t="inlineStr">
@@ -8374,7 +8425,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I20" s="18" t="inlineStr">
@@ -8383,10 +8434,10 @@
         </is>
       </c>
       <c r="J20" s="8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L20" s="8">
         <f>K20+E20</f>
@@ -8452,7 +8503,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>1.5, 3.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I21" s="18" t="inlineStr">
@@ -8461,10 +8512,10 @@
         </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L21" s="8">
         <f>K21+E21</f>
@@ -8530,7 +8581,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I22" s="18" t="inlineStr">
@@ -8539,7 +8590,7 @@
         </is>
       </c>
       <c r="J22" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K22" s="8" t="n">
         <v>27</v>
@@ -8686,7 +8737,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>3.7, 1.7, 1.6</t>
+          <t>5.2, 1.7, 1.6</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -8695,10 +8746,10 @@
         </is>
       </c>
       <c r="J24" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L24" s="8">
         <f>K24+E24</f>
@@ -8764,19 +8815,19 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L25" s="8">
         <f>K25+E25</f>
@@ -8842,19 +8893,19 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>6.13, 2.8, 4.10</t>
+          <t>4.10, 4.11</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L26" s="8">
         <f>K26+E26</f>
@@ -8920,7 +8971,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>5.1, 4.4</t>
+          <t>4.11, 6.8, 6.4</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
@@ -8929,10 +8980,10 @@
         </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L27" s="8">
         <f>K27+E27</f>
@@ -8998,7 +9049,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>2.5, 2.6</t>
+          <t>1.4, 2.2</t>
         </is>
       </c>
       <c r="I28" s="18" t="inlineStr">
@@ -9010,7 +9061,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L28" s="8">
         <f>K28+E28</f>
@@ -9076,7 +9127,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>6.17, 4.9</t>
+          <t>6.17, 5.8</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr">
@@ -9085,10 +9136,10 @@
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L29" s="8">
         <f>K29+E29</f>
@@ -9154,19 +9205,19 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>2.1, 4.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L30" s="8">
         <f>K30+E30</f>
@@ -9232,7 +9283,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>2.2, 2.5</t>
+          <t>2.5, 2.6</t>
         </is>
       </c>
       <c r="I31" s="18" t="inlineStr">
@@ -9244,7 +9295,7 @@
         <v>6</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L31" s="8">
         <f>K31+E31</f>
@@ -9315,7 +9366,7 @@
       </c>
       <c r="I32" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J32" s="8" t="n">
@@ -9388,19 +9439,19 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.10, 4.5</t>
         </is>
       </c>
       <c r="I33" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J33" s="8" t="n">
         <v>19</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L33" s="8">
         <f>K33+E33</f>
@@ -9466,19 +9517,19 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>5.2, 2.12</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I34" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J34" s="8" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L34" s="8">
         <f>K34+E34</f>
@@ -9544,19 +9595,19 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>1.6, 4.11</t>
+          <t>4.2, 3.7</t>
         </is>
       </c>
       <c r="I35" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J35" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L35" s="8">
         <f>K35+E35</f>
@@ -9622,7 +9673,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>5.7, 6.16, 6.9</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr">
@@ -9631,10 +9682,10 @@
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L36" s="8">
         <f>K36+E36</f>
@@ -9700,12 +9751,12 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>3.5, 6.4</t>
+          <t>3.5, 1.5</t>
         </is>
       </c>
       <c r="I37" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J37" s="8" t="n">
@@ -9778,7 +9829,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.5, 3.9</t>
         </is>
       </c>
       <c r="I38" s="18" t="inlineStr">
@@ -9790,7 +9841,7 @@
         <v>20</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L38" s="8">
         <f>K38+E38</f>
@@ -9856,12 +9907,12 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>5.6, 6.12</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J39" s="8" t="n">
@@ -9934,19 +9985,19 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>2.15, 6.19, 6.11, 5.7</t>
+          <t>3.10, 5.7</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J40" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L40" s="8">
         <f>K40+E40</f>
@@ -10016,19 +10067,19 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>2.10, 2.1</t>
+          <t>3.6, 4.2</t>
         </is>
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J41" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L41" s="8">
         <f>K41+E41</f>
@@ -10094,19 +10145,19 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>3.3, 5.2</t>
+          <t>5.5, 5.2</t>
         </is>
       </c>
       <c r="I42" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L42" s="8">
         <f>K42+E42</f>
@@ -10172,7 +10223,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>5.9, 6.15, 6.7</t>
+          <t>6.7, 1.8, 4.8</t>
         </is>
       </c>
       <c r="I43" s="18" t="inlineStr">
@@ -10184,7 +10235,7 @@
         <v>64</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L43" s="8">
         <f>K43+E43</f>
@@ -10250,12 +10301,12 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>6.6, 5.9</t>
+          <t>4.7, 5.9</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J44" s="8" t="n">
@@ -10328,16 +10379,16 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>6.18, 2.13</t>
         </is>
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J45" s="8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K45" s="8" t="n">
         <v>62</v>
@@ -10411,14 +10462,14 @@
       </c>
       <c r="I46" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J46" s="8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L46" s="8">
         <f>K46+E46</f>
@@ -10484,7 +10535,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.14, 2.15</t>
         </is>
       </c>
       <c r="I47" s="18" t="inlineStr">
@@ -10493,10 +10544,10 @@
         </is>
       </c>
       <c r="J47" s="8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L47" s="8">
         <f>K47+E47</f>
@@ -10562,7 +10613,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.9, 6.13</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr">
@@ -10571,10 +10622,10 @@
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L48" s="8">
         <f>K48+E48</f>
@@ -10640,19 +10691,19 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>4.6, 3.7</t>
+          <t>4.6, 2.12</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J49" s="8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L49" s="8">
         <f>K49+E49</f>
@@ -10718,19 +10769,19 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>6.1, 6.18</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I50" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J50" s="8" t="n">
         <v>64</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L50" s="8">
         <f>K50+E50</f>
@@ -10882,19 +10933,19 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="I52" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J52" s="8" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L52" s="8">
         <f>K52+E52</f>
@@ -10960,7 +11011,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I53" s="18" t="inlineStr">
@@ -10972,7 +11023,7 @@
         <v>64</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L53" s="8">
         <f>K53+E53</f>
@@ -11038,19 +11089,19 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>4.4, 3.10</t>
+          <t>4.4, 6.17</t>
         </is>
       </c>
       <c r="I54" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J54" s="8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L54" s="8">
         <f>K54+E54</f>
@@ -11116,19 +11167,19 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J55" s="8" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L55" s="8">
         <f>K55+E55</f>
@@ -11194,12 +11245,12 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>4.8, 4.7</t>
+          <t>4.8, 6.6</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J56" s="8" t="n">
@@ -11284,7 +11335,7 @@
         <v>64</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="L57" s="8">
         <f>K57+E57</f>
@@ -11350,7 +11401,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>6.2, 5.3</t>
+          <t>5.6, 6.2</t>
         </is>
       </c>
       <c r="I58" s="18" t="inlineStr">
@@ -11440,7 +11491,7 @@
         <v>67</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L59" s="8">
         <f>K59+E59</f>
@@ -11506,7 +11557,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>1.8, 6.14</t>
+          <t>6.12, 6.15, 6.14</t>
         </is>
       </c>
       <c r="I60" s="18" t="inlineStr">
@@ -11515,10 +11566,10 @@
         </is>
       </c>
       <c r="J60" s="8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L60" s="8">
         <f>K60+E60</f>
@@ -11584,19 +11635,19 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I61" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="L61" s="8">
         <f>K61+E61</f>
@@ -11671,10 +11722,10 @@
         </is>
       </c>
       <c r="J62" s="8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L62" s="8">
         <f>K62+E62</f>
@@ -11740,7 +11791,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>5.10, 4.8</t>
+          <t>5.9, 5.10</t>
         </is>
       </c>
       <c r="I63" s="18" t="inlineStr">
@@ -11749,10 +11800,10 @@
         </is>
       </c>
       <c r="J63" s="8" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L63" s="8">
         <f>K63+E63</f>
@@ -11827,10 +11878,10 @@
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="L64" s="8">
         <f>K64+E64</f>
@@ -11896,19 +11947,19 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I65" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J65" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L65" s="8">
         <f>K65+E65</f>
@@ -11974,7 +12025,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I66" s="18" t="inlineStr">
@@ -11983,10 +12034,10 @@
         </is>
       </c>
       <c r="J66" s="8" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L66" s="8">
         <f>K66+E66</f>
@@ -12061,7 +12112,7 @@
         </is>
       </c>
       <c r="J67" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K67" s="8" t="n">
         <v>15</v>
@@ -12130,7 +12181,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I68" s="18" t="inlineStr">
@@ -12139,10 +12190,10 @@
         </is>
       </c>
       <c r="J68" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L68" s="8">
         <f>K68+E68</f>
@@ -12208,7 +12259,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I69" s="18" t="inlineStr">
@@ -12220,7 +12271,7 @@
         <v>64</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L69" s="8">
         <f>K69+E69</f>
@@ -12286,7 +12337,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I70" s="18" t="inlineStr">
@@ -12295,7 +12346,7 @@
         </is>
       </c>
       <c r="J70" s="8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K70" s="8" t="n">
         <v>45</v>
@@ -12376,7 +12427,7 @@
         <v>64</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L71" s="8">
         <f>K71+E71</f>
@@ -12442,19 +12493,19 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I72" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J72" s="8" t="n">
         <v>70</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="L72" s="8">
         <f>K72+E72</f>
@@ -12520,19 +12571,19 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J73" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L73" s="8">
         <f>K73+E73</f>
@@ -12598,7 +12649,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="I74" s="18" t="inlineStr">
@@ -12607,10 +12658,10 @@
         </is>
       </c>
       <c r="J74" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L74" s="8">
         <f>K74+E74</f>
@@ -12676,7 +12727,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>2.13, 3.2</t>
+          <t>5.7, 3.2</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr">
@@ -12685,10 +12736,10 @@
         </is>
       </c>
       <c r="J75" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="K75" s="8" t="n">
         <v>58</v>
-      </c>
-      <c r="K75" s="8" t="n">
-        <v>59</v>
       </c>
       <c r="L75" s="8">
         <f>K75+E75</f>
@@ -12754,7 +12805,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I76" s="18" t="inlineStr">
@@ -12763,10 +12814,10 @@
         </is>
       </c>
       <c r="J76" s="8" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L76" s="8">
         <f>K76+E76</f>
@@ -12782,7 +12833,7 @@
       </c>
       <c r="O76" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P76" s="8" t="inlineStr">
@@ -43144,22 +43195,22 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C9" s="35">
-        <f>Plan!C16</f>
+        <f>Plan!C28</f>
         <v/>
       </c>
       <c r="D9" s="8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E9" s="16">
-        <f>Plan!J16</f>
+        <f>Plan!J28</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>Plan!K16</f>
+        <f>Plan!K28</f>
         <v/>
       </c>
       <c r="G9" s="8">
@@ -43167,11 +43218,11 @@
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>Plan!I16</f>
+        <f>Plan!I28</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>Plan!O16</f>
+        <f>Plan!O28</f>
         <v/>
       </c>
     </row>
@@ -43218,22 +43269,22 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C11" s="35">
-        <f>Plan!C31</f>
+        <f>Plan!C17</f>
         <v/>
       </c>
       <c r="D11" s="8" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E11" s="16">
-        <f>Plan!J31</f>
+        <f>Plan!J17</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>Plan!K31</f>
+        <f>Plan!K17</f>
         <v/>
       </c>
       <c r="G11" s="8">
@@ -43241,11 +43292,11 @@
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>Plan!I31</f>
+        <f>Plan!I17</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>Plan!O31</f>
+        <f>Plan!O17</f>
         <v/>
       </c>
     </row>
@@ -43255,22 +43306,22 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C12" s="35">
-        <f>Plan!C17</f>
+        <f>Plan!C15</f>
         <v/>
       </c>
       <c r="D12" s="8" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E12" s="16">
-        <f>Plan!J17</f>
+        <f>Plan!J15</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>Plan!K17</f>
+        <f>Plan!K15</f>
         <v/>
       </c>
       <c r="G12" s="8">
@@ -43278,11 +43329,11 @@
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>Plan!I17</f>
+        <f>Plan!I15</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>Plan!O17</f>
+        <f>Plan!O15</f>
         <v/>
       </c>
     </row>
@@ -43292,22 +43343,22 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C13" s="35">
-        <f>Plan!C28</f>
+        <f>Plan!C31</f>
         <v/>
       </c>
       <c r="D13" s="8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E13" s="16">
-        <f>Plan!J28</f>
+        <f>Plan!J31</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>Plan!K28</f>
+        <f>Plan!K31</f>
         <v/>
       </c>
       <c r="G13" s="8">
@@ -43315,11 +43366,11 @@
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>Plan!I28</f>
+        <f>Plan!I31</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>Plan!O28</f>
+        <f>Plan!O31</f>
         <v/>
       </c>
     </row>
@@ -43366,22 +43417,22 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C15" s="35">
-        <f>Plan!C15</f>
+        <f>Plan!C16</f>
         <v/>
       </c>
       <c r="D15" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E15" s="16">
-        <f>Plan!J15</f>
+        <f>Plan!J16</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>Plan!K15</f>
+        <f>Plan!K16</f>
         <v/>
       </c>
       <c r="G15" s="8">
@@ -43389,11 +43440,11 @@
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>Plan!I15</f>
+        <f>Plan!I16</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>Plan!O15</f>
+        <f>Plan!O16</f>
         <v/>
       </c>
     </row>
@@ -43551,22 +43602,22 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C20" s="35">
-        <f>Plan!C61</f>
+        <f>Plan!C9</f>
         <v/>
       </c>
       <c r="D20" s="8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E20" s="16">
-        <f>Plan!J61</f>
+        <f>Plan!J9</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>Plan!K61</f>
+        <f>Plan!K9</f>
         <v/>
       </c>
       <c r="G20" s="8">
@@ -43574,11 +43625,11 @@
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>Plan!I61</f>
+        <f>Plan!I9</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>Plan!O61</f>
+        <f>Plan!O9</f>
         <v/>
       </c>
     </row>
@@ -43588,22 +43639,22 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="C21" s="35">
-        <f>Plan!C9</f>
+        <f>Plan!C21</f>
         <v/>
       </c>
       <c r="D21" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E21" s="16">
-        <f>Plan!J9</f>
+        <f>Plan!J21</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>Plan!K9</f>
+        <f>Plan!K21</f>
         <v/>
       </c>
       <c r="G21" s="8">
@@ -43611,11 +43662,11 @@
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>Plan!I9</f>
+        <f>Plan!I21</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>Plan!O9</f>
+        <f>Plan!O21</f>
         <v/>
       </c>
     </row>
@@ -43625,22 +43676,22 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C22" s="35">
-        <f>Plan!C38</f>
+        <f>Plan!C13</f>
         <v/>
       </c>
       <c r="D22" s="8" t="n">
         <v>16</v>
       </c>
       <c r="E22" s="16">
-        <f>Plan!J38</f>
+        <f>Plan!J13</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>Plan!K38</f>
+        <f>Plan!K13</f>
         <v/>
       </c>
       <c r="G22" s="8">
@@ -43648,11 +43699,11 @@
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>Plan!I38</f>
+        <f>Plan!I13</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>Plan!O38</f>
+        <f>Plan!O13</f>
         <v/>
       </c>
     </row>
@@ -43662,22 +43713,22 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C23" s="35">
-        <f>Plan!C21</f>
+        <f>Plan!C30</f>
         <v/>
       </c>
       <c r="D23" s="8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E23" s="16">
-        <f>Plan!J21</f>
+        <f>Plan!J30</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>Plan!K21</f>
+        <f>Plan!K30</f>
         <v/>
       </c>
       <c r="G23" s="8">
@@ -43685,11 +43736,11 @@
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>Plan!I21</f>
+        <f>Plan!I30</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>Plan!O21</f>
+        <f>Plan!O30</f>
         <v/>
       </c>
     </row>
@@ -43736,22 +43787,22 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C25" s="35">
-        <f>Plan!C41</f>
+        <f>Plan!C22</f>
         <v/>
       </c>
       <c r="D25" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E25" s="16">
-        <f>Plan!J41</f>
+        <f>Plan!J22</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>Plan!K41</f>
+        <f>Plan!K22</f>
         <v/>
       </c>
       <c r="G25" s="8">
@@ -43759,11 +43810,11 @@
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>Plan!I41</f>
+        <f>Plan!I22</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>Plan!O41</f>
+        <f>Plan!O22</f>
         <v/>
       </c>
     </row>
@@ -43773,22 +43824,22 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C26" s="35">
-        <f>Plan!C22</f>
+        <f>Plan!C41</f>
         <v/>
       </c>
       <c r="D26" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E26" s="16">
-        <f>Plan!J22</f>
+        <f>Plan!J41</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>Plan!K22</f>
+        <f>Plan!K41</f>
         <v/>
       </c>
       <c r="G26" s="8">
@@ -43796,11 +43847,11 @@
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>Plan!I22</f>
+        <f>Plan!I41</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>Plan!O22</f>
+        <f>Plan!O41</f>
         <v/>
       </c>
     </row>
@@ -43810,22 +43861,22 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C27" s="35">
-        <f>Plan!C13</f>
+        <f>Plan!C38</f>
         <v/>
       </c>
       <c r="D27" s="8" t="n">
         <v>16</v>
       </c>
       <c r="E27" s="16">
-        <f>Plan!J13</f>
+        <f>Plan!J38</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>Plan!K13</f>
+        <f>Plan!K38</f>
         <v/>
       </c>
       <c r="G27" s="8">
@@ -43833,11 +43884,11 @@
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>Plan!I13</f>
+        <f>Plan!I38</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>Plan!O13</f>
+        <f>Plan!O38</f>
         <v/>
       </c>
     </row>
@@ -43847,22 +43898,22 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C28" s="35">
-        <f>Plan!C30</f>
+        <f>Plan!C35</f>
         <v/>
       </c>
       <c r="D28" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E28" s="16">
-        <f>Plan!J30</f>
+        <f>Plan!J35</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>Plan!K30</f>
+        <f>Plan!K35</f>
         <v/>
       </c>
       <c r="G28" s="8">
@@ -43870,11 +43921,11 @@
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>Plan!I30</f>
+        <f>Plan!I35</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>Plan!O30</f>
+        <f>Plan!O35</f>
         <v/>
       </c>
     </row>
@@ -43884,22 +43935,22 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="C29" s="35">
-        <f>Plan!C42</f>
+        <f>Plan!C34</f>
         <v/>
       </c>
       <c r="D29" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29" s="16">
-        <f>Plan!J42</f>
+        <f>Plan!J34</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>Plan!K42</f>
+        <f>Plan!K34</f>
         <v/>
       </c>
       <c r="G29" s="8">
@@ -43907,11 +43958,11 @@
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>Plan!I42</f>
+        <f>Plan!I34</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>Plan!O42</f>
+        <f>Plan!O34</f>
         <v/>
       </c>
     </row>
@@ -43921,22 +43972,22 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C30" s="35">
-        <f>Plan!C49</f>
+        <f>Plan!C42</f>
         <v/>
       </c>
       <c r="D30" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E30" s="16">
-        <f>Plan!J49</f>
+        <f>Plan!J42</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>Plan!K49</f>
+        <f>Plan!K42</f>
         <v/>
       </c>
       <c r="G30" s="8">
@@ -43944,11 +43995,11 @@
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>Plan!I49</f>
+        <f>Plan!I42</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>Plan!O49</f>
+        <f>Plan!O42</f>
         <v/>
       </c>
     </row>
@@ -43958,22 +44009,22 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C31" s="35">
-        <f>Plan!C34</f>
+        <f>Plan!C52</f>
         <v/>
       </c>
       <c r="D31" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E31" s="16">
-        <f>Plan!J34</f>
+        <f>Plan!J52</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>Plan!K34</f>
+        <f>Plan!K52</f>
         <v/>
       </c>
       <c r="G31" s="8">
@@ -43981,11 +44032,11 @@
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>Plan!I34</f>
+        <f>Plan!I52</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>Plan!O34</f>
+        <f>Plan!O52</f>
         <v/>
       </c>
     </row>
@@ -43995,22 +44046,22 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C32" s="35">
-        <f>Plan!C24</f>
+        <f>Plan!C49</f>
         <v/>
       </c>
       <c r="D32" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E32" s="16">
-        <f>Plan!J24</f>
+        <f>Plan!J49</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>Plan!K24</f>
+        <f>Plan!K49</f>
         <v/>
       </c>
       <c r="G32" s="8">
@@ -44018,11 +44069,11 @@
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>Plan!I24</f>
+        <f>Plan!I49</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>Plan!O24</f>
+        <f>Plan!O49</f>
         <v/>
       </c>
     </row>
@@ -44032,22 +44083,22 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="C33" s="35">
-        <f>Plan!C11</f>
+        <f>Plan!C24</f>
         <v/>
       </c>
       <c r="D33" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E33" s="16">
-        <f>Plan!J11</f>
+        <f>Plan!J24</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>Plan!K11</f>
+        <f>Plan!K24</f>
         <v/>
       </c>
       <c r="G33" s="8">
@@ -44055,11 +44106,11 @@
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>Plan!I11</f>
+        <f>Plan!I24</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>Plan!O11</f>
+        <f>Plan!O24</f>
         <v/>
       </c>
     </row>
@@ -44069,22 +44120,22 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C34" s="35">
-        <f>Plan!C10</f>
+        <f>Plan!C11</f>
         <v/>
       </c>
       <c r="D34" s="8" t="n">
         <v>11</v>
       </c>
       <c r="E34" s="16">
-        <f>Plan!J10</f>
+        <f>Plan!J11</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>Plan!K10</f>
+        <f>Plan!K11</f>
         <v/>
       </c>
       <c r="G34" s="8">
@@ -44092,11 +44143,11 @@
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>Plan!I10</f>
+        <f>Plan!I11</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>Plan!O10</f>
+        <f>Plan!O11</f>
         <v/>
       </c>
     </row>
@@ -44106,22 +44157,22 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C35" s="35">
-        <f>Plan!C52</f>
+        <f>Plan!C10</f>
         <v/>
       </c>
       <c r="D35" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E35" s="16">
-        <f>Plan!J52</f>
+        <f>Plan!J10</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>Plan!K52</f>
+        <f>Plan!K10</f>
         <v/>
       </c>
       <c r="G35" s="8">
@@ -44129,11 +44180,11 @@
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>Plan!I52</f>
+        <f>Plan!I10</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>Plan!O52</f>
+        <f>Plan!O10</f>
         <v/>
       </c>
     </row>
@@ -44143,22 +44194,22 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C36" s="35">
-        <f>Plan!C35</f>
+        <f>Plan!C20</f>
         <v/>
       </c>
       <c r="D36" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E36" s="16">
-        <f>Plan!J35</f>
+        <f>Plan!J20</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>Plan!K35</f>
+        <f>Plan!K20</f>
         <v/>
       </c>
       <c r="G36" s="8">
@@ -44166,11 +44217,11 @@
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>Plan!I35</f>
+        <f>Plan!I20</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>Plan!O35</f>
+        <f>Plan!O20</f>
         <v/>
       </c>
     </row>
@@ -44180,22 +44231,22 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="C37" s="35">
-        <f>Plan!C47</f>
+        <f>Plan!C68</f>
         <v/>
       </c>
       <c r="D37" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E37" s="16">
-        <f>Plan!J47</f>
+        <f>Plan!J68</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>Plan!K47</f>
+        <f>Plan!K68</f>
         <v/>
       </c>
       <c r="G37" s="8">
@@ -44203,11 +44254,11 @@
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>Plan!I47</f>
+        <f>Plan!I68</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>Plan!O47</f>
+        <f>Plan!O68</f>
         <v/>
       </c>
     </row>
@@ -44217,22 +44268,22 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C38" s="35">
-        <f>Plan!C26</f>
+        <f>Plan!C66</f>
         <v/>
       </c>
       <c r="D38" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E38" s="16">
-        <f>Plan!J26</f>
+        <f>Plan!J66</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>Plan!K26</f>
+        <f>Plan!K66</f>
         <v/>
       </c>
       <c r="G38" s="8">
@@ -44240,11 +44291,11 @@
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>Plan!I26</f>
+        <f>Plan!I66</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>Plan!O26</f>
+        <f>Plan!O66</f>
         <v/>
       </c>
     </row>
@@ -44254,22 +44305,22 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C39" s="35">
-        <f>Plan!C70</f>
+        <f>Plan!C48</f>
         <v/>
       </c>
       <c r="D39" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" s="16">
-        <f>Plan!J70</f>
+        <f>Plan!J48</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>Plan!K70</f>
+        <f>Plan!K48</f>
         <v/>
       </c>
       <c r="G39" s="8">
@@ -44277,11 +44328,11 @@
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>Plan!I70</f>
+        <f>Plan!I48</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>Plan!O70</f>
+        <f>Plan!O48</f>
         <v/>
       </c>
     </row>
@@ -44291,22 +44342,22 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="C40" s="35">
-        <f>Plan!C20</f>
+        <f>Plan!C70</f>
         <v/>
       </c>
       <c r="D40" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E40" s="16">
-        <f>Plan!J20</f>
+        <f>Plan!J70</f>
         <v/>
       </c>
       <c r="F40" s="16">
-        <f>Plan!K20</f>
+        <f>Plan!K70</f>
         <v/>
       </c>
       <c r="G40" s="8">
@@ -44314,11 +44365,11 @@
         <v/>
       </c>
       <c r="H40" s="16">
-        <f>Plan!I20</f>
+        <f>Plan!I70</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>Plan!O20</f>
+        <f>Plan!O70</f>
         <v/>
       </c>
     </row>
@@ -44328,22 +44379,22 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="C41" s="35">
-        <f>Plan!C46</f>
+        <f>Plan!C26</f>
         <v/>
       </c>
       <c r="D41" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E41" s="16">
-        <f>Plan!J46</f>
+        <f>Plan!J26</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>Plan!K46</f>
+        <f>Plan!K26</f>
         <v/>
       </c>
       <c r="G41" s="8">
@@ -44351,11 +44402,11 @@
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>Plan!I46</f>
+        <f>Plan!I26</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>Plan!O46</f>
+        <f>Plan!O26</f>
         <v/>
       </c>
     </row>
@@ -44365,22 +44416,22 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C42" s="35">
-        <f>Plan!C27</f>
+        <f>Plan!C46</f>
         <v/>
       </c>
       <c r="D42" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E42" s="16">
-        <f>Plan!J27</f>
+        <f>Plan!J46</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>Plan!K27</f>
+        <f>Plan!K46</f>
         <v/>
       </c>
       <c r="G42" s="8">
@@ -44388,11 +44439,11 @@
         <v/>
       </c>
       <c r="H42" s="16">
-        <f>Plan!I27</f>
+        <f>Plan!I46</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>Plan!O27</f>
+        <f>Plan!O46</f>
         <v/>
       </c>
     </row>
@@ -44402,22 +44453,22 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="C43" s="35">
-        <f>Plan!C48</f>
+        <f>Plan!C47</f>
         <v/>
       </c>
       <c r="D43" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43" s="16">
-        <f>Plan!J48</f>
+        <f>Plan!J47</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>Plan!K48</f>
+        <f>Plan!K47</f>
         <v/>
       </c>
       <c r="G43" s="8">
@@ -44425,11 +44476,11 @@
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>Plan!I48</f>
+        <f>Plan!I47</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>Plan!O48</f>
+        <f>Plan!O47</f>
         <v/>
       </c>
     </row>
@@ -44439,22 +44490,22 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C44" s="35">
-        <f>Plan!C40</f>
+        <f>Plan!C27</f>
         <v/>
       </c>
       <c r="D44" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E44" s="16">
-        <f>Plan!J40</f>
+        <f>Plan!J27</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>Plan!K40</f>
+        <f>Plan!K27</f>
         <v/>
       </c>
       <c r="G44" s="8">
@@ -44462,11 +44513,11 @@
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>Plan!I40</f>
+        <f>Plan!I27</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>Plan!O40</f>
+        <f>Plan!O27</f>
         <v/>
       </c>
     </row>
@@ -44476,22 +44527,22 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="C45" s="35">
-        <f>Plan!C74</f>
+        <f>Plan!C65</f>
         <v/>
       </c>
       <c r="D45" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45" s="16">
-        <f>Plan!J74</f>
+        <f>Plan!J65</f>
         <v/>
       </c>
       <c r="F45" s="16">
-        <f>Plan!K74</f>
+        <f>Plan!K65</f>
         <v/>
       </c>
       <c r="G45" s="8">
@@ -44499,11 +44550,11 @@
         <v/>
       </c>
       <c r="H45" s="16">
-        <f>Plan!I74</f>
+        <f>Plan!I65</f>
         <v/>
       </c>
       <c r="I45" s="16">
-        <f>Plan!O74</f>
+        <f>Plan!O65</f>
         <v/>
       </c>
     </row>
@@ -44513,22 +44564,22 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="C46" s="35">
-        <f>Plan!C68</f>
+        <f>Plan!C61</f>
         <v/>
       </c>
       <c r="D46" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E46" s="16">
-        <f>Plan!J68</f>
+        <f>Plan!J61</f>
         <v/>
       </c>
       <c r="F46" s="16">
-        <f>Plan!K68</f>
+        <f>Plan!K61</f>
         <v/>
       </c>
       <c r="G46" s="8">
@@ -44536,11 +44587,11 @@
         <v/>
       </c>
       <c r="H46" s="16">
-        <f>Plan!I68</f>
+        <f>Plan!I61</f>
         <v/>
       </c>
       <c r="I46" s="16">
-        <f>Plan!O68</f>
+        <f>Plan!O61</f>
         <v/>
       </c>
     </row>
@@ -44550,22 +44601,22 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="C47" s="35">
-        <f>Plan!C54</f>
+        <f>Plan!C73</f>
         <v/>
       </c>
       <c r="D47" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E47" s="16">
-        <f>Plan!J54</f>
+        <f>Plan!J73</f>
         <v/>
       </c>
       <c r="F47" s="16">
-        <f>Plan!K54</f>
+        <f>Plan!K73</f>
         <v/>
       </c>
       <c r="G47" s="8">
@@ -44573,11 +44624,11 @@
         <v/>
       </c>
       <c r="H47" s="16">
-        <f>Plan!I54</f>
+        <f>Plan!I73</f>
         <v/>
       </c>
       <c r="I47" s="16">
-        <f>Plan!O54</f>
+        <f>Plan!O73</f>
         <v/>
       </c>
     </row>
@@ -44587,22 +44638,22 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="C48" s="35">
-        <f>Plan!C36</f>
+        <f>Plan!C74</f>
         <v/>
       </c>
       <c r="D48" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E48" s="16">
-        <f>Plan!J36</f>
+        <f>Plan!J74</f>
         <v/>
       </c>
       <c r="F48" s="16">
-        <f>Plan!K36</f>
+        <f>Plan!K74</f>
         <v/>
       </c>
       <c r="G48" s="8">
@@ -44610,11 +44661,11 @@
         <v/>
       </c>
       <c r="H48" s="16">
-        <f>Plan!I36</f>
+        <f>Plan!I74</f>
         <v/>
       </c>
       <c r="I48" s="16">
-        <f>Plan!O36</f>
+        <f>Plan!O74</f>
         <v/>
       </c>
     </row>
@@ -44624,22 +44675,22 @@
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C49" s="35">
-        <f>Plan!C73</f>
+        <f>Plan!C36</f>
         <v/>
       </c>
       <c r="D49" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E49" s="16">
-        <f>Plan!J73</f>
+        <f>Plan!J36</f>
         <v/>
       </c>
       <c r="F49" s="16">
-        <f>Plan!K73</f>
+        <f>Plan!K36</f>
         <v/>
       </c>
       <c r="G49" s="8">
@@ -44647,11 +44698,11 @@
         <v/>
       </c>
       <c r="H49" s="16">
-        <f>Plan!I73</f>
+        <f>Plan!I36</f>
         <v/>
       </c>
       <c r="I49" s="16">
-        <f>Plan!O73</f>
+        <f>Plan!O36</f>
         <v/>
       </c>
     </row>
@@ -44661,22 +44712,22 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C50" s="35">
-        <f>Plan!C66</f>
+        <f>Plan!C40</f>
         <v/>
       </c>
       <c r="D50" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" s="16">
-        <f>Plan!J66</f>
+        <f>Plan!J40</f>
         <v/>
       </c>
       <c r="F50" s="16">
-        <f>Plan!K66</f>
+        <f>Plan!K40</f>
         <v/>
       </c>
       <c r="G50" s="8">
@@ -44684,11 +44735,11 @@
         <v/>
       </c>
       <c r="H50" s="16">
-        <f>Plan!I66</f>
+        <f>Plan!I40</f>
         <v/>
       </c>
       <c r="I50" s="16">
-        <f>Plan!O66</f>
+        <f>Plan!O40</f>
         <v/>
       </c>
     </row>
@@ -44698,22 +44749,22 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="C51" s="35">
-        <f>Plan!C65</f>
+        <f>Plan!C54</f>
         <v/>
       </c>
       <c r="D51" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E51" s="16">
-        <f>Plan!J65</f>
+        <f>Plan!J54</f>
         <v/>
       </c>
       <c r="F51" s="16">
-        <f>Plan!K65</f>
+        <f>Plan!K54</f>
         <v/>
       </c>
       <c r="G51" s="8">
@@ -44721,11 +44772,11 @@
         <v/>
       </c>
       <c r="H51" s="16">
-        <f>Plan!I65</f>
+        <f>Plan!I54</f>
         <v/>
       </c>
       <c r="I51" s="16">
-        <f>Plan!O65</f>
+        <f>Plan!O54</f>
         <v/>
       </c>
     </row>
@@ -44735,22 +44786,22 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="C52" s="35">
-        <f>Plan!C55</f>
+        <f>Plan!C75</f>
         <v/>
       </c>
       <c r="D52" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E52" s="16">
-        <f>Plan!J55</f>
+        <f>Plan!J75</f>
         <v/>
       </c>
       <c r="F52" s="16">
-        <f>Plan!K55</f>
+        <f>Plan!K75</f>
         <v/>
       </c>
       <c r="G52" s="8">
@@ -44758,11 +44809,11 @@
         <v/>
       </c>
       <c r="H52" s="16">
-        <f>Plan!I55</f>
+        <f>Plan!I75</f>
         <v/>
       </c>
       <c r="I52" s="16">
-        <f>Plan!O55</f>
+        <f>Plan!O75</f>
         <v/>
       </c>
     </row>
@@ -44772,22 +44823,22 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C53" s="35">
-        <f>Plan!C75</f>
+        <f>Plan!C29</f>
         <v/>
       </c>
       <c r="D53" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53" s="16">
-        <f>Plan!J75</f>
+        <f>Plan!J29</f>
         <v/>
       </c>
       <c r="F53" s="16">
-        <f>Plan!K75</f>
+        <f>Plan!K29</f>
         <v/>
       </c>
       <c r="G53" s="8">
@@ -44795,11 +44846,11 @@
         <v/>
       </c>
       <c r="H53" s="16">
-        <f>Plan!I75</f>
+        <f>Plan!I29</f>
         <v/>
       </c>
       <c r="I53" s="16">
-        <f>Plan!O75</f>
+        <f>Plan!O29</f>
         <v/>
       </c>
     </row>
@@ -44809,22 +44860,22 @@
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="C54" s="35">
-        <f>Plan!C25</f>
+        <f>Plan!C55</f>
         <v/>
       </c>
       <c r="D54" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E54" s="16">
-        <f>Plan!J25</f>
+        <f>Plan!J55</f>
         <v/>
       </c>
       <c r="F54" s="16">
-        <f>Plan!K25</f>
+        <f>Plan!K55</f>
         <v/>
       </c>
       <c r="G54" s="8">
@@ -44832,11 +44883,11 @@
         <v/>
       </c>
       <c r="H54" s="16">
-        <f>Plan!I25</f>
+        <f>Plan!I55</f>
         <v/>
       </c>
       <c r="I54" s="16">
-        <f>Plan!O25</f>
+        <f>Plan!O55</f>
         <v/>
       </c>
     </row>
@@ -44846,22 +44897,22 @@
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C55" s="35">
-        <f>Plan!C29</f>
+        <f>Plan!C45</f>
         <v/>
       </c>
       <c r="D55" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" s="16">
-        <f>Plan!J29</f>
+        <f>Plan!J45</f>
         <v/>
       </c>
       <c r="F55" s="16">
-        <f>Plan!K29</f>
+        <f>Plan!K45</f>
         <v/>
       </c>
       <c r="G55" s="8">
@@ -44869,11 +44920,11 @@
         <v/>
       </c>
       <c r="H55" s="16">
-        <f>Plan!I29</f>
+        <f>Plan!I45</f>
         <v/>
       </c>
       <c r="I55" s="16">
-        <f>Plan!O29</f>
+        <f>Plan!O45</f>
         <v/>
       </c>
     </row>
@@ -44883,22 +44934,22 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="C56" s="35">
-        <f>Plan!C45</f>
+        <f>Plan!C76</f>
         <v/>
       </c>
       <c r="D56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="16">
-        <f>Plan!J45</f>
+        <f>Plan!J76</f>
         <v/>
       </c>
       <c r="F56" s="16">
-        <f>Plan!K45</f>
+        <f>Plan!K76</f>
         <v/>
       </c>
       <c r="G56" s="8">
@@ -44906,11 +44957,11 @@
         <v/>
       </c>
       <c r="H56" s="16">
-        <f>Plan!I45</f>
+        <f>Plan!I76</f>
         <v/>
       </c>
       <c r="I56" s="16">
-        <f>Plan!O45</f>
+        <f>Plan!O76</f>
         <v/>
       </c>
     </row>
@@ -44920,22 +44971,22 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C57" s="35">
-        <f>Plan!C23</f>
+        <f>Plan!C25</f>
         <v/>
       </c>
       <c r="D57" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E57" s="16">
-        <f>Plan!J23</f>
+        <f>Plan!J25</f>
         <v/>
       </c>
       <c r="F57" s="16">
-        <f>Plan!K23</f>
+        <f>Plan!K25</f>
         <v/>
       </c>
       <c r="G57" s="8">
@@ -44943,11 +44994,11 @@
         <v/>
       </c>
       <c r="H57" s="16">
-        <f>Plan!I23</f>
+        <f>Plan!I25</f>
         <v/>
       </c>
       <c r="I57" s="16">
-        <f>Plan!O23</f>
+        <f>Plan!O25</f>
         <v/>
       </c>
     </row>
@@ -44957,22 +45008,22 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="C58" s="35">
-        <f>Plan!C51</f>
+        <f>Plan!C23</f>
         <v/>
       </c>
       <c r="D58" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E58" s="16">
-        <f>Plan!J51</f>
+        <f>Plan!J23</f>
         <v/>
       </c>
       <c r="F58" s="16">
-        <f>Plan!K51</f>
+        <f>Plan!K23</f>
         <v/>
       </c>
       <c r="G58" s="8">
@@ -44980,11 +45031,11 @@
         <v/>
       </c>
       <c r="H58" s="16">
-        <f>Plan!I51</f>
+        <f>Plan!I23</f>
         <v/>
       </c>
       <c r="I58" s="16">
-        <f>Plan!O51</f>
+        <f>Plan!O23</f>
         <v/>
       </c>
     </row>
@@ -44994,22 +45045,22 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="C59" s="35">
-        <f>Plan!C39</f>
+        <f>Plan!C51</f>
         <v/>
       </c>
       <c r="D59" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E59" s="16">
-        <f>Plan!J39</f>
+        <f>Plan!J51</f>
         <v/>
       </c>
       <c r="F59" s="16">
-        <f>Plan!K39</f>
+        <f>Plan!K51</f>
         <v/>
       </c>
       <c r="G59" s="8">
@@ -45017,11 +45068,11 @@
         <v/>
       </c>
       <c r="H59" s="16">
-        <f>Plan!I39</f>
+        <f>Plan!I51</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>Plan!O39</f>
+        <f>Plan!O51</f>
         <v/>
       </c>
     </row>
@@ -45031,22 +45082,22 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C60" s="35">
-        <f>Plan!C53</f>
+        <f>Plan!C39</f>
         <v/>
       </c>
       <c r="D60" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E60" s="16">
-        <f>Plan!J53</f>
+        <f>Plan!J39</f>
         <v/>
       </c>
       <c r="F60" s="16">
-        <f>Plan!K53</f>
+        <f>Plan!K39</f>
         <v/>
       </c>
       <c r="G60" s="8">
@@ -45054,11 +45105,11 @@
         <v/>
       </c>
       <c r="H60" s="16">
-        <f>Plan!I53</f>
+        <f>Plan!I39</f>
         <v/>
       </c>
       <c r="I60" s="16">
-        <f>Plan!O53</f>
+        <f>Plan!O39</f>
         <v/>
       </c>
     </row>
@@ -45068,22 +45119,22 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C61" s="35">
-        <f>Plan!C69</f>
+        <f>Plan!C50</f>
         <v/>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E61" s="16">
-        <f>Plan!J69</f>
+        <f>Plan!J50</f>
         <v/>
       </c>
       <c r="F61" s="16">
-        <f>Plan!K69</f>
+        <f>Plan!K50</f>
         <v/>
       </c>
       <c r="G61" s="8">
@@ -45091,11 +45142,11 @@
         <v/>
       </c>
       <c r="H61" s="16">
-        <f>Plan!I69</f>
+        <f>Plan!I50</f>
         <v/>
       </c>
       <c r="I61" s="16">
-        <f>Plan!O69</f>
+        <f>Plan!O50</f>
         <v/>
       </c>
     </row>
@@ -45142,22 +45193,22 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="C63" s="35">
-        <f>Plan!C59</f>
+        <f>Plan!C53</f>
         <v/>
       </c>
       <c r="D63" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E63" s="16">
-        <f>Plan!J59</f>
+        <f>Plan!J53</f>
         <v/>
       </c>
       <c r="F63" s="16">
-        <f>Plan!K59</f>
+        <f>Plan!K53</f>
         <v/>
       </c>
       <c r="G63" s="8">
@@ -45165,11 +45216,11 @@
         <v/>
       </c>
       <c r="H63" s="16">
-        <f>Plan!I59</f>
+        <f>Plan!I53</f>
         <v/>
       </c>
       <c r="I63" s="16">
-        <f>Plan!O59</f>
+        <f>Plan!O53</f>
         <v/>
       </c>
     </row>
@@ -45179,22 +45230,22 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="C64" s="35">
-        <f>Plan!C50</f>
+        <f>Plan!C59</f>
         <v/>
       </c>
       <c r="D64" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E64" s="16">
-        <f>Plan!J50</f>
+        <f>Plan!J59</f>
         <v/>
       </c>
       <c r="F64" s="16">
-        <f>Plan!K50</f>
+        <f>Plan!K59</f>
         <v/>
       </c>
       <c r="G64" s="8">
@@ -45202,11 +45253,11 @@
         <v/>
       </c>
       <c r="H64" s="16">
-        <f>Plan!I50</f>
+        <f>Plan!I59</f>
         <v/>
       </c>
       <c r="I64" s="16">
-        <f>Plan!O50</f>
+        <f>Plan!O59</f>
         <v/>
       </c>
     </row>
@@ -45216,22 +45267,22 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="C65" s="35">
-        <f>Plan!C76</f>
+        <f>Plan!C60</f>
         <v/>
       </c>
       <c r="D65" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E65" s="16">
-        <f>Plan!J76</f>
+        <f>Plan!J60</f>
         <v/>
       </c>
       <c r="F65" s="16">
-        <f>Plan!K76</f>
+        <f>Plan!K60</f>
         <v/>
       </c>
       <c r="G65" s="8">
@@ -45239,11 +45290,11 @@
         <v/>
       </c>
       <c r="H65" s="16">
-        <f>Plan!I76</f>
+        <f>Plan!I60</f>
         <v/>
       </c>
       <c r="I65" s="16">
-        <f>Plan!O76</f>
+        <f>Plan!O60</f>
         <v/>
       </c>
     </row>
@@ -45253,22 +45304,22 @@
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="C66" s="35">
-        <f>Plan!C60</f>
+        <f>Plan!C69</f>
         <v/>
       </c>
       <c r="D66" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E66" s="16">
-        <f>Plan!J60</f>
+        <f>Plan!J69</f>
         <v/>
       </c>
       <c r="F66" s="16">
-        <f>Plan!K60</f>
+        <f>Plan!K69</f>
         <v/>
       </c>
       <c r="G66" s="8">
@@ -45276,11 +45327,11 @@
         <v/>
       </c>
       <c r="H66" s="16">
-        <f>Plan!I60</f>
+        <f>Plan!I69</f>
         <v/>
       </c>
       <c r="I66" s="16">
-        <f>Plan!O60</f>
+        <f>Plan!O69</f>
         <v/>
       </c>
     </row>
@@ -45290,22 +45341,22 @@
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="C67" s="35">
-        <f>Plan!C12</f>
+        <f>Plan!C72</f>
         <v/>
       </c>
       <c r="D67" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="16">
-        <f>Plan!J12</f>
+        <f>Plan!J72</f>
         <v/>
       </c>
       <c r="F67" s="16">
-        <f>Plan!K12</f>
+        <f>Plan!K72</f>
         <v/>
       </c>
       <c r="G67" s="8">
@@ -45313,11 +45364,11 @@
         <v/>
       </c>
       <c r="H67" s="16">
-        <f>Plan!I12</f>
+        <f>Plan!I72</f>
         <v/>
       </c>
       <c r="I67" s="16">
-        <f>Plan!O12</f>
+        <f>Plan!O72</f>
         <v/>
       </c>
     </row>
@@ -45401,22 +45452,22 @@
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C70" s="35">
-        <f>Plan!C63</f>
+        <f>Plan!C43</f>
         <v/>
       </c>
       <c r="D70" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E70" s="16">
-        <f>Plan!J63</f>
+        <f>Plan!J43</f>
         <v/>
       </c>
       <c r="F70" s="16">
-        <f>Plan!K63</f>
+        <f>Plan!K43</f>
         <v/>
       </c>
       <c r="G70" s="8">
@@ -45424,11 +45475,11 @@
         <v/>
       </c>
       <c r="H70" s="16">
-        <f>Plan!I63</f>
+        <f>Plan!I43</f>
         <v/>
       </c>
       <c r="I70" s="16">
-        <f>Plan!O63</f>
+        <f>Plan!O43</f>
         <v/>
       </c>
     </row>
@@ -45438,22 +45489,22 @@
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="C71" s="35">
-        <f>Plan!C57</f>
+        <f>Plan!C64</f>
         <v/>
       </c>
       <c r="D71" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="16">
-        <f>Plan!J57</f>
+        <f>Plan!J64</f>
         <v/>
       </c>
       <c r="F71" s="16">
-        <f>Plan!K57</f>
+        <f>Plan!K64</f>
         <v/>
       </c>
       <c r="G71" s="8">
@@ -45461,11 +45512,11 @@
         <v/>
       </c>
       <c r="H71" s="16">
-        <f>Plan!I57</f>
+        <f>Plan!I64</f>
         <v/>
       </c>
       <c r="I71" s="16">
-        <f>Plan!O57</f>
+        <f>Plan!O64</f>
         <v/>
       </c>
     </row>
@@ -45475,22 +45526,22 @@
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C72" s="35">
-        <f>Plan!C44</f>
+        <f>Plan!C12</f>
         <v/>
       </c>
       <c r="D72" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" s="16">
-        <f>Plan!J44</f>
+        <f>Plan!J12</f>
         <v/>
       </c>
       <c r="F72" s="16">
-        <f>Plan!K44</f>
+        <f>Plan!K12</f>
         <v/>
       </c>
       <c r="G72" s="8">
@@ -45498,11 +45549,11 @@
         <v/>
       </c>
       <c r="H72" s="16">
-        <f>Plan!I44</f>
+        <f>Plan!I12</f>
         <v/>
       </c>
       <c r="I72" s="16">
-        <f>Plan!O44</f>
+        <f>Plan!O12</f>
         <v/>
       </c>
     </row>
@@ -45512,22 +45563,22 @@
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C73" s="35">
-        <f>Plan!C56</f>
+        <f>Plan!C44</f>
         <v/>
       </c>
       <c r="D73" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E73" s="16">
-        <f>Plan!J56</f>
+        <f>Plan!J44</f>
         <v/>
       </c>
       <c r="F73" s="16">
-        <f>Plan!K56</f>
+        <f>Plan!K44</f>
         <v/>
       </c>
       <c r="G73" s="8">
@@ -45535,11 +45586,11 @@
         <v/>
       </c>
       <c r="H73" s="16">
-        <f>Plan!I56</f>
+        <f>Plan!I44</f>
         <v/>
       </c>
       <c r="I73" s="16">
-        <f>Plan!O56</f>
+        <f>Plan!O44</f>
         <v/>
       </c>
     </row>
@@ -45549,22 +45600,22 @@
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="C74" s="35">
-        <f>Plan!C43</f>
+        <f>Plan!C56</f>
         <v/>
       </c>
       <c r="D74" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74" s="16">
-        <f>Plan!J43</f>
+        <f>Plan!J56</f>
         <v/>
       </c>
       <c r="F74" s="16">
-        <f>Plan!K43</f>
+        <f>Plan!K56</f>
         <v/>
       </c>
       <c r="G74" s="8">
@@ -45572,11 +45623,11 @@
         <v/>
       </c>
       <c r="H74" s="16">
-        <f>Plan!I43</f>
+        <f>Plan!I56</f>
         <v/>
       </c>
       <c r="I74" s="16">
-        <f>Plan!O43</f>
+        <f>Plan!O56</f>
         <v/>
       </c>
     </row>
@@ -45586,22 +45637,22 @@
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="C75" s="35">
-        <f>Plan!C72</f>
+        <f>Plan!C63</f>
         <v/>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="16">
-        <f>Plan!J72</f>
+        <f>Plan!J63</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>Plan!K72</f>
+        <f>Plan!K63</f>
         <v/>
       </c>
       <c r="G75" s="8">
@@ -45609,11 +45660,11 @@
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>Plan!I72</f>
+        <f>Plan!I63</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>Plan!O72</f>
+        <f>Plan!O63</f>
         <v/>
       </c>
     </row>
@@ -45623,22 +45674,22 @@
       </c>
       <c r="B76" s="18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="C76" s="35">
-        <f>Plan!C64</f>
+        <f>Plan!C57</f>
         <v/>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="16">
-        <f>Plan!J64</f>
+        <f>Plan!J57</f>
         <v/>
       </c>
       <c r="F76" s="16">
-        <f>Plan!K64</f>
+        <f>Plan!K57</f>
         <v/>
       </c>
       <c r="G76" s="8">
@@ -45646,11 +45697,11 @@
         <v/>
       </c>
       <c r="H76" s="16">
-        <f>Plan!I64</f>
+        <f>Plan!I57</f>
         <v/>
       </c>
       <c r="I76" s="16">
-        <f>Plan!O64</f>
+        <f>Plan!O57</f>
         <v/>
       </c>
     </row>
@@ -46348,7 +46399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46402,7 +46453,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -46412,24 +46463,24 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-69, P-72</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Se corrige la dependencia de 6.18: ya no depende de 1.8</t>
+          <t>Primera entrega de Carlos Pardo revisada: NO fusionable</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>6.18 (fusionar rediseno-c-plus a develop) dependía por error de 1.8 (aplicar las 5 migraciones de backend del rediseño). El código del rediseño funciona sin esas migraciones (KPIs con su propio fallback, tope real leído de grados_credito, nota interna oculta detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false) y lo que sí las necesita queda oculto hasta que se apliquen. Con 6.17 y 6.19 en Hecho, el rediseño C+ queda completo y verificado de punta a punta en la rama rediseno-c-plus (9 commits locales sobre develop, sin push); 6.18 queda Pendiente solo de que Sebas autorice el push de la rama y abra el PR a develop.</t>
+          <t>Revisión del ZIP del repo privado de Carlos (base main anterior al rediseño C+, no rediseno-c-plus). Motivos: reintroduce la fuga F2-03 y pierde el revoke en resumen_clientes_asesor; el motivo de rechazo de afiliación usa una columna inexistente sin migración (rechazar dejaría de funcionar); convenios administrables usa columnas y un bucket de Storage inexistentes y acciones sin exigirAdmin ni validación; la purga Ley 1581 usa columnas/bucket equivocados y el cron queda abierto si falta CRON_SECRET; claves en .env.example, console.log y configuración de túnel; borra /asesor/demo (ya en producción) y renombra /cuenta/solicitar (ya en producción); sin pruebas. Se le envió a Carlos la lista de correcciones para rehacer el encargo sobre rediseno-c-plus, con un PR por tarea. 4.7, 4.8, 5.9, 5.10, 6.14 y 6.15 siguen Pendiente; P-69 con el mismo detalle y P-72 (acceso de colaborador en GitHub) sigue En curso, con la nota de que el ZIP en vez de un PR sugiere que ese acceso todavía no está confirmado.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -46439,44 +46490,44 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>6.17; 3.10, 4.10</t>
+          <t>6.18; nuevo P-104</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Correcciones responsive del C+ (commit b0239a8): barra inferior siempre visible en vez de oculta hasta el primer scroll</t>
+          <t>Push y fusión de rediseno-c-plus a develop autorizados por Sebas; 6.18 pasa a Hecho</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Se descartó la solución de ga-diseno-a-codigo de ocultar la barra inferior de /cuenta y /asesor hasta el primer scroll (con `inert`) porque ocultar la navegación principal al cargar la página perjudicaba la usabilidad y la accesibilidad. En su lugar, la barra queda siempre visible con espacio reservado al final de la página. Incluye también las correcciones de admin en celular y de la vista en tarjetas de /admin/sorteo, y el contraste de /admin/demo. e2e k-roles, c-cuenta y f-accesibilidad en verde (50 pasadas) tras `supabase db reset`.</t>
+          <t>Con la suite e2e en 290/290, Sebas autorizó subir a producción el rediseño C+ con el arreglo de la tasa; la sesión principal fusionó rediseno-c-plus a develop y la subió a origin. 6.18 pasa a Hecho. Nuevo pendiente P-104 (Alta, responsable Sebas): falta que apruebe/fusione el PR develop → main para que Vercel despliegue en producción.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>4.11; 6.17</t>
+          <t>6.18 (verificación pre-commit de rediseno-c-plus)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Hallazgo 0 corregido en producción del rediseño (commit 846657b): colores del admin oscuro en su propio grupo de Tailwind</t>
+          <t>Suite e2e completa 290/290 tras independizar las pruebas del crédito de ejemplo</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Los colores bg-admin-*/text-admin-* estaban anidados bajo la paleta ga en tailwind.config.ts, por lo que Tailwind nunca generaba esas clases y el panel /admin se veía blanco/sin tema oscuro en todos los anchos. Se movieron a su propio grupo admin en tailwind.config.ts; pruebas de responsive actualizadas en el mismo commit.</t>
+          <t>Encontró que, además del crédito huérfano ya corregido por el afterAll de la sesión principal, el segundo test de k-roles.spec.ts también resuelve el crédito del seed (cédula 1234567890), que queda inmutable por un trigger de negocio. Agregó restaurarCreditoDeEjemplo() en tests/e2e/utils.ts (borra y recrea la fila del seed) y la usó en c-cuenta.spec.ts, e-diseno.spec.ts e i-despliegue.spec.ts (sin tocar k-roles.spec.ts). Resultado: 4 suites afectadas en 0 fallas (antes 2), suite e2e completa 290/290 (antes 285/5), tsc/vitest (347)/lint/build en verde. Detalle en docs/verificaciones/2026-09-29-pre-commit.md. Listo para que la sesión principal haga el commit y la fusión a develop.</t>
         </is>
       </c>
     </row>
@@ -46488,22 +46539,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>2.14; P-103</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Corregidos todos los hallazgos del informe de responsive; 6.17 pasa a Hecho en su parte de código</t>
+          <t>Se quita la sección de testimonios de la landing (decisión de Sebas)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Confirmado con capturas que el hallazgo 0 (colores admin-* fuera de la clave ga) ya estaba resuelto en el código. De paso, axe encontró y se corrigió un contraste nuevo: EncabezadoAdmin se volvía transparente en escritorio asumiendo que siempre estaría sobre el fondo oscuro del admin, pero en /admin/demo esa misma barra flota sobre el fondo claro de la vista de asociado. Corregidos también: flex-wrap en el filtro de /admin/creditos, controles del encabezado móvil del admin a 44×44, tabla de /admin/sorteo con versión en tarjetas, botones de /cuenta/solicitar y casillas OTP a 44px, selects de /admin/sorteo a 16px. La corrección de la barra inferior flotante de /cuenta y /asesor de este commit (ocultarla hasta el primer scroll con `inert`) fue reemplazada después por la sesión principal, ver el siguiente asiento. tsc, lint, build, vitest (316/316) y playwright k-roles+f-accesibilidad (36/36, 6 skip esperados) en verde tras `npx supabase db reset`.</t>
+          <t>Commit 4c63924: sección de testimonios (que estaba oculta desde P-102 por tener textos de ejemplo) eliminada de la landing por decisión de Sebas. P-103 (D-07, ¿se mantiene la sección?) cierra Hecho con esa decisión: no se mantiene.</t>
         </is>
       </c>
     </row>
@@ -46515,22 +46566,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>4.11; P-95, P-96</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive de punta a punta del rediseño C+; 6.19 pasa a Hecho</t>
+          <t>Sebas aprueba P-95 y P-96; ambos pasan a Hecho</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>15 rutas × 10 anchos (320-1920 px) + horizontal 844×390, Playwright/Chrome contra Supabase local. 9 hallazgos responsive (5 críticos: barra inferior flotante tapaba contenido real en /cuenta y /asesor, scroll horizontal real en /admin/creditos, botones &lt;44px en el encabezado móvil del admin, tabla de /admin/sorteo sin versión en tarjetas; 4 menores) más 1 hallazgo crítico fuera del alcance responsive estricto: los colores bg-admin-*/text-admin-* no existían en el CSS compilado (tailwind.config.ts los anidaba bajo la paleta ga en vez de un grupo propio admin), así que el panel se veía sin tema oscuro. tests/responsive/responsive.spec.ts y logo-y-fotos.spec.ts actualizados. No se pudo probar /admin/* en horizontal por el límite diario de reenvío de código del correo de prueba (no es un hallazgo nuevo). Informe: docs/verificaciones/2026-09-27-rediseno-c-plus-responsive.md.</t>
+          <t>P-95 (botón «Escribir por WhatsApp» en el detalle de afiliación) aprobado tal cual estaba diseñado e implementado. P-96 (asignar asesor) aprobado con alcance limitado por ahora: solo asignar, solo cuando la afiliación está aprobada y el asociado todavía no tiene asesor; sin cambiar ni quitar un asesor ya asignado. La sesión principal agregó el estado «ya asignado» persistente al recargar (commit 3b5ae14), cerrando el residuo que había dejado ga-diseno-a-codigo.</t>
         </is>
       </c>
     </row>
@@ -46542,22 +46593,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>4.11; P-99, P-100, P-101, P-102, P-103</t>
+          <t>4.11 (revisión de diseño 3e/3i)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>H1 corregido (tasa de interés fuera del payload de /cuenta) y H2/B-01 cerrados (cédula de las «hermanas» enmascarada en servidor, testimonios de ejemplo ocultos)</t>
+          <t>Revisión de diseño aprobada con cambios menores</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Commit e650033: la tasa de interés ya no viaja al navegador del asociado en /cuenta ni /cuenta/solicitar (hallazgo H1 de ga-revisor-seguridad; el problema también estaba en producción desde el 25-sep, se sugiere llevarlo también a main). Queda un residuo (P-100): un asociado podría seguir leyendo la tasa consultando la API directo con su sesión (la RLS le deja leer sus solicitudes y grados_credito); ocultarlo del todo requiere una migración de permisos por columna, a decisión de Sebas. Commit fdab456: cédula de las «hermanas» del detalle de afiliación enmascarada en el servidor (cierra H2/M-01, P-101) y sección de testimonios de la landing oculta mientras tenga textos de ejemplo (cierra B-01, P-102; D-07 queda abierto como pedido de diseño en P-103: contenido real de testimonios y si la sección se mantiene). e2e de landing y k-roles vueltos a correr en verde.</t>
+          <t>Comparó el lienzo (piezas 3e/3i) contra PanelAfiliacionDetalle.tsx, AsignarAsesor.tsx, Iconos.tsx y lib/admin/whatsapp.ts. Veredicto: aprobado con cambios menores, incluido el estado «ya asignado» persistente al recargar. Corrigió 4 detalles menores en el propio lienzo (layout del botón de WhatsApp, glifo de las mini-muestras, foco sin halo extra, color suelto #182530 → token #1C2F3B). No tocó código. Detalle en docs/verificaciones/2026-09-27-revision-diseno-3e-3i.md.</t>
         </is>
       </c>
     </row>
@@ -46569,22 +46620,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>4.11, P-94, P-71; 6.16 pasa a Hecho; nuevos P-102, P-103</t>
+          <t>4.11, P-95, P-96</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>QA completo del rediseño C+ en verde: 161/162 escritorio, 129/129 celular</t>
+          <t>WhatsApp y bloque «Asesor» maquetados y conectados en código</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>QA de punta a punta contra Supabase local (escritorio 1280×800, celular 390×844). Actualizó las pruebas desactualizadas por el rediseño: a-navegacion (nav sin «Historias»), e-diseno (reescrita casi entera, textos verificados contra el código), afiliación v2 en utils.ts/f-accesibilidad (cierra P-94), aprobar en 2 pasos + atajos de teclado + KPIs + nota interna oculta (k-roles), máscara de correo con dominio oculto en b-ingreso y j-produccion (cierra P-71; i-despliegue ya usaba el formato nuevo). Agregó pruebas de reduced-motion y de que ninguna pantalla diga «Correo institucional». De paso corrigió una prueba de seguridad de i-despliegue que fallaba por una causa ajena al rediseño (React 19 ya no serializa el DOM en un `&lt;form action={...}&gt;`), reescribiéndola con intercepción de red. Hallazgos: 1 Media (cédula de las «hermanas», ya reportada por ga-revisor-seguridad, ver P-101) y 2 Bajos (testimonios de ejemplo con corchetes en la landing, ver P-102/P-103; y los marcadores ya conocidos de /politica-de-datos). 0 violaciones de axe en 19 combinaciones. Informe en docs/verificaciones/2026-09-27-rediseno-c-plus-qa.md.</t>
+          <t>Botón «Escribir por WhatsApp» habilitado en PanelAfiliacionDetalle.tsx (enlace wa.me en pestaña nueva con mensaje prellenado, glifo SVG IconoWhatsapp, normalización pura del celular en lib/admin/whatsapp.ts con pruebas Vitest, estado deshabilitado con motivo si el celular no es válido). Bloque «Asesor» nuevo (components/admin/AsignarAsesor.tsx) conectado a asignarAsesor con useActionState y sus 5 estados; corrigió una condición de carrera real (revalidatePath refrescaba la página y dejaba perfilAsociado en null justo tras el éxito) «congelando» la prop inicial con useState en PanelAfiliacionDetalle. Prueba nueva en tests/e2e/k-roles.spec.ts. tsc, lint, build, vitest (360) y Playwright (k-roles, escritorio) en verde. Dejó abierto para la sesión principal el estado «ya asignado» persistente al recargar (requería tocar la página de servidor, fuera de su encargo); cerrado después por la sesión principal (commit 3b5ae14, ver más abajo).</t>
         </is>
       </c>
     </row>
@@ -46596,22 +46647,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>4.11; nuevos P-99, P-100, P-101</t>
+          <t>4.11, P-96</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad del rediseño C+ aprobada; 2 fugas de datos confirmadas (no introducidas por el rediseño)</t>
+          <t>Server Action asignarAsesor lista en el servidor</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Revisó el diff completo de rediseno-c-plus contra develop (app, components, lib, proxy.ts, supabase): sin cambios en Server Actions ni en proxy.ts, el asesor sigue sin ver datos sensibles de sus clientes, la aprobación en 2 pasos exige confirmar, el login no cambió en funcionalidad. Encontró 2 hallazgos de fuga de datos al payload del cliente, vigentes desde antes de este diff: la tasa de interés viaja en las props de CuentaCliente aunque no se renderice (H1, ver P-99/P-100) y la cédula sin enmascarar de las «hermanas» viaja completa al detalle de afiliación aunque se muestre enmascarada (H2, ver P-101). Revisó también las 5 migraciones propuestas de 1.8 (bien construidas, coherentes con el flag de nota interna). npm audit --omit=dev: 0 vulnerabilidades. Pidió a ga-funcionalidad-botones corregir ambas fugas y a Sebas decidir sobre las 5 migraciones de 1.8.</t>
+          <t>asignarAsesor en app/admin/afiliaciones/actions.ts (exigirAdmin, zod esquemaAsignarAsesor, re-verificación en servidor de afiliación aprobada + perfil sin asesor + update condicional .is("asesor_id", null)); app/admin/afiliaciones/[id]/page.tsx carga perfilAsociado y asesores solo cuando aplica y los pasa como props opcionales nuevas a PanelAfiliacionDetalle (sin maquetar nada, TODO hacia D-09). 14 pruebas nuevas (9 de la Server Action, 5 del esquema zod); tsc/lint/build/vitest en verde (334 pruebas). Confirmó que no hace falta una migración nueva: la RLS perfiles_update y el trigger proteger_campos_perfil ya permiten el cambio a un admin, con validar_perfil_asesor_id validando que el elegido tenga rol asesor. Queda para ga-diseno-a-codigo maquetar y conectar la pieza 3i.</t>
         </is>
       </c>
     </row>
@@ -46623,22 +46674,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.11 (D-08, D-09)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>KPIs reales, tope real de grados_credito y nota interna oculta en el admin C+</t>
+          <t>Diseñado el botón WhatsApp habilitado (3e) y el bloque «Asesor» (3i) en el lienzo</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Cerró los 2 frentes de backend que dejó abiertos el maquetado del admin en modo oscuro (commit e39ad72): (1) los 4 KPI de /admin/creditos ahora son siempre exactos (lib/admin/kpis.ts: 3 conteos exactos + suma de aprobadas del mes, con el cliente de sesión del admin vía RLS, sin service role; mes calendario en hora de Colombia; pruebas nuevas en tests/unit/admin-kpis.test.ts); (2) el aviso «Dentro/Supera el tope» y el bloqueo de «Aprobar» usan el tope real de grados_credito (cargarPaquetesDemo, con su fallback a la copia estática). Ocultó el textarea de «Nota interna» detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false (lib/admin/flags.ts) con un TODO(backend) hacia la migración sin aplicar 20260925200200_historial_y_notas_internas.sql. Confirmó sin cambios de código que la aprobación en 2 pasos, el rechazo con motivo obligatorio, los atajos J/K/A/R/Esc y el invariante monto≤tope (triggers de la base) siguen intactos. tsc, lint, build y 316 pruebas de vitest (19 archivos) en verde. Sin commits. Sin bloqueos nuevos; sigue pendiente 1.8 (migraciones sin aplicar) para conectar una Server Action a agregar_nota_solicitud() y activar la bandera.</t>
+          <t>En docs/Green Alliance C+.dc.html: botón «Escribir por WhatsApp» de la pieza 3e con glifo oficial en SVG en línea y enlace wa.me con mensaje prellenado (4 estados: normal, hover, foco, deshabilitado por falta de celular); pieza 3i nueva, bloque «Asesor» para asignar perfiles.asesor_id a un asociado aprobado (estados sin elegir, asignando, éxito, error, ya asignado, sin asesores registrados). Trabajo nuevo dejado para ga-diseno-a-codigo: habilitar el botón en PanelAfiliacionDetalle.tsx y crear la Server Action «asignar asesor» sobre perfiles.asesor_id (sin migración nueva) más el bloque visible solo si la afiliación está aprobada y el asociado no tiene asesor.</t>
         </is>
       </c>
     </row>
@@ -46650,22 +46701,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Panel del admin C+ en modo oscuro maquetado en código; 4.11 pasa a Hecho</t>
+          <t>Se corrige la dependencia de 6.18: ya no depende de 1.8</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Maquetó el panel de administración completo en modo oscuro (piezas 2d y 3e–3h): Créditos (menú lateral, 4 KPI con guion donde falta consulta nueva, búsqueda, filtro, lista+ficha, aprobar en 2 pasos, rechazar con motivo obligatorio, nota interna e historial UI), Afiliaciones (lista+ficha, visor de 3 fotos con sus 3 estados, aprobar/rechazar en 2 pasos, WhatsApp deshabilitado por P-95), Asesores y Sorteo con el mismo restyle, y EncabezadoAdmin (patrón de celular) también en /admin/demo. Tokens nuevos en globals.css/tailwind.config.ts. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus (junto con 4.10). Pasa a Hecho en maquetación con 2 frentes abiertos: (1) tests/e2e/k-roles.spec.ts va a fallar porque Aprobar ahora pide un segundo clic «Sí, aprobar» — hace falta que ga-verificador-qa/ga-escritor-tests actualicen ese paso; (2) sin backend nuevo, KPIs completos, tope real desde grados_credito y nota interna/historial reales siguen bloqueados por las 5 migraciones de 1.8 (docs/auditorias/2026-09-25-backend-rediseno-c-plus.md), sin aplicar.</t>
+          <t>6.18 (fusionar rediseno-c-plus a develop) dependía por error de 1.8 (aplicar las 5 migraciones de backend del rediseño). El código del rediseño funciona sin esas migraciones (KPIs con su propio fallback, tope real leído de grados_credito, nota interna oculta detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false) y lo que sí las necesita queda oculto hasta que se apliquen. Con 6.17 y 6.19 en Hecho, el rediseño C+ queda completo y verificado de punta a punta en la rama rediseno-c-plus (9 commits locales sobre develop, sin push); 6.18 queda Pendiente solo de que Sebas autorice el push de la rama y abra el PR a develop.</t>
         </is>
       </c>
     </row>
@@ -46677,22 +46728,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>4.10; nuevo P-98</t>
+          <t>6.17; 3.10, 4.10</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Panel del asesor C+ maquetado en código; 4.10 pasa a Hecho</t>
+          <t>Correcciones responsive del C+ (commit b0239a8): barra inferior siempre visible en vez de oculta hasta el primer scroll</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Maquetó /asesor y /asesor/demo siguiendo las piezas 2c/3h del lienzo: EncabezadoAsesor en píldora, tarjetas de resumen con categoría de afiliación, chips de filtro, buscador, tabla de 5 columnas reescrita (sin datos de contacto), estado vacío, transición de lista y barra inferior en celular; agregó el marco ámbar de demostración compartido con /admin/demo y el estado «neutral» a Badge. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus. Documentó como pedido D-06 (docs/diseno/pedidos.md) la falta de regla de diseño para categorizar asociados ya afiliados (no solo solicitudes) en las tarjetas/chips; se registra como decisión provisional de la sesión principal, pendiente de que Sebas la confirme (nuevo pendiente P-98).</t>
+          <t>Se descartó la solución de ga-diseno-a-codigo de ocultar la barra inferior de /cuenta y /asesor hasta el primer scroll (con `inert`) porque ocultar la navegación principal al cargar la página perjudicaba la usabilidad y la accesibilidad. En su lugar, la barra queda siempre visible con espacio reservado al final de la página. Incluye también las correcciones de admin en celular y de la vista en tarjetas de /admin/sorteo, y el contraste de /admin/demo. e2e k-roles, c-cuenta y f-accesibilidad en verde (50 pasadas) tras `supabase db reset`.</t>
         </is>
       </c>
     </row>
@@ -46704,29 +46755,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.11; 6.17</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Panel del asociado C+ maquetado en código; 3.10 pasa a Hecho</t>
+          <t>Hallazgo 0 corregido en producción del rediseño (commit 846657b): colores del admin oscuro en su propio grupo de Tailwind</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Maquetó /cuenta y /cuenta/solicitar siguiendo las piezas 2b/3d del lienzo: EncabezadoCuenta en píldora flotante, comprobante «Tu solicitud» con sello y pasos animados, insignia de estado con color real, tope con medidor, carné de asociado (institución/activo como props opcionales sin usar, TODO backend), franja del sorteo, barra inferior en celular y deslizador de monto propio en /cuenta/solicitar; agregó enmascararCedula a lib/mascara.ts. tsc, lint, build y 311 pruebas de vitest en verde; no corrió Playwright (requiere Supabase local). Commit local 51da63f en rediseno-c-plus. «Tu camino a la estabilidad» sigue sin renderizarse por P-90 (fecha del primer descuento del embargo solidario); el carné de asociado sigue esperando institución/activo en perfiles (1.8). Falta correr tests/e2e/c-cuenta, h-credito, i-despliegue, j-produccion y k-roles contra Supabase local (ga-verificador-qa).</t>
+          <t>Los colores bg-admin-*/text-admin-* estaban anidados bajo la paleta ga en tailwind.config.ts, por lo que Tailwind nunca generaba esas clases y el panel /admin se veía blanco/sin tema oscuro en todos los anchos. Se movieron a su propio grupo admin en tailwind.config.ts; pruebas de responsive actualizadas en el mismo commit.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -46736,233 +46787,233 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
+          <t>Corregidos todos los hallazgos del informe de responsive; 6.17 pasa a Hecho en su parte de código</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
+          <t>Confirmado con capturas que el hallazgo 0 (colores admin-* fuera de la clave ga) ya estaba resuelto en el código. De paso, axe encontró y se corrigió un contraste nuevo: EncabezadoAdmin se volvía transparente en escritorio asumiendo que siempre estaría sobre el fondo oscuro del admin, pero en /admin/demo esa misma barra flota sobre el fondo claro de la vista de asociado. Corregidos también: flex-wrap en el filtro de /admin/creditos, controles del encabezado móvil del admin a 44×44, tabla de /admin/sorteo con versión en tarjetas, botones de /cuenta/solicitar y casillas OTP a 44px, selects de /admin/sorteo a 16px. La corrección de la barra inferior flotante de /cuenta y /asesor de este commit (ocultarla hasta el primer scroll con `inert`) fue reemplazada después por la sesión principal, ver el siguiente asiento. tsc, lint, build, vitest (316/316) y playwright k-roles+f-accesibilidad (36/36, 6 skip esperados) en verde tras `npx supabase db reset`.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>3.10, 4.10, 4.11</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
+          <t>Verificación responsive de punta a punta del rediseño C+; 6.19 pasa a Hecho</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
+          <t>15 rutas × 10 anchos (320-1920 px) + horizontal 844×390, Playwright/Chrome contra Supabase local. 9 hallazgos responsive (5 críticos: barra inferior flotante tapaba contenido real en /cuenta y /asesor, scroll horizontal real en /admin/creditos, botones &lt;44px en el encabezado móvil del admin, tabla de /admin/sorteo sin versión en tarjetas; 4 menores) más 1 hallazgo crítico fuera del alcance responsive estricto: los colores bg-admin-*/text-admin-* no existían en el CSS compilado (tailwind.config.ts los anidaba bajo la paleta ga en vez de un grupo propio admin), así que el panel se veía sin tema oscuro. tests/responsive/responsive.spec.ts y logo-y-fotos.spec.ts actualizados. No se pudo probar /admin/* en horizontal por el límite diario de reenvío de código del correo de prueba (no es un hallazgo nuevo). Informe: docs/verificaciones/2026-09-27-rediseno-c-plus-responsive.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.14; nuevo 6.16</t>
+          <t>4.11; P-99, P-100, P-101, P-102, P-103</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Tokens y landing del rediseño C+ llevados a código</t>
+          <t>H1 corregido (tasa de interés fuera del payload de /cuenta) y H2/B-01 cerrados (cédula de las «hermanas» enmascarada en servidor, testimonios de ejemplo ocultos)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
+          <t>Commit e650033: la tasa de interés ya no viaja al navegador del asociado en /cuenta ni /cuenta/solicitar (hallazgo H1 de ga-revisor-seguridad; el problema también estaba en producción desde el 25-sep, se sugiere llevarlo también a main). Queda un residuo (P-100): un asociado podría seguir leyendo la tasa consultando la API directo con su sesión (la RLS le deja leer sus solicitudes y grados_credito); ocultarlo del todo requiere una migración de permisos por columna, a decisión de Sebas. Commit fdab456: cédula de las «hermanas» del detalle de afiliación enmascarada en el servidor (cierra H2/M-01, P-101) y sección de testimonios de la landing oculta mientras tenga textos de ejemplo (cierra B-01, P-102; D-07 queda abierto como pedido de diseño en P-103: contenido real de testimonios y si la sección se mantiene). e2e de landing y k-roles vueltos a correr en verde.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
+          <t>4.11, P-94, P-71; 6.16 pasa a Hecho; nuevos P-102, P-103</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
+          <t>QA completo del rediseño C+ en verde: 161/162 escritorio, 129/129 celular</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
+          <t>QA de punta a punta contra Supabase local (escritorio 1280×800, celular 390×844). Actualizó las pruebas desactualizadas por el rediseño: a-navegacion (nav sin «Historias»), e-diseno (reescrita casi entera, textos verificados contra el código), afiliación v2 en utils.ts/f-accesibilidad (cierra P-94), aprobar en 2 pasos + atajos de teclado + KPIs + nota interna oculta (k-roles), máscara de correo con dominio oculto en b-ingreso y j-produccion (cierra P-71; i-despliegue ya usaba el formato nuevo). Agregó pruebas de reduced-motion y de que ninguna pantalla diga «Correo institucional». De paso corrigió una prueba de seguridad de i-despliegue que fallaba por una causa ajena al rediseño (React 19 ya no serializa el DOM en un `&lt;form action={...}&gt;`), reescribiéndola con intercepción de red. Hallazgos: 1 Media (cédula de las «hermanas», ya reportada por ga-revisor-seguridad, ver P-101) y 2 Bajos (testimonios de ejemplo con corchetes en la landing, ver P-102/P-103; y los marcadores ya conocidos de /politica-de-datos). 0 violaciones de axe en 19 combinaciones. Informe en docs/verificaciones/2026-09-27-rediseno-c-plus-qa.md.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>1.8; P-47, P-90, P-91, P-92</t>
+          <t>4.11; nuevos P-99, P-100, P-101</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
+          <t>Revisión de seguridad del rediseño C+ aprobada; 2 fugas de datos confirmadas (no introducidas por el rediseño)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
+          <t>Revisó el diff completo de rediseno-c-plus contra develop (app, components, lib, proxy.ts, supabase): sin cambios en Server Actions ni en proxy.ts, el asesor sigue sin ver datos sensibles de sus clientes, la aprobación en 2 pasos exige confirmar, el login no cambió en funcionalidad. Encontró 2 hallazgos de fuga de datos al payload del cliente, vigentes desde antes de este diff: la tasa de interés viaja en las props de CuentaCliente aunque no se renderice (H1, ver P-99/P-100) y la cédula sin enmascarar de las «hermanas» viaja completa al detalle de afiliación aunque se muestre enmascarada (H2, ver P-101). Revisó también las 5 migraciones propuestas de 1.8 (bien construidas, coherentes con el flag de nota interna). npm audit --omit=dev: 0 vulnerabilidades. Pidió a ga-funcionalidad-botones corregir ambas fugas y a Sebas decidir sobre las 5 migraciones de 1.8.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (despliegue PR #2)</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
+          <t>KPIs reales, tope real de grados_credito y nota interna oculta en el admin C+</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
+          <t>Cerró los 2 frentes de backend que dejó abiertos el maquetado del admin en modo oscuro (commit e39ad72): (1) los 4 KPI de /admin/creditos ahora son siempre exactos (lib/admin/kpis.ts: 3 conteos exactos + suma de aprobadas del mes, con el cliente de sesión del admin vía RLS, sin service role; mes calendario en hora de Colombia; pruebas nuevas en tests/unit/admin-kpis.test.ts); (2) el aviso «Dentro/Supera el tope» y el bloqueo de «Aprobar» usan el tope real de grados_credito (cargarPaquetesDemo, con su fallback a la copia estática). Ocultó el textarea de «Nota interna» detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false (lib/admin/flags.ts) con un TODO(backend) hacia la migración sin aplicar 20260925200200_historial_y_notas_internas.sql. Confirmó sin cambios de código que la aprobación en 2 pasos, el rechazo con motivo obligatorio, los atajos J/K/A/R/Esc y el invariante monto≤tope (triggers de la base) siguen intactos. tsc, lint, build y 316 pruebas de vitest (19 archivos) en verde. Sin commits. Sin bloqueos nuevos; sigue pendiente 1.8 (migraciones sin aplicar) para conectar una Server Action a agregar_nota_solicitud() y activar la bandera.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
+          <t>Panel del admin C+ en modo oscuro maquetado en código; 4.11 pasa a Hecho</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
+          <t>Maquetó el panel de administración completo en modo oscuro (piezas 2d y 3e–3h): Créditos (menú lateral, 4 KPI con guion donde falta consulta nueva, búsqueda, filtro, lista+ficha, aprobar en 2 pasos, rechazar con motivo obligatorio, nota interna e historial UI), Afiliaciones (lista+ficha, visor de 3 fotos con sus 3 estados, aprobar/rechazar en 2 pasos, WhatsApp deshabilitado por P-95), Asesores y Sorteo con el mismo restyle, y EncabezadoAdmin (patrón de celular) también en /admin/demo. Tokens nuevos en globals.css/tailwind.config.ts. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus (junto con 4.10). Pasa a Hecho en maquetación con 2 frentes abiertos: (1) tests/e2e/k-roles.spec.ts va a fallar porque Aprobar ahora pide un segundo clic «Sí, aprobar» — hace falta que ga-verificador-qa/ga-escritor-tests actualicen ese paso; (2) sin backend nuevo, KPIs completos, tope real desde grados_credito y nota interna/historial reales siguen bloqueados por las 5 migraciones de 1.8 (docs/auditorias/2026-09-25-backend-rediseno-c-plus.md), sin aplicar.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-13</t>
+          <t>4.10; nuevo P-98</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Texto de vigilancia de Supersolidaria confirmado</t>
+          <t>Panel del asesor C+ maquetado en código; 4.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
+          <t>Maquetó /asesor y /asesor/demo siguiendo las piezas 2c/3h del lienzo: EncabezadoAsesor en píldora, tarjetas de resumen con categoría de afiliación, chips de filtro, buscador, tabla de 5 columnas reescrita (sin datos de contacto), estado vacío, transición de lista y barra inferior en celular; agregó el marco ámbar de demostración compartido con /admin/demo y el estado «neutral» a Badge. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus. Documentó como pedido D-06 (docs/diseno/pedidos.md) la falta de regla de diseño para categorizar asociados ya afiliados (no solo solicitudes) en las tarjetas/chips; se registra como decisión provisional de la sesión principal, pendiente de que Sebas la confirme (nuevo pendiente P-98).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>6.3; nuevos P-84, P-86, P-87</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>QA de producción: con observaciones</t>
+          <t>Panel del asociado C+ maquetado en código; 3.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
+          <t>Maquetó /cuenta y /cuenta/solicitar siguiendo las piezas 2b/3d del lienzo: EncabezadoCuenta en píldora flotante, comprobante «Tu solicitud» con sello y pasos animados, insignia de estado con color real, tope con medidor, carné de asociado (institución/activo como props opcionales sin usar, TODO backend), franja del sorteo, barra inferior en celular y deslizador de monto propio en /cuenta/solicitar; agregó enmascararCedula a lib/mascara.ts. tsc, lint, build y 311 pruebas de vitest en verde; no corrió Playwright (requiere Supabase local). Commit local 51da63f en rediseno-c-plus. «Tu camino a la estabilidad» sigue sin renderizarse por P-90 (fecha del primer descuento del embargo solidario); el carné de asociado sigue esperando institución/activo en perfiles (1.8). Falta correr tests/e2e/c-cuenta, h-credito, i-despliegue, j-produccion y k-roles contra Supabase local (ga-verificador-qa).</t>
         </is>
       </c>
     </row>
@@ -46974,22 +47025,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>2.12; nuevo P-85</t>
+          <t>1.7, 2.15</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
+          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
+          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
         </is>
       </c>
     </row>
@@ -47001,22 +47052,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>6.2; nuevos P-83, P-88</t>
+          <t>3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
+          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
+          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
         </is>
       </c>
     </row>
@@ -47026,24 +47077,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
+          <t>1.7, 2.14; nuevo 6.16</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
+          <t>Tokens y landing del rediseño C+ llevados a código</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
+          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
         </is>
       </c>
     </row>
@@ -47053,267 +47104,267 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>6.9, 6.13; P-44, P-59, P-61</t>
+          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
+          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
+          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
+          <t>1.8; P-47, P-90, P-91, P-92</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
+          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
+          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Sebas (acuerdo con Carlos Pardo)</t>
+          <t>sesión principal (despliegue PR #2)</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
+          <t>4.9; P-83, P-84, P-85, P-89</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
+          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
+          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>6.1, P-58</t>
+          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
+          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
+          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Sebas (coordinación con la cooperativa)</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
+          <t>5.3; P-13</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
+          <t>Texto de vigilancia de Supersolidaria confirmado</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
+          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
+          <t>6.3; nuevos P-84, P-86, P-87</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
+          <t>QA de producción: con observaciones</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
+          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>2.12; nuevo P-85</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
+          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
+          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>6.2; nuevos P-83, P-88</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
+          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
+          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Sorteo mensual en /cuenta</t>
+          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
+          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>4.6; P-57</t>
+          <t>6.9, 6.13; P-44, P-59, P-61</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
+          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
+          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
         </is>
       </c>
     </row>
@@ -47323,112 +47374,112 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>ga-auditor-supabase</t>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>1.5; P-63</t>
+          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
+          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
+          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
+          <t>Sebas (acuerdo con Carlos Pardo)</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
+          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
+          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive + ga-verificador-qa</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>6.3; P-39</t>
+          <t>6.1, P-58</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
+          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
+          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (coordinación con la cooperativa)</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 5.8; P-39, P-53</t>
+          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
+          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
+          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -47438,152 +47489,152 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
+          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
+          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
+          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>5.2, 5.8, 6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
+          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
+          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
+          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
+          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>2.1, 5.3, 5.7; P-16, P-52</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
+          <t>Sorteo mensual en /cuenta</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
+          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
+          <t>4.6; P-57</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
+          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
+          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
+          <t>1.5; P-63</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
+          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
+          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
         </is>
       </c>
     </row>
@@ -47593,24 +47644,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Sebas</t>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Agente ga-auditor-supabase corregido</t>
+          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
         </is>
       </c>
     </row>
@@ -47622,22 +47673,22 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Sebas + ga-auditor-supabase</t>
+          <t>ga-verificador-responsive + ga-verificador-qa</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>3.1, 6.5, 6.10; P-09</t>
+          <t>6.3; P-39</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
         </is>
       </c>
     </row>
@@ -47649,22 +47700,22 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ga-escritor-tests</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.3, 5.2, 5.8; P-39, P-53</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
         </is>
       </c>
     </row>
@@ -47674,24 +47725,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-funcionalidad-botones</t>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
         </is>
       </c>
     </row>
@@ -47703,22 +47754,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+          <t>5.2, 5.8, 6.3</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
         </is>
       </c>
     </row>
@@ -47730,22 +47781,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
         </is>
       </c>
     </row>
@@ -47757,20 +47808,263 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
+          <t>ga-diseno-a-codigo</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>2.1, 5.3, 5.7; P-16, P-52</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Sebas</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Agente ga-auditor-supabase corregido</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>3.1, 6.5, 6.10; P-09</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>ga-verificador-qa</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
           <t>Claude (sesión principal)</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Todas</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>Creación del Excel de avances</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>Pendientes desde PENDIENTES.md, plan desde la propuesta (6 fases, 8 semanas) reorganizado en 2 filas con cola infinita y pesos 1–5.</t>
         </is>

--- a/docs/avances/Avances_Green_Alliance.xlsx
+++ b/docs/avances/Avances_Green_Alliance.xlsx
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1814,32 +1814,32 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Plantilla del correo con {{ .Token }} (código, no enlace)</t>
+          <t>Alerta en los logs de Vercel para limite_de_intentos_fallo y limite_secreto_faltante</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Yo (panel Supabase/Resend)</t>
+          <t>Yo (panel Vercel)</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="I5" s="21">
@@ -1848,14 +1848,14 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>23-sep: supabase/templates/codigo-ingreso.html rediseñada (HTML con la marca Green Alliance) y probada en local (llega a Mailpit con el código). Falta que Sebas la pegue en Authentication → Emails → Templates → Magic Link del panel de producción.</t>
+          <t>Sugerido por ga-auditor-supabase en la auditoría de P-43.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>P-105</t>
+          <t>P-73</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Vercel/Resend</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>CRON_SECRET de 32+ caracteres, publicar plantilla ga-aviso-institucional y crear RESEND_TEMPLATE_AVISO_INSTITUCIONAL</t>
+          <t>Pagar a Carlos Pardo 150.000 COP (cierre del encargo; no sigue en el proyecto)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1890,19 +1890,23 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$85,MATCH(H6,Plan!$A$5:$A$85,0)),"—")</f>
         <v/>
       </c>
-      <c r="J6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Pago único por P-66 a P-71 (4.7, 4.8, 5.9, 5.10, 6.14, 6.15). Cada PR de Carlos lo revisa un agente ga-* antes de fusionarlo a develop.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>P-43</t>
+          <t>P-55</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1917,17 +1921,17 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Aplicar en producción la migración 20260923210000_limite_de_intentos.sql</t>
+          <t>Opcional: revocar la secuencia limites_intentos_id_seq a anon y authenticated</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Sebas (ga-auditor-supabase revisa antes)</t>
+          <t>Yo + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1946,14 +1950,14 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Crea la tabla limites_intentos y la función registrar_intento, que usan /afiliacion, /ingresar y «Reenviar código» (dentroDelLimite). Sin ella esos límites fallan en producción. Antes del despliegue (6.5). 23-sep: auditada por ga-auditor-supabase, se puede aplicar tal cual (docs/auditorias/2026-09-23-limite-de-intentos.md); falta que Sebas haga db push.</t>
+          <t>Sugerido por ga-auditor-supabase en la auditoría de P-43.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>P-45</t>
+          <t>P-105</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1963,17 +1967,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Vercel/Resend</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Panel de producción: OTP de 6 dígitos, vencimiento del código en 600 s (10 min) e intervalo entre correos ≤ 45 s</t>
+          <t>CRON_SECRET de 32+ caracteres, publicar plantilla ga-aviso-institucional y crear RESEND_TEMPLATE_AVISO_INSTITUCIONAL</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Yo (panel Supabase/Resend)</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -1983,12 +1987,12 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="I8" s="21">
@@ -1997,14 +2001,14 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Complementa P-19 (SMTP) y P-20 (plantilla Magic Link con {{ .Token }}).</t>
+          <t>30-sep: Sebas lo hizo en producción.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2014,27 +2018,27 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Revisar el límite de Resend (plan gratis ≈ 100 correos/día)</t>
+          <t>SMTP propio con Resend (Authentication → Emails → SMTP Settings)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Yo (panel Supabase/Resend)</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -2048,14 +2052,14 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>30-sep: con ~500 asociados el plan gratis se queda corto; confirmar plan.</t>
+          <t>Configurado por Sebas el 23-sep. El código de 6 dígitos lo envía Supabase Auth (no Resend desde la app); funciona en local. Ver docs/resend-plantillas.md.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>P-54</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2065,32 +2069,32 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Alerta en los logs de Vercel para limite_de_intentos_fallo y limite_secreto_faltante</t>
+          <t>Plantilla del correo con {{ .Token }} (código, no enlace)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Yo (panel Vercel)</t>
+          <t>Yo (panel Supabase/Resend)</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I10" s="21">
@@ -2099,14 +2103,14 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-auditor-supabase en la auditoría de P-43.</t>
+          <t>23-sep: supabase/templates/codigo-ingreso.html rediseñada (HTML con la marca Green Alliance) y probada en local (llega a Mailpit con el código). Falta que Sebas la pegue en Authentication → Emails → Templates → Magic Link del panel de producción. 30-sep: Sebas lo hizo en producción.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>P-73</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2116,32 +2120,32 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Pagar a Carlos Pardo 150.000 COP (cierre del encargo; no sigue en el proyecto)</t>
+          <t>Aplicar en producción la migración 20260923210000_limite_de_intentos.sql</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Sebas (ga-auditor-supabase revisa antes)</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="I11" s="21">
@@ -2150,14 +2154,14 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Pago único por P-66 a P-71 (4.7, 4.8, 5.9, 5.10, 6.14, 6.15). Cada PR de Carlos lo revisa un agente ga-* antes de fusionarlo a develop.</t>
+          <t>Crea la tabla limites_intentos y la función registrar_intento, que usan /afiliacion, /ingresar y «Reenviar código» (dentroDelLimite). Sin ella esos límites fallan en producción. Antes del despliegue (6.5). 23-sep: auditada por ga-auditor-supabase, se puede aplicar tal cual (docs/auditorias/2026-09-23-limite-de-intentos.md); falta que Sebas haga db push. 30-sep: Sebas lo hizo en producción.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>P-55</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2167,32 +2171,32 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Opcional: revocar la secuencia limites_intentos_id_seq a anon y authenticated</t>
+          <t>Variables: SUPABASE_SERVICE_ROLE_KEY, INGRESO_COOKIE_SECRET, LIMITE_HMAC_SECRET, RESEND_API_KEY, EMAIL_FROM, SITIO_URL, RESEND_TEMPLATE_INGRESO_ACEPTADO, RESEND_TEMPLATE_CREDITO_APROBADO, RESEND_TEMPLATE_CREDITO_RECHAZADO, RESEND_TEMPLATE_SORTEO_BOLETA, NEXT_PUBLIC_WHATSAPP</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Yo + ga-auditor-supabase</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="I12" s="21">
@@ -2201,14 +2205,14 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-auditor-supabase en la auditoría de P-43.</t>
+          <t>NEXT_PUBLIC_WHATSAPP ya tenía dato (P-10, 311 724 1942). 25-sep: Sebas puso el resto de variables en Vercel (SITIO_URL=https://www.greenallianceco.com, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_*), tras crear y publicar las plantillas en Resend (P-61). Queda abierto por separado que SUPABASE_SERVICE_ROLE_KEY siga dando «Invalid API key» (P-60).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-45</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2223,7 +2227,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>SMTP propio con Resend (Authentication → Emails → SMTP Settings)</t>
+          <t>Panel de producción: OTP de 6 dígitos, vencimiento del código en 600 s (10 min) e intervalo entre correos ≤ 45 s</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -2252,14 +2256,14 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Configurado por Sebas el 23-sep. El código de 6 dígitos lo envía Supabase Auth (no Resend desde la app); funciona en local. Ver docs/resend-plantillas.md.</t>
+          <t>Complementa P-19 (SMTP) y P-20 (plantilla Magic Link con {{ .Token }}). 30-sep: Sebas lo hizo en producción.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>P-44</t>
+          <t>P-59</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2269,17 +2273,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Variables: SUPABASE_SERVICE_ROLE_KEY, INGRESO_COOKIE_SECRET, LIMITE_HMAC_SECRET, RESEND_API_KEY, EMAIL_FROM, SITIO_URL, RESEND_TEMPLATE_INGRESO_ACEPTADO, RESEND_TEMPLATE_CREDITO_APROBADO, RESEND_TEMPLATE_CREDITO_RECHAZADO, RESEND_TEMPLATE_SORTEO_BOLETA, NEXT_PUBLIC_WHATSAPP</t>
+          <t>Aplicar en producción las 9 migraciones de fase 2 (20260924000000…000800) y desplegar enseguida</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Sebas (ga-auditor-supabase revisa antes)</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -2294,7 +2298,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I14" s="21">
@@ -2303,14 +2307,14 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>NEXT_PUBLIC_WHATSAPP ya tenía dato (P-10, 311 724 1942). 25-sep: Sebas puso el resto de variables en Vercel (SITIO_URL=https://www.greenallianceco.com, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_*), tras crear y publicar las plantillas en Resend (P-61). Queda abierto por separado que SUPABASE_SERVICE_ROLE_KEY siga dando «Invalid API key» (P-60).</t>
+          <t>25-sep: Sebas aplicó las 9 migraciones en producción con `supabase db push` (dry-run confirmó exactamente esas 9) y fusionó el PR develop → main; Vercel desplegó fase 2 en www.greenallianceco.com, verificado por HTTP.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>P-59</t>
+          <t>P-60</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2320,17 +2324,17 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Aplicar en producción las 9 migraciones de fase 2 (20260924000000…000800) y desplegar enseguida</t>
+          <t>Corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (hoy da «Invalid API key»)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Sebas (ga-auditor-supabase revisa antes)</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -2345,7 +2349,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="I15" s="21">
@@ -2354,14 +2358,14 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>25-sep: Sebas aplicó las 9 migraciones en producción con `supabase db push` (dry-run confirmó exactamente esas 9) y fusionó el PR develop → main; Vercel desplegó fase 2 en www.greenallianceco.com, verificado por HTTP.</t>
+          <t>24-sep: Sebas corrigió la llave en Vercel (confirmado el 25-sep).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>P-60</t>
+          <t>P-61</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2371,12 +2375,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (hoy da «Invalid API key»)</t>
+          <t>Crear en Resend las plantillas de ingreso aceptado, crédito aprobado/rechazado y boleta del sorteo (ga-sorteo-boleta); confirmar el tope de 3 reenvíos de boleta al día</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -2405,14 +2409,14 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>24-sep: Sebas corrigió la llave en Vercel (confirmado el 25-sep).</t>
+          <t>RESEND_API_KEY, EMAIL_FROM y RESEND_TEMPLATE_SORTEO_BOLETA ya son obligatorias para el build. 24-sep: el HTML de las 4 plantillas listo en docs/resend/. 25-sep: Sebas creó y publicó las 4 plantillas en Resend.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>P-61</t>
+          <t>P-72</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2422,12 +2426,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Crear en Resend las plantillas de ingreso aceptado, crédito aprobado/rechazado y boleta del sorteo (ga-sorteo-boleta); confirmar el tope de 3 reenvíos de boleta al día</t>
+          <t>Dar a Carlos acceso de colaborador al repo GitHub GreenAllianceCoo/PagGreenAlliance y compartirle el encargo (sin llaves de producción)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -2447,7 +2451,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="21">
@@ -2456,14 +2460,14 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>RESEND_API_KEY, EMAIL_FROM y RESEND_TEMPLATE_SORTEO_BOLETA ya son obligatorias para el build. 24-sep: el HTML de las 4 plantillas listo en docs/resend/. 25-sep: Sebas creó y publicó las 4 plantillas en Resend.</t>
+          <t>Necesario antes de que Carlos pueda abrir PRs a develop desde su propia rama. 24-sep: Sebas ya habló con Carlos para darle el acceso; falta confirmarlo en GitHub. 29-sep: la primera entrega de Carlos llegó como ZIP de un repo privado propio (no como PR al repo de Green Alliance), señal de que este acceso sigue sin confirmarse; además trabajó sobre una base main anterior al rediseño C+ en vez de rediseno-c-plus. Se le pidió que la próxima entrega sea un PR por tarea sobre rediseno-c-plus, lo que requiere este acceso ya confirmado. 30-sep: cerrado, Carlos Pardo ya no trabaja en el proyecto.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>P-72</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2473,22 +2477,22 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Dar a Carlos acceso de colaborador al repo GitHub GreenAllianceCoo/PagGreenAlliance y compartirle el encargo (sin llaves de producción)</t>
+          <t>(Cancelado) Revisar el límite de Resend (plan gratis ≈ 100 correos/día)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -2498,7 +2502,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I18" s="21">
@@ -2507,7 +2511,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Necesario antes de que Carlos pueda abrir PRs a develop desde su propia rama. 24-sep: Sebas ya habló con Carlos para darle el acceso; falta confirmarlo en GitHub. 29-sep: la primera entrega de Carlos llegó como ZIP de un repo privado propio (no como PR al repo de Green Alliance), señal de que este acceso sigue sin confirmarse; además trabajó sobre una base main anterior al rediseño C+ en vez de rediseno-c-plus. Se le pidió que la próxima entrega sea un PR por tarea sobre rediseno-c-plus, lo que requiere este acceso ya confirmado. 30-sep: cerrado, Carlos Pardo ya no trabaja en el proyecto.</t>
+          <t>30-sep: con ~500 asociados el plan gratis se queda corto; confirmar plan. 30-sep: Sebas decide que el límite de Resend no es problema por ahora; se quita.</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7822,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>2.6, 2.7, 2.3</t>
+          <t>2.3, 2.7, 2.8, 6.10</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -7830,7 +7834,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L9" s="8">
         <f>K9+E9</f>
@@ -7896,7 +7900,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.4, 3.10</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
@@ -7905,10 +7909,10 @@
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L10" s="8">
         <f>K10+E10</f>
@@ -7974,19 +7978,19 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>2.8, 6.4</t>
+          <t>2.6, 2.3</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J11" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L11" s="8">
         <f>K11+E11</f>
@@ -8057,14 +8061,14 @@
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L12" s="8">
         <f>K12+E12</f>
@@ -8286,7 +8290,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7, 1.5</t>
         </is>
       </c>
       <c r="I15" s="18" t="inlineStr">
@@ -8298,7 +8302,7 @@
         <v>6</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L15" s="8">
         <f>K15+E15</f>
@@ -8520,7 +8524,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>3.1, 1.5</t>
+          <t>3.1, 1.7</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr">
@@ -8610,7 +8614,7 @@
         <v>14</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L19" s="8">
         <f>K19+E19</f>
@@ -8676,16 +8680,16 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I20" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J20" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" s="8" t="n">
         <v>18</v>
@@ -8754,7 +8758,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>6.17, 6.18, 4.12</t>
+          <t>4.2, 6.4</t>
         </is>
       </c>
       <c r="I21" s="18" t="inlineStr">
@@ -8763,10 +8767,10 @@
         </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L21" s="8">
         <f>K21+E21</f>
@@ -8832,19 +8836,19 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I22" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J22" s="8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="L22" s="8">
         <f>K22+E22</f>
@@ -8919,7 +8923,7 @@
         </is>
       </c>
       <c r="J23" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>77</v>
@@ -8988,19 +8992,19 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>4.2, 3.9</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J24" s="8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L24" s="8">
         <f>K24+E24</f>
@@ -9066,19 +9070,19 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L25" s="8">
         <f>K25+E25</f>
@@ -9144,7 +9148,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>2.15, 4.1</t>
+          <t>4.1, 4.10, 4.11</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
@@ -9153,10 +9157,10 @@
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L26" s="8">
         <f>K26+E26</f>
@@ -9222,19 +9226,19 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>4.11, 3.4</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L27" s="8">
         <f>K27+E27</f>
@@ -9378,7 +9382,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>5.8, 5.13</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr">
@@ -9390,7 +9394,7 @@
         <v>13</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="L29" s="8">
         <f>K29+E29</f>
@@ -9456,7 +9460,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
@@ -9468,7 +9472,7 @@
         <v>13</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L30" s="8">
         <f>K30+E30</f>
@@ -9534,19 +9538,19 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.15, 6.16, 1.6</t>
         </is>
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J31" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L31" s="8">
         <f>K31+E31</f>
@@ -9612,7 +9616,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>6.18, 4.12</t>
         </is>
       </c>
       <c r="I32" s="18" t="inlineStr">
@@ -9621,10 +9625,10 @@
         </is>
       </c>
       <c r="J32" s="8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L32" s="8">
         <f>K32+E32</f>
@@ -9690,7 +9694,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>3.9, 2.10</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I33" s="18" t="inlineStr">
@@ -9699,10 +9703,10 @@
         </is>
       </c>
       <c r="J33" s="8" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L33" s="8">
         <f>K33+E33</f>
@@ -9768,7 +9772,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>6.11, 6.9, 5.1</t>
+          <t>6.11, 6.8, 6.9</t>
         </is>
       </c>
       <c r="I34" s="18" t="inlineStr">
@@ -9777,7 +9781,7 @@
         </is>
       </c>
       <c r="J34" s="8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K34" s="8" t="n">
         <v>60</v>
@@ -9846,7 +9850,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>2.12, 3.6</t>
+          <t>5.2, 3.6, 4.13</t>
         </is>
       </c>
       <c r="I35" s="18" t="inlineStr">
@@ -9855,10 +9859,10 @@
         </is>
       </c>
       <c r="J35" s="8" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L35" s="8">
         <f>K35+E35</f>
@@ -9924,7 +9928,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>4.10, 6.10</t>
+          <t>1.6, 6.19</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr">
@@ -9933,10 +9937,10 @@
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L36" s="8">
         <f>K36+E36</f>
@@ -10002,7 +10006,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>2.14, 3.4</t>
+          <t>4.6, 2.14</t>
         </is>
       </c>
       <c r="I37" s="18" t="inlineStr">
@@ -10011,10 +10015,10 @@
         </is>
       </c>
       <c r="J37" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L37" s="8">
         <f>K37+E37</f>
@@ -10080,19 +10084,19 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>5.2, 2.12</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I38" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J38" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L38" s="8">
         <f>K38+E38</f>
@@ -10158,7 +10162,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>2.11, 6.12</t>
+          <t>2.11, 6.14</t>
         </is>
       </c>
       <c r="I39" s="18" t="inlineStr">
@@ -10167,7 +10171,7 @@
         </is>
       </c>
       <c r="J39" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K39" s="8" t="n">
         <v>77</v>
@@ -10236,7 +10240,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>4.14, 4.9</t>
+          <t>5.5, 3.2</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">
@@ -10248,7 +10252,7 @@
         <v>4</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L40" s="8">
         <f>K40+E40</f>
@@ -10318,7 +10322,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>4.13, 5.2</t>
+          <t>2.10, 5.2</t>
         </is>
       </c>
       <c r="I41" s="18" t="inlineStr">
@@ -10327,7 +10331,7 @@
         </is>
       </c>
       <c r="J41" s="8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K41" s="8" t="n">
         <v>48</v>
@@ -10396,19 +10400,19 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>6.19, 6.16, 6.13</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I42" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L42" s="8">
         <f>K42+E42</f>
@@ -10474,7 +10478,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>5.11, 6.6</t>
+          <t>5.12, 4.8</t>
         </is>
       </c>
       <c r="I43" s="18" t="inlineStr">
@@ -10483,10 +10487,10 @@
         </is>
       </c>
       <c r="J43" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L43" s="8">
         <f>K43+E43</f>
@@ -10552,7 +10556,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>5.12, 5.9</t>
+          <t>4.7, 5.9</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr">
@@ -10561,10 +10565,10 @@
         </is>
       </c>
       <c r="J44" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L44" s="8">
         <f>K44+E44</f>
@@ -10630,19 +10634,19 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>4.4, 5.10</t>
+          <t>5.8, 5.13</t>
         </is>
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J45" s="8" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L45" s="8">
         <f>K45+E45</f>
@@ -10708,19 +10712,19 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I46" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J46" s="8" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L46" s="8">
         <f>K46+E46</f>
@@ -10786,7 +10790,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.14, 2.15</t>
         </is>
       </c>
       <c r="I47" s="18" t="inlineStr">
@@ -10795,10 +10799,10 @@
         </is>
       </c>
       <c r="J47" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L47" s="8">
         <f>K47+E47</f>
@@ -10864,7 +10868,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>3.7, 5.5</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr">
@@ -10873,10 +10877,10 @@
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L48" s="8">
         <f>K48+E48</f>
@@ -10942,7 +10946,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>4.5, 4.2</t>
+          <t>4.5, 3.9</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
@@ -10951,10 +10955,10 @@
         </is>
       </c>
       <c r="J49" s="8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L49" s="8">
         <f>K49+E49</f>
@@ -11020,19 +11024,19 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>5.4, 5.6</t>
+          <t>6.1, 6.15</t>
         </is>
       </c>
       <c r="I50" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J50" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L50" s="8">
         <f>K50+E50</f>
@@ -11102,19 +11106,19 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J51" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L51" s="8">
         <f>K51+E51</f>
@@ -11184,7 +11188,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I52" s="18" t="inlineStr">
@@ -11262,7 +11266,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I53" s="18" t="inlineStr">
@@ -11271,7 +11275,7 @@
         </is>
       </c>
       <c r="J53" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K53" s="8" t="n">
         <v>76</v>
@@ -11340,19 +11344,19 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>5.10, 2.13</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I54" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J54" s="8" t="n">
         <v>9</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L54" s="8">
         <f>K54+E54</f>
@@ -11418,16 +11422,16 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J55" s="8" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K55" s="8" t="n">
         <v>72</v>
@@ -11496,7 +11500,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>4.8, 5.11</t>
+          <t>4.8, 6.7, 6.6</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr">
@@ -11505,10 +11509,10 @@
         </is>
       </c>
       <c r="J56" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L56" s="8">
         <f>K56+E56</f>
@@ -11574,7 +11578,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>4.9, 5.7</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I57" s="18" t="inlineStr">
@@ -11583,10 +11587,10 @@
         </is>
       </c>
       <c r="J57" s="8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L57" s="8">
         <f>K57+E57</f>
@@ -11652,7 +11656,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>6.2, 6.21</t>
+          <t>6.2, 5.3</t>
         </is>
       </c>
       <c r="I58" s="18" t="inlineStr">
@@ -11808,7 +11812,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>6.21, 6.15, 6.14</t>
+          <t>5.11, 6.12</t>
         </is>
       </c>
       <c r="I60" s="18" t="inlineStr">
@@ -11817,10 +11821,10 @@
         </is>
       </c>
       <c r="J60" s="8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L60" s="8">
         <f>K60+E60</f>
@@ -11886,19 +11890,19 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I61" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="L61" s="8">
         <f>K61+E61</f>
@@ -11973,10 +11977,10 @@
         </is>
       </c>
       <c r="J62" s="8" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L62" s="8">
         <f>K62+E62</f>
@@ -12042,7 +12046,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.9, 6.21</t>
         </is>
       </c>
       <c r="I63" s="18" t="inlineStr">
@@ -12051,7 +12055,7 @@
         </is>
       </c>
       <c r="J63" s="8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K63" s="8" t="n">
         <v>94</v>
@@ -12120,7 +12124,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="I64" s="18" t="inlineStr">
@@ -12129,10 +12133,10 @@
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L64" s="8">
         <f>K64+E64</f>
@@ -12198,7 +12202,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I65" s="18" t="inlineStr">
@@ -12207,10 +12211,10 @@
         </is>
       </c>
       <c r="J65" s="8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L65" s="8">
         <f>K65+E65</f>
@@ -12288,7 +12292,7 @@
         <v>61</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L66" s="8">
         <f>K66+E66</f>
@@ -12354,7 +12358,7 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I67" s="18" t="inlineStr">
@@ -12366,7 +12370,7 @@
         <v>13</v>
       </c>
       <c r="K67" s="8" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="L67" s="8">
         <f>K67+E67</f>
@@ -12441,7 +12445,7 @@
         </is>
       </c>
       <c r="J68" s="8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K68" s="8" t="n">
         <v>60</v>
@@ -12510,7 +12514,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I69" s="18" t="inlineStr">
@@ -12519,10 +12523,10 @@
         </is>
       </c>
       <c r="J69" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L69" s="8">
         <f>K69+E69</f>
@@ -12588,7 +12592,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="I70" s="18" t="inlineStr">
@@ -12597,10 +12601,10 @@
         </is>
       </c>
       <c r="J70" s="8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L70" s="8">
         <f>K70+E70</f>
@@ -12666,7 +12670,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I71" s="18" t="inlineStr">
@@ -12675,10 +12679,10 @@
         </is>
       </c>
       <c r="J71" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L71" s="8">
         <f>K71+E71</f>
@@ -12744,19 +12748,19 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I72" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J72" s="8" t="n">
         <v>82</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L72" s="8">
         <f>K72+E72</f>
@@ -12822,7 +12826,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I73" s="18" t="inlineStr">
@@ -12831,10 +12835,10 @@
         </is>
       </c>
       <c r="J73" s="8" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L73" s="8">
         <f>K73+E73</f>
@@ -12900,7 +12904,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I74" s="18" t="inlineStr">
@@ -12909,10 +12913,10 @@
         </is>
       </c>
       <c r="J74" s="8" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L74" s="8">
         <f>K74+E74</f>
@@ -12978,19 +12982,19 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>1.8, 2.9</t>
+          <t>1.8, 6.13</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J75" s="8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L75" s="8">
         <f>K75+E75</f>
@@ -13056,7 +13060,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I76" s="18" t="inlineStr">
@@ -13065,10 +13069,10 @@
         </is>
       </c>
       <c r="J76" s="8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L76" s="8">
         <f>K76+E76</f>
@@ -13134,7 +13138,7 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>2.9, 3.5</t>
+          <t>3.5, 3.3</t>
         </is>
       </c>
       <c r="I77" s="18" t="inlineStr">
@@ -13143,10 +13147,10 @@
         </is>
       </c>
       <c r="J77" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K77" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L77" s="8">
         <f>K77+E77</f>
@@ -13212,7 +13216,7 @@
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>3.3, 4.5</t>
+          <t>3.9, 2.12</t>
         </is>
       </c>
       <c r="I78" s="18" t="inlineStr">
@@ -13221,10 +13225,10 @@
         </is>
       </c>
       <c r="J78" s="8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K78" s="8" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="L78" s="8">
         <f>K78+E78</f>
@@ -13299,7 +13303,7 @@
         </is>
       </c>
       <c r="J79" s="8" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K79" s="8" t="n">
         <v>59</v>
@@ -13368,7 +13372,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>6.8, 4.4</t>
+          <t>5.1, 5.7</t>
         </is>
       </c>
       <c r="I80" s="18" t="inlineStr">
@@ -13380,7 +13384,7 @@
         <v>60</v>
       </c>
       <c r="K80" s="8" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L80" s="8">
         <f>K80+E80</f>
@@ -13446,19 +13450,19 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>6.1, 6.3</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="I81" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J81" s="8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K81" s="8" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="L81" s="8">
         <f>K81+E81</f>
@@ -13514,7 +13518,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>4.14, 6.21</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
@@ -13533,10 +13537,10 @@
         </is>
       </c>
       <c r="J82" s="8" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="K82" s="8" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="L82" s="8">
         <f>K82+E82</f>
@@ -13552,7 +13556,7 @@
       </c>
       <c r="O82" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P82" s="8" t="inlineStr">
@@ -13602,7 +13606,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>5.9, 4.7</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I83" s="18" t="inlineStr">
@@ -13611,10 +13615,10 @@
         </is>
       </c>
       <c r="J83" s="8" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K83" s="8" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="L83" s="8">
         <f>K83+E83</f>
@@ -13680,16 +13684,16 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>6.7, 4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I84" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J84" s="8" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K84" s="8" t="n">
         <v>88</v>
@@ -13758,16 +13762,16 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I85" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J85" s="8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K85" s="8" t="n">
         <v>73</v>
@@ -50944,7 +50948,7 @@
         <v/>
       </c>
       <c r="D5" s="8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5" s="16">
         <f>Plan!J5</f>
@@ -50981,7 +50985,7 @@
         <v/>
       </c>
       <c r="D6" s="8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E6" s="16">
         <f>Plan!J7</f>
@@ -51018,7 +51022,7 @@
         <v/>
       </c>
       <c r="D7" s="8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E7" s="16">
         <f>Plan!J6</f>
@@ -51055,7 +51059,7 @@
         <v/>
       </c>
       <c r="D8" s="8" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="16">
         <f>Plan!J8</f>
@@ -51129,7 +51133,7 @@
         <v/>
       </c>
       <c r="D10" s="8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E10" s="16">
         <f>Plan!J14</f>
@@ -51166,7 +51170,7 @@
         <v/>
       </c>
       <c r="D11" s="8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" s="16">
         <f>Plan!J13</f>
@@ -51203,7 +51207,7 @@
         <v/>
       </c>
       <c r="D12" s="8" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E12" s="16">
         <f>Plan!J17</f>
@@ -51240,7 +51244,7 @@
         <v/>
       </c>
       <c r="D13" s="8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E13" s="16">
         <f>Plan!J28</f>
@@ -51277,7 +51281,7 @@
         <v/>
       </c>
       <c r="D14" s="8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14" s="16">
         <f>Plan!J18</f>
@@ -51306,22 +51310,22 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C15" s="35">
-        <f>Plan!C9</f>
+        <f>Plan!C11</f>
         <v/>
       </c>
       <c r="D15" s="8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E15" s="16">
-        <f>Plan!J9</f>
+        <f>Plan!J11</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>Plan!K9</f>
+        <f>Plan!K11</f>
         <v/>
       </c>
       <c r="G15" s="8">
@@ -51329,11 +51333,11 @@
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>Plan!I9</f>
+        <f>Plan!I11</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>Plan!O9</f>
+        <f>Plan!O11</f>
         <v/>
       </c>
     </row>
@@ -51343,22 +51347,22 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C16" s="35">
-        <f>Plan!C19</f>
+        <f>Plan!C15</f>
         <v/>
       </c>
       <c r="D16" s="8" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E16" s="16">
-        <f>Plan!J19</f>
+        <f>Plan!J15</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>Plan!K19</f>
+        <f>Plan!K15</f>
         <v/>
       </c>
       <c r="G16" s="8">
@@ -51366,11 +51370,11 @@
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>Plan!I19</f>
+        <f>Plan!I15</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>Plan!O19</f>
+        <f>Plan!O15</f>
         <v/>
       </c>
     </row>
@@ -51380,22 +51384,22 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C17" s="35">
-        <f>Plan!C15</f>
+        <f>Plan!C9</f>
         <v/>
       </c>
       <c r="D17" s="8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E17" s="16">
-        <f>Plan!J15</f>
+        <f>Plan!J9</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>Plan!K15</f>
+        <f>Plan!K9</f>
         <v/>
       </c>
       <c r="G17" s="8">
@@ -51403,11 +51407,11 @@
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>Plan!I15</f>
+        <f>Plan!I9</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>Plan!O15</f>
+        <f>Plan!O9</f>
         <v/>
       </c>
     </row>
@@ -51417,22 +51421,22 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C18" s="35">
-        <f>Plan!C11</f>
+        <f>Plan!C19</f>
         <v/>
       </c>
       <c r="D18" s="8" t="n">
         <v>31</v>
       </c>
       <c r="E18" s="16">
-        <f>Plan!J11</f>
+        <f>Plan!J19</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>Plan!K11</f>
+        <f>Plan!K19</f>
         <v/>
       </c>
       <c r="G18" s="8">
@@ -51440,11 +51444,11 @@
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>Plan!I11</f>
+        <f>Plan!I19</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>Plan!O11</f>
+        <f>Plan!O19</f>
         <v/>
       </c>
     </row>
@@ -51491,22 +51495,22 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="C20" s="35">
-        <f>Plan!C61</f>
+        <f>Plan!C67</f>
         <v/>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="16">
-        <f>Plan!J61</f>
+        <f>Plan!J67</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>Plan!K61</f>
+        <f>Plan!K67</f>
         <v/>
       </c>
       <c r="G20" s="8">
@@ -51514,11 +51518,11 @@
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>Plan!I61</f>
+        <f>Plan!I67</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>Plan!O61</f>
+        <f>Plan!O67</f>
         <v/>
       </c>
     </row>
@@ -51528,22 +51532,22 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C21" s="35">
-        <f>Plan!C26</f>
+        <f>Plan!C37</f>
         <v/>
       </c>
       <c r="D21" s="8" t="n">
         <v>29</v>
       </c>
       <c r="E21" s="16">
-        <f>Plan!J26</f>
+        <f>Plan!J37</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>Plan!K26</f>
+        <f>Plan!K37</f>
         <v/>
       </c>
       <c r="G21" s="8">
@@ -51551,11 +51555,11 @@
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>Plan!I26</f>
+        <f>Plan!I37</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>Plan!O26</f>
+        <f>Plan!O37</f>
         <v/>
       </c>
     </row>
@@ -51565,22 +51569,22 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C22" s="35">
-        <f>Plan!C27</f>
+        <f>Plan!C42</f>
         <v/>
       </c>
       <c r="D22" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" s="16">
-        <f>Plan!J27</f>
+        <f>Plan!J42</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>Plan!K27</f>
+        <f>Plan!K42</f>
         <v/>
       </c>
       <c r="G22" s="8">
@@ -51588,11 +51592,11 @@
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>Plan!I27</f>
+        <f>Plan!I42</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>Plan!O27</f>
+        <f>Plan!O42</f>
         <v/>
       </c>
     </row>
@@ -51602,22 +51606,22 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="C23" s="35">
-        <f>Plan!C37</f>
+        <f>Plan!C26</f>
         <v/>
       </c>
       <c r="D23" s="8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E23" s="16">
-        <f>Plan!J37</f>
+        <f>Plan!J26</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>Plan!K37</f>
+        <f>Plan!K26</f>
         <v/>
       </c>
       <c r="G23" s="8">
@@ -51625,11 +51629,11 @@
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>Plan!I37</f>
+        <f>Plan!I26</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>Plan!O37</f>
+        <f>Plan!O26</f>
         <v/>
       </c>
     </row>
@@ -51639,22 +51643,22 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C24" s="35">
-        <f>Plan!C31</f>
+        <f>Plan!C46</f>
         <v/>
       </c>
       <c r="D24" s="8" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E24" s="16">
-        <f>Plan!J31</f>
+        <f>Plan!J46</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>Plan!K31</f>
+        <f>Plan!K46</f>
         <v/>
       </c>
       <c r="G24" s="8">
@@ -51662,11 +51666,11 @@
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>Plan!I31</f>
+        <f>Plan!I46</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>Plan!O31</f>
+        <f>Plan!O46</f>
         <v/>
       </c>
     </row>
@@ -51684,7 +51688,7 @@
         <v/>
       </c>
       <c r="D25" s="8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="16">
         <f>Plan!J47</f>
@@ -51713,22 +51717,22 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C26" s="35">
-        <f>Plan!C10</f>
+        <f>Plan!C27</f>
         <v/>
       </c>
       <c r="D26" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="16">
-        <f>Plan!J10</f>
+        <f>Plan!J27</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>Plan!K10</f>
+        <f>Plan!K27</f>
         <v/>
       </c>
       <c r="G26" s="8">
@@ -51736,11 +51740,11 @@
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>Plan!I10</f>
+        <f>Plan!I27</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>Plan!O10</f>
+        <f>Plan!O27</f>
         <v/>
       </c>
     </row>
@@ -51750,22 +51754,22 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C27" s="35">
-        <f>Plan!C42</f>
+        <f>Plan!C31</f>
         <v/>
       </c>
       <c r="D27" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E27" s="16">
-        <f>Plan!J42</f>
+        <f>Plan!J31</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>Plan!K42</f>
+        <f>Plan!K31</f>
         <v/>
       </c>
       <c r="G27" s="8">
@@ -51773,11 +51777,11 @@
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>Plan!I42</f>
+        <f>Plan!I31</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>Plan!O42</f>
+        <f>Plan!O31</f>
         <v/>
       </c>
     </row>
@@ -51787,22 +51791,22 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="C28" s="35">
-        <f>Plan!C74</f>
+        <f>Plan!C73</f>
         <v/>
       </c>
       <c r="D28" s="8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E28" s="16">
-        <f>Plan!J74</f>
+        <f>Plan!J73</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>Plan!K74</f>
+        <f>Plan!K73</f>
         <v/>
       </c>
       <c r="G28" s="8">
@@ -51810,11 +51814,11 @@
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>Plan!I74</f>
+        <f>Plan!I73</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>Plan!O74</f>
+        <f>Plan!O73</f>
         <v/>
       </c>
     </row>
@@ -51824,22 +51828,22 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C29" s="35">
-        <f>Plan!C73</f>
+        <f>Plan!C10</f>
         <v/>
       </c>
       <c r="D29" s="8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E29" s="16">
-        <f>Plan!J73</f>
+        <f>Plan!J10</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>Plan!K73</f>
+        <f>Plan!K10</f>
         <v/>
       </c>
       <c r="G29" s="8">
@@ -51847,11 +51851,11 @@
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>Plan!I73</f>
+        <f>Plan!I10</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>Plan!O73</f>
+        <f>Plan!O10</f>
         <v/>
       </c>
     </row>
@@ -51861,22 +51865,22 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C30" s="35">
-        <f>Plan!C70</f>
+        <f>Plan!C36</f>
         <v/>
       </c>
       <c r="D30" s="8" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E30" s="16">
-        <f>Plan!J70</f>
+        <f>Plan!J36</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>Plan!K70</f>
+        <f>Plan!K36</f>
         <v/>
       </c>
       <c r="G30" s="8">
@@ -51884,11 +51888,11 @@
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>Plan!I70</f>
+        <f>Plan!I36</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>Plan!O70</f>
+        <f>Plan!O36</f>
         <v/>
       </c>
     </row>
@@ -51898,22 +51902,22 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="C31" s="35">
-        <f>Plan!C36</f>
+        <f>Plan!C74</f>
         <v/>
       </c>
       <c r="D31" s="8" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E31" s="16">
-        <f>Plan!J36</f>
+        <f>Plan!J74</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>Plan!K36</f>
+        <f>Plan!K74</f>
         <v/>
       </c>
       <c r="G31" s="8">
@@ -51921,11 +51925,11 @@
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>Plan!I36</f>
+        <f>Plan!I74</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>Plan!O36</f>
+        <f>Plan!O74</f>
         <v/>
       </c>
     </row>
@@ -51935,22 +51939,22 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="C32" s="35">
-        <f>Plan!C46</f>
+        <f>Plan!C75</f>
         <v/>
       </c>
       <c r="D32" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E32" s="16">
-        <f>Plan!J46</f>
+        <f>Plan!J75</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>Plan!K46</f>
+        <f>Plan!K75</f>
         <v/>
       </c>
       <c r="G32" s="8">
@@ -51958,11 +51962,11 @@
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>Plan!I46</f>
+        <f>Plan!I75</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>Plan!O46</f>
+        <f>Plan!O75</f>
         <v/>
       </c>
     </row>
@@ -51972,22 +51976,22 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="C33" s="35">
-        <f>Plan!C67</f>
+        <f>Plan!C12</f>
         <v/>
       </c>
       <c r="D33" s="8" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E33" s="16">
-        <f>Plan!J67</f>
+        <f>Plan!J12</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>Plan!K67</f>
+        <f>Plan!K12</f>
         <v/>
       </c>
       <c r="G33" s="8">
@@ -51995,11 +51999,11 @@
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>Plan!I67</f>
+        <f>Plan!I12</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>Plan!O67</f>
+        <f>Plan!O12</f>
         <v/>
       </c>
     </row>
@@ -52009,22 +52013,22 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="C34" s="35">
-        <f>Plan!C75</f>
+        <f>Plan!C70</f>
         <v/>
       </c>
       <c r="D34" s="8" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E34" s="16">
-        <f>Plan!J75</f>
+        <f>Plan!J70</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>Plan!K75</f>
+        <f>Plan!K70</f>
         <v/>
       </c>
       <c r="G34" s="8">
@@ -52032,11 +52036,11 @@
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>Plan!I75</f>
+        <f>Plan!I70</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>Plan!O75</f>
+        <f>Plan!O70</f>
         <v/>
       </c>
     </row>
@@ -52046,22 +52050,22 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="C35" s="35">
-        <f>Plan!C12</f>
+        <f>Plan!C76</f>
         <v/>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E35" s="16">
-        <f>Plan!J12</f>
+        <f>Plan!J76</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>Plan!K12</f>
+        <f>Plan!K76</f>
         <v/>
       </c>
       <c r="G35" s="8">
@@ -52069,11 +52073,11 @@
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>Plan!I12</f>
+        <f>Plan!I76</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>Plan!O12</f>
+        <f>Plan!O76</f>
         <v/>
       </c>
     </row>
@@ -52083,22 +52087,22 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="C36" s="35">
-        <f>Plan!C21</f>
+        <f>Plan!C32</f>
         <v/>
       </c>
       <c r="D36" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E36" s="16">
-        <f>Plan!J21</f>
+        <f>Plan!J32</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>Plan!K21</f>
+        <f>Plan!K32</f>
         <v/>
       </c>
       <c r="G36" s="8">
@@ -52106,11 +52110,11 @@
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>Plan!I21</f>
+        <f>Plan!I32</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>Plan!O21</f>
+        <f>Plan!O32</f>
         <v/>
       </c>
     </row>
@@ -52120,22 +52124,22 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="C37" s="35">
-        <f>Plan!C76</f>
+        <f>Plan!C77</f>
         <v/>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E37" s="16">
-        <f>Plan!J76</f>
+        <f>Plan!J77</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>Plan!K76</f>
+        <f>Plan!K77</f>
         <v/>
       </c>
       <c r="G37" s="8">
@@ -52143,11 +52147,11 @@
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>Plan!I76</f>
+        <f>Plan!I77</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>Plan!O76</f>
+        <f>Plan!O77</f>
         <v/>
       </c>
     </row>
@@ -52157,22 +52161,22 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C38" s="35">
-        <f>Plan!C77</f>
+        <f>Plan!C30</f>
         <v/>
       </c>
       <c r="D38" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E38" s="16">
-        <f>Plan!J77</f>
+        <f>Plan!J30</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>Plan!K77</f>
+        <f>Plan!K30</f>
         <v/>
       </c>
       <c r="G38" s="8">
@@ -52180,11 +52184,11 @@
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>Plan!I77</f>
+        <f>Plan!I30</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>Plan!O77</f>
+        <f>Plan!O30</f>
         <v/>
       </c>
     </row>
@@ -52194,22 +52198,22 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="C39" s="35">
-        <f>Plan!C32</f>
+        <f>Plan!C21</f>
         <v/>
       </c>
       <c r="D39" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E39" s="16">
-        <f>Plan!J32</f>
+        <f>Plan!J21</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>Plan!K32</f>
+        <f>Plan!K21</f>
         <v/>
       </c>
       <c r="G39" s="8">
@@ -52217,11 +52221,11 @@
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>Plan!I32</f>
+        <f>Plan!I21</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>Plan!O32</f>
+        <f>Plan!O21</f>
         <v/>
       </c>
     </row>
@@ -52231,22 +52235,22 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C40" s="35">
-        <f>Plan!C30</f>
+        <f>Plan!C38</f>
         <v/>
       </c>
       <c r="D40" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E40" s="16">
-        <f>Plan!J30</f>
+        <f>Plan!J38</f>
         <v/>
       </c>
       <c r="F40" s="16">
-        <f>Plan!K30</f>
+        <f>Plan!K38</f>
         <v/>
       </c>
       <c r="G40" s="8">
@@ -52254,11 +52258,11 @@
         <v/>
       </c>
       <c r="H40" s="16">
-        <f>Plan!I30</f>
+        <f>Plan!I38</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>Plan!O30</f>
+        <f>Plan!O38</f>
         <v/>
       </c>
     </row>
@@ -52268,22 +52272,22 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="C41" s="35">
-        <f>Plan!C78</f>
+        <f>Plan!C61</f>
         <v/>
       </c>
       <c r="D41" s="8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E41" s="16">
-        <f>Plan!J78</f>
+        <f>Plan!J61</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>Plan!K78</f>
+        <f>Plan!K61</f>
         <v/>
       </c>
       <c r="G41" s="8">
@@ -52291,11 +52295,11 @@
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>Plan!I78</f>
+        <f>Plan!I61</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>Plan!O78</f>
+        <f>Plan!O61</f>
         <v/>
       </c>
     </row>
@@ -52342,22 +52346,22 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C43" s="35">
-        <f>Plan!C49</f>
+        <f>Plan!C22</f>
         <v/>
       </c>
       <c r="D43" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E43" s="16">
-        <f>Plan!J49</f>
+        <f>Plan!J22</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>Plan!K49</f>
+        <f>Plan!K22</f>
         <v/>
       </c>
       <c r="G43" s="8">
@@ -52365,11 +52369,11 @@
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>Plan!I49</f>
+        <f>Plan!I22</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>Plan!O49</f>
+        <f>Plan!O22</f>
         <v/>
       </c>
     </row>
@@ -52379,22 +52383,22 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C44" s="35">
-        <f>Plan!C38</f>
+        <f>Plan!C49</f>
         <v/>
       </c>
       <c r="D44" s="8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E44" s="16">
-        <f>Plan!J38</f>
+        <f>Plan!J49</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>Plan!K38</f>
+        <f>Plan!K49</f>
         <v/>
       </c>
       <c r="G44" s="8">
@@ -52402,11 +52406,11 @@
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>Plan!I38</f>
+        <f>Plan!I49</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>Plan!O38</f>
+        <f>Plan!O49</f>
         <v/>
       </c>
     </row>
@@ -52416,22 +52420,22 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C45" s="35">
-        <f>Plan!C24</f>
+        <f>Plan!C35</f>
         <v/>
       </c>
       <c r="D45" s="8" t="n">
         <v>12</v>
       </c>
       <c r="E45" s="16">
-        <f>Plan!J24</f>
+        <f>Plan!J35</f>
         <v/>
       </c>
       <c r="F45" s="16">
-        <f>Plan!K24</f>
+        <f>Plan!K35</f>
         <v/>
       </c>
       <c r="G45" s="8">
@@ -52439,11 +52443,11 @@
         <v/>
       </c>
       <c r="H45" s="16">
-        <f>Plan!I24</f>
+        <f>Plan!I35</f>
         <v/>
       </c>
       <c r="I45" s="16">
-        <f>Plan!O24</f>
+        <f>Plan!O35</f>
         <v/>
       </c>
     </row>
@@ -52453,22 +52457,22 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="C46" s="35">
-        <f>Plan!C35</f>
+        <f>Plan!C33</f>
         <v/>
       </c>
       <c r="D46" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E46" s="16">
-        <f>Plan!J35</f>
+        <f>Plan!J33</f>
         <v/>
       </c>
       <c r="F46" s="16">
-        <f>Plan!K35</f>
+        <f>Plan!K33</f>
         <v/>
       </c>
       <c r="G46" s="8">
@@ -52476,11 +52480,11 @@
         <v/>
       </c>
       <c r="H46" s="16">
-        <f>Plan!I35</f>
+        <f>Plan!I33</f>
         <v/>
       </c>
       <c r="I46" s="16">
-        <f>Plan!O35</f>
+        <f>Plan!O33</f>
         <v/>
       </c>
     </row>
@@ -52490,22 +52494,22 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="C47" s="35">
-        <f>Plan!C33</f>
+        <f>Plan!C78</f>
         <v/>
       </c>
       <c r="D47" s="8" t="n">
         <v>13</v>
       </c>
       <c r="E47" s="16">
-        <f>Plan!J33</f>
+        <f>Plan!J78</f>
         <v/>
       </c>
       <c r="F47" s="16">
-        <f>Plan!K33</f>
+        <f>Plan!K78</f>
         <v/>
       </c>
       <c r="G47" s="8">
@@ -52513,11 +52517,11 @@
         <v/>
       </c>
       <c r="H47" s="16">
-        <f>Plan!I33</f>
+        <f>Plan!I78</f>
         <v/>
       </c>
       <c r="I47" s="16">
-        <f>Plan!O33</f>
+        <f>Plan!O78</f>
         <v/>
       </c>
     </row>
@@ -52527,22 +52531,22 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="C48" s="35">
-        <f>Plan!C22</f>
+        <f>Plan!C24</f>
         <v/>
       </c>
       <c r="D48" s="8" t="n">
         <v>12</v>
       </c>
       <c r="E48" s="16">
-        <f>Plan!J22</f>
+        <f>Plan!J24</f>
         <v/>
       </c>
       <c r="F48" s="16">
-        <f>Plan!K22</f>
+        <f>Plan!K24</f>
         <v/>
       </c>
       <c r="G48" s="8">
@@ -52550,11 +52554,11 @@
         <v/>
       </c>
       <c r="H48" s="16">
-        <f>Plan!I22</f>
+        <f>Plan!I24</f>
         <v/>
       </c>
       <c r="I48" s="16">
-        <f>Plan!O22</f>
+        <f>Plan!O24</f>
         <v/>
       </c>
     </row>
@@ -52572,7 +52576,7 @@
         <v/>
       </c>
       <c r="D49" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E49" s="16">
         <f>Plan!J79</f>
@@ -52675,22 +52679,22 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="C52" s="35">
-        <f>Plan!C66</f>
+        <f>Plan!C65</f>
         <v/>
       </c>
       <c r="D52" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E52" s="16">
-        <f>Plan!J66</f>
+        <f>Plan!J65</f>
         <v/>
       </c>
       <c r="F52" s="16">
-        <f>Plan!K66</f>
+        <f>Plan!K65</f>
         <v/>
       </c>
       <c r="G52" s="8">
@@ -52698,11 +52702,11 @@
         <v/>
       </c>
       <c r="H52" s="16">
-        <f>Plan!I66</f>
+        <f>Plan!I65</f>
         <v/>
       </c>
       <c r="I52" s="16">
-        <f>Plan!O66</f>
+        <f>Plan!O65</f>
         <v/>
       </c>
     </row>
@@ -52712,22 +52716,22 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C53" s="35">
-        <f>Plan!C48</f>
+        <f>Plan!C66</f>
         <v/>
       </c>
       <c r="D53" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E53" s="16">
-        <f>Plan!J48</f>
+        <f>Plan!J66</f>
         <v/>
       </c>
       <c r="F53" s="16">
-        <f>Plan!K48</f>
+        <f>Plan!K66</f>
         <v/>
       </c>
       <c r="G53" s="8">
@@ -52735,11 +52739,11 @@
         <v/>
       </c>
       <c r="H53" s="16">
-        <f>Plan!I48</f>
+        <f>Plan!I66</f>
         <v/>
       </c>
       <c r="I53" s="16">
-        <f>Plan!O48</f>
+        <f>Plan!O66</f>
         <v/>
       </c>
     </row>
@@ -52786,22 +52790,22 @@
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C55" s="35">
-        <f>Plan!C80</f>
+        <f>Plan!C40</f>
         <v/>
       </c>
       <c r="D55" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E55" s="16">
-        <f>Plan!J80</f>
+        <f>Plan!J40</f>
         <v/>
       </c>
       <c r="F55" s="16">
-        <f>Plan!K80</f>
+        <f>Plan!K40</f>
         <v/>
       </c>
       <c r="G55" s="8">
@@ -52809,11 +52813,11 @@
         <v/>
       </c>
       <c r="H55" s="16">
-        <f>Plan!I80</f>
+        <f>Plan!I40</f>
         <v/>
       </c>
       <c r="I55" s="16">
-        <f>Plan!O80</f>
+        <f>Plan!O40</f>
         <v/>
       </c>
     </row>
@@ -52823,22 +52827,22 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C56" s="35">
-        <f>Plan!C65</f>
+        <f>Plan!C29</f>
         <v/>
       </c>
       <c r="D56" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E56" s="16">
-        <f>Plan!J65</f>
+        <f>Plan!J29</f>
         <v/>
       </c>
       <c r="F56" s="16">
-        <f>Plan!K65</f>
+        <f>Plan!K29</f>
         <v/>
       </c>
       <c r="G56" s="8">
@@ -52846,11 +52850,11 @@
         <v/>
       </c>
       <c r="H56" s="16">
-        <f>Plan!I65</f>
+        <f>Plan!I29</f>
         <v/>
       </c>
       <c r="I56" s="16">
-        <f>Plan!O65</f>
+        <f>Plan!O29</f>
         <v/>
       </c>
     </row>
@@ -52860,22 +52864,22 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="C57" s="35">
-        <f>Plan!C40</f>
+        <f>Plan!C80</f>
         <v/>
       </c>
       <c r="D57" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E57" s="16">
-        <f>Plan!J40</f>
+        <f>Plan!J80</f>
         <v/>
       </c>
       <c r="F57" s="16">
-        <f>Plan!K40</f>
+        <f>Plan!K80</f>
         <v/>
       </c>
       <c r="G57" s="8">
@@ -52883,11 +52887,11 @@
         <v/>
       </c>
       <c r="H57" s="16">
-        <f>Plan!I40</f>
+        <f>Plan!I80</f>
         <v/>
       </c>
       <c r="I57" s="16">
-        <f>Plan!O40</f>
+        <f>Plan!O80</f>
         <v/>
       </c>
     </row>
@@ -52897,22 +52901,22 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C58" s="35">
-        <f>Plan!C45</f>
+        <f>Plan!C48</f>
         <v/>
       </c>
       <c r="D58" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E58" s="16">
-        <f>Plan!J45</f>
+        <f>Plan!J48</f>
         <v/>
       </c>
       <c r="F58" s="16">
-        <f>Plan!K45</f>
+        <f>Plan!K48</f>
         <v/>
       </c>
       <c r="G58" s="8">
@@ -52920,11 +52924,11 @@
         <v/>
       </c>
       <c r="H58" s="16">
-        <f>Plan!I45</f>
+        <f>Plan!I48</f>
         <v/>
       </c>
       <c r="I58" s="16">
-        <f>Plan!O45</f>
+        <f>Plan!O48</f>
         <v/>
       </c>
     </row>
@@ -52934,22 +52938,22 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="C59" s="35">
-        <f>Plan!C57</f>
+        <f>Plan!C54</f>
         <v/>
       </c>
       <c r="D59" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" s="16">
-        <f>Plan!J57</f>
+        <f>Plan!J54</f>
         <v/>
       </c>
       <c r="F59" s="16">
-        <f>Plan!K57</f>
+        <f>Plan!K54</f>
         <v/>
       </c>
       <c r="G59" s="8">
@@ -52957,11 +52961,11 @@
         <v/>
       </c>
       <c r="H59" s="16">
-        <f>Plan!I57</f>
+        <f>Plan!I54</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>Plan!O57</f>
+        <f>Plan!O54</f>
         <v/>
       </c>
     </row>
@@ -52971,22 +52975,22 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="C60" s="35">
-        <f>Plan!C54</f>
+        <f>Plan!C82</f>
         <v/>
       </c>
       <c r="D60" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E60" s="16">
-        <f>Plan!J54</f>
+        <f>Plan!J82</f>
         <v/>
       </c>
       <c r="F60" s="16">
-        <f>Plan!K54</f>
+        <f>Plan!K82</f>
         <v/>
       </c>
       <c r="G60" s="8">
@@ -52994,11 +52998,11 @@
         <v/>
       </c>
       <c r="H60" s="16">
-        <f>Plan!I54</f>
+        <f>Plan!I82</f>
         <v/>
       </c>
       <c r="I60" s="16">
-        <f>Plan!O54</f>
+        <f>Plan!O82</f>
         <v/>
       </c>
     </row>
@@ -53008,22 +53012,22 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C61" s="35">
-        <f>Plan!C25</f>
+        <f>Plan!C45</f>
         <v/>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="16">
-        <f>Plan!J25</f>
+        <f>Plan!J45</f>
         <v/>
       </c>
       <c r="F61" s="16">
-        <f>Plan!K25</f>
+        <f>Plan!K45</f>
         <v/>
       </c>
       <c r="G61" s="8">
@@ -53031,11 +53035,11 @@
         <v/>
       </c>
       <c r="H61" s="16">
-        <f>Plan!I25</f>
+        <f>Plan!I45</f>
         <v/>
       </c>
       <c r="I61" s="16">
-        <f>Plan!O25</f>
+        <f>Plan!O45</f>
         <v/>
       </c>
     </row>
@@ -53045,22 +53049,22 @@
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="C62" s="35">
-        <f>Plan!C29</f>
+        <f>Plan!C55</f>
         <v/>
       </c>
       <c r="D62" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" s="16">
-        <f>Plan!J29</f>
+        <f>Plan!J55</f>
         <v/>
       </c>
       <c r="F62" s="16">
-        <f>Plan!K29</f>
+        <f>Plan!K55</f>
         <v/>
       </c>
       <c r="G62" s="8">
@@ -53068,11 +53072,11 @@
         <v/>
       </c>
       <c r="H62" s="16">
-        <f>Plan!I29</f>
+        <f>Plan!I55</f>
         <v/>
       </c>
       <c r="I62" s="16">
-        <f>Plan!O29</f>
+        <f>Plan!O55</f>
         <v/>
       </c>
     </row>
@@ -53082,22 +53086,22 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="C63" s="35">
-        <f>Plan!C55</f>
+        <f>Plan!C85</f>
         <v/>
       </c>
       <c r="D63" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="16">
-        <f>Plan!J55</f>
+        <f>Plan!J85</f>
         <v/>
       </c>
       <c r="F63" s="16">
-        <f>Plan!K55</f>
+        <f>Plan!K85</f>
         <v/>
       </c>
       <c r="G63" s="8">
@@ -53105,11 +53109,11 @@
         <v/>
       </c>
       <c r="H63" s="16">
-        <f>Plan!I55</f>
+        <f>Plan!I85</f>
         <v/>
       </c>
       <c r="I63" s="16">
-        <f>Plan!O55</f>
+        <f>Plan!O85</f>
         <v/>
       </c>
     </row>
@@ -53119,22 +53123,22 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="C64" s="35">
-        <f>Plan!C85</f>
+        <f>Plan!C57</f>
         <v/>
       </c>
       <c r="D64" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="16">
-        <f>Plan!J85</f>
+        <f>Plan!J57</f>
         <v/>
       </c>
       <c r="F64" s="16">
-        <f>Plan!K85</f>
+        <f>Plan!K57</f>
         <v/>
       </c>
       <c r="G64" s="8">
@@ -53142,11 +53146,11 @@
         <v/>
       </c>
       <c r="H64" s="16">
-        <f>Plan!I85</f>
+        <f>Plan!I57</f>
         <v/>
       </c>
       <c r="I64" s="16">
-        <f>Plan!O85</f>
+        <f>Plan!O57</f>
         <v/>
       </c>
     </row>
@@ -53156,22 +53160,22 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C65" s="35">
-        <f>Plan!C50</f>
+        <f>Plan!C25</f>
         <v/>
       </c>
       <c r="D65" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E65" s="16">
-        <f>Plan!J50</f>
+        <f>Plan!J25</f>
         <v/>
       </c>
       <c r="F65" s="16">
-        <f>Plan!K50</f>
+        <f>Plan!K25</f>
         <v/>
       </c>
       <c r="G65" s="8">
@@ -53179,11 +53183,11 @@
         <v/>
       </c>
       <c r="H65" s="16">
-        <f>Plan!I50</f>
+        <f>Plan!I25</f>
         <v/>
       </c>
       <c r="I65" s="16">
-        <f>Plan!O50</f>
+        <f>Plan!O25</f>
         <v/>
       </c>
     </row>
@@ -53341,22 +53345,22 @@
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="C70" s="35">
-        <f>Plan!C69</f>
+        <f>Plan!C71</f>
         <v/>
       </c>
       <c r="D70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="16">
-        <f>Plan!J69</f>
+        <f>Plan!J71</f>
         <v/>
       </c>
       <c r="F70" s="16">
-        <f>Plan!K69</f>
+        <f>Plan!K71</f>
         <v/>
       </c>
       <c r="G70" s="8">
@@ -53364,11 +53368,11 @@
         <v/>
       </c>
       <c r="H70" s="16">
-        <f>Plan!I69</f>
+        <f>Plan!I71</f>
         <v/>
       </c>
       <c r="I70" s="16">
-        <f>Plan!O69</f>
+        <f>Plan!O71</f>
         <v/>
       </c>
     </row>
@@ -53452,22 +53456,22 @@
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C73" s="35">
-        <f>Plan!C81</f>
+        <f>Plan!C50</f>
         <v/>
       </c>
       <c r="D73" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E73" s="16">
-        <f>Plan!J81</f>
+        <f>Plan!J50</f>
         <v/>
       </c>
       <c r="F73" s="16">
-        <f>Plan!K81</f>
+        <f>Plan!K50</f>
         <v/>
       </c>
       <c r="G73" s="8">
@@ -53475,11 +53479,11 @@
         <v/>
       </c>
       <c r="H73" s="16">
-        <f>Plan!I81</f>
+        <f>Plan!I50</f>
         <v/>
       </c>
       <c r="I73" s="16">
-        <f>Plan!O81</f>
+        <f>Plan!O50</f>
         <v/>
       </c>
     </row>
@@ -53489,22 +53493,22 @@
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="C74" s="35">
-        <f>Plan!C60</f>
+        <f>Plan!C72</f>
         <v/>
       </c>
       <c r="D74" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E74" s="16">
-        <f>Plan!J60</f>
+        <f>Plan!J72</f>
         <v/>
       </c>
       <c r="F74" s="16">
-        <f>Plan!K60</f>
+        <f>Plan!K72</f>
         <v/>
       </c>
       <c r="G74" s="8">
@@ -53512,11 +53516,11 @@
         <v/>
       </c>
       <c r="H74" s="16">
-        <f>Plan!I60</f>
+        <f>Plan!I72</f>
         <v/>
       </c>
       <c r="I74" s="16">
-        <f>Plan!O60</f>
+        <f>Plan!O72</f>
         <v/>
       </c>
     </row>
@@ -53526,22 +53530,22 @@
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="C75" s="35">
-        <f>Plan!C72</f>
+        <f>Plan!C60</f>
         <v/>
       </c>
       <c r="D75" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E75" s="16">
-        <f>Plan!J72</f>
+        <f>Plan!J60</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>Plan!K72</f>
+        <f>Plan!K60</f>
         <v/>
       </c>
       <c r="G75" s="8">
@@ -53549,11 +53553,11 @@
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>Plan!I72</f>
+        <f>Plan!I60</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>Plan!O72</f>
+        <f>Plan!O60</f>
         <v/>
       </c>
     </row>
@@ -53563,22 +53567,22 @@
       </c>
       <c r="B76" s="18" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="C76" s="35">
-        <f>Plan!C71</f>
+        <f>Plan!C83</f>
         <v/>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="16">
-        <f>Plan!J71</f>
+        <f>Plan!J83</f>
         <v/>
       </c>
       <c r="F76" s="16">
-        <f>Plan!K71</f>
+        <f>Plan!K83</f>
         <v/>
       </c>
       <c r="G76" s="8">
@@ -53586,11 +53590,11 @@
         <v/>
       </c>
       <c r="H76" s="16">
-        <f>Plan!I71</f>
+        <f>Plan!I83</f>
         <v/>
       </c>
       <c r="I76" s="16">
-        <f>Plan!O71</f>
+        <f>Plan!O83</f>
         <v/>
       </c>
     </row>
@@ -53600,22 +53604,22 @@
       </c>
       <c r="B77" s="18" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="C77" s="35">
-        <f>Plan!C62</f>
+        <f>Plan!C69</f>
         <v/>
       </c>
       <c r="D77" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E77" s="16">
-        <f>Plan!J62</f>
+        <f>Plan!J69</f>
         <v/>
       </c>
       <c r="F77" s="16">
-        <f>Plan!K62</f>
+        <f>Plan!K69</f>
         <v/>
       </c>
       <c r="G77" s="8">
@@ -53623,11 +53627,11 @@
         <v/>
       </c>
       <c r="H77" s="16">
-        <f>Plan!I62</f>
+        <f>Plan!I69</f>
         <v/>
       </c>
       <c r="I77" s="16">
-        <f>Plan!O62</f>
+        <f>Plan!O69</f>
         <v/>
       </c>
     </row>
@@ -53637,22 +53641,22 @@
       </c>
       <c r="B78" s="18" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="C78" s="35">
-        <f>Plan!C82</f>
+        <f>Plan!C62</f>
         <v/>
       </c>
       <c r="D78" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E78" s="16">
-        <f>Plan!J82</f>
+        <f>Plan!J62</f>
         <v/>
       </c>
       <c r="F78" s="16">
-        <f>Plan!K82</f>
+        <f>Plan!K62</f>
         <v/>
       </c>
       <c r="G78" s="8">
@@ -53660,11 +53664,11 @@
         <v/>
       </c>
       <c r="H78" s="16">
-        <f>Plan!I82</f>
+        <f>Plan!I62</f>
         <v/>
       </c>
       <c r="I78" s="16">
-        <f>Plan!O82</f>
+        <f>Plan!O62</f>
         <v/>
       </c>
     </row>
@@ -53674,22 +53678,22 @@
       </c>
       <c r="B79" s="18" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C79" s="35">
-        <f>Plan!C84</f>
+        <f>Plan!C43</f>
         <v/>
       </c>
       <c r="D79" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" s="16">
-        <f>Plan!J84</f>
+        <f>Plan!J43</f>
         <v/>
       </c>
       <c r="F79" s="16">
-        <f>Plan!K84</f>
+        <f>Plan!K43</f>
         <v/>
       </c>
       <c r="G79" s="8">
@@ -53697,11 +53701,11 @@
         <v/>
       </c>
       <c r="H79" s="16">
-        <f>Plan!I84</f>
+        <f>Plan!I43</f>
         <v/>
       </c>
       <c r="I79" s="16">
-        <f>Plan!O84</f>
+        <f>Plan!O43</f>
         <v/>
       </c>
     </row>
@@ -53711,22 +53715,22 @@
       </c>
       <c r="B80" s="18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="C80" s="35">
-        <f>Plan!C64</f>
+        <f>Plan!C84</f>
         <v/>
       </c>
       <c r="D80" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="16">
-        <f>Plan!J64</f>
+        <f>Plan!J84</f>
         <v/>
       </c>
       <c r="F80" s="16">
-        <f>Plan!K64</f>
+        <f>Plan!K84</f>
         <v/>
       </c>
       <c r="G80" s="8">
@@ -53734,11 +53738,11 @@
         <v/>
       </c>
       <c r="H80" s="16">
-        <f>Plan!I64</f>
+        <f>Plan!I84</f>
         <v/>
       </c>
       <c r="I80" s="16">
-        <f>Plan!O64</f>
+        <f>Plan!O84</f>
         <v/>
       </c>
     </row>
@@ -53822,22 +53826,22 @@
       </c>
       <c r="B83" s="18" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="C83" s="35">
-        <f>Plan!C83</f>
+        <f>Plan!C64</f>
         <v/>
       </c>
       <c r="D83" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="16">
-        <f>Plan!J83</f>
+        <f>Plan!J64</f>
         <v/>
       </c>
       <c r="F83" s="16">
-        <f>Plan!K83</f>
+        <f>Plan!K64</f>
         <v/>
       </c>
       <c r="G83" s="8">
@@ -53845,11 +53849,11 @@
         <v/>
       </c>
       <c r="H83" s="16">
-        <f>Plan!I83</f>
+        <f>Plan!I64</f>
         <v/>
       </c>
       <c r="I83" s="16">
-        <f>Plan!O83</f>
+        <f>Plan!O64</f>
         <v/>
       </c>
     </row>
@@ -53859,22 +53863,22 @@
       </c>
       <c r="B84" s="18" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="C84" s="35">
-        <f>Plan!C43</f>
+        <f>Plan!C63</f>
         <v/>
       </c>
       <c r="D84" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" s="16">
-        <f>Plan!J43</f>
+        <f>Plan!J63</f>
         <v/>
       </c>
       <c r="F84" s="16">
-        <f>Plan!K43</f>
+        <f>Plan!K63</f>
         <v/>
       </c>
       <c r="G84" s="8">
@@ -53882,11 +53886,11 @@
         <v/>
       </c>
       <c r="H84" s="16">
-        <f>Plan!I43</f>
+        <f>Plan!I63</f>
         <v/>
       </c>
       <c r="I84" s="16">
-        <f>Plan!O43</f>
+        <f>Plan!O63</f>
         <v/>
       </c>
     </row>
@@ -53896,22 +53900,22 @@
       </c>
       <c r="B85" s="18" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="C85" s="35">
-        <f>Plan!C63</f>
+        <f>Plan!C81</f>
         <v/>
       </c>
       <c r="D85" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="16">
-        <f>Plan!J63</f>
+        <f>Plan!J81</f>
         <v/>
       </c>
       <c r="F85" s="16">
-        <f>Plan!K63</f>
+        <f>Plan!K81</f>
         <v/>
       </c>
       <c r="G85" s="8">
@@ -53919,11 +53923,11 @@
         <v/>
       </c>
       <c r="H85" s="16">
-        <f>Plan!I63</f>
+        <f>Plan!I81</f>
         <v/>
       </c>
       <c r="I85" s="16">
-        <f>Plan!O63</f>
+        <f>Plan!O81</f>
         <v/>
       </c>
     </row>
@@ -54621,7 +54625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -54685,17 +54689,17 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>5.4, 6.21, 6.22; P-81</t>
+          <t>6.22; P-20, P-21, P-43, P-45, P-105</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Política v1 en publicación; tanda 2 en develop</t>
+          <t>Tanda 2 en producción y pendientes de configuración cerrados</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Tanda 2 en develop e4b8350 con 7 migraciones 20260930200* por aplicar y develop a main pendiente (6.22). Política v1 del Dr. Breinner con 7.3, 8 y 18 en revisión. E2E desactualizadas (6.21). Copia de seguridad de producción del 30-sep.</t>
+          <t>Sebas aplicó las 7 migraciones 20260930200* y fusionó develop→main. Hechos: P-20 (plantilla del código), P-43 (límite de intentos), P-45 (ajustes OTP), P-105 (CRON_SECRET y plantilla del aviso institucional). P-21 cancelado: el límite de Resend no preocupa por ahora. P-54 y P-73 siguen pendientes.</t>
         </is>
       </c>
     </row>
@@ -54707,22 +54711,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal (Sebas)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.4, 6.21, 6.22; P-81</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Medios en el detalle de convenios</t>
+          <t>Política v1 en publicación; tanda 2 en develop</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Videos y PDF de Racing Tours mapeados por NIT en lib/convenios.ts; develop 4357939 (video de Locos en politica-datos-v1).</t>
+          <t>Tanda 2 en develop e4b8350 con 7 migraciones 20260930200* por aplicar y develop a main pendiente (6.22). Política v1 del Dr. Breinner con 7.3, 8 y 18 en revisión. E2E desactualizadas (6.21). Copia de seguridad de producción del 30-sep.</t>
         </is>
       </c>
     </row>
@@ -54734,22 +54738,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>4.14, 6.22</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>SP remapeado a IJ (§12.14)</t>
+          <t>Medios en el detalle de convenios</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>En la migración 20260930200100 (sin aplicar); R-10/R-11 decididos; pgTAP, db reset y vitest en verde.</t>
+          <t>Videos y PDF de Racing Tours mapeados por NIT en lib/convenios.ts; develop 4357939 (video de Locos en politica-datos-v1).</t>
         </is>
       </c>
     </row>
@@ -54759,24 +54763,24 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>ga-disenador-lienzo + ga-auditor-supabase + ga-funcionalidad-botones + ga-diseno-a-codigo</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>4.14, 6.21, 6.22, 5.11, 5.12</t>
+          <t>4.14, 6.22</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Tanda 2 (§12) hecha en local</t>
+          <t>SP remapeado a IJ (§12.14)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Lienzo 3q, migraciones 20260930200000–200600 (pgTAP 464/464), acciones y UI (vitest 516, build en verde). Sin aplicar en producción. Backlog §12.12 agregado.</t>
+          <t>En la migración 20260930200100 (sin aplicar); R-10/R-11 decididos; pgTAP, db reset y vitest en verde.</t>
         </is>
       </c>
     </row>
@@ -54786,24 +54790,24 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ga-enlace-cooperativa</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>ga-disenador-lienzo + ga-auditor-supabase + ga-funcionalidad-botones + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>P-14, P-47, P-76..P-80, P-90..P-93, P-97; P-106</t>
+          <t>4.14, 6.21, 6.22, 5.11, 5.12</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Respuestas de la cooperativa</t>
+          <t>Tanda 2 (§12) hecha en local</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>docs/cooperativa/preguntas.md. R-10 y R-11 cerrados por Sebas (§12.14, SP a IJ); abierta R-09.</t>
+          <t>Lienzo 3q, migraciones 20260930200000–200600 (pgTAP 464/464), acciones y UI (vitest 516, build en verde). Sin aplicar en producción. Backlog §12.12 agregado.</t>
         </is>
       </c>
     </row>
@@ -54815,22 +54819,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>sesión principal (Sebas)</t>
+          <t>ga-enlace-cooperativa</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>1.8, 6.20, 5.10, 4.7, 4.8, 5.9, 6.14, 6.15; P-104, P-46, P-75, P-69, P-72, P-73</t>
+          <t>P-14, P-47, P-76..P-80, P-90..P-93, P-97; P-106</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>C+ y tanda 1 de Ricardo en producción; Carlos sale</t>
+          <t>Respuestas de la cooperativa</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>PR develop a main de C+ fusionado; PR #5 fusionado y 19 migraciones aplicadas. Asesores Miguel Rueda, Rafael González y Nany Barón creados. Vercel Pro (cron cada hora). Carlos Pardo no sigue: se le pagan 150.000 COP; sus tareas pasan a agentes/Sebas (5.10 ya hecha).</t>
+          <t>docs/cooperativa/preguntas.md. R-10 y R-11 cerrados por Sebas (§12.14, SP a IJ); abierta R-09.</t>
         </is>
       </c>
     </row>
@@ -54842,22 +54846,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ga-correos</t>
+          <t>sesión principal (Sebas)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>4.13; P-105</t>
+          <t>1.8, 6.20, 5.10, 4.7, 4.8, 5.9, 6.14, 6.15; P-104, P-46, P-75, P-69, P-72, P-73</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Plantilla ga-aviso-institucional</t>
+          <t>C+ y tanda 1 de Ricardo en producción; Carlos sale</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>docs/resend/aviso-institucional.*; falta publicarla y crear la variable en Vercel.</t>
+          <t>PR develop a main de C+ fusionado; PR #5 fusionado y 19 migraciones aplicadas. Asesores Miguel Rueda, Rafael González y Nany Barón creados. Vercel Pro (cron cada hora). Carlos Pardo no sigue: se le pagan 150.000 COP; sus tareas pasan a agentes/Sebas (5.10 ya hecha).</t>
         </is>
       </c>
     </row>
@@ -54869,22 +54873,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-correos</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>6.2, 4.13</t>
+          <t>4.13; P-105</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Dos pasadas de seguridad</t>
+          <t>Plantilla ga-aviso-institucional</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>RS-01 a RS-22 sobre migraciones y pantallas de Ricardo. 6.2 sigue En curso (depende de 4.3).</t>
+          <t>docs/resend/aviso-institucional.*; falta publicarla y crear la variable en Vercel.</t>
         </is>
       </c>
     </row>
@@ -54896,22 +54900,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>6.2, 4.13</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>UI 3j–3p</t>
+          <t>Dos pasadas de seguridad</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Pantallas y revisión de diseño A1–A3.</t>
+          <t>RS-01 a RS-22 sobre migraciones y pantallas de Ricardo. 6.2 sigue En curso (depende de 4.3).</t>
         </is>
       </c>
     </row>
@@ -54923,7 +54927,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -54933,12 +54937,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Lógica y datos de 3j–3p y correcciones de seguridad</t>
+          <t>UI 3j–3p</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>RS-01..RS-22 de código, limpieza de fotos por RPC (5.10), aviso institucional siempre. vitest 503, build en verde.</t>
+          <t>Pantallas y revisión de diseño A1–A3.</t>
         </is>
       </c>
     </row>
@@ -54950,22 +54954,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Lienzo 3j–3p</t>
+          <t>Lógica y datos de 3j–3p y correcciones de seguridad</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Piezas 3j–3n, 3o/3p (D-15, D-16) y revisión de fidelidad.</t>
+          <t>RS-01..RS-22 de código, limpieza de fotos por RPC (5.10), aviso institucional siempre. vitest 503, build en verde.</t>
         </is>
       </c>
     </row>
@@ -54977,49 +54981,49 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>4.12; P-46</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Migraciones tanda 1 de Ricardo (29/30-sep)</t>
+          <t>Lienzo 3j–3p</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>20260929100000..100700, 20260930100000..100500: grados, nómina, proceso ejecutivo, alertas, comisiones con pagos editables, tasa oculta (P-100), crédito solo en «operando», segunda pasada RS-17/18/20/21. pgTAP en verde.</t>
+          <t>Piezas 3j–3n, 3o/3p (D-15, D-16) y revisión de fidelidad.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-69, P-72</t>
+          <t>4.12; P-46</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Primera entrega de Carlos Pardo revisada: NO fusionable</t>
+          <t>Migraciones tanda 1 de Ricardo (29/30-sep)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Revisión del ZIP del repo privado de Carlos (base main anterior al rediseño C+, no rediseno-c-plus). Motivos: reintroduce la fuga F2-03 y pierde el revoke en resumen_clientes_asesor; el motivo de rechazo de afiliación usa una columna inexistente sin migración (rechazar dejaría de funcionar); convenios administrables usa columnas y un bucket de Storage inexistentes y acciones sin exigirAdmin ni validación; la purga Ley 1581 usa columnas/bucket equivocados y el cron queda abierto si falta CRON_SECRET; claves en .env.example, console.log y configuración de túnel; borra /asesor/demo (ya en producción) y renombra /cuenta/solicitar (ya en producción); sin pruebas. Se le envió a Carlos la lista de correcciones para rehacer el encargo sobre rediseno-c-plus, con un PR por tarea. 4.7, 4.8, 5.9, 5.10, 6.14 y 6.15 siguen Pendiente; P-69 con el mismo detalle y P-72 (acceso de colaborador en GitHub) sigue En curso, con la nota de que el ZIP en vez de un PR sugiere que ese acceso todavía no está confirmado.</t>
+          <t>20260929100000..100700, 20260930100000..100500: grados, nómina, proceso ejecutivo, alertas, comisiones con pagos editables, tasa oculta (P-100), crédito solo en «operando», segunda pasada RS-17/18/20/21. pgTAP en verde.</t>
         </is>
       </c>
     </row>
@@ -55036,17 +55040,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>6.18; nuevo P-104</t>
+          <t>4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-69, P-72</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Push y fusión de rediseno-c-plus a develop autorizados por Sebas; 6.18 pasa a Hecho</t>
+          <t>Primera entrega de Carlos Pardo revisada: NO fusionable</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Con la suite e2e en 290/290, Sebas autorizó subir a producción el rediseño C+ con el arreglo de la tasa; la sesión principal fusionó rediseno-c-plus a develop y la subió a origin. 6.18 pasa a Hecho. Nuevo pendiente P-104 (Alta, responsable Sebas): falta que apruebe/fusione el PR develop → main para que Vercel despliegue en producción.</t>
+          <t>Revisión del ZIP del repo privado de Carlos (base main anterior al rediseño C+, no rediseno-c-plus). Motivos: reintroduce la fuga F2-03 y pierde el revoke en resumen_clientes_asesor; el motivo de rechazo de afiliación usa una columna inexistente sin migración (rechazar dejaría de funcionar); convenios administrables usa columnas y un bucket de Storage inexistentes y acciones sin exigirAdmin ni validación; la purga Ley 1581 usa columnas/bucket equivocados y el cron queda abierto si falta CRON_SECRET; claves en .env.example, console.log y configuración de túnel; borra /asesor/demo (ya en producción) y renombra /cuenta/solicitar (ya en producción); sin pruebas. Se le envió a Carlos la lista de correcciones para rehacer el encargo sobre rediseno-c-plus, con un PR por tarea. 4.7, 4.8, 5.9, 5.10, 6.14 y 6.15 siguen Pendiente; P-69 con el mismo detalle y P-72 (acceso de colaborador en GitHub) sigue En curso, con la nota de que el ZIP en vez de un PR sugiere que ese acceso todavía no está confirmado.</t>
         </is>
       </c>
     </row>
@@ -55058,49 +55062,49 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>6.18 (verificación pre-commit de rediseno-c-plus)</t>
+          <t>6.18; nuevo P-104</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Suite e2e completa 290/290 tras independizar las pruebas del crédito de ejemplo</t>
+          <t>Push y fusión de rediseno-c-plus a develop autorizados por Sebas; 6.18 pasa a Hecho</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Encontró que, además del crédito huérfano ya corregido por el afterAll de la sesión principal, el segundo test de k-roles.spec.ts también resuelve el crédito del seed (cédula 1234567890), que queda inmutable por un trigger de negocio. Agregó restaurarCreditoDeEjemplo() en tests/e2e/utils.ts (borra y recrea la fila del seed) y la usó en c-cuenta.spec.ts, e-diseno.spec.ts e i-despliegue.spec.ts (sin tocar k-roles.spec.ts). Resultado: 4 suites afectadas en 0 fallas (antes 2), suite e2e completa 290/290 (antes 285/5), tsc/vitest (347)/lint/build en verde. Detalle en docs/verificaciones/2026-09-29-pre-commit.md. Listo para que la sesión principal haga el commit y la fusión a develop.</t>
+          <t>Con la suite e2e en 290/290, Sebas autorizó subir a producción el rediseño C+ con el arreglo de la tasa; la sesión principal fusionó rediseno-c-plus a develop y la subió a origin. 6.18 pasa a Hecho. Nuevo pendiente P-104 (Alta, responsable Sebas): falta que apruebe/fusione el PR develop → main para que Vercel despliegue en producción.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>2.14; P-103</t>
+          <t>6.18 (verificación pre-commit de rediseno-c-plus)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Se quita la sección de testimonios de la landing (decisión de Sebas)</t>
+          <t>Suite e2e completa 290/290 tras independizar las pruebas del crédito de ejemplo</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Commit 4c63924: sección de testimonios (que estaba oculta desde P-102 por tener textos de ejemplo) eliminada de la landing por decisión de Sebas. P-103 (D-07, ¿se mantiene la sección?) cierra Hecho con esa decisión: no se mantiene.</t>
+          <t>Encontró que, además del crédito huérfano ya corregido por el afterAll de la sesión principal, el segundo test de k-roles.spec.ts también resuelve el crédito del seed (cédula 1234567890), que queda inmutable por un trigger de negocio. Agregó restaurarCreditoDeEjemplo() en tests/e2e/utils.ts (borra y recrea la fila del seed) y la usó en c-cuenta.spec.ts, e-diseno.spec.ts e i-despliegue.spec.ts (sin tocar k-roles.spec.ts). Resultado: 4 suites afectadas en 0 fallas (antes 2), suite e2e completa 290/290 (antes 285/5), tsc/vitest (347)/lint/build en verde. Detalle en docs/verificaciones/2026-09-29-pre-commit.md. Listo para que la sesión principal haga el commit y la fusión a develop.</t>
         </is>
       </c>
     </row>
@@ -55117,17 +55121,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>4.11; P-95, P-96</t>
+          <t>2.14; P-103</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Sebas aprueba P-95 y P-96; ambos pasan a Hecho</t>
+          <t>Se quita la sección de testimonios de la landing (decisión de Sebas)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>P-95 (botón «Escribir por WhatsApp» en el detalle de afiliación) aprobado tal cual estaba diseñado e implementado. P-96 (asignar asesor) aprobado con alcance limitado por ahora: solo asignar, solo cuando la afiliación está aprobada y el asociado todavía no tiene asesor; sin cambiar ni quitar un asesor ya asignado. La sesión principal agregó el estado «ya asignado» persistente al recargar (commit 3b5ae14), cerrando el residuo que había dejado ga-diseno-a-codigo.</t>
+          <t>Commit 4c63924: sección de testimonios (que estaba oculta desde P-102 por tener textos de ejemplo) eliminada de la landing por decisión de Sebas. P-103 (D-07, ¿se mantiene la sección?) cierra Hecho con esa decisión: no se mantiene.</t>
         </is>
       </c>
     </row>
@@ -55139,22 +55143,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>4.11 (revisión de diseño 3e/3i)</t>
+          <t>4.11; P-95, P-96</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Revisión de diseño aprobada con cambios menores</t>
+          <t>Sebas aprueba P-95 y P-96; ambos pasan a Hecho</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Comparó el lienzo (piezas 3e/3i) contra PanelAfiliacionDetalle.tsx, AsignarAsesor.tsx, Iconos.tsx y lib/admin/whatsapp.ts. Veredicto: aprobado con cambios menores, incluido el estado «ya asignado» persistente al recargar. Corrigió 4 detalles menores en el propio lienzo (layout del botón de WhatsApp, glifo de las mini-muestras, foco sin halo extra, color suelto #182530 → token #1C2F3B). No tocó código. Detalle en docs/verificaciones/2026-09-27-revision-diseno-3e-3i.md.</t>
+          <t>P-95 (botón «Escribir por WhatsApp» en el detalle de afiliación) aprobado tal cual estaba diseñado e implementado. P-96 (asignar asesor) aprobado con alcance limitado por ahora: solo asignar, solo cuando la afiliación está aprobada y el asociado todavía no tiene asesor; sin cambiar ni quitar un asesor ya asignado. La sesión principal agregó el estado «ya asignado» persistente al recargar (commit 3b5ae14), cerrando el residuo que había dejado ga-diseno-a-codigo.</t>
         </is>
       </c>
     </row>
@@ -55166,22 +55170,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>4.11, P-95, P-96</t>
+          <t>4.11 (revisión de diseño 3e/3i)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>WhatsApp y bloque «Asesor» maquetados y conectados en código</t>
+          <t>Revisión de diseño aprobada con cambios menores</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Botón «Escribir por WhatsApp» habilitado en PanelAfiliacionDetalle.tsx (enlace wa.me en pestaña nueva con mensaje prellenado, glifo SVG IconoWhatsapp, normalización pura del celular en lib/admin/whatsapp.ts con pruebas Vitest, estado deshabilitado con motivo si el celular no es válido). Bloque «Asesor» nuevo (components/admin/AsignarAsesor.tsx) conectado a asignarAsesor con useActionState y sus 5 estados; corrigió una condición de carrera real (revalidatePath refrescaba la página y dejaba perfilAsociado en null justo tras el éxito) «congelando» la prop inicial con useState en PanelAfiliacionDetalle. Prueba nueva en tests/e2e/k-roles.spec.ts. tsc, lint, build, vitest (360) y Playwright (k-roles, escritorio) en verde. Dejó abierto para la sesión principal el estado «ya asignado» persistente al recargar (requería tocar la página de servidor, fuera de su encargo); cerrado después por la sesión principal (commit 3b5ae14, ver más abajo).</t>
+          <t>Comparó el lienzo (piezas 3e/3i) contra PanelAfiliacionDetalle.tsx, AsignarAsesor.tsx, Iconos.tsx y lib/admin/whatsapp.ts. Veredicto: aprobado con cambios menores, incluido el estado «ya asignado» persistente al recargar. Corrigió 4 detalles menores en el propio lienzo (layout del botón de WhatsApp, glifo de las mini-muestras, foco sin halo extra, color suelto #182530 → token #1C2F3B). No tocó código. Detalle en docs/verificaciones/2026-09-27-revision-diseno-3e-3i.md.</t>
         </is>
       </c>
     </row>
@@ -55193,22 +55197,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>4.11, P-96</t>
+          <t>4.11, P-95, P-96</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Server Action asignarAsesor lista en el servidor</t>
+          <t>WhatsApp y bloque «Asesor» maquetados y conectados en código</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>asignarAsesor en app/admin/afiliaciones/actions.ts (exigirAdmin, zod esquemaAsignarAsesor, re-verificación en servidor de afiliación aprobada + perfil sin asesor + update condicional .is("asesor_id", null)); app/admin/afiliaciones/[id]/page.tsx carga perfilAsociado y asesores solo cuando aplica y los pasa como props opcionales nuevas a PanelAfiliacionDetalle (sin maquetar nada, TODO hacia D-09). 14 pruebas nuevas (9 de la Server Action, 5 del esquema zod); tsc/lint/build/vitest en verde (334 pruebas). Confirmó que no hace falta una migración nueva: la RLS perfiles_update y el trigger proteger_campos_perfil ya permiten el cambio a un admin, con validar_perfil_asesor_id validando que el elegido tenga rol asesor. Queda para ga-diseno-a-codigo maquetar y conectar la pieza 3i.</t>
+          <t>Botón «Escribir por WhatsApp» habilitado en PanelAfiliacionDetalle.tsx (enlace wa.me en pestaña nueva con mensaje prellenado, glifo SVG IconoWhatsapp, normalización pura del celular en lib/admin/whatsapp.ts con pruebas Vitest, estado deshabilitado con motivo si el celular no es válido). Bloque «Asesor» nuevo (components/admin/AsignarAsesor.tsx) conectado a asignarAsesor con useActionState y sus 5 estados; corrigió una condición de carrera real (revalidatePath refrescaba la página y dejaba perfilAsociado en null justo tras el éxito) «congelando» la prop inicial con useState en PanelAfiliacionDetalle. Prueba nueva en tests/e2e/k-roles.spec.ts. tsc, lint, build, vitest (360) y Playwright (k-roles, escritorio) en verde. Dejó abierto para la sesión principal el estado «ya asignado» persistente al recargar (requería tocar la página de servidor, fuera de su encargo); cerrado después por la sesión principal (commit 3b5ae14, ver más abajo).</t>
         </is>
       </c>
     </row>
@@ -55220,22 +55224,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>4.11 (D-08, D-09)</t>
+          <t>4.11, P-96</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Diseñado el botón WhatsApp habilitado (3e) y el bloque «Asesor» (3i) en el lienzo</t>
+          <t>Server Action asignarAsesor lista en el servidor</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>En docs/Green Alliance C+.dc.html: botón «Escribir por WhatsApp» de la pieza 3e con glifo oficial en SVG en línea y enlace wa.me con mensaje prellenado (4 estados: normal, hover, foco, deshabilitado por falta de celular); pieza 3i nueva, bloque «Asesor» para asignar perfiles.asesor_id a un asociado aprobado (estados sin elegir, asignando, éxito, error, ya asignado, sin asesores registrados). Trabajo nuevo dejado para ga-diseno-a-codigo: habilitar el botón en PanelAfiliacionDetalle.tsx y crear la Server Action «asignar asesor» sobre perfiles.asesor_id (sin migración nueva) más el bloque visible solo si la afiliación está aprobada y el asociado no tiene asesor.</t>
+          <t>asignarAsesor en app/admin/afiliaciones/actions.ts (exigirAdmin, zod esquemaAsignarAsesor, re-verificación en servidor de afiliación aprobada + perfil sin asesor + update condicional .is("asesor_id", null)); app/admin/afiliaciones/[id]/page.tsx carga perfilAsociado y asesores solo cuando aplica y los pasa como props opcionales nuevas a PanelAfiliacionDetalle (sin maquetar nada, TODO hacia D-09). 14 pruebas nuevas (9 de la Server Action, 5 del esquema zod); tsc/lint/build/vitest en verde (334 pruebas). Confirmó que no hace falta una migración nueva: la RLS perfiles_update y el trigger proteger_campos_perfil ya permiten el cambio a un admin, con validar_perfil_asesor_id validando que el elegido tenga rol asesor. Queda para ga-diseno-a-codigo maquetar y conectar la pieza 3i.</t>
         </is>
       </c>
     </row>
@@ -55247,22 +55251,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>4.11 (D-08, D-09)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Se corrige la dependencia de 6.18: ya no depende de 1.8</t>
+          <t>Diseñado el botón WhatsApp habilitado (3e) y el bloque «Asesor» (3i) en el lienzo</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>6.18 (fusionar rediseno-c-plus a develop) dependía por error de 1.8 (aplicar las 5 migraciones de backend del rediseño). El código del rediseño funciona sin esas migraciones (KPIs con su propio fallback, tope real leído de grados_credito, nota interna oculta detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false) y lo que sí las necesita queda oculto hasta que se apliquen. Con 6.17 y 6.19 en Hecho, el rediseño C+ queda completo y verificado de punta a punta en la rama rediseno-c-plus (9 commits locales sobre develop, sin push); 6.18 queda Pendiente solo de que Sebas autorice el push de la rama y abra el PR a develop.</t>
+          <t>En docs/Green Alliance C+.dc.html: botón «Escribir por WhatsApp» de la pieza 3e con glifo oficial en SVG en línea y enlace wa.me con mensaje prellenado (4 estados: normal, hover, foco, deshabilitado por falta de celular); pieza 3i nueva, bloque «Asesor» para asignar perfiles.asesor_id a un asociado aprobado (estados sin elegir, asignando, éxito, error, ya asignado, sin asesores registrados). Trabajo nuevo dejado para ga-diseno-a-codigo: habilitar el botón en PanelAfiliacionDetalle.tsx y crear la Server Action «asignar asesor» sobre perfiles.asesor_id (sin migración nueva) más el bloque visible solo si la afiliación está aprobada y el asociado no tiene asesor.</t>
         </is>
       </c>
     </row>
@@ -55279,17 +55283,17 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>6.17; 3.10, 4.10</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Correcciones responsive del C+ (commit b0239a8): barra inferior siempre visible en vez de oculta hasta el primer scroll</t>
+          <t>Se corrige la dependencia de 6.18: ya no depende de 1.8</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Se descartó la solución de ga-diseno-a-codigo de ocultar la barra inferior de /cuenta y /asesor hasta el primer scroll (con `inert`) porque ocultar la navegación principal al cargar la página perjudicaba la usabilidad y la accesibilidad. En su lugar, la barra queda siempre visible con espacio reservado al final de la página. Incluye también las correcciones de admin en celular y de la vista en tarjetas de /admin/sorteo, y el contraste de /admin/demo. e2e k-roles, c-cuenta y f-accesibilidad en verde (50 pasadas) tras `supabase db reset`.</t>
+          <t>6.18 (fusionar rediseno-c-plus a develop) dependía por error de 1.8 (aplicar las 5 migraciones de backend del rediseño). El código del rediseño funciona sin esas migraciones (KPIs con su propio fallback, tope real leído de grados_credito, nota interna oculta detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false) y lo que sí las necesita queda oculto hasta que se apliquen. Con 6.17 y 6.19 en Hecho, el rediseño C+ queda completo y verificado de punta a punta en la rama rediseno-c-plus (9 commits locales sobre develop, sin push); 6.18 queda Pendiente solo de que Sebas autorice el push de la rama y abra el PR a develop.</t>
         </is>
       </c>
     </row>
@@ -55306,17 +55310,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>4.11; 6.17</t>
+          <t>6.17; 3.10, 4.10</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Hallazgo 0 corregido en producción del rediseño (commit 846657b): colores del admin oscuro en su propio grupo de Tailwind</t>
+          <t>Correcciones responsive del C+ (commit b0239a8): barra inferior siempre visible en vez de oculta hasta el primer scroll</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Los colores bg-admin-*/text-admin-* estaban anidados bajo la paleta ga en tailwind.config.ts, por lo que Tailwind nunca generaba esas clases y el panel /admin se veía blanco/sin tema oscuro en todos los anchos. Se movieron a su propio grupo admin en tailwind.config.ts; pruebas de responsive actualizadas en el mismo commit.</t>
+          <t>Se descartó la solución de ga-diseno-a-codigo de ocultar la barra inferior de /cuenta y /asesor hasta el primer scroll (con `inert`) porque ocultar la navegación principal al cargar la página perjudicaba la usabilidad y la accesibilidad. En su lugar, la barra queda siempre visible con espacio reservado al final de la página. Incluye también las correcciones de admin en celular y de la vista en tarjetas de /admin/sorteo, y el contraste de /admin/demo. e2e k-roles, c-cuenta y f-accesibilidad en verde (50 pasadas) tras `supabase db reset`.</t>
         </is>
       </c>
     </row>
@@ -55328,22 +55332,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>4.11; 6.17</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Corregidos todos los hallazgos del informe de responsive; 6.17 pasa a Hecho en su parte de código</t>
+          <t>Hallazgo 0 corregido en producción del rediseño (commit 846657b): colores del admin oscuro en su propio grupo de Tailwind</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Confirmado con capturas que el hallazgo 0 (colores admin-* fuera de la clave ga) ya estaba resuelto en el código. De paso, axe encontró y se corrigió un contraste nuevo: EncabezadoAdmin se volvía transparente en escritorio asumiendo que siempre estaría sobre el fondo oscuro del admin, pero en /admin/demo esa misma barra flota sobre el fondo claro de la vista de asociado. Corregidos también: flex-wrap en el filtro de /admin/creditos, controles del encabezado móvil del admin a 44×44, tabla de /admin/sorteo con versión en tarjetas, botones de /cuenta/solicitar y casillas OTP a 44px, selects de /admin/sorteo a 16px. La corrección de la barra inferior flotante de /cuenta y /asesor de este commit (ocultarla hasta el primer scroll con `inert`) fue reemplazada después por la sesión principal, ver el siguiente asiento. tsc, lint, build, vitest (316/316) y playwright k-roles+f-accesibilidad (36/36, 6 skip esperados) en verde tras `npx supabase db reset`.</t>
+          <t>Los colores bg-admin-*/text-admin-* estaban anidados bajo la paleta ga en tailwind.config.ts, por lo que Tailwind nunca generaba esas clases y el panel /admin se veía blanco/sin tema oscuro en todos los anchos. Se movieron a su propio grupo admin en tailwind.config.ts; pruebas de responsive actualizadas en el mismo commit.</t>
         </is>
       </c>
     </row>
@@ -55355,22 +55359,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive de punta a punta del rediseño C+; 6.19 pasa a Hecho</t>
+          <t>Corregidos todos los hallazgos del informe de responsive; 6.17 pasa a Hecho en su parte de código</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>15 rutas × 10 anchos (320-1920 px) + horizontal 844×390, Playwright/Chrome contra Supabase local. 9 hallazgos responsive (5 críticos: barra inferior flotante tapaba contenido real en /cuenta y /asesor, scroll horizontal real en /admin/creditos, botones &lt;44px en el encabezado móvil del admin, tabla de /admin/sorteo sin versión en tarjetas; 4 menores) más 1 hallazgo crítico fuera del alcance responsive estricto: los colores bg-admin-*/text-admin-* no existían en el CSS compilado (tailwind.config.ts los anidaba bajo la paleta ga en vez de un grupo propio admin), así que el panel se veía sin tema oscuro. tests/responsive/responsive.spec.ts y logo-y-fotos.spec.ts actualizados. No se pudo probar /admin/* en horizontal por el límite diario de reenvío de código del correo de prueba (no es un hallazgo nuevo). Informe: docs/verificaciones/2026-09-27-rediseno-c-plus-responsive.md.</t>
+          <t>Confirmado con capturas que el hallazgo 0 (colores admin-* fuera de la clave ga) ya estaba resuelto en el código. De paso, axe encontró y se corrigió un contraste nuevo: EncabezadoAdmin se volvía transparente en escritorio asumiendo que siempre estaría sobre el fondo oscuro del admin, pero en /admin/demo esa misma barra flota sobre el fondo claro de la vista de asociado. Corregidos también: flex-wrap en el filtro de /admin/creditos, controles del encabezado móvil del admin a 44×44, tabla de /admin/sorteo con versión en tarjetas, botones de /cuenta/solicitar y casillas OTP a 44px, selects de /admin/sorteo a 16px. La corrección de la barra inferior flotante de /cuenta y /asesor de este commit (ocultarla hasta el primer scroll con `inert`) fue reemplazada después por la sesión principal, ver el siguiente asiento. tsc, lint, build, vitest (316/316) y playwright k-roles+f-accesibilidad (36/36, 6 skip esperados) en verde tras `npx supabase db reset`.</t>
         </is>
       </c>
     </row>
@@ -55382,22 +55386,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>4.11; P-99, P-100, P-101, P-102, P-103</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>H1 corregido (tasa de interés fuera del payload de /cuenta) y H2/B-01 cerrados (cédula de las «hermanas» enmascarada en servidor, testimonios de ejemplo ocultos)</t>
+          <t>Verificación responsive de punta a punta del rediseño C+; 6.19 pasa a Hecho</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Commit e650033: la tasa de interés ya no viaja al navegador del asociado en /cuenta ni /cuenta/solicitar (hallazgo H1 de ga-revisor-seguridad; el problema también estaba en producción desde el 25-sep, se sugiere llevarlo también a main). Queda un residuo (P-100): un asociado podría seguir leyendo la tasa consultando la API directo con su sesión (la RLS le deja leer sus solicitudes y grados_credito); ocultarlo del todo requiere una migración de permisos por columna, a decisión de Sebas. Commit fdab456: cédula de las «hermanas» del detalle de afiliación enmascarada en el servidor (cierra H2/M-01, P-101) y sección de testimonios de la landing oculta mientras tenga textos de ejemplo (cierra B-01, P-102; D-07 queda abierto como pedido de diseño en P-103: contenido real de testimonios y si la sección se mantiene). e2e de landing y k-roles vueltos a correr en verde.</t>
+          <t>15 rutas × 10 anchos (320-1920 px) + horizontal 844×390, Playwright/Chrome contra Supabase local. 9 hallazgos responsive (5 críticos: barra inferior flotante tapaba contenido real en /cuenta y /asesor, scroll horizontal real en /admin/creditos, botones &lt;44px en el encabezado móvil del admin, tabla de /admin/sorteo sin versión en tarjetas; 4 menores) más 1 hallazgo crítico fuera del alcance responsive estricto: los colores bg-admin-*/text-admin-* no existían en el CSS compilado (tailwind.config.ts los anidaba bajo la paleta ga en vez de un grupo propio admin), así que el panel se veía sin tema oscuro. tests/responsive/responsive.spec.ts y logo-y-fotos.spec.ts actualizados. No se pudo probar /admin/* en horizontal por el límite diario de reenvío de código del correo de prueba (no es un hallazgo nuevo). Informe: docs/verificaciones/2026-09-27-rediseno-c-plus-responsive.md.</t>
         </is>
       </c>
     </row>
@@ -55409,22 +55413,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>4.11, P-94, P-71; 6.16 pasa a Hecho; nuevos P-102, P-103</t>
+          <t>4.11; P-99, P-100, P-101, P-102, P-103</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>QA completo del rediseño C+ en verde: 161/162 escritorio, 129/129 celular</t>
+          <t>H1 corregido (tasa de interés fuera del payload de /cuenta) y H2/B-01 cerrados (cédula de las «hermanas» enmascarada en servidor, testimonios de ejemplo ocultos)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>QA de punta a punta contra Supabase local (escritorio 1280×800, celular 390×844). Actualizó las pruebas desactualizadas por el rediseño: a-navegacion (nav sin «Historias»), e-diseno (reescrita casi entera, textos verificados contra el código), afiliación v2 en utils.ts/f-accesibilidad (cierra P-94), aprobar en 2 pasos + atajos de teclado + KPIs + nota interna oculta (k-roles), máscara de correo con dominio oculto en b-ingreso y j-produccion (cierra P-71; i-despliegue ya usaba el formato nuevo). Agregó pruebas de reduced-motion y de que ninguna pantalla diga «Correo institucional». De paso corrigió una prueba de seguridad de i-despliegue que fallaba por una causa ajena al rediseño (React 19 ya no serializa el DOM en un `&lt;form action={...}&gt;`), reescribiéndola con intercepción de red. Hallazgos: 1 Media (cédula de las «hermanas», ya reportada por ga-revisor-seguridad, ver P-101) y 2 Bajos (testimonios de ejemplo con corchetes en la landing, ver P-102/P-103; y los marcadores ya conocidos de /politica-de-datos). 0 violaciones de axe en 19 combinaciones. Informe en docs/verificaciones/2026-09-27-rediseno-c-plus-qa.md.</t>
+          <t>Commit e650033: la tasa de interés ya no viaja al navegador del asociado en /cuenta ni /cuenta/solicitar (hallazgo H1 de ga-revisor-seguridad; el problema también estaba en producción desde el 25-sep, se sugiere llevarlo también a main). Queda un residuo (P-100): un asociado podría seguir leyendo la tasa consultando la API directo con su sesión (la RLS le deja leer sus solicitudes y grados_credito); ocultarlo del todo requiere una migración de permisos por columna, a decisión de Sebas. Commit fdab456: cédula de las «hermanas» del detalle de afiliación enmascarada en el servidor (cierra H2/M-01, P-101) y sección de testimonios de la landing oculta mientras tenga textos de ejemplo (cierra B-01, P-102; D-07 queda abierto como pedido de diseño en P-103: contenido real de testimonios y si la sección se mantiene). e2e de landing y k-roles vueltos a correr en verde.</t>
         </is>
       </c>
     </row>
@@ -55436,22 +55440,22 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>4.11; nuevos P-99, P-100, P-101</t>
+          <t>4.11, P-94, P-71; 6.16 pasa a Hecho; nuevos P-102, P-103</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad del rediseño C+ aprobada; 2 fugas de datos confirmadas (no introducidas por el rediseño)</t>
+          <t>QA completo del rediseño C+ en verde: 161/162 escritorio, 129/129 celular</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Revisó el diff completo de rediseno-c-plus contra develop (app, components, lib, proxy.ts, supabase): sin cambios en Server Actions ni en proxy.ts, el asesor sigue sin ver datos sensibles de sus clientes, la aprobación en 2 pasos exige confirmar, el login no cambió en funcionalidad. Encontró 2 hallazgos de fuga de datos al payload del cliente, vigentes desde antes de este diff: la tasa de interés viaja en las props de CuentaCliente aunque no se renderice (H1, ver P-99/P-100) y la cédula sin enmascarar de las «hermanas» viaja completa al detalle de afiliación aunque se muestre enmascarada (H2, ver P-101). Revisó también las 5 migraciones propuestas de 1.8 (bien construidas, coherentes con el flag de nota interna). npm audit --omit=dev: 0 vulnerabilidades. Pidió a ga-funcionalidad-botones corregir ambas fugas y a Sebas decidir sobre las 5 migraciones de 1.8.</t>
+          <t>QA de punta a punta contra Supabase local (escritorio 1280×800, celular 390×844). Actualizó las pruebas desactualizadas por el rediseño: a-navegacion (nav sin «Historias»), e-diseno (reescrita casi entera, textos verificados contra el código), afiliación v2 en utils.ts/f-accesibilidad (cierra P-94), aprobar en 2 pasos + atajos de teclado + KPIs + nota interna oculta (k-roles), máscara de correo con dominio oculto en b-ingreso y j-produccion (cierra P-71; i-despliegue ya usaba el formato nuevo). Agregó pruebas de reduced-motion y de que ninguna pantalla diga «Correo institucional». De paso corrigió una prueba de seguridad de i-despliegue que fallaba por una causa ajena al rediseño (React 19 ya no serializa el DOM en un `&lt;form action={...}&gt;`), reescribiéndola con intercepción de red. Hallazgos: 1 Media (cédula de las «hermanas», ya reportada por ga-revisor-seguridad, ver P-101) y 2 Bajos (testimonios de ejemplo con corchetes en la landing, ver P-102/P-103; y los marcadores ya conocidos de /politica-de-datos). 0 violaciones de axe en 19 combinaciones. Informe en docs/verificaciones/2026-09-27-rediseno-c-plus-qa.md.</t>
         </is>
       </c>
     </row>
@@ -55463,22 +55467,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.11; nuevos P-99, P-100, P-101</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>KPIs reales, tope real de grados_credito y nota interna oculta en el admin C+</t>
+          <t>Revisión de seguridad del rediseño C+ aprobada; 2 fugas de datos confirmadas (no introducidas por el rediseño)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Cerró los 2 frentes de backend que dejó abiertos el maquetado del admin en modo oscuro (commit e39ad72): (1) los 4 KPI de /admin/creditos ahora son siempre exactos (lib/admin/kpis.ts: 3 conteos exactos + suma de aprobadas del mes, con el cliente de sesión del admin vía RLS, sin service role; mes calendario en hora de Colombia; pruebas nuevas en tests/unit/admin-kpis.test.ts); (2) el aviso «Dentro/Supera el tope» y el bloqueo de «Aprobar» usan el tope real de grados_credito (cargarPaquetesDemo, con su fallback a la copia estática). Ocultó el textarea de «Nota interna» detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false (lib/admin/flags.ts) con un TODO(backend) hacia la migración sin aplicar 20260925200200_historial_y_notas_internas.sql. Confirmó sin cambios de código que la aprobación en 2 pasos, el rechazo con motivo obligatorio, los atajos J/K/A/R/Esc y el invariante monto≤tope (triggers de la base) siguen intactos. tsc, lint, build y 316 pruebas de vitest (19 archivos) en verde. Sin commits. Sin bloqueos nuevos; sigue pendiente 1.8 (migraciones sin aplicar) para conectar una Server Action a agregar_nota_solicitud() y activar la bandera.</t>
+          <t>Revisó el diff completo de rediseno-c-plus contra develop (app, components, lib, proxy.ts, supabase): sin cambios en Server Actions ni en proxy.ts, el asesor sigue sin ver datos sensibles de sus clientes, la aprobación en 2 pasos exige confirmar, el login no cambió en funcionalidad. Encontró 2 hallazgos de fuga de datos al payload del cliente, vigentes desde antes de este diff: la tasa de interés viaja en las props de CuentaCliente aunque no se renderice (H1, ver P-99/P-100) y la cédula sin enmascarar de las «hermanas» viaja completa al detalle de afiliación aunque se muestre enmascarada (H2, ver P-101). Revisó también las 5 migraciones propuestas de 1.8 (bien construidas, coherentes con el flag de nota interna). npm audit --omit=dev: 0 vulnerabilidades. Pidió a ga-funcionalidad-botones corregir ambas fugas y a Sebas decidir sobre las 5 migraciones de 1.8.</t>
         </is>
       </c>
     </row>
@@ -55490,7 +55494,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -55500,12 +55504,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Panel del admin C+ en modo oscuro maquetado en código; 4.11 pasa a Hecho</t>
+          <t>KPIs reales, tope real de grados_credito y nota interna oculta en el admin C+</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Maquetó el panel de administración completo en modo oscuro (piezas 2d y 3e–3h): Créditos (menú lateral, 4 KPI con guion donde falta consulta nueva, búsqueda, filtro, lista+ficha, aprobar en 2 pasos, rechazar con motivo obligatorio, nota interna e historial UI), Afiliaciones (lista+ficha, visor de 3 fotos con sus 3 estados, aprobar/rechazar en 2 pasos, WhatsApp deshabilitado por P-95), Asesores y Sorteo con el mismo restyle, y EncabezadoAdmin (patrón de celular) también en /admin/demo. Tokens nuevos en globals.css/tailwind.config.ts. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus (junto con 4.10). Pasa a Hecho en maquetación con 2 frentes abiertos: (1) tests/e2e/k-roles.spec.ts va a fallar porque Aprobar ahora pide un segundo clic «Sí, aprobar» — hace falta que ga-verificador-qa/ga-escritor-tests actualicen ese paso; (2) sin backend nuevo, KPIs completos, tope real desde grados_credito y nota interna/historial reales siguen bloqueados por las 5 migraciones de 1.8 (docs/auditorias/2026-09-25-backend-rediseno-c-plus.md), sin aplicar.</t>
+          <t>Cerró los 2 frentes de backend que dejó abiertos el maquetado del admin en modo oscuro (commit e39ad72): (1) los 4 KPI de /admin/creditos ahora son siempre exactos (lib/admin/kpis.ts: 3 conteos exactos + suma de aprobadas del mes, con el cliente de sesión del admin vía RLS, sin service role; mes calendario en hora de Colombia; pruebas nuevas en tests/unit/admin-kpis.test.ts); (2) el aviso «Dentro/Supera el tope» y el bloqueo de «Aprobar» usan el tope real de grados_credito (cargarPaquetesDemo, con su fallback a la copia estática). Ocultó el textarea de «Nota interna» detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false (lib/admin/flags.ts) con un TODO(backend) hacia la migración sin aplicar 20260925200200_historial_y_notas_internas.sql. Confirmó sin cambios de código que la aprobación en 2 pasos, el rechazo con motivo obligatorio, los atajos J/K/A/R/Esc y el invariante monto≤tope (triggers de la base) siguen intactos. tsc, lint, build y 316 pruebas de vitest (19 archivos) en verde. Sin commits. Sin bloqueos nuevos; sigue pendiente 1.8 (migraciones sin aplicar) para conectar una Server Action a agregar_nota_solicitud() y activar la bandera.</t>
         </is>
       </c>
     </row>
@@ -55522,17 +55526,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>4.10; nuevo P-98</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Panel del asesor C+ maquetado en código; 4.10 pasa a Hecho</t>
+          <t>Panel del admin C+ en modo oscuro maquetado en código; 4.11 pasa a Hecho</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Maquetó /asesor y /asesor/demo siguiendo las piezas 2c/3h del lienzo: EncabezadoAsesor en píldora, tarjetas de resumen con categoría de afiliación, chips de filtro, buscador, tabla de 5 columnas reescrita (sin datos de contacto), estado vacío, transición de lista y barra inferior en celular; agregó el marco ámbar de demostración compartido con /admin/demo y el estado «neutral» a Badge. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus. Documentó como pedido D-06 (docs/diseno/pedidos.md) la falta de regla de diseño para categorizar asociados ya afiliados (no solo solicitudes) en las tarjetas/chips; se registra como decisión provisional de la sesión principal, pendiente de que Sebas la confirme (nuevo pendiente P-98).</t>
+          <t>Maquetó el panel de administración completo en modo oscuro (piezas 2d y 3e–3h): Créditos (menú lateral, 4 KPI con guion donde falta consulta nueva, búsqueda, filtro, lista+ficha, aprobar en 2 pasos, rechazar con motivo obligatorio, nota interna e historial UI), Afiliaciones (lista+ficha, visor de 3 fotos con sus 3 estados, aprobar/rechazar en 2 pasos, WhatsApp deshabilitado por P-95), Asesores y Sorteo con el mismo restyle, y EncabezadoAdmin (patrón de celular) también en /admin/demo. Tokens nuevos en globals.css/tailwind.config.ts. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus (junto con 4.10). Pasa a Hecho en maquetación con 2 frentes abiertos: (1) tests/e2e/k-roles.spec.ts va a fallar porque Aprobar ahora pide un segundo clic «Sí, aprobar» — hace falta que ga-verificador-qa/ga-escritor-tests actualicen ese paso; (2) sin backend nuevo, KPIs completos, tope real desde grados_credito y nota interna/historial reales siguen bloqueados por las 5 migraciones de 1.8 (docs/auditorias/2026-09-25-backend-rediseno-c-plus.md), sin aplicar.</t>
         </is>
       </c>
     </row>
@@ -55549,24 +55553,24 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.10; nuevo P-98</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Panel del asociado C+ maquetado en código; 3.10 pasa a Hecho</t>
+          <t>Panel del asesor C+ maquetado en código; 4.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Maquetó /cuenta y /cuenta/solicitar siguiendo las piezas 2b/3d del lienzo: EncabezadoCuenta en píldora flotante, comprobante «Tu solicitud» con sello y pasos animados, insignia de estado con color real, tope con medidor, carné de asociado (institución/activo como props opcionales sin usar, TODO backend), franja del sorteo, barra inferior en celular y deslizador de monto propio en /cuenta/solicitar; agregó enmascararCedula a lib/mascara.ts. tsc, lint, build y 311 pruebas de vitest en verde; no corrió Playwright (requiere Supabase local). Commit local 51da63f en rediseno-c-plus. «Tu camino a la estabilidad» sigue sin renderizarse por P-90 (fecha del primer descuento del embargo solidario); el carné de asociado sigue esperando institución/activo en perfiles (1.8). Falta correr tests/e2e/c-cuenta, h-credito, i-despliegue, j-produccion y k-roles contra Supabase local (ga-verificador-qa).</t>
+          <t>Maquetó /asesor y /asesor/demo siguiendo las piezas 2c/3h del lienzo: EncabezadoAsesor en píldora, tarjetas de resumen con categoría de afiliación, chips de filtro, buscador, tabla de 5 columnas reescrita (sin datos de contacto), estado vacío, transición de lista y barra inferior en celular; agregó el marco ámbar de demostración compartido con /admin/demo y el estado «neutral» a Badge. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus. Documentó como pedido D-06 (docs/diseno/pedidos.md) la falta de regla de diseño para categorizar asociados ya afiliados (no solo solicitudes) en las tarjetas/chips; se registra como decisión provisional de la sesión principal, pendiente de que Sebas la confirme (nuevo pendiente P-98).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -55576,17 +55580,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
+          <t>Panel del asociado C+ maquetado en código; 3.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
+          <t>Maquetó /cuenta y /cuenta/solicitar siguiendo las piezas 2b/3d del lienzo: EncabezadoCuenta en píldora flotante, comprobante «Tu solicitud» con sello y pasos animados, insignia de estado con color real, tope con medidor, carné de asociado (institución/activo como props opcionales sin usar, TODO backend), franja del sorteo, barra inferior en celular y deslizador de monto propio en /cuenta/solicitar; agregó enmascararCedula a lib/mascara.ts. tsc, lint, build y 311 pruebas de vitest en verde; no corrió Playwright (requiere Supabase local). Commit local 51da63f en rediseno-c-plus. «Tu camino a la estabilidad» sigue sin renderizarse por P-90 (fecha del primer descuento del embargo solidario); el carné de asociado sigue esperando institución/activo en perfiles (1.8). Falta correr tests/e2e/c-cuenta, h-credito, i-despliegue, j-produccion y k-roles contra Supabase local (ga-verificador-qa).</t>
         </is>
       </c>
     </row>
@@ -55598,22 +55602,22 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>3.10, 4.10, 4.11</t>
+          <t>1.7, 2.15</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
+          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
+          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
         </is>
       </c>
     </row>
@@ -55625,22 +55629,22 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.14; nuevo 6.16</t>
+          <t>3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Tokens y landing del rediseño C+ llevados a código</t>
+          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
+          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
         </is>
       </c>
     </row>
@@ -55652,22 +55656,22 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
+          <t>1.7, 2.14; nuevo 6.16</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
+          <t>Tokens y landing del rediseño C+ llevados a código</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
+          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
         </is>
       </c>
     </row>
@@ -55679,22 +55683,22 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>1.8; P-47, P-90, P-91, P-92</t>
+          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
+          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
+          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
         </is>
       </c>
     </row>
@@ -55704,24 +55708,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (despliegue PR #2)</t>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89</t>
+          <t>1.8; P-47, P-90, P-91, P-92</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
+          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
+          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
         </is>
       </c>
     </row>
@@ -55733,22 +55737,22 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>sesión principal (coordinador)</t>
+          <t>sesión principal (despliegue PR #2)</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
+          <t>4.9; P-83, P-84, P-85, P-89</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
+          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
+          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
         </is>
       </c>
     </row>
@@ -55758,24 +55762,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>sesión principal</t>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-13</t>
+          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Texto de vigilancia de Supersolidaria confirmado</t>
+          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
+          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
         </is>
       </c>
     </row>
@@ -55787,22 +55791,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>6.3; nuevos P-84, P-86, P-87</t>
+          <t>5.3; P-13</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>QA de producción: con observaciones</t>
+          <t>Texto de vigilancia de Supersolidaria confirmado</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
+          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
         </is>
       </c>
     </row>
@@ -55814,22 +55818,22 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>2.12; nuevo P-85</t>
+          <t>6.3; nuevos P-84, P-86, P-87</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
+          <t>QA de producción: con observaciones</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
+          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a39d34), sin enviar el formulario de afiliación ni pedir códigos reales. Landing, /ingresar, /afiliacion, /politica-de-datos, redirecciones de /admin, /asesor y /cuenta sin sesión, 404 y cabeceras de seguridad correctos y fieles al diseño; axe sin violaciones serias/críticas. 6.3 sigue En curso porque depende de 6.1, 5.3, 5.4, 2.11 y 5.6, que no están Hecho. Hallazgos: A-01 (Alta, la ayuda del dominio de correo institucional en /afiliacion no se actualiza en vivo al elegir Policía/Ejército) → nuevo pendiente P-86, condicionado a P-85; M-01 (Media, el WhatsApp se muestra sin espacios por un typo de regex en lib/config.ts) → nuevo pendiente P-84, ya corregido en local con pruebas (tests/unit/config-whatsapp.test.ts), falta desplegar; M-02 (Media, greenallianceco.com a veces sirve 200 en vez de redirigir 308 a www) → nuevo pendiente P-87 para Sebas en Vercel → Domains; M-03 (texto de vigilancia) ya resuelto, ver P-13. Informe completo en docs/verificaciones/2026-09-25-produccion.md.</t>
         </is>
       </c>
     </row>
@@ -55841,22 +55845,22 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>6.2; nuevos P-83, P-88</t>
+          <t>2.12; nuevo P-85</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
+          <t>El formulario de afiliación acepta correo de cualquier dominio</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
+          <t>Antes exigía @policia.gov.co / @ejercito.mil.co según la institución; se cambió el esquema zod, el campo «Correo electrónico» y las pruebas unitarias, e2e y pgTAP. Migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (quita el chk de dominio institucional, mantiene el de formato). Nuevo pendiente P-85 (En curso): falta desplegar el código (commit + merge a main); hasta entonces el formulario en vivo sigue rechazando correos no institucionales.</t>
         </is>
       </c>
     </row>
@@ -55866,24 +55870,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
+          <t>6.2; nuevos P-83, P-88</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
+          <t>Revisión de seguridad final de producción: aprobado con observaciones</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
+          <t>Contra main (merge 5a39d34, www.greenallianceco.com): F2-01, S-05 a S-13, el límite de 1 MB de Server Actions y el enlace a la política de datos, correctos; revisó lo nuevo desde a13c2de (correo institucional, plantillas de Resend, lib/correo/credito.ts, /politica-de-datos). 6.2 sigue En curso porque depende de 4.3, que no está Hecho. Hallazgos: S-15 (Media, variables NOMBRE/MOTIVO sin escapar en los correos de Resend, un admin puede meter HTML vía perfiles.nombre_completo o el motivo de rechazo) → nuevo pendiente P-83 para ga-funcionalidad-botones; F2-08 (Baja, ya documentado en la auditoría del 24-sep, tr_componer_nombre_afiliacion no cubre el update directo de nombre por un admin, sigue sin corregir) → nuevo pendiente P-88 para ga-auditor-supabase; /politica-de-datos en producción sigue con varios [Pendiente: NIT, dirección, plazos de retención...] visibles al público (ya rastreado en P-75 a P-81); no pudo confirmar desde afuera si las plantillas de Resend y el SMTP de Supabase Auth están realmente publicados (P-61 y 6.9 los dan por hechos desde otra sesión, sin verificación externa).</t>
         </is>
       </c>
     </row>
@@ -55900,24 +55904,24 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>6.9, 6.13; P-44, P-59, P-61</t>
+          <t>6.5, 6.13; P-59, P-64; nuevo P-82</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
+          <t>PR develop → main fusionado; fase 2 desplegada en producción</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
+          <t>Sebas abrió y fusionó el PR #1 develop → main (merge 5a39d34); Vercel desplegó fase 2 en www.greenallianceco.com. Verificado por HTTP: /, /ingresar, /afiliacion y /politica-de-datos responden 200; /admin, /cuenta y /asesor redirigen a /ingresar sin sesión; el logo de los correos ya carga; /afiliacion muestra correo institucional, Nequi, institución, selfie y el desplegable de asesores; contacto real visible (soporte@greenallianceco.com, WhatsApp 311 724 1942, 4 horas o menos). 6.13 y P-59 pasan a Hecho (migraciones + despliegue completos) y P-64 pasa a Hecho (PR fusionado). 6.5 se deja En curso, no Hecho: aunque el código ya está en producción, la tarea del plan sigue dependiendo de 6.2 (revisión de seguridad), 6.3 (QA E2E), 6.4 (dominio), 2.4 (SMTP) y 6.8 (migración de límite de intentos), ninguna Hecho todavía; el generador de Excel no permite marcar Hecho una tarea con dependencias sin terminar. Trabajo nuevo: pendiente P-82 (prueba manual con sesión real de los 3 admins: ingreso con código OTP y logo del correo), a cargo de Sebas, reportado como abierto en este mismo mensaje. La política de datos sigue con huecos (P-75 a P-81), sin cambios.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -55927,17 +55931,17 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
+          <t>6.9, 6.13; P-44, P-59, P-61</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
+          <t>Migraciones de fase 2 aplicadas en producción; plantillas de Resend y variables de Vercel puestas</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
+          <t>Sebas aplicó en producción (PagGreenAlliance) las 9 migraciones de fase 2 con `supabase db push` (de 20260924000000_rol_asesor_enum a 20260924000800_sincronizar_perfil_desde_app_metadata), tras un --dry-run que listó exactamente esas 9: 6.13 y P-59 pasan a En curso (falta la parte de desplegar). También creó y publicó las 4 plantillas en Resend (P-61 Hecho) y puso el resto de variables en Vercel: SITIO_URL, RESEND_API_KEY, EMAIL_FROM, LIMITE_HMAC_SECRET y las 4 RESEND_TEMPLATE_* (P-44 Hecho; 6.9 pasa a En curso porque P-60, SUPABASE_SERVICE_ROLE_KEY con «Invalid API key», sigue Pendiente). develop subido a origin (commit debe226, 6 commits nuevos). Bloqueo nuevo: falta fusionar el PR develop → main para desplegar; producción ya tiene la base de datos nueva pero sigue con el código viejo (ver P-64, 6.5). La política de datos sigue con huecos (P-75 a P-81), sin cambios en este reporte.</t>
         </is>
       </c>
     </row>
@@ -55949,22 +55953,22 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Sebas (acuerdo con Carlos Pardo)</t>
+          <t>sesión principal (coordinador)</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
+          <t>5.4, P-14, P-61, P-62, P-72; nuevos P-75 a P-81</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
+          <t>Borrador de la política de datos y plantillas de Resend listas; Test QA borrado y dominio conectado</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
+          <t>Borrador completo de /politica-de-datos (10 secciones, Ley 1581 y Decreto 1377, con la autorización de datos sensibles para las fotos de cédula y la selfie), con los datos que faltan resaltados en la página con &lt;Pendiente&gt;; 5.4 y P-14 actualizan su bloqueo con la lista concreta que falta de la cooperativa: NIT/dirección/ciudad (P-75), fecha de vigencia (P-76), país o región de los servidores -Supabase, Vercel, Resend- (P-77), alternativa sin selfie (P-78), plazos de conservación -fotos ligadas a P-63- (P-79) y si reportan a centrales de riesgo Ley 1266 (P-80); más la revisión de un abogado (P-81, nuevo pendiente para Sebas). HTML de las 4 plantillas de Resend (ingreso aceptado, crédito aprobado, crédito rechazado, boleta del sorteo) listo en docs/resend/, con el mismo diseño del correo del código; P-61 se actualiza con esa nota, falta que Sebas las cree y publique en Resend junto con las variables de Vercel (RESEND_API_KEY, EMAIL_FROM, RESEND_TEMPLATE_*, SITIO_URL=https://www.greenallianceco.com), ya anotadas en P-44. Sebas: plantilla del código puesta en Supabase, dominio www.greenallianceco.com conectado a producción en Vercel, usuario «Test QA» borrado de producción (P-62 pasa a Hecho), primera variable de Vercel corregida y habló con Carlos para darle acceso de colaborador (P-72 pasa a En curso). El logo de los correos da 404 hasta desplegar develop en main (public/logos no está en producción).</t>
         </is>
       </c>
     </row>
@@ -55974,24 +55978,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (acuerdo con Carlos Pardo)</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>6.1, P-58</t>
+          <t>4.1, 4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-65 a P-74</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
+          <t>Corrección de 4.1 y encargo externo a Carlos Pardo (500.000 COP) por PR a develop</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
+          <t>4.1 corregida: su texto decía «listado de solicitudes y asociados» pero /admin no tiene lista de asociados ni dashboard, solo afiliaciones, créditos, asesores y sorteo; queda Hecho con el texto correcto. Se contrata a Carlos Pardo, desarrollador externo, para un paquete de 6 actividades que entregará por PR a develop desde su propia rama (cada PR lo revisa un agente ga-* antes de fusionar): 4.7 dashboard de clientes en /admin (peso 4), 4.8 dashboard del asesor en /asesor sin datos sensibles (peso 3), 5.9 convenios administrables desde /admin (peso 3), 5.10 Ley 1581 (borrado automático de fotos rechazadas y motivo de rechazo, peso 2), 6.14 pruebas en celulares reales con informe (peso 1) y 6.15 actualizar los tests e2e viejos al formato de máscara nuevo (peso 1); pendientes P-66 a P-71 en espejo. Nuevos pendientes para Sebas: P-72 (dar acceso de colaborador en GitHub, sin llaves de producción) y P-73 (revisar y pagar los 500.000 COP al fusionar el paquete en develop). P-65 se cierra como Hecho: se decidió que solo participan asociados en el sorteo (S-13, ya implementado).</t>
         </is>
       </c>
     </row>
@@ -56001,24 +56005,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Sebas (coordinación con la cooperativa)</t>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
+          <t>6.1, P-58</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
+          <t>tests/e2e/d-afiliacion.spec.ts reescrito para la afiliación v2; bug real encontrado en esquemaAfiliacion</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
+          <t>Reescritura completa de d-afiliacion.spec.ts (nombres/apellidos, institución + correo institucional, Nequi, asesor, 3 fotos con magic bytes y bucket privado): 48 pruebas × 2 proyectos (escritorio/celular) = 96 contra Supabase local, 92 pasan y 4 fallan (2 por proyecto) por un bug real de la app, no de la prueba. Bug reproducido también como prueba unitaria en tests/unit/validaciones.test.ts (falla a propósito, documentando el defecto): nueva actividad 2.13 y pendiente P-74 para ga-funcionalidad-botones. k-roles.spec.ts (referencia) 4/4 en escritorio, tras corregir a mano el estado de una solicitud de ejemplo que había quedado mal de una corrida previa (no se pudo usar supabase db reset por el permiso de la sandbox). npm run test:unit: 307 pasan, 1 falla (la nueva, documentando el bug); npx tsc --noEmit sin errores. Sigue bloqueado correr npm run test:db (pgTAP) por el mismo permiso de sandbox. Queda fuera de esta tarea, y se delega a Carlos Pardo (ver 6.15, P-71), reescribir b-ingreso.spec.ts, i-despliegue.spec.ts y j-produccion.spec.ts al formato nuevo de máscara de correo.</t>
         </is>
       </c>
     </row>
@@ -56028,24 +56032,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones</t>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Sebas (coordinación con la cooperativa)</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
+          <t>5.3; P-10, P-11, P-12, P-17, P-18, P-38, P-44</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
+          <t>Datos reales de contacto entregados; se cancela la importación de Excel; 3 admins reales en producción</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
+          <t>La cooperativa entregó WhatsApp (311 724 1942), correo de soporte (soporte@greenallianceco.com) y tiempo de respuesta («4 horas o menos»): P-10, P-11, P-12 y P-17 pasan a Hecho; 5.3 actualiza su bloqueo (quedan pendientes texto de vigilancia Supersolidaria, fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Decisión de la cooperativa: no habrá importación de Excel de asociados (la afiliación v2 + aprobación en /admin la reemplaza); P-18 y P-38 pasan a Hecho como «ya no aplica», y 4.4 se cierra igual con nota de cancelación. Ya hay 3 administradores reales en producción (Ricardo, Abogados Prieto y Sebas); la cuenta de prueba «Test QA» (1099887766) sigue siendo admin y hay que borrarla (P-62). Nuevos pendientes de alta prioridad para Sebas: aplicar las 9 migraciones de fase 2 y desplegar (P-59), corregir SUPABASE_SERVICE_ROLE_KEY en Vercel (P-60), crear las plantillas en Resend (P-61), borrar Test QA (P-62), preguntas abiertas a la cooperativa (P-63) y abrir el PR de develop a main (P-64); P-44 actualizado con las variables nuevas (SITIO_URL, RESEND_TEMPLATE_SORTEO_BOLETA).</t>
         </is>
       </c>
     </row>
@@ -56057,22 +56061,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>2.12, 4.1, 4.2, 4.5, 4.6, 6.2; P-36, P-37</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
+          <t>Afiliación v2, panel /admin y correcciones de la auditoría y la revisión de seguridad (F2-01/F2-04, S-01 a S-14)</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
+          <t>Según la coordinación del 24-sep y los commits 235ffbe (afiliación v2 con fotos, panel /admin, vista del asesor y sorteo) y a13c2de (arreglos de auditoría y seguridad), en rama develop, sin tocar producción: formulario de afiliación v2 completo (nombres/apellidos, institución con correo institucional, Nequi, asesor, 3 fotos con subida al bucket privado) y panel /admin (listado de solicitudes y afiliaciones, aprobar/rechazar con motivo, correo «Ingreso aceptado»). Correcciones: (1) F2-01/S-01 boleta oculta, migraciones 000600/000700/000800 aplicadas en local y pasadas a RPC (mi_boleta_sorteo, boletas_confirmadas_sorteo), «Reenviar mi boleta» con tope 3/día; (2) fotos comprimidas a JPEG ≤1600px y bodySizeLimit 3mb; (3) magic bytes para validar el tipo real de la foto; (4) número de boleta fuera de los logs en producción, variables de Resend obligatorias en el build; (5) se quitó `workflow` (0 vulnerabilidades altas); (6) update de solicitudes_credito filtra por estado pendiente; (7) SITIO_URL para el correo «Ingreso aceptado»; (8) participarSorteo exige rol asociado; (9) cabeceras Strict-Transport-Security y Permissions-Policy; (10) vista previa /cuenta?sorteo=demo solo fuera de producción; (11) S-06 respuesta idéntica para cédula duplicada en afiliación, sin filtrar si ya existe. Verificación: tsc, eslint, build y test:unit (307/307) sin errores; playwright k-roles (4/4). 4.1, 4.2, 4.5 pasan a Hecho (panel /admin probado). Pendiente: tests/e2e/d-afiliacion.spec.ts desactualizado (ver P-58); variables nuevas de Vercel (ver P-59 a P-61).</t>
         </is>
       </c>
     </row>
@@ -56084,22 +56088,22 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
+          <t>Revisión de seguridad de fase 2: 3 bloqueos para el despliegue</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
+          <t>Diff 4545c0e..235ffbe (/admin, /asesor, /afiliacion v2, sorteo, proxy, ingreso por rol, cabeceras, llaves). Sin secretos expuestos, open redirect ni bypass de rol; /admin y /asesor verifican el rol en el servidor antes de usar service role. Bloquean el despliegue: (1) F2-01 boleta legible por API REST (ya reportado por ga-auditor-supabase); (2) la autorización de datos sensibles enlaza a una política de datos todavía placeholder; (3) el límite de 1 MB de las Server Actions tumba el envío de las 3 fotos. 6.2 sigue En curso (pasa a depender también de 2.12, 3.9 y 4.6): la mayoría de estos hallazgos ya se corrigieron en el siguiente reporte, falta el visto bueno final. Nuevo pendiente P-65 (si admin o asesor pueden participar en el sorteo).</t>
         </is>
       </c>
     </row>
@@ -56111,22 +56115,22 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Sorteo mensual en /cuenta</t>
+          <t>Auditoría de las 6 migraciones de fase 2: 1 hallazgo alto, 3 migraciones correctivas propuestas</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
+          <t>Auditoría de solo lectura contra el repo y Supabase local (203/203 pgTAP). Sin nada crítico. Hallazgo alto: el asociado podía leer el número de su boleta del sorteo por la API REST antes de confirmarlo. 3 migraciones nuevas propuestas sin aplicar: 000600 (oculta el número y corrige las carreras del sorteo), 000700 (el asesor degradado deja de ver a sus clientes), 000800 (trigger que sincroniza cédula y grado desde app_metadata). Reporte: docs/auditorias/2026-09-24-fase-2.md. Nueva actividad 1.6 (peso 3, depende de 1.5).</t>
         </is>
       </c>
     </row>
@@ -56143,17 +56147,17 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>4.6; P-57</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
+          <t>Sorteo mensual en /cuenta</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
+          <t>Botón «Sorteo del mes» y modal en /cuenta (components/sorteo/SorteoDelMes.tsx): participar (RPC participar_sorteo, correo con el número por Resend), confirmar (RPC confirmar_boleta_sorteo, tope 5 intentos) y celebración con confeti (respeta prefers-reduced-motion). El número de boleta nunca sale del servidor antes de confirmar. 31 pruebas unitarias nuevas; docs/mapa-de-botones.md §4 y .env.example (RESEND_TEMPLATE_SORTEO_BOLETA) actualizados. tsc, eslint y build sin errores nuevos. No se pudo probar el flujo feliz completo en vivo (24-sep está fuera de la ventana 1–5); cubierto con pruebas unitarias y revisión de código. Nueva actividad 3.9 (peso 4, depende de 3.5 y 1.5). Pendiente: aprobar la plantilla ga-sorteo-boleta en Resend (ver P-61).</t>
         </is>
       </c>
     </row>
@@ -56165,49 +56169,49 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>1.5; P-63</t>
+          <t>4.6; P-57</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
+          <t>Rol asesor: /asesor (mis clientes) y /asesor/demo</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
+          <t>/asesor («Mis clientes», buscador y filtro por estado sobre resumen_clientes_asesor()) y /asesor/demo (cuenta fantasma que no escribe nada), ambas con guardia de rol propia en el servidor; 26 pruebas unitarias nuevas; docs/mapa-de-botones.md actualizado (§7, §7b). Verificado contra Supabase local con el asesor de prueba (cédula 1234567892). Nueva actividad 4.6 (peso 3, depende de 1.5). Pendiente nuevo P-57: agregar /asesor al matcher de proxy.ts y redirigir por rol tras login.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>1.5; P-63</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
+          <t>Modelo de datos de fase 2: rol asesor, afiliación v2, bucket de fotos y sorteo mensual</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
+          <t>6 migraciones nuevas probadas contra Supabase local (no aplicadas a producción): enum 'asesor', perfiles.asesor_id con validaciones, solicitudes_afiliacion v2 (nombres/apellidos, institución + correo institucional, Nequi, asesor_id, 3 fotos obligatorias), obtener_asesores_publico()/resumen_clientes_asesor() (SECURITY DEFINER), bucket privado afiliacion-documentos (5 MB, sin políticas de storage.objects, todo por service_role + URL firmada) y sorteo mensual (boletas_sorteo, participar_sorteo(), confirmar_boleta_sorteo(), ventana 1–5 hora Bogotá, tope 5 intentos). seed.sql actualizado; 4 archivos pgTAP nuevos y 2 ajustados; docs/spec-fase-2.md nuevo. Verificado: supabase db reset + supabase test db (203/203) + test:unit (163/163) + tsc sin errores. Nueva actividad 1.5 (peso 5, depende de 1.2). Pendientes abiertos para la cooperativa recogidos en P-63.</t>
         </is>
       </c>
     </row>
@@ -56219,22 +56223,22 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive + ga-verificador-qa</t>
+          <t>ga-funcionalidad-botones + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>6.3; P-39</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
+          <t>Corregidos F-01 a F-08 de verificación 3 y los 8 hallazgos responsive</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
+          <t>ga-funcionalidad-botones: F-01 (correo enmascarado ya no delata la cédula, también oculta el dominio), F-02 (tope de intentos al verificar código: 5 por cédula y 30 por IP cada 15 min), F-05 (cabeceras X-Frame-Options, CSP frame-ancestors, Referrer-Policy, X-Content-Type-Options), F-06 (monto múltiplo de $50.000) y F-08 (código pegado durante «Reenviar» ya no se borra); documentó O-01 (x-forwarded-for solo confiable detrás de Vercel, ver P-49). ga-diseno-a-codigo: los 8 hallazgos responsive (tarjetas 50/100 %, deslizador, «Reenviar código», header /cuenta, hero y landing 1024–1150, /afiliacion y /cuenta 640–1023, hueco /afiliacion/enviada en tableta) y F-03/F-04/F-07 (Cerrar sesión en celular, 404 en español, hueco de tableta); nueva app/not-found.tsx. Todo terminó en el commit bf09975→4545c0e (arreglos de QA). Pendiente: tests/e2e con el formato viejo de máscara y dominios (ver P-58); confirmar con la cooperativa que solo hay 3 dominios institucionales (ver P-63); hallazgo #7 (grid de /afiliacion a 1024 px) quedó pendiente para la tanda que reescribiera Afiliacion.tsx, ya superado por la afiliación v2 (2.12).</t>
         </is>
       </c>
     </row>
@@ -56244,24 +56248,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-responsive</t>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>ga-verificador-responsive + ga-verificador-qa</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 5.8; P-39, P-53</t>
+          <t>6.3; P-39</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
+          <t>Responsive 3 (8 hallazgos menores) y QA E2E 3 (236/241, NO APROBADO)</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
+          <t>Responsive: 8 rutas × 9 anchos (360–1440) contra develop bf09975, 0 críticos y 8 menores (docs/verificaciones/responsive-2026-09-23/). QA: Supabase local, 236 pasan y 5 fallan; unitarias (140), pgTAP (143), tsc y eslint sin errores; docs/verificaciones/2026-09-23-verificacion-3.md. Bloqueaban producción: F-01 crítica (el dominio del correo enmascarado delataba si la cédula existe) y F-02 alta (sin tope de intentos al verificar el código); además contenido pendiente de la cooperativa, política de datos vacía, configuración de producción por revisar (SMTP/Resend, P-45, secretos en Vercel, P-43, P-09), F-03/F-04 (diseño), F-05 (cabeceras anti-clickjacking) y F-06 a F-08 bajas.</t>
         </is>
       </c>
     </row>
@@ -56273,22 +56277,22 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
+          <t>6.3, 5.2, 5.8; P-39, P-53</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
+          <t>Verificación responsive 2: 0 fallas en 13 anchos; tests/responsive 10/10</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
+          <t>Sin scroll horizontal en /, /ingresar, /ingresar/codigo, /afiliacion, /politica-de-datos, /cuenta y /cuenta/solicitar (con cookie y sesión reales) de 320 a 1920 px. P-39 pasa a Hecho (QA y responsive corridas); 6.3 sigue En curso porque depende de trabajo sin terminar. Menor y opcional: P-53 («COOPERATIVA» del logo a 320 px ~5 px de alto).</t>
         </is>
       </c>
     </row>
@@ -56300,22 +56304,22 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>5.2, 5.8, 6.3</t>
+          <t>3.7, 5.5, 5.6, 6.9, 6.11; P-35, P-40, P-44, P-56</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
+          <t>HMAC en el límite de intentos, crédito en /cuenta/solicitar y borradas /login y /dashboard</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
+          <t>Nueva actividad 6.11 (Hecho, peso 1): clave del límite con HMAC-SHA256 y LIMITE_HMAC_SECRET (sin el secreto el build falla). Formulario de crédito movido a /cuenta/solicitar con EncabezadoCuenta; 5.5 y P-40 pasan a Hecho. 6.9 y P-44 suman LIMITE_HMAC_SECRET y 6.9 depende de 6.11. Pruebas: 140/140 unitarias, 143/143 base, tsc, lint y build limpios. Trabajo nuevo: 5.6 revisar el diseño de /cuenta/solicitar (ga-diseno-a-codigo, peso 1) con P-56; 6.3 pasa a depender de 5.6.</t>
         </is>
       </c>
     </row>
@@ -56327,22 +56331,22 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
+          <t>5.2, 5.8, 6.3</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
+          <t>Corregido el scroll horizontal y marca de agua más tenue</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
+          <t>Enlace del logo encoge (min-w-0 shrink) en los 5 headers; formulario de ingreso w-full con máximo 440 px y relleno de 32 px entre 1024 y 1279 px; marca de agua del hero en la esquina contraria y más tenue. 5.8 queda Hecho (peso 1, depende de 5.2 y 5.7).</t>
         </is>
       </c>
     </row>
@@ -56354,22 +56358,22 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>2.1, 5.3, 5.7; P-16, P-52</t>
+          <t>6.3, 5.2, 2.1, 5.8; P-39</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
+          <t>Verificación responsive 1: logo y fotos bien; 2 fallas críticas de scroll previas</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
+          <t>Playwright en 10 anchos (320–1920 px) sobre 7 rutas. Logo nítido y proporcionado en dark y light; fotos decorativas correctas. Fallas: landing a 320 px («Ingresar» cortado, enlace del logo fijo en 240 px) y /ingresar y /ingresar/codigo entre 1024 y 1075 px (540 + 440 + padding = 1076 px). Se abre 5.8 para corregirlas.</t>
         </is>
       </c>
     </row>
@@ -56381,22 +56385,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
+          <t>2.1, 5.3, 5.7; P-16, P-52</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
+          <t>Logo con letras oficiales en SVG y espacios de foto de marca en la landing</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
+          <t>green-alliance-wordmark.svg (y versión blanca) reemplaza Montserrat; EspacioFoto con degradado, patrón, isotipo e ilustración, listo para recibir { src, alt }. Mapa de botones revisado contra el diseño (2.2, 2.3, 3.4): todo existe y está bien ubicado. Nueva actividad 5.7 (Hecho, peso 2, depende de 2.1). 5.3 sigue Bloqueado; P-16 sigue Pendiente (fotos reales de la cooperativa). P-52 (actualizar el mapa: §4 «Nueva solicitud» → /cuenta/solicitar y documentar esa ruta) se registra como Hecho: el documento ya lo tiene tras el cambio de ga-funcionalidad-botones.</t>
         </is>
       </c>
     </row>
@@ -56406,24 +56410,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
+          <t>6.8, 6.11, 6.12; P-43, P-54, P-55</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
+          <t>Migración limite_de_intentos auditada: se puede aplicar tal cual</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
+          <t>Auditoría de solo lectura contra producción, sin críticos ni altos (docs/auditorias/2026-09-23-limite-de-intentos.md). 6.8 pasa a En curso (revisión hecha, falta que Sebas haga db push antes de 6.5); P-43 sigue Pendiente con nota. Trabajo nuevo: hash HMAC de la clave (queda en 6.11, ver reporte de ga-funcionalidad-botones), 6.12 alerta en logs de Vercel (peso 1) con P-54, y P-55 opcional (revocar limites_intentos_id_seq a anon y authenticated).</t>
         </is>
       </c>
     </row>
@@ -56433,24 +56437,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Sebas</t>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.4, 6.8, 6.10; P-09, P-19, P-20, P-43, P-45</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Agente ga-auditor-supabase corregido</t>
+          <t>SMTP de Resend configurado, plantilla del código lista en local y blindar confirmada en producción</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
+          <t>P-19 Hecho (Sebas configuró el SMTP). P-20 sigue En curso: supabase/templates/codigo-ingreso.html rediseñada con la marca y probada en Mailpit; falta pegarla en Magic Link del panel. P-45 sin confirmar, sin cambios; por eso 2.4 sigue En curso. list_migrations confirma que producción ya tiene 20260923173355_blindar_solicitudes_y_revisiones: 6.10 y P-09 pasan a Hecho (el reporte anterior de atraso estaba equivocado). Falta en producción 20260923210000_limite_de_intentos (limites_intentos y registrar_intento, usadas por dentroDelLimite en /afiliacion, /ingresar y «Reenviar código»): ya existía como 6.8 / P-43 y 6.5 ya dependía de 6.8; se actualizan responsable (Sebas, revisa ga-auditor-supabase) y nota en vez de duplicar.</t>
         </is>
       </c>
     </row>
@@ -56460,24 +56464,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-auditor-supabase</t>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>3.1, 6.5, 6.10; P-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
+          <t>Agente ga-auditor-supabase corregido</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
+          <t>Sus disallowedTools ahora usan los nombres reales del MCP (mcp__claude_ai_Supabase__*). Sin efecto en el plan.</t>
         </is>
       </c>
     </row>
@@ -56487,24 +56491,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>ga-escritor-tests</t>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>3.1, 6.5, 6.10; P-09</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
+          <t>Producción atrasada: falta la migración blindar_solicitudes_y_revisiones</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
+          <t>PagGreenAlliance tiene 10 migraciones hasta 20260923123937_fecha_solicitud_en_servidor; le falta blindar_solicitudes_y_revisiones (en el repo es 20260923173355; el reporte la nombra 20260923160000) y la app lee tasa_interes_mensual, que en producción no existe. P-09 estaba Hecho por error: se reabre como Pendiente Alta (Sebas aplica, ga-auditor-supabase revisa antes). 3.1 se deja Hecho (el trabajo en la base está hecho y tiene hechas que dependen de él) pero se quita «y migración a producción» de su texto; nueva actividad 6.10 (peso 1, depende de 3.1) para aplicarla, y 6.5 (despliegue) pasa a depender de 6.10.</t>
         </is>
       </c>
     </row>
@@ -56514,24 +56518,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Sebas + ga-funcionalidad-botones</t>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
+          <t>132/132 unitarias, 131/131 pgTAP y tsc sin errores</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
+          <t>Corridas con Node v24 y Supabase local en Docker. Se agregaron supabase/seed.sql con asociados de prueba y .env.development.local para que npm run dev use Supabase local en vez de producción. 6.1 sigue En curso: faltan las pruebas de las acciones de admin (4.3, 4.5).</t>
         </is>
       </c>
     </row>
@@ -56541,24 +56545,24 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>ga-verificador-qa</t>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Sebas + ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
+          <t>2.9, 3.8, 4.5, 6.1, 6.2, 6.9; P-19, P-20, P-28, P-36, P-37, P-44, P-45, P-50, P-51</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
+          <t>Se quitan del código los correos de aviso de afiliación y de solicitud de crédito; docs/resend-plantillas.md reescrito</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
+          <t>Decisión de Sebas: ya no se envían avisos Resend al guardar una afiliación (equipo y solicitante) ni una solicitud de crédito (equipo y asociado). Se borró lib/correo/afiliacion.ts y enviarAvisoNuevaSolicitudCredito; salen del .env.example AFILIACION_EMAIL_EQUIPO, CREDITOS_EMAIL_EQUIPO y cuatro RESEND_TEMPLATE_*, entra RESEND_TEMPLATE_INGRESO_ACEPTADO. El equipo revisa solicitudes y afiliaciones en Supabase hasta que exista /admin. Se elimina la actividad 3.8 (correo al equipo, estaba En curso, peso 2) y se quita de las dependencias de 6.1 y 6.2. 2.9 y P-28 ya no mencionan el correo. 6.9 y P-44: fuera AFILIACION_EMAIL_EQUIPO, entran RESEND_TEMPLATE_INGRESO_ACEPTADO, _CREDITO_APROBADO y _CREDITO_RECHAZADO. Plantillas: (a) «Ingreso aceptado» → nueva actividad 4.5 (aprobar afiliación en /admin, crear usuario y enviar correo; peso 3, depende de 4.1 y 2.9; 6.1 y 6.2 pasan a depender de ella) y pendiente P-51; (b) código de 6 dígitos lo envía Supabase Auth, funciona en local, en producción falta SMTP de Resend, plantilla Magic Link con {{ .Token }}, OTP de 6 dígitos y 600 s → se actualizan P-19, P-20 y P-45 (responsable «Yo (panel Supabase/Resend)»), ligados a 2.4; (c) «Resultado del crédito»: enviarResultadoCredito existe sin conectar → P-37 se redefine y pasa a 4.3. P-50 queda Hecho como «ya no aplica».</t>
         </is>
       </c>
     </row>
@@ -56570,22 +56574,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+          <t>6.3, 2.11; P-39, P-48, P-49, P-50</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+          <t>QA 1 de punta a punta: 186 pruebas pasan, 2 fallan</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+          <t>Playwright contra Supabase local (1280 y 390 px); pruebas en tests/e2e/ e informe en docs/verificaciones/2026-09-23-verificacion-1.md. Sin fallas críticas ni altas; una media (F-01: el select «Grado» de /afiliacion se vacía tras un error de validación). 6.3 y P-39 pasan a En curso (falta ga-verificador-responsive). Nueva actividad 2.11 (corregir F-01, peso 1, depende de 2.9) y 6.3 pasa a depender de ella. Pendientes nuevos: P-48 (F-01), P-49 (revisar x-forwarded-for para el límite por IP, ligado a 6.2) y P-50 (confirmar el envío de los correos de afiliación, ligado a 3.8).</t>
         </is>
       </c>
     </row>
@@ -56597,20 +56601,47 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
+          <t>ga-funcionalidad-botones</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>2.4, 2.5, 2.6, 2.7, 2.8, 2.9, 2.10, 3.5, 3.6, 3.7, 3.8, 5.4, 6.1, 6.5, 6.8, 6.9; P-15, P-20, P-22 a P-35, P-43 a P-47</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Botones de /, /ingresar, /ingresar/codigo, /afiliacion, /afiliacion/enviada y /cuenta funcionando en local</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Hecho: 2.5–2.10 y 3.5–3.7 (ingreso con código, proxy, Salir, Mis datos, afiliación con límites y honeypot, crédito conectado a /cuenta), contra Supabase local. En curso: 2.4 (plantilla local con {{ .Token }} lista; faltan SMTP y plantilla en producción), 3.8 (correos con Resend listos, falta RESEND_API_KEY), 5.4 (placeholder de /politica-de-datos, falta el texto de la cooperativa), 6.1 (pruebas de zod y /cuenta; faltan las de Server Actions). Dependencias: se quitó 2.4 de 2.5 y 2.9 porque el código funciona en local sin la configuración de producción; en su lugar 6.5 (despliegue) pasa a depender de 2.4, y 6.6/6.7 lo heredan vía 6.5. 3.8 y 4.3 siguen dependiendo de 2.4. Nuevas: 6.8 migración 20260923210000_limite_de_intentos.sql en producción (peso 1) y 6.9 variables en Vercel (peso 1), ambas antes de 6.5. Pendientes nuevos: P-43 (migración), P-44 (Vercel), P-45 (vencimiento 10 min e intervalo ≤ 45 s en Supabase, ligado a 2.4), P-46 (nombres de grados) y P-47 (estado de desembolso) de la cooperativa; 5.3 suma estos dos datos a su bloqueo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
           <t>Claude (sesión principal)</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Todas</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>Creación del Excel de avances</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>Pendientes desde PENDIENTES.md, plan desde la propuesta (6 fases, 8 semanas) reorganizado en 2 filas con cola infinita y pesos 1–5.</t>
         </is>

--- a/docs/avances/Avances_Green_Alliance.xlsx
+++ b/docs/avances/Avances_Green_Alliance.xlsx
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>P-55</t>
+          <t>P-113</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Opcional: revocar la secuencia limites_intentos_id_seq a anon y authenticated</t>
+          <t>Docker: db reset + test db local y aplicar la migración 20261001100000 en producción</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Yo + ga-auditor-supabase</t>
+          <t>Sebas</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="I5" s="21">
@@ -1848,14 +1848,14 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Sugerido por ga-auditor-supabase en la auditoría de P-43. 30-sep: revoke incluido en la migración 20261001000000 (pgTAP 20 en verde); falta aplicarla (6.23).</t>
+          <t>01-oct: Docker Desktop no arranca («unable to start»). 01-oct: Docker de vuelta; db test local en verde (22 archivos, 497 pruebas). Falta solo db push --linked de 20261001000000 y 20261001100000 y fusionar develop→main.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>P-110</t>
+          <t>P-55</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Aplicar la migración 20261001000000 antes de desplegar (sin ella falla el insert de afiliación por la columna version_politica_datos)</t>
+          <t>Opcional: revocar la secuencia limites_intentos_id_seq a anon y authenticated</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Sebas</t>
+          <t>Yo + ga-auditor-supabase</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="I6" s="21">
@@ -1899,14 +1899,14 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>30-sep: reportado por ga-auditor-supabase y ga-funcionalidad-botones.</t>
+          <t>Sugerido por ga-auditor-supabase en la auditoría de P-43. 30-sep: revoke incluido en la migración 20261001000000 (pgTAP 20 en verde); falta aplicarla (6.23).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>P-113</t>
+          <t>P-110</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Docker: db reset + test db local y aplicar la migración 20261001100000 en producción</t>
+          <t>Aplicar la migración 20261001000000 antes de desplegar (sin ella falla el insert de afiliación por la columna version_politica_datos)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="I7" s="21">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>01-oct: Docker Desktop no arranca («unable to start»).</t>
+          <t>30-sep: reportado por ga-auditor-supabase y ga-funcionalidad-botones.</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>/cuenta/solicitar</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>F-01: el select «Grado» se vacía tras un error de validación</t>
+          <t>Revisar el diseño de /cuenta/solicitar (sin maqueta; selector 50/100 como radios)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I26" s="21">
@@ -2919,14 +2919,14 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>Falla media de la verificación QA 1 (docs/verificaciones/2026-09-23-verificacion-1.md).</t>
+          <t>Pedido por ga-funcionalidad-botones el 23-sep.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>P-56</t>
+          <t>P-57</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>/cuenta/solicitar</t>
+          <t>/asesor</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Revisar el diseño de /cuenta/solicitar (sin maqueta; selector 50/100 como radios)</t>
+          <t>Agregar /asesor al matcher de proxy.ts y redirigir por rol tras el login</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="I27" s="21">
@@ -2970,14 +2970,14 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>Pedido por ga-funcionalidad-botones el 23-sep.</t>
+          <t>Hoy un asesor que ingresa cae en /cuenta, no en /asesor; la página /asesor igual se protege por su cuenta si se navega directo.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>P-57</t>
+          <t>P-68</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2987,17 +2987,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>/asesor</t>
+          <t>Convenios</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Agregar /asesor al matcher de proxy.ts y redirigir por rol tras el login</t>
+          <t>Convenios administrables desde /admin (crear, editar, ocultar, ordenar, logo en Storage); landing y /cuenta leen de la tabla convenios</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Carlos Pardo</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="I28" s="21">
@@ -3021,14 +3021,14 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>Hoy un asesor que ingresa cae en /cuenta, no en /asesor; la página /asesor igual se protege por su cuenta si se navega directo.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73. 30-sep: Carlos salió; pasa a ga-funcionalidad-botones.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>P-68</t>
+          <t>P-108</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Convenios</t>
+          <t>Asesor</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Convenios administrables desde /admin (crear, editar, ocultar, ordenar, logo en Storage); landing y /cuenta leen de la tabla convenios</t>
+          <t>Backlog: premio al primer asesor</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Carlos Pardo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="I29" s="21">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Ver P-73. 30-sep: Carlos salió; pasa a ga-funcionalidad-botones.</t>
+          <t>Spec §12.12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>P-108</t>
+          <t>P-109</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Asesor</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Backlog: premio al primer asesor</t>
+          <t>Backlog: carné virtual del asociado</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="I30" s="21">
@@ -3130,7 +3130,7 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>P-109</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3140,48 +3140,44 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>/ingresar</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Backlog: carné virtual del asociado</t>
+          <t>Server Action: correo_por_cedula(), signInWithOtp, cookie firmada, ir a /ingresar/codigo</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I31" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$88,MATCH(H31,Plan!$A$5:$A$88,0)),"—")</f>
         <v/>
       </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>Spec §12.12</t>
-        </is>
-      </c>
+      <c r="J31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3191,12 +3187,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>/ingresar/codigo</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Server Action: correo_por_cedula(), signInWithOtp, cookie firmada, ir a /ingresar/codigo</t>
+          <t>Leer la cookie del paso 1; sin cookie, volver a /ingresar</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -3216,7 +3212,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I32" s="21">
@@ -3228,7 +3224,7 @@
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3243,7 +3239,7 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Leer la cookie del paso 1; sin cookie, volver a /ingresar</t>
+          <t>verifyOtp y entrar a /cuenta</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -3275,7 +3271,7 @@
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3285,12 +3281,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>/ingresar/codigo</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>verifyOtp y entrar a /cuenta</t>
+          <t>Server Action: zod, límites por IP y cédula, guardar</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -3310,19 +3306,23 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I34" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$88,MATCH(H34,Plan!$A$5:$A$88,0)),"—")</f>
         <v/>
       </c>
-      <c r="J34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>23-sep: se quitaron los correos al equipo y al solicitante (decisión de Sebas). El equipo revisa las afiliaciones en Supabase hasta que exista el panel /admin; el correo «Ingreso aceptado» sale al aprobar (P-51).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-31</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Server Action: zod, límites por IP y cédula, guardar</t>
+          <t>Proteger con proxy.ts y «Salir» con signOut</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -3357,23 +3357,19 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I35" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$88,MATCH(H35,Plan!$A$5:$A$88,0)),"—")</f>
         <v/>
       </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>23-sep: se quitaron los correos al equipo y al solicitante (decisión de Sebas). El equipo revisa las afiliaciones en Supabase hasta que exista el panel /admin; el correo «Ingreso aceptado» sale al aprobar (P-51).</t>
-        </is>
-      </c>
+      <c r="J35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3388,7 +3384,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Proteger con proxy.ts y «Salir» con signOut</t>
+          <t>Cargar perfil, última solicitud (con tasa), tope y convenios</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -3408,7 +3404,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I36" s="21">
@@ -3420,7 +3416,7 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>P-32</t>
+          <t>P-35</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -3430,12 +3426,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>Crédito</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Cargar perfil, última solicitud (con tasa), tope y convenios</t>
+          <t>Conectar el formulario de crédito a /cuenta</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -3455,19 +3451,23 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I37" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$88,MATCH(H37,Plan!$A$5:$A$88,0)),"—")</f>
         <v/>
       </c>
-      <c r="J37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>23-sep: el formulario vive en /cuenta/solicitar (protegida por proxy.ts, encabezado compartido EncabezadoCuenta); «Nueva solicitud» lleva ahí.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-36</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Crédito</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Conectar el formulario de crédito a /cuenta</t>
+          <t>Panel /admin: listado, aprobar y rechazar con motivo</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I38" s="21">
@@ -3511,14 +3511,14 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>23-sep: el formulario vive en /cuenta/solicitar (protegida por proxy.ts, encabezado compartido EncabezadoCuenta); «Nueva solicitud» lleva ahí.</t>
+          <t>24-sep: implementado y probado en local (commits 235ffbe, a13c2de). Un admin no puede resolver su propia solicitud.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-38</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Asociados</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Panel /admin: listado, aprobar y rechazar con motivo</t>
+          <t>Importación de asociados desde Excel</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I39" s="21">
@@ -3562,14 +3562,14 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>24-sep: implementado y probado en local (commits 235ffbe, a13c2de). Un admin no puede resolver su propia solicitud.</t>
+          <t>Ya no aplica: decisión de la cooperativa 2026-09-24, no habrá importación de Excel.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-69</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Asociados</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Importación de asociados desde Excel</t>
+          <t>Ley 1581: borrado automático de fotos de afiliaciones rechazadas tras X días y motivo de rechazo en /admin</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>Carlos Pardo</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="I40" s="21">
@@ -3613,14 +3613,14 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>Ya no aplica: decisión de la cooperativa 2026-09-24, no habrá importación de Excel.</t>
+          <t>Encargo externo (500.000 COP) por PR a develop. Falta que la cooperativa dé el X de días (ver P-63). Ver P-73. 29-sep: primera entrega (ZIP, base main anterior al rediseño C+) NO fusionable — reintroduce F2-03, pierde el revoke en resumen_clientes_asesor, columna de motivo de rechazo inexistente sin migración, purga con columnas/bucket equivocados y cron abierto sin CRON_SECRET, claves en .env.example, console.log, config de túnel, sin pruebas. Se le envió la lista de correcciones para rehacer sobre rediseno-c-plus, un PR por tarea. 30-sep: hecho por agentes (cron cada hora + RPC fotos_huerfanas_afiliacion).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>P-69</t>
+          <t>P-85</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Ley 1581: borrado automático de fotos de afiliaciones rechazadas tras X días y motivo de rechazo en /admin</t>
+          <t>Correo de afiliación acepta cualquier dominio (ya no exige @policia.gov.co / @ejercito.mil.co)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Carlos Pardo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I41" s="21">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>Encargo externo (500.000 COP) por PR a develop. Falta que la cooperativa dé el X de días (ver P-63). Ver P-73. 29-sep: primera entrega (ZIP, base main anterior al rediseño C+) NO fusionable — reintroduce F2-03, pierde el revoke en resumen_clientes_asesor, columna de motivo de rechazo inexistente sin migración, purga con columnas/bucket equivocados y cron abierto sin CRON_SECRET, claves en .env.example, console.log, config de túnel, sin pruebas. Se le envió la lista de correcciones para rehacer sobre rediseno-c-plus, un PR por tarea. 30-sep: hecho por agentes (cron cada hora + RPC fotos_huerfanas_afiliacion).</t>
+          <t>25-sep: esquema zod, campo del formulario y pruebas (unitarias, e2e, pgTAP) actualizados; migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (base de datos) y el archivo local renombrado a esa versión para que el historial coincida. F-01 revisado: la máscara del correo ahora oculta también el dominio («ju•••@•••»). 25-sep: desplegado con el PR #2 (merge 2c19d02); confirmado en vivo que /afiliacion ya no exige correo institucional.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>P-85</t>
+          <t>P-112</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -3681,22 +3681,22 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Correo de afiliación acepta cualquier dominio (ya no exige @policia.gov.co / @ejercito.mil.co)</t>
+          <t>Agregar admin_metricas_dashboard y asesor_metricas_dashboard a las listas blancas de security definer (pgTAP 00 #14 y 15 #24)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-escritor-tests</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="I42" s="21">
@@ -3715,14 +3715,14 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>25-sep: esquema zod, campo del formulario y pruebas (unitarias, e2e, pgTAP) actualizados; migración 20260925194922_correo_afiliacion_cualquier_dominio aplicada en producción (base de datos) y el archivo local renombrado a esa versión para que el historial coincida. F-01 revisado: la máscara del correo ahora oculta también el dominio («ju•••@•••»). 25-sep: desplegado con el PR #2 (merge 2c19d02); confirmado en vivo que /afiliacion ya no exige correo institucional.</t>
+          <t>30-sep: reportado por ga-auditor-supabase. 01-oct: listas blancas de 00 y 15 actualizadas por ga-auditor-supabase (falta correrlas: Docker).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>P-112</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -3732,17 +3732,17 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>/ingresar</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Agregar admin_metricas_dashboard y asesor_metricas_dashboard a las listas blancas de security definer (pgTAP 00 #14 y 15 #24)</t>
+          <t>Estado «Enviando…» (prop cargando) y errores (prop error)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>ga-escritor-tests</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -3757,23 +3757,19 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I43" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$88,MATCH(H43,Plan!$A$5:$A$88,0)),"—")</f>
         <v/>
       </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>30-sep: reportado por ga-auditor-supabase. 01-oct: listas blancas de 00 y 15 actualizadas por ga-auditor-supabase (falta correrlas: Docker).</t>
-        </is>
-      </c>
+      <c r="J43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -3783,12 +3779,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>/ingresar</t>
+          <t>/ingresar/codigo</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Estado «Enviando…» (prop cargando) y errores (prop error)</t>
+          <t>Casillas OTP: avance automático, Backspace, pegar; «Entrar» con 6 dígitos</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -3808,7 +3804,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I44" s="21">
@@ -3820,7 +3816,7 @@
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -3835,7 +3831,7 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Casillas OTP: avance automático, Backspace, pegar; «Entrar» con 6 dígitos</t>
+          <t>«Reenviar código» con contador de 45 s; «Cambiar cédula» limpia la cookie</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -3867,7 +3863,7 @@
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3877,12 +3873,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>/ingresar/codigo</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>«Reenviar código» con contador de 45 s; «Cambiar cédula» limpia la cookie</t>
+          <t>Grados desde grados_credito, honeypot, errores y estado de carga</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -3902,7 +3898,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I46" s="21">
@@ -3914,7 +3910,7 @@
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -3924,12 +3920,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>/afiliacion</t>
+          <t>/cuenta</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Grados desde grados_credito, honeypot, errores y estado de carga</t>
+          <t>«Mis datos»: actualizar solo perfiles.telefono</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -3949,19 +3945,23 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I47" s="21">
         <f>IFERROR(INDEX(Plan!$B$5:$B$88,MATCH(H47,Plan!$A$5:$A$88,0)),"—")</f>
         <v/>
       </c>
-      <c r="J47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>Con error, alinear «Guardar» con el campo desde 640 px.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>/cuenta</t>
+          <t>/afiliacion</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>«Mis datos»: actualizar solo perfiles.telefono</t>
+          <t>F-01: el select «Grado» se vacía tras un error de validación</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I48" s="21">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>Con error, alinear «Guardar» con el campo desde 640 px.</t>
+          <t>Falla media de la verificación QA 1 (docs/verificaciones/2026-09-23-verificacion-1.md). 01-oct: corregido (formulario se rehace con key; conserva Institución/Grado).</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>2.5, 2.6</t>
+          <t>1.4, 2.2, 2.5</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -8038,7 +8038,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L9" s="8">
         <f>K9+E9</f>
@@ -8104,19 +8104,19 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>6.19, 6.17</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L10" s="8">
         <f>K10+E10</f>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>3.1, 6.10</t>
+          <t>3.4, 6.10</t>
         </is>
       </c>
       <c r="I11" s="18" t="inlineStr">
@@ -8194,7 +8194,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L11" s="8">
         <f>K11+E11</f>
@@ -8269,7 +8269,7 @@
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K12" s="8" t="n">
         <v>37</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>2.2, 2.5</t>
+          <t>2.5, 2.6</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
@@ -8350,7 +8350,7 @@
         <v>6</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L13" s="8">
         <f>K13+E13</f>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -8506,7 +8506,7 @@
         <v>6</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" s="8">
         <f>K15+E15</f>
@@ -8572,19 +8572,19 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="I16" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J16" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="L16" s="8">
         <f>K16+E16</f>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>2.1, 1.5</t>
+          <t>1.5, 2.1</t>
         </is>
       </c>
       <c r="I17" s="18" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.1, 3.1</t>
         </is>
       </c>
       <c r="I18" s="18" t="inlineStr">
@@ -8818,7 +8818,7 @@
         <v>14</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L19" s="8">
         <f>K19+E19</f>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I20" s="18" t="inlineStr">
@@ -8893,10 +8893,10 @@
         </is>
       </c>
       <c r="J20" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L20" s="8">
         <f>K20+E20</f>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>4.12, 4.13</t>
+          <t>4.12, 3.6</t>
         </is>
       </c>
       <c r="I21" s="18" t="inlineStr">
@@ -8971,7 +8971,7 @@
         </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>42</v>
@@ -9040,19 +9040,19 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I22" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J22" s="8" t="n">
         <v>46</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L22" s="8">
         <f>K22+E22</f>
@@ -9118,19 +9118,19 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J23" s="8" t="n">
         <v>46</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L23" s="8">
         <f>K23+E23</f>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.7, 2.10, 3.9</t>
         </is>
       </c>
       <c r="I24" s="18" t="inlineStr">
@@ -9208,7 +9208,7 @@
         <v>46</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="L24" s="8">
         <f>K24+E24</f>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I25" s="18" t="inlineStr">
@@ -9283,10 +9283,10 @@
         </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L25" s="8">
         <f>K25+E25</f>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3.4, 2.7</t>
+          <t>4.6, 2.7</t>
         </is>
       </c>
       <c r="I26" s="18" t="inlineStr">
@@ -9361,10 +9361,10 @@
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L26" s="8">
         <f>K26+E26</f>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>4.1, 4.11</t>
+          <t>4.1, 2.8</t>
         </is>
       </c>
       <c r="I27" s="18" t="inlineStr">
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L27" s="8">
         <f>K27+E27</f>
@@ -9508,19 +9508,19 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>4.6, 1.7</t>
+          <t>2.6, 3.4</t>
         </is>
       </c>
       <c r="I28" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J28" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L28" s="8">
         <f>K28+E28</f>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>4.9, 5.1</t>
+          <t>4.15, 4.9</t>
         </is>
       </c>
       <c r="I29" s="18" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L29" s="8">
         <f>K29+E29</f>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="I30" s="18" t="inlineStr">
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L30" s="8">
         <f>K30+E30</f>
@@ -9742,19 +9742,19 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.1, 1.7</t>
         </is>
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J31" s="8" t="n">
         <v>6</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L31" s="8">
         <f>K31+E31</f>
@@ -9820,19 +9820,19 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I32" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J32" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="L32" s="8">
         <f>K32+E32</f>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>2.10, 4.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I33" s="18" t="inlineStr">
@@ -9907,10 +9907,10 @@
         </is>
       </c>
       <c r="J33" s="8" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L33" s="8">
         <f>K33+E33</f>
@@ -9976,7 +9976,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>2.11, 6.11, 6.9</t>
+          <t>4.3, 2.12</t>
         </is>
       </c>
       <c r="I34" s="18" t="inlineStr">
@@ -9988,7 +9988,7 @@
         <v>52</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L34" s="8">
         <f>K34+E34</f>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.12, 4.13</t>
         </is>
       </c>
       <c r="I35" s="18" t="inlineStr">
@@ -10063,10 +10063,10 @@
         </is>
       </c>
       <c r="J35" s="8" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L35" s="8">
         <f>K35+E35</f>
@@ -10132,19 +10132,19 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>4.11, 4.10</t>
+          <t>4.10, 6.16, 4.11</t>
         </is>
       </c>
       <c r="I36" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L36" s="8">
         <f>K36+E36</f>
@@ -10219,10 +10219,10 @@
         </is>
       </c>
       <c r="J37" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L37" s="8">
         <f>K37+E37</f>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I38" s="18" t="inlineStr">
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="J38" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L38" s="8">
         <f>K38+E38</f>
@@ -10366,19 +10366,19 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J39" s="8" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L39" s="8">
         <f>K39+E39</f>
@@ -10444,19 +10444,19 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>4.15, 6.8</t>
+          <t>4.7, 5.1</t>
         </is>
       </c>
       <c r="I40" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J40" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L40" s="8">
         <f>K40+E40</f>
@@ -10526,19 +10526,19 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>3.6, 4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J41" s="8" t="n">
         <v>46</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L41" s="8">
         <f>K41+E41</f>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I42" s="18" t="inlineStr">
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="J42" s="8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L42" s="8">
         <f>K42+E42</f>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>6.11, 6.9, 4.4</t>
         </is>
       </c>
       <c r="I43" s="18" t="inlineStr">
@@ -10691,10 +10691,10 @@
         </is>
       </c>
       <c r="J43" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L43" s="8">
         <f>K43+E43</f>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>5.8, 2.13</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr">
@@ -10769,10 +10769,10 @@
         </is>
       </c>
       <c r="J44" s="8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="L44" s="8">
         <f>K44+E44</f>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.2, 5.10</t>
         </is>
       </c>
       <c r="I45" s="18" t="inlineStr">
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="J45" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L45" s="8">
         <f>K45+E45</f>
@@ -10916,19 +10916,19 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.19, 3.10</t>
         </is>
       </c>
       <c r="I46" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J46" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L46" s="8">
         <f>K46+E46</f>
@@ -10994,19 +10994,19 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>2.15, 6.16, 3.10</t>
+          <t>3.10, 2.4</t>
         </is>
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J47" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L47" s="8">
         <f>K47+E47</f>
@@ -11072,19 +11072,19 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>3.2, 5.13</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J48" s="8" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L48" s="8">
         <f>K48+E48</f>
@@ -11150,16 +11150,16 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J49" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K49" s="8" t="n">
         <v>49</v>
@@ -11228,19 +11228,19 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>5.4, 6.2</t>
+          <t>6.14, 6.12</t>
         </is>
       </c>
       <c r="I50" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J50" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L50" s="8">
         <f>K50+E50</f>
@@ -11310,19 +11310,19 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J51" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L51" s="8">
         <f>K51+E51</f>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I52" s="18" t="inlineStr">
@@ -11401,10 +11401,10 @@
         </is>
       </c>
       <c r="J52" s="8" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L52" s="8">
         <f>K52+E52</f>
@@ -11470,19 +11470,19 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I53" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J53" s="8" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L53" s="8">
         <f>K53+E53</f>
@@ -11548,19 +11548,19 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>2.13, 5.13</t>
         </is>
       </c>
       <c r="I54" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J54" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L54" s="8">
         <f>K54+E54</f>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="I55" s="18" t="inlineStr">
@@ -11635,10 +11635,10 @@
         </is>
       </c>
       <c r="J55" s="8" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L55" s="8">
         <f>K55+E55</f>
@@ -11704,16 +11704,16 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>6.15, 6.21</t>
+          <t>6.6, 5.11</t>
         </is>
       </c>
       <c r="I56" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J56" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K56" s="8" t="n">
         <v>97</v>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I57" s="18" t="inlineStr">
@@ -11791,10 +11791,10 @@
         </is>
       </c>
       <c r="J57" s="8" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="L57" s="8">
         <f>K57+E57</f>
@@ -11860,19 +11860,19 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>6.2, 6.12, 6.14</t>
+          <t>5.4, 6.2</t>
         </is>
       </c>
       <c r="I58" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J58" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L58" s="8">
         <f>K58+E58</f>
@@ -11938,19 +11938,19 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>5.3, 6.1</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="I59" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J59" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L59" s="8">
         <f>K59+E59</f>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>5.11, 6.24</t>
+          <t>6.15, 5.12</t>
         </is>
       </c>
       <c r="I60" s="18" t="inlineStr">
@@ -12025,10 +12025,10 @@
         </is>
       </c>
       <c r="J60" s="8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L60" s="8">
         <f>K60+E60</f>
@@ -12106,7 +12106,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L61" s="8">
         <f>K61+E61</f>
@@ -12181,10 +12181,10 @@
         </is>
       </c>
       <c r="J62" s="8" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L62" s="8">
         <f>K62+E62</f>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>6.7, 5.12</t>
+          <t>6.24, 6.7, 5.9</t>
         </is>
       </c>
       <c r="I63" s="18" t="inlineStr">
@@ -12259,10 +12259,10 @@
         </is>
       </c>
       <c r="J63" s="8" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L63" s="8">
         <f>K63+E63</f>
@@ -12337,10 +12337,10 @@
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L64" s="8">
         <f>K64+E64</f>
@@ -12406,19 +12406,19 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I65" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J65" s="8" t="n">
         <v>46</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="L65" s="8">
         <f>K65+E65</f>
@@ -12484,19 +12484,19 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I66" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J66" s="8" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="L66" s="8">
         <f>K66+E66</f>
@@ -12571,10 +12571,10 @@
         </is>
       </c>
       <c r="J67" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K67" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L67" s="8">
         <f>K67+E67</f>
@@ -12640,19 +12640,19 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="I68" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J68" s="8" t="n">
         <v>46</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="L68" s="8">
         <f>K68+E68</f>
@@ -12718,19 +12718,19 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J69" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L69" s="8">
         <f>K69+E69</f>
@@ -12805,7 +12805,7 @@
         </is>
       </c>
       <c r="J70" s="8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K70" s="8" t="n">
         <v>38</v>
@@ -12874,16 +12874,16 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I71" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J71" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K71" s="8" t="n">
         <v>87</v>
@@ -12952,7 +12952,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I72" s="18" t="inlineStr">
@@ -12961,10 +12961,10 @@
         </is>
       </c>
       <c r="J72" s="8" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="L72" s="8">
         <f>K72+E72</f>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="O72" s="8" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>En curso</t>
         </is>
       </c>
       <c r="P72" s="8" t="inlineStr">
@@ -12993,11 +12993,7 @@
           <t>ga-verificador-qa (antes Carlos Pardo)</t>
         </is>
       </c>
-      <c r="R72" s="7" t="inlineStr">
-        <is>
-          <t>Docker Desktop se cayó y Supabase local no responde: Sebas reinicia Docker, supabase db reset y corre Playwright (-c tests/e2e/playwright.config.ts).</t>
-        </is>
-      </c>
+      <c r="R72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
@@ -13034,7 +13030,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I73" s="18" t="inlineStr">
@@ -13043,10 +13039,10 @@
         </is>
       </c>
       <c r="J73" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L73" s="8">
         <f>K73+E73</f>
@@ -13112,19 +13108,19 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="I74" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J74" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L74" s="8">
         <f>K74+E74</f>
@@ -13190,12 +13186,12 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>1.6, 2.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J75" s="8" t="n">
@@ -13346,7 +13342,7 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>4.2, 2.9</t>
+          <t>3.5, 2.9</t>
         </is>
       </c>
       <c r="I77" s="18" t="inlineStr">
@@ -13424,19 +13420,19 @@
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>2.9, 3.3</t>
+          <t>3.9, 5.5, 5.6, 2.11</t>
         </is>
       </c>
       <c r="I78" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J78" s="8" t="n">
         <v>44</v>
       </c>
       <c r="K78" s="8" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="L78" s="8">
         <f>K78+E78</f>
@@ -13511,10 +13507,10 @@
         </is>
       </c>
       <c r="J79" s="8" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="K79" s="8" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L79" s="8">
         <f>K79+E79</f>
@@ -13580,7 +13576,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.8, 4.8</t>
         </is>
       </c>
       <c r="I80" s="18" t="inlineStr">
@@ -13589,10 +13585,10 @@
         </is>
       </c>
       <c r="J80" s="8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K80" s="8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L80" s="8">
         <f>K80+E80</f>
@@ -13658,7 +13654,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.21, 3.2</t>
         </is>
       </c>
       <c r="I81" s="18" t="inlineStr">
@@ -13667,10 +13663,10 @@
         </is>
       </c>
       <c r="J81" s="8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K81" s="8" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L81" s="8">
         <f>K81+E81</f>
@@ -13736,7 +13732,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.8, 4.15</t>
         </is>
       </c>
       <c r="I82" s="18" t="inlineStr">
@@ -13745,10 +13741,10 @@
         </is>
       </c>
       <c r="J82" s="8" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="K82" s="8" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="L82" s="8">
         <f>K82+E82</f>
@@ -13764,7 +13760,7 @@
       </c>
       <c r="O82" s="8" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="P82" s="8" t="inlineStr">
@@ -13777,11 +13773,7 @@
           <t>ga-verificador-qa</t>
         </is>
       </c>
-      <c r="R82" s="7" t="inlineStr">
-        <is>
-          <t>Docker Desktop se cayó y Supabase local no responde: Sebas reinicia Docker, supabase db reset y corre Playwright (-c tests/e2e/playwright.config.ts).</t>
-        </is>
-      </c>
+      <c r="R82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
@@ -13827,10 +13819,10 @@
         </is>
       </c>
       <c r="J83" s="8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K83" s="8" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="L83" s="8">
         <f>K83+E83</f>
@@ -13896,19 +13888,19 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="I84" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J84" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K84" s="8" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L84" s="8">
         <f>K84+E84</f>
@@ -13974,7 +13966,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I85" s="18" t="inlineStr">
@@ -13983,10 +13975,10 @@
         </is>
       </c>
       <c r="J85" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K85" s="8" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L85" s="8">
         <f>K85+E85</f>
@@ -14052,12 +14044,12 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I86" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J86" s="8" t="n">
@@ -14139,10 +14131,10 @@
         </is>
       </c>
       <c r="J87" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K87" s="8" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L87" s="8">
         <f>K87+E87</f>
@@ -14208,7 +14200,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="I88" s="18" t="inlineStr">
@@ -14217,10 +14209,10 @@
         </is>
       </c>
       <c r="J88" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K88" s="8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L88" s="8">
         <f>K88+E88</f>
@@ -52824,22 +52816,22 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C9" s="35">
-        <f>Plan!C16</f>
+        <f>Plan!C9</f>
         <v/>
       </c>
       <c r="D9" s="8" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E9" s="16">
-        <f>Plan!J16</f>
+        <f>Plan!J9</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>Plan!K16</f>
+        <f>Plan!K9</f>
         <v/>
       </c>
       <c r="G9" s="8">
@@ -52847,11 +52839,11 @@
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>Plan!I16</f>
+        <f>Plan!I9</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>Plan!O16</f>
+        <f>Plan!O9</f>
         <v/>
       </c>
     </row>
@@ -52898,22 +52890,22 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C11" s="35">
-        <f>Plan!C13</f>
+        <f>Plan!C17</f>
         <v/>
       </c>
       <c r="D11" s="8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E11" s="16">
-        <f>Plan!J13</f>
+        <f>Plan!J17</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>Plan!K13</f>
+        <f>Plan!K17</f>
         <v/>
       </c>
       <c r="G11" s="8">
@@ -52921,11 +52913,11 @@
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>Plan!I13</f>
+        <f>Plan!I17</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>Plan!O13</f>
+        <f>Plan!O17</f>
         <v/>
       </c>
     </row>
@@ -52935,22 +52927,22 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C12" s="35">
-        <f>Plan!C17</f>
+        <f>Plan!C13</f>
         <v/>
       </c>
       <c r="D12" s="8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E12" s="16">
-        <f>Plan!J17</f>
+        <f>Plan!J13</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>Plan!K17</f>
+        <f>Plan!K13</f>
         <v/>
       </c>
       <c r="G12" s="8">
@@ -52958,11 +52950,11 @@
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>Plan!I17</f>
+        <f>Plan!I13</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>Plan!O17</f>
+        <f>Plan!O13</f>
         <v/>
       </c>
     </row>
@@ -52972,22 +52964,22 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="C13" s="35">
-        <f>Plan!C9</f>
+        <f>Plan!C18</f>
         <v/>
       </c>
       <c r="D13" s="8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E13" s="16">
-        <f>Plan!J9</f>
+        <f>Plan!J18</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>Plan!K9</f>
+        <f>Plan!K18</f>
         <v/>
       </c>
       <c r="G13" s="8">
@@ -52995,11 +52987,11 @@
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>Plan!I9</f>
+        <f>Plan!I18</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>Plan!O9</f>
+        <f>Plan!O18</f>
         <v/>
       </c>
     </row>
@@ -53009,22 +53001,22 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C14" s="35">
-        <f>Plan!C18</f>
+        <f>Plan!C28</f>
         <v/>
       </c>
       <c r="D14" s="8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="16">
-        <f>Plan!J18</f>
+        <f>Plan!J28</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>Plan!K18</f>
+        <f>Plan!K28</f>
         <v/>
       </c>
       <c r="G14" s="8">
@@ -53032,11 +53024,11 @@
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>Plan!I18</f>
+        <f>Plan!I28</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>Plan!O18</f>
+        <f>Plan!O28</f>
         <v/>
       </c>
     </row>
@@ -53046,22 +53038,22 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C15" s="35">
-        <f>Plan!C28</f>
+        <f>Plan!C31</f>
         <v/>
       </c>
       <c r="D15" s="8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E15" s="16">
-        <f>Plan!J28</f>
+        <f>Plan!J31</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>Plan!K28</f>
+        <f>Plan!K31</f>
         <v/>
       </c>
       <c r="G15" s="8">
@@ -53069,11 +53061,11 @@
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>Plan!I28</f>
+        <f>Plan!I31</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>Plan!O28</f>
+        <f>Plan!O31</f>
         <v/>
       </c>
     </row>
@@ -53083,22 +53075,22 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="C16" s="35">
-        <f>Plan!C42</f>
+        <f>Plan!C11</f>
         <v/>
       </c>
       <c r="D16" s="8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E16" s="16">
-        <f>Plan!J42</f>
+        <f>Plan!J11</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>Plan!K42</f>
+        <f>Plan!K11</f>
         <v/>
       </c>
       <c r="G16" s="8">
@@ -53106,11 +53098,11 @@
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>Plan!I42</f>
+        <f>Plan!I11</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>Plan!O42</f>
+        <f>Plan!O11</f>
         <v/>
       </c>
     </row>
@@ -53120,22 +53112,22 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="C17" s="35">
-        <f>Plan!C11</f>
+        <f>Plan!C67</f>
         <v/>
       </c>
       <c r="D17" s="8" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E17" s="16">
-        <f>Plan!J11</f>
+        <f>Plan!J67</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>Plan!K11</f>
+        <f>Plan!K67</f>
         <v/>
       </c>
       <c r="G17" s="8">
@@ -53143,11 +53135,11 @@
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>Plan!I11</f>
+        <f>Plan!I67</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>Plan!O11</f>
+        <f>Plan!O67</f>
         <v/>
       </c>
     </row>
@@ -53157,22 +53149,22 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="C18" s="35">
-        <f>Plan!C67</f>
+        <f>Plan!C26</f>
         <v/>
       </c>
       <c r="D18" s="8" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E18" s="16">
-        <f>Plan!J67</f>
+        <f>Plan!J26</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>Plan!K67</f>
+        <f>Plan!K26</f>
         <v/>
       </c>
       <c r="G18" s="8">
@@ -53180,11 +53172,11 @@
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>Plan!I67</f>
+        <f>Plan!I26</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>Plan!O67</f>
+        <f>Plan!O26</f>
         <v/>
       </c>
     </row>
@@ -53194,22 +53186,22 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C19" s="35">
-        <f>Plan!C31</f>
+        <f>Plan!C42</f>
         <v/>
       </c>
       <c r="D19" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" s="16">
-        <f>Plan!J31</f>
+        <f>Plan!J42</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>Plan!K31</f>
+        <f>Plan!K42</f>
         <v/>
       </c>
       <c r="G19" s="8">
@@ -53217,11 +53209,11 @@
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>Plan!I31</f>
+        <f>Plan!I42</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>Plan!O31</f>
+        <f>Plan!O42</f>
         <v/>
       </c>
     </row>
@@ -53231,22 +53223,22 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C20" s="35">
-        <f>Plan!C26</f>
+        <f>Plan!C19</f>
         <v/>
       </c>
       <c r="D20" s="8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E20" s="16">
-        <f>Plan!J26</f>
+        <f>Plan!J19</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>Plan!K26</f>
+        <f>Plan!K19</f>
         <v/>
       </c>
       <c r="G20" s="8">
@@ -53254,11 +53246,11 @@
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>Plan!I26</f>
+        <f>Plan!I19</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>Plan!O26</f>
+        <f>Plan!O19</f>
         <v/>
       </c>
     </row>
@@ -53268,22 +53260,22 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="C21" s="35">
-        <f>Plan!C19</f>
+        <f>Plan!C61</f>
         <v/>
       </c>
       <c r="D21" s="8" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E21" s="16">
-        <f>Plan!J19</f>
+        <f>Plan!J61</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>Plan!K19</f>
+        <f>Plan!K61</f>
         <v/>
       </c>
       <c r="G21" s="8">
@@ -53291,11 +53283,11 @@
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>Plan!I19</f>
+        <f>Plan!I61</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>Plan!O19</f>
+        <f>Plan!O61</f>
         <v/>
       </c>
     </row>
@@ -53305,22 +53297,22 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C22" s="35">
-        <f>Plan!C61</f>
+        <f>Plan!C37</f>
         <v/>
       </c>
       <c r="D22" s="8" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E22" s="16">
-        <f>Plan!J61</f>
+        <f>Plan!J37</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>Plan!K61</f>
+        <f>Plan!K37</f>
         <v/>
       </c>
       <c r="G22" s="8">
@@ -53328,11 +53320,11 @@
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>Plan!I61</f>
+        <f>Plan!I37</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>Plan!O61</f>
+        <f>Plan!O37</f>
         <v/>
       </c>
     </row>
@@ -53342,22 +53334,22 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C23" s="35">
-        <f>Plan!C37</f>
+        <f>Plan!C15</f>
         <v/>
       </c>
       <c r="D23" s="8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" s="16">
-        <f>Plan!J37</f>
+        <f>Plan!J15</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>Plan!K37</f>
+        <f>Plan!K15</f>
         <v/>
       </c>
       <c r="G23" s="8">
@@ -53365,11 +53357,11 @@
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>Plan!I37</f>
+        <f>Plan!I15</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>Plan!O37</f>
+        <f>Plan!O15</f>
         <v/>
       </c>
     </row>
@@ -53379,22 +53371,22 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C24" s="35">
-        <f>Plan!C15</f>
+        <f>Plan!C27</f>
         <v/>
       </c>
       <c r="D24" s="8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E24" s="16">
-        <f>Plan!J15</f>
+        <f>Plan!J27</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>Plan!K15</f>
+        <f>Plan!K27</f>
         <v/>
       </c>
       <c r="G24" s="8">
@@ -53402,11 +53394,11 @@
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>Plan!I15</f>
+        <f>Plan!I27</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>Plan!O15</f>
+        <f>Plan!O27</f>
         <v/>
       </c>
     </row>
@@ -53416,22 +53408,22 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C25" s="35">
-        <f>Plan!C27</f>
+        <f>Plan!C20</f>
         <v/>
       </c>
       <c r="D25" s="8" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E25" s="16">
-        <f>Plan!J27</f>
+        <f>Plan!J20</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>Plan!K27</f>
+        <f>Plan!K20</f>
         <v/>
       </c>
       <c r="G25" s="8">
@@ -53439,11 +53431,11 @@
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>Plan!I27</f>
+        <f>Plan!I20</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>Plan!O27</f>
+        <f>Plan!O20</f>
         <v/>
       </c>
     </row>
@@ -53453,22 +53445,22 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C26" s="35">
-        <f>Plan!C47</f>
+        <f>Plan!C46</f>
         <v/>
       </c>
       <c r="D26" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="16">
-        <f>Plan!J47</f>
+        <f>Plan!J46</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>Plan!K47</f>
+        <f>Plan!K46</f>
         <v/>
       </c>
       <c r="G26" s="8">
@@ -53476,11 +53468,11 @@
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>Plan!I47</f>
+        <f>Plan!I46</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>Plan!O47</f>
+        <f>Plan!O46</f>
         <v/>
       </c>
     </row>
@@ -53490,22 +53482,22 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="C27" s="35">
-        <f>Plan!C73</f>
+        <f>Plan!C74</f>
         <v/>
       </c>
       <c r="D27" s="8" t="n">
         <v>24</v>
       </c>
       <c r="E27" s="16">
-        <f>Plan!J73</f>
+        <f>Plan!J74</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>Plan!K73</f>
+        <f>Plan!K74</f>
         <v/>
       </c>
       <c r="G27" s="8">
@@ -53513,11 +53505,11 @@
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>Plan!I73</f>
+        <f>Plan!I74</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>Plan!O73</f>
+        <f>Plan!O74</f>
         <v/>
       </c>
     </row>
@@ -53564,22 +53556,22 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="C29" s="35">
-        <f>Plan!C46</f>
+        <f>Plan!C73</f>
         <v/>
       </c>
       <c r="D29" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" s="16">
-        <f>Plan!J46</f>
+        <f>Plan!J73</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>Plan!K46</f>
+        <f>Plan!K73</f>
         <v/>
       </c>
       <c r="G29" s="8">
@@ -53587,11 +53579,11 @@
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>Plan!I46</f>
+        <f>Plan!I73</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>Plan!O46</f>
+        <f>Plan!O73</f>
         <v/>
       </c>
     </row>
@@ -53601,22 +53593,22 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="C30" s="35">
-        <f>Plan!C10</f>
+        <f>Plan!C47</f>
         <v/>
       </c>
       <c r="D30" s="8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E30" s="16">
-        <f>Plan!J10</f>
+        <f>Plan!J47</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>Plan!K10</f>
+        <f>Plan!K47</f>
         <v/>
       </c>
       <c r="G30" s="8">
@@ -53624,11 +53616,11 @@
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>Plan!I10</f>
+        <f>Plan!I47</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>Plan!O10</f>
+        <f>Plan!O47</f>
         <v/>
       </c>
     </row>
@@ -53638,22 +53630,22 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C31" s="35">
-        <f>Plan!C74</f>
+        <f>Plan!C16</f>
         <v/>
       </c>
       <c r="D31" s="8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E31" s="16">
-        <f>Plan!J74</f>
+        <f>Plan!J16</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>Plan!K74</f>
+        <f>Plan!K16</f>
         <v/>
       </c>
       <c r="G31" s="8">
@@ -53661,11 +53653,11 @@
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>Plan!I74</f>
+        <f>Plan!I16</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>Plan!O74</f>
+        <f>Plan!O16</f>
         <v/>
       </c>
     </row>
@@ -53675,22 +53667,22 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="C32" s="35">
-        <f>Plan!C75</f>
+        <f>Plan!C10</f>
         <v/>
       </c>
       <c r="D32" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32" s="16">
-        <f>Plan!J75</f>
+        <f>Plan!J10</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>Plan!K75</f>
+        <f>Plan!K10</f>
         <v/>
       </c>
       <c r="G32" s="8">
@@ -53698,11 +53690,11 @@
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>Plan!I75</f>
+        <f>Plan!I10</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>Plan!O75</f>
+        <f>Plan!O10</f>
         <v/>
       </c>
     </row>
@@ -53712,22 +53704,22 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="C33" s="35">
-        <f>Plan!C20</f>
+        <f>Plan!C75</f>
         <v/>
       </c>
       <c r="D33" s="8" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E33" s="16">
-        <f>Plan!J20</f>
+        <f>Plan!J75</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>Plan!K20</f>
+        <f>Plan!K75</f>
         <v/>
       </c>
       <c r="G33" s="8">
@@ -53735,11 +53727,11 @@
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>Plan!I20</f>
+        <f>Plan!I75</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>Plan!O20</f>
+        <f>Plan!O75</f>
         <v/>
       </c>
     </row>
@@ -53897,22 +53889,22 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="C38" s="35">
-        <f>Plan!C38</f>
+        <f>Plan!C32</f>
         <v/>
       </c>
       <c r="D38" s="8" t="n">
         <v>16</v>
       </c>
       <c r="E38" s="16">
-        <f>Plan!J38</f>
+        <f>Plan!J32</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>Plan!K38</f>
+        <f>Plan!K32</f>
         <v/>
       </c>
       <c r="G38" s="8">
@@ -53920,11 +53912,11 @@
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>Plan!I38</f>
+        <f>Plan!I32</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>Plan!O38</f>
+        <f>Plan!O32</f>
         <v/>
       </c>
     </row>
@@ -53971,22 +53963,22 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="C40" s="35">
-        <f>Plan!C78</f>
+        <f>Plan!C33</f>
         <v/>
       </c>
       <c r="D40" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E40" s="16">
-        <f>Plan!J78</f>
+        <f>Plan!J33</f>
         <v/>
       </c>
       <c r="F40" s="16">
-        <f>Plan!K78</f>
+        <f>Plan!K33</f>
         <v/>
       </c>
       <c r="G40" s="8">
@@ -53994,11 +53986,11 @@
         <v/>
       </c>
       <c r="H40" s="16">
-        <f>Plan!I78</f>
+        <f>Plan!I33</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>Plan!O78</f>
+        <f>Plan!O33</f>
         <v/>
       </c>
     </row>
@@ -54008,22 +54000,22 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C41" s="35">
-        <f>Plan!C30</f>
+        <f>Plan!C38</f>
         <v/>
       </c>
       <c r="D41" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E41" s="16">
-        <f>Plan!J30</f>
+        <f>Plan!J38</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>Plan!K30</f>
+        <f>Plan!K38</f>
         <v/>
       </c>
       <c r="G41" s="8">
@@ -54031,11 +54023,11 @@
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>Plan!I30</f>
+        <f>Plan!I38</f>
         <v/>
       </c>
       <c r="I41" s="16">
-        <f>Plan!O30</f>
+        <f>Plan!O38</f>
         <v/>
       </c>
     </row>
@@ -54045,22 +54037,22 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C42" s="35">
-        <f>Plan!C32</f>
+        <f>Plan!C41</f>
         <v/>
       </c>
       <c r="D42" s="8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E42" s="16">
-        <f>Plan!J32</f>
+        <f>Plan!J41</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>Plan!K32</f>
+        <f>Plan!K41</f>
         <v/>
       </c>
       <c r="G42" s="8">
@@ -54068,11 +54060,11 @@
         <v/>
       </c>
       <c r="H42" s="16">
-        <f>Plan!I32</f>
+        <f>Plan!I41</f>
         <v/>
       </c>
       <c r="I42" s="16">
-        <f>Plan!O32</f>
+        <f>Plan!O41</f>
         <v/>
       </c>
     </row>
@@ -54082,22 +54074,22 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C43" s="35">
-        <f>Plan!C49</f>
+        <f>Plan!C30</f>
         <v/>
       </c>
       <c r="D43" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E43" s="16">
-        <f>Plan!J49</f>
+        <f>Plan!J30</f>
         <v/>
       </c>
       <c r="F43" s="16">
-        <f>Plan!K49</f>
+        <f>Plan!K30</f>
         <v/>
       </c>
       <c r="G43" s="8">
@@ -54105,11 +54097,11 @@
         <v/>
       </c>
       <c r="H43" s="16">
-        <f>Plan!I49</f>
+        <f>Plan!I30</f>
         <v/>
       </c>
       <c r="I43" s="16">
-        <f>Plan!O49</f>
+        <f>Plan!O30</f>
         <v/>
       </c>
     </row>
@@ -54119,22 +54111,22 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C44" s="35">
-        <f>Plan!C33</f>
+        <f>Plan!C49</f>
         <v/>
       </c>
       <c r="D44" s="8" t="n">
         <v>13</v>
       </c>
       <c r="E44" s="16">
-        <f>Plan!J33</f>
+        <f>Plan!J49</f>
         <v/>
       </c>
       <c r="F44" s="16">
-        <f>Plan!K33</f>
+        <f>Plan!K49</f>
         <v/>
       </c>
       <c r="G44" s="8">
@@ -54142,11 +54134,11 @@
         <v/>
       </c>
       <c r="H44" s="16">
-        <f>Plan!I33</f>
+        <f>Plan!I49</f>
         <v/>
       </c>
       <c r="I44" s="16">
-        <f>Plan!O33</f>
+        <f>Plan!O49</f>
         <v/>
       </c>
     </row>
@@ -54156,22 +54148,22 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C45" s="35">
-        <f>Plan!C22</f>
+        <f>Plan!C39</f>
         <v/>
       </c>
       <c r="D45" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" s="16">
-        <f>Plan!J22</f>
+        <f>Plan!J39</f>
         <v/>
       </c>
       <c r="F45" s="16">
-        <f>Plan!K22</f>
+        <f>Plan!K39</f>
         <v/>
       </c>
       <c r="G45" s="8">
@@ -54179,11 +54171,11 @@
         <v/>
       </c>
       <c r="H45" s="16">
-        <f>Plan!I22</f>
+        <f>Plan!I39</f>
         <v/>
       </c>
       <c r="I45" s="16">
-        <f>Plan!O22</f>
+        <f>Plan!O39</f>
         <v/>
       </c>
     </row>
@@ -54193,22 +54185,22 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="C46" s="35">
-        <f>Plan!C41</f>
+        <f>Plan!C34</f>
         <v/>
       </c>
       <c r="D46" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E46" s="16">
-        <f>Plan!J41</f>
+        <f>Plan!J34</f>
         <v/>
       </c>
       <c r="F46" s="16">
-        <f>Plan!K41</f>
+        <f>Plan!K34</f>
         <v/>
       </c>
       <c r="G46" s="8">
@@ -54216,11 +54208,11 @@
         <v/>
       </c>
       <c r="H46" s="16">
-        <f>Plan!I41</f>
+        <f>Plan!I34</f>
         <v/>
       </c>
       <c r="I46" s="16">
-        <f>Plan!O41</f>
+        <f>Plan!O34</f>
         <v/>
       </c>
     </row>
@@ -54230,22 +54222,22 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="C47" s="35">
-        <f>Plan!C39</f>
+        <f>Plan!C24</f>
         <v/>
       </c>
       <c r="D47" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" s="16">
-        <f>Plan!J39</f>
+        <f>Plan!J24</f>
         <v/>
       </c>
       <c r="F47" s="16">
-        <f>Plan!K39</f>
+        <f>Plan!K24</f>
         <v/>
       </c>
       <c r="G47" s="8">
@@ -54253,11 +54245,11 @@
         <v/>
       </c>
       <c r="H47" s="16">
-        <f>Plan!I39</f>
+        <f>Plan!I24</f>
         <v/>
       </c>
       <c r="I47" s="16">
-        <f>Plan!O39</f>
+        <f>Plan!O24</f>
         <v/>
       </c>
     </row>
@@ -54267,22 +54259,22 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C48" s="35">
-        <f>Plan!C34</f>
+        <f>Plan!C22</f>
         <v/>
       </c>
       <c r="D48" s="8" t="n">
         <v>12</v>
       </c>
       <c r="E48" s="16">
-        <f>Plan!J34</f>
+        <f>Plan!J22</f>
         <v/>
       </c>
       <c r="F48" s="16">
-        <f>Plan!K34</f>
+        <f>Plan!K22</f>
         <v/>
       </c>
       <c r="G48" s="8">
@@ -54290,11 +54282,11 @@
         <v/>
       </c>
       <c r="H48" s="16">
-        <f>Plan!I34</f>
+        <f>Plan!I22</f>
         <v/>
       </c>
       <c r="I48" s="16">
-        <f>Plan!O34</f>
+        <f>Plan!O22</f>
         <v/>
       </c>
     </row>
@@ -54304,22 +54296,22 @@
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C49" s="35">
-        <f>Plan!C23</f>
+        <f>Plan!C35</f>
         <v/>
       </c>
       <c r="D49" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E49" s="16">
-        <f>Plan!J23</f>
+        <f>Plan!J35</f>
         <v/>
       </c>
       <c r="F49" s="16">
-        <f>Plan!K23</f>
+        <f>Plan!K35</f>
         <v/>
       </c>
       <c r="G49" s="8">
@@ -54327,11 +54319,11 @@
         <v/>
       </c>
       <c r="H49" s="16">
-        <f>Plan!I23</f>
+        <f>Plan!I35</f>
         <v/>
       </c>
       <c r="I49" s="16">
-        <f>Plan!O23</f>
+        <f>Plan!O35</f>
         <v/>
       </c>
     </row>
@@ -54341,22 +54333,22 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="C50" s="35">
-        <f>Plan!C68</f>
+        <f>Plan!C78</f>
         <v/>
       </c>
       <c r="D50" s="8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E50" s="16">
-        <f>Plan!J68</f>
+        <f>Plan!J78</f>
         <v/>
       </c>
       <c r="F50" s="16">
-        <f>Plan!K68</f>
+        <f>Plan!K78</f>
         <v/>
       </c>
       <c r="G50" s="8">
@@ -54364,11 +54356,11 @@
         <v/>
       </c>
       <c r="H50" s="16">
-        <f>Plan!I68</f>
+        <f>Plan!I78</f>
         <v/>
       </c>
       <c r="I50" s="16">
-        <f>Plan!O68</f>
+        <f>Plan!O78</f>
         <v/>
       </c>
     </row>
@@ -54378,22 +54370,22 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C51" s="35">
-        <f>Plan!C66</f>
+        <f>Plan!C52</f>
         <v/>
       </c>
       <c r="D51" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E51" s="16">
-        <f>Plan!J66</f>
+        <f>Plan!J52</f>
         <v/>
       </c>
       <c r="F51" s="16">
-        <f>Plan!K66</f>
+        <f>Plan!K52</f>
         <v/>
       </c>
       <c r="G51" s="8">
@@ -54401,11 +54393,11 @@
         <v/>
       </c>
       <c r="H51" s="16">
-        <f>Plan!I66</f>
+        <f>Plan!I52</f>
         <v/>
       </c>
       <c r="I51" s="16">
-        <f>Plan!O66</f>
+        <f>Plan!O52</f>
         <v/>
       </c>
     </row>
@@ -54415,22 +54407,22 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="C52" s="35">
-        <f>Plan!C79</f>
+        <f>Plan!C53</f>
         <v/>
       </c>
       <c r="D52" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E52" s="16">
-        <f>Plan!J79</f>
+        <f>Plan!J53</f>
         <v/>
       </c>
       <c r="F52" s="16">
-        <f>Plan!K79</f>
+        <f>Plan!K53</f>
         <v/>
       </c>
       <c r="G52" s="8">
@@ -54438,11 +54430,11 @@
         <v/>
       </c>
       <c r="H52" s="16">
-        <f>Plan!I79</f>
+        <f>Plan!I53</f>
         <v/>
       </c>
       <c r="I52" s="16">
-        <f>Plan!O79</f>
+        <f>Plan!O53</f>
         <v/>
       </c>
     </row>
@@ -54452,22 +54444,22 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="C53" s="35">
-        <f>Plan!C24</f>
+        <f>Plan!C23</f>
         <v/>
       </c>
       <c r="D53" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E53" s="16">
-        <f>Plan!J24</f>
+        <f>Plan!J23</f>
         <v/>
       </c>
       <c r="F53" s="16">
-        <f>Plan!K24</f>
+        <f>Plan!K23</f>
         <v/>
       </c>
       <c r="G53" s="8">
@@ -54475,11 +54467,11 @@
         <v/>
       </c>
       <c r="H53" s="16">
-        <f>Plan!I24</f>
+        <f>Plan!I23</f>
         <v/>
       </c>
       <c r="I53" s="16">
-        <f>Plan!O24</f>
+        <f>Plan!O23</f>
         <v/>
       </c>
     </row>
@@ -54489,22 +54481,22 @@
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="C54" s="35">
-        <f>Plan!C35</f>
+        <f>Plan!C79</f>
         <v/>
       </c>
       <c r="D54" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E54" s="16">
-        <f>Plan!J35</f>
+        <f>Plan!J79</f>
         <v/>
       </c>
       <c r="F54" s="16">
-        <f>Plan!K35</f>
+        <f>Plan!K79</f>
         <v/>
       </c>
       <c r="G54" s="8">
@@ -54512,11 +54504,11 @@
         <v/>
       </c>
       <c r="H54" s="16">
-        <f>Plan!I35</f>
+        <f>Plan!I79</f>
         <v/>
       </c>
       <c r="I54" s="16">
-        <f>Plan!O35</f>
+        <f>Plan!O79</f>
         <v/>
       </c>
     </row>
@@ -54526,22 +54518,22 @@
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="C55" s="35">
-        <f>Plan!C52</f>
+        <f>Plan!C80</f>
         <v/>
       </c>
       <c r="D55" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55" s="16">
-        <f>Plan!J52</f>
+        <f>Plan!J80</f>
         <v/>
       </c>
       <c r="F55" s="16">
-        <f>Plan!K52</f>
+        <f>Plan!K80</f>
         <v/>
       </c>
       <c r="G55" s="8">
@@ -54549,11 +54541,11 @@
         <v/>
       </c>
       <c r="H55" s="16">
-        <f>Plan!I52</f>
+        <f>Plan!I80</f>
         <v/>
       </c>
       <c r="I55" s="16">
-        <f>Plan!O52</f>
+        <f>Plan!O80</f>
         <v/>
       </c>
     </row>
@@ -54563,22 +54555,22 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="C56" s="35">
-        <f>Plan!C53</f>
+        <f>Plan!C65</f>
         <v/>
       </c>
       <c r="D56" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E56" s="16">
-        <f>Plan!J53</f>
+        <f>Plan!J65</f>
         <v/>
       </c>
       <c r="F56" s="16">
-        <f>Plan!K53</f>
+        <f>Plan!K65</f>
         <v/>
       </c>
       <c r="G56" s="8">
@@ -54586,11 +54578,11 @@
         <v/>
       </c>
       <c r="H56" s="16">
-        <f>Plan!I53</f>
+        <f>Plan!I65</f>
         <v/>
       </c>
       <c r="I56" s="16">
-        <f>Plan!O53</f>
+        <f>Plan!O65</f>
         <v/>
       </c>
     </row>
@@ -54600,22 +54592,22 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C57" s="35">
-        <f>Plan!C80</f>
+        <f>Plan!C44</f>
         <v/>
       </c>
       <c r="D57" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E57" s="16">
-        <f>Plan!J80</f>
+        <f>Plan!J44</f>
         <v/>
       </c>
       <c r="F57" s="16">
-        <f>Plan!K80</f>
+        <f>Plan!K44</f>
         <v/>
       </c>
       <c r="G57" s="8">
@@ -54623,11 +54615,11 @@
         <v/>
       </c>
       <c r="H57" s="16">
-        <f>Plan!I80</f>
+        <f>Plan!I44</f>
         <v/>
       </c>
       <c r="I57" s="16">
-        <f>Plan!O80</f>
+        <f>Plan!O44</f>
         <v/>
       </c>
     </row>
@@ -54637,22 +54629,22 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="C58" s="35">
-        <f>Plan!C43</f>
+        <f>Plan!C68</f>
         <v/>
       </c>
       <c r="D58" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E58" s="16">
-        <f>Plan!J43</f>
+        <f>Plan!J68</f>
         <v/>
       </c>
       <c r="F58" s="16">
-        <f>Plan!K43</f>
+        <f>Plan!K68</f>
         <v/>
       </c>
       <c r="G58" s="8">
@@ -54660,11 +54652,11 @@
         <v/>
       </c>
       <c r="H58" s="16">
-        <f>Plan!I43</f>
+        <f>Plan!I68</f>
         <v/>
       </c>
       <c r="I58" s="16">
-        <f>Plan!O43</f>
+        <f>Plan!O68</f>
         <v/>
       </c>
     </row>
@@ -54674,22 +54666,22 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C59" s="35">
-        <f>Plan!C40</f>
+        <f>Plan!C43</f>
         <v/>
       </c>
       <c r="D59" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E59" s="16">
-        <f>Plan!J40</f>
+        <f>Plan!J43</f>
         <v/>
       </c>
       <c r="F59" s="16">
-        <f>Plan!K40</f>
+        <f>Plan!K43</f>
         <v/>
       </c>
       <c r="G59" s="8">
@@ -54697,11 +54689,11 @@
         <v/>
       </c>
       <c r="H59" s="16">
-        <f>Plan!I40</f>
+        <f>Plan!I43</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>Plan!O40</f>
+        <f>Plan!O43</f>
         <v/>
       </c>
     </row>
@@ -54711,22 +54703,22 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C60" s="35">
-        <f>Plan!C81</f>
+        <f>Plan!C66</f>
         <v/>
       </c>
       <c r="D60" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E60" s="16">
-        <f>Plan!J81</f>
+        <f>Plan!J66</f>
         <v/>
       </c>
       <c r="F60" s="16">
-        <f>Plan!K81</f>
+        <f>Plan!K66</f>
         <v/>
       </c>
       <c r="G60" s="8">
@@ -54734,11 +54726,11 @@
         <v/>
       </c>
       <c r="H60" s="16">
-        <f>Plan!I81</f>
+        <f>Plan!I66</f>
         <v/>
       </c>
       <c r="I60" s="16">
-        <f>Plan!O81</f>
+        <f>Plan!O66</f>
         <v/>
       </c>
     </row>
@@ -54748,22 +54740,22 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C61" s="35">
-        <f>Plan!C65</f>
+        <f>Plan!C40</f>
         <v/>
       </c>
       <c r="D61" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E61" s="16">
-        <f>Plan!J65</f>
+        <f>Plan!J40</f>
         <v/>
       </c>
       <c r="F61" s="16">
-        <f>Plan!K65</f>
+        <f>Plan!K40</f>
         <v/>
       </c>
       <c r="G61" s="8">
@@ -54771,11 +54763,11 @@
         <v/>
       </c>
       <c r="H61" s="16">
-        <f>Plan!I65</f>
+        <f>Plan!I40</f>
         <v/>
       </c>
       <c r="I61" s="16">
-        <f>Plan!O65</f>
+        <f>Plan!O40</f>
         <v/>
       </c>
     </row>
@@ -54785,22 +54777,22 @@
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C62" s="35">
-        <f>Plan!C29</f>
+        <f>Plan!C48</f>
         <v/>
       </c>
       <c r="D62" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E62" s="16">
-        <f>Plan!J29</f>
+        <f>Plan!J48</f>
         <v/>
       </c>
       <c r="F62" s="16">
-        <f>Plan!K29</f>
+        <f>Plan!K48</f>
         <v/>
       </c>
       <c r="G62" s="8">
@@ -54808,11 +54800,11 @@
         <v/>
       </c>
       <c r="H62" s="16">
-        <f>Plan!I29</f>
+        <f>Plan!I48</f>
         <v/>
       </c>
       <c r="I62" s="16">
-        <f>Plan!O29</f>
+        <f>Plan!O48</f>
         <v/>
       </c>
     </row>
@@ -54822,22 +54814,22 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="C63" s="35">
-        <f>Plan!C45</f>
+        <f>Plan!C83</f>
         <v/>
       </c>
       <c r="D63" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="16">
-        <f>Plan!J45</f>
+        <f>Plan!J83</f>
         <v/>
       </c>
       <c r="F63" s="16">
-        <f>Plan!K45</f>
+        <f>Plan!K83</f>
         <v/>
       </c>
       <c r="G63" s="8">
@@ -54845,11 +54837,11 @@
         <v/>
       </c>
       <c r="H63" s="16">
-        <f>Plan!I45</f>
+        <f>Plan!I83</f>
         <v/>
       </c>
       <c r="I63" s="16">
-        <f>Plan!O45</f>
+        <f>Plan!O83</f>
         <v/>
       </c>
     </row>
@@ -54859,22 +54851,22 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="C64" s="35">
-        <f>Plan!C48</f>
+        <f>Plan!C54</f>
         <v/>
       </c>
       <c r="D64" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E64" s="16">
-        <f>Plan!J48</f>
+        <f>Plan!J54</f>
         <v/>
       </c>
       <c r="F64" s="16">
-        <f>Plan!K48</f>
+        <f>Plan!K54</f>
         <v/>
       </c>
       <c r="G64" s="8">
@@ -54882,11 +54874,11 @@
         <v/>
       </c>
       <c r="H64" s="16">
-        <f>Plan!I48</f>
+        <f>Plan!I54</f>
         <v/>
       </c>
       <c r="I64" s="16">
-        <f>Plan!O48</f>
+        <f>Plan!O54</f>
         <v/>
       </c>
     </row>
@@ -54896,22 +54888,22 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="C65" s="35">
-        <f>Plan!C86</f>
+        <f>Plan!C25</f>
         <v/>
       </c>
       <c r="D65" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E65" s="16">
-        <f>Plan!J86</f>
+        <f>Plan!J25</f>
         <v/>
       </c>
       <c r="F65" s="16">
-        <f>Plan!K86</f>
+        <f>Plan!K25</f>
         <v/>
       </c>
       <c r="G65" s="8">
@@ -54919,11 +54911,11 @@
         <v/>
       </c>
       <c r="H65" s="16">
-        <f>Plan!I86</f>
+        <f>Plan!I25</f>
         <v/>
       </c>
       <c r="I65" s="16">
-        <f>Plan!O86</f>
+        <f>Plan!O25</f>
         <v/>
       </c>
     </row>
@@ -54933,22 +54925,22 @@
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="C66" s="35">
-        <f>Plan!C54</f>
+        <f>Plan!C86</f>
         <v/>
       </c>
       <c r="D66" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" s="16">
-        <f>Plan!J54</f>
+        <f>Plan!J86</f>
         <v/>
       </c>
       <c r="F66" s="16">
-        <f>Plan!K54</f>
+        <f>Plan!K86</f>
         <v/>
       </c>
       <c r="G66" s="8">
@@ -54956,11 +54948,11 @@
         <v/>
       </c>
       <c r="H66" s="16">
-        <f>Plan!I54</f>
+        <f>Plan!I86</f>
         <v/>
       </c>
       <c r="I66" s="16">
-        <f>Plan!O54</f>
+        <f>Plan!O86</f>
         <v/>
       </c>
     </row>
@@ -54970,22 +54962,22 @@
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="C67" s="35">
-        <f>Plan!C57</f>
+        <f>Plan!C82</f>
         <v/>
       </c>
       <c r="D67" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E67" s="16">
-        <f>Plan!J57</f>
+        <f>Plan!J82</f>
         <v/>
       </c>
       <c r="F67" s="16">
-        <f>Plan!K57</f>
+        <f>Plan!K82</f>
         <v/>
       </c>
       <c r="G67" s="8">
@@ -54993,11 +54985,11 @@
         <v/>
       </c>
       <c r="H67" s="16">
-        <f>Plan!I57</f>
+        <f>Plan!I82</f>
         <v/>
       </c>
       <c r="I67" s="16">
-        <f>Plan!O57</f>
+        <f>Plan!O82</f>
         <v/>
       </c>
     </row>
@@ -55007,22 +54999,22 @@
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="C68" s="35">
-        <f>Plan!C44</f>
+        <f>Plan!C55</f>
         <v/>
       </c>
       <c r="D68" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68" s="16">
-        <f>Plan!J44</f>
+        <f>Plan!J55</f>
         <v/>
       </c>
       <c r="F68" s="16">
-        <f>Plan!K44</f>
+        <f>Plan!K55</f>
         <v/>
       </c>
       <c r="G68" s="8">
@@ -55030,11 +55022,11 @@
         <v/>
       </c>
       <c r="H68" s="16">
-        <f>Plan!I44</f>
+        <f>Plan!I55</f>
         <v/>
       </c>
       <c r="I68" s="16">
-        <f>Plan!O44</f>
+        <f>Plan!O55</f>
         <v/>
       </c>
     </row>
@@ -55044,22 +55036,22 @@
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="C69" s="35">
-        <f>Plan!C55</f>
+        <f>Plan!C81</f>
         <v/>
       </c>
       <c r="D69" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E69" s="16">
-        <f>Plan!J55</f>
+        <f>Plan!J81</f>
         <v/>
       </c>
       <c r="F69" s="16">
-        <f>Plan!K55</f>
+        <f>Plan!K81</f>
         <v/>
       </c>
       <c r="G69" s="8">
@@ -55067,11 +55059,11 @@
         <v/>
       </c>
       <c r="H69" s="16">
-        <f>Plan!I55</f>
+        <f>Plan!I81</f>
         <v/>
       </c>
       <c r="I69" s="16">
-        <f>Plan!O55</f>
+        <f>Plan!O81</f>
         <v/>
       </c>
     </row>
@@ -55081,22 +55073,22 @@
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C70" s="35">
-        <f>Plan!C25</f>
+        <f>Plan!C29</f>
         <v/>
       </c>
       <c r="D70" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="16">
-        <f>Plan!J25</f>
+        <f>Plan!J29</f>
         <v/>
       </c>
       <c r="F70" s="16">
-        <f>Plan!K25</f>
+        <f>Plan!K29</f>
         <v/>
       </c>
       <c r="G70" s="8">
@@ -55104,11 +55096,11 @@
         <v/>
       </c>
       <c r="H70" s="16">
-        <f>Plan!I25</f>
+        <f>Plan!I29</f>
         <v/>
       </c>
       <c r="I70" s="16">
-        <f>Plan!O25</f>
+        <f>Plan!O29</f>
         <v/>
       </c>
     </row>
@@ -55118,22 +55110,22 @@
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C71" s="35">
-        <f>Plan!C83</f>
+        <f>Plan!C45</f>
         <v/>
       </c>
       <c r="D71" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" s="16">
-        <f>Plan!J83</f>
+        <f>Plan!J45</f>
         <v/>
       </c>
       <c r="F71" s="16">
-        <f>Plan!K83</f>
+        <f>Plan!K45</f>
         <v/>
       </c>
       <c r="G71" s="8">
@@ -55141,11 +55133,11 @@
         <v/>
       </c>
       <c r="H71" s="16">
-        <f>Plan!I83</f>
+        <f>Plan!I45</f>
         <v/>
       </c>
       <c r="I71" s="16">
-        <f>Plan!O83</f>
+        <f>Plan!O45</f>
         <v/>
       </c>
     </row>
@@ -55155,22 +55147,22 @@
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="C72" s="35">
-        <f>Plan!C50</f>
+        <f>Plan!C57</f>
         <v/>
       </c>
       <c r="D72" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E72" s="16">
-        <f>Plan!J50</f>
+        <f>Plan!J57</f>
         <v/>
       </c>
       <c r="F72" s="16">
-        <f>Plan!K50</f>
+        <f>Plan!K57</f>
         <v/>
       </c>
       <c r="G72" s="8">
@@ -55178,11 +55170,11 @@
         <v/>
       </c>
       <c r="H72" s="16">
-        <f>Plan!I50</f>
+        <f>Plan!I57</f>
         <v/>
       </c>
       <c r="I72" s="16">
-        <f>Plan!O50</f>
+        <f>Plan!O57</f>
         <v/>
       </c>
     </row>
@@ -55192,22 +55184,22 @@
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="C73" s="35">
-        <f>Plan!C51</f>
+        <f>Plan!C58</f>
         <v/>
       </c>
       <c r="D73" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E73" s="16">
-        <f>Plan!J51</f>
+        <f>Plan!J58</f>
         <v/>
       </c>
       <c r="F73" s="16">
-        <f>Plan!K51</f>
+        <f>Plan!K58</f>
         <v/>
       </c>
       <c r="G73" s="8">
@@ -55215,11 +55207,11 @@
         <v/>
       </c>
       <c r="H73" s="16">
-        <f>Plan!I51</f>
+        <f>Plan!I58</f>
         <v/>
       </c>
       <c r="I73" s="16">
-        <f>Plan!O51</f>
+        <f>Plan!O58</f>
         <v/>
       </c>
     </row>
@@ -55229,22 +55221,22 @@
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="C74" s="35">
-        <f>Plan!C59</f>
+        <f>Plan!C51</f>
         <v/>
       </c>
       <c r="D74" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E74" s="16">
-        <f>Plan!J59</f>
+        <f>Plan!J51</f>
         <v/>
       </c>
       <c r="F74" s="16">
-        <f>Plan!K59</f>
+        <f>Plan!K51</f>
         <v/>
       </c>
       <c r="G74" s="8">
@@ -55252,11 +55244,11 @@
         <v/>
       </c>
       <c r="H74" s="16">
-        <f>Plan!I59</f>
+        <f>Plan!I51</f>
         <v/>
       </c>
       <c r="I74" s="16">
-        <f>Plan!O59</f>
+        <f>Plan!O51</f>
         <v/>
       </c>
     </row>
@@ -55266,22 +55258,22 @@
       </c>
       <c r="B75" s="18" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="C75" s="35">
-        <f>Plan!C58</f>
+        <f>Plan!C59</f>
         <v/>
       </c>
       <c r="D75" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E75" s="16">
-        <f>Plan!J58</f>
+        <f>Plan!J59</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>Plan!K58</f>
+        <f>Plan!K59</f>
         <v/>
       </c>
       <c r="G75" s="8">
@@ -55289,11 +55281,11 @@
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>Plan!I58</f>
+        <f>Plan!I59</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>Plan!O58</f>
+        <f>Plan!O59</f>
         <v/>
       </c>
     </row>
@@ -55303,22 +55295,22 @@
       </c>
       <c r="B76" s="18" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C76" s="35">
-        <f>Plan!C69</f>
+        <f>Plan!C50</f>
         <v/>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E76" s="16">
-        <f>Plan!J69</f>
+        <f>Plan!J50</f>
         <v/>
       </c>
       <c r="F76" s="16">
-        <f>Plan!K69</f>
+        <f>Plan!K50</f>
         <v/>
       </c>
       <c r="G76" s="8">
@@ -55326,11 +55318,11 @@
         <v/>
       </c>
       <c r="H76" s="16">
-        <f>Plan!I69</f>
+        <f>Plan!I50</f>
         <v/>
       </c>
       <c r="I76" s="16">
-        <f>Plan!O69</f>
+        <f>Plan!O50</f>
         <v/>
       </c>
     </row>
@@ -55377,22 +55369,22 @@
       </c>
       <c r="B78" s="18" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="C78" s="35">
-        <f>Plan!C60</f>
+        <f>Plan!C69</f>
         <v/>
       </c>
       <c r="D78" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E78" s="16">
-        <f>Plan!J60</f>
+        <f>Plan!J69</f>
         <v/>
       </c>
       <c r="F78" s="16">
-        <f>Plan!K60</f>
+        <f>Plan!K69</f>
         <v/>
       </c>
       <c r="G78" s="8">
@@ -55400,11 +55392,11 @@
         <v/>
       </c>
       <c r="H78" s="16">
-        <f>Plan!I60</f>
+        <f>Plan!I69</f>
         <v/>
       </c>
       <c r="I78" s="16">
-        <f>Plan!O60</f>
+        <f>Plan!O69</f>
         <v/>
       </c>
     </row>
@@ -55414,22 +55406,22 @@
       </c>
       <c r="B79" s="18" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="C79" s="35">
-        <f>Plan!C84</f>
+        <f>Plan!C60</f>
         <v/>
       </c>
       <c r="D79" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E79" s="16">
-        <f>Plan!J84</f>
+        <f>Plan!J60</f>
         <v/>
       </c>
       <c r="F79" s="16">
-        <f>Plan!K84</f>
+        <f>Plan!K60</f>
         <v/>
       </c>
       <c r="G79" s="8">
@@ -55437,11 +55429,11 @@
         <v/>
       </c>
       <c r="H79" s="16">
-        <f>Plan!I84</f>
+        <f>Plan!I60</f>
         <v/>
       </c>
       <c r="I79" s="16">
-        <f>Plan!O84</f>
+        <f>Plan!O60</f>
         <v/>
       </c>
     </row>
@@ -55451,22 +55443,22 @@
       </c>
       <c r="B80" s="18" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="C80" s="35">
-        <f>Plan!C88</f>
+        <f>Plan!C72</f>
         <v/>
       </c>
       <c r="D80" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E80" s="16">
-        <f>Plan!J88</f>
+        <f>Plan!J72</f>
         <v/>
       </c>
       <c r="F80" s="16">
-        <f>Plan!K88</f>
+        <f>Plan!K72</f>
         <v/>
       </c>
       <c r="G80" s="8">
@@ -55474,11 +55466,11 @@
         <v/>
       </c>
       <c r="H80" s="16">
-        <f>Plan!I88</f>
+        <f>Plan!I72</f>
         <v/>
       </c>
       <c r="I80" s="16">
-        <f>Plan!O88</f>
+        <f>Plan!O72</f>
         <v/>
       </c>
     </row>
@@ -55488,22 +55480,22 @@
       </c>
       <c r="B81" s="18" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="C81" s="35">
-        <f>Plan!C62</f>
+        <f>Plan!C85</f>
         <v/>
       </c>
       <c r="D81" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E81" s="16">
-        <f>Plan!J62</f>
+        <f>Plan!J85</f>
         <v/>
       </c>
       <c r="F81" s="16">
-        <f>Plan!K62</f>
+        <f>Plan!K85</f>
         <v/>
       </c>
       <c r="G81" s="8">
@@ -55511,11 +55503,11 @@
         <v/>
       </c>
       <c r="H81" s="16">
-        <f>Plan!I62</f>
+        <f>Plan!I85</f>
         <v/>
       </c>
       <c r="I81" s="16">
-        <f>Plan!O62</f>
+        <f>Plan!O85</f>
         <v/>
       </c>
     </row>
@@ -55525,22 +55517,22 @@
       </c>
       <c r="B82" s="18" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="C82" s="35">
-        <f>Plan!C63</f>
+        <f>Plan!C87</f>
         <v/>
       </c>
       <c r="D82" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" s="16">
-        <f>Plan!J63</f>
+        <f>Plan!J87</f>
         <v/>
       </c>
       <c r="F82" s="16">
-        <f>Plan!K63</f>
+        <f>Plan!K87</f>
         <v/>
       </c>
       <c r="G82" s="8">
@@ -55548,11 +55540,11 @@
         <v/>
       </c>
       <c r="H82" s="16">
-        <f>Plan!I63</f>
+        <f>Plan!I87</f>
         <v/>
       </c>
       <c r="I82" s="16">
-        <f>Plan!O63</f>
+        <f>Plan!O87</f>
         <v/>
       </c>
     </row>
@@ -55562,22 +55554,22 @@
       </c>
       <c r="B83" s="18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="C83" s="35">
-        <f>Plan!C64</f>
+        <f>Plan!C62</f>
         <v/>
       </c>
       <c r="D83" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E83" s="16">
-        <f>Plan!J64</f>
+        <f>Plan!J62</f>
         <v/>
       </c>
       <c r="F83" s="16">
-        <f>Plan!K64</f>
+        <f>Plan!K62</f>
         <v/>
       </c>
       <c r="G83" s="8">
@@ -55585,11 +55577,11 @@
         <v/>
       </c>
       <c r="H83" s="16">
-        <f>Plan!I64</f>
+        <f>Plan!I62</f>
         <v/>
       </c>
       <c r="I83" s="16">
-        <f>Plan!O64</f>
+        <f>Plan!O62</f>
         <v/>
       </c>
     </row>
@@ -55599,22 +55591,22 @@
       </c>
       <c r="B84" s="18" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="C84" s="35">
-        <f>Plan!C85</f>
+        <f>Plan!C63</f>
         <v/>
       </c>
       <c r="D84" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" s="16">
-        <f>Plan!J85</f>
+        <f>Plan!J63</f>
         <v/>
       </c>
       <c r="F84" s="16">
-        <f>Plan!K85</f>
+        <f>Plan!K63</f>
         <v/>
       </c>
       <c r="G84" s="8">
@@ -55622,11 +55614,11 @@
         <v/>
       </c>
       <c r="H84" s="16">
-        <f>Plan!I85</f>
+        <f>Plan!I63</f>
         <v/>
       </c>
       <c r="I84" s="16">
-        <f>Plan!O85</f>
+        <f>Plan!O63</f>
         <v/>
       </c>
     </row>
@@ -55636,22 +55628,22 @@
       </c>
       <c r="B85" s="18" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="C85" s="35">
-        <f>Plan!C87</f>
+        <f>Plan!C88</f>
         <v/>
       </c>
       <c r="D85" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E85" s="16">
-        <f>Plan!J87</f>
+        <f>Plan!J88</f>
         <v/>
       </c>
       <c r="F85" s="16">
-        <f>Plan!K87</f>
+        <f>Plan!K88</f>
         <v/>
       </c>
       <c r="G85" s="8">
@@ -55659,11 +55651,11 @@
         <v/>
       </c>
       <c r="H85" s="16">
-        <f>Plan!I87</f>
+        <f>Plan!I88</f>
         <v/>
       </c>
       <c r="I85" s="16">
-        <f>Plan!O87</f>
+        <f>Plan!O88</f>
         <v/>
       </c>
     </row>
@@ -55673,22 +55665,22 @@
       </c>
       <c r="B86" s="18" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="C86" s="35">
-        <f>Plan!C56</f>
+        <f>Plan!C64</f>
         <v/>
       </c>
       <c r="D86" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" s="16">
-        <f>Plan!J56</f>
+        <f>Plan!J64</f>
         <v/>
       </c>
       <c r="F86" s="16">
-        <f>Plan!K56</f>
+        <f>Plan!K64</f>
         <v/>
       </c>
       <c r="G86" s="8">
@@ -55696,11 +55688,11 @@
         <v/>
       </c>
       <c r="H86" s="16">
-        <f>Plan!I56</f>
+        <f>Plan!I64</f>
         <v/>
       </c>
       <c r="I86" s="16">
-        <f>Plan!O56</f>
+        <f>Plan!O64</f>
         <v/>
       </c>
     </row>
@@ -55710,22 +55702,22 @@
       </c>
       <c r="B87" s="18" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="C87" s="35">
-        <f>Plan!C72</f>
+        <f>Plan!C56</f>
         <v/>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" s="16">
-        <f>Plan!J72</f>
+        <f>Plan!J56</f>
         <v/>
       </c>
       <c r="F87" s="16">
-        <f>Plan!K72</f>
+        <f>Plan!K56</f>
         <v/>
       </c>
       <c r="G87" s="8">
@@ -55733,11 +55725,11 @@
         <v/>
       </c>
       <c r="H87" s="16">
-        <f>Plan!I72</f>
+        <f>Plan!I56</f>
         <v/>
       </c>
       <c r="I87" s="16">
-        <f>Plan!O72</f>
+        <f>Plan!O56</f>
         <v/>
       </c>
     </row>
@@ -55747,22 +55739,22 @@
       </c>
       <c r="B88" s="18" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="C88" s="35">
-        <f>Plan!C82</f>
+        <f>Plan!C84</f>
         <v/>
       </c>
       <c r="D88" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E88" s="16">
-        <f>Plan!J82</f>
+        <f>Plan!J84</f>
         <v/>
       </c>
       <c r="F88" s="16">
-        <f>Plan!K82</f>
+        <f>Plan!K84</f>
         <v/>
       </c>
       <c r="G88" s="8">
@@ -55770,11 +55762,11 @@
         <v/>
       </c>
       <c r="H88" s="16">
-        <f>Plan!I82</f>
+        <f>Plan!I84</f>
         <v/>
       </c>
       <c r="I88" s="16">
-        <f>Plan!O82</f>
+        <f>Plan!O84</f>
         <v/>
       </c>
     </row>
@@ -56472,7 +56464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -56531,22 +56523,22 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>4.15, 4.7, 4.8</t>
+          <t>6.23, 6.24</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>4.7, 4.8 y 4.15 Hecho</t>
+          <t>QA-06 corregido y develop subido</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Ícono WhatsApp en el pie, botón «Habilitar nuevo crédito», selector segmentado en la demo, 8 estados y KPI Desembolsos del mes en admin, chips en asesor. e2e sin ejecutar.</t>
+          <t>Aviso de cuenta inactiva en app/ingresar/actions.ts; y-tanda2 escritorio 14/14; commit 7526e7d en develop. Pendiente de Sebas: db push --linked de 20261001000000 y 20261001100000 y fusionar develop→main.</t>
         </is>
       </c>
     </row>
@@ -56558,22 +56550,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>4.15, 4.7, 4.8</t>
+          <t>6.21, 6.15</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Pedidos §13 en servidor y front</t>
+          <t>6.21 Hecho; 6.15 desbloqueada (En curso)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Correos con respaldo en texto plano y log correo_plantilla_faltante; acción Habilitar crédito; /cuenta con tarjeta vacía; loaders con por_estado_proceso y desembolsos_mes; demo Policía/Ejército; wa.me en el pie. 552 vitest y build en verde.</t>
+          <t>E2E ajustadas a v3/S-06/crédito: escritorio 171/4, celular 143/3, fallas corregidas y confirmadas. Bug QA-06 reportado.</t>
         </is>
       </c>
     </row>
@@ -56585,22 +56577,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>4.15, 4.7, 4.8, P-112, 6.24, P-113</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Migración 20261001100000 y pgTAP 21</t>
+          <t>QA-01 a QA-05 de /afiliacion corregidos</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>admin_habilitar_credito, mi_habilitacion_credito, por_estado_proceso y desembolsos_mes; listas blancas 00/15 (P-112 Hecho). Diagnóstico: el bloqueo tras rechazo es de pantalla, no de base. Sin db reset por Docker: nueva 6.24/P-113 (Sebas).</t>
+          <t>Texto restaurado, contador, formulario con key (conserva selects, cierra F-01), aviso de fotos rechazadas, tabIndex de SelectBusqueda.</t>
         </is>
       </c>
     </row>
@@ -56612,29 +56604,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>6.15, 6.21</t>
+          <t>6.24, P-113</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>E2E al día pero sin ejecutar: Bloqueado</t>
+          <t>pgTAP 20261001* en verde</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>y-tanda2.spec.ts y ajustes de e2e (370 pruebas listadas, tsc y eslint en verde). Docker se cayó: Sebas reinicia Docker, db reset y corre Playwright.</t>
+          <t>Arreglado admin_habilitar_credito (array_append) y pruebas 21 y 10; 22 archivos, 497 pruebas. Falta aplicar en remoto.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -56644,125 +56636,125 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>4.7, 4.8, 5.6</t>
+          <t>4.7, 4.8, 4.15</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Pantallas Resumen y /cuenta/solicitar en código</t>
+          <t>Verificación visual tanda §13</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>4.7 y 4.8 En curso: falta estado_proceso y desembolsos del mes en las RPC y decisión P-111. tsc, lint, vitest y build en verde.</t>
+          <t>CuentaDemo, WhatsApp en el pie, paneles por estado y desembolsos, HabilitarCredito; tsc, lint, vitest 552 y build en verde.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>2.11, 4.3, 4.7, 4.8</t>
+          <t>4.15, 4.7, 4.8</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>F-01 corregido, revalidación de /cuenta y loaders de métricas</t>
+          <t>4.7, 4.8 y 4.15 Hecho</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>2.11 y 4.3 Hecho. Afiliación guarda version_politica_datos; loaders cargarMetricasAdmin/Asesor con 8 pruebas (523 vitest en verde).</t>
+          <t>Ícono WhatsApp en el pie, botón «Habilitar nuevo crédito», selector segmentado en la demo, 8 estados y KPI Desembolsos del mes en admin, chips en asesor. e2e sin ejecutar.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>P-55, 4.7, 4.8, 6.23</t>
+          <t>4.15, 4.7, 4.8</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Migración 20261001000000 y pgTAP 20</t>
+          <t>Pedidos §13 en servidor y front</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>version_politica_datos sellada, revoke de limites_intentos_id_seq, RPC de métricas solo con conteos; 16 pruebas en verde. Sin aplicar: nueva 6.23/P-110. Listas blancas pgTAP: P-112.</t>
+          <t>Correos con respaldo en texto plano y log correo_plantilla_faltante; acción Habilitar crédito; /cuenta con tarjeta vacía; loaders con por_estado_proceso y desembolsos_mes; demo Policía/Ejército; wa.me en el pie. 552 vitest y build en verde.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>4.7, 4.8, 5.6</t>
+          <t>4.15, 4.7, 4.8, P-112, 6.24, P-113</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Lienzo 3r, 3s, 3t</t>
+          <t>Migración 20261001100000 y pgTAP 21</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Dashboards admin y asesor y /cuenta/solicitar maquetados en el lienzo (D-22 a D-24). 5.6 Hecho.</t>
+          <t>admin_habilitar_credito, mi_habilitacion_credito, por_estado_proceso y desembolsos_mes; listas blancas 00/15 (P-112 Hecho). Diagnóstico: el bloqueo tras rechazo es de pantalla, no de base. Sin db reset por Docker: nueva 6.24/P-113 (Sebas).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>P-81 (política v1.0)</t>
+          <t>6.15, 6.21</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Política de datos v1.0 publicada en código</t>
+          <t>E2E al día pero sin ejecutar: Bloqueado</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>/politica-de-datos con 28 secciones, anexo, índice, aviso de revisión jurídica en 7.3, 8 y 18 y botón PDF. Por definir: horario, órgano y acta de aprobación.</t>
+          <t>y-tanda2.spec.ts y ajustes de e2e (370 pruebas listadas, tsc y eslint en verde). Docker se cayó: Sebas reinicia Docker, db reset y corre Playwright.</t>
         </is>
       </c>
     </row>
@@ -56774,22 +56766,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>sesión principal (Sebas)</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>6.22; P-20, P-21, P-43, P-45, P-105</t>
+          <t>4.7, 4.8, 5.6</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Tanda 2 en producción y pendientes de configuración cerrados</t>
+          <t>Pantallas Resumen y /cuenta/solicitar en código</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Sebas aplicó las 7 migraciones 20260930200* y fusionó develop→main. Hechos: P-20 (plantilla del código), P-43 (límite de intentos), P-45 (ajustes OTP), P-105 (CRON_SECRET y plantilla del aviso institucional). P-21 cancelado: el límite de Resend no preocupa por ahora. P-54 y P-73 siguen pendientes.</t>
+          <t>4.7 y 4.8 En curso: falta estado_proceso y desembolsos del mes en las RPC y decisión P-111. tsc, lint, vitest y build en verde.</t>
         </is>
       </c>
     </row>
@@ -56801,22 +56793,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>sesión principal (Sebas)</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>5.4, 6.21, 6.22; P-81</t>
+          <t>2.11, 4.3, 4.7, 4.8</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Política v1 en publicación; tanda 2 en develop</t>
+          <t>F-01 corregido, revalidación de /cuenta y loaders de métricas</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Tanda 2 en develop e4b8350 con 7 migraciones 20260930200* por aplicar y develop a main pendiente (6.22). Política v1 del Dr. Breinner con 7.3, 8 y 18 en revisión. E2E desactualizadas (6.21). Copia de seguridad de producción del 30-sep.</t>
+          <t>2.11 y 4.3 Hecho. Afiliación guarda version_politica_datos; loaders cargarMetricasAdmin/Asesor con 8 pruebas (523 vitest en verde).</t>
         </is>
       </c>
     </row>
@@ -56828,22 +56820,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>P-55, 4.7, 4.8, 6.23</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Medios en el detalle de convenios</t>
+          <t>Migración 20261001000000 y pgTAP 20</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Videos y PDF de Racing Tours mapeados por NIT en lib/convenios.ts; develop 4357939 (video de Locos en politica-datos-v1).</t>
+          <t>version_politica_datos sellada, revoke de limites_intentos_id_seq, RPC de métricas solo con conteos; 16 pruebas en verde. Sin aplicar: nueva 6.23/P-110. Listas blancas pgTAP: P-112.</t>
         </is>
       </c>
     </row>
@@ -56855,22 +56847,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>4.14, 6.22</t>
+          <t>4.7, 4.8, 5.6</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>SP remapeado a IJ (§12.14)</t>
+          <t>Lienzo 3r, 3s, 3t</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>En la migración 20260930200100 (sin aplicar); R-10/R-11 decididos; pgTAP, db reset y vitest en verde.</t>
+          <t>Dashboards admin y asesor y /cuenta/solicitar maquetados en el lienzo (D-22 a D-24). 5.6 Hecho.</t>
         </is>
       </c>
     </row>
@@ -56880,24 +56872,24 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>ga-disenador-lienzo + ga-auditor-supabase + ga-funcionalidad-botones + ga-diseno-a-codigo</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>4.14, 6.21, 6.22, 5.11, 5.12</t>
+          <t>P-81 (política v1.0)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Tanda 2 (§12) hecha en local</t>
+          <t>Política de datos v1.0 publicada en código</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Lienzo 3q, migraciones 20260930200000–200600 (pgTAP 464/464), acciones y UI (vitest 516, build en verde). Sin aplicar en producción. Backlog §12.12 agregado.</t>
+          <t>/politica-de-datos con 28 secciones, anexo, índice, aviso de revisión jurídica en 7.3, 8 y 18 y botón PDF. Por definir: horario, órgano y acta de aprobación.</t>
         </is>
       </c>
     </row>
@@ -56909,22 +56901,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ga-enlace-cooperativa</t>
+          <t>sesión principal (Sebas)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>P-14, P-47, P-76..P-80, P-90..P-93, P-97; P-106</t>
+          <t>6.22; P-20, P-21, P-43, P-45, P-105</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Respuestas de la cooperativa</t>
+          <t>Tanda 2 en producción y pendientes de configuración cerrados</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>docs/cooperativa/preguntas.md. R-10 y R-11 cerrados por Sebas (§12.14, SP a IJ); abierta R-09.</t>
+          <t>Sebas aplicó las 7 migraciones 20260930200* y fusionó develop→main. Hechos: P-20 (plantilla del código), P-43 (límite de intentos), P-45 (ajustes OTP), P-105 (CRON_SECRET y plantilla del aviso institucional). P-21 cancelado: el límite de Resend no preocupa por ahora. P-54 y P-73 siguen pendientes.</t>
         </is>
       </c>
     </row>
@@ -56941,17 +56933,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>1.8, 6.20, 5.10, 4.7, 4.8, 5.9, 6.14, 6.15; P-104, P-46, P-75, P-69, P-72, P-73</t>
+          <t>5.4, 6.21, 6.22; P-81</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>C+ y tanda 1 de Ricardo en producción; Carlos sale</t>
+          <t>Política v1 en publicación; tanda 2 en develop</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>PR develop a main de C+ fusionado; PR #5 fusionado y 19 migraciones aplicadas. Asesores Miguel Rueda, Rafael González y Nany Barón creados. Vercel Pro (cron cada hora). Carlos Pardo no sigue: se le pagan 150.000 COP; sus tareas pasan a agentes/Sebas (5.10 ya hecha).</t>
+          <t>Tanda 2 en develop e4b8350 con 7 migraciones 20260930200* por aplicar y develop a main pendiente (6.22). Política v1 del Dr. Breinner con 7.3, 8 y 18 en revisión. E2E desactualizadas (6.21). Copia de seguridad de producción del 30-sep.</t>
         </is>
       </c>
     </row>
@@ -56963,22 +56955,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ga-correos</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>4.13; P-105</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Plantilla ga-aviso-institucional</t>
+          <t>Medios en el detalle de convenios</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>docs/resend/aviso-institucional.*; falta publicarla y crear la variable en Vercel.</t>
+          <t>Videos y PDF de Racing Tours mapeados por NIT en lib/convenios.ts; develop 4357939 (video de Locos en politica-datos-v1).</t>
         </is>
       </c>
     </row>
@@ -56990,22 +56982,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>6.2, 4.13</t>
+          <t>4.14, 6.22</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Dos pasadas de seguridad</t>
+          <t>SP remapeado a IJ (§12.14)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>RS-01 a RS-22 sobre migraciones y pantallas de Ricardo. 6.2 sigue En curso (depende de 4.3).</t>
+          <t>En la migración 20260930200100 (sin aplicar); R-10/R-11 decididos; pgTAP, db reset y vitest en verde.</t>
         </is>
       </c>
     </row>
@@ -57015,24 +57007,24 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>ga-diseno-a-codigo</t>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>ga-disenador-lienzo + ga-auditor-supabase + ga-funcionalidad-botones + ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.14, 6.21, 6.22, 5.11, 5.12</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>UI 3j–3p</t>
+          <t>Tanda 2 (§12) hecha en local</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Pantallas y revisión de diseño A1–A3.</t>
+          <t>Lienzo 3q, migraciones 20260930200000–200600 (pgTAP 464/464), acciones y UI (vitest 516, build en verde). Sin aplicar en producción. Backlog §12.12 agregado.</t>
         </is>
       </c>
     </row>
@@ -57044,22 +57036,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-enlace-cooperativa</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>P-14, P-47, P-76..P-80, P-90..P-93, P-97; P-106</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Lógica y datos de 3j–3p y correcciones de seguridad</t>
+          <t>Respuestas de la cooperativa</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>RS-01..RS-22 de código, limpieza de fotos por RPC (5.10), aviso institucional siempre. vitest 503, build en verde.</t>
+          <t>docs/cooperativa/preguntas.md. R-10 y R-11 cerrados por Sebas (§12.14, SP a IJ); abierta R-09.</t>
         </is>
       </c>
     </row>
@@ -57071,22 +57063,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>sesión principal (Sebas)</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>1.8, 6.20, 5.10, 4.7, 4.8, 5.9, 6.14, 6.15; P-104, P-46, P-75, P-69, P-72, P-73</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Lienzo 3j–3p</t>
+          <t>C+ y tanda 1 de Ricardo en producción; Carlos sale</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Piezas 3j–3n, 3o/3p (D-15, D-16) y revisión de fidelidad.</t>
+          <t>PR develop a main de C+ fusionado; PR #5 fusionado y 19 migraciones aplicadas. Asesores Miguel Rueda, Rafael González y Nany Barón creados. Vercel Pro (cron cada hora). Carlos Pardo no sigue: se le pagan 150.000 COP; sus tareas pasan a agentes/Sebas (5.10 ya hecha).</t>
         </is>
       </c>
     </row>
@@ -57098,238 +57090,238 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-correos</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>4.12; P-46</t>
+          <t>4.13; P-105</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Migraciones tanda 1 de Ricardo (29/30-sep)</t>
+          <t>Plantilla ga-aviso-institucional</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>20260929100000..100700, 20260930100000..100500: grados, nómina, proceso ejecutivo, alertas, comisiones con pagos editables, tasa oculta (P-100), crédito solo en «operando», segunda pasada RS-17/18/20/21. pgTAP en verde.</t>
+          <t>docs/resend/aviso-institucional.*; falta publicarla y crear la variable en Vercel.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-69, P-72</t>
+          <t>6.2, 4.13</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Primera entrega de Carlos Pardo revisada: NO fusionable</t>
+          <t>Dos pasadas de seguridad</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Revisión del ZIP del repo privado de Carlos (base main anterior al rediseño C+, no rediseno-c-plus). Motivos: reintroduce la fuga F2-03 y pierde el revoke en resumen_clientes_asesor; el motivo de rechazo de afiliación usa una columna inexistente sin migración (rechazar dejaría de funcionar); convenios administrables usa columnas y un bucket de Storage inexistentes y acciones sin exigirAdmin ni validación; la purga Ley 1581 usa columnas/bucket equivocados y el cron queda abierto si falta CRON_SECRET; claves en .env.example, console.log y configuración de túnel; borra /asesor/demo (ya en producción) y renombra /cuenta/solicitar (ya en producción); sin pruebas. Se le envió a Carlos la lista de correcciones para rehacer el encargo sobre rediseno-c-plus, con un PR por tarea. 4.7, 4.8, 5.9, 5.10, 6.14 y 6.15 siguen Pendiente; P-69 con el mismo detalle y P-72 (acceso de colaborador en GitHub) sigue En curso, con la nota de que el ZIP en vez de un PR sugiere que ese acceso todavía no está confirmado.</t>
+          <t>RS-01 a RS-22 sobre migraciones y pantallas de Ricardo. 6.2 sigue En curso (depende de 4.3).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>6.18; nuevo P-104</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Push y fusión de rediseno-c-plus a develop autorizados por Sebas; 6.18 pasa a Hecho</t>
+          <t>UI 3j–3p</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Con la suite e2e en 290/290, Sebas autorizó subir a producción el rediseño C+ con el arreglo de la tasa; la sesión principal fusionó rediseno-c-plus a develop y la subió a origin. 6.18 pasa a Hecho. Nuevo pendiente P-104 (Alta, responsable Sebas): falta que apruebe/fusione el PR develop → main para que Vercel despliegue en producción.</t>
+          <t>Pantallas y revisión de diseño A1–A3.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>6.18 (verificación pre-commit de rediseno-c-plus)</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Suite e2e completa 290/290 tras independizar las pruebas del crédito de ejemplo</t>
+          <t>Lógica y datos de 3j–3p y correcciones de seguridad</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Encontró que, además del crédito huérfano ya corregido por el afterAll de la sesión principal, el segundo test de k-roles.spec.ts también resuelve el crédito del seed (cédula 1234567890), que queda inmutable por un trigger de negocio. Agregó restaurarCreditoDeEjemplo() en tests/e2e/utils.ts (borra y recrea la fila del seed) y la usó en c-cuenta.spec.ts, e-diseno.spec.ts e i-despliegue.spec.ts (sin tocar k-roles.spec.ts). Resultado: 4 suites afectadas en 0 fallas (antes 2), suite e2e completa 290/290 (antes 285/5), tsc/vitest (347)/lint/build en verde. Detalle en docs/verificaciones/2026-09-29-pre-commit.md. Listo para que la sesión principal haga el commit y la fusión a develop.</t>
+          <t>RS-01..RS-22 de código, limpieza de fotos por RPC (5.10), aviso institucional siempre. vitest 503, build en verde.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>2.14; P-103</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Se quita la sección de testimonios de la landing (decisión de Sebas)</t>
+          <t>Lienzo 3j–3p</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Commit 4c63924: sección de testimonios (que estaba oculta desde P-102 por tener textos de ejemplo) eliminada de la landing por decisión de Sebas. P-103 (D-07, ¿se mantiene la sección?) cierra Hecho con esa decisión: no se mantiene.</t>
+          <t>Piezas 3j–3n, 3o/3p (D-15, D-16) y revisión de fidelidad.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-auditor-supabase</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>4.11; P-95, P-96</t>
+          <t>4.12; P-46</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Sebas aprueba P-95 y P-96; ambos pasan a Hecho</t>
+          <t>Migraciones tanda 1 de Ricardo (29/30-sep)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>P-95 (botón «Escribir por WhatsApp» en el detalle de afiliación) aprobado tal cual estaba diseñado e implementado. P-96 (asignar asesor) aprobado con alcance limitado por ahora: solo asignar, solo cuando la afiliación está aprobada y el asociado todavía no tiene asesor; sin cambiar ni quitar un asesor ya asignado. La sesión principal agregó el estado «ya asignado» persistente al recargar (commit 3b5ae14), cerrando el residuo que había dejado ga-diseno-a-codigo.</t>
+          <t>20260929100000..100700, 20260930100000..100500: grados, nómina, proceso ejecutivo, alertas, comisiones con pagos editables, tasa oculta (P-100), crédito solo en «operando», segunda pasada RS-17/18/20/21. pgTAP en verde.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>4.11 (revisión de diseño 3e/3i)</t>
+          <t>4.7, 4.8, 5.9, 5.10, 6.14, 6.15; P-69, P-72</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Revisión de diseño aprobada con cambios menores</t>
+          <t>Primera entrega de Carlos Pardo revisada: NO fusionable</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Comparó el lienzo (piezas 3e/3i) contra PanelAfiliacionDetalle.tsx, AsignarAsesor.tsx, Iconos.tsx y lib/admin/whatsapp.ts. Veredicto: aprobado con cambios menores, incluido el estado «ya asignado» persistente al recargar. Corrigió 4 detalles menores en el propio lienzo (layout del botón de WhatsApp, glifo de las mini-muestras, foco sin halo extra, color suelto #182530 → token #1C2F3B). No tocó código. Detalle en docs/verificaciones/2026-09-27-revision-diseno-3e-3i.md.</t>
+          <t>Revisión del ZIP del repo privado de Carlos (base main anterior al rediseño C+, no rediseno-c-plus). Motivos: reintroduce la fuga F2-03 y pierde el revoke en resumen_clientes_asesor; el motivo de rechazo de afiliación usa una columna inexistente sin migración (rechazar dejaría de funcionar); convenios administrables usa columnas y un bucket de Storage inexistentes y acciones sin exigirAdmin ni validación; la purga Ley 1581 usa columnas/bucket equivocados y el cron queda abierto si falta CRON_SECRET; claves en .env.example, console.log y configuración de túnel; borra /asesor/demo (ya en producción) y renombra /cuenta/solicitar (ya en producción); sin pruebas. Se le envió a Carlos la lista de correcciones para rehacer el encargo sobre rediseno-c-plus, con un PR por tarea. 4.7, 4.8, 5.9, 5.10, 6.14 y 6.15 siguen Pendiente; P-69 con el mismo detalle y P-72 (acceso de colaborador en GitHub) sigue En curso, con la nota de que el ZIP en vez de un PR sugiere que ese acceso todavía no está confirmado.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>4.11, P-95, P-96</t>
+          <t>6.18; nuevo P-104</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>WhatsApp y bloque «Asesor» maquetados y conectados en código</t>
+          <t>Push y fusión de rediseno-c-plus a develop autorizados por Sebas; 6.18 pasa a Hecho</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Botón «Escribir por WhatsApp» habilitado en PanelAfiliacionDetalle.tsx (enlace wa.me en pestaña nueva con mensaje prellenado, glifo SVG IconoWhatsapp, normalización pura del celular en lib/admin/whatsapp.ts con pruebas Vitest, estado deshabilitado con motivo si el celular no es válido). Bloque «Asesor» nuevo (components/admin/AsignarAsesor.tsx) conectado a asignarAsesor con useActionState y sus 5 estados; corrigió una condición de carrera real (revalidatePath refrescaba la página y dejaba perfilAsociado en null justo tras el éxito) «congelando» la prop inicial con useState en PanelAfiliacionDetalle. Prueba nueva en tests/e2e/k-roles.spec.ts. tsc, lint, build, vitest (360) y Playwright (k-roles, escritorio) en verde. Dejó abierto para la sesión principal el estado «ya asignado» persistente al recargar (requería tocar la página de servidor, fuera de su encargo); cerrado después por la sesión principal (commit 3b5ae14, ver más abajo).</t>
+          <t>Con la suite e2e en 290/290, Sebas autorizó subir a producción el rediseño C+ con el arreglo de la tasa; la sesión principal fusionó rediseno-c-plus a develop y la subió a origin. 6.18 pasa a Hecho. Nuevo pendiente P-104 (Alta, responsable Sebas): falta que apruebe/fusione el PR develop → main para que Vercel despliegue en producción.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>4.11, P-96</t>
+          <t>6.18 (verificación pre-commit de rediseno-c-plus)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Server Action asignarAsesor lista en el servidor</t>
+          <t>Suite e2e completa 290/290 tras independizar las pruebas del crédito de ejemplo</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>asignarAsesor en app/admin/afiliaciones/actions.ts (exigirAdmin, zod esquemaAsignarAsesor, re-verificación en servidor de afiliación aprobada + perfil sin asesor + update condicional .is("asesor_id", null)); app/admin/afiliaciones/[id]/page.tsx carga perfilAsociado y asesores solo cuando aplica y los pasa como props opcionales nuevas a PanelAfiliacionDetalle (sin maquetar nada, TODO hacia D-09). 14 pruebas nuevas (9 de la Server Action, 5 del esquema zod); tsc/lint/build/vitest en verde (334 pruebas). Confirmó que no hace falta una migración nueva: la RLS perfiles_update y el trigger proteger_campos_perfil ya permiten el cambio a un admin, con validar_perfil_asesor_id validando que el elegido tenga rol asesor. Queda para ga-diseno-a-codigo maquetar y conectar la pieza 3i.</t>
+          <t>Encontró que, además del crédito huérfano ya corregido por el afterAll de la sesión principal, el segundo test de k-roles.spec.ts también resuelve el crédito del seed (cédula 1234567890), que queda inmutable por un trigger de negocio. Agregó restaurarCreditoDeEjemplo() en tests/e2e/utils.ts (borra y recrea la fila del seed) y la usó en c-cuenta.spec.ts, e-diseno.spec.ts e i-despliegue.spec.ts (sin tocar k-roles.spec.ts). Resultado: 4 suites afectadas en 0 fallas (antes 2), suite e2e completa 290/290 (antes 285/5), tsc/vitest (347)/lint/build en verde. Detalle en docs/verificaciones/2026-09-29-pre-commit.md. Listo para que la sesión principal haga el commit y la fusión a develop.</t>
         </is>
       </c>
     </row>
@@ -57341,22 +57333,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>4.11 (D-08, D-09)</t>
+          <t>2.14; P-103</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Diseñado el botón WhatsApp habilitado (3e) y el bloque «Asesor» (3i) en el lienzo</t>
+          <t>Se quita la sección de testimonios de la landing (decisión de Sebas)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>En docs/Green Alliance C+.dc.html: botón «Escribir por WhatsApp» de la pieza 3e con glifo oficial en SVG en línea y enlace wa.me con mensaje prellenado (4 estados: normal, hover, foco, deshabilitado por falta de celular); pieza 3i nueva, bloque «Asesor» para asignar perfiles.asesor_id a un asociado aprobado (estados sin elegir, asignando, éxito, error, ya asignado, sin asesores registrados). Trabajo nuevo dejado para ga-diseno-a-codigo: habilitar el botón en PanelAfiliacionDetalle.tsx y crear la Server Action «asignar asesor» sobre perfiles.asesor_id (sin migración nueva) más el bloque visible solo si la afiliación está aprobada y el asociado no tiene asesor.</t>
+          <t>Commit 4c63924: sección de testimonios (que estaba oculta desde P-102 por tener textos de ejemplo) eliminada de la landing por decisión de Sebas. P-103 (D-07, ¿se mantiene la sección?) cierra Hecho con esa decisión: no se mantiene.</t>
         </is>
       </c>
     </row>
@@ -57373,17 +57365,17 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>4.11; P-95, P-96</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Se corrige la dependencia de 6.18: ya no depende de 1.8</t>
+          <t>Sebas aprueba P-95 y P-96; ambos pasan a Hecho</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>6.18 (fusionar rediseno-c-plus a develop) dependía por error de 1.8 (aplicar las 5 migraciones de backend del rediseño). El código del rediseño funciona sin esas migraciones (KPIs con su propio fallback, tope real leído de grados_credito, nota interna oculta detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false) y lo que sí las necesita queda oculto hasta que se apliquen. Con 6.17 y 6.19 en Hecho, el rediseño C+ queda completo y verificado de punta a punta en la rama rediseno-c-plus (9 commits locales sobre develop, sin push); 6.18 queda Pendiente solo de que Sebas autorice el push de la rama y abra el PR a develop.</t>
+          <t>P-95 (botón «Escribir por WhatsApp» en el detalle de afiliación) aprobado tal cual estaba diseñado e implementado. P-96 (asignar asesor) aprobado con alcance limitado por ahora: solo asignar, solo cuando la afiliación está aprobada y el asociado todavía no tiene asesor; sin cambiar ni quitar un asesor ya asignado. La sesión principal agregó el estado «ya asignado» persistente al recargar (commit 3b5ae14), cerrando el residuo que había dejado ga-diseno-a-codigo.</t>
         </is>
       </c>
     </row>
@@ -57395,22 +57387,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>6.17; 3.10, 4.10</t>
+          <t>4.11 (revisión de diseño 3e/3i)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Correcciones responsive del C+ (commit b0239a8): barra inferior siempre visible en vez de oculta hasta el primer scroll</t>
+          <t>Revisión de diseño aprobada con cambios menores</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Se descartó la solución de ga-diseno-a-codigo de ocultar la barra inferior de /cuenta y /asesor hasta el primer scroll (con `inert`) porque ocultar la navegación principal al cargar la página perjudicaba la usabilidad y la accesibilidad. En su lugar, la barra queda siempre visible con espacio reservado al final de la página. Incluye también las correcciones de admin en celular y de la vista en tarjetas de /admin/sorteo, y el contraste de /admin/demo. e2e k-roles, c-cuenta y f-accesibilidad en verde (50 pasadas) tras `supabase db reset`.</t>
+          <t>Comparó el lienzo (piezas 3e/3i) contra PanelAfiliacionDetalle.tsx, AsignarAsesor.tsx, Iconos.tsx y lib/admin/whatsapp.ts. Veredicto: aprobado con cambios menores, incluido el estado «ya asignado» persistente al recargar. Corrigió 4 detalles menores en el propio lienzo (layout del botón de WhatsApp, glifo de las mini-muestras, foco sin halo extra, color suelto #182530 → token #1C2F3B). No tocó código. Detalle en docs/verificaciones/2026-09-27-revision-diseno-3e-3i.md.</t>
         </is>
       </c>
     </row>
@@ -57422,22 +57414,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>4.11; 6.17</t>
+          <t>4.11, P-95, P-96</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Hallazgo 0 corregido en producción del rediseño (commit 846657b): colores del admin oscuro en su propio grupo de Tailwind</t>
+          <t>WhatsApp y bloque «Asesor» maquetados y conectados en código</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Los colores bg-admin-*/text-admin-* estaban anidados bajo la paleta ga en tailwind.config.ts, por lo que Tailwind nunca generaba esas clases y el panel /admin se veía blanco/sin tema oscuro en todos los anchos. Se movieron a su propio grupo admin en tailwind.config.ts; pruebas de responsive actualizadas en el mismo commit.</t>
+          <t>Botón «Escribir por WhatsApp» habilitado en PanelAfiliacionDetalle.tsx (enlace wa.me en pestaña nueva con mensaje prellenado, glifo SVG IconoWhatsapp, normalización pura del celular en lib/admin/whatsapp.ts con pruebas Vitest, estado deshabilitado con motivo si el celular no es válido). Bloque «Asesor» nuevo (components/admin/AsignarAsesor.tsx) conectado a asignarAsesor con useActionState y sus 5 estados; corrigió una condición de carrera real (revalidatePath refrescaba la página y dejaba perfilAsociado en null justo tras el éxito) «congelando» la prop inicial con useState en PanelAfiliacionDetalle. Prueba nueva en tests/e2e/k-roles.spec.ts. tsc, lint, build, vitest (360) y Playwright (k-roles, escritorio) en verde. Dejó abierto para la sesión principal el estado «ya asignado» persistente al recargar (requería tocar la página de servidor, fuera de su encargo); cerrado después por la sesión principal (commit 3b5ae14, ver más abajo).</t>
         </is>
       </c>
     </row>
@@ -57449,22 +57441,22 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>4.11, P-96</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Corregidos todos los hallazgos del informe de responsive; 6.17 pasa a Hecho en su parte de código</t>
+          <t>Server Action asignarAsesor lista en el servidor</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Confirmado con capturas que el hallazgo 0 (colores admin-* fuera de la clave ga) ya estaba resuelto en el código. De paso, axe encontró y se corrigió un contraste nuevo: EncabezadoAdmin se volvía transparente en escritorio asumiendo que siempre estaría sobre el fondo oscuro del admin, pero en /admin/demo esa misma barra flota sobre el fondo claro de la vista de asociado. Corregidos también: flex-wrap en el filtro de /admin/creditos, controles del encabezado móvil del admin a 44×44, tabla de /admin/sorteo con versión en tarjetas, botones de /cuenta/solicitar y casillas OTP a 44px, selects de /admin/sorteo a 16px. La corrección de la barra inferior flotante de /cuenta y /asesor de este commit (ocultarla hasta el primer scroll con `inert`) fue reemplazada después por la sesión principal, ver el siguiente asiento. tsc, lint, build, vitest (316/316) y playwright k-roles+f-accesibilidad (36/36, 6 skip esperados) en verde tras `npx supabase db reset`.</t>
+          <t>asignarAsesor en app/admin/afiliaciones/actions.ts (exigirAdmin, zod esquemaAsignarAsesor, re-verificación en servidor de afiliación aprobada + perfil sin asesor + update condicional .is("asesor_id", null)); app/admin/afiliaciones/[id]/page.tsx carga perfilAsociado y asesores solo cuando aplica y los pasa como props opcionales nuevas a PanelAfiliacionDetalle (sin maquetar nada, TODO hacia D-09). 14 pruebas nuevas (9 de la Server Action, 5 del esquema zod); tsc/lint/build/vitest en verde (334 pruebas). Confirmó que no hace falta una migración nueva: la RLS perfiles_update y el trigger proteger_campos_perfil ya permiten el cambio a un admin, con validar_perfil_asesor_id validando que el elegido tenga rol asesor. Queda para ga-diseno-a-codigo maquetar y conectar la pieza 3i.</t>
         </is>
       </c>
     </row>
@@ -57476,22 +57468,22 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-responsive</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>4.11 (D-08, D-09)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Verificación responsive de punta a punta del rediseño C+; 6.19 pasa a Hecho</t>
+          <t>Diseñado el botón WhatsApp habilitado (3e) y el bloque «Asesor» (3i) en el lienzo</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>15 rutas × 10 anchos (320-1920 px) + horizontal 844×390, Playwright/Chrome contra Supabase local. 9 hallazgos responsive (5 críticos: barra inferior flotante tapaba contenido real en /cuenta y /asesor, scroll horizontal real en /admin/creditos, botones &lt;44px en el encabezado móvil del admin, tabla de /admin/sorteo sin versión en tarjetas; 4 menores) más 1 hallazgo crítico fuera del alcance responsive estricto: los colores bg-admin-*/text-admin-* no existían en el CSS compilado (tailwind.config.ts los anidaba bajo la paleta ga en vez de un grupo propio admin), así que el panel se veía sin tema oscuro. tests/responsive/responsive.spec.ts y logo-y-fotos.spec.ts actualizados. No se pudo probar /admin/* en horizontal por el límite diario de reenvío de código del correo de prueba (no es un hallazgo nuevo). Informe: docs/verificaciones/2026-09-27-rediseno-c-plus-responsive.md.</t>
+          <t>En docs/Green Alliance C+.dc.html: botón «Escribir por WhatsApp» de la pieza 3e con glifo oficial en SVG en línea y enlace wa.me con mensaje prellenado (4 estados: normal, hover, foco, deshabilitado por falta de celular); pieza 3i nueva, bloque «Asesor» para asignar perfiles.asesor_id a un asociado aprobado (estados sin elegir, asignando, éxito, error, ya asignado, sin asesores registrados). Trabajo nuevo dejado para ga-diseno-a-codigo: habilitar el botón en PanelAfiliacionDetalle.tsx y crear la Server Action «asignar asesor» sobre perfiles.asesor_id (sin migración nueva) más el bloque visible solo si la afiliación está aprobada y el asociado no tiene asesor.</t>
         </is>
       </c>
     </row>
@@ -57508,17 +57500,17 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>4.11; P-99, P-100, P-101, P-102, P-103</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>H1 corregido (tasa de interés fuera del payload de /cuenta) y H2/B-01 cerrados (cédula de las «hermanas» enmascarada en servidor, testimonios de ejemplo ocultos)</t>
+          <t>Se corrige la dependencia de 6.18: ya no depende de 1.8</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Commit e650033: la tasa de interés ya no viaja al navegador del asociado en /cuenta ni /cuenta/solicitar (hallazgo H1 de ga-revisor-seguridad; el problema también estaba en producción desde el 25-sep, se sugiere llevarlo también a main). Queda un residuo (P-100): un asociado podría seguir leyendo la tasa consultando la API directo con su sesión (la RLS le deja leer sus solicitudes y grados_credito); ocultarlo del todo requiere una migración de permisos por columna, a decisión de Sebas. Commit fdab456: cédula de las «hermanas» del detalle de afiliación enmascarada en el servidor (cierra H2/M-01, P-101) y sección de testimonios de la landing oculta mientras tenga textos de ejemplo (cierra B-01, P-102; D-07 queda abierto como pedido de diseño en P-103: contenido real de testimonios y si la sección se mantiene). e2e de landing y k-roles vueltos a correr en verde.</t>
+          <t>6.18 (fusionar rediseno-c-plus a develop) dependía por error de 1.8 (aplicar las 5 migraciones de backend del rediseño). El código del rediseño funciona sin esas migraciones (KPIs con su propio fallback, tope real leído de grados_credito, nota interna oculta detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false) y lo que sí las necesita queda oculto hasta que se apliquen. Con 6.17 y 6.19 en Hecho, el rediseño C+ queda completo y verificado de punta a punta en la rama rediseno-c-plus (9 commits locales sobre develop, sin push); 6.18 queda Pendiente solo de que Sebas autorice el push de la rama y abra el PR a develop.</t>
         </is>
       </c>
     </row>
@@ -57530,22 +57522,22 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>4.11, P-94, P-71; 6.16 pasa a Hecho; nuevos P-102, P-103</t>
+          <t>6.17; 3.10, 4.10</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>QA completo del rediseño C+ en verde: 161/162 escritorio, 129/129 celular</t>
+          <t>Correcciones responsive del C+ (commit b0239a8): barra inferior siempre visible en vez de oculta hasta el primer scroll</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>QA de punta a punta contra Supabase local (escritorio 1280×800, celular 390×844). Actualizó las pruebas desactualizadas por el rediseño: a-navegacion (nav sin «Historias»), e-diseno (reescrita casi entera, textos verificados contra el código), afiliación v2 en utils.ts/f-accesibilidad (cierra P-94), aprobar en 2 pasos + atajos de teclado + KPIs + nota interna oculta (k-roles), máscara de correo con dominio oculto en b-ingreso y j-produccion (cierra P-71; i-despliegue ya usaba el formato nuevo). Agregó pruebas de reduced-motion y de que ninguna pantalla diga «Correo institucional». De paso corrigió una prueba de seguridad de i-despliegue que fallaba por una causa ajena al rediseño (React 19 ya no serializa el DOM en un `&lt;form action={...}&gt;`), reescribiéndola con intercepción de red. Hallazgos: 1 Media (cédula de las «hermanas», ya reportada por ga-revisor-seguridad, ver P-101) y 2 Bajos (testimonios de ejemplo con corchetes en la landing, ver P-102/P-103; y los marcadores ya conocidos de /politica-de-datos). 0 violaciones de axe en 19 combinaciones. Informe en docs/verificaciones/2026-09-27-rediseno-c-plus-qa.md.</t>
+          <t>Se descartó la solución de ga-diseno-a-codigo de ocultar la barra inferior de /cuenta y /asesor hasta el primer scroll (con `inert`) porque ocultar la navegación principal al cargar la página perjudicaba la usabilidad y la accesibilidad. En su lugar, la barra queda siempre visible con espacio reservado al final de la página. Incluye también las correcciones de admin en celular y de la vista en tarjetas de /admin/sorteo, y el contraste de /admin/demo. e2e k-roles, c-cuenta y f-accesibilidad en verde (50 pasadas) tras `supabase db reset`.</t>
         </is>
       </c>
     </row>
@@ -57557,22 +57549,22 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>ga-revisor-seguridad</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>4.11; nuevos P-99, P-100, P-101</t>
+          <t>4.11; 6.17</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Revisión de seguridad del rediseño C+ aprobada; 2 fugas de datos confirmadas (no introducidas por el rediseño)</t>
+          <t>Hallazgo 0 corregido en producción del rediseño (commit 846657b): colores del admin oscuro en su propio grupo de Tailwind</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Revisó el diff completo de rediseno-c-plus contra develop (app, components, lib, proxy.ts, supabase): sin cambios en Server Actions ni en proxy.ts, el asesor sigue sin ver datos sensibles de sus clientes, la aprobación en 2 pasos exige confirmar, el login no cambió en funcionalidad. Encontró 2 hallazgos de fuga de datos al payload del cliente, vigentes desde antes de este diff: la tasa de interés viaja en las props de CuentaCliente aunque no se renderice (H1, ver P-99/P-100) y la cédula sin enmascarar de las «hermanas» viaja completa al detalle de afiliación aunque se muestre enmascarada (H2, ver P-101). Revisó también las 5 migraciones propuestas de 1.8 (bien construidas, coherentes con el flag de nota interna). npm audit --omit=dev: 0 vulnerabilidades. Pidió a ga-funcionalidad-botones corregir ambas fugas y a Sebas decidir sobre las 5 migraciones de 1.8.</t>
+          <t>Los colores bg-admin-*/text-admin-* estaban anidados bajo la paleta ga en tailwind.config.ts, por lo que Tailwind nunca generaba esas clases y el panel /admin se veía blanco/sin tema oscuro en todos los anchos. Se movieron a su propio grupo admin en tailwind.config.ts; pruebas de responsive actualizadas en el mismo commit.</t>
         </is>
       </c>
     </row>
@@ -57584,22 +57576,22 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>ga-funcionalidad-botones</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>KPIs reales, tope real de grados_credito y nota interna oculta en el admin C+</t>
+          <t>Corregidos todos los hallazgos del informe de responsive; 6.17 pasa a Hecho en su parte de código</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Cerró los 2 frentes de backend que dejó abiertos el maquetado del admin en modo oscuro (commit e39ad72): (1) los 4 KPI de /admin/creditos ahora son siempre exactos (lib/admin/kpis.ts: 3 conteos exactos + suma de aprobadas del mes, con el cliente de sesión del admin vía RLS, sin service role; mes calendario en hora de Colombia; pruebas nuevas en tests/unit/admin-kpis.test.ts); (2) el aviso «Dentro/Supera el tope» y el bloqueo de «Aprobar» usan el tope real de grados_credito (cargarPaquetesDemo, con su fallback a la copia estática). Ocultó el textarea de «Nota interna» detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false (lib/admin/flags.ts) con un TODO(backend) hacia la migración sin aplicar 20260925200200_historial_y_notas_internas.sql. Confirmó sin cambios de código que la aprobación en 2 pasos, el rechazo con motivo obligatorio, los atajos J/K/A/R/Esc y el invariante monto≤tope (triggers de la base) siguen intactos. tsc, lint, build y 316 pruebas de vitest (19 archivos) en verde. Sin commits. Sin bloqueos nuevos; sigue pendiente 1.8 (migraciones sin aplicar) para conectar una Server Action a agregar_nota_solicitud() y activar la bandera.</t>
+          <t>Confirmado con capturas que el hallazgo 0 (colores admin-* fuera de la clave ga) ya estaba resuelto en el código. De paso, axe encontró y se corrigió un contraste nuevo: EncabezadoAdmin se volvía transparente en escritorio asumiendo que siempre estaría sobre el fondo oscuro del admin, pero en /admin/demo esa misma barra flota sobre el fondo claro de la vista de asociado. Corregidos también: flex-wrap en el filtro de /admin/creditos, controles del encabezado móvil del admin a 44×44, tabla de /admin/sorteo con versión en tarjetas, botones de /cuenta/solicitar y casillas OTP a 44px, selects de /admin/sorteo a 16px. La corrección de la barra inferior flotante de /cuenta y /asesor de este commit (ocultarla hasta el primer scroll con `inert`) fue reemplazada después por la sesión principal, ver el siguiente asiento. tsc, lint, build, vitest (316/316) y playwright k-roles+f-accesibilidad (36/36, 6 skip esperados) en verde tras `npx supabase db reset`.</t>
         </is>
       </c>
     </row>
@@ -57611,22 +57603,22 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-verificador-responsive</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Panel del admin C+ en modo oscuro maquetado en código; 4.11 pasa a Hecho</t>
+          <t>Verificación responsive de punta a punta del rediseño C+; 6.19 pasa a Hecho</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Maquetó el panel de administración completo en modo oscuro (piezas 2d y 3e–3h): Créditos (menú lateral, 4 KPI con guion donde falta consulta nueva, búsqueda, filtro, lista+ficha, aprobar en 2 pasos, rechazar con motivo obligatorio, nota interna e historial UI), Afiliaciones (lista+ficha, visor de 3 fotos con sus 3 estados, aprobar/rechazar en 2 pasos, WhatsApp deshabilitado por P-95), Asesores y Sorteo con el mismo restyle, y EncabezadoAdmin (patrón de celular) también en /admin/demo. Tokens nuevos en globals.css/tailwind.config.ts. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus (junto con 4.10). Pasa a Hecho en maquetación con 2 frentes abiertos: (1) tests/e2e/k-roles.spec.ts va a fallar porque Aprobar ahora pide un segundo clic «Sí, aprobar» — hace falta que ga-verificador-qa/ga-escritor-tests actualicen ese paso; (2) sin backend nuevo, KPIs completos, tope real desde grados_credito y nota interna/historial reales siguen bloqueados por las 5 migraciones de 1.8 (docs/auditorias/2026-09-25-backend-rediseno-c-plus.md), sin aplicar.</t>
+          <t>15 rutas × 10 anchos (320-1920 px) + horizontal 844×390, Playwright/Chrome contra Supabase local. 9 hallazgos responsive (5 críticos: barra inferior flotante tapaba contenido real en /cuenta y /asesor, scroll horizontal real en /admin/creditos, botones &lt;44px en el encabezado móvil del admin, tabla de /admin/sorteo sin versión en tarjetas; 4 menores) más 1 hallazgo crítico fuera del alcance responsive estricto: los colores bg-admin-*/text-admin-* no existían en el CSS compilado (tailwind.config.ts los anidaba bajo la paleta ga en vez de un grupo propio admin), así que el panel se veía sin tema oscuro. tests/responsive/responsive.spec.ts y logo-y-fotos.spec.ts actualizados. No se pudo probar /admin/* en horizontal por el límite diario de reenvío de código del correo de prueba (no es un hallazgo nuevo). Informe: docs/verificaciones/2026-09-27-rediseno-c-plus-responsive.md.</t>
         </is>
       </c>
     </row>
@@ -57638,22 +57630,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>sesión principal</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>4.10; nuevo P-98</t>
+          <t>4.11; P-99, P-100, P-101, P-102, P-103</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Panel del asesor C+ maquetado en código; 4.10 pasa a Hecho</t>
+          <t>H1 corregido (tasa de interés fuera del payload de /cuenta) y H2/B-01 cerrados (cédula de las «hermanas» enmascarada en servidor, testimonios de ejemplo ocultos)</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Maquetó /asesor y /asesor/demo siguiendo las piezas 2c/3h del lienzo: EncabezadoAsesor en píldora, tarjetas de resumen con categoría de afiliación, chips de filtro, buscador, tabla de 5 columnas reescrita (sin datos de contacto), estado vacío, transición de lista y barra inferior en celular; agregó el marco ámbar de demostración compartido con /admin/demo y el estado «neutral» a Badge. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus. Documentó como pedido D-06 (docs/diseno/pedidos.md) la falta de regla de diseño para categorizar asociados ya afiliados (no solo solicitudes) en las tarjetas/chips; se registra como decisión provisional de la sesión principal, pendiente de que Sebas la confirme (nuevo pendiente P-98).</t>
+          <t>Commit e650033: la tasa de interés ya no viaja al navegador del asociado en /cuenta ni /cuenta/solicitar (hallazgo H1 de ga-revisor-seguridad; el problema también estaba en producción desde el 25-sep, se sugiere llevarlo también a main). Queda un residuo (P-100): un asociado podría seguir leyendo la tasa consultando la API directo con su sesión (la RLS le deja leer sus solicitudes y grados_credito); ocultarlo del todo requiere una migración de permisos por columna, a decisión de Sebas. Commit fdab456: cédula de las «hermanas» del detalle de afiliación enmascarada en el servidor (cierra H2/M-01, P-101) y sección de testimonios de la landing oculta mientras tenga textos de ejemplo (cierra B-01, P-102; D-07 queda abierto como pedido de diseño en P-103: contenido real de testimonios y si la sección se mantiene). e2e de landing y k-roles vueltos a correr en verde.</t>
         </is>
       </c>
     </row>
@@ -57665,83 +57657,83 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-verificador-qa</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.11, P-94, P-71; 6.16 pasa a Hecho; nuevos P-102, P-103</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Panel del asociado C+ maquetado en código; 3.10 pasa a Hecho</t>
+          <t>QA completo del rediseño C+ en verde: 161/162 escritorio, 129/129 celular</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Maquetó /cuenta y /cuenta/solicitar siguiendo las piezas 2b/3d del lienzo: EncabezadoCuenta en píldora flotante, comprobante «Tu solicitud» con sello y pasos animados, insignia de estado con color real, tope con medidor, carné de asociado (institución/activo como props opcionales sin usar, TODO backend), franja del sorteo, barra inferior en celular y deslizador de monto propio en /cuenta/solicitar; agregó enmascararCedula a lib/mascara.ts. tsc, lint, build y 311 pruebas de vitest en verde; no corrió Playwright (requiere Supabase local). Commit local 51da63f en rediseno-c-plus. «Tu camino a la estabilidad» sigue sin renderizarse por P-90 (fecha del primer descuento del embargo solidario); el carné de asociado sigue esperando institución/activo en perfiles (1.8). Falta correr tests/e2e/c-cuenta, h-credito, i-despliegue, j-produccion y k-roles contra Supabase local (ga-verificador-qa).</t>
+          <t>QA de punta a punta contra Supabase local (escritorio 1280×800, celular 390×844). Actualizó las pruebas desactualizadas por el rediseño: a-navegacion (nav sin «Historias»), e-diseno (reescrita casi entera, textos verificados contra el código), afiliación v2 en utils.ts/f-accesibilidad (cierra P-94), aprobar en 2 pasos + atajos de teclado + KPIs + nota interna oculta (k-roles), máscara de correo con dominio oculto en b-ingreso y j-produccion (cierra P-71; i-despliegue ya usaba el formato nuevo). Agregó pruebas de reduced-motion y de que ninguna pantalla diga «Correo institucional». De paso corrigió una prueba de seguridad de i-despliegue que fallaba por una causa ajena al rediseño (React 19 ya no serializa el DOM en un `&lt;form action={...}&gt;`), reescribiéndola con intercepción de red. Hallazgos: 1 Media (cédula de las «hermanas», ya reportada por ga-revisor-seguridad, ver P-101) y 2 Bajos (testimonios de ejemplo con corchetes en la landing, ver P-102/P-103; y los marcadores ya conocidos de /politica-de-datos). 0 violaciones de axe en 19 combinaciones. Informe en docs/verificaciones/2026-09-27-rediseno-c-plus-qa.md.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>ga-diseno-a-codigo</t>
+          <t>ga-revisor-seguridad</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15</t>
+          <t>4.11; nuevos P-99, P-100, P-101</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
+          <t>Revisión de seguridad del rediseño C+ aprobada; 2 fugas de datos confirmadas (no introducidas por el rediseño)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
+          <t>Revisó el diff completo de rediseno-c-plus contra develop (app, components, lib, proxy.ts, supabase): sin cambios en Server Actions ni en proxy.ts, el asesor sigue sin ver datos sensibles de sus clientes, la aprobación en 2 pasos exige confirmar, el login no cambió en funcionalidad. Encontró 2 hallazgos de fuga de datos al payload del cliente, vigentes desde antes de este diff: la tasa de interés viaja en las props de CuentaCliente aunque no se renderice (H1, ver P-99/P-100) y la cédula sin enmascarar de las «hermanas» viaja completa al detalle de afiliación aunque se muestre enmascarada (H2, ver P-101). Revisó también las 5 migraciones propuestas de 1.8 (bien construidas, coherentes con el flag de nota interna). npm audit --omit=dev: 0 vulnerabilidades. Pidió a ga-funcionalidad-botones corregir ambas fugas y a Sebas decidir sobre las 5 migraciones de 1.8.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-funcionalidad-botones</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>3.10, 4.10, 4.11</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
+          <t>KPIs reales, tope real de grados_credito y nota interna oculta en el admin C+</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
+          <t>Cerró los 2 frentes de backend que dejó abiertos el maquetado del admin en modo oscuro (commit e39ad72): (1) los 4 KPI de /admin/creditos ahora son siempre exactos (lib/admin/kpis.ts: 3 conteos exactos + suma de aprobadas del mes, con el cliente de sesión del admin vía RLS, sin service role; mes calendario en hora de Colombia; pruebas nuevas en tests/unit/admin-kpis.test.ts); (2) el aviso «Dentro/Supera el tope» y el bloqueo de «Aprobar» usan el tope real de grados_credito (cargarPaquetesDemo, con su fallback a la copia estática). Ocultó el textarea de «Nota interna» detrás de HISTORIAL_NOTAS_INTERNAS_HABILITADO=false (lib/admin/flags.ts) con un TODO(backend) hacia la migración sin aplicar 20260925200200_historial_y_notas_internas.sql. Confirmó sin cambios de código que la aprobación en 2 pasos, el rechazo con motivo obligatorio, los atajos J/K/A/R/Esc y el invariante monto≤tope (triggers de la base) siguen intactos. tsc, lint, build y 316 pruebas de vitest (19 archivos) en verde. Sin commits. Sin bloqueos nuevos; sigue pendiente 1.8 (migraciones sin aplicar) para conectar una Server Action a agregar_nota_solicitud() y activar la bandera.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -57751,71 +57743,71 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.14; nuevo 6.16</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Tokens y landing del rediseño C+ llevados a código</t>
+          <t>Panel del admin C+ en modo oscuro maquetado en código; 4.11 pasa a Hecho</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
+          <t>Maquetó el panel de administración completo en modo oscuro (piezas 2d y 3e–3h): Créditos (menú lateral, 4 KPI con guion donde falta consulta nueva, búsqueda, filtro, lista+ficha, aprobar en 2 pasos, rechazar con motivo obligatorio, nota interna e historial UI), Afiliaciones (lista+ficha, visor de 3 fotos con sus 3 estados, aprobar/rechazar en 2 pasos, WhatsApp deshabilitado por P-95), Asesores y Sorteo con el mismo restyle, y EncabezadoAdmin (patrón de celular) también en /admin/demo. Tokens nuevos en globals.css/tailwind.config.ts. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus (junto con 4.10). Pasa a Hecho en maquetación con 2 frentes abiertos: (1) tests/e2e/k-roles.spec.ts va a fallar porque Aprobar ahora pide un segundo clic «Sí, aprobar» — hace falta que ga-verificador-qa/ga-escritor-tests actualicen ese paso; (2) sin backend nuevo, KPIs completos, tope real desde grados_credito y nota interna/historial reales siguen bloqueados por las 5 migraciones de 1.8 (docs/auditorias/2026-09-25-backend-rediseno-c-plus.md), sin aplicar.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ga-disenador-lienzo</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
+          <t>4.10; nuevo P-98</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
+          <t>Panel del asesor C+ maquetado en código; 4.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>En docs/Green Alliance C+.dc.html, sección t3 con 3 piezas nuevas: 3a design system C+ (tokens claro/oscuro, tipografía, espaciado, radios, sombras, movimiento con nombre, 16 componentes con sus estados), 3b Ingreso (/ingresar y /ingresar/codigo, normal/cargando/código inválido/bloqueado/éxito) y 3c Afiliación (/afiliacion y /afiliacion/enviada, errores por campo, foto con error, envío, cédula con solicitud pendiente); corrigió además «Correo institucional» → «Correo» en 2d (parte de D-05). D-01, D-02 y D-03 marcados Resuelto en docs/diseno/pedidos.md; 3 filas nuevas en docs/diseno/lienzo-indice.md. Script y etiquetas del lienzo verificados (JS válido, sc-for/sc-if y &lt;div&gt; balanceados). Nuevas actividades: 1.7 (Hecho, la parte de diseño de tokens), 2.15 (diseño de ingreso/afiliación C+ Hecho, código todavía no empezado), 3.10 (asociado C+, diseño en curso vía D-04, prioridad media) y 4.10/4.11 (asesor y admin C+, diseño en curso vía D-05, falta detalle de Asesores/Sorteo/Demostración/admin en celular).</t>
+          <t>Maquetó /asesor y /asesor/demo siguiendo las piezas 2c/3h del lienzo: EncabezadoAsesor en píldora, tarjetas de resumen con categoría de afiliación, chips de filtro, buscador, tabla de 5 columnas reescrita (sin datos de contacto), estado vacío, transición de lista y barra inferior en celular; agregó el marco ámbar de demostración compartido con /admin/demo y el estado «neutral» a Badge. tsc, lint, build y 311 pruebas de vitest en verde. Commit local e39ad72 en rediseno-c-plus. Documentó como pedido D-06 (docs/diseno/pedidos.md) la falta de regla de diseño para categorizar asociados ya afiliados (no solo solicitudes) en las tarjetas/chips; se registra como decisión provisional de la sesión principal, pendiente de que Sebas la confirme (nuevo pendiente P-98).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>ga-auditor-supabase</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>1.8; P-47, P-90, P-91, P-92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de backend para el rediseño C+: 5 migraciones propuestas sin aplicar</t>
+          <t>Panel del asociado C+ maquetado en código; 3.10 pasa a Hecho</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Trabajo nuevo pedido por Sebas hoy (rama rediseno-c-plus, lienzo docs/Green Alliance C+.dc.html). Análisis de brechas de backend para las piezas 2b/2c/2d del lienzo contra supabase/migrations/, sin MCP de Supabase en esta sesión (solo contra el repo, falta confirmar contra producción); informe en docs/auditorias/2026-09-25-backend-rediseno-c-plus.md. 5 migraciones nuevas sin aplicar: preferencia de aviso del sorteo, institución/activo en perfiles, historial + nota interna del admin, Realtime de solicitudes e índices de búsqueda opcionales. Nueva actividad 1.8 (peso 2, depende de 1.6). Preguntas abiertas para la cooperativa: estado «Desembolso» (ya era P-47, se anota la coincidencia), origen de la fecha del primer descuento del embargo solidario (P-90), proceso para dar de baja a un asociado (P-91) y quién dispara el correo del aviso del sorteo (P-92).</t>
+          <t>Maquetó /cuenta y /cuenta/solicitar siguiendo las piezas 2b/3d del lienzo: EncabezadoCuenta en píldora flotante, comprobante «Tu solicitud» con sello y pasos animados, insignia de estado con color real, tope con medidor, carné de asociado (institución/activo como props opcionales sin usar, TODO backend), franja del sorteo, barra inferior en celular y deslizador de monto propio en /cuenta/solicitar; agregó enmascararCedula a lib/mascara.ts. tsc, lint, build y 311 pruebas de vitest en verde; no corrió Playwright (requiere Supabase local). Commit local 51da63f en rediseno-c-plus. «Tu camino a la estabilidad» sigue sin renderizarse por P-90 (fecha del primer descuento del embargo solidario); el carné de asociado sigue esperando institución/activo en perfiles (1.8). Falta correr tests/e2e/c-cuenta, h-credito, i-despliegue, j-produccion y k-roles contra Supabase local (ga-verificador-qa).</t>
         </is>
       </c>
     </row>
@@ -57825,24 +57817,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (despliegue PR #2)</t>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89</t>
+          <t>1.7, 2.15</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Despliegue confirmado en producción: 4.9, P-83, P-84, P-85 y P-89 pasan a Hecho</t>
+          <t>Componentes base y maquetación C+ de ingreso/afiliación llevados a código; 2.15 pasa a Hecho</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Sebas fusionó el PR #2 develop → main (merge 2c19d02) y Vercel desplegó. Comprobado por HTTP en www.greenallianceco.com: WhatsApp «311 724 1942» (P-84), «Vigilada por Supersolidaria», /afiliacion sin exigir correo institucional (P-85), correos de Resend con NOMBRE/MOTIVO escapados (P-83), y /admin/demo y /asesor/demo redirigen a /ingresar sin sesión (4.9, P-89). La migración 20260925194922 ya estaba aplicada en producción. Falta que Sebas abra /admin/demo con su propia sesión para confirmarla a ojo.</t>
+          <t>Reestilizó components/ui/* (Button, Input, Select, Textarea, Checkbox, Field, OtpInput, Badge, ProgressSteps, PasosSolicitud, carga de foto) según la pieza 3a, y maquetó /ingresar, /ingresar/codigo, /afiliacion y /afiliacion/enviada según 3b/3c con sus animaciones (foco animado, sacudida del OTP en código inválido, aro que se vacía en «Reenviar código», vista previa de foto y sello del comprobante). tsc, lint, build y las 308 pruebas de vitest pasan. 2.15 pasa a Hecho en código; queda pendiente P-94 (correr tests/e2e/b-ingreso.spec.ts y d-afiliacion.spec.ts contra estos cambios con Supabase local, no corridos en este reporte). tests/e2e/e-diseno.spec.ts sigue desactualizado desde antes de esta tanda (ya cubierto por 6.16). El commit local 63d4b4d en la rama rediseno-c-plus guarda este avance junto con el trabajo de ga-disenador-lienzo (tokens, Bricolage, landing, componentes base, ingreso y afiliación, lienzo completo 3a–3h).</t>
         </is>
       </c>
     </row>
@@ -57852,24 +57844,24 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>sesión principal (coordinador)</t>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>4.9; P-83, P-84, P-85, P-89; 6.15</t>
+          <t>3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Cuenta demo para admin, máscara de correo sin dominio y cierre de P-86/P-87</t>
+          <t>Lienzo C+ completo: piezas 3d (asociado) y 3e–3h (admin)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Nueva pestaña «Demostración» en /admin/demo: reutiliza la cuenta fantasma de /asesor/demo (selector de grado, no guarda nada, solo lee grados_credito), lectura compartida en lib/asesor/cargarPaquetesDemo.ts, un asesor no puede entrar; nueva actividad 4.9 (peso 2, depende de 4.1 y 4.6) y pendiente P-89, ambos En curso hasta desplegar. F-01 revisado por el cambio a correo de cualquier dominio (P-85): la máscara ahora oculta también el dominio, formato «xx•••@•••»; 6.15 suma nota con el formato nuevo. La migración 20260925194922_correo_afiliacion_cualquier_dominio ya estaba aplicada en producción; el archivo local se renombró a esa versión para que el historial coincida. P-83, P-84 y P-85 siguen En curso: corregidos en local (con pruebas), en el commit de hoy, falta desplegar. P-86 y P-87 confirmados Hecho (sin cambios). Verificado: tsc, eslint, 308 unitarias, 222 pgTAP, 53 e2e de escritorio (k-roles + d-afiliacion) y build.</t>
+          <t>Pedido D-04/D-05 cerrado: agregó al lienzo docs/Green Alliance C+.dc.html la pieza 3d (asociado: /cuenta/solicitar, estado vacío, Mis datos y la boleta del sorteo con sus 3 pasos) y las piezas 3e–3h (admin: detalle de afiliación, Asesores, Sorteo, pestaña Demostración y el patrón del admin en celular), con escritorio, celular y todos los estados reales. El diseño en el lienzo de asociado, asesor y admin queda completo; 3.10, 4.10 y 4.11 siguen En curso porque falta maquetar en código (ga-diseno-a-codigo). Casi todas las piezas 3d–3h usan componentes/rutas que ya existen, salvo el botón «Escribir por WhatsApp» del detalle de afiliación (nuevo, ver P-95). Nuevos pendientes de decisión para la cooperativa: P-95 (botón WhatsApp), P-96 (asignar/desactivar el asesor de un asociado, sin proceso definido) y P-97 (motivo de rechazo visible en el detalle de afiliación, requiere migración; relacionado con P-69/5.10). Ajuste de estilo pendiente de aplicar en código: franja azul → marco ámbar en /admin/demo (3h) y la corrección «Correo institucional» → «Correo» en 2d (ya hecha en el lienzo).</t>
         </is>
       </c>
     </row>
@@ -57881,22 +57873,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>sesión principal</t>
+          <t>ga-diseno-a-codigo</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>5.3; P-13</t>
+          <t>1.7, 2.14; nuevo 6.16</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Texto de vigilancia de Supersolidaria confirmado</t>
+          <t>Tokens y landing del rediseño C+ llevados a código</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Sebas confirmó que la cooperativa está vigilada por la Supersolidaria; TEXTO_VIGILANCIA (lib/config.ts) pasa de «[Vigilada por Supersolidaria — confirmar]» a «Vigilada por Supersolidaria» en local, con tests/e2e/e-diseno.spec.ts ajustado. P-13 pasa a Hecho; 5.3 actualiza su bloqueo (quedan fotos/cifras/testimonios, nombres de los grados y estado de desembolso). Falta desplegar (commit + merge a main).</t>
+          <t>Tokens del rediseño C+ agregados a app/globals.css y tailwind.config.ts (colores claro/oscuro, radios grandes, sombras, curva «spring», utilidades de movimiento con red de seguridad prefers-reduced-motion), reconciliados con la pieza 3a del lienzo; Bricolage Grotesque (600/800) cargada junto a Manrope en app/layout.tsx. 1.7 pasa a Hecho (tokens en el lienzo y en código). Landing reescrita (components/pantallas/Landing.tsx) siguiendo la pieza 2a: header píldora, hero con comprobante vivo, misión/visión, «Si hoy el banco te dice que no…», servicios, convenios, sedes, footer; dos componentes cliente nuevos MatrizCirculos y ComprobanteSolicitud, sin librerías nuevas. npx tsc --noEmit, npm run lint y npm run build pasan. Nueva actividad 2.14 (Hecho, peso 4, depende de 2.1 y 1.7). Trabajo nuevo: 6.16 (actualizar tests/e2e/e-diseno.spec.ts, tests/e2e/a-navegacion.spec.ts y tests/responsive/logo-y-fotos.spec.ts, que quedaron desactualizados por el cambio de copy y de layout del hero) y pendiente P-93 (confirmar las cifras nuevas de la landing con la cooperativa). ga-disenador-lienzo dejó 3b/3c (ingreso y afiliación en estilo C+) pendientes de maquetar en código (2.15).</t>
         </is>
       </c>
     </row>
@@ -57908,22 +57900,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>ga-verificador-qa</t>
+          <t>ga-disenador-lienzo</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>6.3; nuevos P-84, P-86, P-87</t>
+          <t>1.7, 2.15, 3.10, 4.10, 4.11</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>QA de producción: con observaciones</t>
+          <t>Lienzo C+ ampliado: design system, Ingreso y Afiliación (piezas 3a/3b/3c)</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Playwright en escritorio (1280×800) y celular (390×844) contra www.greenallianceco.com (main, merge 5a3